--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="737">
   <si>
     <t>Order Estimate - (from 1-Jul-2023)</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 15-Feb-26</t>
+    <t>1-Jul-25 to 16-Feb-26</t>
   </si>
   <si>
     <t/>
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA (25/251)</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA (25/262)</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA (25/261)</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA (25/361/861)</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA (25/362/862)</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA (25/282)</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA (25/281)</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC) (2595 PINK)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
+    <t>.1001 PATRIKA</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA (6321)</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA (11043 OFFSET)</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA (1011 OFFSET)</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA (1014 OFFSET)</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA (1222 SBC)</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA (1235)</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA (2101 VV)</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC) (25409)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA (25418)</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA (25322)</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA (25323)</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC) (1173 SBC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC) (5346)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC) (2596)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA (1042)</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA (1043)</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA (GOPAL 11)</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA (GOPAL 1)</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA (2002 YLW)</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA (2003 R)</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA (276-A)</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW (25419)</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED (25420)</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y (25421)</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R (25422)</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA (277-B)</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA (1819 MONARCH)</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN (1709)</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155) (17.02) (1155 JSK)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 (NEW SAVASHREE 52)</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51) (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52) (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53) (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54) (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R) (120 GSM RED)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01) (JCC 01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02) (JCC 02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU) (BP RED)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
+    <t>1010 PATRIKA</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB)</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G)</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L) (16.02) (LEGACY - 09)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA (LEGACY - 10)</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA (LEGACY - 11)</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA (LEGACY - 12)</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA (TUESDAY) (LOTTERY - 80)</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
+    <t>2101 PATRIKA (L)-DC</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (16.02)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (TUESDAY)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -551,1234 +551,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC) (5342)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA (5207)</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA (5206)</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210) (10273/10277)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA (82)</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC) (1129)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC) (101 SBC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA (1102)</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC) (959)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC) (2571)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU) (1351)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA (83)</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA (25-145)</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC) (25-046)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA (111 SBC)</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA (1151 GGN)</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC) (25216)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA (2547)</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC) (25369)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA (25367)</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA (25368)</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA (1031)</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA (25301)</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA (25312 MYRA)</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA (3117)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN) (3116)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA (1173 VV)</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA (5254  RJN)</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA (25402)</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA (10001 NEW)</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA (10002 NEW)</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA (316 MYRA)</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA (25401)</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA (25311)</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA (25312)</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA (5273)</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA (286-A)</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA (1407)</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA (306)</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA (5501)</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA (2011)</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA (25314)</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA (25315)</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU) (1402)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC) (1234*-M)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA (5172)</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA (25313)</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA (BALAJI 5202)</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA (LOTUS 430)</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU) (251 KBC)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU) (273-A)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M) (5087)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA (5295)</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA (5213)</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M) (25/162)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA (25/272)</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC) (25/271)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA (FRIDAY ) (25/171)</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA (8802)</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA (8803)</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC) (7713)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU) (1405)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA (7705)</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA (2522 GE)</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA (2517 GE)</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA (2527)</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA (2536)</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC) (S-301)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU) (S-305)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC) (1103)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी) (741)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA (5347 DIRECT)</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M) (3161)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA (1151 VV)</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC) (25-082)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC) (3701 SBC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA (2081)</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA (296-A (NEHA)</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA (2501 GE NEW)</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA (2520 GE)</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (5267)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA (5258 RJ)</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA (2023)</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC) (2206)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA (25214)</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA (2061 SBC)</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA (5236 RJ)</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC) (1411 KBC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA (5350)</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA (5251)</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA (5240)</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA (25316)</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA (25321)</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M) (857)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU) (5339)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021) (2456)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA (2071)</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA (5261 RJND)</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC) (5335)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA (253-A / 257-A)</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA (5356 RJ)</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (5333)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA (5308)</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC) (AS-402)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC) (5313)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA (5305)</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA (2031)</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU) (3331)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU) (25436)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA (5186)</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC) (7033)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M) (25/122)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC) (8055 VV)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC) (612 VV)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC) (25/072)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC) (2525 /2552)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA (2515)</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (2542)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA (2523)</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M) (7066)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA (1054)</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA (2231)</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA (2232)</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU) (5382)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M) (5283)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC) (25-052)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B (2942-B)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC) (2942)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M) (S-96)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC) (2101)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA (2261)</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA (2353)</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M) (2732)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (2791)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA (718)</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M) (S-32)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU) (2792)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA (5261 NICE)</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M) (5424)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA (5231)</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M) (5004)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G) (5379)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA (2903)</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M) (2952)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA (2312 SBC)</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA (2293)</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-* (2915)</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M) (25358)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA (5387)</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA (175)</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M) (1742-B)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA (1679)</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M) (3002)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M) (S-39)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M) (S-74)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M) (25353)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M) (25351)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA (2205)</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA (25335)</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M) (S-77)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA (2531)</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M) (5808)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA (S-326)</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M) (3471)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA (3211 SBC)</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC) (2202 SBC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M) (S-51)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA (2264)</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M) (25133)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA (3131 SBC)</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M) (2365)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA (2803)</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC) (2931)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M) (226)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M) (2541)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M) (77-B)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC) (25324)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA (2771)</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA (3271)</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M) (6125)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA (242-A)</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC) (3102)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M) (221-A)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA (25442)</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA (25440)</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA (993)</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC) (2373)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M) (1211)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU) (5276)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA (2111)</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU) (7069)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M) (7067)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC) (1131)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC) (15)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M) (25337)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA (064)</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC) (2753)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU) (772)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU) (GOL)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L) (5164)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA (5126)</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA (5111)</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M) (5196)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA (5191)</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R (3023)</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (0523)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA (95)</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M) (3053)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M) (3019)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (3017 VV)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA (3015)</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA (TUESDAY) (25164)</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU) (25131)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M) (3422)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M) (1193)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA (25184)</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M) (25135)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M) (25116)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (25161)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M) (25111)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU) (932)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA (3562)</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M) (S-313)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M) (25183)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA (25162 GE)</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M) (3014)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (2291)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B) (2291-B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M) (25380)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU) (25132)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M) (3031)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M) (3034)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M) (25382)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M) (3402)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC (3431)</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA (3421)</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M) (3461)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M) (5319)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA (25193 (Padding))</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA (25194 (Padding))</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M) (1281)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA (3424)</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA (7103 (PADDING))</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M) (5823)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU) (8102)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU) (6197)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M) (1868-B)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M) (1868)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M) (1872)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M) (6132)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU) (6196)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU) (1503)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M) (1282)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU) (533 KBC)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.) (133)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.) (1522)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.) (1178)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.) (AS-20)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.) (4087)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.) (2204)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.) (2482)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.) (12)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA (25/252)</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA (25/264-263)</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA (25/363/863)</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA (25/283)</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA (25/273)</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA (25/172)</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU) (25895)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA (2521)</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA (2526)</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA (2535)</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA (84)</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA (2543 INV OFFSET)</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA (2234)</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA (S-201 INV)</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA (5121)</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA (720)</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F) (25-146)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA (3702)</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA (254 SBC)</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F) (25-047)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA (2082)</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-* (4052)</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA (2103)</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA (1223 SBC)</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA (6310 GE)</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA (2532)</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA (1174)</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA (1034)</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA (2204 INV)</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA (06)</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA (303)</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA (25323 INV)</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA (25413)</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA (2597)</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA (25896)</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F) (243-C)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA (1855)</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA (1044 SBC)</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA (2014)</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA (2006)</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU) (6106)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA (GOPAL 32)</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA (2005- G)</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA (5180)</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU) (3753)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA (273 NEHA)</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA (278-B)</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
+    <t>4251 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (FRIDAY )</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (TUESDAY)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc'''</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1790,7 +1790,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.) (2498 Cream)</t>
+    <t>9001 CARD (O.C.)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1814,298 +1814,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
-  </si>
-  <si>
-    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
-  </si>
-  <si>
-    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
-  </si>
-  <si>
-    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
-  </si>
-  <si>
-    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9301 CARDS (4242)</t>
-  </si>
-  <si>
-    <t>9302 CARDS (5076)</t>
-  </si>
-  <si>
-    <t>9303 CARDS (5080 Pink)</t>
-  </si>
-  <si>
-    <t>9304 CARDS (5083 Blue)</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070) (4701 Nice)</t>
-  </si>
-  <si>
-    <t>9306 CARDS (0543 Nice)</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M) (5243 Nice)</t>
-  </si>
-  <si>
-    <t>9308 CARDS (9852)</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
-  </si>
-  <si>
-    <t>9310 CARDS (3103)</t>
-  </si>
-  <si>
-    <t>9311 CARDS (3115)</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T) (208 VV)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T) (216)</t>
-  </si>
-  <si>
-    <t>9314 CARDS (P-1)</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU) (P-2)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU) (P-3)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (Aa Gya ) (P-4)</t>
-  </si>
-  <si>
-    <t>9318 CARDS (25905)</t>
-  </si>
-  <si>
-    <t>9319 CARDS (25906)</t>
-  </si>
-  <si>
-    <t>9320 CARDS (S-20)</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9325 CARDS (5229)</t>
-  </si>
-  <si>
-    <t>9326 CARDS (500 18.02) (1601)</t>
-  </si>
-  <si>
-    <t>9327 CARDS (25908)</t>
-  </si>
-  <si>
-    <t>9328 CARDS (2543)</t>
-  </si>
-  <si>
-    <t>9329 CARDS (3606)</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T) (9557)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T) (9560)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC (9847)</t>
-  </si>
-  <si>
-    <t>9333 CARDS (6042)</t>
-  </si>
-  <si>
-    <t>9334 CARDS (10X6 WHITE (2898))</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (2884)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (1635 AP)</t>
-  </si>
-  <si>
-    <t>9338 CARDS (18.02) (1637 AP)</t>
-  </si>
-  <si>
-    <t>9339 CARDS (5361)</t>
-  </si>
-  <si>
-    <t>9340 CARDS (5658)</t>
-  </si>
-  <si>
-    <t>9341 CARDS (5497)</t>
-  </si>
-  <si>
-    <t>9342 CARDS (2861)</t>
-  </si>
-  <si>
-    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu) (689)</t>
-  </si>
-  <si>
-    <t>9345 CARDS (358 KALYANI)</t>
-  </si>
-  <si>
-    <t>9346 CARDS (359)</t>
-  </si>
-  <si>
-    <t>9347 CARDS (2853)</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी) (S-124)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window) (S-120)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T) (1632)</t>
-  </si>
-  <si>
-    <t>9351 Card - B (1603 B)</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) (1603)</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) (1606 AP)</t>
-  </si>
-  <si>
-    <t>9353 CARDS (1618)</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU) (345)</t>
-  </si>
-  <si>
-    <t>9355 CARDS (1624)</t>
-  </si>
-  <si>
-    <t>9356 CARDS (2895/2897)</t>
-  </si>
-  <si>
-    <t>9357 CARDS (2872)</t>
-  </si>
-  <si>
-    <t>9358 CARDS (WHITE PATTA)</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
-  </si>
-  <si>
-    <t>9361 CARDS (25426)</t>
-  </si>
-  <si>
-    <t>9362 CARDS (363)</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T) (1652)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T) (1612)</t>
-  </si>
-  <si>
-    <t>9365 CARDS (25429)</t>
-  </si>
-  <si>
-    <t>9366 CARDS (25427 GOLDEN)</t>
-  </si>
-  <si>
-    <t>9367 CARDS (5652)</t>
-  </si>
-  <si>
-    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
-  </si>
-  <si>
-    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
-  </si>
-  <si>
-    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
-  </si>
-  <si>
-    <t>9371 CARDS (3111 VP)</t>
-  </si>
-  <si>
-    <t>9372 CARDS (9*5 YLW SET (2841))</t>
-  </si>
-  <si>
-    <t>9373 CARDS (1482)</t>
-  </si>
-  <si>
-    <t>9374 CARDS (1485)</t>
-  </si>
-  <si>
-    <t>9375 CARDS (1452 WHITE)</t>
-  </si>
-  <si>
-    <t>9376 CARDS (1529 PRINCE)</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
-  </si>
-  <si>
-    <t>9378 CARDS (2892)</t>
+    <t>9231 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS</t>
+  </si>
+  <si>
+    <t>9240 CARDS</t>
+  </si>
+  <si>
+    <t>9241 CARDS</t>
+  </si>
+  <si>
+    <t>9242 CARDS</t>
+  </si>
+  <si>
+    <t>9243 CARDS</t>
+  </si>
+  <si>
+    <t>9244 CARDS</t>
+  </si>
+  <si>
+    <t>9301 CARDS</t>
+  </si>
+  <si>
+    <t>9302 CARDS</t>
+  </si>
+  <si>
+    <t>9303 CARDS</t>
+  </si>
+  <si>
+    <t>9304 CARDS</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070)</t>
+  </si>
+  <si>
+    <t>9306 CARDS</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M)</t>
+  </si>
+  <si>
+    <t>9308 CARDS</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc)</t>
+  </si>
+  <si>
+    <t>9310 CARDS</t>
+  </si>
+  <si>
+    <t>9311 CARDS</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9314 CARDS</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (Aa Gya )</t>
+  </si>
+  <si>
+    <t>9318 CARDS</t>
+  </si>
+  <si>
+    <t>9319 CARDS</t>
+  </si>
+  <si>
+    <t>9320 CARDS</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD)</t>
+  </si>
+  <si>
+    <t>9324 CARDS</t>
+  </si>
+  <si>
+    <t>9325 CARDS</t>
+  </si>
+  <si>
+    <t>9326 CARDS (500 18.02)</t>
+  </si>
+  <si>
+    <t>9327 CARDS</t>
+  </si>
+  <si>
+    <t>9328 CARDS</t>
+  </si>
+  <si>
+    <t>9329 CARDS</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC</t>
+  </si>
+  <si>
+    <t>9333 CARDS</t>
+  </si>
+  <si>
+    <t>9334 CARDS</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD)</t>
+  </si>
+  <si>
+    <t>9336 CARDS</t>
+  </si>
+  <si>
+    <t>9337 CARDS</t>
+  </si>
+  <si>
+    <t>9338 CARDS (18.02)</t>
+  </si>
+  <si>
+    <t>9339 CARDS</t>
+  </si>
+  <si>
+    <t>9340 CARDS</t>
+  </si>
+  <si>
+    <t>9341 CARDS</t>
+  </si>
+  <si>
+    <t>9342 CARDS</t>
+  </si>
+  <si>
+    <t>9343 CARDS</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu)</t>
+  </si>
+  <si>
+    <t>9345 CARDS</t>
+  </si>
+  <si>
+    <t>9346 CARDS</t>
+  </si>
+  <si>
+    <t>9347 CARDS</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1000 19.02)</t>
+  </si>
+  <si>
+    <t>9351 Card - B</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9353 CARDS</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9355 CARDS</t>
+  </si>
+  <si>
+    <t>9356 CARDS</t>
+  </si>
+  <si>
+    <t>9357 CARDS</t>
+  </si>
+  <si>
+    <t>9358 CARDS</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega</t>
+  </si>
+  <si>
+    <t>9361 CARDS</t>
+  </si>
+  <si>
+    <t>9362 CARDS</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9365 CARDS</t>
+  </si>
+  <si>
+    <t>9366 CARDS</t>
+  </si>
+  <si>
+    <t>9367 CARDS</t>
+  </si>
+  <si>
+    <t>9368 CARDS</t>
+  </si>
+  <si>
+    <t>9369 CARDS</t>
+  </si>
+  <si>
+    <t>9370 CARDS</t>
+  </si>
+  <si>
+    <t>9371 CARDS</t>
+  </si>
+  <si>
+    <t>9372 CARDS</t>
+  </si>
+  <si>
+    <t>9373 CARDS</t>
+  </si>
+  <si>
+    <t>9374 CARDS</t>
+  </si>
+  <si>
+    <t>9375 CARDS</t>
+  </si>
+  <si>
+    <t>9376 CARDS</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9378 CARDS</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2138,19 +2138,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS (9147 RJ)</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU) (118KBC)</t>
+    <t>9389 CARDS</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
+    <t>9*4 ENVELOPE (SBC)</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2174,10 +2174,13 @@
     <t>CHARLA 1967</t>
   </si>
   <si>
+    <t>CHARLA 9286</t>
+  </si>
+  <si>
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
+    <t>FANCY GIFT ENVELOPE-(SR)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2198,37 +2201,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (LX01)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (LX02)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE (LX03)</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (LX04)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (LX05)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE (LX06)</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (LX07)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (LX08)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (LX09)</t>
+    <t>RX-01 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
+    <t>गोल गणेश / गोल फ्लावर</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2755,10 +2758,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E733"/>
+  <dimension ref="A1:E734"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2897,16 +2900,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="25">
-        <v>177.5</v>
+        <v>178.5</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>346.13</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2931,16 +2934,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="25">
-        <v>181</v>
+        <v>174.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3033,16 +3036,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" s="25">
-        <v>-233</v>
+        <v>-247</v>
       </c>
       <c r="D20" s="26">
         <v>0.25</v>
       </c>
       <c r="E20" s="27">
-        <v>-58.25</v>
+        <v>-61.75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3053,13 +3056,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="25">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D21" s="26">
         <v>2.6</v>
       </c>
       <c r="E21" s="27">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -3104,13 +3107,13 @@
         <v>20</v>
       </c>
       <c r="C24" s="25">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3118,16 +3121,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C25" s="25">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>37.950000000000003</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3310,16 +3313,16 @@
         <v>39</v>
       </c>
       <c r="B37" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D37" s="26">
         <v>2.66</v>
       </c>
       <c r="E37" s="27">
-        <v>61.18</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3395,7 +3398,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C42" s="25">
         <v>64</v>
@@ -3480,16 +3483,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C47" s="25">
-        <v>244.5</v>
+        <v>240.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>310.41000000000003</v>
+        <v>305.33</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3497,16 +3500,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C48" s="25">
-        <v>185.5</v>
+        <v>177.5</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>236.38</v>
+        <v>226.19</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3514,16 +3517,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C49" s="25">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>50.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3548,16 +3551,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51" s="25">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>340.2</v>
+        <v>322.2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3565,16 +3568,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C52" s="25">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>122.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3582,16 +3585,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" s="25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3633,16 +3636,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C56" s="25">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>369</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3704,13 +3707,13 @@
         <v>47</v>
       </c>
       <c r="C60" s="25">
-        <v>80.5</v>
+        <v>969.5</v>
       </c>
       <c r="D60" s="26">
-        <v>1.1100000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>89.36</v>
+        <v>1102.8800000000001</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3720,9 +3723,15 @@
       <c r="B61" s="24">
         <v>63</v>
       </c>
-      <c r="C61" s="28"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="28"/>
+      <c r="C61" s="25">
+        <v>1111</v>
+      </c>
+      <c r="D61" s="26">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E61" s="27">
+        <v>1265.81</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
@@ -3746,16 +3755,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C63" s="25">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>120.45</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,16 +3789,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65" s="25">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>562.65</v>
+        <v>559.35</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3797,16 +3806,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66" s="25">
-        <v>81.5</v>
+        <v>76.5</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>134.47999999999999</v>
+        <v>126.23</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,16 +3868,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C70" s="25">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>646.79999999999995</v>
+        <v>610.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3876,16 +3885,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C71" s="25">
-        <v>141</v>
+        <v>105.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>197.4</v>
+        <v>147.69999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3893,16 +3902,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C72" s="25">
-        <v>415.5</v>
+        <v>377</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>581.70000000000005</v>
+        <v>527.79999999999995</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,16 +3919,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C73" s="25">
-        <v>598.5</v>
+        <v>572.5</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>837.9</v>
+        <v>801.5</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3936,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C74" s="25">
-        <v>292.5</v>
+        <v>288.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>351</v>
+        <v>346.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3944,16 +3953,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C75" s="25">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>201.6</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4106,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C84" s="25">
-        <v>1556.5</v>
+        <v>1548.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>2023.45</v>
+        <v>2013.05</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4131,16 +4140,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C86" s="25">
-        <v>1236</v>
+        <v>1221</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2101.1999999999998</v>
+        <v>2075.6999999999998</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4148,16 +4157,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C87" s="25">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1463.7</v>
+        <v>1446.7</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4165,16 +4174,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C88" s="25">
-        <v>1086.5</v>
+        <v>1076.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1847.05</v>
+        <v>1830.05</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4191,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C89" s="25">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D89" s="26">
         <v>1.44</v>
       </c>
       <c r="E89" s="27">
-        <v>279.45</v>
+        <v>267.92</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4216,16 +4225,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C91" s="25">
-        <v>-40</v>
+        <v>80</v>
       </c>
       <c r="D91" s="26">
-        <v>0.66</v>
+        <v>1.04</v>
       </c>
       <c r="E91" s="27">
-        <v>-26.59</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4233,16 +4242,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C92" s="25">
-        <v>596.5</v>
+        <v>576.5</v>
       </c>
       <c r="D92" s="26">
         <v>1.76</v>
       </c>
       <c r="E92" s="27">
-        <v>1052.48</v>
+        <v>1017.19</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4274,16 +4283,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C95" s="25">
-        <v>484.5</v>
+        <v>474.5</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>436.05</v>
+        <v>427.05</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4291,16 +4300,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C96" s="25">
-        <v>205.5</v>
+        <v>183.5</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>184.95</v>
+        <v>165.15</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4308,16 +4317,16 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C97" s="25">
-        <v>43.5</v>
+        <v>33.5</v>
       </c>
       <c r="D97" s="26">
         <v>0.9</v>
       </c>
       <c r="E97" s="27">
-        <v>39.15</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4419,16 +4428,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C104" s="25">
-        <v>260</v>
+        <v>246.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>650</v>
+        <v>616.25</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4436,16 +4445,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C105" s="25">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>942.5</v>
+        <v>917.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4453,16 +4462,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C106" s="25">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4470,16 +4479,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C107" s="25">
-        <v>389.5</v>
+        <v>379.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>973.75</v>
+        <v>948.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4487,16 +4496,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C108" s="25">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>950</v>
+        <v>925</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4504,10 +4513,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C109" s="25">
-        <v>142.5</v>
+        <v>134.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4517,10 +4526,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="25">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4606,7 +4615,9 @@
         <v>119</v>
       </c>
       <c r="B117" s="24"/>
-      <c r="C117" s="28"/>
+      <c r="C117" s="25">
+        <v>101</v>
+      </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
     </row>
@@ -4615,16 +4626,16 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C118" s="25">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D118" s="26">
         <v>0.7</v>
       </c>
       <c r="E118" s="27">
-        <v>60.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4678,10 +4689,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C123" s="25">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -4797,16 +4808,16 @@
         <v>134</v>
       </c>
       <c r="B132" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C132" s="25">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>181.25</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4865,16 +4876,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C136" s="25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4902,13 +4913,13 @@
         <v>36</v>
       </c>
       <c r="C138" s="25">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D138" s="26">
         <v>12.78</v>
       </c>
       <c r="E138" s="27">
-        <v>95.83</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5282,16 +5293,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C161" s="25">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="D161" s="26">
         <v>11.5</v>
       </c>
       <c r="E161" s="27">
-        <v>166.75</v>
+        <v>120.75</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5316,16 +5327,16 @@
         <v>165</v>
       </c>
       <c r="B163" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C163" s="25">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="D163" s="26">
         <v>11.5</v>
       </c>
       <c r="E163" s="27">
-        <v>178.25</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -5431,16 +5442,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C170" s="25">
-        <v>-226.5</v>
+        <v>-231.5</v>
       </c>
       <c r="D170" s="26">
         <v>1.3</v>
       </c>
       <c r="E170" s="27">
-        <v>-294.45</v>
+        <v>-300.95</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5527,16 +5538,16 @@
         <v>178</v>
       </c>
       <c r="B176" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C176" s="25">
-        <v>59.5</v>
+        <v>57.5</v>
       </c>
       <c r="D176" s="26">
         <v>2.7</v>
       </c>
       <c r="E176" s="27">
-        <v>160.65</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -5587,16 +5598,16 @@
         <v>182</v>
       </c>
       <c r="B180" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C180" s="25">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D180" s="26">
         <v>2.8</v>
       </c>
       <c r="E180" s="27">
-        <v>204.63</v>
+        <v>201.83</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -5638,16 +5649,16 @@
         <v>185</v>
       </c>
       <c r="B183" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C183" s="25">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D183" s="26">
         <v>3.33</v>
       </c>
       <c r="E183" s="27">
-        <v>103.23</v>
+        <v>99.9</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5711,16 +5722,16 @@
         <v>190</v>
       </c>
       <c r="B188" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C188" s="25">
-        <v>25.5</v>
+        <v>24</v>
       </c>
       <c r="D188" s="26">
         <v>2.76</v>
       </c>
       <c r="E188" s="27">
-        <v>70.430000000000007</v>
+        <v>66.290000000000006</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -5773,16 +5784,16 @@
         <v>194</v>
       </c>
       <c r="B192" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C192" s="25">
-        <v>26</v>
+        <v>24.5</v>
       </c>
       <c r="D192" s="26">
         <v>3.56</v>
       </c>
       <c r="E192" s="27">
-        <v>92.56</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -5875,16 +5886,16 @@
         <v>200</v>
       </c>
       <c r="B198" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C198" s="25">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="D198" s="26">
         <v>4.5</v>
       </c>
       <c r="E198" s="27">
-        <v>229.5</v>
+        <v>222.75</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -6175,16 +6186,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C216" s="25">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D216" s="26">
         <v>3</v>
       </c>
       <c r="E216" s="27">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6243,16 +6254,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C220" s="25">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D220" s="26">
         <v>3.62</v>
       </c>
       <c r="E220" s="27">
-        <v>151.96</v>
+        <v>141.11000000000001</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6260,16 +6271,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C221" s="25">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="D221" s="26">
         <v>2.7</v>
       </c>
       <c r="E221" s="27">
-        <v>128.25</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6617,16 +6628,16 @@
         <v>246</v>
       </c>
       <c r="B244" s="24">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C244" s="25">
-        <v>79.900000000000006</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="D244" s="26">
         <v>6.3</v>
       </c>
       <c r="E244" s="27">
-        <v>503.37</v>
+        <v>430.92</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6634,16 +6645,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C245" s="25">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="D245" s="26">
         <v>3</v>
       </c>
       <c r="E245" s="27">
-        <v>213</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6679,16 +6690,16 @@
         <v>250</v>
       </c>
       <c r="B248" s="24">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C248" s="25">
-        <v>89</v>
+        <v>82.5</v>
       </c>
       <c r="D248" s="26">
         <v>3.9</v>
       </c>
       <c r="E248" s="27">
-        <v>347.1</v>
+        <v>321.75</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -6696,16 +6707,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C249" s="25">
-        <v>194.5</v>
+        <v>188.5</v>
       </c>
       <c r="D249" s="26">
         <v>3.9</v>
       </c>
       <c r="E249" s="27">
-        <v>758.55</v>
+        <v>735.15</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6848,16 +6859,16 @@
         <v>261</v>
       </c>
       <c r="B259" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C259" s="25">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D259" s="26">
         <v>5.75</v>
       </c>
       <c r="E259" s="27">
-        <v>86.25</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -6910,16 +6921,16 @@
         <v>265</v>
       </c>
       <c r="B263" s="24">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C263" s="25">
-        <v>356.5</v>
+        <v>349.5</v>
       </c>
       <c r="D263" s="26">
         <v>4.28</v>
       </c>
       <c r="E263" s="27">
-        <v>1525.82</v>
+        <v>1495.86</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -6972,16 +6983,16 @@
         <v>269</v>
       </c>
       <c r="B267" s="24">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C267" s="25">
-        <v>40.5</v>
+        <v>37</v>
       </c>
       <c r="D267" s="26">
         <v>3.1</v>
       </c>
       <c r="E267" s="27">
-        <v>125.55</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -7000,16 +7011,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C269" s="25">
-        <v>30.5</v>
+        <v>29.5</v>
       </c>
       <c r="D269" s="26">
         <v>4.5</v>
       </c>
       <c r="E269" s="27">
-        <v>137.25</v>
+        <v>132.75</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7158,16 +7169,16 @@
         <v>281</v>
       </c>
       <c r="B279" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C279" s="25">
-        <v>159.5</v>
+        <v>158.5</v>
       </c>
       <c r="D279" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E279" s="27">
-        <v>773.07</v>
+        <v>768.22</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7197,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C281" s="25">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D281" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E281" s="27">
-        <v>453.7</v>
+        <v>434.8</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7339,16 +7350,16 @@
         <v>292</v>
       </c>
       <c r="B290" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C290" s="25">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D290" s="26">
         <v>4.5</v>
       </c>
       <c r="E290" s="27">
-        <v>544.5</v>
+        <v>499.5</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7356,16 +7367,16 @@
         <v>293</v>
       </c>
       <c r="B291" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C291" s="25">
-        <v>33</v>
+        <v>30.5</v>
       </c>
       <c r="D291" s="26">
         <v>3.8</v>
       </c>
       <c r="E291" s="27">
-        <v>125.4</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -7424,16 +7435,16 @@
         <v>297</v>
       </c>
       <c r="B295" s="24">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C295" s="25">
-        <v>290.5</v>
+        <v>289</v>
       </c>
       <c r="D295" s="26">
         <v>6.06</v>
       </c>
       <c r="E295" s="27">
-        <v>1761.33</v>
+        <v>1752.3</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7526,16 +7537,16 @@
         <v>303</v>
       </c>
       <c r="B301" s="24">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C301" s="25">
-        <v>110.25</v>
+        <v>103.25</v>
       </c>
       <c r="D301" s="26">
         <v>4.3</v>
       </c>
       <c r="E301" s="27">
-        <v>473.77</v>
+        <v>443.69</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7577,16 +7588,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C304" s="25">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="D304" s="26">
         <v>5.13</v>
       </c>
       <c r="E304" s="27">
-        <v>205.2</v>
+        <v>197.51</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -7955,16 +7966,16 @@
         <v>330</v>
       </c>
       <c r="B328" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C328" s="25">
-        <v>135.41</v>
+        <v>130.41</v>
       </c>
       <c r="D328" s="26">
         <v>4.28</v>
       </c>
       <c r="E328" s="27">
-        <v>579.54999999999995</v>
+        <v>558.15</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -7972,16 +7983,16 @@
         <v>331</v>
       </c>
       <c r="B329" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C329" s="25">
-        <v>171.5</v>
+        <v>170</v>
       </c>
       <c r="D329" s="26">
         <v>4.28</v>
       </c>
       <c r="E329" s="27">
-        <v>734.02</v>
+        <v>727.6</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -8275,16 +8286,16 @@
         <v>350</v>
       </c>
       <c r="B348" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C348" s="25">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D348" s="26">
         <v>5.7</v>
       </c>
       <c r="E348" s="27">
-        <v>108.3</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -8675,16 +8686,16 @@
         <v>374</v>
       </c>
       <c r="B372" s="24">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C372" s="25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D372" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E372" s="27">
-        <v>41</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -9015,16 +9026,16 @@
         <v>394</v>
       </c>
       <c r="B392" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C392" s="25">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="D392" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E392" s="27">
-        <v>-78.3</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -9126,16 +9137,16 @@
         <v>401</v>
       </c>
       <c r="B399" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C399" s="25">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D399" s="26">
         <v>6.4</v>
       </c>
       <c r="E399" s="27">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -9154,16 +9165,16 @@
         <v>403</v>
       </c>
       <c r="B401" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C401" s="25">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D401" s="26">
         <v>6.65</v>
       </c>
       <c r="E401" s="27">
-        <v>86.45</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9242,16 +9253,16 @@
         <v>409</v>
       </c>
       <c r="B407" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C407" s="25">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D407" s="26">
         <v>7.13</v>
       </c>
       <c r="E407" s="27">
-        <v>178.25</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -9387,16 +9398,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C416" s="25">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="D416" s="26">
         <v>6.19</v>
       </c>
       <c r="E416" s="27">
-        <v>266.3</v>
+        <v>257.01</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -9533,16 +9544,16 @@
         <v>428</v>
       </c>
       <c r="B426" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C426" s="25">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="D426" s="26">
         <v>8.35</v>
       </c>
       <c r="E426" s="27">
-        <v>246.2</v>
+        <v>237.85</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -9685,16 +9696,16 @@
         <v>438</v>
       </c>
       <c r="B436" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C436" s="25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D436" s="26">
         <v>16</v>
       </c>
       <c r="E436" s="27">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -9881,16 +9892,16 @@
         <v>450</v>
       </c>
       <c r="B448" s="24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C448" s="25">
-        <v>-9.5</v>
+        <v>-2</v>
       </c>
       <c r="D448" s="26">
         <v>10.5</v>
       </c>
       <c r="E448" s="27">
-        <v>-99.75</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -10290,16 +10301,16 @@
         <v>475</v>
       </c>
       <c r="B473" s="24">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C473" s="25">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="D473" s="26">
         <v>9.5</v>
       </c>
       <c r="E473" s="27">
-        <v>147.25</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -10452,16 +10463,16 @@
         <v>485</v>
       </c>
       <c r="B483" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C483" s="25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D483" s="26">
         <v>13</v>
       </c>
       <c r="E483" s="27">
-        <v>182</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -10548,16 +10559,16 @@
         <v>491</v>
       </c>
       <c r="B489" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C489" s="25">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D489" s="26">
         <v>10.45</v>
       </c>
       <c r="E489" s="27">
-        <v>135.85</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -10689,16 +10700,16 @@
         <v>500</v>
       </c>
       <c r="B498" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C498" s="25">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="D498" s="26">
         <v>9</v>
       </c>
       <c r="E498" s="27">
-        <v>180</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -11118,16 +11129,16 @@
         <v>527</v>
       </c>
       <c r="B525" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C525" s="25">
-        <v>113.5</v>
+        <v>110.5</v>
       </c>
       <c r="D525" s="26">
         <v>1.4</v>
       </c>
       <c r="E525" s="27">
-        <v>158.9</v>
+        <v>154.69999999999999</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -11169,16 +11180,16 @@
         <v>530</v>
       </c>
       <c r="B528" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C528" s="25">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D528" s="26">
         <v>1.95</v>
       </c>
       <c r="E528" s="27">
-        <v>105.3</v>
+        <v>103.35</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11624,16 +11635,16 @@
         <v>557</v>
       </c>
       <c r="B555" s="24">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C555" s="25">
-        <v>102.7</v>
+        <v>96.7</v>
       </c>
       <c r="D555" s="26">
         <v>3.9</v>
       </c>
       <c r="E555" s="27">
-        <v>400.53</v>
+        <v>377.13</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -11811,16 +11822,16 @@
         <v>568</v>
       </c>
       <c r="B566" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C566" s="25">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D566" s="26">
         <v>3.5</v>
       </c>
       <c r="E566" s="27">
-        <v>82.25</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
@@ -12101,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="C583" s="25">
-        <v>-100</v>
+        <v>1</v>
       </c>
       <c r="D583" s="29"/>
       <c r="E583" s="28"/>
@@ -12114,7 +12125,7 @@
         <v>1</v>
       </c>
       <c r="C584" s="25">
-        <v>-50</v>
+        <v>9</v>
       </c>
       <c r="D584" s="29"/>
       <c r="E584" s="28"/>
@@ -12154,9 +12165,11 @@
         <v>589</v>
       </c>
       <c r="B587" s="24">
-        <v>121</v>
-      </c>
-      <c r="C587" s="28"/>
+        <v>122</v>
+      </c>
+      <c r="C587" s="25">
+        <v>382.5</v>
+      </c>
       <c r="D587" s="29"/>
       <c r="E587" s="28"/>
     </row>
@@ -12207,7 +12220,7 @@
         <v>49</v>
       </c>
       <c r="C591" s="25">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12217,16 +12230,16 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C592" s="25">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="D592" s="26">
         <v>0.87</v>
       </c>
       <c r="E592" s="27">
-        <v>157.47</v>
+        <v>387.15</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
@@ -12234,16 +12247,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C593" s="25">
-        <v>817</v>
+        <v>787</v>
       </c>
       <c r="D593" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E593" s="27">
-        <v>473.86</v>
+        <v>456.46</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -12251,16 +12264,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C594" s="25">
-        <v>749.5</v>
+        <v>739.5</v>
       </c>
       <c r="D594" s="26">
         <v>0.85</v>
       </c>
       <c r="E594" s="27">
-        <v>637.08000000000004</v>
+        <v>628.58000000000004</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12279,16 +12292,16 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C596" s="25">
-        <v>229.5</v>
+        <v>219.5</v>
       </c>
       <c r="D596" s="26">
         <v>0.85</v>
       </c>
       <c r="E596" s="27">
-        <v>195.08</v>
+        <v>186.58</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -12365,10 +12378,10 @@
         <v>604</v>
       </c>
       <c r="B602" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C602" s="25">
-        <v>216</v>
+        <v>106</v>
       </c>
       <c r="D602" s="29"/>
       <c r="E602" s="28"/>
@@ -12603,13 +12616,13 @@
         <v>13</v>
       </c>
       <c r="C617" s="25">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="D617" s="26">
         <v>5.5</v>
       </c>
       <c r="E617" s="27">
-        <v>68.75</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
@@ -12719,16 +12732,16 @@
         <v>626</v>
       </c>
       <c r="B624" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C624" s="25">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="D624" s="26">
         <v>6.5</v>
       </c>
       <c r="E624" s="27">
-        <v>107.25</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -12855,16 +12868,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C632" s="25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D632" s="26">
         <v>1.5</v>
       </c>
       <c r="E632" s="27">
-        <v>16.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12906,16 +12919,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C635" s="25">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D635" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E635" s="27">
-        <v>127.68</v>
+        <v>123.12</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -12974,16 +12987,16 @@
         <v>641</v>
       </c>
       <c r="B639" s="24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C639" s="25">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="D639" s="26">
         <v>3</v>
       </c>
       <c r="E639" s="27">
-        <v>49.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -12991,16 +13004,16 @@
         <v>642</v>
       </c>
       <c r="B640" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C640" s="25">
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
       <c r="D640" s="26">
         <v>4.6500000000000004</v>
       </c>
       <c r="E640" s="27">
-        <v>132.53</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
@@ -13008,16 +13021,16 @@
         <v>643</v>
       </c>
       <c r="B641" s="24">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C641" s="25">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="D641" s="26">
         <v>5</v>
       </c>
       <c r="E641" s="27">
-        <v>82.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -13104,16 +13117,16 @@
         <v>649</v>
       </c>
       <c r="B647" s="24">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C647" s="25">
-        <v>162.86000000000001</v>
+        <v>161.86000000000001</v>
       </c>
       <c r="D647" s="26">
         <v>1.7</v>
       </c>
       <c r="E647" s="27">
-        <v>276.86</v>
+        <v>275.16000000000003</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -13186,13 +13199,13 @@
         <v>13</v>
       </c>
       <c r="C652" s="25">
-        <v>-1.5</v>
+        <v>3.5</v>
       </c>
       <c r="D652" s="26">
         <v>8.75</v>
       </c>
       <c r="E652" s="27">
-        <v>-13.13</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13217,16 +13230,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C654" s="25">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D654" s="26">
         <v>2.85</v>
       </c>
       <c r="E654" s="27">
-        <v>259.35000000000002</v>
+        <v>253.65</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13279,16 +13292,16 @@
         <v>660</v>
       </c>
       <c r="B658" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C658" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D658" s="26">
         <v>5.5</v>
       </c>
       <c r="E658" s="27">
-        <v>22</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
@@ -13296,16 +13309,16 @@
         <v>661</v>
       </c>
       <c r="B659" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C659" s="25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D659" s="26">
         <v>3.1</v>
       </c>
       <c r="E659" s="27">
-        <v>65.099999999999994</v>
+        <v>62</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -13466,16 +13479,16 @@
         <v>671</v>
       </c>
       <c r="B669" s="24">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C669" s="25">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D669" s="26">
         <v>3.1</v>
       </c>
       <c r="E669" s="27">
-        <v>173.6</v>
+        <v>130.19999999999999</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13534,16 +13547,16 @@
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C673" s="25">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="D673" s="26">
         <v>3.75</v>
       </c>
       <c r="E673" s="27">
-        <v>65.63</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13602,16 +13615,16 @@
         <v>679</v>
       </c>
       <c r="B677" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C677" s="25">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="D677" s="26">
         <v>5.8</v>
       </c>
       <c r="E677" s="27">
-        <v>95.7</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -13893,7 +13906,7 @@
         <v>10</v>
       </c>
       <c r="C695" s="25">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="D695" s="29"/>
       <c r="E695" s="28"/>
@@ -13903,10 +13916,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C696" s="25">
-        <v>14.5</v>
+        <v>62.5</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13932,7 +13945,7 @@
         <v>69</v>
       </c>
       <c r="C698" s="25">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D698" s="29"/>
       <c r="E698" s="28"/>
@@ -13942,10 +13955,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C699" s="25">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -14120,22 +14133,26 @@
         <v>715</v>
       </c>
       <c r="B713" s="24">
-        <v>2</v>
-      </c>
-      <c r="C713" s="28"/>
-      <c r="D713" s="29"/>
-      <c r="E713" s="28"/>
+        <v>3</v>
+      </c>
+      <c r="C713" s="25">
+        <v>-0.5</v>
+      </c>
+      <c r="D713" s="26">
+        <v>18</v>
+      </c>
+      <c r="E713" s="27">
+        <v>-9</v>
+      </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" s="23" t="s">
         <v>716</v>
       </c>
       <c r="B714" s="24">
-        <v>2</v>
-      </c>
-      <c r="C714" s="25">
-        <v>-0.02</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C714" s="28"/>
       <c r="D714" s="29"/>
       <c r="E714" s="28"/>
     </row>
@@ -14144,37 +14161,37 @@
         <v>717</v>
       </c>
       <c r="B715" s="24">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C715" s="25">
-        <v>-96.4</v>
-      </c>
-      <c r="D715" s="26">
-        <v>1.6</v>
-      </c>
-      <c r="E715" s="27">
-        <v>-154.24</v>
-      </c>
+        <v>-0.02</v>
+      </c>
+      <c r="D715" s="29"/>
+      <c r="E715" s="28"/>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" s="23" t="s">
         <v>718</v>
       </c>
-      <c r="B716" s="24"/>
-      <c r="C716" s="28"/>
-      <c r="D716" s="29"/>
-      <c r="E716" s="28"/>
+      <c r="B716" s="24">
+        <v>15</v>
+      </c>
+      <c r="C716" s="25">
+        <v>-104.4</v>
+      </c>
+      <c r="D716" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="E716" s="27">
+        <v>-167.04</v>
+      </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" s="23" t="s">
         <v>719</v>
       </c>
-      <c r="B717" s="24">
-        <v>18</v>
-      </c>
-      <c r="C717" s="25">
-        <v>176</v>
-      </c>
+      <c r="B717" s="24"/>
+      <c r="C717" s="28"/>
       <c r="D717" s="29"/>
       <c r="E717" s="28"/>
     </row>
@@ -14183,10 +14200,10 @@
         <v>720</v>
       </c>
       <c r="B718" s="24">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C718" s="25">
-        <v>-0.42</v>
+        <v>176</v>
       </c>
       <c r="D718" s="29"/>
       <c r="E718" s="28"/>
@@ -14196,10 +14213,10 @@
         <v>721</v>
       </c>
       <c r="B719" s="24">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C719" s="25">
-        <v>-0.77</v>
+        <v>-0.42</v>
       </c>
       <c r="D719" s="29"/>
       <c r="E719" s="28"/>
@@ -14209,39 +14226,41 @@
         <v>722</v>
       </c>
       <c r="B720" s="24">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C720" s="25">
-        <v>-158</v>
-      </c>
-      <c r="D720" s="26">
-        <v>1</v>
-      </c>
-      <c r="E720" s="27">
-        <v>-158</v>
-      </c>
+        <v>-0.77</v>
+      </c>
+      <c r="D720" s="29"/>
+      <c r="E720" s="28"/>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" s="23" t="s">
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C721" s="25">
-        <v>-87.65</v>
-      </c>
-      <c r="D721" s="29"/>
-      <c r="E721" s="28"/>
+        <v>-158</v>
+      </c>
+      <c r="D721" s="26">
+        <v>1</v>
+      </c>
+      <c r="E721" s="27">
+        <v>-158</v>
+      </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" s="23" t="s">
         <v>724</v>
       </c>
       <c r="B722" s="24">
-        <v>25</v>
-      </c>
-      <c r="C722" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="C722" s="25">
+        <v>-87.65</v>
+      </c>
       <c r="D722" s="29"/>
       <c r="E722" s="28"/>
     </row>
@@ -14250,33 +14269,27 @@
         <v>725</v>
       </c>
       <c r="B723" s="24">
-        <v>38</v>
-      </c>
-      <c r="C723" s="25">
-        <v>15.75</v>
-      </c>
-      <c r="D723" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E723" s="27">
-        <v>39.380000000000003</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C723" s="28"/>
+      <c r="D723" s="29"/>
+      <c r="E723" s="28"/>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724" s="23" t="s">
         <v>726</v>
       </c>
       <c r="B724" s="24">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="C724" s="25">
-        <v>30.75</v>
+        <v>15.75</v>
       </c>
       <c r="D724" s="26">
         <v>2.5</v>
       </c>
       <c r="E724" s="27">
-        <v>76.88</v>
+        <v>39.380000000000003</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
@@ -14284,16 +14297,16 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C725" s="25">
-        <v>12</v>
+        <v>30.75</v>
       </c>
       <c r="D725" s="26">
         <v>2.5</v>
       </c>
       <c r="E725" s="27">
-        <v>30</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
@@ -14301,16 +14314,16 @@
         <v>728</v>
       </c>
       <c r="B726" s="24">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C726" s="25">
-        <v>20.25</v>
+        <v>10</v>
       </c>
       <c r="D726" s="26">
         <v>2.5</v>
       </c>
       <c r="E726" s="27">
-        <v>50.63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
@@ -14318,16 +14331,16 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C727" s="25">
-        <v>4.75</v>
+        <v>18.25</v>
       </c>
       <c r="D727" s="26">
         <v>2.5</v>
       </c>
       <c r="E727" s="27">
-        <v>11.88</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -14335,16 +14348,16 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C728" s="25">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="D728" s="26">
         <v>2.5</v>
       </c>
       <c r="E728" s="27">
-        <v>6.25</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -14352,16 +14365,16 @@
         <v>731</v>
       </c>
       <c r="B729" s="24">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C729" s="25">
-        <v>53.25</v>
+        <v>2.5</v>
       </c>
       <c r="D729" s="26">
         <v>2.5</v>
       </c>
       <c r="E729" s="27">
-        <v>133.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
@@ -14369,16 +14382,16 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C730" s="25">
-        <v>49.25</v>
+        <v>53.25</v>
       </c>
       <c r="D730" s="26">
         <v>2.5</v>
       </c>
       <c r="E730" s="27">
-        <v>123.13</v>
+        <v>133.13</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -14386,16 +14399,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="C731" s="25">
-        <v>-87</v>
+        <v>42.25</v>
       </c>
       <c r="D731" s="26">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>-65.25</v>
+        <v>105.63</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14403,25 +14416,42 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>157</v>
+        <v>11</v>
       </c>
       <c r="C732" s="25">
-        <v>-463.5</v>
-      </c>
-      <c r="D732" s="29"/>
-      <c r="E732" s="28"/>
+        <v>-87</v>
+      </c>
+      <c r="D732" s="26">
+        <v>0.75</v>
+      </c>
+      <c r="E732" s="27">
+        <v>-65.25</v>
+      </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A733" s="30" t="s">
+      <c r="A733" s="23" t="s">
         <v>735</v>
       </c>
-      <c r="B733" s="31"/>
-      <c r="C733" s="32">
-        <v>41934.57</v>
-      </c>
-      <c r="D733" s="33"/>
-      <c r="E733" s="34">
-        <v>103929.03</v>
+      <c r="B733" s="24">
+        <v>160</v>
+      </c>
+      <c r="C733" s="25">
+        <v>-469.5</v>
+      </c>
+      <c r="D733" s="29"/>
+      <c r="E733" s="28"/>
+    </row>
+    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A734" s="30" t="s">
+        <v>736</v>
+      </c>
+      <c r="B734" s="31"/>
+      <c r="C734" s="32">
+        <v>44302.559999999998</v>
+      </c>
+      <c r="D734" s="33"/>
+      <c r="E734" s="34">
+        <v>105034.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 17-Feb-26</t>
+    <t>1-Jul-25 to 31-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA (25/251)</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA (25/262)</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA (25/261)</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA (25/361/861)</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA (25/362/862)</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA (25/282)</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA (25/281)</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC) (2595 PINK)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
+    <t>.1001 PATRIKA</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA (6321)</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA (11043 OFFSET)</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA (1011 OFFSET)</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA (1014 OFFSET)</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA (1222 SBC)</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA (1235)</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA (2101 VV)</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC) (25409)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA (25418)</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA (25322)</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA (25323)</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC) (1173 SBC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC) (5346)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC) (2596)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA (1042)</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA (1043)</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA (GOPAL 11)</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA (GOPAL 1)</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA (2002 YLW)</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA (2003 R)</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA (276-A)</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW (25419)</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED (25420)</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y (25421)</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R (25422)</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA (277-B)</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA (1819 MONARCH)</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN (1709)</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155) (1155 JSK)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 (NEW SAVASHREE 52)</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51) (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52) (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53) (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54) (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R) (120 GSM RED)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01) (JCC 01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02) (JCC 02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU) (BP RED)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
+    <t>1010 PATRIKA</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB)</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G)</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L) (16.02) (LEGACY - 09)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA (LEGACY - 10)</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA (LEGACY - 11)</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA (LEGACY - 12)</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA (TUESDAY) (LOTTERY - 80)</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
+    <t>2101 PATRIKA (L)-DC</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (16.02)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (TUESDAY)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -551,1234 +551,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC) (5342)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA (5207)</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA (5206)</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210) (10273/10277)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA (82)</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC) (1129)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC) (101 SBC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA (1102)</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC) (959)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC) (2571)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU) (1351)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA (83)</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA (25-145)</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC) (25-046)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA (111 SBC)</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA (1151 GGN)</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC) (25216)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA (2547)</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC) (25369)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA (25367)</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA (25368)</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA (1031)</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA (25301)</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA (25312 MYRA)</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA (3117)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN) (3116)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA (1173 VV)</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA (5254  RJN)</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA (25402)</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA (10001 NEW)</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA (10002 NEW)</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA (316 MYRA)</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA (25401)</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA (25311)</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA (25312)</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA (5273)</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA (286-A)</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA (1407)</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA (306)</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA (5501)</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA (2011)</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA (25314)</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA (25315)</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU) (1402)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC) (1234*-M)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA (5172)</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA (25313)</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA (BALAJI 5202)</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA (LOTUS 430)</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU) (251 KBC)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU) (273-A)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M) (5087)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA (5295)</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA (5213)</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M) (25/162)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA (25/272)</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC) (25/271)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA (FRIDAY ) (25/171)</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA (8802)</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA (8803)</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC) (7713)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU) (1405)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA (7705)</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA (2522 GE)</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA (2517 GE)</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA (2527)</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA (2536)</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC) (S-301)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU) (S-305)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC) (1103)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी) (741)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA (5347 DIRECT)</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M) (3161)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA (1151 VV)</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC) (25-082)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC) (3701 SBC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA (2081)</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA (296-A (NEHA)</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA (2501 GE NEW)</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA (2520 GE)</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (5267)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA (5258 RJ)</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA (2023)</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC) (2206)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA (25214)</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA (2061 SBC)</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA (5236 RJ)</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC) (1411 KBC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA (5350)</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA (5251)</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA (5240)</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA (25316)</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA (25321)</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M) (857)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU) (5339)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021) (2456)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA (2071)</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA (5261 RJND)</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC) (5335)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA (253-A / 257-A)</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA (5356 RJ)</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (5333)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA (5308)</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC) (AS-402)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC) (5313)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA (5305)</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA (2031)</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU) (3331)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU) (25436)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA (5186)</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC) (7033)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M) (25/122)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC) (8055 VV)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC) (612 VV)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC) (25/072)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC) (2525 /2552)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA (2515)</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU) (2542)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA (2523)</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M) (7066)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA (1054)</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA (2231)</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA (2232)</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU) (5382)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M) (5283)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC) (25-052)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B (2942-B)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC) (2942)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M) (S-96)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC) (2101)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA (2261)</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA (2353)</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M) (2732)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA (718)</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M) (S-32)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU) (2792)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA (5261 NICE)</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M) (5424)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA (5231)</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M) (5004)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G) (5379)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA (2903)</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M) (2952)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA (2312 SBC)</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA (2293)</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-* (2915)</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M) (25358)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA (5387)</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA (175)</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M) (1742-B)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA (1679)</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M) (3002)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M) (S-39)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M) (S-74)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M) (25353)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M) (25351)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA (2205)</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA (25335)</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M) (S-77)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA (2531)</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M) (5808)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA (S-326)</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M) (3471)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA (3211 SBC)</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC) (2202 SBC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M) (S-51)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA (2264)</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M) (25133)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA (3131 SBC)</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M) (2365)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA (2803)</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC) (2931)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M) (226)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M) (2541)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M) (77-B)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC) (25324)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA (2771)</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA (3271)</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M) (6125)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA (242-A)</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC) (3102)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M) (221-A)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA (25442)</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA (25440)</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA (993)</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC) (2373)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M) (1211)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU) (5276)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA (2111)</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU) (7069)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M) (7067)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC) (1131)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC) (15)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M) (25337)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA (064)</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC) (2753)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU) (772)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU) (GOL)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L) (5164)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA (5126)</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA (5111)</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M) (5196)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA (5191)</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R (3023)</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (0523)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA (95)</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M) (3053)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M) (3019)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC) (3017 VV)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA (3015)</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA (TUESDAY) (25164)</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU) (25131)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M) (3422)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M) (1193)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA (25184)</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M) (25135)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M) (25116)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (25161)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M) (25111)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU) (932)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA (3562)</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M) (S-313)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M) (25183)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA (25162 GE)</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M) (3014)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (2291)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B) (2291-B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M) (25380)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU) (25132)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M) (3031)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M) (3034)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M) (25382)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M) (3402)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC (3431)</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA (3421)</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M) (3461)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M) (5319)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA (25193 (Padding))</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA (25194 (Padding))</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M) (1281)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA (3424)</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA (7103 (PADDING))</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M) (5823)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU) (8102)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU) (6197)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M) (1868-B)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M) (1868)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M) (1872)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M) (6132)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU) (6196)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU) (1503)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M) (1282)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU) (533 KBC)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.) (133)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.) (1522)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.) (1178)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.) (AS-20)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.) (4087)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.) (2204)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.) (2482)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.) (12)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA (25/252)</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA (25/264-263)</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA (25/363/863)</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA (25/283)</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA (25/273)</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA (25/172)</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU) (25895)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA (2521)</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA (2526)</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA (2535)</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA (84)</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA (2543 INV OFFSET)</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA (2234)</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA (S-201 INV)</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA (5121)</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA (720)</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F) (25-146)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA (3702)</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA (254 SBC)</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F) (25-047)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA (2082)</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-* (4052)</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA (2103)</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA (1223 SBC)</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA (6310 GE)</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA (2532)</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA (1174)</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA (1034)</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA (2204 INV)</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA (06)</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA (303)</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA (25323 INV)</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA (25413)</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA (2597)</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA (25896)</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F) (243-C)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA (1855)</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA (1044 SBC)</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA (2014)</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA (2006)</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU) (6106)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA (GOPAL 32)</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA (2005- G)</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA (5180)</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU) (3753)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA (273 NEHA)</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA (278-B)</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
+    <t>4251 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (FRIDAY )</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (TUESDAY)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc'''</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1790,7 +1790,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.) (2498 Cream)</t>
+    <t>9001 CARD (O.C.)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1814,298 +1814,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
-  </si>
-  <si>
-    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
-  </si>
-  <si>
-    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
-  </si>
-  <si>
-    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
-  </si>
-  <si>
-    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9301 CARDS (4242)</t>
-  </si>
-  <si>
-    <t>9302 CARDS (5076)</t>
-  </si>
-  <si>
-    <t>9303 CARDS (5080 Pink)</t>
-  </si>
-  <si>
-    <t>9304 CARDS (5083 Blue)</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070) (4701 Nice)</t>
-  </si>
-  <si>
-    <t>9306 CARDS (0543 Nice)</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M) (5243 Nice)</t>
-  </si>
-  <si>
-    <t>9308 CARDS (9852)</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
-  </si>
-  <si>
-    <t>9310 CARDS (3103)</t>
-  </si>
-  <si>
-    <t>9311 CARDS (3115)</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T) (208 VV)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T) (216)</t>
-  </si>
-  <si>
-    <t>9314 CARDS (P-1)</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU) (P-2)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU) (P-3)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (Aa Gya ) (P-4)</t>
-  </si>
-  <si>
-    <t>9318 CARDS (25905)</t>
-  </si>
-  <si>
-    <t>9319 CARDS (25906)</t>
-  </si>
-  <si>
-    <t>9320 CARDS (S-20)</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9325 CARDS (5229)</t>
-  </si>
-  <si>
-    <t>9326 CARDS (500 18.02) (1601)</t>
-  </si>
-  <si>
-    <t>9327 CARDS (25908)</t>
-  </si>
-  <si>
-    <t>9328 CARDS (2543)</t>
-  </si>
-  <si>
-    <t>9329 CARDS (3606)</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T) (9557)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T) (9560)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC (9847)</t>
-  </si>
-  <si>
-    <t>9333 CARDS (6042)</t>
-  </si>
-  <si>
-    <t>9334 CARDS (10X6 WHITE (2898))</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (2884)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC) (1635 AP)</t>
-  </si>
-  <si>
-    <t>9338 CARDS (18.02) (1637 AP)</t>
-  </si>
-  <si>
-    <t>9339 CARDS (5361)</t>
-  </si>
-  <si>
-    <t>9340 CARDS (5658)</t>
-  </si>
-  <si>
-    <t>9341 CARDS (5497)</t>
-  </si>
-  <si>
-    <t>9342 CARDS (2861)</t>
-  </si>
-  <si>
-    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu) (689)</t>
-  </si>
-  <si>
-    <t>9345 CARDS (358 KALYANI)</t>
-  </si>
-  <si>
-    <t>9346 CARDS (359)</t>
-  </si>
-  <si>
-    <t>9347 CARDS (2853)</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी) (S-124)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window) (S-120)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T) (1000 19.02) (1632)</t>
-  </si>
-  <si>
-    <t>9351 Card - B (1603 B)</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC (1603)</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
-  </si>
-  <si>
-    <t>9353 CARDS (1618)</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU) (345)</t>
-  </si>
-  <si>
-    <t>9355 CARDS (1624)</t>
-  </si>
-  <si>
-    <t>9356 CARDS (2895/2897)</t>
-  </si>
-  <si>
-    <t>9357 CARDS (2872)</t>
-  </si>
-  <si>
-    <t>9358 CARDS (WHITE PATTA)</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
-  </si>
-  <si>
-    <t>9361 CARDS (25426)</t>
-  </si>
-  <si>
-    <t>9362 CARDS (363)</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T) (1652)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T) (1612)</t>
-  </si>
-  <si>
-    <t>9365 CARDS (25429)</t>
-  </si>
-  <si>
-    <t>9366 CARDS (25427 GOLDEN)</t>
-  </si>
-  <si>
-    <t>9367 CARDS (5652)</t>
-  </si>
-  <si>
-    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
-  </si>
-  <si>
-    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
-  </si>
-  <si>
-    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
-  </si>
-  <si>
-    <t>9371 CARDS (3111 VP)</t>
-  </si>
-  <si>
-    <t>9372 CARDS (9*5 YLW SET (2841))</t>
-  </si>
-  <si>
-    <t>9373 CARDS (1482)</t>
-  </si>
-  <si>
-    <t>9374 CARDS (1485)</t>
-  </si>
-  <si>
-    <t>9375 CARDS (1452 WHITE)</t>
-  </si>
-  <si>
-    <t>9376 CARDS (1529 PRINCE)</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
-  </si>
-  <si>
-    <t>9378 CARDS (2892)</t>
+    <t>9231 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS</t>
+  </si>
+  <si>
+    <t>9240 CARDS</t>
+  </si>
+  <si>
+    <t>9241 CARDS</t>
+  </si>
+  <si>
+    <t>9242 CARDS</t>
+  </si>
+  <si>
+    <t>9243 CARDS</t>
+  </si>
+  <si>
+    <t>9244 CARDS</t>
+  </si>
+  <si>
+    <t>9301 CARDS</t>
+  </si>
+  <si>
+    <t>9302 CARDS</t>
+  </si>
+  <si>
+    <t>9303 CARDS</t>
+  </si>
+  <si>
+    <t>9304 CARDS</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070)</t>
+  </si>
+  <si>
+    <t>9306 CARDS</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M)</t>
+  </si>
+  <si>
+    <t>9308 CARDS</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc)</t>
+  </si>
+  <si>
+    <t>9310 CARDS</t>
+  </si>
+  <si>
+    <t>9311 CARDS</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9314 CARDS</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (Aa Gya )</t>
+  </si>
+  <si>
+    <t>9318 CARDS</t>
+  </si>
+  <si>
+    <t>9319 CARDS</t>
+  </si>
+  <si>
+    <t>9320 CARDS</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD)</t>
+  </si>
+  <si>
+    <t>9324 CARDS</t>
+  </si>
+  <si>
+    <t>9325 CARDS</t>
+  </si>
+  <si>
+    <t>9326 CARDS (500 18.02)</t>
+  </si>
+  <si>
+    <t>9327 CARDS</t>
+  </si>
+  <si>
+    <t>9328 CARDS</t>
+  </si>
+  <si>
+    <t>9329 CARDS</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC</t>
+  </si>
+  <si>
+    <t>9333 CARDS</t>
+  </si>
+  <si>
+    <t>9334 CARDS</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD)</t>
+  </si>
+  <si>
+    <t>9336 CARDS</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC)</t>
+  </si>
+  <si>
+    <t>9338 CARDS (18.02)</t>
+  </si>
+  <si>
+    <t>9339 CARDS</t>
+  </si>
+  <si>
+    <t>9340 CARDS</t>
+  </si>
+  <si>
+    <t>9341 CARDS</t>
+  </si>
+  <si>
+    <t>9342 CARDS</t>
+  </si>
+  <si>
+    <t>9343 CARDS</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu)</t>
+  </si>
+  <si>
+    <t>9345 CARDS</t>
+  </si>
+  <si>
+    <t>9346 CARDS</t>
+  </si>
+  <si>
+    <t>9347 CARDS</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1000 19.02)</t>
+  </si>
+  <si>
+    <t>9351 Card - B</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9353 CARDS</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9355 CARDS</t>
+  </si>
+  <si>
+    <t>9356 CARDS</t>
+  </si>
+  <si>
+    <t>9357 CARDS</t>
+  </si>
+  <si>
+    <t>9358 CARDS</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega</t>
+  </si>
+  <si>
+    <t>9361 CARDS</t>
+  </si>
+  <si>
+    <t>9362 CARDS</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9365 CARDS</t>
+  </si>
+  <si>
+    <t>9366 CARDS</t>
+  </si>
+  <si>
+    <t>9367 CARDS</t>
+  </si>
+  <si>
+    <t>9368 CARDS</t>
+  </si>
+  <si>
+    <t>9369 CARDS</t>
+  </si>
+  <si>
+    <t>9370 CARDS</t>
+  </si>
+  <si>
+    <t>9371 CARDS</t>
+  </si>
+  <si>
+    <t>9372 CARDS</t>
+  </si>
+  <si>
+    <t>9373 CARDS</t>
+  </si>
+  <si>
+    <t>9374 CARDS</t>
+  </si>
+  <si>
+    <t>9375 CARDS</t>
+  </si>
+  <si>
+    <t>9376 CARDS</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9378 CARDS</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2138,19 +2138,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS (9147 RJ)</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU) (118KBC)</t>
+    <t>9389 CARDS</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
+    <t>9*4 ENVELOPE (SBC)</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2180,7 +2180,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
+    <t>FANCY GIFT ENVELOPE-(SR)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2201,37 +2201,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (LX01)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (LX02)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE (LX03)</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (LX04)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (LX05)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE (LX06)</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (LX07)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (LX08)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (LX09)</t>
+    <t>RX-01 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
+    <t>गोल गणेश / गोल फ्लावर</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2761,7 +2761,7 @@
   <dimension ref="A1:E734"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2917,16 +2917,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="25">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>286.64999999999998</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,16 +2934,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="25">
-        <v>174.5</v>
+        <v>171</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,16 +2951,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="25">
-        <v>65.5</v>
+        <v>63</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3104,16 +3104,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="25">
-        <v>-0.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>-0.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3121,16 +3121,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>24.75</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3138,16 +3138,16 @@
         <v>28</v>
       </c>
       <c r="B26" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="26">
         <v>1.65</v>
       </c>
       <c r="E26" s="27">
-        <v>8.25</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3885,16 +3885,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C71" s="25">
-        <v>105.5</v>
+        <v>88.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>147.69999999999999</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3902,16 +3902,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C72" s="25">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>527.79999999999995</v>
+        <v>513.79999999999995</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3936,16 +3936,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="25">
-        <v>288.5</v>
+        <v>276.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>346.2</v>
+        <v>331.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3970,16 +3970,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C76" s="25">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>603.6</v>
+        <v>596.4</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4317,16 +4317,16 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C97" s="25">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="D97" s="26">
         <v>0.9</v>
       </c>
       <c r="E97" s="27">
-        <v>30.15</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4626,16 +4626,16 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C118" s="25">
-        <v>67</v>
+        <v>73.25</v>
       </c>
       <c r="D118" s="26">
         <v>0.7</v>
       </c>
       <c r="E118" s="27">
-        <v>46.9</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4993,16 +4993,16 @@
         <v>145</v>
       </c>
       <c r="B143" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C143" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>129.5</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5123,16 +5123,16 @@
         <v>153</v>
       </c>
       <c r="B151" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C151" s="25">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="D151" s="26">
         <v>18.5</v>
       </c>
       <c r="E151" s="27">
-        <v>203.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,16 +5395,16 @@
         <v>169</v>
       </c>
       <c r="B167" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C167" s="25">
-        <v>3.25</v>
+        <v>-1.75</v>
       </c>
       <c r="D167" s="26">
         <v>1</v>
       </c>
       <c r="E167" s="27">
-        <v>3.25</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>171</v>
       </c>
       <c r="B169" s="24">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C169" s="25">
-        <v>17</v>
+        <v>-43</v>
       </c>
       <c r="D169" s="29"/>
       <c r="E169" s="28"/>
@@ -5886,16 +5886,16 @@
         <v>200</v>
       </c>
       <c r="B198" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C198" s="25">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D198" s="26">
         <v>4.5</v>
       </c>
       <c r="E198" s="27">
-        <v>211.5</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -6257,13 +6257,13 @@
         <v>52</v>
       </c>
       <c r="C220" s="25">
-        <v>39</v>
+        <v>99.75</v>
       </c>
       <c r="D220" s="26">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="E220" s="27">
-        <v>141.11000000000001</v>
+        <v>362.69</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6305,16 +6305,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C223" s="25">
-        <v>145.5</v>
+        <v>141.5</v>
       </c>
       <c r="D223" s="26">
         <v>2.66</v>
       </c>
       <c r="E223" s="27">
-        <v>387.03</v>
+        <v>376.39</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6407,16 +6407,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C229" s="25">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="D229" s="26">
         <v>3.5</v>
       </c>
       <c r="E229" s="27">
-        <v>40.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6628,16 +6628,16 @@
         <v>246</v>
       </c>
       <c r="B244" s="24">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C244" s="25">
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="D244" s="26">
         <v>6.3</v>
       </c>
       <c r="E244" s="27">
-        <v>430.92</v>
+        <v>418.32</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6690,16 +6690,16 @@
         <v>250</v>
       </c>
       <c r="B248" s="24">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C248" s="25">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D248" s="26">
         <v>3.9</v>
       </c>
       <c r="E248" s="27">
-        <v>315.89999999999998</v>
+        <v>308.10000000000002</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -6904,16 +6904,16 @@
         <v>264</v>
       </c>
       <c r="B262" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C262" s="25">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="D262" s="26">
         <v>6.15</v>
       </c>
       <c r="E262" s="27">
-        <v>199.99</v>
+        <v>187.68</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -7384,16 +7384,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C292" s="25">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D292" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E292" s="27">
-        <v>557.23</v>
+        <v>532.79</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7435,16 +7435,16 @@
         <v>297</v>
       </c>
       <c r="B295" s="24">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C295" s="25">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D295" s="26">
         <v>6.06</v>
       </c>
       <c r="E295" s="27">
-        <v>1722.23</v>
+        <v>1710.2</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7714,16 +7714,16 @@
         <v>314</v>
       </c>
       <c r="B312" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C312" s="25">
-        <v>13.95</v>
+        <v>11.45</v>
       </c>
       <c r="D312" s="26">
         <v>9.4499999999999993</v>
       </c>
       <c r="E312" s="27">
-        <v>131.83000000000001</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -8533,16 +8533,16 @@
         <v>365</v>
       </c>
       <c r="B363" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C363" s="25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D363" s="26">
         <v>5.94</v>
       </c>
       <c r="E363" s="27">
-        <v>130.68</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -8618,16 +8618,16 @@
         <v>370</v>
       </c>
       <c r="B368" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C368" s="25">
-        <v>126</v>
+        <v>119.5</v>
       </c>
       <c r="D368" s="26">
         <v>6.6</v>
       </c>
       <c r="E368" s="27">
-        <v>831.6</v>
+        <v>788.7</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8669,16 +8669,16 @@
         <v>373</v>
       </c>
       <c r="B371" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C371" s="25">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D371" s="26">
         <v>8.52</v>
       </c>
       <c r="E371" s="27">
-        <v>451.34</v>
+        <v>442.83</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -9165,16 +9165,16 @@
         <v>403</v>
       </c>
       <c r="B401" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C401" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D401" s="26">
         <v>6.65</v>
       </c>
       <c r="E401" s="27">
-        <v>53.2</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9561,16 +9561,16 @@
         <v>429</v>
       </c>
       <c r="B427" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C427" s="25">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D427" s="26">
         <v>6</v>
       </c>
       <c r="E427" s="27">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -9892,16 +9892,16 @@
         <v>450</v>
       </c>
       <c r="B448" s="24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C448" s="25">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="D448" s="26">
         <v>10.5</v>
       </c>
       <c r="E448" s="27">
-        <v>94.5</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -11329,16 +11329,16 @@
         <v>539</v>
       </c>
       <c r="B537" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C537" s="25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D537" s="26">
         <v>4</v>
       </c>
       <c r="E537" s="27">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11363,16 +11363,16 @@
         <v>541</v>
       </c>
       <c r="B539" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C539" s="25">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="D539" s="26">
         <v>1.8</v>
       </c>
       <c r="E539" s="27">
-        <v>65.7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -12007,16 +12007,16 @@
         <v>579</v>
       </c>
       <c r="B577" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C577" s="25">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="D577" s="26">
         <v>1.4</v>
       </c>
       <c r="E577" s="27">
-        <v>147.69999999999999</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -12024,16 +12024,16 @@
         <v>580</v>
       </c>
       <c r="B578" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C578" s="25">
-        <v>101.5</v>
+        <v>96.5</v>
       </c>
       <c r="D578" s="26">
         <v>1.8</v>
       </c>
       <c r="E578" s="27">
-        <v>182.7</v>
+        <v>173.7</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -12122,10 +12122,10 @@
         <v>586</v>
       </c>
       <c r="B584" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C584" s="25">
-        <v>9</v>
+        <v>-37</v>
       </c>
       <c r="D584" s="29"/>
       <c r="E584" s="28"/>
@@ -12264,16 +12264,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C594" s="25">
-        <v>738.5</v>
+        <v>718.5</v>
       </c>
       <c r="D594" s="26">
         <v>0.85</v>
       </c>
       <c r="E594" s="27">
-        <v>627.73</v>
+        <v>610.73</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12496,16 +12496,16 @@
         <v>612</v>
       </c>
       <c r="B610" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C610" s="25">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="D610" s="26">
         <v>0.85</v>
       </c>
       <c r="E610" s="27">
-        <v>73.95</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
@@ -12834,16 +12834,16 @@
         <v>632</v>
       </c>
       <c r="B630" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C630" s="25">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D630" s="26">
         <v>4</v>
       </c>
       <c r="E630" s="27">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -13683,16 +13683,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C681" s="25">
-        <v>24.5</v>
+        <v>19.5</v>
       </c>
       <c r="D681" s="26">
         <v>2.75</v>
       </c>
       <c r="E681" s="27">
-        <v>67.38</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13847,16 +13847,16 @@
         <v>693</v>
       </c>
       <c r="B691" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C691" s="25">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="D691" s="26">
         <v>3.6</v>
       </c>
       <c r="E691" s="27">
-        <v>108</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
@@ -14135,15 +14135,9 @@
       <c r="B713" s="24">
         <v>3</v>
       </c>
-      <c r="C713" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="D713" s="26">
-        <v>18</v>
-      </c>
-      <c r="E713" s="27">
-        <v>-9</v>
-      </c>
+      <c r="C713" s="28"/>
+      <c r="D713" s="29"/>
+      <c r="E713" s="28"/>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" s="23" t="s">
@@ -14226,10 +14220,10 @@
         <v>722</v>
       </c>
       <c r="B720" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C720" s="25">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="D720" s="29"/>
       <c r="E720" s="28"/>
@@ -14447,11 +14441,11 @@
       </c>
       <c r="B734" s="31"/>
       <c r="C734" s="32">
-        <v>44170.559999999998</v>
+        <v>43968.05</v>
       </c>
       <c r="D734" s="33"/>
       <c r="E734" s="34">
-        <v>104854.18</v>
+        <v>104662.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -985,13 +985,13 @@
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="27">
-        <v>12954.76</v>
+        <v>12948.76</v>
       </c>
       <c r="D17" s="28">
         <v>1.76</v>
       </c>
       <c r="E17" s="29">
-        <v>22822.54</v>
+        <v>22814.61</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1045,13 +1045,13 @@
       </c>
       <c r="B21" s="24"/>
       <c r="C21" s="27">
-        <v>2561.86</v>
+        <v>2558.86</v>
       </c>
       <c r="D21" s="28">
         <v>3.81</v>
       </c>
       <c r="E21" s="29">
-        <v>9763.2099999999991</v>
+        <v>9752.7099999999991</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1075,13 +1075,13 @@
       </c>
       <c r="B23" s="24"/>
       <c r="C23" s="27">
-        <v>312.75</v>
+        <v>311.25</v>
       </c>
       <c r="D23" s="28">
         <v>6.43</v>
       </c>
       <c r="E23" s="29">
-        <v>2010.18</v>
+        <v>2000.89</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1120,13 +1120,13 @@
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="27">
-        <v>2694.39</v>
+        <v>2692.39</v>
       </c>
       <c r="D26" s="28">
         <v>2.6</v>
       </c>
       <c r="E26" s="29">
-        <v>7001.06</v>
+        <v>6995.66</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1165,13 +1165,13 @@
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="27">
-        <v>398.95</v>
+        <v>398.45</v>
       </c>
       <c r="D29" s="28">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
       <c r="E29" s="29">
-        <v>3358.2</v>
+        <v>3350.2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1240,13 +1240,13 @@
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="27">
-        <v>11395.07</v>
+        <v>11393.57</v>
       </c>
       <c r="D34" s="28">
         <v>2.2200000000000002</v>
       </c>
       <c r="E34" s="29">
-        <v>25352.77</v>
+        <v>25343.39</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1255,13 +1255,13 @@
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="27">
-        <v>3793.04</v>
+        <v>3787.04</v>
       </c>
       <c r="D35" s="28">
         <v>0.6</v>
       </c>
       <c r="E35" s="29">
-        <v>2275.4699999999998</v>
+        <v>2270.17</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1765,11 +1765,11 @@
       </c>
       <c r="B71" s="35"/>
       <c r="C71" s="36">
-        <v>43761.55</v>
+        <v>43741.05</v>
       </c>
       <c r="D71" s="37"/>
       <c r="E71" s="38">
-        <v>104486.32</v>
+        <v>104430.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7650" windowHeight="8835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="10215"/>
   </bookViews>
   <sheets>
     <sheet name="PATRIKA 25-26" sheetId="1" r:id="rId1"/>
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA (25/251)</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA (25/262)</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA (25/261)</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA (25/361/861)</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA (25/362/862)</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA (25/282)</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA (25/281)</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC) (2595 PINK)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
+    <t>.1001 PATRIKA</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA (6321)</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA (11043 OFFSET)</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA (1011 OFFSET)</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA (1014 OFFSET)</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA (1222 SBC)</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA (1235)</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA (2101 VV)</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC) (25409)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA (25418)</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA (25322)</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA (25323)</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC) (1173 SBC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC) (5346)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC) (2596)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA (1042)</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA (1043)</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA (GOPAL 11)</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA (GOPAL 1)</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA (2002 YLW)</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA (2003 R)</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA (276-A)</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW (25419)</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED (25420)</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y (25421)</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R (25422)</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA (277-B)</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA (1819 MONARCH)</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN (1709)</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155) (1155 JSK)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 (NEW SAVASHREE 52)</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51) (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52) (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53) (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54) (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R) (120 GSM RED)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01) (JCC 01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02) (JCC 02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU) (BP RED)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
+    <t>1010 PATRIKA</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB)</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G)</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA (LEGACY - 10)</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA (LEGACY - 11)</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA (LEGACY - 12)</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA (LOTTERY - 80)</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
+    <t>2101 PATRIKA (L)-DC</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -551,1234 +551,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC) (5342)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA (5207)</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA (5206)</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210) (10273/10277)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA (82)</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC) (1129)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC) (101 SBC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA (1102)</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC) (959)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC) (2571)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU) (1351)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA (83)</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA (25-145)</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC) (25-046)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA (111 SBC)</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA (1151 GGN)</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC) (25216)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA (2547)</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC) (25369)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA (25367)</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA (25368)</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA (1031)</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA (25301)</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA (25312 MYRA)</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA (3117)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN) (3116)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA (1173 VV)</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA (5254  RJN)</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA (25402)</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA (10001 NEW)</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA (10002 NEW)</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA (316 MYRA)</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA (25401)</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA (25311)</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA (25312)</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA (5273)</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA (286-A)</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA (1407)</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA (306)</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA (5501)</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA (2011)</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA (25314)</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA (25315)</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU) (1402)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC) (1234*-M)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA (5172)</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA (25313)</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA (BALAJI 5202)</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA (LOTUS 430)</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU) (251 KBC)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU) (273-A)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M) (5087)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA (5295)</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA (5213)</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M) (25/162)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA (25/272)</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC) (25/271)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA (FRIDAY ) (25/171)</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA (8802)</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA (8803)</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC) (7713)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU) (1405)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA (7705)</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA (2522 GE)</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA (2517 GE)</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA (2527)</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA (2536)</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC) (S-301)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU) (S-305)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC) (1103)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी) (741)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA (5347 DIRECT)</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M) (3161)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA (1151 VV)</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC) (25-082)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC) (3701 SBC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA (2081)</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA (296-A (NEHA)</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA (2501 GE NEW)</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA (2520 GE)</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (5267)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA (5258 RJ)</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA (2023)</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC) (2206)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA (25214)</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA (2061 SBC)</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA (5236 RJ)</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC) (1411 KBC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA (5350)</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA (5251)</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA (5240)</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA (25316)</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA (25321)</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M) (857)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU) (5339)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021) (2456)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA (2071)</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA (5261 RJND)</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC) (5335)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA (253-A / 257-A)</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA (5356 RJ)</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (5333)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA (5308)</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC) (AS-402)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC) (5313)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA (5305)</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA (2031)</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU) (3331)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU) (25436)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA (5186)</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC) (7033)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M) (25/122)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC) (8055 VV)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC) (612 VV)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC) (25/072)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC) (2525 /2552)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA (2515)</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU) (2542)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA (2523)</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M) (7066)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA (1054)</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA (2231)</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA (2232)</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU) (5382)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M) (5283)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC) (25-052)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B (2942-B)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC) (2942)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M) (S-96)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC) (2101)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA (2261)</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA (2353)</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M) (2732)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA (718)</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M) (S-32)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU) (2792)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA (5261 NICE)</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M) (5424)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA (5231)</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M) (5004)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G) (5379)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA (2903)</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M) (2952)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA (2312 SBC)</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA (2293)</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-* (2915)</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M) (25358)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA (5387)</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA (175)</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M) (1742-B)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA (1679)</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M) (3002)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M) (S-39)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M) (S-74)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M) (25353)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M) (25351)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA (2205)</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA (25335)</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M) (S-77)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA (2531)</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M) (5808)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA (S-326)</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M) (3471)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA (3211 SBC)</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC) (2202 SBC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M) (S-51)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA (2264)</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M) (25133)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA (3131 SBC)</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M) (2365)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA (2803)</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC) (2931)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M) (226)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M) (2541)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M) (77-B)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC) (25324)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA (2771)</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA (3271)</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M) (6125)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA (242-A)</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC) (3102)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M) (221-A)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA (25442)</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA (25440)</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA (993)</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC) (2373)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M) (1211)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU) (5276)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA (2111)</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU) (7069)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M) (7067)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC) (1131)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC) (15)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M) (25337)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA (064)</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC) (2753)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU) (772)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU) (GOL)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L) (5164)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA (5126)</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA (5111)</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M) (5196)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA (5191)</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R (3023)</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (TUESDAY) (0523)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA (95)</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M) (3053)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M) (3019)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC) (3017 VV)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA (3015)</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA (25164)</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU) (25131)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M) (3422)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M) (1193)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA (25184)</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M) (25135)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M) (25116)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (25161)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M) (25111)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU) (932)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA (3562)</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M) (S-313)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M) (25183)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA (25162 GE)</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M) (3014)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (2291)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B) (2291-B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M) (25380)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU) (25132)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M) (3031)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M) (3034)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M) (25382)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M) (3402)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC (3431)</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA (3421)</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M) (3461)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M) (5319)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA (25193 (Padding))</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA (25194 (Padding))</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M) (1281)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA (3424)</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA (7103 (PADDING))</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M) (5823)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU) (8102)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU) (6197)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M) (1868-B)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M) (1868)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M) (1872)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M) (6132)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU) (6196)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU) (1503)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M) (1282)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU) (533 KBC)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.) (133)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.) (1522)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.) (1178)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.) (AS-20)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.) (4087)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.) (2204)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.) (2482)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.) (12)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA (25/252)</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA (25/264-263)</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA (25/363/863)</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA (25/283)</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA (25/273)</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA (25/172)</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU) (25895)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA (2521)</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA (2526)</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA (2535)</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA (84)</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA (2543 INV OFFSET)</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA (2234)</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA (S-201 INV)</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA (5121)</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA (720)</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F) (25-146)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA (3702)</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA (254 SBC)</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F) (25-047)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA (2082)</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-* (4052)</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA (2103)</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA (1223 SBC)</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA (6310 GE)</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA (2532)</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA (1174)</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA (1034)</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA (2204 INV)</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA (06)</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA (303)</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA (25323 INV)</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA (25413)</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA (2597)</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA (25896)</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F) (243-C)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA (1855)</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA (1044 SBC)</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA (2014)</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA (2006)</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU) (6106)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA (GOPAL 32)</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA (2005- G)</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA (5180)</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU) (3753)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA (273 NEHA)</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA (278-B)</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
+    <t>4251 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (FRIDAY )</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M) (TUESDAY)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc'''</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1790,7 +1790,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.) (2498 Cream)</t>
+    <t>9001 CARD (O.C.)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1814,298 +1814,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
-  </si>
-  <si>
-    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
-  </si>
-  <si>
-    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
-  </si>
-  <si>
-    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
-  </si>
-  <si>
-    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9301 CARDS (4242)</t>
-  </si>
-  <si>
-    <t>9302 CARDS (5076)</t>
-  </si>
-  <si>
-    <t>9303 CARDS (5080 Pink)</t>
-  </si>
-  <si>
-    <t>9304 CARDS (5083 Blue)</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070) (4701 Nice)</t>
-  </si>
-  <si>
-    <t>9306 CARDS (0543 Nice)</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M) (5243 Nice)</t>
-  </si>
-  <si>
-    <t>9308 CARDS (9852)</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
-  </si>
-  <si>
-    <t>9310 CARDS (3103)</t>
-  </si>
-  <si>
-    <t>9311 CARDS (3115)</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T) (208 VV)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T) (216)</t>
-  </si>
-  <si>
-    <t>9314 CARDS (P-1)</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU) (P-2)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU) (P-3)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (Aa Gya ) (P-4)</t>
-  </si>
-  <si>
-    <t>9318 CARDS (25905)</t>
-  </si>
-  <si>
-    <t>9319 CARDS (25906)</t>
-  </si>
-  <si>
-    <t>9320 CARDS (S-20)</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9325 CARDS (5229)</t>
-  </si>
-  <si>
-    <t>9326 CARDS (1601)</t>
-  </si>
-  <si>
-    <t>9327 CARDS (25908)</t>
-  </si>
-  <si>
-    <t>9328 CARDS (2543)</t>
-  </si>
-  <si>
-    <t>9329 CARDS (3606)</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T) (9557)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T) (9560)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC (9847)</t>
-  </si>
-  <si>
-    <t>9333 CARDS (6042)</t>
-  </si>
-  <si>
-    <t>9334 CARDS (10X6 WHITE (2898))</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (2884)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC) (1635 AP)</t>
-  </si>
-  <si>
-    <t>9338 CARDS (1637 AP)</t>
-  </si>
-  <si>
-    <t>9339 CARDS (5361)</t>
-  </si>
-  <si>
-    <t>9340 CARDS (5658)</t>
-  </si>
-  <si>
-    <t>9341 CARDS (5497)</t>
-  </si>
-  <si>
-    <t>9342 CARDS (2861)</t>
-  </si>
-  <si>
-    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu) (689)</t>
-  </si>
-  <si>
-    <t>9345 CARDS (358 KALYANI)</t>
-  </si>
-  <si>
-    <t>9346 CARDS (359)</t>
-  </si>
-  <si>
-    <t>9347 CARDS (2853)</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी) (S-124)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window) (S-120)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T) (1000 19.02) (1632)</t>
-  </si>
-  <si>
-    <t>9351 Card - B (1603 B)</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC (1603)</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
-  </si>
-  <si>
-    <t>9353 CARDS (1618)</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU) (345)</t>
-  </si>
-  <si>
-    <t>9355 CARDS (1624)</t>
-  </si>
-  <si>
-    <t>9356 CARDS (2895/2897)</t>
-  </si>
-  <si>
-    <t>9357 CARDS (2872)</t>
-  </si>
-  <si>
-    <t>9358 CARDS (WHITE PATTA)</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
-  </si>
-  <si>
-    <t>9361 CARDS (25426)</t>
-  </si>
-  <si>
-    <t>9362 CARDS (363)</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T) (1652)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T) (1612)</t>
-  </si>
-  <si>
-    <t>9365 CARDS (25429)</t>
-  </si>
-  <si>
-    <t>9366 CARDS (25427 GOLDEN)</t>
-  </si>
-  <si>
-    <t>9367 CARDS (5652)</t>
-  </si>
-  <si>
-    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
-  </si>
-  <si>
-    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
-  </si>
-  <si>
-    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
-  </si>
-  <si>
-    <t>9371 CARDS (3111 VP)</t>
-  </si>
-  <si>
-    <t>9372 CARDS (9*5 YLW SET (2841))</t>
-  </si>
-  <si>
-    <t>9373 CARDS (1482)</t>
-  </si>
-  <si>
-    <t>9374 CARDS (1485)</t>
-  </si>
-  <si>
-    <t>9375 CARDS (1452 WHITE)</t>
-  </si>
-  <si>
-    <t>9376 CARDS (1529 PRINCE)</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
-  </si>
-  <si>
-    <t>9378 CARDS (2892)</t>
+    <t>9231 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS</t>
+  </si>
+  <si>
+    <t>9240 CARDS</t>
+  </si>
+  <si>
+    <t>9241 CARDS</t>
+  </si>
+  <si>
+    <t>9242 CARDS</t>
+  </si>
+  <si>
+    <t>9243 CARDS</t>
+  </si>
+  <si>
+    <t>9244 CARDS</t>
+  </si>
+  <si>
+    <t>9301 CARDS</t>
+  </si>
+  <si>
+    <t>9302 CARDS</t>
+  </si>
+  <si>
+    <t>9303 CARDS</t>
+  </si>
+  <si>
+    <t>9304 CARDS</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070)</t>
+  </si>
+  <si>
+    <t>9306 CARDS</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M)</t>
+  </si>
+  <si>
+    <t>9308 CARDS</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc)</t>
+  </si>
+  <si>
+    <t>9310 CARDS</t>
+  </si>
+  <si>
+    <t>9311 CARDS</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9314 CARDS</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (Aa Gya )</t>
+  </si>
+  <si>
+    <t>9318 CARDS</t>
+  </si>
+  <si>
+    <t>9319 CARDS</t>
+  </si>
+  <si>
+    <t>9320 CARDS</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD)</t>
+  </si>
+  <si>
+    <t>9324 CARDS</t>
+  </si>
+  <si>
+    <t>9325 CARDS</t>
+  </si>
+  <si>
+    <t>9326 CARDS</t>
+  </si>
+  <si>
+    <t>9327 CARDS</t>
+  </si>
+  <si>
+    <t>9328 CARDS</t>
+  </si>
+  <si>
+    <t>9329 CARDS</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC</t>
+  </si>
+  <si>
+    <t>9333 CARDS</t>
+  </si>
+  <si>
+    <t>9334 CARDS</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD)</t>
+  </si>
+  <si>
+    <t>9336 CARDS</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC)</t>
+  </si>
+  <si>
+    <t>9338 CARDS</t>
+  </si>
+  <si>
+    <t>9339 CARDS</t>
+  </si>
+  <si>
+    <t>9340 CARDS</t>
+  </si>
+  <si>
+    <t>9341 CARDS</t>
+  </si>
+  <si>
+    <t>9342 CARDS</t>
+  </si>
+  <si>
+    <t>9343 CARDS</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu)</t>
+  </si>
+  <si>
+    <t>9345 CARDS</t>
+  </si>
+  <si>
+    <t>9346 CARDS</t>
+  </si>
+  <si>
+    <t>9347 CARDS</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1000 19.02)</t>
+  </si>
+  <si>
+    <t>9351 Card - B</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9353 CARDS</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9355 CARDS</t>
+  </si>
+  <si>
+    <t>9356 CARDS</t>
+  </si>
+  <si>
+    <t>9357 CARDS</t>
+  </si>
+  <si>
+    <t>9358 CARDS</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega</t>
+  </si>
+  <si>
+    <t>9361 CARDS</t>
+  </si>
+  <si>
+    <t>9362 CARDS</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9365 CARDS</t>
+  </si>
+  <si>
+    <t>9366 CARDS</t>
+  </si>
+  <si>
+    <t>9367 CARDS</t>
+  </si>
+  <si>
+    <t>9368 CARDS</t>
+  </si>
+  <si>
+    <t>9369 CARDS</t>
+  </si>
+  <si>
+    <t>9370 CARDS</t>
+  </si>
+  <si>
+    <t>9371 CARDS</t>
+  </si>
+  <si>
+    <t>9372 CARDS</t>
+  </si>
+  <si>
+    <t>9373 CARDS</t>
+  </si>
+  <si>
+    <t>9374 CARDS</t>
+  </si>
+  <si>
+    <t>9375 CARDS</t>
+  </si>
+  <si>
+    <t>9376 CARDS</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9378 CARDS</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2138,19 +2138,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS (9147 RJ)</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU) (118KBC)</t>
+    <t>9389 CARDS</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
+    <t>9*4 ENVELOPE (SBC)</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2180,7 +2180,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
+    <t>FANCY GIFT ENVELOPE-(SR)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2204,37 +2204,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (LX01)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (LX02)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE (LX03)</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (LX04)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (LX05)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE (LX06)</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (LX07)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (LX08)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (LX09)</t>
+    <t>RX-01 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
+    <t>गोल गणेश / गोल फ्लावर</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2764,7 +2764,7 @@
   <dimension ref="A1:E735"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2903,16 +2903,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="25">
-        <v>178.5</v>
+        <v>173.5</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>348.08</v>
+        <v>338.33</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3041,9 +3041,15 @@
       <c r="B20" s="24">
         <v>32</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="28"/>
+      <c r="C20" s="25">
+        <v>105</v>
+      </c>
+      <c r="D20" s="26">
+        <v>0.64</v>
+      </c>
+      <c r="E20" s="27">
+        <v>67.680000000000007</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -3118,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" s="25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>18.149999999999999</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,16 +3877,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C70" s="25">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>596.4</v>
+        <v>582.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,16 +3894,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C71" s="25">
-        <v>70.5</v>
+        <v>64.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>98.7</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4177,16 +4183,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C88" s="25">
-        <v>1076.5</v>
+        <v>1066.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1830.05</v>
+        <v>1813.05</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -5117,16 +5123,16 @@
         <v>152</v>
       </c>
       <c r="B150" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C150" s="25">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D150" s="26">
         <v>18.5</v>
       </c>
       <c r="E150" s="27">
-        <v>64.75</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -5437,13 +5443,13 @@
         <v>27</v>
       </c>
       <c r="C169" s="25">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D169" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E169" s="27">
-        <v>14.55</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5453,9 +5459,15 @@
       <c r="B170" s="24">
         <v>70</v>
       </c>
-      <c r="C170" s="28"/>
-      <c r="D170" s="29"/>
-      <c r="E170" s="28"/>
+      <c r="C170" s="25">
+        <v>23</v>
+      </c>
+      <c r="D170" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="E170" s="27">
+        <v>29.9</v>
+      </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="23" t="s">
@@ -6081,16 +6093,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C210" s="25">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D210" s="26">
         <v>3.93</v>
       </c>
       <c r="E210" s="27">
-        <v>573.48</v>
+        <v>553.84</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6166,16 +6178,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C215" s="25">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D215" s="26">
         <v>4.5</v>
       </c>
       <c r="E215" s="27">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6217,16 +6229,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C218" s="25">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D218" s="26">
         <v>3.93</v>
       </c>
       <c r="E218" s="27">
-        <v>750.47</v>
+        <v>734.76</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6404,16 +6416,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C229" s="25">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="D229" s="26">
         <v>3.5</v>
       </c>
       <c r="E229" s="27">
-        <v>225.75</v>
+        <v>222.25</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6594,13 +6606,13 @@
         <v>24</v>
       </c>
       <c r="C242" s="25">
-        <v>6.5</v>
+        <v>21.5</v>
       </c>
       <c r="D242" s="26">
         <v>5.75</v>
       </c>
       <c r="E242" s="27">
-        <v>37.380000000000003</v>
+        <v>123.63</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -6608,16 +6620,16 @@
         <v>245</v>
       </c>
       <c r="B243" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C243" s="25">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D243" s="26">
         <v>4.8</v>
       </c>
       <c r="E243" s="27">
-        <v>177.6</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -7534,16 +7546,16 @@
         <v>303</v>
       </c>
       <c r="B301" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C301" s="25">
-        <v>103.25</v>
+        <v>99.25</v>
       </c>
       <c r="D301" s="26">
         <v>4.3</v>
       </c>
       <c r="E301" s="27">
-        <v>443.69</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7711,16 +7723,16 @@
         <v>314</v>
       </c>
       <c r="B312" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C312" s="25">
-        <v>11.45</v>
+        <v>10.95</v>
       </c>
       <c r="D312" s="26">
         <v>9.4499999999999993</v>
       </c>
       <c r="E312" s="27">
-        <v>108.2</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -9793,17 +9805,11 @@
         <v>444</v>
       </c>
       <c r="B442" s="24">
-        <v>5</v>
-      </c>
-      <c r="C442" s="25">
-        <v>-7.5</v>
-      </c>
-      <c r="D442" s="26">
-        <v>15.5</v>
-      </c>
-      <c r="E442" s="27">
-        <v>-116.25</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C442" s="28"/>
+      <c r="D442" s="29"/>
+      <c r="E442" s="28"/>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="23" t="s">
@@ -12933,16 +12939,16 @@
         <v>638</v>
       </c>
       <c r="B636" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C636" s="25">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D636" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E636" s="27">
-        <v>22.8</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -13021,13 +13027,13 @@
         <v>38</v>
       </c>
       <c r="C641" s="25">
-        <v>18.5</v>
+        <v>40.5</v>
       </c>
       <c r="D641" s="26">
         <v>5</v>
       </c>
       <c r="E641" s="27">
-        <v>92.5</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -13227,16 +13233,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C654" s="25">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D654" s="26">
         <v>2.85</v>
       </c>
       <c r="E654" s="27">
-        <v>253.65</v>
+        <v>259.35000000000002</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13894,10 +13900,10 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C695" s="25">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="D695" s="29"/>
       <c r="E695" s="28"/>
@@ -14161,9 +14167,15 @@
       <c r="B716" s="24">
         <v>15</v>
       </c>
-      <c r="C716" s="28"/>
-      <c r="D716" s="29"/>
-      <c r="E716" s="28"/>
+      <c r="C716" s="25">
+        <v>61</v>
+      </c>
+      <c r="D716" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="E716" s="27">
+        <v>97.6</v>
+      </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" s="23" t="s">
@@ -14182,7 +14194,7 @@
         <v>18</v>
       </c>
       <c r="C718" s="25">
-        <v>176</v>
+        <v>400</v>
       </c>
       <c r="D718" s="29"/>
       <c r="E718" s="28"/>
@@ -14431,11 +14443,11 @@
       </c>
       <c r="B735" s="31"/>
       <c r="C735" s="32">
-        <v>44780.68</v>
+        <v>45197.68</v>
       </c>
       <c r="D735" s="33"/>
       <c r="E735" s="34">
-        <v>105656.11</v>
+        <v>106026.54</v>
       </c>
     </row>
   </sheetData>
@@ -14451,6 +14463,6 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -3543,16 +3543,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50" s="25">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>116.2</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C61" s="25">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1247.58</v>
+        <v>1240.74</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3962,16 +3962,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C75" s="25">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3979,16 +3979,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C76" s="25">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>596.4</v>
+        <v>584.4</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4013,16 +4013,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C78" s="25">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>472.8</v>
+        <v>460.8</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4611,10 +4611,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C116" s="25">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4970,16 +4970,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C141" s="25">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="D141" s="26">
         <v>18.5</v>
       </c>
       <c r="E141" s="27">
-        <v>249.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5957,16 +5957,16 @@
         <v>204</v>
       </c>
       <c r="B202" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C202" s="25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D202" s="26">
         <v>2.85</v>
       </c>
       <c r="E202" s="27">
-        <v>57</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -6127,16 +6127,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C212" s="25">
-        <v>363</v>
+        <v>356.5</v>
       </c>
       <c r="D212" s="26">
         <v>2.7</v>
       </c>
       <c r="E212" s="27">
-        <v>980.1</v>
+        <v>962.55</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6297,16 +6297,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C222" s="25">
-        <v>5.53</v>
+        <v>4.53</v>
       </c>
       <c r="D222" s="26">
         <v>3.16</v>
       </c>
       <c r="E222" s="27">
-        <v>17.48</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6716,16 +6716,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C249" s="25">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D249" s="26">
         <v>3.9</v>
       </c>
       <c r="E249" s="27">
-        <v>709.8</v>
+        <v>698.1</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6992,16 +6992,16 @@
         <v>269</v>
       </c>
       <c r="B267" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C267" s="25">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D267" s="26">
         <v>3.1</v>
       </c>
       <c r="E267" s="27">
-        <v>96.1</v>
+        <v>89.9</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -7206,16 +7206,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C281" s="25">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="D281" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E281" s="27">
-        <v>434.8</v>
+        <v>432.43</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -8026,16 +8026,16 @@
         <v>333</v>
       </c>
       <c r="B331" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C331" s="25">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D331" s="26">
         <v>7.97</v>
       </c>
       <c r="E331" s="27">
-        <v>175.37</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -8071,16 +8071,16 @@
         <v>336</v>
       </c>
       <c r="B334" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C334" s="25">
-        <v>46.5</v>
+        <v>43.5</v>
       </c>
       <c r="D334" s="26">
         <v>9</v>
       </c>
       <c r="E334" s="27">
-        <v>418.5</v>
+        <v>391.5</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -8712,16 +8712,16 @@
         <v>375</v>
       </c>
       <c r="B373" s="24">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C373" s="25">
-        <v>78.83</v>
+        <v>76.83</v>
       </c>
       <c r="D373" s="26">
         <v>4.5</v>
       </c>
       <c r="E373" s="27">
-        <v>354.74</v>
+        <v>345.74</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8763,16 +8763,16 @@
         <v>378</v>
       </c>
       <c r="B376" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C376" s="25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D376" s="26">
         <v>8.25</v>
       </c>
       <c r="E376" s="27">
-        <v>231</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -8848,16 +8848,16 @@
         <v>383</v>
       </c>
       <c r="B381" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C381" s="25">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D381" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E381" s="27">
-        <v>229.5</v>
+        <v>219.3</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -9191,16 +9191,16 @@
         <v>404</v>
       </c>
       <c r="B402" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C402" s="25">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="D402" s="26">
         <v>7</v>
       </c>
       <c r="E402" s="27">
-        <v>122.5</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -11149,16 +11149,16 @@
         <v>528</v>
       </c>
       <c r="B526" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C526" s="25">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="D526" s="26">
         <v>1.4</v>
       </c>
       <c r="E526" s="27">
-        <v>151.9</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -12112,10 +12112,10 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C583" s="25">
-        <v>1</v>
+        <v>-49</v>
       </c>
       <c r="D583" s="29"/>
       <c r="E583" s="28"/>
@@ -12168,10 +12168,10 @@
         <v>589</v>
       </c>
       <c r="B587" s="24">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C587" s="25">
-        <v>372.5</v>
+        <v>362.5</v>
       </c>
       <c r="D587" s="29"/>
       <c r="E587" s="28"/>
@@ -12250,16 +12250,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C593" s="25">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D593" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E593" s="27">
-        <v>447.76</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -12854,16 +12854,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C631" s="25">
-        <v>28.5</v>
+        <v>23.5</v>
       </c>
       <c r="D631" s="26">
         <v>4</v>
       </c>
       <c r="E631" s="27">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -14299,16 +14299,16 @@
         <v>728</v>
       </c>
       <c r="B726" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C726" s="25">
-        <v>23.75</v>
+        <v>22.75</v>
       </c>
       <c r="D726" s="26">
         <v>2.5</v>
       </c>
       <c r="E726" s="27">
-        <v>59.38</v>
+        <v>56.88</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
@@ -14443,11 +14443,11 @@
       </c>
       <c r="B735" s="31"/>
       <c r="C735" s="32">
-        <v>45197.68</v>
+        <v>44995.68</v>
       </c>
       <c r="D735" s="33"/>
       <c r="E735" s="34">
-        <v>106026.54</v>
+        <v>105660.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC)</t>
+    <t>.1001 PATRIKA (25/251)</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA (25/262)</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA (25/261)</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA (25/361/861)</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA (25/362/862)</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA (25/282)</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA (25/281)</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC) (2595 PINK)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB)</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G)</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU)</t>
+    <t>1010 PATRIKA (6321)</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA (11043 OFFSET)</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA (1011 OFFSET)</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA (1014 OFFSET)</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA (1222 SBC)</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA (1235)</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA (2101 VV)</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC) (25409)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA (25418)</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA (25322)</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA (25323)</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC) (1173 SBC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC) (5346)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC) (2596)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA (1042)</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA (1043)</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA (GOPAL 11)</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA (GOPAL 1)</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA (2002 YLW)</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA (2003 R)</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA (276-A)</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW (25419)</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED (25420)</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y (25421)</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R (25422)</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA (277-B)</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA (1819 MONARCH)</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN (1709)</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155) (1155 JSK)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908 (NEW SAVASHREE 52)</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51) (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52) (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53) (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54) (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R) (120 GSM RED)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01) (JCC 01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02) (JCC 02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU) (BP RED)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M)</t>
+    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA (LEGACY - 10)</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA (LEGACY - 11)</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA (LEGACY - 12)</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (LOTTERY - 80)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -551,1234 +551,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA (FRIDAY )</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (TUESDAY)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc'''</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV)</t>
+    <t>4251 PATRIKA (JC) (5342)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA (5207)</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA (5206)</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210) (10273/10277)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA (82)</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC) (1129)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC) (101 SBC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA (1102)</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC) (959)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC) (2571)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU) (1351)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA (83)</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA (25-145)</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC) (25-046)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA (111 SBC)</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA (1151 GGN)</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC) (25216)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA (2547)</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC) (25369)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA (25367)</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA (25368)</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA (1031)</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA (25301)</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA (25312 MYRA)</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA (3117)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN) (3116)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA (1173 VV)</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA (5254  RJN)</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA (25402)</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA (10001 NEW)</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA (10002 NEW)</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA (316 MYRA)</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA (25401)</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA (25311)</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA (25312)</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA (5273)</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA (286-A)</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA (1407)</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA (306)</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA (5501)</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA (2011)</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA (25314)</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA (25315)</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU) (1402)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC) (1234*-M)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA (5172)</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA (25313)</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA (BALAJI 5202)</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA (LOTUS 430)</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU) (251 KBC)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU) (273-A)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M) (5087)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA (5295)</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA (5213)</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M) (25/162)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA (25/272)</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC) (25/271)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (FRIDAY ) (25/171)</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA (8802)</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA (8803)</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC) (7713)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU) (1405)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA (7705)</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA (2522 GE)</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA (2517 GE)</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA (2527)</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA (2536)</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC) (S-301)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU) (S-305)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC) (1103)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी) (741)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA (5347 DIRECT)</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M) (3161)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA (1151 VV)</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC) (25-082)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC) (3701 SBC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA (2081)</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA (296-A (NEHA)</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA (2501 GE NEW)</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA (2520 GE)</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA (5267)</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA (5258 RJ)</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA (2023)</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC) (2206)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA (25214)</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA (2061 SBC)</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA (5236 RJ)</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC) (1411 KBC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA (5350)</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA (5251)</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA (5240)</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA (25316)</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA (25321)</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M) (857)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU) (5339)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021) (2456)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA (2071)</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA (5261 RJND)</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC) (5335)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA (253-A / 257-A)</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA (5356 RJ)</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA (5333)</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA (5308)</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC) (AS-402)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC) (5313)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA (5305)</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA (2031)</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU) (3331)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU) (25436)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA (5186)</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC) (7033)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M) (25/122)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC) (8055 VV)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC) (612 VV)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC) (25/072)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC) (2525 /2552)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA (2515)</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU) (2542)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA (2523)</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M) (7066)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA (1054)</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA (2231)</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA (2232)</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU) (5382)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M) (5283)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC) (25-052)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B (2942-B)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC) (2942)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M) (S-96)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC) (2101)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA (2261)</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA (2353)</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M) (2732)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA (718)</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M) (S-32)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU) (2792)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA (5261 NICE)</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M) (5424)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA (5231)</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M) (5004)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G) (5379)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA (2903)</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M) (2952)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA (2312 SBC)</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA (2293)</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-* (2915)</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M) (25358)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA (5387)</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA (175)</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M) (1742-B)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA (1679)</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M) (3002)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M) (S-39)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M) (S-74)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M) (25353)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M) (25351)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA (2205)</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA (25335)</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M) (S-77)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA (2531)</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M) (5808)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA (S-326)</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M) (3471)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA (3211 SBC)</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC) (2202 SBC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M) (S-51)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA (2264)</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M) (25133)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA (3131 SBC)</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M) (2365)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA (2803)</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC) (2931)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M) (226)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M) (2541)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M) (77-B)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC) (25324)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA (2771)</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA (3271)</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M) (6125)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA (242-A)</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC) (3102)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M) (221-A)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA (25442)</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA (25440)</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA (993)</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC) (2373)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M) (1211)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU) (5276)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA (2111)</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU) (7069)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M) (7067)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC) (1131)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC) (15)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M) (25337)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA (064)</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC) (2753)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU) (772)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU) (GOL)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L) (5164)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA (5126)</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA (5111)</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M) (5196)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA (5191)</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R (3023)</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M) (TUESDAY) (0523)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA (95)</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M) (3053)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M) (3019)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC) (3017 VV)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA (3015)</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (25164)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU) (25131)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M) (3422)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M) (1193)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA (25184)</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M) (25135)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M) (25116)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M) (25161)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M) (25111)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU) (932)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA (3562)</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M) (S-313)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M) (25183)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA (25162 GE)</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M) (3014)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (2291)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B) (2291-B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M) (25380)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU) (25132)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M) (3031)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M) (3034)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M) (25382)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M) (3402)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC (3431)</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA (3421)</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M) (3461)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M) (5319)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA (25193 (Padding))</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA (25194 (Padding))</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M) (1281)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA (3424)</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA (7103 (PADDING))</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M) (5823)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU) (8102)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU) (6197)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M) (1868-B)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M) (1868)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M) (1872)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M) (6132)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU) (6196)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU) (1503)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M) (1282)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU) (533 KBC)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.) (133)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.) (1522)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.) (1178)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.) (AS-20)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.) (4087)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.) (2204)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.) (2482)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.) (12)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA (25/252)</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA (25/264-263)</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA (25/363/863)</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA (25/283)</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA (25/273)</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA (25/172)</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU) (25895)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA (2521)</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA (2526)</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA (2535)</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA (84)</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA (2543 INV OFFSET)</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA (2234)</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA (S-201 INV)</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA (5121)</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA (720)</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F) (25-146)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA (3702)</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA (254 SBC)</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F) (25-047)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA (2082)</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-* (4052)</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA (2103)</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA (1223 SBC)</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA (6310 GE)</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA (2532)</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA (1174)</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA (1034)</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA (2204 INV)</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA (06)</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA (303)</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA (25323 INV)</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA (25413)</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA (2597)</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA (25896)</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F) (243-C)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA (1855)</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA (1044 SBC)</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA (2014)</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA (2006)</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU) (6106)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA (GOPAL 32)</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA (2005- G)</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA (5180)</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU) (3753)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA (273 NEHA)</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA (278-B)</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1790,7 +1790,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.)</t>
+    <t>9001 CARD (O.C.) (2498 Cream)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1814,298 +1814,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS</t>
-  </si>
-  <si>
-    <t>9240 CARDS</t>
-  </si>
-  <si>
-    <t>9241 CARDS</t>
-  </si>
-  <si>
-    <t>9242 CARDS</t>
-  </si>
-  <si>
-    <t>9243 CARDS</t>
-  </si>
-  <si>
-    <t>9244 CARDS</t>
-  </si>
-  <si>
-    <t>9301 CARDS</t>
-  </si>
-  <si>
-    <t>9302 CARDS</t>
-  </si>
-  <si>
-    <t>9303 CARDS</t>
-  </si>
-  <si>
-    <t>9304 CARDS</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070)</t>
-  </si>
-  <si>
-    <t>9306 CARDS</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M)</t>
-  </si>
-  <si>
-    <t>9308 CARDS</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc)</t>
-  </si>
-  <si>
-    <t>9310 CARDS</t>
-  </si>
-  <si>
-    <t>9311 CARDS</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9314 CARDS</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (Aa Gya )</t>
-  </si>
-  <si>
-    <t>9318 CARDS</t>
-  </si>
-  <si>
-    <t>9319 CARDS</t>
-  </si>
-  <si>
-    <t>9320 CARDS</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD)</t>
-  </si>
-  <si>
-    <t>9324 CARDS</t>
-  </si>
-  <si>
-    <t>9325 CARDS</t>
-  </si>
-  <si>
-    <t>9326 CARDS</t>
-  </si>
-  <si>
-    <t>9327 CARDS</t>
-  </si>
-  <si>
-    <t>9328 CARDS</t>
-  </si>
-  <si>
-    <t>9329 CARDS</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC</t>
-  </si>
-  <si>
-    <t>9333 CARDS</t>
-  </si>
-  <si>
-    <t>9334 CARDS</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD)</t>
-  </si>
-  <si>
-    <t>9336 CARDS</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC)</t>
-  </si>
-  <si>
-    <t>9338 CARDS</t>
-  </si>
-  <si>
-    <t>9339 CARDS</t>
-  </si>
-  <si>
-    <t>9340 CARDS</t>
-  </si>
-  <si>
-    <t>9341 CARDS</t>
-  </si>
-  <si>
-    <t>9342 CARDS</t>
-  </si>
-  <si>
-    <t>9343 CARDS</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu)</t>
-  </si>
-  <si>
-    <t>9345 CARDS</t>
-  </si>
-  <si>
-    <t>9346 CARDS</t>
-  </si>
-  <si>
-    <t>9347 CARDS</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T) (1000 19.02)</t>
-  </si>
-  <si>
-    <t>9351 Card - B</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9353 CARDS</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9355 CARDS</t>
-  </si>
-  <si>
-    <t>9356 CARDS</t>
-  </si>
-  <si>
-    <t>9357 CARDS</t>
-  </si>
-  <si>
-    <t>9358 CARDS</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega</t>
-  </si>
-  <si>
-    <t>9361 CARDS</t>
-  </si>
-  <si>
-    <t>9362 CARDS</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9365 CARDS</t>
-  </si>
-  <si>
-    <t>9366 CARDS</t>
-  </si>
-  <si>
-    <t>9367 CARDS</t>
-  </si>
-  <si>
-    <t>9368 CARDS</t>
-  </si>
-  <si>
-    <t>9369 CARDS</t>
-  </si>
-  <si>
-    <t>9370 CARDS</t>
-  </si>
-  <si>
-    <t>9371 CARDS</t>
-  </si>
-  <si>
-    <t>9372 CARDS</t>
-  </si>
-  <si>
-    <t>9373 CARDS</t>
-  </si>
-  <si>
-    <t>9374 CARDS</t>
-  </si>
-  <si>
-    <t>9375 CARDS</t>
-  </si>
-  <si>
-    <t>9376 CARDS</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9378 CARDS</t>
+    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
+  </si>
+  <si>
+    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
+  </si>
+  <si>
+    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
+  </si>
+  <si>
+    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
+  </si>
+  <si>
+    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9301 CARDS (4242)</t>
+  </si>
+  <si>
+    <t>9302 CARDS (5076)</t>
+  </si>
+  <si>
+    <t>9303 CARDS (5080 Pink)</t>
+  </si>
+  <si>
+    <t>9304 CARDS (5083 Blue)</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070) (4701 Nice)</t>
+  </si>
+  <si>
+    <t>9306 CARDS (0543 Nice)</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M) (5243 Nice)</t>
+  </si>
+  <si>
+    <t>9308 CARDS (9852)</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
+  </si>
+  <si>
+    <t>9310 CARDS (3103)</t>
+  </si>
+  <si>
+    <t>9311 CARDS (3115)</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T) (208 VV)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T) (216)</t>
+  </si>
+  <si>
+    <t>9314 CARDS (P-1)</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU) (P-2)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU) (P-3)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (Aa Gya ) (P-4)</t>
+  </si>
+  <si>
+    <t>9318 CARDS (25905)</t>
+  </si>
+  <si>
+    <t>9319 CARDS (25906)</t>
+  </si>
+  <si>
+    <t>9320 CARDS (S-20)</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9325 CARDS (5229)</t>
+  </si>
+  <si>
+    <t>9326 CARDS (1601)</t>
+  </si>
+  <si>
+    <t>9327 CARDS (25908)</t>
+  </si>
+  <si>
+    <t>9328 CARDS (2543)</t>
+  </si>
+  <si>
+    <t>9329 CARDS (3606)</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T) (9557)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T) (9560)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC (9847)</t>
+  </si>
+  <si>
+    <t>9333 CARDS (6042)</t>
+  </si>
+  <si>
+    <t>9334 CARDS (10X6 WHITE (2898))</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
+  </si>
+  <si>
+    <t>9336 CARDS (2884)</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC) (1635 AP)</t>
+  </si>
+  <si>
+    <t>9338 CARDS (1637 AP)</t>
+  </si>
+  <si>
+    <t>9339 CARDS (5361)</t>
+  </si>
+  <si>
+    <t>9340 CARDS (5658)</t>
+  </si>
+  <si>
+    <t>9341 CARDS (5497)</t>
+  </si>
+  <si>
+    <t>9342 CARDS (2861)</t>
+  </si>
+  <si>
+    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu) (689)</t>
+  </si>
+  <si>
+    <t>9345 CARDS (358 KALYANI)</t>
+  </si>
+  <si>
+    <t>9346 CARDS (359)</t>
+  </si>
+  <si>
+    <t>9347 CARDS (2853)</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी) (S-124)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window) (S-120)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1000 19.02) (1632)</t>
+  </si>
+  <si>
+    <t>9351 Card - B (1603 B)</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC (1603)</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
+  </si>
+  <si>
+    <t>9353 CARDS (1618)</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU) (345)</t>
+  </si>
+  <si>
+    <t>9355 CARDS (1624)</t>
+  </si>
+  <si>
+    <t>9356 CARDS (2895/2897)</t>
+  </si>
+  <si>
+    <t>9357 CARDS (2872)</t>
+  </si>
+  <si>
+    <t>9358 CARDS (WHITE PATTA)</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
+  </si>
+  <si>
+    <t>9361 CARDS (25426)</t>
+  </si>
+  <si>
+    <t>9362 CARDS (363)</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T) (1652)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T) (1612)</t>
+  </si>
+  <si>
+    <t>9365 CARDS (25429)</t>
+  </si>
+  <si>
+    <t>9366 CARDS (25427 GOLDEN)</t>
+  </si>
+  <si>
+    <t>9367 CARDS (5652)</t>
+  </si>
+  <si>
+    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
+  </si>
+  <si>
+    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
+  </si>
+  <si>
+    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
+  </si>
+  <si>
+    <t>9371 CARDS (3111 VP)</t>
+  </si>
+  <si>
+    <t>9372 CARDS (9*5 YLW SET (2841))</t>
+  </si>
+  <si>
+    <t>9373 CARDS (1482)</t>
+  </si>
+  <si>
+    <t>9374 CARDS (1485)</t>
+  </si>
+  <si>
+    <t>9375 CARDS (1452 WHITE)</t>
+  </si>
+  <si>
+    <t>9376 CARDS (1529 PRINCE)</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
+  </si>
+  <si>
+    <t>9378 CARDS (2892)</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2138,19 +2138,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU)</t>
+    <t>9389 CARDS (9147 RJ)</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU) (118KBC)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC)</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC</t>
+    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2180,7 +2180,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR)</t>
+    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2204,37 +2204,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE</t>
+    <t>RX-01 ENVELOPE (LX01)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (LX02)</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE (LX03)</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE (LX04)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (LX05)</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE (LX06)</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE (LX07)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (LX08)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (LX09)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर</t>
+    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2764,7 +2764,7 @@
   <dimension ref="A1:E735"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -3628,16 +3628,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" s="25">
-        <v>43.25</v>
+        <v>38.25</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>118.94</v>
+        <v>105.19</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -4132,16 +4132,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C85" s="25">
-        <v>1457</v>
+        <v>1450.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1894.1</v>
+        <v>1885.65</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4805,13 +4805,13 @@
         <v>33</v>
       </c>
       <c r="C131" s="25">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="D131" s="26">
         <v>12.5</v>
       </c>
       <c r="E131" s="27">
-        <v>93.75</v>
+        <v>218.75</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4822,13 +4822,13 @@
         <v>57</v>
       </c>
       <c r="C132" s="25">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>31.25</v>
+        <v>218.75</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4924,13 +4924,13 @@
         <v>36</v>
       </c>
       <c r="C138" s="25">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="D138" s="26">
-        <v>12.78</v>
+        <v>12.75</v>
       </c>
       <c r="E138" s="27">
-        <v>83.06</v>
+        <v>210.37</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5123,16 +5123,16 @@
         <v>152</v>
       </c>
       <c r="B150" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C150" s="25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D150" s="26">
         <v>18.5</v>
       </c>
       <c r="E150" s="27">
-        <v>55.5</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -6127,16 +6127,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C212" s="25">
-        <v>356.5</v>
+        <v>351.5</v>
       </c>
       <c r="D212" s="26">
         <v>2.7</v>
       </c>
       <c r="E212" s="27">
-        <v>962.55</v>
+        <v>949.05</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -8091,13 +8091,13 @@
         <v>20</v>
       </c>
       <c r="C335" s="25">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="D335" s="26">
         <v>9</v>
       </c>
       <c r="E335" s="27">
-        <v>22.5</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -8108,13 +8108,13 @@
         <v>39</v>
       </c>
       <c r="C336" s="25">
-        <v>11</v>
+        <v>33.5</v>
       </c>
       <c r="D336" s="26">
         <v>9</v>
       </c>
       <c r="E336" s="27">
-        <v>99</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -12181,10 +12181,10 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C588" s="25">
-        <v>210.5</v>
+        <v>208.5</v>
       </c>
       <c r="D588" s="29"/>
       <c r="E588" s="28"/>
@@ -14443,11 +14443,11 @@
       </c>
       <c r="B735" s="31"/>
       <c r="C735" s="32">
-        <v>44995.68</v>
+        <v>45053.68</v>
       </c>
       <c r="D735" s="33"/>
       <c r="E735" s="34">
-        <v>105660.58</v>
+        <v>106476.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -2954,16 +2954,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="25">
-        <v>63</v>
+        <v>60.5</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" s="25">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>85.68</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3543,16 +3543,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" s="25">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>103.6</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -4013,16 +4013,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C78" s="25">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>460.8</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4535,10 +4535,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C110" s="25">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -5327,16 +5327,16 @@
         <v>164</v>
       </c>
       <c r="B162" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C162" s="25">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D162" s="26">
         <v>11.5</v>
       </c>
       <c r="E162" s="27">
-        <v>69</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -6093,16 +6093,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C210" s="25">
-        <v>141</v>
+        <v>140.5</v>
       </c>
       <c r="D210" s="26">
         <v>3.93</v>
       </c>
       <c r="E210" s="27">
-        <v>553.84</v>
+        <v>551.88</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6178,16 +6178,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C215" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D215" s="26">
         <v>4.5</v>
       </c>
       <c r="E215" s="27">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6314,16 +6314,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C223" s="25">
-        <v>141.5</v>
+        <v>140</v>
       </c>
       <c r="D223" s="26">
         <v>2.66</v>
       </c>
       <c r="E223" s="27">
-        <v>376.39</v>
+        <v>372.4</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6416,16 +6416,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C229" s="25">
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="D229" s="26">
         <v>3.5</v>
       </c>
       <c r="E229" s="27">
-        <v>222.25</v>
+        <v>215.25</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -7464,13 +7464,13 @@
         <v>12</v>
       </c>
       <c r="C296" s="25">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D296" s="26">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="E296" s="27">
-        <v>60.32</v>
+        <v>276.44</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -8133,16 +8133,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C338" s="25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8831,16 +8831,16 @@
         <v>382</v>
       </c>
       <c r="B380" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C380" s="25">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D380" s="26">
         <v>6</v>
       </c>
       <c r="E380" s="27">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -9805,11 +9805,17 @@
         <v>444</v>
       </c>
       <c r="B442" s="24">
-        <v>4</v>
-      </c>
-      <c r="C442" s="28"/>
-      <c r="D442" s="29"/>
-      <c r="E442" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="C442" s="25">
+        <v>-7.5</v>
+      </c>
+      <c r="D442" s="26">
+        <v>15.5</v>
+      </c>
+      <c r="E442" s="27">
+        <v>-116.25</v>
+      </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="23" t="s">
@@ -11383,16 +11389,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C540" s="25">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="D540" s="26">
         <v>2</v>
       </c>
       <c r="E540" s="27">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11655,16 +11661,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C556" s="25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D556" s="26">
         <v>1.8</v>
       </c>
       <c r="E556" s="27">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11774,16 +11780,16 @@
         <v>565</v>
       </c>
       <c r="B563" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C563" s="25">
-        <v>86.25</v>
+        <v>85.25</v>
       </c>
       <c r="D563" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E563" s="27">
-        <v>198.38</v>
+        <v>196.08</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -12250,16 +12256,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C593" s="25">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D593" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E593" s="27">
-        <v>447.18</v>
+        <v>446.02</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -13366,13 +13372,13 @@
         <v>38</v>
       </c>
       <c r="C662" s="25">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="D662" s="26">
         <v>4.8</v>
       </c>
       <c r="E662" s="27">
-        <v>36</v>
+        <v>84</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -13604,13 +13610,13 @@
         <v>7</v>
       </c>
       <c r="C676" s="25">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D676" s="26">
         <v>5.75</v>
       </c>
       <c r="E676" s="27">
-        <v>5.75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13652,16 +13658,16 @@
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C679" s="25">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="D679" s="26">
         <v>2.25</v>
       </c>
       <c r="E679" s="27">
-        <v>264.38</v>
+        <v>259.88</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13844,16 +13850,16 @@
         <v>693</v>
       </c>
       <c r="B691" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C691" s="25">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="D691" s="26">
         <v>3.6</v>
       </c>
       <c r="E691" s="27">
-        <v>106.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
@@ -14204,16 +14210,16 @@
         <v>721</v>
       </c>
       <c r="B719" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C719" s="25">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D719" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E719" s="27">
-        <v>66.12</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
@@ -14443,11 +14449,11 @@
       </c>
       <c r="B735" s="31"/>
       <c r="C735" s="32">
-        <v>45053.68</v>
+        <v>45065.18</v>
       </c>
       <c r="D735" s="33"/>
       <c r="E735" s="34">
-        <v>106476.19</v>
+        <v>106542.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -3801,16 +3801,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C65" s="25">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>559.35</v>
+        <v>554.4</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4135,16 +4135,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C85" s="25">
-        <v>1446.5</v>
+        <v>1444.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1880.45</v>
+        <v>1877.85</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4822,16 +4822,16 @@
         <v>134</v>
       </c>
       <c r="B132" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C132" s="25">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>218.75</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5561,16 +5561,16 @@
         <v>179</v>
       </c>
       <c r="B177" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C177" s="25">
-        <v>56.5</v>
+        <v>53</v>
       </c>
       <c r="D177" s="26">
         <v>2.7</v>
       </c>
       <c r="E177" s="27">
-        <v>152.55000000000001</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -6475,16 +6475,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C233" s="25">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>152.75</v>
+        <v>146.25</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -13517,16 +13517,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C671" s="25">
-        <v>26.43</v>
+        <v>25.43</v>
       </c>
       <c r="D671" s="26">
         <v>3.6</v>
       </c>
       <c r="E671" s="27">
-        <v>95.15</v>
+        <v>91.55</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -14461,11 +14461,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45306.18</v>
+        <v>45291.68</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>106667.09</v>
+        <v>106602.49</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -770,7 +770,7 @@
     <t>5056 PATRIKA (JC) (25/271)</t>
   </si>
   <si>
-    <t>5057 PATRIKA (FRIDAY ) (25/171)</t>
+    <t>5057 PATRIKA (25/171)</t>
   </si>
   <si>
     <t>5058 PATRIKA (8802)</t>
@@ -1412,7 +1412,7 @@
     <t>6625 PATRIKA *-* (M) (25116)</t>
   </si>
   <si>
-    <t>6626 PATRIKA *-* (M) (25161)</t>
+    <t>6626 PATRIKA *-* (M) (Alter Available) (25161)</t>
   </si>
   <si>
     <t>6627 PATRIKA *-* (M) (25111)</t>
@@ -1517,7 +1517,7 @@
     <t>6659 PATRIKA (25193 (Padding))</t>
   </si>
   <si>
-    <t>6660 PATRIKA (25194 (Padding))</t>
+    <t>6660 PATRIKA (200 26.02) (25194 (Padding))</t>
   </si>
   <si>
     <t>6661 PATRIKA *-* (M) (1281)</t>
@@ -1973,7 +1973,7 @@
     <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
   </si>
   <si>
-    <t>9336 CARDS (2884)</t>
+    <t>9336 CARDS (Design Change) (2884)</t>
   </si>
   <si>
     <t>9337 CARDS (DC) (1635 AP)</t>
@@ -2899,13 +2899,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="20">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="C15" s="21">
         <v>2</v>
       </c>
       <c r="D15" s="22">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3025,13 +3025,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="20">
-        <v>4.5</v>
+        <v>52.5</v>
       </c>
       <c r="C24" s="21">
         <v>1.8</v>
       </c>
       <c r="D24" s="22">
-        <v>8.1</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3067,13 +3067,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="20">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="C27" s="21">
         <v>2</v>
       </c>
       <c r="D27" s="22">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3081,13 +3081,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C28" s="21">
         <v>2</v>
       </c>
       <c r="D28" s="22">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3123,13 +3123,13 @@
         <v>31</v>
       </c>
       <c r="B31" s="20">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" s="21">
         <v>2.85</v>
       </c>
       <c r="D31" s="22">
-        <v>193.8</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3173,13 +3173,13 @@
         <v>35</v>
       </c>
       <c r="B35" s="20">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="21">
         <v>2.2999999999999998</v>
       </c>
       <c r="D35" s="22">
-        <v>172.5</v>
+        <v>170.2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3671,13 +3671,13 @@
         <v>71</v>
       </c>
       <c r="B71" s="20">
-        <v>61.5</v>
+        <v>56.5</v>
       </c>
       <c r="C71" s="21">
         <v>1.4</v>
       </c>
       <c r="D71" s="22">
-        <v>86.1</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -4605,13 +4605,13 @@
         <v>145</v>
       </c>
       <c r="B145" s="20">
-        <v>12.27</v>
+        <v>11.77</v>
       </c>
       <c r="C145" s="21">
         <v>18.5</v>
       </c>
       <c r="D145" s="22">
-        <v>227</v>
+        <v>217.75</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4661,13 +4661,13 @@
         <v>149</v>
       </c>
       <c r="B149" s="20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="C149" s="21">
         <v>18.5</v>
       </c>
       <c r="D149" s="22">
-        <v>240.5</v>
+        <v>231.25</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4963,7 +4963,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="20">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C171" s="24"/>
       <c r="D171" s="23"/>
@@ -5964,9 +5964,15 @@
       <c r="A248" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="23"/>
-      <c r="C248" s="24"/>
-      <c r="D248" s="23"/>
+      <c r="B248" s="20">
+        <v>113</v>
+      </c>
+      <c r="C248" s="21">
+        <v>3.8</v>
+      </c>
+      <c r="D248" s="22">
+        <v>429.4</v>
+      </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="19" t="s">
@@ -6465,13 +6471,13 @@
         <v>288</v>
       </c>
       <c r="B288" s="20">
-        <v>-12.75</v>
+        <v>26.25</v>
       </c>
       <c r="C288" s="21">
-        <v>5.93</v>
+        <v>5.97</v>
       </c>
       <c r="D288" s="22">
-        <v>-75.55</v>
+        <v>156.71</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,13 +6815,13 @@
         <v>313</v>
       </c>
       <c r="B313" s="20">
-        <v>10.95</v>
+        <v>46.95</v>
       </c>
       <c r="C313" s="21">
         <v>9.4499999999999993</v>
       </c>
       <c r="D313" s="22">
-        <v>103.48</v>
+        <v>443.68</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6973,13 +6979,13 @@
         <v>326</v>
       </c>
       <c r="B326" s="20">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="C326" s="21">
         <v>10</v>
       </c>
       <c r="D326" s="22">
-        <v>125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -7439,13 +7445,13 @@
         <v>361</v>
       </c>
       <c r="B361" s="20">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C361" s="21">
         <v>7.76</v>
       </c>
       <c r="D361" s="22">
-        <v>302.58</v>
+        <v>294.82</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7551,13 +7557,13 @@
         <v>369</v>
       </c>
       <c r="B369" s="20">
-        <v>117.5</v>
+        <v>116</v>
       </c>
       <c r="C369" s="21">
         <v>6.6</v>
       </c>
       <c r="D369" s="22">
-        <v>775.5</v>
+        <v>765.6</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -7929,13 +7935,13 @@
         <v>396</v>
       </c>
       <c r="B396" s="20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C396" s="21">
         <v>8.5500000000000007</v>
       </c>
       <c r="D396" s="22">
-        <v>59.85</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -8229,13 +8235,13 @@
         <v>420</v>
       </c>
       <c r="B420" s="20">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="C420" s="21">
         <v>6.46</v>
       </c>
       <c r="D420" s="22">
-        <v>9.69</v>
+        <v>74.290000000000006</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -8507,13 +8513,13 @@
         <v>442</v>
       </c>
       <c r="B442" s="20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C442" s="21">
         <v>9.75</v>
       </c>
       <c r="D442" s="22">
-        <v>126.75</v>
+        <v>117</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -8933,13 +8939,13 @@
         <v>474</v>
       </c>
       <c r="B474" s="20">
-        <v>13.5</v>
+        <v>30.5</v>
       </c>
       <c r="C474" s="21">
         <v>9.5</v>
       </c>
       <c r="D474" s="22">
-        <v>128.25</v>
+        <v>289.75</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -9117,13 +9123,13 @@
         <v>488</v>
       </c>
       <c r="B488" s="20">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="C488" s="21">
         <v>9</v>
       </c>
       <c r="D488" s="22">
-        <v>49.5</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -9236,9 +9242,15 @@
       <c r="A497" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="B497" s="23"/>
-      <c r="C497" s="24"/>
-      <c r="D497" s="23"/>
+      <c r="B497" s="20">
+        <v>-2</v>
+      </c>
+      <c r="C497" s="21">
+        <v>55</v>
+      </c>
+      <c r="D497" s="22">
+        <v>-110</v>
+      </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="19" t="s">
@@ -9717,13 +9729,13 @@
         <v>533</v>
       </c>
       <c r="B533" s="20">
-        <v>46.5</v>
+        <v>53.5</v>
       </c>
       <c r="C533" s="21">
         <v>3.8</v>
       </c>
       <c r="D533" s="22">
-        <v>176.7</v>
+        <v>203.3</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
@@ -10917,13 +10929,13 @@
         <v>624</v>
       </c>
       <c r="B624" s="20">
-        <v>23.85</v>
+        <v>22.85</v>
       </c>
       <c r="C624" s="21">
         <v>4</v>
       </c>
       <c r="D624" s="22">
-        <v>95.4</v>
+        <v>91.4</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
@@ -11260,9 +11272,15 @@
       <c r="A649" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="B649" s="23"/>
-      <c r="C649" s="24"/>
-      <c r="D649" s="23"/>
+      <c r="B649" s="20">
+        <v>35</v>
+      </c>
+      <c r="C649" s="21">
+        <v>3.33</v>
+      </c>
+      <c r="D649" s="22">
+        <v>116.55</v>
+      </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="19" t="s">
@@ -11325,13 +11343,13 @@
         <v>654</v>
       </c>
       <c r="B654" s="20">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="C654" s="21">
         <v>6.25</v>
       </c>
       <c r="D654" s="22">
-        <v>56.25</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
@@ -12093,13 +12111,13 @@
         <v>717</v>
       </c>
       <c r="B717" s="20">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C717" s="21">
         <v>1.6</v>
       </c>
       <c r="D717" s="22">
-        <v>97.6</v>
+        <v>81.599999999999994</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
@@ -12115,7 +12133,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="20">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C719" s="24"/>
       <c r="D719" s="23"/>
@@ -12125,13 +12143,13 @@
         <v>720</v>
       </c>
       <c r="B720" s="20">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C720" s="21">
         <v>1.1599999999999999</v>
       </c>
       <c r="D720" s="22">
-        <v>63.8</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
@@ -12167,7 +12185,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="20">
-        <v>-90.15</v>
+        <v>-91.15</v>
       </c>
       <c r="C724" s="24"/>
       <c r="D724" s="23"/>
@@ -12315,11 +12333,11 @@
         <v>736</v>
       </c>
       <c r="B736" s="26">
-        <v>45203.68</v>
+        <v>45407.18</v>
       </c>
       <c r="C736" s="27"/>
       <c r="D736" s="28">
-        <v>106383.44</v>
+        <v>107574.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC)</t>
+    <t>.1001 PATRIKA (25/251)</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA (25/262)</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA (25/261)</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA (25/361/861)</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA (25/362/862)</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA (25/282)</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA (25/281)</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC) (2595 PINK)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB)</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G)</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU)</t>
+    <t>1010 PATRIKA (6321)</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA (11043 OFFSET)</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA (1011 OFFSET)</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA (1014 OFFSET)</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA (1222 SBC)</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA (1235)</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA (2101 VV)</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC) (25409)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA (25418)</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA (25322)</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA (25323)</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC) (1173 SBC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC) (5346)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC) (2596)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA (1042)</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA (1043)</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA (GOPAL 11)</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA (GOPAL 1)</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA (2002 YLW)</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA (2003 R)</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA (276-A)</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW (25419)</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED (25420)</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y (25421)</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R (25422)</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA (277-B)</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA (1819 MONARCH)</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN (1709)</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155) (1155 JSK)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908 (NEW SAVASHREE 52)</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51) (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52) (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53) (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54) (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R) (120 GSM RED)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01) (JCC 01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02) (JCC 02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU) (BP RED)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M)</t>
+    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA (LEGACY - 10)</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA (LEGACY - 11)</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA (LEGACY - 12)</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (LOTTERY - 80)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -554,1234 +554,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (TUESDAY)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc'''</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (Alter Available)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA (200 26.02)</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV)</t>
+    <t>4251 PATRIKA (JC) (5342)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA (5207)</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA (5206)</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210) (10273/10277)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA (82)</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC) (1129)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC) (101 SBC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA (1102)</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC) (959)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC) (2571)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU) (1351)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA (83)</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA (25-145)</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC) (25-046)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA (111 SBC)</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA (1151 GGN)</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC) (25216)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA (2547)</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC) (25369)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA (25367)</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA (25368)</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA (1031)</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA (25301)</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA (25312 MYRA)</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA (3117)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN) (3116)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA (1173 VV)</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA (5254  RJN)</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA (25402)</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA (10001 NEW)</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA (10002 NEW)</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA (316 MYRA)</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA (25401)</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA (25311)</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA (25312)</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA (5273)</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA (286-A)</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA (1407)</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA (306)</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA (5501)</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA (2011)</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA (25314)</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA (25315)</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU) (1402)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC) (1234*-M)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA (5172)</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA (25313)</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA (BALAJI 5202)</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA (LOTUS 430)</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU) (251 KBC)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU) (273-A)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M) (5087)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA (5295)</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA (5213)</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M) (25/162)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA (25/272)</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC) (25/271)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (25/171)</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA (8802)</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA (8803)</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC) (7713)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU) (1405)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA (7705)</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA (2522 GE)</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA (2517 GE)</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA (2527)</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA (2536)</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC) (S-301)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU) (S-305)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC) (1103)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी) (741)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA (5347 DIRECT)</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M) (3161)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA (1151 VV)</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC) (25-082)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC) (3701 SBC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA (2081)</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA (296-A (NEHA)</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA (2501 GE NEW)</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA (2520 GE)</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA (5267)</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA (5258 RJ)</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA (2023)</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC) (2206)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA (25214)</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA (2061 SBC)</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA (5236 RJ)</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC) (1411 KBC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA (5350)</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA (5251)</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA (5240)</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA (25316)</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA (25321)</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M) (857)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU) (5339)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021) (2456)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA (2071)</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA (5261 RJND)</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC) (5335)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA (253-A / 257-A)</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA (5356 RJ)</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA (5333)</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA (5308)</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC) (AS-402)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC) (5313)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA (5305)</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA (2031)</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU) (3331)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU) (25436)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA (5186)</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC) (7033)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M) (25/122)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC) (8055 VV)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC) (612 VV)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC) (25/072)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC) (2525 /2552)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA (2515)</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU) (2542)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA (2523)</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M) (7066)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA (1054)</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA (2231)</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA (2232)</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU) (5382)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M) (5283)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC) (25-052)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B (2942-B)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC) (2942)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M) (S-96)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC) (2101)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA (2261)</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA (2353)</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M) (2732)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA (718)</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M) (S-32)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU) (2792)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA (5261 NICE)</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M) (5424)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA (5231)</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M) (5004)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G) (5379)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA (2903)</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M) (2952)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA (2312 SBC)</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA (2293)</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-* (2915)</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M) (25358)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA (5387)</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA (175)</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M) (1742-B)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA (1679)</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M) (3002)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M) (S-39)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M) (S-74)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M) (25353)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M) (25351)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA (2205)</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA (25335)</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M) (S-77)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA (2531)</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M) (5808)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA (S-326)</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M) (3471)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA (3211 SBC)</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC) (2202 SBC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M) (S-51)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA (2264)</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M) (25133)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA (3131 SBC)</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M) (2365)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA (2803)</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC) (2931)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M) (226)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M) (2541)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M) (77-B)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC) (25324)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA (2771)</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA (3271)</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M) (6125)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA (242-A)</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC) (3102)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M) (221-A)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA (25442)</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA (25440)</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA (993)</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC) (2373)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M) (1211)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU) (5276)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA (2111)</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU) (7069)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M) (7067)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC) (1131)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC) (15)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M) (25337)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA (064)</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC) (2753)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU) (772)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU) (GOL)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L) (5164)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA (5126)</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA (5111)</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M) (5196)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA (5191)</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R (3023)</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M) (TUESDAY) (0523)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA (95)</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M) (3053)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M) (3019)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC) (3017 VV)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA (3015)</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (25164)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU) (25131)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M) (3422)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M) (1193)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA (25184)</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M) (25135)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M) (25116)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M) (Alter Available) (25161)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M) (25111)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU) (932)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA (3562)</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M) (S-313)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M) (25183)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA (25162 GE)</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M) (3014)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (2291)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B) (2291-B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M) (25380)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU) (25132)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M) (3031)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M) (3034)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M) (25382)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M) (3402)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC (3431)</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA (3421)</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M) (3461)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M) (5319)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA (25193 (Padding))</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA (200 26.02) (25194 (Padding))</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M) (1281)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA (3424)</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA (7103 (PADDING))</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M) (5823)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU) (8102)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU) (6197)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M) (1868-B)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M) (1868)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M) (1872)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M) (6132)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU) (6196)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU) (1503)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M) (1282)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU) (533 KBC)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.) (133)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.) (1522)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.) (1178)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.) (AS-20)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.) (4087)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.) (2204)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.) (2482)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.) (12)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA (25/252)</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA (25/264-263)</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA (25/363/863)</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA (25/283)</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA (25/273)</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA (25/172)</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU) (25895)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA (2521)</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA (2526)</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA (2535)</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA (84)</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA (2543 INV OFFSET)</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA (2234)</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA (S-201 INV)</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA (5121)</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA (720)</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F) (25-146)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA (3702)</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA (254 SBC)</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F) (25-047)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA (2082)</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-* (4052)</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA (2103)</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA (1223 SBC)</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA (6310 GE)</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA (2532)</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA (1174)</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA (1034)</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA (2204 INV)</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA (06)</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA (303)</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA (25323 INV)</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA (25413)</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA (2597)</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA (25896)</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F) (243-C)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA (1855)</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA (1044 SBC)</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA (2014)</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA (2006)</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU) (6106)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA (GOPAL 32)</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA (2005- G)</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA (5180)</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU) (3753)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA (273 NEHA)</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA (278-B)</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1793,7 +1793,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.)</t>
+    <t>9001 CARD (O.C.) (2498 Cream)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1817,298 +1817,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS</t>
-  </si>
-  <si>
-    <t>9240 CARDS</t>
-  </si>
-  <si>
-    <t>9241 CARDS</t>
-  </si>
-  <si>
-    <t>9242 CARDS</t>
-  </si>
-  <si>
-    <t>9243 CARDS</t>
-  </si>
-  <si>
-    <t>9244 CARDS</t>
-  </si>
-  <si>
-    <t>9301 CARDS</t>
-  </si>
-  <si>
-    <t>9302 CARDS</t>
-  </si>
-  <si>
-    <t>9303 CARDS</t>
-  </si>
-  <si>
-    <t>9304 CARDS</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070)</t>
-  </si>
-  <si>
-    <t>9306 CARDS</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M)</t>
-  </si>
-  <si>
-    <t>9308 CARDS</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc)</t>
-  </si>
-  <si>
-    <t>9310 CARDS</t>
-  </si>
-  <si>
-    <t>9311 CARDS</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9314 CARDS</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (Aa Gya )</t>
-  </si>
-  <si>
-    <t>9318 CARDS</t>
-  </si>
-  <si>
-    <t>9319 CARDS</t>
-  </si>
-  <si>
-    <t>9320 CARDS</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD)</t>
-  </si>
-  <si>
-    <t>9324 CARDS</t>
-  </si>
-  <si>
-    <t>9325 CARDS</t>
-  </si>
-  <si>
-    <t>9326 CARDS</t>
-  </si>
-  <si>
-    <t>9327 CARDS</t>
-  </si>
-  <si>
-    <t>9328 CARDS</t>
-  </si>
-  <si>
-    <t>9329 CARDS</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC</t>
-  </si>
-  <si>
-    <t>9333 CARDS</t>
-  </si>
-  <si>
-    <t>9334 CARDS</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (Design Change)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC)</t>
-  </si>
-  <si>
-    <t>9338 CARDS</t>
-  </si>
-  <si>
-    <t>9339 CARDS</t>
-  </si>
-  <si>
-    <t>9340 CARDS</t>
-  </si>
-  <si>
-    <t>9341 CARDS</t>
-  </si>
-  <si>
-    <t>9342 CARDS</t>
-  </si>
-  <si>
-    <t>9343 CARDS</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu)</t>
-  </si>
-  <si>
-    <t>9345 CARDS</t>
-  </si>
-  <si>
-    <t>9346 CARDS</t>
-  </si>
-  <si>
-    <t>9347 CARDS</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9351 Card - B</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9353 CARDS</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9355 CARDS</t>
-  </si>
-  <si>
-    <t>9356 CARDS</t>
-  </si>
-  <si>
-    <t>9357 CARDS</t>
-  </si>
-  <si>
-    <t>9358 CARDS</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega</t>
-  </si>
-  <si>
-    <t>9361 CARDS</t>
-  </si>
-  <si>
-    <t>9362 CARDS</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9365 CARDS</t>
-  </si>
-  <si>
-    <t>9366 CARDS</t>
-  </si>
-  <si>
-    <t>9367 CARDS</t>
-  </si>
-  <si>
-    <t>9368 CARDS</t>
-  </si>
-  <si>
-    <t>9369 CARDS</t>
-  </si>
-  <si>
-    <t>9370 CARDS</t>
-  </si>
-  <si>
-    <t>9371 CARDS</t>
-  </si>
-  <si>
-    <t>9372 CARDS</t>
-  </si>
-  <si>
-    <t>9373 CARDS</t>
-  </si>
-  <si>
-    <t>9374 CARDS</t>
-  </si>
-  <si>
-    <t>9375 CARDS</t>
-  </si>
-  <si>
-    <t>9376 CARDS</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9378 CARDS</t>
+    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
+  </si>
+  <si>
+    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
+  </si>
+  <si>
+    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
+  </si>
+  <si>
+    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
+  </si>
+  <si>
+    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9301 CARDS (4242)</t>
+  </si>
+  <si>
+    <t>9302 CARDS (5076)</t>
+  </si>
+  <si>
+    <t>9303 CARDS (5080 Pink)</t>
+  </si>
+  <si>
+    <t>9304 CARDS (5083 Blue)</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070) (4701 Nice)</t>
+  </si>
+  <si>
+    <t>9306 CARDS (0543 Nice)</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M) (5243 Nice)</t>
+  </si>
+  <si>
+    <t>9308 CARDS (9852)</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
+  </si>
+  <si>
+    <t>9310 CARDS (3103)</t>
+  </si>
+  <si>
+    <t>9311 CARDS (3115)</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T) (208 VV)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T) (216)</t>
+  </si>
+  <si>
+    <t>9314 CARDS (P-1)</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU) (P-2)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU) (P-3)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (Aa Gya ) (P-4)</t>
+  </si>
+  <si>
+    <t>9318 CARDS (25905)</t>
+  </si>
+  <si>
+    <t>9319 CARDS (25906)</t>
+  </si>
+  <si>
+    <t>9320 CARDS (S-20)</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9325 CARDS (5229)</t>
+  </si>
+  <si>
+    <t>9326 CARDS (1601)</t>
+  </si>
+  <si>
+    <t>9327 CARDS (25908)</t>
+  </si>
+  <si>
+    <t>9328 CARDS (2543)</t>
+  </si>
+  <si>
+    <t>9329 CARDS (3606)</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T) (9557)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T) (9560)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC (9847)</t>
+  </si>
+  <si>
+    <t>9333 CARDS (6042)</t>
+  </si>
+  <si>
+    <t>9334 CARDS (10X6 WHITE (2898))</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
+  </si>
+  <si>
+    <t>9336 CARDS (Design Change) (2884)</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC) (1635 AP)</t>
+  </si>
+  <si>
+    <t>9338 CARDS (1637 AP)</t>
+  </si>
+  <si>
+    <t>9339 CARDS (5361)</t>
+  </si>
+  <si>
+    <t>9340 CARDS (5658)</t>
+  </si>
+  <si>
+    <t>9341 CARDS (5497)</t>
+  </si>
+  <si>
+    <t>9342 CARDS (2861)</t>
+  </si>
+  <si>
+    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu) (689)</t>
+  </si>
+  <si>
+    <t>9345 CARDS (358 KALYANI)</t>
+  </si>
+  <si>
+    <t>9346 CARDS (359)</t>
+  </si>
+  <si>
+    <t>9347 CARDS (2853)</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी) (S-124)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window) (S-120)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1632)</t>
+  </si>
+  <si>
+    <t>9351 Card - B (1603 B)</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC (1603)</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
+  </si>
+  <si>
+    <t>9353 CARDS (1618)</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU) (345)</t>
+  </si>
+  <si>
+    <t>9355 CARDS (1624)</t>
+  </si>
+  <si>
+    <t>9356 CARDS (2895/2897)</t>
+  </si>
+  <si>
+    <t>9357 CARDS (2872)</t>
+  </si>
+  <si>
+    <t>9358 CARDS (WHITE PATTA)</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
+  </si>
+  <si>
+    <t>9361 CARDS (25426)</t>
+  </si>
+  <si>
+    <t>9362 CARDS (363)</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T) (1652)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T) (1612)</t>
+  </si>
+  <si>
+    <t>9365 CARDS (25429)</t>
+  </si>
+  <si>
+    <t>9366 CARDS (25427 GOLDEN)</t>
+  </si>
+  <si>
+    <t>9367 CARDS (5652)</t>
+  </si>
+  <si>
+    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
+  </si>
+  <si>
+    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
+  </si>
+  <si>
+    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
+  </si>
+  <si>
+    <t>9371 CARDS (3111 VP)</t>
+  </si>
+  <si>
+    <t>9372 CARDS (9*5 YLW SET (2841))</t>
+  </si>
+  <si>
+    <t>9373 CARDS (1482)</t>
+  </si>
+  <si>
+    <t>9374 CARDS (1485)</t>
+  </si>
+  <si>
+    <t>9375 CARDS (1452 WHITE)</t>
+  </si>
+  <si>
+    <t>9376 CARDS (1529 PRINCE)</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
+  </si>
+  <si>
+    <t>9378 CARDS (2892)</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2141,19 +2141,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU)</t>
+    <t>9389 CARDS (9147 RJ)</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU) (118KBC)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC)</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC</t>
+    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2183,7 +2183,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR)</t>
+    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2207,37 +2207,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE</t>
+    <t>RX-01 ENVELOPE (LX01)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (LX02)</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE (LX03)</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE (LX04)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (LX05)</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE (LX06)</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE (LX07)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (LX08)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (LX09)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर</t>
+    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2767,7 +2767,7 @@
   <dimension ref="A1:E736"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2889,16 +2889,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="25">
-        <v>46</v>
+        <v>39.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>82.8</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3229,16 +3229,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="25">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>185.25</v>
+        <v>176.7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3291,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="25">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>170.2</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,16 +3512,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C48" s="25">
-        <v>133.5</v>
+        <v>117.5</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>170.12</v>
+        <v>149.72999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3801,16 +3801,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" s="25">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>554.4</v>
+        <v>542.85</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3818,16 +3818,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="25">
-        <v>74.5</v>
+        <v>69.5</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>122.93</v>
+        <v>114.68</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3880,16 +3880,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C70" s="25">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>582.4</v>
+        <v>579.6</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3897,16 +3897,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C71" s="25">
-        <v>56.5</v>
+        <v>52.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>79.099999999999994</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4118,16 +4118,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="25">
-        <v>1548.5</v>
+        <v>1543.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>2013.05</v>
+        <v>2006.55</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4135,16 +4135,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C85" s="25">
-        <v>1444.5</v>
+        <v>1441.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1877.85</v>
+        <v>1873.95</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4152,16 +4152,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C86" s="25">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2075.6999999999998</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4254,16 +4254,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C92" s="25">
-        <v>570.5</v>
+        <v>565.5</v>
       </c>
       <c r="D92" s="26">
         <v>1.76</v>
       </c>
       <c r="E92" s="27">
-        <v>1006.6</v>
+        <v>997.78</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4295,16 +4295,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C95" s="25">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>424.8</v>
+        <v>415.8</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4312,16 +4312,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C96" s="25">
-        <v>173.5</v>
+        <v>168.5</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>156.15</v>
+        <v>151.65</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4329,16 +4329,16 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C97" s="25">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="D97" s="26">
         <v>0.9</v>
       </c>
       <c r="E97" s="27">
-        <v>19.350000000000001</v>
+        <v>16.649999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4440,16 +4440,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C104" s="25">
-        <v>246.5</v>
+        <v>242.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>616.25</v>
+        <v>606.25</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4508,16 +4508,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C108" s="25">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>925</v>
+        <v>915</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4525,10 +4525,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C109" s="25">
-        <v>134.5</v>
+        <v>132.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4538,10 +4538,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C110" s="25">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4703,10 +4703,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C123" s="25">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -5657,16 +5657,16 @@
         <v>185</v>
       </c>
       <c r="B183" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" s="25">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="D183" s="26">
         <v>3.33</v>
       </c>
       <c r="E183" s="27">
-        <v>71.599999999999994</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5911,16 +5911,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C199" s="25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D199" s="26">
         <v>4.5</v>
       </c>
       <c r="E199" s="27">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,16 +6262,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C220" s="25">
-        <v>117.75</v>
+        <v>113.75</v>
       </c>
       <c r="D220" s="26">
         <v>3.25</v>
       </c>
       <c r="E220" s="27">
-        <v>382.69</v>
+        <v>369.69</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,16 +6296,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C222" s="25">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="D222" s="26">
         <v>2.7</v>
       </c>
       <c r="E222" s="27">
-        <v>116.1</v>
+        <v>112.05</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6952,16 +6952,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C264" s="25">
-        <v>341.5</v>
+        <v>338.5</v>
       </c>
       <c r="D264" s="26">
         <v>4.28</v>
       </c>
       <c r="E264" s="27">
-        <v>1461.62</v>
+        <v>1448.78</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -7415,16 +7415,16 @@
         <v>295</v>
       </c>
       <c r="B293" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C293" s="25">
-        <v>104</v>
+        <v>102.5</v>
       </c>
       <c r="D293" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E293" s="27">
-        <v>508.35</v>
+        <v>501.02</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7568,16 +7568,16 @@
         <v>304</v>
       </c>
       <c r="B302" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C302" s="25">
-        <v>261.25</v>
+        <v>256.25</v>
       </c>
       <c r="D302" s="26">
         <v>4.3</v>
       </c>
       <c r="E302" s="27">
-        <v>1122.83</v>
+        <v>1101.3399999999999</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -7880,16 +7880,16 @@
         <v>324</v>
       </c>
       <c r="B322" s="24">
+        <v>12</v>
+      </c>
+      <c r="C322" s="25">
         <v>11</v>
-      </c>
-      <c r="C322" s="25">
-        <v>13</v>
       </c>
       <c r="D322" s="26">
         <v>5.25</v>
       </c>
       <c r="E322" s="27">
-        <v>68.25</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -8272,16 +8272,16 @@
         <v>348</v>
       </c>
       <c r="B346" s="24">
+        <v>7</v>
+      </c>
+      <c r="C346" s="25">
         <v>6</v>
-      </c>
-      <c r="C346" s="25">
-        <v>8</v>
       </c>
       <c r="D346" s="26">
         <v>6.46</v>
       </c>
       <c r="E346" s="27">
-        <v>51.68</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -8351,16 +8351,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C351" s="25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D351" s="26">
         <v>6.4</v>
       </c>
       <c r="E351" s="27">
-        <v>76.8</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8734,16 +8734,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C374" s="25">
-        <v>75.33</v>
+        <v>72.83</v>
       </c>
       <c r="D374" s="26">
         <v>4.5</v>
       </c>
       <c r="E374" s="27">
-        <v>338.99</v>
+        <v>327.74</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -9429,16 +9429,16 @@
         <v>419</v>
       </c>
       <c r="B417" s="24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C417" s="25">
-        <v>40</v>
+        <v>29.5</v>
       </c>
       <c r="D417" s="26">
         <v>6.19</v>
       </c>
       <c r="E417" s="27">
-        <v>247.72</v>
+        <v>182.69</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -9776,16 +9776,16 @@
         <v>442</v>
       </c>
       <c r="B440" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C440" s="25">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="D440" s="26">
         <v>11.75</v>
       </c>
       <c r="E440" s="27">
-        <v>193.88</v>
+        <v>170.38</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -11234,16 +11234,16 @@
         <v>532</v>
       </c>
       <c r="B530" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C530" s="25">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D530" s="26">
         <v>2</v>
       </c>
       <c r="E530" s="27">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -11553,16 +11553,16 @@
         <v>551</v>
       </c>
       <c r="B549" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C549" s="25">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="D549" s="26">
         <v>4.28</v>
       </c>
       <c r="E549" s="27">
-        <v>57.78</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11791,16 +11791,16 @@
         <v>565</v>
       </c>
       <c r="B563" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C563" s="25">
-        <v>32.299999999999997</v>
+        <v>31.3</v>
       </c>
       <c r="D563" s="26">
         <v>3.14</v>
       </c>
       <c r="E563" s="27">
-        <v>101.42</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -11859,16 +11859,16 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C567" s="25">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="D567" s="26">
         <v>3.5</v>
       </c>
       <c r="E567" s="27">
-        <v>75.25</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -12202,10 +12202,10 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C588" s="25">
-        <v>346.5</v>
+        <v>342.5</v>
       </c>
       <c r="D588" s="29"/>
       <c r="E588" s="28"/>
@@ -12228,10 +12228,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C590" s="25">
-        <v>262.5</v>
+        <v>255.5</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12387,10 +12387,10 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C601" s="25">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D601" s="29"/>
       <c r="E601" s="28"/>
@@ -13152,16 +13152,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C648" s="25">
-        <v>265.36</v>
+        <v>256.36</v>
       </c>
       <c r="D648" s="26">
         <v>1.7</v>
       </c>
       <c r="E648" s="27">
-        <v>451.11</v>
+        <v>435.81</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13271,16 +13271,16 @@
         <v>657</v>
       </c>
       <c r="B655" s="24">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C655" s="25">
-        <v>88.5</v>
+        <v>85.5</v>
       </c>
       <c r="D655" s="26">
         <v>2.85</v>
       </c>
       <c r="E655" s="27">
-        <v>252.23</v>
+        <v>243.68</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -13537,16 +13537,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C671" s="25">
-        <v>25.43</v>
+        <v>20.93</v>
       </c>
       <c r="D671" s="26">
         <v>3.6</v>
       </c>
       <c r="E671" s="27">
-        <v>91.55</v>
+        <v>75.349999999999994</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13588,16 +13588,16 @@
         <v>676</v>
       </c>
       <c r="B674" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C674" s="25">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="D674" s="26">
         <v>3.75</v>
       </c>
       <c r="E674" s="27">
-        <v>61.88</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -13977,10 +13977,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C699" s="25">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -14337,16 +14337,16 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C727" s="25">
-        <v>22.75</v>
+        <v>21.75</v>
       </c>
       <c r="D727" s="26">
         <v>2.5</v>
       </c>
       <c r="E727" s="27">
-        <v>56.88</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -14481,11 +14481,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45424.68</v>
+        <v>45239.67</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>108522.64</v>
+        <v>108073.78</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -2889,16 +2889,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="25">
-        <v>39.5</v>
+        <v>33</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>71.099999999999994</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,16 +2923,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="25">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>280.8</v>
+        <v>276.89999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2940,16 +2940,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" s="25">
-        <v>171</v>
+        <v>168.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3127,16 +3127,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C25" s="25">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D25" s="26">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="E25" s="27">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3965,16 +3965,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C75" s="25">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>165.6</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3982,16 +3982,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C76" s="25">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>584.4</v>
+        <v>567.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4067,16 +4067,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="25">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>859.2</v>
+        <v>852</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4363,16 +4363,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C99" s="25">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>719.4</v>
+        <v>711.15</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C123" s="25">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -4716,10 +4716,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C124" s="25">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
@@ -5041,16 +5041,16 @@
         <v>147</v>
       </c>
       <c r="B145" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C145" s="25">
-        <v>9.77</v>
+        <v>7.77</v>
       </c>
       <c r="D145" s="26">
         <v>18.5</v>
       </c>
       <c r="E145" s="27">
-        <v>180.75</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,16 +6007,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C205" s="25">
-        <v>36.5</v>
+        <v>33.5</v>
       </c>
       <c r="D205" s="26">
         <v>2.7</v>
       </c>
       <c r="E205" s="27">
-        <v>98.55</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -6024,16 +6024,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C206" s="25">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D206" s="26">
         <v>2.6</v>
       </c>
       <c r="E206" s="27">
-        <v>122.2</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,16 +6160,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C214" s="25">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>346.95</v>
+        <v>345.6</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6228,16 +6228,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C218" s="25">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D218" s="26">
         <v>3</v>
       </c>
       <c r="E218" s="27">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,16 +6296,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C222" s="25">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="D222" s="26">
         <v>2.7</v>
       </c>
       <c r="E222" s="27">
-        <v>112.05</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,16 +6432,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C230" s="25">
-        <v>61.5</v>
+        <v>58.5</v>
       </c>
       <c r="D230" s="26">
         <v>3.5</v>
       </c>
       <c r="E230" s="27">
-        <v>215.25</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6460,16 +6460,16 @@
         <v>234</v>
       </c>
       <c r="B232" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C232" s="25">
-        <v>88.38</v>
+        <v>87.38</v>
       </c>
       <c r="D232" s="26">
         <v>3.25</v>
       </c>
       <c r="E232" s="27">
-        <v>287.24</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,16 +6653,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C245" s="25">
-        <v>63.9</v>
+        <v>59.4</v>
       </c>
       <c r="D245" s="26">
         <v>6.3</v>
       </c>
       <c r="E245" s="27">
-        <v>402.57</v>
+        <v>374.22</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -7398,16 +7398,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C292" s="25">
-        <v>30.5</v>
+        <v>27.5</v>
       </c>
       <c r="D292" s="26">
         <v>3.8</v>
       </c>
       <c r="E292" s="27">
-        <v>115.9</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7432,16 +7432,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C294" s="25">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="D294" s="26">
         <v>5.78</v>
       </c>
       <c r="E294" s="27">
-        <v>60.68</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -8272,16 +8272,16 @@
         <v>348</v>
       </c>
       <c r="B346" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C346" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D346" s="26">
         <v>6.46</v>
       </c>
       <c r="E346" s="27">
-        <v>38.76</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -8451,16 +8451,16 @@
         <v>359</v>
       </c>
       <c r="B357" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C357" s="25">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="D357" s="26">
         <v>7.98</v>
       </c>
       <c r="E357" s="27">
-        <v>303.41000000000003</v>
+        <v>291.43</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -8734,16 +8734,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C374" s="25">
-        <v>72.83</v>
+        <v>70.33</v>
       </c>
       <c r="D374" s="26">
         <v>4.5</v>
       </c>
       <c r="E374" s="27">
-        <v>327.74</v>
+        <v>316.49</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8822,13 +8822,13 @@
         <v>12</v>
       </c>
       <c r="C379" s="25">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="D379" s="26">
         <v>9.5</v>
       </c>
       <c r="E379" s="27">
-        <v>204.25</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -9412,16 +9412,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C416" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D416" s="26">
         <v>4.9000000000000004</v>
       </c>
       <c r="E416" s="27">
-        <v>73.5</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -10332,16 +10332,16 @@
         <v>476</v>
       </c>
       <c r="B474" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C474" s="25">
-        <v>30.5</v>
+        <v>20.5</v>
       </c>
       <c r="D474" s="26">
         <v>9.5</v>
       </c>
       <c r="E474" s="27">
-        <v>289.75</v>
+        <v>194.75</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -11400,16 +11400,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C540" s="25">
-        <v>35.5</v>
+        <v>34</v>
       </c>
       <c r="D540" s="26">
         <v>1.8</v>
       </c>
       <c r="E540" s="27">
-        <v>63.9</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11859,16 +11859,16 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C567" s="25">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="D567" s="26">
         <v>3.5</v>
       </c>
       <c r="E567" s="27">
-        <v>61.25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -11910,16 +11910,16 @@
         <v>572</v>
       </c>
       <c r="B570" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C570" s="25">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D570" s="26">
         <v>2.14</v>
       </c>
       <c r="E570" s="27">
-        <v>39.590000000000003</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -12044,16 +12044,16 @@
         <v>580</v>
       </c>
       <c r="B578" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C578" s="25">
-        <v>101</v>
+        <v>98.5</v>
       </c>
       <c r="D578" s="26">
         <v>1.4</v>
       </c>
       <c r="E578" s="27">
-        <v>141.4</v>
+        <v>137.9</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -12267,16 +12267,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C593" s="25">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D593" s="26">
         <v>0.87</v>
       </c>
       <c r="E593" s="27">
-        <v>383.67</v>
+        <v>379.32</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -13523,13 +13523,13 @@
         <v>141</v>
       </c>
       <c r="C670" s="25">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="D670" s="26">
         <v>3.1</v>
       </c>
       <c r="E670" s="27">
-        <v>130.19999999999999</v>
+        <v>390.6</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13656,16 +13656,16 @@
         <v>680</v>
       </c>
       <c r="B678" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C678" s="25">
-        <v>0.5</v>
+        <v>-9.5</v>
       </c>
       <c r="D678" s="26">
         <v>5.8</v>
       </c>
       <c r="E678" s="27">
-        <v>2.9</v>
+        <v>-55.1</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
@@ -13741,16 +13741,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C683" s="25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D683" s="26">
         <v>2.75</v>
       </c>
       <c r="E683" s="27">
-        <v>55</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13977,10 +13977,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C699" s="25">
-        <v>43</v>
+        <v>40.5</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -14259,10 +14259,10 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C721" s="25">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="D721" s="29"/>
       <c r="E721" s="28"/>
@@ -14481,11 +14481,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45239.67</v>
+        <v>45205.14</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>108073.78</v>
+        <v>107887.77</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -1361,7 +1361,7 @@
     <t>6606 PATRIKA (*-*) R (3023)</t>
   </si>
   <si>
-    <t>6607 PATRIKA *-* (M) (TUESDAY) (0523)</t>
+    <t>6607 PATRIKA *-* (M) (0523)</t>
   </si>
   <si>
     <t>6608 PATRIKA (95)</t>
@@ -1523,7 +1523,7 @@
     <t>6659 PATRIKA (25193 (Padding))</t>
   </si>
   <si>
-    <t>6660 PATRIKA (200 26.02) (25194 (Padding))</t>
+    <t>6660 PATRIKA (25194 (Padding))</t>
   </si>
   <si>
     <t>6661 PATRIKA *-* (M) (1281)</t>
@@ -2889,16 +2889,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="25">
-        <v>33</v>
+        <v>39.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>59.4</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2991,16 +2991,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="25">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>310.8</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3144,16 +3144,16 @@
         <v>28</v>
       </c>
       <c r="B26" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" s="26">
         <v>1.65</v>
       </c>
       <c r="E26" s="27">
-        <v>6.6</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3427,16 +3427,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" s="25">
-        <v>148.5</v>
+        <v>144.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>366.11</v>
+        <v>356.25</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,16 +3512,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" s="25">
-        <v>117.5</v>
+        <v>113.5</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>149.72999999999999</v>
+        <v>144.63</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3597,16 +3597,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C53" s="25">
-        <v>6</v>
+        <v>27.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>15</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3648,16 +3648,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C56" s="25">
-        <v>198</v>
+        <v>192.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>356.4</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3818,16 +3818,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="25">
-        <v>69.5</v>
+        <v>67.5</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>114.68</v>
+        <v>111.38</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3880,16 +3880,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C70" s="25">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>579.6</v>
+        <v>565.6</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3948,16 +3948,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C74" s="25">
-        <v>248.5</v>
+        <v>238.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>298.2</v>
+        <v>286.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3965,16 +3965,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C75" s="25">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3982,16 +3982,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C76" s="25">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>567.6</v>
+        <v>555.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4118,16 +4118,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C84" s="25">
-        <v>1543.5</v>
+        <v>1537</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>2006.55</v>
+        <v>1998.1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4135,16 +4135,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C85" s="25">
-        <v>1441.5</v>
+        <v>1439.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1873.95</v>
+        <v>1871.35</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4155,13 +4155,13 @@
         <v>34</v>
       </c>
       <c r="C86" s="25">
-        <v>1220</v>
+        <v>1211</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2074</v>
+        <v>2058.6999999999998</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4206,13 +4206,13 @@
         <v>76</v>
       </c>
       <c r="C89" s="25">
-        <v>227.5</v>
+        <v>247.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.45</v>
       </c>
       <c r="E89" s="27">
-        <v>329.67</v>
+        <v>359.44</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4240,13 +4240,13 @@
         <v>26</v>
       </c>
       <c r="C91" s="25">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D91" s="26">
-        <v>1.08</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>86.32</v>
+        <v>134.58000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4257,13 +4257,13 @@
         <v>22</v>
       </c>
       <c r="C92" s="25">
-        <v>565.5</v>
+        <v>756.5</v>
       </c>
       <c r="D92" s="26">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>997.78</v>
+        <v>1367.52</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4312,16 +4312,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C96" s="25">
-        <v>168.5</v>
+        <v>166</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>151.65</v>
+        <v>149.4</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4329,16 +4329,16 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C97" s="25">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="D97" s="26">
         <v>0.9</v>
       </c>
       <c r="E97" s="27">
-        <v>16.649999999999999</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C123" s="25">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -4822,16 +4822,16 @@
         <v>134</v>
       </c>
       <c r="B132" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C132" s="25">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>181.25</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4924,7 +4924,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C138" s="25">
         <v>16.5</v>
@@ -5041,16 +5041,16 @@
         <v>147</v>
       </c>
       <c r="B145" s="24">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C145" s="25">
-        <v>7.77</v>
+        <v>9.77</v>
       </c>
       <c r="D145" s="26">
         <v>18.5</v>
       </c>
       <c r="E145" s="27">
-        <v>143.75</v>
+        <v>180.75</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5477,10 +5477,10 @@
         <v>173</v>
       </c>
       <c r="B171" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C171" s="25">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D171" s="29"/>
       <c r="E171" s="28"/>
@@ -5956,16 +5956,16 @@
         <v>204</v>
       </c>
       <c r="B202" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C202" s="25">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="D202" s="26">
         <v>4.5</v>
       </c>
       <c r="E202" s="27">
-        <v>236.25</v>
+        <v>216</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5973,16 +5973,16 @@
         <v>205</v>
       </c>
       <c r="B203" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C203" s="25">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="D203" s="26">
         <v>2.85</v>
       </c>
       <c r="E203" s="27">
-        <v>54.15</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -6109,16 +6109,16 @@
         <v>213</v>
       </c>
       <c r="B211" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C211" s="25">
-        <v>180</v>
+        <v>175.5</v>
       </c>
       <c r="D211" s="26">
         <v>3.93</v>
       </c>
       <c r="E211" s="27">
-        <v>707.41</v>
+        <v>689.72</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,16 +6143,16 @@
         <v>215</v>
       </c>
       <c r="B213" s="24">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C213" s="25">
-        <v>351.5</v>
+        <v>341.5</v>
       </c>
       <c r="D213" s="26">
         <v>2.7</v>
       </c>
       <c r="E213" s="27">
-        <v>949.05</v>
+        <v>922.05</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,16 +6160,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C214" s="25">
-        <v>128</v>
+        <v>126.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>345.6</v>
+        <v>341.55</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6211,16 +6211,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C217" s="25">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="D217" s="26">
         <v>3</v>
       </c>
       <c r="E217" s="27">
-        <v>123</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6245,16 +6245,16 @@
         <v>221</v>
       </c>
       <c r="B219" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C219" s="25">
-        <v>187</v>
+        <v>185.5</v>
       </c>
       <c r="D219" s="26">
         <v>3.93</v>
       </c>
       <c r="E219" s="27">
-        <v>734.76</v>
+        <v>728.86</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,16 +6432,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C230" s="25">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="D230" s="26">
         <v>3.5</v>
       </c>
       <c r="E230" s="27">
-        <v>204.75</v>
+        <v>190.75</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6460,16 +6460,16 @@
         <v>234</v>
       </c>
       <c r="B232" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C232" s="25">
-        <v>87.38</v>
+        <v>84.88</v>
       </c>
       <c r="D232" s="26">
         <v>3.25</v>
       </c>
       <c r="E232" s="27">
-        <v>283.99</v>
+        <v>275.86</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6619,16 +6619,16 @@
         <v>245</v>
       </c>
       <c r="B243" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C243" s="25">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D243" s="26">
         <v>5.75</v>
       </c>
       <c r="E243" s="27">
-        <v>123.63</v>
+        <v>117.88</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,16 +6653,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C245" s="25">
-        <v>59.4</v>
+        <v>49.4</v>
       </c>
       <c r="D245" s="26">
         <v>6.3</v>
       </c>
       <c r="E245" s="27">
-        <v>374.22</v>
+        <v>311.22000000000003</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6918,16 +6918,16 @@
         <v>264</v>
       </c>
       <c r="B262" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C262" s="25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D262" s="26">
         <v>4.75</v>
       </c>
       <c r="E262" s="27">
-        <v>90.25</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -7228,16 +7228,16 @@
         <v>284</v>
       </c>
       <c r="B282" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C282" s="25">
-        <v>91.5</v>
+        <v>90.5</v>
       </c>
       <c r="D282" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E282" s="27">
-        <v>432.43</v>
+        <v>427.71</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7415,16 +7415,16 @@
         <v>295</v>
       </c>
       <c r="B293" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C293" s="25">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="D293" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E293" s="27">
-        <v>501.02</v>
+        <v>496.13</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7466,16 +7466,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C296" s="25">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D296" s="26">
         <v>6.06</v>
       </c>
       <c r="E296" s="27">
-        <v>1848.78</v>
+        <v>1824.71</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -8127,16 +8127,16 @@
         <v>339</v>
       </c>
       <c r="B337" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C337" s="25">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="D337" s="26">
         <v>9</v>
       </c>
       <c r="E337" s="27">
-        <v>301.5</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -8155,16 +8155,16 @@
         <v>341</v>
       </c>
       <c r="B339" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C339" s="25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D339" s="26">
         <v>9</v>
       </c>
       <c r="E339" s="27">
-        <v>99</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -8255,16 +8255,16 @@
         <v>347</v>
       </c>
       <c r="B345" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C345" s="25">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="D345" s="26">
         <v>6.46</v>
       </c>
       <c r="E345" s="27">
-        <v>67.83</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -8272,16 +8272,16 @@
         <v>348</v>
       </c>
       <c r="B346" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C346" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D346" s="26">
         <v>6.46</v>
       </c>
       <c r="E346" s="27">
-        <v>25.84</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -8737,13 +8737,13 @@
         <v>131</v>
       </c>
       <c r="C374" s="25">
-        <v>70.33</v>
+        <v>67.83</v>
       </c>
       <c r="D374" s="26">
         <v>4.5</v>
       </c>
       <c r="E374" s="27">
-        <v>316.49</v>
+        <v>305.24</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8972,17 +8972,11 @@
         <v>390</v>
       </c>
       <c r="B388" s="24">
-        <v>8</v>
-      </c>
-      <c r="C388" s="25">
-        <v>1.5</v>
-      </c>
-      <c r="D388" s="26">
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="E388" s="27">
-        <v>12.83</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C388" s="28"/>
+      <c r="D388" s="29"/>
+      <c r="E388" s="28"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="23" t="s">
@@ -9106,16 +9100,16 @@
         <v>398</v>
       </c>
       <c r="B396" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C396" s="25">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D396" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E396" s="27">
-        <v>51.3</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -9168,16 +9162,16 @@
         <v>402</v>
       </c>
       <c r="B400" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C400" s="25">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D400" s="26">
         <v>6.4</v>
       </c>
       <c r="E400" s="27">
-        <v>9.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -9829,15 +9823,9 @@
       <c r="B443" s="24">
         <v>5</v>
       </c>
-      <c r="C443" s="25">
-        <v>-7.5</v>
-      </c>
-      <c r="D443" s="26">
-        <v>15.5</v>
-      </c>
-      <c r="E443" s="27">
-        <v>-116.25</v>
-      </c>
+      <c r="C443" s="28"/>
+      <c r="D443" s="29"/>
+      <c r="E443" s="28"/>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="23" t="s">
@@ -10019,16 +10007,16 @@
         <v>457</v>
       </c>
       <c r="B455" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C455" s="25">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D455" s="26">
         <v>14.25</v>
       </c>
       <c r="E455" s="27">
-        <v>128.25</v>
+        <v>106.88</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -10264,16 +10252,16 @@
         <v>472</v>
       </c>
       <c r="B470" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C470" s="25">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D470" s="26">
         <v>12.5</v>
       </c>
       <c r="E470" s="27">
-        <v>100</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -10411,16 +10399,16 @@
         <v>481</v>
       </c>
       <c r="B479" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C479" s="25">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="D479" s="26">
         <v>10.32</v>
       </c>
       <c r="E479" s="27">
-        <v>98.05</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -10641,16 +10629,16 @@
         <v>495</v>
       </c>
       <c r="B493" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C493" s="25">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D493" s="26">
         <v>32</v>
       </c>
       <c r="E493" s="27">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
@@ -10669,16 +10657,16 @@
         <v>497</v>
       </c>
       <c r="B495" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C495" s="25">
-        <v>29.88</v>
+        <v>25.88</v>
       </c>
       <c r="D495" s="26">
         <v>11.26</v>
       </c>
       <c r="E495" s="27">
-        <v>336.54</v>
+        <v>291.49</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
@@ -10705,15 +10693,9 @@
       <c r="B497" s="24">
         <v>5</v>
       </c>
-      <c r="C497" s="25">
-        <v>-2</v>
-      </c>
-      <c r="D497" s="26">
-        <v>55</v>
-      </c>
-      <c r="E497" s="27">
-        <v>-110</v>
-      </c>
+      <c r="C497" s="28"/>
+      <c r="D497" s="29"/>
+      <c r="E497" s="28"/>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="23" t="s">
@@ -11166,16 +11148,16 @@
         <v>528</v>
       </c>
       <c r="B526" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C526" s="25">
-        <v>99.5</v>
+        <v>94.5</v>
       </c>
       <c r="D526" s="26">
         <v>1.4</v>
       </c>
       <c r="E526" s="27">
-        <v>139.30000000000001</v>
+        <v>132.30000000000001</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -11183,16 +11165,16 @@
         <v>529</v>
       </c>
       <c r="B527" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C527" s="25">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="D527" s="26">
         <v>1.4</v>
       </c>
       <c r="E527" s="27">
-        <v>149.1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11349,16 +11331,16 @@
         <v>539</v>
       </c>
       <c r="B537" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C537" s="25">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="D537" s="26">
         <v>3.5</v>
       </c>
       <c r="E537" s="27">
-        <v>75.25</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11621,16 +11603,16 @@
         <v>555</v>
       </c>
       <c r="B553" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C553" s="25">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D553" s="26">
         <v>9.5</v>
       </c>
       <c r="E553" s="27">
-        <v>133</v>
+        <v>57</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11672,16 +11654,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C556" s="25">
-        <v>88.2</v>
+        <v>85.2</v>
       </c>
       <c r="D556" s="26">
         <v>3.9</v>
       </c>
       <c r="E556" s="27">
-        <v>343.98</v>
+        <v>332.28</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11689,16 +11671,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C557" s="25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D557" s="26">
         <v>1.8</v>
       </c>
       <c r="E557" s="27">
-        <v>19.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -12061,16 +12043,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C579" s="25">
-        <v>94.5</v>
+        <v>91.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.8</v>
       </c>
       <c r="E579" s="27">
-        <v>170.1</v>
+        <v>164.7</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12149,7 +12131,7 @@
         <v>3</v>
       </c>
       <c r="C584" s="25">
-        <v>-19</v>
+        <v>69</v>
       </c>
       <c r="D584" s="29"/>
       <c r="E584" s="28"/>
@@ -12162,7 +12144,7 @@
         <v>3</v>
       </c>
       <c r="C585" s="25">
-        <v>-29</v>
+        <v>11</v>
       </c>
       <c r="D585" s="29"/>
       <c r="E585" s="28"/>
@@ -12215,10 +12197,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C589" s="25">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12267,16 +12249,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C593" s="25">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D593" s="26">
         <v>0.87</v>
       </c>
       <c r="E593" s="27">
-        <v>379.32</v>
+        <v>378.45</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -12284,16 +12266,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C594" s="25">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="D594" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E594" s="27">
-        <v>446.02</v>
+        <v>440.22</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12852,16 +12834,16 @@
         <v>632</v>
       </c>
       <c r="B630" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C630" s="25">
-        <v>64.5</v>
+        <v>62</v>
       </c>
       <c r="D630" s="26">
         <v>2.76</v>
       </c>
       <c r="E630" s="27">
-        <v>177.95</v>
+        <v>171.05</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -12903,16 +12885,16 @@
         <v>635</v>
       </c>
       <c r="B633" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C633" s="25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D633" s="26">
         <v>1.5</v>
       </c>
       <c r="E633" s="27">
-        <v>10.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -12954,16 +12936,16 @@
         <v>638</v>
       </c>
       <c r="B636" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C636" s="25">
-        <v>87</v>
+        <v>150.5</v>
       </c>
       <c r="D636" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E636" s="27">
-        <v>198.36</v>
+        <v>343.14</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -13523,13 +13505,13 @@
         <v>141</v>
       </c>
       <c r="C670" s="25">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D670" s="26">
         <v>3.1</v>
       </c>
       <c r="E670" s="27">
-        <v>390.6</v>
+        <v>589</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13656,16 +13638,16 @@
         <v>680</v>
       </c>
       <c r="B678" s="24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C678" s="25">
-        <v>-9.5</v>
+        <v>0.5</v>
       </c>
       <c r="D678" s="26">
         <v>5.8</v>
       </c>
       <c r="E678" s="27">
-        <v>-55.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
@@ -13820,16 +13802,16 @@
         <v>690</v>
       </c>
       <c r="B688" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C688" s="25">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D688" s="26">
         <v>4.25</v>
       </c>
       <c r="E688" s="27">
-        <v>95.63</v>
+        <v>91.38</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -13977,10 +13959,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C699" s="25">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -13990,10 +13972,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C700" s="25">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14190,10 +14172,10 @@
         <v>718</v>
       </c>
       <c r="B716" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C716" s="25">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D716" s="29"/>
       <c r="E716" s="28"/>
@@ -14320,16 +14302,16 @@
         <v>728</v>
       </c>
       <c r="B726" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C726" s="25">
-        <v>15.75</v>
+        <v>15.25</v>
       </c>
       <c r="D726" s="26">
         <v>2.5</v>
       </c>
       <c r="E726" s="27">
-        <v>39.380000000000003</v>
+        <v>38.130000000000003</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
@@ -14354,16 +14336,16 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C728" s="25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D728" s="26">
         <v>2.5</v>
       </c>
       <c r="E728" s="27">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -14388,16 +14370,16 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C730" s="25">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="D730" s="26">
         <v>2.5</v>
       </c>
       <c r="E730" s="27">
-        <v>9.3800000000000008</v>
+        <v>8.1300000000000008</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -14422,16 +14404,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C732" s="25">
-        <v>50.25</v>
+        <v>49.75</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>125.63</v>
+        <v>124.38</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14467,10 +14449,10 @@
         <v>737</v>
       </c>
       <c r="B735" s="24">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C735" s="25">
-        <v>-478</v>
+        <v>-481</v>
       </c>
       <c r="D735" s="29"/>
       <c r="E735" s="28"/>
@@ -14481,11 +14463,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45205.14</v>
+        <v>45525.62</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>107887.77</v>
+        <v>108365.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -2983,13 +2983,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="20">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="C21" s="21">
         <v>2.6</v>
       </c>
       <c r="D21" s="22">
-        <v>7.8</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3039,13 +3039,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="20">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C25" s="21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="D25" s="22">
-        <v>0.83</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3123,13 +3123,13 @@
         <v>31</v>
       </c>
       <c r="B31" s="20">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="21">
         <v>2.85</v>
       </c>
       <c r="D31" s="22">
-        <v>176.7</v>
+        <v>173.85</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3243,13 +3243,13 @@
         <v>40</v>
       </c>
       <c r="B40" s="20">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="C40" s="21">
         <v>2.14</v>
       </c>
       <c r="D40" s="22">
-        <v>7.49</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3341,13 +3341,13 @@
         <v>47</v>
       </c>
       <c r="B47" s="20">
-        <v>216.5</v>
+        <v>213.5</v>
       </c>
       <c r="C47" s="21">
         <v>1.27</v>
       </c>
       <c r="D47" s="22">
-        <v>274.86</v>
+        <v>271.05</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3369,13 +3369,13 @@
         <v>49</v>
       </c>
       <c r="B49" s="20">
-        <v>26</v>
+        <v>24.5</v>
       </c>
       <c r="C49" s="21">
         <v>1.4</v>
       </c>
       <c r="D49" s="22">
-        <v>36.4</v>
+        <v>34.299999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3411,13 +3411,13 @@
         <v>52</v>
       </c>
       <c r="B52" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C52" s="21">
         <v>2.5</v>
       </c>
       <c r="D52" s="22">
-        <v>70</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3425,13 +3425,13 @@
         <v>53</v>
       </c>
       <c r="B53" s="20">
-        <v>27.5</v>
+        <v>3.5</v>
       </c>
       <c r="C53" s="21">
         <v>2.5</v>
       </c>
       <c r="D53" s="22">
-        <v>68.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3467,13 +3467,13 @@
         <v>56</v>
       </c>
       <c r="B56" s="20">
-        <v>192.5</v>
+        <v>188.5</v>
       </c>
       <c r="C56" s="21">
         <v>1.8</v>
       </c>
       <c r="D56" s="22">
-        <v>346.5</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3537,13 +3537,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="20">
-        <v>1075</v>
+        <v>1073.5</v>
       </c>
       <c r="C61" s="21">
         <v>1.1399999999999999</v>
       </c>
       <c r="D61" s="22">
-        <v>1224.79</v>
+        <v>1223.08</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3607,13 +3607,13 @@
         <v>66</v>
       </c>
       <c r="B66" s="20">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="C66" s="21">
         <v>1.65</v>
       </c>
       <c r="D66" s="22">
-        <v>111.38</v>
+        <v>110.55</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3853,13 +3853,13 @@
         <v>84</v>
       </c>
       <c r="B84" s="20">
-        <v>1537</v>
+        <v>1534.5</v>
       </c>
       <c r="C84" s="21">
         <v>1.3</v>
       </c>
       <c r="D84" s="22">
-        <v>1998.1</v>
+        <v>1994.85</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3997,13 +3997,13 @@
         <v>95</v>
       </c>
       <c r="B95" s="20">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C95" s="21">
         <v>0.9</v>
       </c>
       <c r="D95" s="22">
-        <v>415.8</v>
+        <v>414</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -4123,13 +4123,13 @@
         <v>104</v>
       </c>
       <c r="B104" s="20">
-        <v>242.5</v>
+        <v>202.5</v>
       </c>
       <c r="C104" s="21">
         <v>2.5</v>
       </c>
       <c r="D104" s="22">
-        <v>606.25</v>
+        <v>506.25</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4137,13 +4137,13 @@
         <v>105</v>
       </c>
       <c r="B105" s="20">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="C105" s="21">
         <v>2.5</v>
       </c>
       <c r="D105" s="22">
-        <v>917.5</v>
+        <v>817.5</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4151,13 +4151,13 @@
         <v>106</v>
       </c>
       <c r="B106" s="20">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="C106" s="21">
         <v>2.5</v>
       </c>
       <c r="D106" s="22">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4165,13 +4165,13 @@
         <v>107</v>
       </c>
       <c r="B107" s="20">
-        <v>369.5</v>
+        <v>329.5</v>
       </c>
       <c r="C107" s="21">
         <v>2.5</v>
       </c>
       <c r="D107" s="22">
-        <v>923.75</v>
+        <v>823.75</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4179,13 +4179,13 @@
         <v>108</v>
       </c>
       <c r="B108" s="20">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="C108" s="21">
         <v>2.5</v>
       </c>
       <c r="D108" s="22">
-        <v>915</v>
+        <v>815</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -5287,13 +5287,13 @@
         <v>197</v>
       </c>
       <c r="B197" s="20">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="C197" s="21">
         <v>4.5</v>
       </c>
       <c r="D197" s="22">
-        <v>51.75</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -6043,13 +6043,13 @@
         <v>254</v>
       </c>
       <c r="B254" s="20">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C254" s="21">
         <v>3.5</v>
       </c>
       <c r="D254" s="22">
-        <v>248.5</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -6307,13 +6307,13 @@
         <v>275</v>
       </c>
       <c r="B275" s="20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C275" s="21">
         <v>4.28</v>
       </c>
       <c r="D275" s="22">
-        <v>68.48</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6485,13 +6485,13 @@
         <v>289</v>
       </c>
       <c r="B289" s="20">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C289" s="21">
         <v>4.66</v>
       </c>
       <c r="D289" s="22">
-        <v>251.62</v>
+        <v>237.65</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6583,13 +6583,13 @@
         <v>296</v>
       </c>
       <c r="B296" s="20">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C296" s="21">
         <v>6.06</v>
       </c>
       <c r="D296" s="22">
-        <v>1824.71</v>
+        <v>1812.68</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -7177,13 +7177,13 @@
         <v>341</v>
       </c>
       <c r="B341" s="20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="C341" s="21">
         <v>9</v>
       </c>
       <c r="D341" s="22">
-        <v>99</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -7445,13 +7445,13 @@
         <v>361</v>
       </c>
       <c r="B361" s="20">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="C361" s="21">
         <v>7.76</v>
       </c>
       <c r="D361" s="22">
-        <v>294.82</v>
+        <v>290.94</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7613,13 +7613,13 @@
         <v>373</v>
       </c>
       <c r="B373" s="20">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C373" s="21">
         <v>7.42</v>
       </c>
       <c r="D373" s="22">
-        <v>341.21</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7711,13 +7711,13 @@
         <v>380</v>
       </c>
       <c r="B380" s="20">
-        <v>96.5</v>
+        <v>93.5</v>
       </c>
       <c r="C380" s="21">
         <v>3.6</v>
       </c>
       <c r="D380" s="22">
-        <v>347.4</v>
+        <v>336.6</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -8165,13 +8165,13 @@
         <v>415</v>
       </c>
       <c r="B415" s="20">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="C415" s="21">
         <v>5.3</v>
       </c>
       <c r="D415" s="22">
-        <v>119.25</v>
+        <v>108.65</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -8193,13 +8193,13 @@
         <v>417</v>
       </c>
       <c r="B417" s="20">
-        <v>29.5</v>
+        <v>34.5</v>
       </c>
       <c r="C417" s="21">
         <v>6.19</v>
       </c>
       <c r="D417" s="22">
-        <v>182.69</v>
+        <v>213.66</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -9851,13 +9851,13 @@
         <v>543</v>
       </c>
       <c r="B543" s="20">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C543" s="21">
         <v>4.28</v>
       </c>
       <c r="D543" s="22">
-        <v>124.12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
@@ -10033,13 +10033,13 @@
         <v>556</v>
       </c>
       <c r="B556" s="20">
-        <v>85.2</v>
+        <v>84.2</v>
       </c>
       <c r="C556" s="21">
         <v>3.9</v>
       </c>
       <c r="D556" s="22">
-        <v>332.28</v>
+        <v>328.38</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
@@ -10047,13 +10047,13 @@
         <v>557</v>
       </c>
       <c r="B557" s="20">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C557" s="21">
         <v>1.8</v>
       </c>
       <c r="D557" s="22">
-        <v>12.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
@@ -10173,13 +10173,13 @@
         <v>566</v>
       </c>
       <c r="B566" s="20">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="C566" s="21">
         <v>2.5</v>
       </c>
       <c r="D566" s="22">
-        <v>108.75</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
@@ -10469,7 +10469,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="20">
-        <v>342.5</v>
+        <v>332.5</v>
       </c>
       <c r="C588" s="24"/>
       <c r="D588" s="23"/>
@@ -10479,7 +10479,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="20">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C589" s="24"/>
       <c r="D589" s="23"/>
@@ -12305,7 +12305,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="20">
-        <v>-481</v>
+        <v>-482</v>
       </c>
       <c r="C735" s="24"/>
       <c r="D735" s="23"/>
@@ -12315,11 +12315,11 @@
         <v>736</v>
       </c>
       <c r="B736" s="26">
-        <v>45502.12</v>
+        <v>45222.62</v>
       </c>
       <c r="C736" s="27"/>
       <c r="D736" s="28">
-        <v>108297.68</v>
+        <v>107582.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -146,10 +146,10 @@
     <t>1028 PATRIKA (JC) (2596)</t>
   </si>
   <si>
-    <t>1029 PATRIKA (1042)</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA (1043)</t>
+    <t>1029 PATRIKA (2 DIN MAI MAAL AYGA ) (1042)</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA (2 DIN BAD MAL AYGA AUR) (1043)</t>
   </si>
   <si>
     <t>1031 PATRIKA (GOPAL 11)</t>
@@ -935,7 +935,7 @@
     <t>5113 PATRIKA (5305)</t>
   </si>
   <si>
-    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
+    <t>5114 PATRIKA *-* (डोरी) (2 DIN BAD AYGA 450 AVLBL) (2091)</t>
   </si>
   <si>
     <t>5115 PATRIKA (DCU) (5363 RJND)</t>
@@ -2843,13 +2843,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="20">
-        <v>39.5</v>
+        <v>29.5</v>
       </c>
       <c r="C11" s="21">
         <v>1.8</v>
       </c>
       <c r="D11" s="22">
-        <v>71.099999999999994</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2899,13 +2899,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="20">
-        <v>56.5</v>
+        <v>51.5</v>
       </c>
       <c r="C15" s="21">
         <v>2</v>
       </c>
       <c r="D15" s="22">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3109,13 +3109,13 @@
         <v>30</v>
       </c>
       <c r="B30" s="20">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="21">
         <v>2.38</v>
       </c>
       <c r="D30" s="22">
-        <v>83.3</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3187,13 +3187,13 @@
         <v>36</v>
       </c>
       <c r="B36" s="20">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="C36" s="21">
         <v>2.2999999999999998</v>
       </c>
       <c r="D36" s="22">
-        <v>139.15</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3243,13 +3243,13 @@
         <v>40</v>
       </c>
       <c r="B40" s="20">
-        <v>0.5</v>
+        <v>50.5</v>
       </c>
       <c r="C40" s="21">
         <v>2.14</v>
       </c>
       <c r="D40" s="22">
-        <v>1.07</v>
+        <v>108.07</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3257,13 +3257,13 @@
         <v>41</v>
       </c>
       <c r="B41" s="20">
-        <v>27.5</v>
+        <v>67.5</v>
       </c>
       <c r="C41" s="21">
         <v>2.14</v>
       </c>
       <c r="D41" s="22">
-        <v>58.85</v>
+        <v>144.44999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3341,13 +3341,13 @@
         <v>47</v>
       </c>
       <c r="B47" s="20">
-        <v>213.5</v>
+        <v>183.5</v>
       </c>
       <c r="C47" s="21">
         <v>1.27</v>
       </c>
       <c r="D47" s="22">
-        <v>271.05</v>
+        <v>232.96</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3355,13 +3355,13 @@
         <v>48</v>
       </c>
       <c r="B48" s="20">
-        <v>113.5</v>
+        <v>80.5</v>
       </c>
       <c r="C48" s="21">
         <v>1.27</v>
       </c>
       <c r="D48" s="22">
-        <v>144.63</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3369,13 +3369,13 @@
         <v>49</v>
       </c>
       <c r="B49" s="20">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="C49" s="21">
         <v>1.4</v>
       </c>
       <c r="D49" s="22">
-        <v>34.299999999999997</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3453,13 +3453,13 @@
         <v>55</v>
       </c>
       <c r="B55" s="20">
-        <v>38.25</v>
+        <v>28.25</v>
       </c>
       <c r="C55" s="21">
         <v>2.75</v>
       </c>
       <c r="D55" s="22">
-        <v>105.19</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3713,13 +3713,13 @@
         <v>74</v>
       </c>
       <c r="B74" s="20">
-        <v>238.5</v>
+        <v>218.5</v>
       </c>
       <c r="C74" s="21">
         <v>1.2</v>
       </c>
       <c r="D74" s="22">
-        <v>286.2</v>
+        <v>262.2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3727,13 +3727,13 @@
         <v>75</v>
       </c>
       <c r="B75" s="20">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C75" s="21">
         <v>1.2</v>
       </c>
       <c r="D75" s="22">
-        <v>150</v>
+        <v>145.19999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3853,13 +3853,13 @@
         <v>84</v>
       </c>
       <c r="B84" s="20">
-        <v>1534.5</v>
+        <v>1483.5</v>
       </c>
       <c r="C84" s="21">
         <v>1.3</v>
       </c>
       <c r="D84" s="22">
-        <v>1994.85</v>
+        <v>1928.55</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3895,13 +3895,13 @@
         <v>87</v>
       </c>
       <c r="B87" s="20">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="C87" s="21">
         <v>1.7</v>
       </c>
       <c r="D87" s="22">
-        <v>1446.7</v>
+        <v>1429.7</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3923,13 +3923,13 @@
         <v>89</v>
       </c>
       <c r="B89" s="20">
-        <v>247.5</v>
+        <v>244.5</v>
       </c>
       <c r="C89" s="21">
         <v>1.45</v>
       </c>
       <c r="D89" s="22">
-        <v>359.44</v>
+        <v>355.09</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3951,13 +3951,13 @@
         <v>91</v>
       </c>
       <c r="B91" s="20">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C91" s="21">
         <v>1.1200000000000001</v>
       </c>
       <c r="D91" s="22">
-        <v>134.58000000000001</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3965,13 +3965,13 @@
         <v>92</v>
       </c>
       <c r="B92" s="20">
-        <v>756.5</v>
+        <v>746.5</v>
       </c>
       <c r="C92" s="21">
         <v>1.81</v>
       </c>
       <c r="D92" s="22">
-        <v>1367.52</v>
+        <v>1349.44</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -4025,13 +4025,13 @@
         <v>97</v>
       </c>
       <c r="B97" s="20">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="C97" s="21">
         <v>0.9</v>
       </c>
       <c r="D97" s="22">
-        <v>7.65</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -4271,7 +4271,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="20">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C117" s="24"/>
       <c r="D117" s="23"/>
@@ -4331,7 +4331,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="20">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="C123" s="24"/>
       <c r="D123" s="23"/>
@@ -4465,13 +4465,13 @@
         <v>135</v>
       </c>
       <c r="B135" s="20">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="C135" s="21">
         <v>12.5</v>
       </c>
       <c r="D135" s="22">
-        <v>93.75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -5151,13 +5151,13 @@
         <v>186</v>
       </c>
       <c r="B186" s="20">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C186" s="21">
         <v>3.56</v>
       </c>
       <c r="D186" s="22">
-        <v>74.760000000000005</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5287,13 +5287,13 @@
         <v>197</v>
       </c>
       <c r="B197" s="20">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="C197" s="21">
         <v>4.5</v>
       </c>
       <c r="D197" s="22">
-        <v>42.75</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5519,13 +5519,13 @@
         <v>214</v>
       </c>
       <c r="B214" s="20">
-        <v>125.5</v>
+        <v>122</v>
       </c>
       <c r="C214" s="21">
         <v>2.7</v>
       </c>
       <c r="D214" s="22">
-        <v>338.85</v>
+        <v>329.4</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5589,13 +5589,13 @@
         <v>219</v>
       </c>
       <c r="B219" s="20">
-        <v>185.5</v>
+        <v>184.5</v>
       </c>
       <c r="C219" s="21">
         <v>3.93</v>
       </c>
       <c r="D219" s="22">
-        <v>728.86</v>
+        <v>724.93</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5617,13 +5617,13 @@
         <v>221</v>
       </c>
       <c r="B221" s="20">
-        <v>86.25</v>
+        <v>85.25</v>
       </c>
       <c r="C221" s="21">
         <v>3.64</v>
       </c>
       <c r="D221" s="22">
-        <v>313.61</v>
+        <v>309.97000000000003</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5645,13 +5645,13 @@
         <v>223</v>
       </c>
       <c r="B223" s="20">
-        <v>4.53</v>
+        <v>4.03</v>
       </c>
       <c r="C223" s="21">
         <v>3.16</v>
       </c>
       <c r="D223" s="22">
-        <v>14.32</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5743,13 +5743,13 @@
         <v>230</v>
       </c>
       <c r="B230" s="20">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="C230" s="21">
         <v>3.5</v>
       </c>
       <c r="D230" s="22">
-        <v>180.25</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5909,13 +5909,13 @@
         <v>244</v>
       </c>
       <c r="B244" s="20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C244" s="21">
         <v>4.8</v>
       </c>
       <c r="D244" s="22">
-        <v>153.6</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -6215,13 +6215,13 @@
         <v>268</v>
       </c>
       <c r="B268" s="20">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C268" s="21">
         <v>3.1</v>
       </c>
       <c r="D268" s="22">
-        <v>89.9</v>
+        <v>80.599999999999994</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6681,13 +6681,13 @@
         <v>303</v>
       </c>
       <c r="B303" s="20">
-        <v>4.5</v>
+        <v>20.5</v>
       </c>
       <c r="C303" s="21">
         <v>4.75</v>
       </c>
       <c r="D303" s="22">
-        <v>21.38</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -7627,13 +7627,13 @@
         <v>374</v>
       </c>
       <c r="B374" s="20">
-        <v>67.83</v>
+        <v>65.83</v>
       </c>
       <c r="C374" s="21">
         <v>4.5</v>
       </c>
       <c r="D374" s="22">
-        <v>305.24</v>
+        <v>296.24</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7683,13 +7683,13 @@
         <v>378</v>
       </c>
       <c r="B378" s="20">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="C378" s="21">
         <v>7</v>
       </c>
       <c r="D378" s="22">
-        <v>255.5</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -8927,13 +8927,13 @@
         <v>474</v>
       </c>
       <c r="B474" s="20">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="C474" s="21">
         <v>9.5</v>
       </c>
       <c r="D474" s="22">
-        <v>194.75</v>
+        <v>156.75</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -10103,13 +10103,13 @@
         <v>561</v>
       </c>
       <c r="B561" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C561" s="21">
         <v>3.6</v>
       </c>
       <c r="D561" s="22">
-        <v>14.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
@@ -10569,13 +10569,13 @@
         <v>597</v>
       </c>
       <c r="B597" s="20">
-        <v>199.5</v>
+        <v>189.5</v>
       </c>
       <c r="C597" s="21">
         <v>0.85</v>
       </c>
       <c r="D597" s="22">
-        <v>169.58</v>
+        <v>161.08000000000001</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
@@ -12315,11 +12315,11 @@
         <v>736</v>
       </c>
       <c r="B736" s="26">
-        <v>45222.62</v>
+        <v>45038.61</v>
       </c>
       <c r="C736" s="27"/>
       <c r="D736" s="28">
-        <v>107582.52</v>
+        <v>107334.37</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -236,7 +236,7 @@
     <t>1121 PATRIKA(सवाश्री-53)</t>
   </si>
   <si>
-    <t>1122 - B PATRIKA (SS-52) 1908</t>
+    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70</t>
   </si>
   <si>
     <t>1122 PATRIKA (DCU) (S.S. 54)</t>
@@ -851,7 +851,7 @@
     <t>5081 PATRIKA</t>
   </si>
   <si>
-    <t>5083 PATRIKA</t>
+    <t>5083 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>5084 PATRIKA</t>
@@ -923,7 +923,7 @@
     <t>5107 PATRIKA</t>
   </si>
   <si>
-    <t>5108 PATRIKA</t>
+    <t>5108 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>5109 PATRIKA</t>
@@ -2991,16 +2991,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="25">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>298.2</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3181,13 +3181,13 @@
         <v>46</v>
       </c>
       <c r="C28" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3393,16 +3393,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="25">
-        <v>67.5</v>
+        <v>62.5</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>144.44999999999999</v>
+        <v>133.75</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3410,16 +3410,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" s="25">
-        <v>64</v>
+        <v>62.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>156.72</v>
+        <v>153.05000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3427,16 +3427,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" s="25">
-        <v>144.5</v>
+        <v>140.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>356.25</v>
+        <v>346.39</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,13 +3447,13 @@
         <v>32</v>
       </c>
       <c r="C44" s="25">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="D44" s="26">
         <v>2.71</v>
       </c>
       <c r="E44" s="27">
-        <v>39.24</v>
+        <v>32.47</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3495,16 +3495,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" s="25">
-        <v>178.5</v>
+        <v>128.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>226.62</v>
+        <v>163.13999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,16 +3512,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C48" s="25">
-        <v>77.5</v>
+        <v>19.5</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>98.76</v>
+        <v>24.85</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3634,13 +3634,13 @@
         <v>19</v>
       </c>
       <c r="C55" s="25">
-        <v>242.75</v>
+        <v>242.65</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>667.56</v>
+        <v>667.29</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3897,16 +3897,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C71" s="25">
-        <v>52.5</v>
+        <v>50.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>73.5</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3982,16 +3982,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C76" s="25">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>553.20000000000005</v>
+        <v>546</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4118,16 +4118,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C84" s="25">
-        <v>1478.5</v>
+        <v>1475.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1922.05</v>
+        <v>1918.15</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4220,16 +4220,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C90" s="25">
-        <v>423.7</v>
+        <v>373.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>543.48</v>
+        <v>479.34</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C123" s="25">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -5443,16 +5443,16 @@
         <v>171</v>
       </c>
       <c r="B169" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C169" s="25">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D169" s="26">
         <v>0.87</v>
       </c>
       <c r="E169" s="27">
-        <v>110.41</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5764,16 +5764,16 @@
         <v>192</v>
       </c>
       <c r="B190" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C190" s="25">
-        <v>89.31</v>
+        <v>87.81</v>
       </c>
       <c r="D190" s="26">
         <v>2.65</v>
       </c>
       <c r="E190" s="27">
-        <v>236.67</v>
+        <v>232.7</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,16 +6143,16 @@
         <v>215</v>
       </c>
       <c r="B213" s="24">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C213" s="25">
-        <v>331.5</v>
+        <v>330.5</v>
       </c>
       <c r="D213" s="26">
         <v>2.7</v>
       </c>
       <c r="E213" s="27">
-        <v>895.05</v>
+        <v>892.35</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,16 +6296,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C222" s="25">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="D222" s="26">
         <v>2.7</v>
       </c>
       <c r="E222" s="27">
-        <v>106.65</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6313,16 +6313,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C223" s="25">
-        <v>4.03</v>
+        <v>1.53</v>
       </c>
       <c r="D223" s="26">
         <v>3.16</v>
       </c>
       <c r="E223" s="27">
-        <v>12.74</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6477,16 +6477,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C233" s="25">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>149.5</v>
+        <v>146.25</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6952,16 +6952,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C264" s="25">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D264" s="26">
         <v>4.28</v>
       </c>
       <c r="E264" s="27">
-        <v>1438.08</v>
+        <v>1395.28</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -7296,16 +7296,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C286" s="25">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D286" s="26">
         <v>5</v>
       </c>
       <c r="E286" s="27">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -8175,13 +8175,13 @@
         <v>21</v>
       </c>
       <c r="C340" s="25">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="D340" s="26">
         <v>9</v>
       </c>
       <c r="E340" s="27">
-        <v>40.5</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -8802,16 +8802,16 @@
         <v>380</v>
       </c>
       <c r="B378" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C378" s="25">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="D378" s="26">
         <v>7</v>
       </c>
       <c r="E378" s="27">
-        <v>248.5</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -11148,16 +11148,16 @@
         <v>528</v>
       </c>
       <c r="B526" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C526" s="25">
-        <v>94.5</v>
+        <v>64.5</v>
       </c>
       <c r="D526" s="26">
         <v>1.4</v>
       </c>
       <c r="E526" s="27">
-        <v>132.30000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -11165,16 +11165,16 @@
         <v>529</v>
       </c>
       <c r="B527" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C527" s="25">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D527" s="26">
         <v>1.4</v>
       </c>
       <c r="E527" s="27">
-        <v>147</v>
+        <v>142.80000000000001</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11586,16 +11586,16 @@
         <v>554</v>
       </c>
       <c r="B552" s="24">
+        <v>29</v>
+      </c>
+      <c r="C552" s="25">
         <v>28</v>
-      </c>
-      <c r="C552" s="25">
-        <v>31</v>
       </c>
       <c r="D552" s="26">
         <v>3.1</v>
       </c>
       <c r="E552" s="27">
-        <v>96.1</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11790,16 +11790,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C564" s="25">
-        <v>85.25</v>
+        <v>82.25</v>
       </c>
       <c r="D564" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E564" s="27">
-        <v>196.08</v>
+        <v>189.18</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -12197,10 +12197,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C589" s="25">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -14224,16 +14224,16 @@
         <v>722</v>
       </c>
       <c r="B720" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C720" s="25">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D720" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E720" s="27">
-        <v>40.6</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
@@ -14241,10 +14241,10 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C721" s="25">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="D721" s="29"/>
       <c r="E721" s="28"/>
@@ -14404,16 +14404,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C732" s="25">
-        <v>49.75</v>
+        <v>47.75</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>124.38</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14463,11 +14463,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45037.1</v>
+        <v>44752.97</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>107372.98</v>
+        <v>107061.07</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -2207,31 +2207,31 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE</t>
+    <t>RX-01 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (DC)</t>
   </si>
   <si>
     <t>RX-03 ENVELOPE</t>
   </si>
   <si>
-    <t>RX-04 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE</t>
+    <t>RX-04 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (DC)</t>
   </si>
   <si>
     <t>RX-06 ENVELOPE</t>
   </si>
   <si>
-    <t>RX-07 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE</t>
+    <t>RX-07 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (DC)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
@@ -2940,16 +2940,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="25">
-        <v>163.5</v>
+        <v>158.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3223,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="25">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>173.85</v>
+        <v>159.6</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3285,16 +3285,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="25">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>158.69999999999999</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3404,16 +3404,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C42" s="25">
-        <v>62.5</v>
+        <v>60.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>153.05000000000001</v>
+        <v>148.15</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3421,16 +3421,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" s="25">
-        <v>140.5</v>
+        <v>138.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>346.39</v>
+        <v>341.46</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3506,16 +3506,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" s="25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>21.66</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3526,13 +3526,13 @@
         <v>32</v>
       </c>
       <c r="C49" s="25">
-        <v>22</v>
+        <v>259</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>30.8</v>
+        <v>362.6</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3574,16 +3574,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C52" s="25">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>130</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3642,16 +3642,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C56" s="25">
-        <v>188.5</v>
+        <v>173.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>339.3</v>
+        <v>312.3</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3710,16 +3710,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="25">
-        <v>964.5</v>
+        <v>961.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1097.2</v>
+        <v>1093.78</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3727,16 +3727,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C61" s="25">
-        <v>1058.5</v>
+        <v>1055.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1205.99</v>
+        <v>1202.57</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3874,16 +3874,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C70" s="25">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>565.6</v>
+        <v>560</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3891,16 +3891,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C71" s="25">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>69.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3908,16 +3908,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C72" s="25">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>492.8</v>
+        <v>478.8</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3942,16 +3942,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C74" s="25">
-        <v>206.5</v>
+        <v>186.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>247.8</v>
+        <v>223.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3959,16 +3959,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C75" s="25">
-        <v>106</v>
+        <v>88.5</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>127.2</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3976,16 +3976,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C76" s="25">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>549.6</v>
+        <v>544.79999999999995</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4010,16 +4010,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C78" s="25">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>445.2</v>
+        <v>439.2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4129,16 +4129,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C85" s="25">
-        <v>1429.5</v>
+        <v>1424.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1858.35</v>
+        <v>1851.85</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4197,16 +4197,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C89" s="25">
-        <v>304.5</v>
+        <v>294.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>444.92</v>
+        <v>430.31</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4289,16 +4289,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C95" s="25">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4323,17 +4323,11 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>46</v>
-      </c>
-      <c r="C97" s="25">
-        <v>2</v>
-      </c>
-      <c r="D97" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="E97" s="27">
-        <v>1.8</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C97" s="28"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="28"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="23" t="s">
@@ -4404,16 +4398,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" s="25">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>249.48</v>
+        <v>246.91</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4521,10 +4515,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C109" s="25">
-        <v>129.5</v>
+        <v>114.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4610,10 +4604,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" s="25">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4623,10 +4617,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C117" s="25">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4636,16 +4630,16 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C118" s="25">
-        <v>73.25</v>
+        <v>58.25</v>
       </c>
       <c r="D118" s="26">
         <v>0.7</v>
       </c>
       <c r="E118" s="27">
-        <v>51.28</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4699,10 +4693,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="24">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C123" s="25">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="28"/>
@@ -4801,16 +4795,16 @@
         <v>133</v>
       </c>
       <c r="B131" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C131" s="25">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D131" s="26">
         <v>12.5</v>
       </c>
       <c r="E131" s="27">
-        <v>200</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5442,13 +5436,13 @@
         <v>38</v>
       </c>
       <c r="C169" s="25">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="D169" s="26">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E169" s="27">
-        <v>53.03</v>
+        <v>142.15</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5907,16 +5901,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C199" s="25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D199" s="26">
         <v>4.5</v>
       </c>
       <c r="E199" s="27">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -6020,16 +6014,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C206" s="25">
-        <v>42.5</v>
+        <v>39.5</v>
       </c>
       <c r="D206" s="26">
         <v>2.6</v>
       </c>
       <c r="E206" s="27">
-        <v>110.5</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6071,16 +6065,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C209" s="25">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="D209" s="26">
         <v>3.5</v>
       </c>
       <c r="E209" s="27">
-        <v>187.25</v>
+        <v>180.25</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6326,16 +6320,16 @@
         <v>226</v>
       </c>
       <c r="B224" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C224" s="25">
-        <v>135</v>
+        <v>132.5</v>
       </c>
       <c r="D224" s="26">
         <v>2.66</v>
       </c>
       <c r="E224" s="27">
-        <v>359.1</v>
+        <v>352.45</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6456,16 +6450,16 @@
         <v>234</v>
       </c>
       <c r="B232" s="24">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C232" s="25">
-        <v>84.88</v>
+        <v>80.88</v>
       </c>
       <c r="D232" s="26">
         <v>3.25</v>
       </c>
       <c r="E232" s="27">
-        <v>275.86</v>
+        <v>262.86</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6473,16 +6467,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C233" s="25">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>146.25</v>
+        <v>141.38</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6666,16 +6660,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C246" s="25">
-        <v>62.5</v>
+        <v>60.5</v>
       </c>
       <c r="D246" s="26">
         <v>3</v>
       </c>
       <c r="E246" s="27">
-        <v>187.5</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6717,16 +6711,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C249" s="25">
-        <v>70</v>
+        <v>191.5</v>
       </c>
       <c r="D249" s="26">
         <v>3.9</v>
       </c>
       <c r="E249" s="27">
-        <v>273</v>
+        <v>746.85</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6948,16 +6942,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C264" s="25">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D264" s="26">
         <v>4.28</v>
       </c>
       <c r="E264" s="27">
-        <v>1395.28</v>
+        <v>1386.72</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -7106,16 +7100,16 @@
         <v>276</v>
       </c>
       <c r="B274" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C274" s="25">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D274" s="26">
         <v>4.3899999999999997</v>
       </c>
       <c r="E274" s="27">
-        <v>351.19</v>
+        <v>338.02</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -7411,16 +7405,16 @@
         <v>295</v>
       </c>
       <c r="B293" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C293" s="25">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="D293" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E293" s="27">
-        <v>496.13</v>
+        <v>491.24</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7462,16 +7456,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C296" s="25">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D296" s="26">
         <v>6.06</v>
       </c>
       <c r="E296" s="27">
-        <v>1794.63</v>
+        <v>1752.52</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7910,16 +7904,16 @@
         <v>326</v>
       </c>
       <c r="B324" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C324" s="25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D324" s="26">
         <v>7.63</v>
       </c>
       <c r="E324" s="27">
-        <v>49.59</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -7993,16 +7987,16 @@
         <v>331</v>
       </c>
       <c r="B329" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C329" s="25">
-        <v>129.41</v>
+        <v>125.91</v>
       </c>
       <c r="D329" s="26">
         <v>4.28</v>
       </c>
       <c r="E329" s="27">
-        <v>553.87</v>
+        <v>538.89</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -8044,16 +8038,16 @@
         <v>334</v>
       </c>
       <c r="B332" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C332" s="25">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D332" s="26">
         <v>7.97</v>
       </c>
       <c r="E332" s="27">
-        <v>135.51</v>
+        <v>123.56</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -8447,16 +8441,16 @@
         <v>359</v>
       </c>
       <c r="B357" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C357" s="25">
-        <v>36.5</v>
+        <v>35</v>
       </c>
       <c r="D357" s="26">
         <v>7.98</v>
       </c>
       <c r="E357" s="27">
-        <v>291.43</v>
+        <v>279.45999999999998</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -8645,16 +8639,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C369" s="25">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D369" s="26">
         <v>6.6</v>
       </c>
       <c r="E369" s="27">
-        <v>765.6</v>
+        <v>752.4</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8730,16 +8724,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C374" s="25">
-        <v>65.33</v>
+        <v>58.33</v>
       </c>
       <c r="D374" s="26">
         <v>4.5</v>
       </c>
       <c r="E374" s="27">
-        <v>293.99</v>
+        <v>262.49</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -9336,16 +9330,16 @@
         <v>414</v>
       </c>
       <c r="B412" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C412" s="25">
-        <v>65.5</v>
+        <v>63.5</v>
       </c>
       <c r="D412" s="26">
         <v>5.2</v>
       </c>
       <c r="E412" s="27">
-        <v>340.6</v>
+        <v>330.2</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -9419,16 +9413,16 @@
         <v>419</v>
       </c>
       <c r="B417" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C417" s="25">
-        <v>34.5</v>
+        <v>58.5</v>
       </c>
       <c r="D417" s="26">
-        <v>6.19</v>
+        <v>6.2</v>
       </c>
       <c r="E417" s="27">
-        <v>213.66</v>
+        <v>362.91</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -10316,16 +10310,16 @@
         <v>476</v>
       </c>
       <c r="B474" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C474" s="25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D474" s="26">
         <v>9.5</v>
       </c>
       <c r="E474" s="27">
-        <v>156.75</v>
+        <v>152</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -10395,16 +10389,16 @@
         <v>481</v>
       </c>
       <c r="B479" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C479" s="25">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="D479" s="26">
         <v>10.32</v>
       </c>
       <c r="E479" s="27">
-        <v>87.73</v>
+        <v>36.119999999999997</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -10523,16 +10517,16 @@
         <v>489</v>
       </c>
       <c r="B487" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C487" s="25">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D487" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E487" s="27">
-        <v>40.799999999999997</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -11144,16 +11138,16 @@
         <v>528</v>
       </c>
       <c r="B526" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C526" s="25">
-        <v>64.5</v>
+        <v>59.5</v>
       </c>
       <c r="D526" s="26">
         <v>1.4</v>
       </c>
       <c r="E526" s="27">
-        <v>90.3</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -11195,16 +11189,16 @@
         <v>531</v>
       </c>
       <c r="B529" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C529" s="25">
-        <v>53</v>
+        <v>51.5</v>
       </c>
       <c r="D529" s="26">
         <v>1.95</v>
       </c>
       <c r="E529" s="27">
-        <v>103.35</v>
+        <v>100.43</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11246,16 +11240,16 @@
         <v>534</v>
       </c>
       <c r="B532" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C532" s="25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D532" s="26">
         <v>3</v>
       </c>
       <c r="E532" s="27">
-        <v>39</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -11582,16 +11576,16 @@
         <v>554</v>
       </c>
       <c r="B552" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C552" s="25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D552" s="26">
         <v>3.1</v>
       </c>
       <c r="E552" s="27">
-        <v>86.8</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11599,16 +11593,16 @@
         <v>555</v>
       </c>
       <c r="B553" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C553" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D553" s="26">
         <v>9.5</v>
       </c>
       <c r="E553" s="27">
-        <v>57</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11650,16 +11644,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C556" s="25">
-        <v>73.2</v>
+        <v>56.2</v>
       </c>
       <c r="D556" s="26">
         <v>3.9</v>
       </c>
       <c r="E556" s="27">
-        <v>285.48</v>
+        <v>219.18</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11735,16 +11729,16 @@
         <v>563</v>
       </c>
       <c r="B561" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C561" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D561" s="26">
         <v>3.6</v>
       </c>
       <c r="E561" s="27">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
@@ -11769,16 +11763,16 @@
         <v>565</v>
       </c>
       <c r="B563" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C563" s="25">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="D563" s="26">
         <v>3.14</v>
       </c>
       <c r="E563" s="27">
-        <v>98.28</v>
+        <v>95.14</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -11786,16 +11780,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C564" s="25">
-        <v>82.25</v>
+        <v>80.75</v>
       </c>
       <c r="D564" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E564" s="27">
-        <v>189.18</v>
+        <v>185.73</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11837,17 +11831,11 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>59</v>
-      </c>
-      <c r="C567" s="25">
-        <v>3</v>
-      </c>
-      <c r="D567" s="26">
-        <v>3.5</v>
-      </c>
-      <c r="E567" s="27">
-        <v>10.5</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C567" s="28"/>
+      <c r="D567" s="29"/>
+      <c r="E567" s="28"/>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="23" t="s">
@@ -11973,16 +11961,16 @@
         <v>577</v>
       </c>
       <c r="B575" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C575" s="25">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="D575" s="26">
         <v>2.71</v>
       </c>
       <c r="E575" s="27">
-        <v>39.32</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12041,16 +12029,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C579" s="25">
-        <v>91.5</v>
+        <v>89</v>
       </c>
       <c r="D579" s="26">
         <v>1.8</v>
       </c>
       <c r="E579" s="27">
-        <v>164.7</v>
+        <v>160.19999999999999</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12182,10 +12170,10 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C588" s="25">
-        <v>293.5</v>
+        <v>275.5</v>
       </c>
       <c r="D588" s="29"/>
       <c r="E588" s="28"/>
@@ -12195,10 +12183,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C589" s="25">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12221,10 +12209,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C591" s="25">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12247,16 +12235,16 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C593" s="25">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="D593" s="26">
         <v>0.87</v>
       </c>
       <c r="E593" s="27">
-        <v>349.74</v>
+        <v>341.04</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -12264,16 +12252,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C594" s="25">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="D594" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E594" s="27">
-        <v>440.22</v>
+        <v>437.32</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12393,10 +12381,10 @@
         <v>605</v>
       </c>
       <c r="B603" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C603" s="25">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D603" s="29"/>
       <c r="E603" s="28"/>
@@ -12679,16 +12667,16 @@
         <v>623</v>
       </c>
       <c r="B621" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C621" s="25">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="D621" s="26">
         <v>3.5</v>
       </c>
       <c r="E621" s="27">
-        <v>56</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
@@ -12713,16 +12701,16 @@
         <v>625</v>
       </c>
       <c r="B623" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C623" s="25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D623" s="26">
         <v>5.75</v>
       </c>
       <c r="E623" s="27">
-        <v>89.13</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
@@ -12866,16 +12854,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C632" s="25">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -13101,13 +13089,13 @@
         <v>12</v>
       </c>
       <c r="C646" s="25">
-        <v>0.5</v>
+        <v>15.5</v>
       </c>
       <c r="D646" s="26">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="E646" s="27">
-        <v>2.73</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -13132,16 +13120,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C648" s="25">
-        <v>226.36</v>
+        <v>223.86</v>
       </c>
       <c r="D648" s="26">
         <v>1.7</v>
       </c>
       <c r="E648" s="27">
-        <v>384.81</v>
+        <v>380.56</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13200,16 +13188,16 @@
         <v>654</v>
       </c>
       <c r="B652" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C652" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D652" s="26">
         <v>7.5</v>
       </c>
       <c r="E652" s="27">
-        <v>26.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13251,16 +13239,16 @@
         <v>657</v>
       </c>
       <c r="B655" s="24">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C655" s="25">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="D655" s="26">
         <v>2.85</v>
       </c>
       <c r="E655" s="27">
-        <v>237.98</v>
+        <v>235.13</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -13500,16 +13488,16 @@
         <v>672</v>
       </c>
       <c r="B670" s="24">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C670" s="25">
-        <v>159</v>
+        <v>155.5</v>
       </c>
       <c r="D670" s="26">
         <v>3.1</v>
       </c>
       <c r="E670" s="27">
-        <v>492.9</v>
+        <v>482.05</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13568,16 +13556,16 @@
         <v>676</v>
       </c>
       <c r="B674" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C674" s="25">
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
       <c r="D674" s="26">
         <v>3.75</v>
       </c>
       <c r="E674" s="27">
-        <v>129.38</v>
+        <v>125.63</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -13895,7 +13883,7 @@
         <v>14</v>
       </c>
       <c r="C694" s="25">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D694" s="29"/>
       <c r="E694" s="28"/>
@@ -13957,10 +13945,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C699" s="25">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -13970,10 +13958,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C700" s="25">
-        <v>69.5</v>
+        <v>68.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14317,16 +14305,16 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C727" s="25">
-        <v>21.75</v>
+        <v>21.5</v>
       </c>
       <c r="D727" s="26">
         <v>2.5</v>
       </c>
       <c r="E727" s="27">
-        <v>54.38</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -14402,16 +14390,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C732" s="25">
-        <v>47.75</v>
+        <v>44.5</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>119.38</v>
+        <v>111.25</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14447,10 +14435,10 @@
         <v>737</v>
       </c>
       <c r="B735" s="24">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C735" s="25">
-        <v>-494</v>
+        <v>-511</v>
       </c>
       <c r="D735" s="29"/>
       <c r="E735" s="28"/>
@@ -14461,11 +14449,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>44882.720000000001</v>
+        <v>45034.71</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>107616.3</v>
+        <v>107907.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC)</t>
+    <t>.1001 PATRIKA (25/251)</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA (25/262)</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA (25/261)</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA (25/361/861)</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA (25/362/862)</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA (25/282)</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA (25/281)</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC) (2595 PINK)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB)</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G)</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU)</t>
+    <t>1010 PATRIKA (6321)</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA (11043 OFFSET)</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA (1011 OFFSET)</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA (1014 OFFSET)</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA (1222 SBC)</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA (1235)</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA (2101 VV)</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC) (25409)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA (25418)</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA (25322)</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA (25323)</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC) (1173 SBC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC) (5346)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC) (2596)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA (1042)</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA (1043)</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA (GOPAL 11)</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA (GOPAL 1)</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA (2002 YLW)</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA (2003 R)</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA (276-A)</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW (25419)</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED (25420)</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y (25421)</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R (25422)</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA (277-B)</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA (1819 MONARCH)</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN (1709)</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155) (1155 JSK)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70 (NEW SAVASHREE 52)</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51) (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52) (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53) (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54) (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R) (120 GSM RED)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01) (JCC 01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02) (JCC 02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU) (BP RED)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -422,109 +422,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M)</t>
+    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA (LEGACY - 10)</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA (LEGACY - 11)</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA (LEGACY - 12)</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (LOTTERY - 80)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -554,1234 +554,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc'''</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (Alter Available)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV)</t>
+    <t>4251 PATRIKA (JC) (5342)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA (5207)</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA (5206)</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210) (10273/10277)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA (82)</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC) (1129)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC) (101 SBC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA (1102)</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC) (959)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC) (2571)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU) (1351)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA (83)</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA (25-145)</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC) (25-046)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA (111 SBC)</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA (1151 GGN)</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC) (25216)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA (2547)</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC) (25369)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA (25367)</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA (25368)</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA (1031)</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA (25301)</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA (25312 MYRA)</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA (3117)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN) (3116)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA (1173 VV)</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA (5254  RJN)</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA (25402)</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA (10001 NEW)</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA (10002 NEW)</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA (316 MYRA)</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA (25401)</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA (25311)</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA (25312)</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA (5273)</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA (286-A)</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA (1407)</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA (306)</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA (5501)</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA (2011)</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA (25314)</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA (25315)</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU) (1402)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC) (1234*-M)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA (5172)</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA (25313)</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA (BALAJI 5202)</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA (LOTUS 430)</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU) (251 KBC)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU) (273-A)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M) (5087)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA (5295)</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA (5213)</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M) (25/162)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA (25/272)</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC) (25/271)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (25/171)</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA (8802)</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA (8803)</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC) (7713)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU) (1405)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA (7705)</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA (2522 GE)</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA (2517 GE)</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA (2527)</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA (2536)</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC) (S-301)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU) (S-305)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC) (1103)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी) (741)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA (5347 DIRECT)</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M) (3161)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA (1151 VV)</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC) (25-082)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC) (3701 SBC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA (2081)</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA (296-A (NEHA)</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA (2501 GE NEW)</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA (2520 GE)</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA (DCU) (5267)</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA (5258 RJ)</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA (2023)</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC) (2206)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA (25214)</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA (2061 SBC)</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA (5236 RJ)</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC) (1411 KBC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA (5350)</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA (5251)</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA (5240)</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA (25316)</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA (25321)</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M) (857)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU) (5339)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021) (2456)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA (2071)</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA (5261 RJND)</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC) (5335)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA (253-A / 257-A)</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA (5356 RJ)</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA (DCU) (5333)</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA (5308)</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC) (AS-402)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC) (5313)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA (5305)</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA (2031)</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU) (3331)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU) (25436)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA (5186)</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC) (7033)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M) (25/122)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC) (8055 VV)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC) (612 VV)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC) (25/072)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC) (2525 /2552)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA (2515)</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU) (2542)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA (2523)</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M) (7066)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA (1054)</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA (2231)</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA (2232)</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU) (5382)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M) (5283)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC) (25-052)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B (2942-B)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC) (2942)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M) (S-96)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC) (2101)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA (2261)</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA (2353)</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M) (2732)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA (718)</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M) (S-32)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU) (2792)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA (5261 NICE)</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M) (5424)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA (5231)</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M) (5004)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G) (5379)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA (2903)</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M) (2952)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA (2312 SBC)</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA (2293)</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-* (2915)</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M) (25358)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA (5387)</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA (175)</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M) (1742-B)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA (1679)</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M) (3002)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M) (S-39)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M) (S-74)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M) (25353)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M) (25351)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA (2205)</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA (25335)</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M) (S-77)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA (2531)</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M) (5808)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA (S-326)</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M) (3471)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA (3211 SBC)</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC) (2202 SBC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M) (S-51)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA (2264)</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M) (25133)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA (3131 SBC)</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M) (2365)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA (2803)</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC) (2931)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M) (226)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M) (2541)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M) (77-B)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC) (25324)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA (2771)</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA (3271)</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M) (6125)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA (242-A)</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC) (3102)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M) (221-A)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA (25442)</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA (25440)</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA (993)</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC) (2373)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M) (1211)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU) (5276)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA (2111)</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU) (7069)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M) (7067)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC) (1131)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC) (15)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M) (25337)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA (064)</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC) (2753)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU) (772)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU) (GOL)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L) (5164)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA (5126)</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA (5111)</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M) (5196)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA (5191)</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R (3023)</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M) (0523)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA (95)</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M) (3053)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M) (3019)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC) (3017 VV)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA (3015)</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (25164)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU) (25131)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M) (3422)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M) (1193)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA (25184)</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M) (25135)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M) (25116)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M) (Alter Available) (25161)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M) (25111)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU) (932)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA (3562)</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M) (S-313)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M) (25183)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA (25162 GE)</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M) (3014)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (2291)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B) (2291-B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M) (25380)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU) (25132)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M) (3031)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M) (3034)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M) (25382)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M) (3402)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC (3431)</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA (3421)</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M) (3461)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M) (5319)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA (25193 (Padding))</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA (25194 (Padding))</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M) (1281)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA (3424)</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA (7103 (PADDING))</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M) (5823)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU) (8102)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU) (6197)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M) (1868-B)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M) (1868)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M) (1872)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M) (6132)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU) (6196)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU) (1503)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M) (1282)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU) (533 KBC)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.) (133)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.) (1522)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.) (1178)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.) (AS-20)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.) (4087)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.) (2204)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.) (2482)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.) (12)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA (25/252)</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA (25/264-263)</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA (25/363/863)</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA (25/283)</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA (25/273)</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA (25/172)</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU) (25895)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA (2521)</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA (2526)</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA (2535)</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA (84)</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA (2543 INV OFFSET)</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA (2234)</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA (S-201 INV)</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA (5121)</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA (720)</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F) (25-146)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA (3702)</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA (254 SBC)</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F) (25-047)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA (2082)</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-* (4052)</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA (2103)</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA (1223 SBC)</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA (6310 GE)</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA (2532)</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA (1174)</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA (1034)</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA (2204 INV)</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA (06)</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA (303)</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA (25323 INV)</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA (25413)</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA (2597)</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA (25896)</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F) (243-C)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA (1855)</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA (1044 SBC)</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA (2014)</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA (2006)</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU) (6106)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA (GOPAL 32)</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA (2005- G)</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA (5180)</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU) (3753)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA (273 NEHA)</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA (278-B)</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1793,7 +1793,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.)</t>
+    <t>9001 CARD (O.C.) (2498 Cream)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1817,298 +1817,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS</t>
-  </si>
-  <si>
-    <t>9240 CARDS</t>
-  </si>
-  <si>
-    <t>9241 CARDS</t>
-  </si>
-  <si>
-    <t>9242 CARDS</t>
-  </si>
-  <si>
-    <t>9243 CARDS</t>
-  </si>
-  <si>
-    <t>9244 CARDS</t>
-  </si>
-  <si>
-    <t>9301 CARDS</t>
-  </si>
-  <si>
-    <t>9302 CARDS</t>
-  </si>
-  <si>
-    <t>9303 CARDS</t>
-  </si>
-  <si>
-    <t>9304 CARDS</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070)</t>
-  </si>
-  <si>
-    <t>9306 CARDS</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M)</t>
-  </si>
-  <si>
-    <t>9308 CARDS</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc)</t>
-  </si>
-  <si>
-    <t>9310 CARDS</t>
-  </si>
-  <si>
-    <t>9311 CARDS</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9314 CARDS</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9317 CARDS</t>
-  </si>
-  <si>
-    <t>9318 CARDS</t>
-  </si>
-  <si>
-    <t>9319 CARDS</t>
-  </si>
-  <si>
-    <t>9320 CARDS</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD)</t>
-  </si>
-  <si>
-    <t>9324 CARDS</t>
-  </si>
-  <si>
-    <t>9325 CARDS</t>
-  </si>
-  <si>
-    <t>9326 CARDS</t>
-  </si>
-  <si>
-    <t>9327 CARDS</t>
-  </si>
-  <si>
-    <t>9328 CARDS</t>
-  </si>
-  <si>
-    <t>9329 CARDS</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC</t>
-  </si>
-  <si>
-    <t>9333 CARDS</t>
-  </si>
-  <si>
-    <t>9334 CARDS</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (Design Change)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC)</t>
-  </si>
-  <si>
-    <t>9338 CARDS</t>
-  </si>
-  <si>
-    <t>9339 CARDS</t>
-  </si>
-  <si>
-    <t>9340 CARDS</t>
-  </si>
-  <si>
-    <t>9341 CARDS</t>
-  </si>
-  <si>
-    <t>9342 CARDS</t>
-  </si>
-  <si>
-    <t>9343 CARDS</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu)</t>
-  </si>
-  <si>
-    <t>9345 CARDS</t>
-  </si>
-  <si>
-    <t>9346 CARDS</t>
-  </si>
-  <si>
-    <t>9347 CARDS</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9351 Card - B</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9353 CARDS</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9355 CARDS</t>
-  </si>
-  <si>
-    <t>9356 CARDS</t>
-  </si>
-  <si>
-    <t>9357 CARDS</t>
-  </si>
-  <si>
-    <t>9358 CARDS</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega</t>
-  </si>
-  <si>
-    <t>9361 CARDS</t>
-  </si>
-  <si>
-    <t>9362 CARDS</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9365 CARDS</t>
-  </si>
-  <si>
-    <t>9366 CARDS</t>
-  </si>
-  <si>
-    <t>9367 CARDS</t>
-  </si>
-  <si>
-    <t>9368 CARDS</t>
-  </si>
-  <si>
-    <t>9369 CARDS</t>
-  </si>
-  <si>
-    <t>9370 CARDS</t>
-  </si>
-  <si>
-    <t>9371 CARDS</t>
-  </si>
-  <si>
-    <t>9372 CARDS</t>
-  </si>
-  <si>
-    <t>9373 CARDS</t>
-  </si>
-  <si>
-    <t>9374 CARDS</t>
-  </si>
-  <si>
-    <t>9375 CARDS</t>
-  </si>
-  <si>
-    <t>9376 CARDS</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9378 CARDS</t>
+    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
+  </si>
+  <si>
+    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
+  </si>
+  <si>
+    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
+  </si>
+  <si>
+    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
+  </si>
+  <si>
+    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9301 CARDS (4242)</t>
+  </si>
+  <si>
+    <t>9302 CARDS (5076)</t>
+  </si>
+  <si>
+    <t>9303 CARDS (5080 Pink)</t>
+  </si>
+  <si>
+    <t>9304 CARDS (5083 Blue)</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070) (4701 Nice)</t>
+  </si>
+  <si>
+    <t>9306 CARDS (0543 Nice)</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M) (5243 Nice)</t>
+  </si>
+  <si>
+    <t>9308 CARDS (9852)</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
+  </si>
+  <si>
+    <t>9310 CARDS (3103)</t>
+  </si>
+  <si>
+    <t>9311 CARDS (3115)</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T) (208 VV)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T) (216)</t>
+  </si>
+  <si>
+    <t>9314 CARDS (P-1)</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU) (P-2)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU) (P-3)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (P-4)</t>
+  </si>
+  <si>
+    <t>9318 CARDS (25905)</t>
+  </si>
+  <si>
+    <t>9319 CARDS (25906)</t>
+  </si>
+  <si>
+    <t>9320 CARDS (S-20)</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9325 CARDS (5229)</t>
+  </si>
+  <si>
+    <t>9326 CARDS (1601)</t>
+  </si>
+  <si>
+    <t>9327 CARDS (25908)</t>
+  </si>
+  <si>
+    <t>9328 CARDS (2543)</t>
+  </si>
+  <si>
+    <t>9329 CARDS (3606)</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T) (9557)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T) (9560)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC (9847)</t>
+  </si>
+  <si>
+    <t>9333 CARDS (6042)</t>
+  </si>
+  <si>
+    <t>9334 CARDS (10X6 WHITE (2898))</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
+  </si>
+  <si>
+    <t>9336 CARDS (Design Change) (2884)</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC) (1635 AP)</t>
+  </si>
+  <si>
+    <t>9338 CARDS (1637 AP)</t>
+  </si>
+  <si>
+    <t>9339 CARDS (5361)</t>
+  </si>
+  <si>
+    <t>9340 CARDS (5658)</t>
+  </si>
+  <si>
+    <t>9341 CARDS (5497)</t>
+  </si>
+  <si>
+    <t>9342 CARDS (2861)</t>
+  </si>
+  <si>
+    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu) (689)</t>
+  </si>
+  <si>
+    <t>9345 CARDS (358 KALYANI)</t>
+  </si>
+  <si>
+    <t>9346 CARDS (359)</t>
+  </si>
+  <si>
+    <t>9347 CARDS (2853)</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी) (S-124)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window) (S-120)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1632)</t>
+  </si>
+  <si>
+    <t>9351 Card - B (1603 B)</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC (1603)</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
+  </si>
+  <si>
+    <t>9353 CARDS (1618)</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU) (345)</t>
+  </si>
+  <si>
+    <t>9355 CARDS (1624)</t>
+  </si>
+  <si>
+    <t>9356 CARDS (2895/2897)</t>
+  </si>
+  <si>
+    <t>9357 CARDS (2872)</t>
+  </si>
+  <si>
+    <t>9358 CARDS (WHITE PATTA)</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
+  </si>
+  <si>
+    <t>9361 CARDS (25426)</t>
+  </si>
+  <si>
+    <t>9362 CARDS (363)</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T) (1652)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T) (1612)</t>
+  </si>
+  <si>
+    <t>9365 CARDS (25429)</t>
+  </si>
+  <si>
+    <t>9366 CARDS (25427 GOLDEN)</t>
+  </si>
+  <si>
+    <t>9367 CARDS (5652)</t>
+  </si>
+  <si>
+    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
+  </si>
+  <si>
+    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
+  </si>
+  <si>
+    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
+  </si>
+  <si>
+    <t>9371 CARDS (3111 VP)</t>
+  </si>
+  <si>
+    <t>9372 CARDS (9*5 YLW SET (2841))</t>
+  </si>
+  <si>
+    <t>9373 CARDS (1482)</t>
+  </si>
+  <si>
+    <t>9374 CARDS (1485)</t>
+  </si>
+  <si>
+    <t>9375 CARDS (1452 WHITE)</t>
+  </si>
+  <si>
+    <t>9376 CARDS (1529 PRINCE)</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
+  </si>
+  <si>
+    <t>9378 CARDS (2892)</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2141,19 +2141,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU)</t>
+    <t>9389 CARDS (9147 RJ)</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU) (118KBC)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC)</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC</t>
+    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2183,7 +2183,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR)</t>
+    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2207,37 +2207,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (DC)</t>
+    <t>RX-01 ENVELOPE (DC) (LX01)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (DC) (LX02)</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE (LX03)</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE (DC) (LX04)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (DC) (LX05)</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE (LX06)</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE (DC) (LX07)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (DC) (LX08)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (DC) (LX09)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर</t>
+    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2767,7 +2767,7 @@
   <dimension ref="A1:E736"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -3121,17 +3121,11 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>45</v>
-      </c>
-      <c r="C25" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="26">
-        <v>1.66</v>
-      </c>
-      <c r="E25" s="27">
-        <v>0.83</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="28"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
@@ -3172,16 +3166,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" s="25">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,16 +3200,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" s="25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>80.92</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3302,16 +3296,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" s="25">
-        <v>56.5</v>
+        <v>51.5</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>129.94999999999999</v>
+        <v>118.45</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3404,16 +3398,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C42" s="25">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>148.15</v>
+        <v>145.69999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3421,16 +3415,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C43" s="25">
-        <v>138.5</v>
+        <v>134.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>341.46</v>
+        <v>331.6</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3523,16 +3517,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C49" s="25">
-        <v>259</v>
+        <v>258.5</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>362.6</v>
+        <v>361.9</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3557,16 +3551,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51" s="25">
-        <v>179</v>
+        <v>175.5</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>322.2</v>
+        <v>315.89999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3642,16 +3636,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C56" s="25">
-        <v>173.5</v>
+        <v>170.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>312.3</v>
+        <v>306.89999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3761,16 +3755,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63" s="25">
-        <v>65.5</v>
+        <v>60.5</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>108.08</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3874,16 +3868,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C70" s="25">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>560</v>
+        <v>557.20000000000005</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3976,16 +3970,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C76" s="25">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>544.79999999999995</v>
+        <v>537.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4180,16 +4174,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C88" s="25">
-        <v>1066.5</v>
+        <v>1065.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1813.05</v>
+        <v>1811.35</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4289,16 +4283,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C95" s="25">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4430,16 +4424,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C104" s="25">
-        <v>202.5</v>
+        <v>199.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>506.25</v>
+        <v>498.75</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4515,10 +4509,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C109" s="25">
-        <v>114.5</v>
+        <v>111.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4528,10 +4522,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C110" s="25">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4897,16 +4891,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C137" s="25">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D137" s="26">
         <v>12.5</v>
       </c>
       <c r="E137" s="27">
-        <v>162.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5269,16 +5263,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C159" s="25">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="D159" s="26">
         <v>11.5</v>
       </c>
       <c r="E159" s="27">
-        <v>120.75</v>
+        <v>345</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5286,16 +5280,16 @@
         <v>162</v>
       </c>
       <c r="B160" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C160" s="25">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="D160" s="26">
         <v>11.5</v>
       </c>
       <c r="E160" s="27">
-        <v>276</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5320,16 +5314,16 @@
         <v>164</v>
       </c>
       <c r="B162" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C162" s="25">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D162" s="26">
         <v>11.5</v>
       </c>
       <c r="E162" s="27">
-        <v>51.75</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -6133,16 +6127,16 @@
         <v>215</v>
       </c>
       <c r="B213" s="24">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C213" s="25">
-        <v>328.5</v>
+        <v>323.5</v>
       </c>
       <c r="D213" s="26">
         <v>2.7</v>
       </c>
       <c r="E213" s="27">
-        <v>886.95</v>
+        <v>873.45</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -6422,16 +6416,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C230" s="25">
-        <v>44.5</v>
+        <v>42.5</v>
       </c>
       <c r="D230" s="26">
         <v>3.5</v>
       </c>
       <c r="E230" s="27">
-        <v>155.75</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6629,13 +6623,13 @@
         <v>47</v>
       </c>
       <c r="C244" s="25">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D244" s="26">
         <v>4.8</v>
       </c>
       <c r="E244" s="27">
-        <v>129.6</v>
+        <v>225.6</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6728,16 +6722,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C250" s="25">
-        <v>179</v>
+        <v>175.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>698.1</v>
+        <v>684.45</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6942,16 +6936,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C264" s="25">
-        <v>324</v>
+        <v>321.5</v>
       </c>
       <c r="D264" s="26">
         <v>4.28</v>
       </c>
       <c r="E264" s="27">
-        <v>1386.72</v>
+        <v>1376.02</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -7218,16 +7212,16 @@
         <v>284</v>
       </c>
       <c r="B282" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C282" s="25">
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
       <c r="D282" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E282" s="27">
-        <v>427.71</v>
+        <v>422.98</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7456,16 +7450,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C296" s="25">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D296" s="26">
         <v>6.06</v>
       </c>
       <c r="E296" s="27">
-        <v>1752.52</v>
+        <v>1734.47</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -8324,16 +8318,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C350" s="25">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="D350" s="26">
         <v>5.94</v>
       </c>
       <c r="E350" s="27">
-        <v>371.25</v>
+        <v>368.28</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8375,16 +8369,16 @@
         <v>355</v>
       </c>
       <c r="B353" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C353" s="25">
-        <v>35.35</v>
+        <v>32.85</v>
       </c>
       <c r="D353" s="26">
         <v>4.75</v>
       </c>
       <c r="E353" s="27">
-        <v>167.91</v>
+        <v>156.04</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -9347,16 +9341,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C413" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D413" s="26">
         <v>8</v>
       </c>
       <c r="E413" s="27">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -10242,16 +10236,16 @@
         <v>472</v>
       </c>
       <c r="B470" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C470" s="25">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D470" s="26">
         <v>12.5</v>
       </c>
       <c r="E470" s="27">
-        <v>81.25</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -10293,16 +10287,16 @@
         <v>475</v>
       </c>
       <c r="B473" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C473" s="25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D473" s="26">
         <v>10</v>
       </c>
       <c r="E473" s="27">
-        <v>140</v>
+        <v>70</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -10389,16 +10383,16 @@
         <v>481</v>
       </c>
       <c r="B479" s="24">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C479" s="25">
-        <v>3.5</v>
+        <v>-7</v>
       </c>
       <c r="D479" s="26">
         <v>10.32</v>
       </c>
       <c r="E479" s="27">
-        <v>36.119999999999997</v>
+        <v>-72.25</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -11257,16 +11251,16 @@
         <v>535</v>
       </c>
       <c r="B533" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C533" s="25">
-        <v>49.5</v>
+        <v>48</v>
       </c>
       <c r="D533" s="26">
         <v>3.8</v>
       </c>
       <c r="E533" s="27">
-        <v>188.1</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11576,16 +11570,16 @@
         <v>554</v>
       </c>
       <c r="B552" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C552" s="25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D552" s="26">
         <v>3.1</v>
       </c>
       <c r="E552" s="27">
-        <v>71.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11596,13 +11590,13 @@
         <v>39</v>
       </c>
       <c r="C553" s="25">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D553" s="26">
         <v>9.5</v>
       </c>
       <c r="E553" s="27">
-        <v>47.5</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11893,16 +11887,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C571" s="25">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
       <c r="D571" s="26">
         <v>2.66</v>
       </c>
       <c r="E571" s="27">
-        <v>54.53</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11961,16 +11955,16 @@
         <v>577</v>
       </c>
       <c r="B575" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C575" s="25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="D575" s="26">
         <v>2.71</v>
       </c>
       <c r="E575" s="27">
-        <v>36.61</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12097,16 +12091,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C583" s="25">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D583" s="26">
         <v>1.2</v>
       </c>
       <c r="E583" s="27">
-        <v>228</v>
+        <v>225.6</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12153,16 +12147,16 @@
         <v>589</v>
       </c>
       <c r="B587" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C587" s="25">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D587" s="26">
         <v>1.5</v>
       </c>
       <c r="E587" s="27">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -12196,10 +12190,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C590" s="25">
-        <v>253.5</v>
+        <v>233.5</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12252,16 +12246,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C594" s="25">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="D594" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E594" s="27">
-        <v>437.32</v>
+        <v>425.72</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -13120,16 +13114,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C648" s="25">
-        <v>223.86</v>
+        <v>222.86</v>
       </c>
       <c r="D648" s="26">
         <v>1.7</v>
       </c>
       <c r="E648" s="27">
-        <v>380.56</v>
+        <v>378.86</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13369,16 +13363,16 @@
         <v>665</v>
       </c>
       <c r="B663" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C663" s="25">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="D663" s="26">
         <v>4.8</v>
       </c>
       <c r="E663" s="27">
-        <v>84</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -13488,16 +13482,16 @@
         <v>672</v>
       </c>
       <c r="B670" s="24">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C670" s="25">
-        <v>155.5</v>
+        <v>153.5</v>
       </c>
       <c r="D670" s="26">
         <v>3.1</v>
       </c>
       <c r="E670" s="27">
-        <v>482.05</v>
+        <v>475.85</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13556,16 +13550,16 @@
         <v>676</v>
       </c>
       <c r="B674" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C674" s="25">
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
       <c r="D674" s="26">
         <v>3.75</v>
       </c>
       <c r="E674" s="27">
-        <v>125.63</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -13658,16 +13652,16 @@
         <v>682</v>
       </c>
       <c r="B680" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C680" s="25">
-        <v>115.5</v>
+        <v>113.5</v>
       </c>
       <c r="D680" s="26">
         <v>2.25</v>
       </c>
       <c r="E680" s="27">
-        <v>259.88</v>
+        <v>255.38</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -14240,10 +14234,10 @@
         <v>724</v>
       </c>
       <c r="B722" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C722" s="25">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="D722" s="29"/>
       <c r="E722" s="28"/>
@@ -14305,16 +14299,16 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C727" s="25">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="D727" s="26">
         <v>2.5</v>
       </c>
       <c r="E727" s="27">
-        <v>53.75</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -14356,16 +14350,16 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C730" s="25">
-        <v>3.25</v>
+        <v>0.25</v>
       </c>
       <c r="D730" s="26">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="E730" s="27">
-        <v>8.1300000000000008</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -14407,16 +14401,16 @@
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C733" s="25">
-        <v>39.25</v>
+        <v>34.25</v>
       </c>
       <c r="D733" s="26">
         <v>2.5</v>
       </c>
       <c r="E733" s="27">
-        <v>98.13</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -14449,11 +14443,11 @@
       </c>
       <c r="B736" s="31"/>
       <c r="C736" s="32">
-        <v>45034.71</v>
+        <v>44878.2</v>
       </c>
       <c r="D736" s="33"/>
       <c r="E736" s="34">
-        <v>107907.94</v>
+        <v>107452.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC)</t>
+    <t>.1001 PATRIKA (25/251)</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA (25/262)</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA (25/261)</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA (25/361/861)</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA (25/362/862)</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA (25/282)</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA (25/281)</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC) (2595 PINK)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB)</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G)</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR)</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY)</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU)</t>
+    <t>1010 PATRIKA (6321)</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA (11043 OFFSET)</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA (1011 OFFSET)</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA (1014 OFFSET)</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA (1222 SBC)</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA (1235)</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA (2101 VV)</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC) (25409)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA (25418)</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA (25322)</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA (25323)</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC) (1173 SBC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC) (5346)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC) (2596)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA (1042)</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA (1043)</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA (GOPAL 11)</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA (GOPAL 1)</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA (2002 YLW)</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA (2003 R)</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA (276-A)</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW (25419)</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED (25420)</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y (25421)</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R (25422)</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA (277-B)</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA (1819 MONARCH)</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN (1709)</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155) (1155 JSK)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70 (NEW SAVASHREE 52)</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51) (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52) (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53) (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54) (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R) (120 GSM RED)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01) (JCC 01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02) (JCC 02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU) (BP RED)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -425,109 +425,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M)</t>
+    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA (LEGACY - 10)</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA (LEGACY - 11)</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA (LEGACY - 12)</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA (LOTTERY - 80)</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -557,1234 +557,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc'''</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (Alter Available)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L)</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-*</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV)</t>
+    <t>4251 PATRIKA (JC) (5342)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA (5207)</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA (5206)</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210) (10273/10277)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA (82)</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC) (1129)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC) (101 SBC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA (1102)</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC) (959)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC) (2571)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU) (1351)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA (83)</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA (25-145)</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC) (25-046)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA (111 SBC)</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA (1151 GGN)</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC) (25216)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA (2547)</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC) (25369)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA (25367)</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA (25368)</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA (1031)</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA (25301)</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA (25312 MYRA)</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA (3117)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN) (3116)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA (1173 VV)</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA (5254  RJN)</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA (25402)</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA (10001 NEW)</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA (10002 NEW)</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA (316 MYRA)</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA (25401)</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA (25311)</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA (25312)</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA (5273)</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA (286-A)</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA (1407)</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA (306)</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA (5501)</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA (2011)</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA (25314)</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA (25315)</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU) (1402)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC) (1234*-M)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA (5172)</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA (25313)</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA (BALAJI 5202)</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA (LOTUS 430)</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU) (251 KBC)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU) (273-A)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M) (5087)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA (5295)</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA (5213)</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M) (25/162)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA (25/272)</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC) (25/271)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA (25/171)</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA (8802)</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA (8803)</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC) (7713)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU) (1405)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA (7705)</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA (2522 GE)</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA (2517 GE)</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA (2527)</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA (2536)</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC) (S-301)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU) (S-305)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC) (1103)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी) (741)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA (5347 DIRECT)</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M) (3161)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA (1151 VV)</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC) (25-082)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC) (3701 SBC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA (2081)</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA (296-A (NEHA)</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA (2501 GE NEW)</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA (2520 GE)</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA (DCU) (5267)</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA (5258 RJ)</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA (2023)</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC) (2206)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA (25214)</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA (2061 SBC)</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA (5236 RJ)</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC) (1411 KBC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA (5350)</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA (5251)</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA (5240)</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA (25316)</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA (25321)</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M) (857)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU) (5339)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021) (2456)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA (2071)</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA (5261 RJND)</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC) (5335)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA (253-A / 257-A)</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA (5356 RJ)</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA (DCU) (5333)</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA (5308)</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC) (AS-402)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC) (5313)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA (5305)</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA (2031)</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU) (3331)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU) (25436)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA (5186)</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC) (7033)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M) (25/122)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC) (8055 VV)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC) (612 VV)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC) (25/072)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC) (2525 /2552)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA (2515)</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU) (2542)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA (2523)</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M) (7066)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA (1054)</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA (2231)</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA (2232)</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU) (5382)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M) (5283)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC) (25-052)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B (2942-B)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC) (2942)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M) (S-96)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC) (2101)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA (2261)</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA (2353)</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M) (2732)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA (718)</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M) (S-32)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU) (2792)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA (5261 NICE)</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M) (5424)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA (5231)</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M) (5004)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G) (5379)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA (2903)</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M) (2952)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA (2312 SBC)</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA (2293)</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-* (2915)</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M) (25358)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA (5387)</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA (175)</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M) (1742-B)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA (1679)</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M) (3002)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M) (S-39)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M) (S-74)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M) (25353)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M) (25351)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA (2205)</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA (25335)</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M) (S-77)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA (2531)</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M) (5808)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA (S-326)</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M) (3471)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA (3211 SBC)</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC) (2202 SBC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M) (S-51)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA (2264)</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M) (25133)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA (3131 SBC)</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M) (2365)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA (2803)</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC) (2931)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M) (226)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M) (2541)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M) (77-B)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC) (25324)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA (2771)</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA (3271)</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M) (6125)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA (242-A)</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC) (3102)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M) (221-A)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA (25442)</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA (25440)</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA (993)</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC) (2373)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M) (1211)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU) (5276)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA (2111)</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU) (7069)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M) (7067)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC) (1131)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC) (15)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M) (25337)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA (064)</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC) (2753)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU) (772)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU) (GOL)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L) (5164)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA (5126)</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA (5111)</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M) (5196)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA (5191)</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R (3023)</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M) (0523)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA (95)</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M) (3053)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M) (3019)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC) (3017 VV)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA (3015)</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA (25164)</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU) (25131)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M) (3422)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M) (1193)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA (25184)</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M) (25135)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M) (25116)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M) (Alter Available) (25161)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M) (25111)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU) (932)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA (3562)</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M) (S-313)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M) (25183)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA (25162 GE)</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M) (3014)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (2291)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B) (2291-B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M) (25380)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU) (25132)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M) (3031)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M) (3034)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M) (25382)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M) (3402)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC (3431)</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA (3421)</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M) (3461)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M) (5319)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA (25193 (Padding))</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA (25194 (Padding))</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M) (1281)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA (3424)</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA (7103 (PADDING))</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M) (5823)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU) (8102)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU) (6197)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M) (1868-B)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M) (1868)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M) (1872)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M) (6132)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU) (6196)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU) (1503)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M) (1282)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU) (533 KBC)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.) (133)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.) (1522)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.) (1178)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.) (AS-20)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.) (4087)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.) (2204)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.) (2482)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.) (12)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA (25/252)</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA (25/264-263)</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA (25/363/863)</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA (25/283)</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA (25/273)</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA (25/172)</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU) (25895)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA (2521)</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA (2526)</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA (2535)</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA (84)</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA (2543 INV OFFSET)</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA (2234)</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA (S-201 INV)</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA (5121)</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA (720)</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F) (25-146)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA (3702)</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA (254 SBC)</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F) (25-047)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA (2082)</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-* (4052)</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA (2103)</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA (1223 SBC)</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA (6310 GE)</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA (2532)</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA (1174)</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA (1034)</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA (2204 INV)</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA (06)</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA (303)</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA (25323 INV)</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA (25413)</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA (2597)</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA (25896)</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F) (243-C)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA (1855)</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA (1044 SBC)</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA (2014)</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA (2006)</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU) (6106)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA (GOPAL 32)</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA (2005- G)</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA (5180)</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU) (3753)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA (273 NEHA)</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA (278-B)</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1796,7 +1796,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.)</t>
+    <t>9001 CARD (O.C.) (2498 Cream)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1820,298 +1820,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS</t>
-  </si>
-  <si>
-    <t>9240 CARDS</t>
-  </si>
-  <si>
-    <t>9241 CARDS</t>
-  </si>
-  <si>
-    <t>9242 CARDS</t>
-  </si>
-  <si>
-    <t>9243 CARDS</t>
-  </si>
-  <si>
-    <t>9244 CARDS</t>
-  </si>
-  <si>
-    <t>9301 CARDS</t>
-  </si>
-  <si>
-    <t>9302 CARDS</t>
-  </si>
-  <si>
-    <t>9303 CARDS</t>
-  </si>
-  <si>
-    <t>9304 CARDS</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070)</t>
-  </si>
-  <si>
-    <t>9306 CARDS</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M)</t>
-  </si>
-  <si>
-    <t>9308 CARDS</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc)</t>
-  </si>
-  <si>
-    <t>9310 CARDS</t>
-  </si>
-  <si>
-    <t>9311 CARDS</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9314 CARDS</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9317 CARDS</t>
-  </si>
-  <si>
-    <t>9318 CARDS</t>
-  </si>
-  <si>
-    <t>9319 CARDS</t>
-  </si>
-  <si>
-    <t>9320 CARDS</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD)</t>
-  </si>
-  <si>
-    <t>9324 CARDS</t>
-  </si>
-  <si>
-    <t>9325 CARDS</t>
-  </si>
-  <si>
-    <t>9326 CARDS</t>
-  </si>
-  <si>
-    <t>9327 CARDS</t>
-  </si>
-  <si>
-    <t>9328 CARDS</t>
-  </si>
-  <si>
-    <t>9329 CARDS</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC</t>
-  </si>
-  <si>
-    <t>9333 CARDS</t>
-  </si>
-  <si>
-    <t>9334 CARDS</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (Design Change)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC)</t>
-  </si>
-  <si>
-    <t>9338 CARDS</t>
-  </si>
-  <si>
-    <t>9339 CARDS</t>
-  </si>
-  <si>
-    <t>9340 CARDS</t>
-  </si>
-  <si>
-    <t>9341 CARDS</t>
-  </si>
-  <si>
-    <t>9342 CARDS</t>
-  </si>
-  <si>
-    <t>9343 CARDS</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu)</t>
-  </si>
-  <si>
-    <t>9345 CARDS</t>
-  </si>
-  <si>
-    <t>9346 CARDS</t>
-  </si>
-  <si>
-    <t>9347 CARDS</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9351 Card - B</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC</t>
-  </si>
-  <si>
-    <t>9353 CARDS</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9355 CARDS</t>
-  </si>
-  <si>
-    <t>9356 CARDS</t>
-  </si>
-  <si>
-    <t>9357 CARDS</t>
-  </si>
-  <si>
-    <t>9358 CARDS</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega</t>
-  </si>
-  <si>
-    <t>9361 CARDS</t>
-  </si>
-  <si>
-    <t>9362 CARDS</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T)</t>
-  </si>
-  <si>
-    <t>9365 CARDS</t>
-  </si>
-  <si>
-    <t>9366 CARDS</t>
-  </si>
-  <si>
-    <t>9367 CARDS</t>
-  </si>
-  <si>
-    <t>9368 CARDS</t>
-  </si>
-  <si>
-    <t>9369 CARDS</t>
-  </si>
-  <si>
-    <t>9370 CARDS</t>
-  </si>
-  <si>
-    <t>9371 CARDS</t>
-  </si>
-  <si>
-    <t>9372 CARDS</t>
-  </si>
-  <si>
-    <t>9373 CARDS</t>
-  </si>
-  <si>
-    <t>9374 CARDS</t>
-  </si>
-  <si>
-    <t>9375 CARDS</t>
-  </si>
-  <si>
-    <t>9376 CARDS</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU)</t>
-  </si>
-  <si>
-    <t>9378 CARDS</t>
+    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
+  </si>
+  <si>
+    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
+  </si>
+  <si>
+    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
+  </si>
+  <si>
+    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
+  </si>
+  <si>
+    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
+  </si>
+  <si>
+    <t>9301 CARDS (4242)</t>
+  </si>
+  <si>
+    <t>9302 CARDS (5076)</t>
+  </si>
+  <si>
+    <t>9303 CARDS (5080 Pink)</t>
+  </si>
+  <si>
+    <t>9304 CARDS (5083 Blue)</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070) (4701 Nice)</t>
+  </si>
+  <si>
+    <t>9306 CARDS (0543 Nice)</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M) (5243 Nice)</t>
+  </si>
+  <si>
+    <t>9308 CARDS (9852)</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
+  </si>
+  <si>
+    <t>9310 CARDS (3103)</t>
+  </si>
+  <si>
+    <t>9311 CARDS (3115)</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T) (208 VV)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T) (216)</t>
+  </si>
+  <si>
+    <t>9314 CARDS (P-1)</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU) (P-2)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU) (P-3)</t>
+  </si>
+  <si>
+    <t>9317 CARDS (P-4)</t>
+  </si>
+  <si>
+    <t>9318 CARDS (25905)</t>
+  </si>
+  <si>
+    <t>9319 CARDS (25906)</t>
+  </si>
+  <si>
+    <t>9320 CARDS (S-20)</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
+  </si>
+  <si>
+    <t>9325 CARDS (5229)</t>
+  </si>
+  <si>
+    <t>9326 CARDS (1601)</t>
+  </si>
+  <si>
+    <t>9327 CARDS (25908)</t>
+  </si>
+  <si>
+    <t>9328 CARDS (2543)</t>
+  </si>
+  <si>
+    <t>9329 CARDS (3606)</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T) (9557)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T) (9560)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC (9847)</t>
+  </si>
+  <si>
+    <t>9333 CARDS (6042)</t>
+  </si>
+  <si>
+    <t>9334 CARDS (10X6 WHITE (2898))</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
+  </si>
+  <si>
+    <t>9336 CARDS (Design Change) (2884)</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC) (1635 AP)</t>
+  </si>
+  <si>
+    <t>9338 CARDS (1637 AP)</t>
+  </si>
+  <si>
+    <t>9339 CARDS (5361)</t>
+  </si>
+  <si>
+    <t>9340 CARDS (5658)</t>
+  </si>
+  <si>
+    <t>9341 CARDS (5497)</t>
+  </si>
+  <si>
+    <t>9342 CARDS (2861)</t>
+  </si>
+  <si>
+    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu) (689)</t>
+  </si>
+  <si>
+    <t>9345 CARDS (358 KALYANI)</t>
+  </si>
+  <si>
+    <t>9346 CARDS (359)</t>
+  </si>
+  <si>
+    <t>9347 CARDS (2853)</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी) (S-124)</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window) (S-120)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T) (1632)</t>
+  </si>
+  <si>
+    <t>9351 Card - B (1603 B)</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC (1603)</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
+  </si>
+  <si>
+    <t>9353 CARDS (1618)</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU) (345)</t>
+  </si>
+  <si>
+    <t>9355 CARDS (1624)</t>
+  </si>
+  <si>
+    <t>9356 CARDS (2895/2897)</t>
+  </si>
+  <si>
+    <t>9357 CARDS (2872)</t>
+  </si>
+  <si>
+    <t>9358 CARDS (WHITE PATTA)</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
+  </si>
+  <si>
+    <t>9361 CARDS (25426)</t>
+  </si>
+  <si>
+    <t>9362 CARDS (363)</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T) (1652)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T) (1612)</t>
+  </si>
+  <si>
+    <t>9365 CARDS (25429)</t>
+  </si>
+  <si>
+    <t>9366 CARDS (25427 GOLDEN)</t>
+  </si>
+  <si>
+    <t>9367 CARDS (5652)</t>
+  </si>
+  <si>
+    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
+  </si>
+  <si>
+    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
+  </si>
+  <si>
+    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
+  </si>
+  <si>
+    <t>9371 CARDS (3111 VP)</t>
+  </si>
+  <si>
+    <t>9372 CARDS (9*5 YLW SET (2841))</t>
+  </si>
+  <si>
+    <t>9373 CARDS (1482)</t>
+  </si>
+  <si>
+    <t>9374 CARDS (1485)</t>
+  </si>
+  <si>
+    <t>9375 CARDS (1452 WHITE)</t>
+  </si>
+  <si>
+    <t>9376 CARDS (1529 PRINCE)</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
+  </si>
+  <si>
+    <t>9378 CARDS (2892)</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2144,19 +2144,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU)</t>
+    <t>9389 CARDS (9147 RJ)</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU) (118KBC)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC)</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC</t>
+    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2186,7 +2186,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR)</t>
+    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2210,37 +2210,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (DC)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (DC)</t>
+    <t>RX-01 ENVELOPE (DC) (LX01)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (DC) (LX02)</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE (LX03)</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE (DC) (LX04)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (DC) (LX05)</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE (LX06)</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE (DC) (LX07)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (DC) (LX08)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (DC) (LX09)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर</t>
+    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2770,7 +2770,7 @@
   <dimension ref="A1:E737"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="25">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>333.45</v>
+        <v>329.55</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="25">
-        <v>154.5</v>
+        <v>153</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2994,16 +2994,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="25">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>289.8</v>
+        <v>279.3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3090,16 +3090,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="25">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D23" s="26">
         <v>1.8</v>
       </c>
       <c r="E23" s="27">
-        <v>163.80000000000001</v>
+        <v>158.4</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3169,16 +3169,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" s="25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3186,16 +3186,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="25">
-        <v>35.5</v>
+        <v>33.5</v>
       </c>
       <c r="D29" s="26">
         <v>2.6</v>
       </c>
       <c r="E29" s="27">
-        <v>92.3</v>
+        <v>87.1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3203,16 +3203,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" s="25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>76.16</v>
+        <v>69.02</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3220,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
+        <v>37</v>
+      </c>
+      <c r="C31" s="25">
         <v>36</v>
-      </c>
-      <c r="C31" s="25">
-        <v>41</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>116.85</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3299,16 +3299,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36" s="25">
-        <v>51.5</v>
+        <v>46.5</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>118.45</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3367,16 +3367,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C40" s="25">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>108.07</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3418,16 +3418,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C43" s="25">
-        <v>129.5</v>
+        <v>123.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>319.27</v>
+        <v>304.48</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,16 +3486,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C47" s="25">
-        <v>118.5</v>
+        <v>110</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>150.44</v>
+        <v>139.65</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3503,16 +3503,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C48" s="25">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="D48" s="26">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="E48" s="27">
-        <v>6.37</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3639,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C56" s="25">
-        <v>170.5</v>
+        <v>163.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>306.89999999999998</v>
+        <v>294.3</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,16 +3707,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C60" s="25">
-        <v>938.5</v>
+        <v>936.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1067.6199999999999</v>
+        <v>1065.3399999999999</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3882,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C71" s="25">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>66.5</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3950,16 +3950,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C75" s="25">
-        <v>88.5</v>
+        <v>83.5</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>106.2</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,16 +3967,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C76" s="25">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>537.6</v>
+        <v>530.4</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +4001,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C78" s="25">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>439.2</v>
+        <v>433.2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C84" s="25">
-        <v>1475.5</v>
+        <v>1472.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1918.15</v>
+        <v>1914.25</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4120,16 +4120,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C85" s="25">
-        <v>1424.5</v>
+        <v>1415.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1851.85</v>
+        <v>1840.15</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4137,16 +4137,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C86" s="25">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2058.6999999999998</v>
+        <v>2053.6</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,16 +4154,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C87" s="25">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1344.7</v>
+        <v>1339.6</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4171,16 +4171,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" s="25">
-        <v>1065.5</v>
+        <v>1062.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1811.35</v>
+        <v>1806.25</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C89" s="25">
-        <v>264.5</v>
+        <v>254.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>386.47</v>
+        <v>371.86</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,16 +4205,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C90" s="25">
-        <v>333.7</v>
+        <v>328.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>428.03</v>
+        <v>421.62</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4222,16 +4222,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C91" s="25">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>84.11</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4421,16 +4421,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C104" s="25">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>416.25</v>
+        <v>412.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4472,16 +4472,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C107" s="25">
-        <v>329.5</v>
+        <v>325.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>823.75</v>
+        <v>813.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4608,10 +4608,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C117" s="25">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4918,16 +4918,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C139" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D139" s="26">
         <v>12.75</v>
       </c>
       <c r="E139" s="27">
-        <v>210.37</v>
+        <v>197.62</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,16 +5523,16 @@
         <v>178</v>
       </c>
       <c r="B176" s="24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C176" s="25">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D176" s="26">
         <v>3.25</v>
       </c>
       <c r="E176" s="27">
-        <v>126.75</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -5557,16 +5557,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C178" s="25">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>143.1</v>
+        <v>132.30000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5967,16 +5967,16 @@
         <v>206</v>
       </c>
       <c r="B204" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C204" s="25">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="D204" s="26">
         <v>2.85</v>
       </c>
       <c r="E204" s="27">
-        <v>44.18</v>
+        <v>35.630000000000003</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -6018,16 +6018,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C207" s="25">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>102.7</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6112,7 +6112,7 @@
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1071.77</v>
+        <v>1071.25</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6137,16 +6137,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C214" s="25">
-        <v>323.5</v>
+        <v>316.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>873.45</v>
+        <v>854.55</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6154,16 +6154,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C215" s="25">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>288.89999999999998</v>
+        <v>279.45</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6273,16 +6273,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C222" s="25">
-        <v>101.5</v>
+        <v>99.5</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>369.49</v>
+        <v>362.21</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6324,16 +6324,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C225" s="25">
-        <v>132.5</v>
+        <v>130.5</v>
       </c>
       <c r="D225" s="26">
         <v>2.66</v>
       </c>
       <c r="E225" s="27">
-        <v>352.45</v>
+        <v>347.13</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6426,16 +6426,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C231" s="25">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>148.75</v>
+        <v>140</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6715,16 +6715,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C250" s="25">
-        <v>189.5</v>
+        <v>181</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>739.05</v>
+        <v>705.9</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -7008,16 +7008,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C269" s="25">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>43.4</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7121,16 +7121,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C276" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D276" s="26">
         <v>4.28</v>
       </c>
       <c r="E276" s="27">
-        <v>55.64</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7239,16 +7239,16 @@
         <v>286</v>
       </c>
       <c r="B284" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C284" s="25">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D284" s="26">
         <v>6.19</v>
       </c>
       <c r="E284" s="27">
-        <v>445.35</v>
+        <v>414.42</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7409,16 +7409,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C294" s="25">
-        <v>100.5</v>
+        <v>98.5</v>
       </c>
       <c r="D294" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E294" s="27">
-        <v>491.24</v>
+        <v>481.47</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7460,16 +7460,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C297" s="25">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D297" s="26">
         <v>6.06</v>
       </c>
       <c r="E297" s="27">
-        <v>1734.47</v>
+        <v>1722.27</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7562,16 +7562,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C303" s="25">
-        <v>256.25</v>
+        <v>252.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1101.3399999999999</v>
+        <v>1084.1500000000001</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -8008,16 +8008,16 @@
         <v>333</v>
       </c>
       <c r="B331" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C331" s="25">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D331" s="26">
         <v>4.28</v>
       </c>
       <c r="E331" s="27">
-        <v>727.6</v>
+        <v>714.76</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -8042,16 +8042,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C333" s="25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D333" s="26">
         <v>7.97</v>
       </c>
       <c r="E333" s="27">
-        <v>123.56</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8396,16 +8396,16 @@
         <v>357</v>
       </c>
       <c r="B355" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C355" s="25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D355" s="26">
         <v>9.1999999999999993</v>
       </c>
       <c r="E355" s="27">
-        <v>193.2</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -8462,16 +8462,16 @@
         <v>361</v>
       </c>
       <c r="B359" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C359" s="25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D359" s="26">
         <v>6.64</v>
       </c>
       <c r="E359" s="27">
-        <v>119.54</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8558,16 +8558,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C365" s="25">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>106.92</v>
+        <v>83.16</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8643,16 +8643,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C370" s="25">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>673.2</v>
+        <v>660</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8728,16 +8728,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C375" s="25">
-        <v>58.33</v>
+        <v>56.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>262.49</v>
+        <v>255.74</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8915,16 +8915,16 @@
         <v>388</v>
       </c>
       <c r="B386" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C386" s="25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D386" s="26">
         <v>8.4700000000000006</v>
       </c>
       <c r="E386" s="27">
-        <v>220.3</v>
+        <v>211.83</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -9334,16 +9334,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C413" s="25">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>327.60000000000002</v>
+        <v>325</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9438,10 +9438,10 @@
         <v>28.5</v>
       </c>
       <c r="D419" s="26">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="E419" s="27">
-        <v>222.3</v>
+        <v>222.75</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9973,16 +9973,16 @@
         <v>456</v>
       </c>
       <c r="B454" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C454" s="25">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D454" s="26">
         <v>9.75</v>
       </c>
       <c r="E454" s="27">
-        <v>73.13</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10182,17 +10182,11 @@
         <v>469</v>
       </c>
       <c r="B467" s="24">
-        <v>13</v>
-      </c>
-      <c r="C467" s="25">
-        <v>7.5</v>
-      </c>
-      <c r="D467" s="26">
-        <v>15.5</v>
-      </c>
-      <c r="E467" s="27">
-        <v>116.25</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C467" s="28"/>
+      <c r="D467" s="29"/>
+      <c r="E467" s="28"/>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="23" t="s">
@@ -10297,17 +10291,11 @@
         <v>476</v>
       </c>
       <c r="B474" s="24">
-        <v>13</v>
-      </c>
-      <c r="C474" s="25">
-        <v>7</v>
-      </c>
-      <c r="D474" s="26">
-        <v>10</v>
-      </c>
-      <c r="E474" s="27">
-        <v>70</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C474" s="28"/>
+      <c r="D474" s="29"/>
+      <c r="E474" s="28"/>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="23" t="s">
@@ -10459,16 +10447,16 @@
         <v>486</v>
       </c>
       <c r="B484" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C484" s="25">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="D484" s="26">
         <v>11.88</v>
       </c>
       <c r="E484" s="27">
-        <v>100.98</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -11159,16 +11147,16 @@
         <v>530</v>
       </c>
       <c r="B528" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C528" s="25">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D528" s="26">
         <v>1.4</v>
       </c>
       <c r="E528" s="27">
-        <v>142.80000000000001</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11261,16 +11249,16 @@
         <v>536</v>
       </c>
       <c r="B534" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C534" s="25">
-        <v>48</v>
+        <v>44.5</v>
       </c>
       <c r="D534" s="26">
         <v>3.8</v>
       </c>
       <c r="E534" s="27">
-        <v>182.4</v>
+        <v>169.1</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11427,16 +11415,16 @@
         <v>546</v>
       </c>
       <c r="B544" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C544" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D544" s="26">
         <v>4.28</v>
       </c>
       <c r="E544" s="27">
-        <v>81.319999999999993</v>
+        <v>72.760000000000005</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11478,16 +11466,16 @@
         <v>549</v>
       </c>
       <c r="B547" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C547" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D547" s="26">
         <v>6.5</v>
       </c>
       <c r="E547" s="27">
-        <v>32.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -11512,16 +11500,16 @@
         <v>551</v>
       </c>
       <c r="B549" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C549" s="25">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="D549" s="26">
         <v>2.65</v>
       </c>
       <c r="E549" s="27">
-        <v>162.97999999999999</v>
+        <v>159</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11699,16 +11687,16 @@
         <v>562</v>
       </c>
       <c r="B560" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C560" s="25">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D560" s="26">
         <v>2.66</v>
       </c>
       <c r="E560" s="27">
-        <v>59.85</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11767,16 +11755,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C564" s="25">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="D564" s="26">
         <v>3.14</v>
       </c>
       <c r="E564" s="27">
-        <v>95.14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11784,16 +11772,16 @@
         <v>567</v>
       </c>
       <c r="B565" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C565" s="25">
-        <v>78.75</v>
+        <v>72.25</v>
       </c>
       <c r="D565" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E565" s="27">
-        <v>181.13</v>
+        <v>166.18</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11965,16 +11953,16 @@
         <v>578</v>
       </c>
       <c r="B576" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C576" s="25">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="D576" s="26">
         <v>2.71</v>
       </c>
       <c r="E576" s="27">
-        <v>36.61</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12016,16 +12004,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C579" s="25">
-        <v>95.5</v>
+        <v>86.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>133.69999999999999</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12256,16 +12244,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C595" s="25">
-        <v>734</v>
+        <v>705</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>425.72</v>
+        <v>408.9</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12372,10 +12360,10 @@
         <v>605</v>
       </c>
       <c r="B603" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C603" s="25">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D603" s="29"/>
       <c r="E603" s="28"/>
@@ -12480,16 +12468,16 @@
         <v>613</v>
       </c>
       <c r="B611" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C611" s="25">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D611" s="26">
         <v>0.73</v>
       </c>
       <c r="E611" s="27">
-        <v>49.64</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -12631,16 +12619,16 @@
         <v>622</v>
       </c>
       <c r="B620" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C620" s="25">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D620" s="26">
         <v>5</v>
       </c>
       <c r="E620" s="27">
-        <v>62.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -12770,13 +12758,13 @@
         <v>92</v>
       </c>
       <c r="C628" s="25">
-        <v>73.5</v>
+        <v>70</v>
       </c>
       <c r="D628" s="26">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="E628" s="27">
-        <v>202.81</v>
+        <v>193.91</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12821,13 +12809,13 @@
         <v>59</v>
       </c>
       <c r="C631" s="25">
-        <v>62</v>
+        <v>65.5</v>
       </c>
       <c r="D631" s="26">
         <v>2.76</v>
       </c>
       <c r="E631" s="27">
-        <v>171.05</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12835,16 +12823,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C632" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12852,16 +12840,16 @@
         <v>635</v>
       </c>
       <c r="B633" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C633" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D633" s="26">
         <v>4</v>
       </c>
       <c r="E633" s="27">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -13022,16 +13010,16 @@
         <v>645</v>
       </c>
       <c r="B643" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C643" s="25">
-        <v>40.5</v>
+        <v>35.5</v>
       </c>
       <c r="D643" s="26">
         <v>5</v>
       </c>
       <c r="E643" s="27">
-        <v>202.5</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -13367,16 +13355,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C664" s="25">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>64.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13486,16 +13474,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C671" s="25">
-        <v>151.5</v>
+        <v>148.5</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>469.65</v>
+        <v>460.35</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13523,13 +13511,13 @@
         <v>44</v>
       </c>
       <c r="C673" s="25">
-        <v>-7</v>
+        <v>15</v>
       </c>
       <c r="D673" s="26">
         <v>3.5</v>
       </c>
       <c r="E673" s="27">
-        <v>-24.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13554,16 +13542,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C675" s="25">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="D675" s="26">
         <v>3.75</v>
       </c>
       <c r="E675" s="27">
-        <v>125.63</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13786,16 +13774,16 @@
         <v>691</v>
       </c>
       <c r="B689" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C689" s="25">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="D689" s="26">
         <v>4.25</v>
       </c>
       <c r="E689" s="27">
-        <v>87.13</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -13917,10 +13905,10 @@
         <v>700</v>
       </c>
       <c r="B698" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C698" s="25">
-        <v>96.5</v>
+        <v>94.5</v>
       </c>
       <c r="D698" s="29"/>
       <c r="E698" s="28"/>
@@ -13943,10 +13931,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C700" s="25">
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14447,11 +14435,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44543.69</v>
+        <v>44223.54</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>107021.71</v>
+        <v>106031.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -65,316 +65,316 @@
     <t>Value</t>
   </si>
   <si>
-    <t>.1001 PATRIKA (25/251)</t>
-  </si>
-  <si>
-    <t>1002 PATRIKA (25/262)</t>
-  </si>
-  <si>
-    <t>1003 PATRIKA (25/261)</t>
-  </si>
-  <si>
-    <t>1004 PATRIKA (25/361/861)</t>
-  </si>
-  <si>
-    <t>1005 PATRIKA (25/362/862)</t>
-  </si>
-  <si>
-    <t>1006 PATRIKA (25/282)</t>
-  </si>
-  <si>
-    <t>1007 PATRIKA (25/281)</t>
-  </si>
-  <si>
-    <t>1008 PATRIKA (JC) (2595 PINK)</t>
-  </si>
-  <si>
-    <t>1009 PATRIKA (JC) (2595 ORANGE)</t>
+    <t>.1001 PATRIKA</t>
+  </si>
+  <si>
+    <t>1002 PATRIKA</t>
+  </si>
+  <si>
+    <t>1003 PATRIKA</t>
+  </si>
+  <si>
+    <t>1004 PATRIKA</t>
+  </si>
+  <si>
+    <t>1005 PATRIKA</t>
+  </si>
+  <si>
+    <t>1006 PATRIKA</t>
+  </si>
+  <si>
+    <t>1007 PATRIKA</t>
+  </si>
+  <si>
+    <t>1008 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1009 PATRIKA (JC)</t>
   </si>
   <si>
     <t>100 ENVELOPE (SR) OFFSET</t>
   </si>
   <si>
-    <t>1010 PATRIKA (6321)</t>
-  </si>
-  <si>
-    <t>1011 PATRIKA (2563 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1012 PATRIKA (2564 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1013 PATRIKA (2568 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1014 PATRIKA (11043 OFFSET)</t>
-  </si>
-  <si>
-    <t>1015 PATRIKA (DCU) (11041 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1016 PATRIKA (1011 OFFSET)</t>
-  </si>
-  <si>
-    <t>1017 PATRIKA (1014 OFFSET)</t>
-  </si>
-  <si>
-    <t>1018 PATRIKA (10081 OFFSET NEW)</t>
-  </si>
-  <si>
-    <t>1019 PATRIKA (1222 SBC)</t>
-  </si>
-  <si>
-    <t>1020 PATRIKA (1235)</t>
-  </si>
-  <si>
-    <t>1021 PATRIKA (2101 VV)</t>
-  </si>
-  <si>
-    <t>1022 PATRIKA (JC) (25409)</t>
-  </si>
-  <si>
-    <t>1023 PATRIKA (25418)</t>
-  </si>
-  <si>
-    <t>1024 PATRIKA (25322)</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA (25323)</t>
-  </si>
-  <si>
-    <t>1026 PATRIKA (JC) (1173 SBC)</t>
-  </si>
-  <si>
-    <t>1027 PATRIKA (JC) (5346)</t>
-  </si>
-  <si>
-    <t>1028 PATRIKA (JC) (2596)</t>
-  </si>
-  <si>
-    <t>1029 PATRIKA (1042)</t>
-  </si>
-  <si>
-    <t>1030 PATRIKA (1043)</t>
-  </si>
-  <si>
-    <t>1031 PATRIKA (GOPAL 11)</t>
-  </si>
-  <si>
-    <t>1032 PATRIKA (GOPAL 1)</t>
-  </si>
-  <si>
-    <t>1033 PATRIKA (2002 YLW)</t>
-  </si>
-  <si>
-    <t>1034 PATRIKA (2003 R)</t>
-  </si>
-  <si>
-    <t>1035 PATRIKA (DCU) (2201 ROSHAN)</t>
-  </si>
-  <si>
-    <t>1101 PATRIKA (O.2591) (2591 ORANGE)</t>
-  </si>
-  <si>
-    <t>1102 PATRIKA (P.2591) (2591 PINK)</t>
-  </si>
-  <si>
-    <t>1103 PATRIKA(N-271) (271 NEHA)</t>
-  </si>
-  <si>
-    <t>1104 PATRIKA(N-272) (272 NEHA)</t>
-  </si>
-  <si>
-    <t>1105 PATRIKA (276-A)</t>
-  </si>
-  <si>
-    <t>1106 PATRIKA-YELLOW (25419)</t>
-  </si>
-  <si>
-    <t>1107 PATRIKA-RED (25420)</t>
-  </si>
-  <si>
-    <t>1109 PATRIKA-BIG Y (25421)</t>
-  </si>
-  <si>
-    <t>1110 PATRIKA-BIG R (25422)</t>
-  </si>
-  <si>
-    <t>1112 PATRIKA (277-B)</t>
-  </si>
-  <si>
-    <t>1113 PATRIKA (1819 MONARCH)</t>
-  </si>
-  <si>
-    <t>1114 PATRIKA-BROWN (1709)</t>
-  </si>
-  <si>
-    <t>1115 PATRIKA-CREAM (1678 PRINCE)</t>
-  </si>
-  <si>
-    <t>1116 PATRIKA (1153) (1253 Jsk)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA (1155) (1155 JSK)</t>
-  </si>
-  <si>
-    <t>1117 PATRIKA - B (KRISHNA 1155-B)</t>
-  </si>
-  <si>
-    <t>1118 PATRIKA (सवाश्री-57) 51 (NEW SAVASHREE-57)</t>
-  </si>
-  <si>
-    <t>1119 PATRIKA(सवाश्री-55) (NEW SAVASHREE-55)</t>
-  </si>
-  <si>
-    <t>1120 PATRIKA(सवाश्री-59) (NEW SAVASHREE-59)</t>
-  </si>
-  <si>
-    <t>1121 - B PATRIKA (SS.51) (NEW SAVASHREE- 51)</t>
-  </si>
-  <si>
-    <t>1121 PATRIKA(सवाश्री-53) (NEW SAVASHREE-53)</t>
-  </si>
-  <si>
-    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70 (NEW SAVASHREE 52)</t>
-  </si>
-  <si>
-    <t>1122 PATRIKA (DCU) (S.S. 54) (NEW SAVASHREE-54)</t>
-  </si>
-  <si>
-    <t>1123 PATRIKA (LED-51) (LED-51)</t>
-  </si>
-  <si>
-    <t>1124 PATRIKA (LED-52) (LED-52)</t>
-  </si>
-  <si>
-    <t>1125 PATRIKA (LED-53) (LED-53)</t>
-  </si>
-  <si>
-    <t>1126 PATRIKA (LED-54) (LED-54)</t>
-  </si>
-  <si>
-    <t>1127 PATRIKA (Eco-52) (NEW ECO-52)</t>
-  </si>
-  <si>
-    <t>1128 PATRIKA (Eco-55) (NEW ECO-55)</t>
-  </si>
-  <si>
-    <t>1129 PATRIKA (Eco-56) (NEW ECO-56)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA - B (ECO-60) (DCU) (NEW ECO 60)</t>
-  </si>
-  <si>
-    <t>1130 PATRIKA (Eco-59) (NEW ECO-59)</t>
-  </si>
-  <si>
-    <t>1131 PATRIKA (DCU) Eco-51 (NEW ECO- 51)</t>
-  </si>
-  <si>
-    <t>1132 PATRIKA (DCU) Eco-53 (NEW ECO- 53)</t>
-  </si>
-  <si>
-    <t>1133 PATRIKA (DCU) Eco-57 (NEW ECO- 57)</t>
-  </si>
-  <si>
-    <t>1134 PATRIKA (DCU) Eco-58 (NEW ECO- 58)</t>
-  </si>
-  <si>
-    <t>1135 PATRIKA (DCU) Eco-54 (NEW ECO- 54)</t>
-  </si>
-  <si>
-    <t>1136 PATRIKA (R) (120 GSM RED)</t>
-  </si>
-  <si>
-    <t>1137 PATRIKA (P) (120 GSM YELLOW)</t>
-  </si>
-  <si>
-    <t>1138 PATRIKA (BR) (150 GSM FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1139 PATRIKA (BY) (150 GSM FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1140 PATRIKA (BB) (150 GSM FOIL (BROWN))</t>
-  </si>
-  <si>
-    <t>1141 PATRIKA (R) (120 GSM (RED)SELF)</t>
-  </si>
-  <si>
-    <t>1142 PATRIKA (P) (120 GSM (YELLOW) SELF)</t>
-  </si>
-  <si>
-    <t>1143 PATRIKA (G) (120 GSM (OLD GOLDEN))</t>
-  </si>
-  <si>
-    <t>1144 PATRIKA (BR) (170 GSM WITH FOIL (RED))</t>
-  </si>
-  <si>
-    <t>1145 PATRIKA (BY) (170 GSM WITH FOIL (YELLOW))</t>
-  </si>
-  <si>
-    <t>1146 PATRIKA (DCU) (BROWN 170 GSM FOIL)</t>
-  </si>
-  <si>
-    <t>1147 PATRIKA (S.201) (201 WESTERN)</t>
-  </si>
-  <si>
-    <t>1148 PATRIKA (S.202) (202 WESTERN)</t>
-  </si>
-  <si>
-    <t>1149 PATRIKA (S.204) (204 WESTERN)</t>
-  </si>
-  <si>
-    <t>1150 PATRIKA (DCU) (NEW SAVASHREE-58)</t>
-  </si>
-  <si>
-    <t>1151 PATRIKA (DCU) (SS56) (NEW SAVASHREE-56)</t>
-  </si>
-  <si>
-    <t>1152 PATRIKA (DCU) (WESTERN 202 OLD)</t>
-  </si>
-  <si>
-    <t>1153 PATRIKA (DCU) (201 WESTERN (OLD))</t>
-  </si>
-  <si>
-    <t>1154 PATRIKA (DCU) (203 WESTERN A)</t>
-  </si>
-  <si>
-    <t>1155 PATRIKA (DCU) (WESTERN (203) B)</t>
-  </si>
-  <si>
-    <t>1156 PATRIKA-YELLOW (LU-51 (YELLOW))</t>
-  </si>
-  <si>
-    <t>1157 PATRIKA-CREAM (LU-52 (CREAM))</t>
-  </si>
-  <si>
-    <t>1158 PATRIKA-GOLDEN (LU-53 (GOLDEN))</t>
-  </si>
-  <si>
-    <t>1159 PATRIKA-WHITE (LU-54 (WHITE))</t>
-  </si>
-  <si>
-    <t>1160 PATRIKA-PINK (LU-55 (PINK))</t>
-  </si>
-  <si>
-    <t>1161 PATRIKA (01) (JCC 01)</t>
-  </si>
-  <si>
-    <t>1162 PATRIKA (02) (JCC 02)</t>
-  </si>
-  <si>
-    <t>1163 PATRIKA (DCU) (BP RED)</t>
-  </si>
-  <si>
-    <t>1164 PATRIKA (DCU) (BP PINK RIYAZ)</t>
-  </si>
-  <si>
-    <t>1165 PATRIKA (DCU) (BP CREAM)</t>
-  </si>
-  <si>
-    <t>1166 PATRIKA (DCU) (BP YELLOW)</t>
+    <t>1010 PATRIKA</t>
+  </si>
+  <si>
+    <t>1011 PATRIKA</t>
+  </si>
+  <si>
+    <t>1012 PATRIKA</t>
+  </si>
+  <si>
+    <t>1013 PATRIKA</t>
+  </si>
+  <si>
+    <t>1014 PATRIKA</t>
+  </si>
+  <si>
+    <t>1015 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1016 PATRIKA</t>
+  </si>
+  <si>
+    <t>1017 PATRIKA</t>
+  </si>
+  <si>
+    <t>1018 PATRIKA</t>
+  </si>
+  <si>
+    <t>1019 PATRIKA</t>
+  </si>
+  <si>
+    <t>1020 PATRIKA</t>
+  </si>
+  <si>
+    <t>1021 PATRIKA</t>
+  </si>
+  <si>
+    <t>1022 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1023 PATRIKA</t>
+  </si>
+  <si>
+    <t>1024 PATRIKA</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA</t>
+  </si>
+  <si>
+    <t>1026 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1027 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1028 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>1029 PATRIKA</t>
+  </si>
+  <si>
+    <t>1030 PATRIKA</t>
+  </si>
+  <si>
+    <t>1031 PATRIKA</t>
+  </si>
+  <si>
+    <t>1032 PATRIKA</t>
+  </si>
+  <si>
+    <t>1033 PATRIKA</t>
+  </si>
+  <si>
+    <t>1034 PATRIKA</t>
+  </si>
+  <si>
+    <t>1035 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1101 PATRIKA (O.2591)</t>
+  </si>
+  <si>
+    <t>1102 PATRIKA (P.2591) 6 MARCH</t>
+  </si>
+  <si>
+    <t>1103 PATRIKA(N-271)</t>
+  </si>
+  <si>
+    <t>1104 PATRIKA(N-272)</t>
+  </si>
+  <si>
+    <t>1105 PATRIKA</t>
+  </si>
+  <si>
+    <t>1106 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1107 PATRIKA-RED 6/03</t>
+  </si>
+  <si>
+    <t>1109 PATRIKA-BIG Y</t>
+  </si>
+  <si>
+    <t>1110 PATRIKA-BIG R</t>
+  </si>
+  <si>
+    <t>1112 PATRIKA</t>
+  </si>
+  <si>
+    <t>1113 PATRIKA 5/03</t>
+  </si>
+  <si>
+    <t>1114 PATRIKA-BROWN</t>
+  </si>
+  <si>
+    <t>1115 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1116 PATRIKA (1153)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA (1155)</t>
+  </si>
+  <si>
+    <t>1117 PATRIKA - B</t>
+  </si>
+  <si>
+    <t>1118 PATRIKA (सवाश्री-57) 51</t>
+  </si>
+  <si>
+    <t>1119 PATRIKA(सवाश्री-55)</t>
+  </si>
+  <si>
+    <t>1120 PATRIKA(सवाश्री-59)</t>
+  </si>
+  <si>
+    <t>1121 - B PATRIKA (SS.51)</t>
+  </si>
+  <si>
+    <t>1121 PATRIKA(सवाश्री-53)</t>
+  </si>
+  <si>
+    <t>1122 - B PATRIKA (SS-52) 1908 RATE 2.70</t>
+  </si>
+  <si>
+    <t>1122 PATRIKA (DCU) (S.S. 54)</t>
+  </si>
+  <si>
+    <t>1123 PATRIKA (LED-51)</t>
+  </si>
+  <si>
+    <t>1124 PATRIKA (LED-52)</t>
+  </si>
+  <si>
+    <t>1125 PATRIKA (LED-53)</t>
+  </si>
+  <si>
+    <t>1126 PATRIKA (LED-54)</t>
+  </si>
+  <si>
+    <t>1127 PATRIKA (Eco-52)</t>
+  </si>
+  <si>
+    <t>1128 PATRIKA (Eco-55)</t>
+  </si>
+  <si>
+    <t>1129 PATRIKA (Eco-56)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA - B (ECO-60) (DCU)</t>
+  </si>
+  <si>
+    <t>1130 PATRIKA (Eco-59)</t>
+  </si>
+  <si>
+    <t>1131 PATRIKA (DCU) Eco-51</t>
+  </si>
+  <si>
+    <t>1132 PATRIKA (DCU) Eco-53</t>
+  </si>
+  <si>
+    <t>1133 PATRIKA (DCU) Eco-57</t>
+  </si>
+  <si>
+    <t>1134 PATRIKA (DCU) Eco-58</t>
+  </si>
+  <si>
+    <t>1135 PATRIKA (DCU) Eco-54</t>
+  </si>
+  <si>
+    <t>1136 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1137 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1138 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1139 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1140 PATRIKA (BB)</t>
+  </si>
+  <si>
+    <t>1141 PATRIKA (R)</t>
+  </si>
+  <si>
+    <t>1142 PATRIKA (P)</t>
+  </si>
+  <si>
+    <t>1143 PATRIKA (G)</t>
+  </si>
+  <si>
+    <t>1144 PATRIKA (BR)</t>
+  </si>
+  <si>
+    <t>1145 PATRIKA (BY)</t>
+  </si>
+  <si>
+    <t>1146 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1147 PATRIKA (S.201)</t>
+  </si>
+  <si>
+    <t>1148 PATRIKA (S.202)</t>
+  </si>
+  <si>
+    <t>1149 PATRIKA (S.204)</t>
+  </si>
+  <si>
+    <t>1150 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1151 PATRIKA (DCU) (SS56)</t>
+  </si>
+  <si>
+    <t>1152 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1153 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1154 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1155 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1156 PATRIKA-YELLOW</t>
+  </si>
+  <si>
+    <t>1157 PATRIKA-CREAM</t>
+  </si>
+  <si>
+    <t>1158 PATRIKA-GOLDEN</t>
+  </si>
+  <si>
+    <t>1159 PATRIKA-WHITE</t>
+  </si>
+  <si>
+    <t>1160 PATRIKA-PINK</t>
+  </si>
+  <si>
+    <t>1161 PATRIKA (01)</t>
+  </si>
+  <si>
+    <t>1162 PATRIKA (02)</t>
+  </si>
+  <si>
+    <t>1163 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1164 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1165 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>1166 PATRIKA (DCU)</t>
   </si>
   <si>
     <t>1167 PATRIKA (DCU) BROWN</t>
@@ -425,109 +425,109 @@
     <t>2025- INVITAION (BOX) SAMPLES</t>
   </si>
   <si>
-    <t>2101 PATRIKA (L)-DC (LUXYA - 51)</t>
-  </si>
-  <si>
-    <t>2102 PATRIKA *-* (M) (LUXYA - 52)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L) (LUXYA - 53)</t>
-  </si>
-  <si>
-    <t>2104 PATRIKA (DCU) (LUXYA - 54)</t>
-  </si>
-  <si>
-    <t>2105 PATRIKA (DC) (LUXYA - 55)</t>
-  </si>
-  <si>
-    <t>2106 PATRIKA (L) (LUXYA - 56)</t>
-  </si>
-  <si>
-    <t>2107 PATRIKA *-* (M) (LUXYA - 57)</t>
-  </si>
-  <si>
-    <t>2108 PATRIKA *-* (M) (DCU) (LUXYA - 59)</t>
-  </si>
-  <si>
-    <t>2109 PATRIKA (L) (LUXYA - 60)</t>
-  </si>
-  <si>
-    <t>2110 PATRIKA (DC) (LUXYA - 61)</t>
-  </si>
-  <si>
-    <t>2111 PATRIKA *-* (M) (DCU) (LUXYA - 62)</t>
-  </si>
-  <si>
-    <t>2112 PATRIKA (L) (LEGACY - 01)</t>
-  </si>
-  <si>
-    <t>2113 PATRIKA (L) (LEGACY - 02)</t>
-  </si>
-  <si>
-    <t>2114 PATRIKA (L) (LEGACY - 03)</t>
-  </si>
-  <si>
-    <t>2115 PATRIKA (L) (LEGACY - 04)</t>
-  </si>
-  <si>
-    <t>2116 PATRIKA (L) (LEGACY - 05)</t>
-  </si>
-  <si>
-    <t>2117 PATRIKA *-* (M) (DC) (LEGACY - 06)</t>
-  </si>
-  <si>
-    <t>2118 PATRIKA (L) (DC) (LEGACY - 07)</t>
-  </si>
-  <si>
-    <t>2119 PATRIKA (L) (LEGACY - 08)</t>
-  </si>
-  <si>
-    <t>2120 PATRIKA (L) (LEGACY - 09)</t>
-  </si>
-  <si>
-    <t>2121 PATRIKA (LEGACY - 10)</t>
-  </si>
-  <si>
-    <t>2122 PATRIKA (LEGACY - 11)</t>
-  </si>
-  <si>
-    <t>2123 PATRIKA (LEGACY - 12)</t>
-  </si>
-  <si>
-    <t>2124 PATRIKA *-* (M) (LOTTERY - 71)</t>
-  </si>
-  <si>
-    <t>2125 PATRIKA *-* (M) (LOTTERY - 72)</t>
-  </si>
-  <si>
-    <t>2126 PATRIKA *-* (M) (LOTTERY - 73)</t>
-  </si>
-  <si>
-    <t>2127 PATRIKA *-* (M) (DCU) (LOTTERY - 74)</t>
-  </si>
-  <si>
-    <t>2128 PATRIKA *-* (M) (LOTTERY - 75)</t>
-  </si>
-  <si>
-    <t>2129 PATRIKA *-* (M) (DCU) (LOTTERY - 76)</t>
-  </si>
-  <si>
-    <t>2130 PATRIKA *-* (M) (LOTTERY - 77)</t>
-  </si>
-  <si>
-    <t>2131 PATRIKA *-* (M) (DCU) (LOTTERY - 78)</t>
-  </si>
-  <si>
-    <t>2132 PATRIKA *-* (M) (LOTTERY - 79)</t>
-  </si>
-  <si>
-    <t>2133 PATRIKA (LOTTERY - 80)</t>
-  </si>
-  <si>
-    <t>2134 PATRIKA *-* (M) (LOTTERY - 81)</t>
-  </si>
-  <si>
-    <t>2135 PATRIKA *-* (M) (LOTTERY - 82)</t>
+    <t>2101 PATRIKA (L)-DC</t>
+  </si>
+  <si>
+    <t>2102 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2104 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>2105 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2106 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2107 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2108 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2109 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2110 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>2111 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2112 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2113 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2114 PATRIKA (L) (DCU)</t>
+  </si>
+  <si>
+    <t>2115 PATRIKA (L) (DCU)</t>
+  </si>
+  <si>
+    <t>2116 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>2117 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>2118 PATRIKA (L) (DC)</t>
+  </si>
+  <si>
+    <t>2119 PATRIKA (L) (DCU)</t>
+  </si>
+  <si>
+    <t>2120 PATRIKA (L) (DCU)</t>
+  </si>
+  <si>
+    <t>2121 PATRIKA</t>
+  </si>
+  <si>
+    <t>2122 PATRIKA</t>
+  </si>
+  <si>
+    <t>2123 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>2124 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2125 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2126 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2127 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2128 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2129 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2130 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2131 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2132 PATRIKA *-* (M) (DCU)</t>
+  </si>
+  <si>
+    <t>2133 PATRIKA</t>
+  </si>
+  <si>
+    <t>2134 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>2135 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>240 ENVELOPE</t>
@@ -557,1234 +557,1234 @@
     <t>330 ENVELOPE (B)</t>
   </si>
   <si>
-    <t>4251 PATRIKA (JC) (5342)</t>
-  </si>
-  <si>
-    <t>4252 PATRIKA (5207)</t>
-  </si>
-  <si>
-    <t>4253 PATRIKA (5206)</t>
-  </si>
-  <si>
-    <t>4254 PATRIKA (4210) (10273/10277)</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA - B (DCU) (AS-02 (B))</t>
-  </si>
-  <si>
-    <t>4255 PATRIKA (JC) (AS-02 (NEW))</t>
-  </si>
-  <si>
-    <t>4256 PATRIKA (JC) *-* (M) (1352 VV)</t>
-  </si>
-  <si>
-    <t>4257 PATRIKA (82)</t>
-  </si>
-  <si>
-    <t>4258 PATRIKA (JC) (1129)</t>
-  </si>
-  <si>
-    <t>4259 PATRIKA (JC) (101 SBC)</t>
-  </si>
-  <si>
-    <t>4260 PATRIKA (1102)</t>
-  </si>
-  <si>
-    <t>4261 PATRIKA (JC) (959)</t>
-  </si>
-  <si>
-    <t>4262 PATRIKA (JC) (S-201 GANESH JI)</t>
-  </si>
-  <si>
-    <t>4263 PATRIKA (JC) (2571)</t>
-  </si>
-  <si>
-    <t>4264 PATRIKA (DCU) (1351)</t>
-  </si>
-  <si>
-    <t>4265 PATRIKA (83)</t>
-  </si>
-  <si>
-    <t>4266 PATRIKA (25-145)</t>
-  </si>
-  <si>
-    <t>4267 PATRIKA (JC) (25-046)</t>
-  </si>
-  <si>
-    <t>4268 PATRIKA (JC) *-* (M+T) (S-296)</t>
-  </si>
-  <si>
-    <t>4269 PATRIKA (111 SBC)</t>
-  </si>
-  <si>
-    <t>4270 PATRIKA (1151 GGN)</t>
-  </si>
-  <si>
-    <t>4271 PATRIKA (JC) (25216)</t>
-  </si>
-  <si>
-    <t>4272 PATRIKA (JC) (1231 SBC CRM)</t>
-  </si>
-  <si>
-    <t>4273 PATRIKA (2547)</t>
-  </si>
-  <si>
-    <t>4274 PATRIKA (JC) (25369)</t>
-  </si>
-  <si>
-    <t>4275 PATRIKA (25367)</t>
-  </si>
-  <si>
-    <t>4276 PATRIKA (JC) *-* (M) (2632)</t>
-  </si>
-  <si>
-    <t>4277 PATRIKA (JC) *-* (M) (25365)</t>
-  </si>
-  <si>
-    <t>4278 PATRIKA (25368)</t>
-  </si>
-  <si>
-    <t>4279 PATRIKA (1031)</t>
-  </si>
-  <si>
-    <t>4280 PATRIKA (25301)</t>
-  </si>
-  <si>
-    <t>4281 PATRIKA (25312 MYRA)</t>
-  </si>
-  <si>
-    <t>4282 PATRIKA (3117)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA - B (YELLOW) (3116-YLW)</t>
-  </si>
-  <si>
-    <t>4283 PATRIKA (GOLDEN) (3116)</t>
-  </si>
-  <si>
-    <t>4284 PATRIKA (1173 VV)</t>
-  </si>
-  <si>
-    <t>4285 PATRIKA (JC) *-* (M) (4626)</t>
-  </si>
-  <si>
-    <t>4286 PATRIKA (5254  RJN)</t>
-  </si>
-  <si>
-    <t>4287 PATRIKA (25402)</t>
-  </si>
-  <si>
-    <t>4288 PATRIKA (10001 NEW)</t>
-  </si>
-  <si>
-    <t>4289 PATRIKA (10002 NEW)</t>
-  </si>
-  <si>
-    <t>4290 PATRIKA (316 MYRA)</t>
-  </si>
-  <si>
-    <t>4291 PATRIKA (25401)</t>
-  </si>
-  <si>
-    <t>4292 PATRIKA (25311)</t>
-  </si>
-  <si>
-    <t>4293 PATRIKA (25312)</t>
-  </si>
-  <si>
-    <t>4294 PATRIKA (5273)</t>
-  </si>
-  <si>
-    <t>4295 PATRIKA (286-A)</t>
-  </si>
-  <si>
-    <t>4296 PATRIKA (1407)</t>
-  </si>
-  <si>
-    <t>4297 PATRIKA (306)</t>
-  </si>
-  <si>
-    <t>4298 PATRIKA (5501)</t>
-  </si>
-  <si>
-    <t>4299 PATRIKA (2011)</t>
-  </si>
-  <si>
-    <t>4300 PATRIKA (25314)</t>
-  </si>
-  <si>
-    <t>4301 PATRIKA (25315)</t>
-  </si>
-  <si>
-    <t>4302 PATRIKA (DCU) (1402)</t>
-  </si>
-  <si>
-    <t>4303 PATRIKA (JC) (1234*-M)</t>
-  </si>
-  <si>
-    <t>4304 PATRIKA (5172)</t>
-  </si>
-  <si>
-    <t>4305 PATRIKA (25313)</t>
-  </si>
-  <si>
-    <t>4306 PATRIKA (JC) (427 LOTUS)</t>
-  </si>
-  <si>
-    <t>4307 PATRIKA (BALAJI 5202)</t>
-  </si>
-  <si>
-    <t>4308 PATRIKA (LOTUS 430)</t>
-  </si>
-  <si>
-    <t>4309 PATRIKA (DCU) (3751 Patta)</t>
-  </si>
-  <si>
-    <t>4310 PATRIKA (DCU) (3752 Swastik)</t>
-  </si>
-  <si>
-    <t>4311 PATRIKA (DCU) (251 KBC)</t>
-  </si>
-  <si>
-    <t>4312 PATRIKA (DCU) (273-A)</t>
-  </si>
-  <si>
-    <t>4313 PATRIKA (DCU) (RED- YELLOW PAN PATTA)</t>
-  </si>
-  <si>
-    <t>4314 PATRIKA (DCU) (RED-YELLOW SWASTIK)</t>
-  </si>
-  <si>
-    <t>4315 PATRIKA (DCU) (WHITE-PINK PAN PATA)</t>
-  </si>
-  <si>
-    <t>4316 PATRIKA (DCU) (WHITE -ORANGE PAN PATTA)</t>
-  </si>
-  <si>
-    <t>5051 PATRIKA *-* (M) (5087)</t>
-  </si>
-  <si>
-    <t>5052 PATRIKA (5295)</t>
-  </si>
-  <si>
-    <t>5053 PATRIKA (5213)</t>
-  </si>
-  <si>
-    <t>5054 PATRIKA *-* (M) (25/162)</t>
-  </si>
-  <si>
-    <t>5055 PATRIKA (25/272)</t>
-  </si>
-  <si>
-    <t>5056 PATRIKA (JC) (25/271)</t>
-  </si>
-  <si>
-    <t>5057 PATRIKA (25/171)</t>
-  </si>
-  <si>
-    <t>5058 PATRIKA (8802)</t>
-  </si>
-  <si>
-    <t>5059 PATRIKA (8803)</t>
-  </si>
-  <si>
-    <t>5060 PATRIKA (JC) (7713)</t>
-  </si>
-  <si>
-    <t>5061 PATRIKA (DCU) (1405)</t>
-  </si>
-  <si>
-    <t>5062 PATRIKA (7705)</t>
-  </si>
-  <si>
-    <t>5063 PATRIKA (2522 GE)</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA (2517 GE)</t>
-  </si>
-  <si>
-    <t>5065 PATRIKA (2527)</t>
-  </si>
-  <si>
-    <t>5066 PATRIKA (2536)</t>
-  </si>
-  <si>
-    <t>5067 PATRIKA (JC) (S-301)</t>
-  </si>
-  <si>
-    <t>5068 PATRIKA (DCU) (S-305)</t>
-  </si>
-  <si>
-    <t>5069 PATRIKA (JC) (1103)</t>
-  </si>
-  <si>
-    <t>5070 PATRIKA (JC) (2156  YELLOW)</t>
-  </si>
-  <si>
-    <t>5071 PATRIKA *-* (डोरी) (741)</t>
-  </si>
-  <si>
-    <t>5072 PATRIKA (5347 DIRECT)</t>
-  </si>
-  <si>
-    <t>5073 PATRIKA *-* (M) (3161)</t>
-  </si>
-  <si>
-    <t>5074 PATRIKA (1151 VV)</t>
-  </si>
-  <si>
-    <t>5075 PATRIKA (JC) (25-082)</t>
-  </si>
-  <si>
-    <t>5076 PATRIKA (JC) (3701 SBC)</t>
-  </si>
-  <si>
-    <t>5077 PATRIKA (2081)</t>
-  </si>
-  <si>
-    <t>5078 PATRIKA (DCU) (2156 CREAM)</t>
-  </si>
-  <si>
-    <t>5079 PATRIKA (296-A (NEHA)</t>
-  </si>
-  <si>
-    <t>5080 PATRIKA (2501 GE NEW)</t>
-  </si>
-  <si>
-    <t>5081 PATRIKA (2520 GE)</t>
-  </si>
-  <si>
-    <t>5083 PATRIKA (DCU) (5267)</t>
-  </si>
-  <si>
-    <t>5084 PATRIKA (5258 RJ)</t>
-  </si>
-  <si>
-    <t>5085 PATRIKA (2023)</t>
-  </si>
-  <si>
-    <t>5086 PATRIKA (JC) *-* (M+D) (942)</t>
-  </si>
-  <si>
-    <t>5087 PATRIKA (JC) (2206)</t>
-  </si>
-  <si>
-    <t>5088 PATRIKA (25214)</t>
-  </si>
-  <si>
-    <t>5089 PATRIKA (2061 SBC)</t>
-  </si>
-  <si>
-    <t>5090 PATRIKA (5236 RJ)</t>
-  </si>
-  <si>
-    <t>5091 PATRIKA (JC) (1411 KBC)</t>
-  </si>
-  <si>
-    <t>5092 PATRIKA (05 NAVIN BHAI)</t>
-  </si>
-  <si>
-    <t>5093 PATRIKA (5350)</t>
-  </si>
-  <si>
-    <t>5094 PATRIKA (5251)</t>
-  </si>
-  <si>
-    <t>5095 PATRIKA (5240)</t>
-  </si>
-  <si>
-    <t>5096 PATRIKA (25316)</t>
-  </si>
-  <si>
-    <t>5097 PATRIKA (25321)</t>
-  </si>
-  <si>
-    <t>5098 PATRIKA *-* (M) (857)</t>
-  </si>
-  <si>
-    <t>5099 PATRIKA *-* (M) (852 DHANESH)</t>
-  </si>
-  <si>
-    <t>5100 PATRIKA (DCU) (5339)</t>
-  </si>
-  <si>
-    <t>5102 PATRIKA (5021) (2456)</t>
-  </si>
-  <si>
-    <t>5103 PATRIKA (2071)</t>
-  </si>
-  <si>
-    <t>5104 PATRIKA (5261 RJND)</t>
-  </si>
-  <si>
-    <t>5105 PATRIKA (JC) (5335)</t>
-  </si>
-  <si>
-    <t>5106 PATRIKA (253-A / 257-A)</t>
-  </si>
-  <si>
-    <t>5107 PATRIKA (5356 RJ)</t>
-  </si>
-  <si>
-    <t>5108 PATRIKA (DCU) (5333)</t>
-  </si>
-  <si>
-    <t>5109 PATRIKA (5308)</t>
-  </si>
-  <si>
-    <t>5110 PATRIKA (JC) (AS-402)</t>
-  </si>
-  <si>
-    <t>5111 PATRIKA (JC) (5313)</t>
-  </si>
-  <si>
-    <t>5112 PATRIKA (JC) *-* (M) (25437)</t>
-  </si>
-  <si>
-    <t>5113 PATRIKA (5305)</t>
-  </si>
-  <si>
-    <t>5114 PATRIKA *-* (डोरी) (2091)</t>
-  </si>
-  <si>
-    <t>5115 PATRIKA (DCU) (5363 RJND)</t>
-  </si>
-  <si>
-    <t>5116 PATRIKA (2031)</t>
-  </si>
-  <si>
-    <t>5117 PATRIKA (DCU) (3331)</t>
-  </si>
-  <si>
-    <t>5118 PATRIKA (DCU) (25436)</t>
-  </si>
-  <si>
-    <t>5501 PATRIKA (DCU) (985 PISTA)</t>
-  </si>
-  <si>
-    <t>5502 PATRIKA *-* (M) (5355 NICE)</t>
-  </si>
-  <si>
-    <t>5503 PATRIKA (5186)</t>
-  </si>
-  <si>
-    <t>5504 PATRIKA (JC) (7033)</t>
-  </si>
-  <si>
-    <t>5505 PATRIKA (JC) *-* (M) (2282)</t>
-  </si>
-  <si>
-    <t>5506 PATRIKA *-* (M) (25/122)</t>
-  </si>
-  <si>
-    <t>5507 PATRIKA (JC) (8055 VV)</t>
-  </si>
-  <si>
-    <t>5508 PATRIKA (JC) (612 VV)</t>
-  </si>
-  <si>
-    <t>5509 PATRIKA (JC) (25/072)</t>
-  </si>
-  <si>
-    <t>5510 PATRIKA (JC) *-* (M) (AS-950)</t>
-  </si>
-  <si>
-    <t>5511 PATRIKA (JC) *-* (M) (2528)</t>
-  </si>
-  <si>
-    <t>5512 PATRIKA (JC) (2525 /2552)</t>
-  </si>
-  <si>
-    <t>5513 PATRIKA (2515)</t>
-  </si>
-  <si>
-    <t>5514 PATRIKA (DCU) (2542)</t>
-  </si>
-  <si>
-    <t>5515 PATRIKA (2523)</t>
-  </si>
-  <si>
-    <t>5516 PATRIKA (JC) *-* (M) (5302 VV)</t>
-  </si>
-  <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi) (6301)</t>
-  </si>
-  <si>
-    <t>5518 PATRIKA (JC) *-* (M) (922)</t>
-  </si>
-  <si>
-    <t>5519 PATRIKA *-* (M) (7066)</t>
-  </si>
-  <si>
-    <t>5520 PATRIKA (1054)</t>
-  </si>
-  <si>
-    <t>5521 PATRIKA (JC) *-* (M) (35)</t>
-  </si>
-  <si>
-    <t>5522 PATRIKA (2231)</t>
-  </si>
-  <si>
-    <t>5523 PATRIKA (2232)</t>
-  </si>
-  <si>
-    <t>5524 PATRIKA (DCU) (5382)</t>
-  </si>
-  <si>
-    <t>5525 PATRIKA *-* (M) (5283)</t>
-  </si>
-  <si>
-    <t>5526 PATRIKA (DCU) (NEW LUSTER - 01)</t>
-  </si>
-  <si>
-    <t>5527 PATRIKA (DCU) (NEW LUSTER - 02)</t>
-  </si>
-  <si>
-    <t>5528 PATRIKA *-* (M) (NEW LUSTER - 03)</t>
-  </si>
-  <si>
-    <t>5529 PATRIKA *-* (M) (NEW LUSTER - 04)</t>
-  </si>
-  <si>
-    <t>5530 PATRIKA *-* (M) (NEW LUSTER - 05)</t>
-  </si>
-  <si>
-    <t>5531 PATRIKA (DCU) (NEW LUSTER - 06)</t>
-  </si>
-  <si>
-    <t>5532 PATRIKA *-* (M) (NEW LUSTER - 07)</t>
-  </si>
-  <si>
-    <t>5533 PATRIKA *-* (M) (NEW LUSTER - 08)</t>
-  </si>
-  <si>
-    <t>5534 PATRIKA *-* (M) (NEW LUSTER - 09)</t>
-  </si>
-  <si>
-    <t>5535 PATRIKA (JC) *-* (M) (1007)</t>
-  </si>
-  <si>
-    <t>5537 PATRIKA (JC) (25-052)</t>
-  </si>
-  <si>
-    <t>5538 PATRIKA (JC) *-* (M) (7073)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA-B (2942-B)</t>
-  </si>
-  <si>
-    <t>5539 PATRIKA (JC) (2942)</t>
-  </si>
-  <si>
-    <t>5540 PATRIKA *-* (M) (S-96)</t>
-  </si>
-  <si>
-    <t>5541 PATRIKA (JC) (2101)</t>
-  </si>
-  <si>
-    <t>5542 PATRIKA (2261)</t>
-  </si>
-  <si>
-    <t>5543 PATRIKA (2353)</t>
-  </si>
-  <si>
-    <t>5544 PATRIKA *-* (M) (2732)</t>
-  </si>
-  <si>
-    <t>5545 PATRIKA *-* (M) (DC) (2791)</t>
-  </si>
-  <si>
-    <t>5546 PATRIKA (718)</t>
-  </si>
-  <si>
-    <t>5547 PATRIKA *-* (M) (S-32)</t>
-  </si>
-  <si>
-    <t>5548 PATRIKA (DCU) (2792)</t>
-  </si>
-  <si>
-    <t>5549 PATRIKA (5261 NICE)</t>
-  </si>
-  <si>
-    <t>5550 PATRIKA *-* (M) (5424)</t>
-  </si>
-  <si>
-    <t>5551 PATRIKA (5231)</t>
-  </si>
-  <si>
-    <t>5552 PATRIKA (JC) *-* (M) (S-163)</t>
-  </si>
-  <si>
-    <t>5553 PATRIKA *-* (M) (5004)</t>
-  </si>
-  <si>
-    <t>5554 PATRIKA *-* (F/G) (5379)</t>
-  </si>
-  <si>
-    <t>5555 PATRIKA (2903)</t>
-  </si>
-  <si>
-    <t>5556 PATRIKA *-* (M) (2952)</t>
-  </si>
-  <si>
-    <t>5557 PATRIKA (2312 SBC)</t>
-  </si>
-  <si>
-    <t>5558 PATRIKA *-* (M) (121 NEHA)</t>
-  </si>
-  <si>
-    <t>5559 PATRIKA (2293)</t>
-  </si>
-  <si>
-    <t>5560 PATRIKA (F/G) *-* (2915)</t>
-  </si>
-  <si>
-    <t>5561 PATRIKA *-* (M) (25358)</t>
-  </si>
-  <si>
-    <t>5562 PATRIKA *-* (M) (114-B (NEHA))</t>
-  </si>
-  <si>
-    <t>5563 PATRIKA (5387)</t>
-  </si>
-  <si>
-    <t>5564 PATRIKA (JC) *-* (M) (S-107)</t>
-  </si>
-  <si>
-    <t>5565 PATRIKA (175)</t>
-  </si>
-  <si>
-    <t>5566 PATRIKA *-* (M) (1742-B)</t>
-  </si>
-  <si>
-    <t>5567 PATRIKA (1679)</t>
-  </si>
-  <si>
-    <t>5568 PATRIKA *-* (M) (3002)</t>
-  </si>
-  <si>
-    <t>5569 PATRIKA *-* (M) (S-39)</t>
-  </si>
-  <si>
-    <t>5570 PATRIKA *-* (M) (S-74)</t>
-  </si>
-  <si>
-    <t>5571 PATRIKA *-* (M) (25353)</t>
-  </si>
-  <si>
-    <t>5572 PATRIKA *-* (M) (25351)</t>
-  </si>
-  <si>
-    <t>5573 PATRIKA (2205)</t>
-  </si>
-  <si>
-    <t>5574 PATRIKA (25335)</t>
-  </si>
-  <si>
-    <t>5575 PATRIKA *-* (M) (S-77)</t>
-  </si>
-  <si>
-    <t>5576 PATRIKA (2531)</t>
-  </si>
-  <si>
-    <t>5577 PATRIKA *-* (M) (5808)</t>
-  </si>
-  <si>
-    <t>5578 PATRIKA (JC) *-* (M) (AS-104 / S-50)</t>
-  </si>
-  <si>
-    <t>5579 PATRIKA (JC) *-* (M) (AS-102)</t>
-  </si>
-  <si>
-    <t>5580 PATRIKA (S-326)</t>
-  </si>
-  <si>
-    <t>5581 PATRIKA *-* (M) (3471)</t>
-  </si>
-  <si>
-    <t>5582 PATRIKA *-* (M) (3512 SBC)</t>
-  </si>
-  <si>
-    <t>5583 PATRIKA (3211 SBC)</t>
-  </si>
-  <si>
-    <t>5584 PATRIKA (JC) (2202 SBC)</t>
-  </si>
-  <si>
-    <t>5585 PATRIKA *-* (M) (1201 KBC)</t>
-  </si>
-  <si>
-    <t>5586 PATRIKA *-* (M) (S-51)</t>
-  </si>
-  <si>
-    <t>5587 PATRIKA (2264)</t>
-  </si>
-  <si>
-    <t>5588 PATRIKA (JC) *-* (M) (1006)</t>
-  </si>
-  <si>
-    <t>5589 PATRIKA *-* (M) (25133)</t>
-  </si>
-  <si>
-    <t>5590 PATRIKA (3131 SBC)</t>
-  </si>
-  <si>
-    <t>5591 PATRIKA (DCU) (3735 YLW)</t>
-  </si>
-  <si>
-    <t>5592 PATRIKA *-* (M) (2365)</t>
-  </si>
-  <si>
-    <t>5593 PATRIKA (2803)</t>
-  </si>
-  <si>
-    <t>5594 PATRIKA (JC) (2931)</t>
-  </si>
-  <si>
-    <t>5595 PATRIKA *-* (M) (226)</t>
-  </si>
-  <si>
-    <t>5596 PATRIKA *-* (M) (2541)</t>
-  </si>
-  <si>
-    <t>5597 PATRIKA (JC) *-* (M) (AS-104 (B))</t>
-  </si>
-  <si>
-    <t>5599 PATRIKA *-* (M) (77-B)</t>
-  </si>
-  <si>
-    <t>5600 PATRIKA (JC) (25324)</t>
-  </si>
-  <si>
-    <t>5601 PATRIKA (2771)</t>
-  </si>
-  <si>
-    <t>5602 PATRIKA (3271)</t>
-  </si>
-  <si>
-    <t>5603 PATRIKA *-* (M) (6125)</t>
-  </si>
-  <si>
-    <t>5604 PATRIKA (242-A)</t>
-  </si>
-  <si>
-    <t>5605 PATRIKA (JC) (3102)</t>
-  </si>
-  <si>
-    <t>5606 PATRIKA *-* (M) (221-A)</t>
-  </si>
-  <si>
-    <t>5607 PATRIKA (25442)</t>
-  </si>
-  <si>
-    <t>5608 PATRIKA (25440)</t>
-  </si>
-  <si>
-    <t>5609 PATRIKA (993)</t>
-  </si>
-  <si>
-    <t>5610 PATRIKA (JC) (2373)</t>
-  </si>
-  <si>
-    <t>5611 PATRIKA *-* (M) (1211)</t>
-  </si>
-  <si>
-    <t>5612 PATRIKA (DCU) (5276)</t>
-  </si>
-  <si>
-    <t>5613 PATRIKA (JC) (DC) (1841-A)</t>
-  </si>
-  <si>
-    <t>5614 PATRIKA *-* (M) Design Change (2331)</t>
-  </si>
-  <si>
-    <t>5615 PATRIKA (2111)</t>
-  </si>
-  <si>
-    <t>5616 PATRIKA (DCU) (7069)</t>
-  </si>
-  <si>
-    <t>5617 PATRIKA *-* (M) (7067)</t>
-  </si>
-  <si>
-    <t>5618 PATRIKA (JC) *-* (M) (S-52)</t>
-  </si>
-  <si>
-    <t>5619 PATRIKA (JC) (1131)</t>
-  </si>
-  <si>
-    <t>5620 PATRIKA (JC) (15)</t>
-  </si>
-  <si>
-    <t>5621 PATRIKA (JC) *-* (M) (5297)</t>
-  </si>
-  <si>
-    <t>5622 PATRIKA *-* (M) (25337)</t>
-  </si>
-  <si>
-    <t>5623 PATRIKA (064)</t>
-  </si>
-  <si>
-    <t>5624 PATRIKA (JC) (2753)</t>
-  </si>
-  <si>
-    <t>5625 PATRIKA (DCU) (772)</t>
-  </si>
-  <si>
-    <t>5626 PATRIKA (DCU) (FULL JALI)</t>
-  </si>
-  <si>
-    <t>5627 PATRIKA (DCU) (HALF JALI)</t>
-  </si>
-  <si>
-    <t>5628 PATRIKA (DCU) (GOL)</t>
-  </si>
-  <si>
-    <t>5629 PATRIKA (DCU) (9*5 X 6*5 PATTA)</t>
-  </si>
-  <si>
-    <t>5630 PATRIKA (DCU) (SATHIYA)</t>
-  </si>
-  <si>
-    <t>6601 PATRIKA (L) (5164)</t>
-  </si>
-  <si>
-    <t>6602 PATRIKA (5126)</t>
-  </si>
-  <si>
-    <t>6603 PATRIKA (5111)</t>
-  </si>
-  <si>
-    <t>6604 PATRIKA *-* (M) (5196)</t>
-  </si>
-  <si>
-    <t>6605 PATRIKA (5191)</t>
-  </si>
-  <si>
-    <t>6606 PATRIKA (*-*) R (3023)</t>
-  </si>
-  <si>
-    <t>6607 PATRIKA *-* (M) (0523)</t>
-  </si>
-  <si>
-    <t>6608 PATRIKA (95)</t>
-  </si>
-  <si>
-    <t>6609 PATRIKA *-* (M) (3053)</t>
-  </si>
-  <si>
-    <t>6610 PATRIKA *-* (M) (3019)</t>
-  </si>
-  <si>
-    <t>6611 PATRIKA (DC) (3017 VV)</t>
-  </si>
-  <si>
-    <t>6612 PATRIKA (3015)</t>
-  </si>
-  <si>
-    <t>6613 PATRIKA (25164)</t>
-  </si>
-  <si>
-    <t>6614 PATRIKA (DCU) (25131)</t>
-  </si>
-  <si>
-    <t>6615 PATRIKA *-* (M) (915 GAGAN)</t>
-  </si>
-  <si>
-    <t>6616 PATRIKA *-* (M) (911 GAGAN)</t>
-  </si>
-  <si>
-    <t>6617 PATRIKA *-* (M) (3422)</t>
-  </si>
-  <si>
-    <t>6618 PATRIKA *-* (M)''Dc''' (3423)</t>
-  </si>
-  <si>
-    <t>6619 PATRIKA *-* (M) (1193)</t>
-  </si>
-  <si>
-    <t>6620 PATRIKA *-* (M) (1045 GGN (PADDING))</t>
-  </si>
-  <si>
-    <t>6621 PATRIKA *-* (M) (ON ORDER) (7108 (PADDING))</t>
-  </si>
-  <si>
-    <t>6622 PATRIKA *-* (M) (7259 (PADDING))</t>
-  </si>
-  <si>
-    <t>6623 PATRIKA (25184)</t>
-  </si>
-  <si>
-    <t>6624 PATRIKA *-* (M) (25135)</t>
-  </si>
-  <si>
-    <t>6625 PATRIKA *-* (M) (25116)</t>
-  </si>
-  <si>
-    <t>6626 PATRIKA *-* (M) (Alter Available) (25161)</t>
-  </si>
-  <si>
-    <t>6627 PATRIKA *-* (M) (25111)</t>
-  </si>
-  <si>
-    <t>6628 PATRIKA *-* (M) (805 SBC)</t>
-  </si>
-  <si>
-    <t>6629 PATRIKA *-* (M) (812 NEW SBC)</t>
-  </si>
-  <si>
-    <t>6630 PATRIKA *-* (M) (5510 NICE)</t>
-  </si>
-  <si>
-    <t>6631 PATRIKA (DCU) (OLD AP ITEM)</t>
-  </si>
-  <si>
-    <t>6632 PATRIKA (DCU) (932)</t>
-  </si>
-  <si>
-    <t>6633 PATRIKA *-* (M) (7081 VP)</t>
-  </si>
-  <si>
-    <t>6634 PATRIKA (3562)</t>
-  </si>
-  <si>
-    <t>6635 PATRIKA *-* (M) (S-313)</t>
-  </si>
-  <si>
-    <t>6636 PATRIKA *-* (M) (25183)</t>
-  </si>
-  <si>
-    <t>6637 PATRIKA (25162 GE)</t>
-  </si>
-  <si>
-    <t>6638 PATRIKA *-* (M) (3014)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (2291)</t>
-  </si>
-  <si>
-    <t>6639 PATRIKA (B) (2291-B)</t>
-  </si>
-  <si>
-    <t>6640 PATRIKA *-* (M) (5737 PADING)</t>
-  </si>
-  <si>
-    <t>6641 PATRIKA *-* (M) Dc (5435)</t>
-  </si>
-  <si>
-    <t>6642 PATRIKA *-* (M) (5411 RJ)</t>
-  </si>
-  <si>
-    <t>6643 PATRIKA *-* (M) (25380)</t>
-  </si>
-  <si>
-    <t>6644 PATRIKA (DCU) (25132)</t>
-  </si>
-  <si>
-    <t>6645 PATRIKA *-* (M) (3031)</t>
-  </si>
-  <si>
-    <t>6646 PATRIKA *-* (M) (3034)</t>
-  </si>
-  <si>
-    <t>6647 PATRIKA *-* (M) (25382)</t>
-  </si>
-  <si>
-    <t>6648 PATRIKA *-* (M) (5011 (PADDING))</t>
-  </si>
-  <si>
-    <t>6649 PATRIKA *-* (M) (3402)</t>
-  </si>
-  <si>
-    <t>6650 PATRIKA *-* (M) DC (3431)</t>
-  </si>
-  <si>
-    <t>6651 PATRIKA (3421)</t>
-  </si>
-  <si>
-    <t>6652 PATRIKA *-* (M) (2764 SBC)</t>
-  </si>
-  <si>
-    <t>6653 PATRIKA *-* (M) (834 SBC NEW)</t>
-  </si>
-  <si>
-    <t>6654 PATRIKA *-* (M) (3461)</t>
-  </si>
-  <si>
-    <t>6655 PATRIKA *-* (M) (7129 (PADDING))</t>
-  </si>
-  <si>
-    <t>6656 PATRIKA (L) (7113 (PADDING))</t>
-  </si>
-  <si>
-    <t>6657 PATRIKA *-* (M)-DC (563  DHANESH)</t>
-  </si>
-  <si>
-    <t>6658 PATRIKA *-* (M) (5319)</t>
-  </si>
-  <si>
-    <t>6659 PATRIKA (25193 (Padding))</t>
-  </si>
-  <si>
-    <t>6660 PATRIKA (25194 (Padding))</t>
-  </si>
-  <si>
-    <t>6661 PATRIKA *-* (M) (1281)</t>
-  </si>
-  <si>
-    <t>6662 PATRIKA (3424)</t>
-  </si>
-  <si>
-    <t>6663 PATRIKA (7103 (PADDING))</t>
-  </si>
-  <si>
-    <t>6664 PATRIKA *-* (M) (5823)</t>
-  </si>
-  <si>
-    <t>6665 PATRIKA *-* (M) (603 DHANESH)</t>
-  </si>
-  <si>
-    <t>6666 PATRIKA *-* (M) (DC) (1192 KBC)</t>
-  </si>
-  <si>
-    <t>6667 PATRIKA *-* (M) (1192 SBC)</t>
-  </si>
-  <si>
-    <t>6668 PATRIKA (DCU) (8102)</t>
-  </si>
-  <si>
-    <t>6669 PATRIKA (DCU) (6197)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA - B (M) (1868-B)</t>
-  </si>
-  <si>
-    <t>6670 PATRIKA *-* (M) (1868)</t>
-  </si>
-  <si>
-    <t>6671 PATRIKA *-* (M) (1872)</t>
-  </si>
-  <si>
-    <t>6672 PATRIKA *-* (M) (6132)</t>
-  </si>
-  <si>
-    <t>6673 PATRIKA (DCU) (6196)</t>
-  </si>
-  <si>
-    <t>6674 PATRIKA (DCU) (1503)</t>
-  </si>
-  <si>
-    <t>6675 PATRIKA *-* (M) (1282)</t>
-  </si>
-  <si>
-    <t>6676 PATRIKA (DCU) (533 KBC)</t>
-  </si>
-  <si>
-    <t>6677 PATRIKA (DCU) (25191 PADDING)</t>
-  </si>
-  <si>
-    <t>7265 PATRIKA (O.C.) (133)</t>
-  </si>
-  <si>
-    <t>7283 PATRIKA {F} (O.C.) (4148)</t>
-  </si>
-  <si>
-    <t>7287 PATRIKA (O.C.) (1522)</t>
-  </si>
-  <si>
-    <t>7288 PATRIKA (O.C.) (1178)</t>
-  </si>
-  <si>
-    <t>7293 PATRIKA (O.C.) (AS-20)</t>
-  </si>
-  <si>
-    <t>7309 PATRIKA (O.C.) (4087)</t>
-  </si>
-  <si>
-    <t>7312 PATRIKA (O.C.) (SBC 7312)</t>
-  </si>
-  <si>
-    <t>7319 PATRIKA (O.C.) (2204)</t>
-  </si>
-  <si>
-    <t>7332 PATRIKA (O.C.) (2482)</t>
-  </si>
-  <si>
-    <t>7342 PATRIKA (O.C.) (12)</t>
-  </si>
-  <si>
-    <t>7344 PATRIKA (O.C.) (INV B.P. RED (11))</t>
-  </si>
-  <si>
-    <t>7345 PATRIKA (O.C.) (INV B.P. GOLDEN (120) 5)</t>
-  </si>
-  <si>
-    <t>7401 PATRIKA (25/252)</t>
-  </si>
-  <si>
-    <t>7402 PATRIKA (25/264-263)</t>
-  </si>
-  <si>
-    <t>7403 PATRIKA (25/363/863)</t>
-  </si>
-  <si>
-    <t>7404 PATRIKA (25/283)</t>
-  </si>
-  <si>
-    <t>7405 PATRIKA (25/273)</t>
-  </si>
-  <si>
-    <t>7406 PATRIKA (25/172)</t>
-  </si>
-  <si>
-    <t>7407 PATRIKA *-* (F) (7145 VP)</t>
-  </si>
-  <si>
-    <t>7408 PATRIKA (DCU) (25895)</t>
-  </si>
-  <si>
-    <t>7409 PATRIKA (2521)</t>
-  </si>
-  <si>
-    <t>7410 PATRIKA (2526)</t>
-  </si>
-  <si>
-    <t>7411 PATRIKA (2535)</t>
-  </si>
-  <si>
-    <t>7412 PATRIKA (84)</t>
-  </si>
-  <si>
-    <t>7413 PATRIKA (2543 INV OFFSET)</t>
-  </si>
-  <si>
-    <t>7414 PATRIKA (1015 GREEN OFFSET)</t>
-  </si>
-  <si>
-    <t>7415 PATRIKA *-* (F) (3162 SBC)</t>
-  </si>
-  <si>
-    <t>7416 PATRIKA (2234)</t>
-  </si>
-  <si>
-    <t>7417 PATRIKA (S-201 INV)</t>
-  </si>
-  <si>
-    <t>7418 PATRIKA *-* (डोरी) (1639)</t>
-  </si>
-  <si>
-    <t>7419 PATRIKA (5121)</t>
-  </si>
-  <si>
-    <t>7420 PATRIKA (720)</t>
-  </si>
-  <si>
-    <t>7421 PATRIKA *-* (F) (25-146)</t>
-  </si>
-  <si>
-    <t>7422 PATRIKA (3702)</t>
-  </si>
-  <si>
-    <t>7423 PATRIKA (254 SBC)</t>
-  </si>
-  <si>
-    <t>7424 PATRIKA *-* (F) (25-047)</t>
-  </si>
-  <si>
-    <t>7425 PATRIKA (2082)</t>
-  </si>
-  <si>
-    <t>7426 PATRIKA (F/G) *-* (4052)</t>
-  </si>
-  <si>
-    <t>7427 PATRIKA (2103)</t>
-  </si>
-  <si>
-    <t>7428 PATRIKA (1223 SBC)</t>
-  </si>
-  <si>
-    <t>7429 PATRIKA (F/G) *-* (1851 MONARCH)</t>
-  </si>
-  <si>
-    <t>7430 PATRIKA (6310 GE)</t>
-  </si>
-  <si>
-    <t>7431 PATRIKA (2532)</t>
-  </si>
-  <si>
-    <t>7432 PATRIKA (1174)</t>
-  </si>
-  <si>
-    <t>7433 PATRIKA (1034)</t>
-  </si>
-  <si>
-    <t>7434 PATRIKA (2204 INV)</t>
-  </si>
-  <si>
-    <t>7435 PATRIKA (06)</t>
-  </si>
-  <si>
-    <t>7436 PATRIKA (303)</t>
-  </si>
-  <si>
-    <t>7437 PATRIKA (25323 INV)</t>
-  </si>
-  <si>
-    <t>7438 PATRIKA (25413)</t>
-  </si>
-  <si>
-    <t>7439 PATRIKA (2597)</t>
-  </si>
-  <si>
-    <t>7440 PATRIKA (25896)</t>
-  </si>
-  <si>
-    <t>7441 PATRIKA *-* (F) (243-C)</t>
-  </si>
-  <si>
-    <t>7442 PATRIKA (1855)</t>
-  </si>
-  <si>
-    <t>7443 PATRIKA (1044 SBC)</t>
-  </si>
-  <si>
-    <t>7444 PATRIKA (2014)</t>
-  </si>
-  <si>
-    <t>7445 PATRIKA (2006)</t>
-  </si>
-  <si>
-    <t>7446 PATRIKA (DCU) (6106)</t>
-  </si>
-  <si>
-    <t>7447 PATRIKA (GOPAL 32)</t>
-  </si>
-  <si>
-    <t>7448 PATRIKA (2005- G)</t>
-  </si>
-  <si>
-    <t>7449 PATRIKA (5180)</t>
-  </si>
-  <si>
-    <t>7450 PATRIKA (DCU) (3753)</t>
-  </si>
-  <si>
-    <t>7451 PATRIKA (273 NEHA)</t>
-  </si>
-  <si>
-    <t>7452 PATRIKA (278-B)</t>
-  </si>
-  <si>
-    <t>7453 PATRIKA (ECO - 61) Blue (NEW ECO 61)</t>
-  </si>
-  <si>
-    <t>7454 PATRIKA (ECO -63) Green (NEW ECO 63)</t>
-  </si>
-  <si>
-    <t>7455 PATRIKA ( ECO 64 INV) (NEW ECO 64)</t>
-  </si>
-  <si>
-    <t>7456 PATRIKA ( ECO 62 INV) (NEW ECO -62 INV)</t>
+    <t>4251 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4252 PATRIKA</t>
+  </si>
+  <si>
+    <t>4253 PATRIKA</t>
+  </si>
+  <si>
+    <t>4254 PATRIKA (4210)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA - B (DCU)</t>
+  </si>
+  <si>
+    <t>4255 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4256 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4257 PATRIKA</t>
+  </si>
+  <si>
+    <t>4258 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4259 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4260 PATRIKA</t>
+  </si>
+  <si>
+    <t>4261 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4262 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4263 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4264 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4265 PATRIKA</t>
+  </si>
+  <si>
+    <t>4266 PATRIKA</t>
+  </si>
+  <si>
+    <t>4267 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4268 PATRIKA (JC) *-* (M+T)</t>
+  </si>
+  <si>
+    <t>4269 PATRIKA</t>
+  </si>
+  <si>
+    <t>4270 PATRIKA</t>
+  </si>
+  <si>
+    <t>4271 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4272 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4273 PATRIKA</t>
+  </si>
+  <si>
+    <t>4274 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4275 PATRIKA</t>
+  </si>
+  <si>
+    <t>4276 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4277 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4278 PATRIKA</t>
+  </si>
+  <si>
+    <t>4279 PATRIKA</t>
+  </si>
+  <si>
+    <t>4280 PATRIKA</t>
+  </si>
+  <si>
+    <t>4281 PATRIKA</t>
+  </si>
+  <si>
+    <t>4282 PATRIKA</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA - B (YELLOW)</t>
+  </si>
+  <si>
+    <t>4283 PATRIKA (GOLDEN)</t>
+  </si>
+  <si>
+    <t>4284 PATRIKA</t>
+  </si>
+  <si>
+    <t>4285 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>4286 PATRIKA</t>
+  </si>
+  <si>
+    <t>4287 PATRIKA</t>
+  </si>
+  <si>
+    <t>4288 PATRIKA</t>
+  </si>
+  <si>
+    <t>4289 PATRIKA</t>
+  </si>
+  <si>
+    <t>4290 PATRIKA</t>
+  </si>
+  <si>
+    <t>4291 PATRIKA</t>
+  </si>
+  <si>
+    <t>4292 PATRIKA</t>
+  </si>
+  <si>
+    <t>4293 PATRIKA</t>
+  </si>
+  <si>
+    <t>4294 PATRIKA</t>
+  </si>
+  <si>
+    <t>4295 PATRIKA</t>
+  </si>
+  <si>
+    <t>4296 PATRIKA</t>
+  </si>
+  <si>
+    <t>4297 PATRIKA</t>
+  </si>
+  <si>
+    <t>4298 PATRIKA</t>
+  </si>
+  <si>
+    <t>4299 PATRIKA</t>
+  </si>
+  <si>
+    <t>4300 PATRIKA</t>
+  </si>
+  <si>
+    <t>4301 PATRIKA</t>
+  </si>
+  <si>
+    <t>4302 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4303 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4304 PATRIKA</t>
+  </si>
+  <si>
+    <t>4305 PATRIKA</t>
+  </si>
+  <si>
+    <t>4306 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>4307 PATRIKA</t>
+  </si>
+  <si>
+    <t>4308 PATRIKA</t>
+  </si>
+  <si>
+    <t>4309 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4310 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4311 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4312 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4313 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4314 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4315 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>4316 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5051 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5052 PATRIKA</t>
+  </si>
+  <si>
+    <t>5053 PATRIKA</t>
+  </si>
+  <si>
+    <t>5054 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5055 PATRIKA</t>
+  </si>
+  <si>
+    <t>5056 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5057 PATRIKA</t>
+  </si>
+  <si>
+    <t>5058 PATRIKA</t>
+  </si>
+  <si>
+    <t>5059 PATRIKA</t>
+  </si>
+  <si>
+    <t>5060 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5061 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5062 PATRIKA</t>
+  </si>
+  <si>
+    <t>5063 PATRIKA</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA</t>
+  </si>
+  <si>
+    <t>5065 PATRIKA</t>
+  </si>
+  <si>
+    <t>5066 PATRIKA</t>
+  </si>
+  <si>
+    <t>5067 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5068 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5069 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5070 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5071 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5072 PATRIKA</t>
+  </si>
+  <si>
+    <t>5073 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5074 PATRIKA</t>
+  </si>
+  <si>
+    <t>5075 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5076 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5077 PATRIKA</t>
+  </si>
+  <si>
+    <t>5078 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5079 PATRIKA</t>
+  </si>
+  <si>
+    <t>5080 PATRIKA</t>
+  </si>
+  <si>
+    <t>5081 PATRIKA</t>
+  </si>
+  <si>
+    <t>5083 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5084 PATRIKA (05 march 4000)</t>
+  </si>
+  <si>
+    <t>5085 PATRIKA</t>
+  </si>
+  <si>
+    <t>5086 PATRIKA (JC) *-* (M+D)</t>
+  </si>
+  <si>
+    <t>5087 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5088 PATRIKA</t>
+  </si>
+  <si>
+    <t>5089 PATRIKA</t>
+  </si>
+  <si>
+    <t>5090 PATRIKA</t>
+  </si>
+  <si>
+    <t>5091 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5092 PATRIKA</t>
+  </si>
+  <si>
+    <t>5093 PATRIKA</t>
+  </si>
+  <si>
+    <t>5094 PATRIKA</t>
+  </si>
+  <si>
+    <t>5095 PATRIKA</t>
+  </si>
+  <si>
+    <t>5096 PATRIKA</t>
+  </si>
+  <si>
+    <t>5097 PATRIKA</t>
+  </si>
+  <si>
+    <t>5098 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5099 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5100 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5102 PATRIKA (5021)</t>
+  </si>
+  <si>
+    <t>5103 PATRIKA</t>
+  </si>
+  <si>
+    <t>5104 PATRIKA</t>
+  </si>
+  <si>
+    <t>5105 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5106 PATRIKA</t>
+  </si>
+  <si>
+    <t>5107 PATRIKA</t>
+  </si>
+  <si>
+    <t>5108 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5109 PATRIKA</t>
+  </si>
+  <si>
+    <t>5110 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5111 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5112 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5113 PATRIKA</t>
+  </si>
+  <si>
+    <t>5114 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>5115 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5116 PATRIKA</t>
+  </si>
+  <si>
+    <t>5117 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5118 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5501 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5502 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5503 PATRIKA</t>
+  </si>
+  <si>
+    <t>5504 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5505 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5506 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5507 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5508 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5509 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5510 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5511 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5512 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5513 PATRIKA</t>
+  </si>
+  <si>
+    <t>5514 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5515 PATRIKA</t>
+  </si>
+  <si>
+    <t>5516 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
+  </si>
+  <si>
+    <t>5518 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5519 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5520 PATRIKA</t>
+  </si>
+  <si>
+    <t>5521 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5522 PATRIKA</t>
+  </si>
+  <si>
+    <t>5523 PATRIKA</t>
+  </si>
+  <si>
+    <t>5524 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5525 PATRIKA *-* (M) (05 march 2000)</t>
+  </si>
+  <si>
+    <t>5526 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5527 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5528 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5529 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5530 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5531 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5532 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5533 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5534 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5535 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5537 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5538 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA-B</t>
+  </si>
+  <si>
+    <t>5539 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5540 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5541 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5542 PATRIKA</t>
+  </si>
+  <si>
+    <t>5543 PATRIKA</t>
+  </si>
+  <si>
+    <t>5544 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5545 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>5546 PATRIKA</t>
+  </si>
+  <si>
+    <t>5547 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5548 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5549 PATRIKA</t>
+  </si>
+  <si>
+    <t>5550 PATRIKA *-* (M) (05 march 950)</t>
+  </si>
+  <si>
+    <t>5551 PATRIKA</t>
+  </si>
+  <si>
+    <t>5552 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5553 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5554 PATRIKA *-* (F/G) (05 march 3000)</t>
+  </si>
+  <si>
+    <t>5555 PATRIKA</t>
+  </si>
+  <si>
+    <t>5556 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5557 PATRIKA</t>
+  </si>
+  <si>
+    <t>5558 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5559 PATRIKA</t>
+  </si>
+  <si>
+    <t>5560 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>5561 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5562 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5563 PATRIKA</t>
+  </si>
+  <si>
+    <t>5564 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5565 PATRIKA</t>
+  </si>
+  <si>
+    <t>5566 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5567 PATRIKA</t>
+  </si>
+  <si>
+    <t>5568 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5569 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5570 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5571 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5572 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5573 PATRIKA</t>
+  </si>
+  <si>
+    <t>5574 PATRIKA 8/MARCH</t>
+  </si>
+  <si>
+    <t>5575 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5576 PATRIKA</t>
+  </si>
+  <si>
+    <t>5577 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5578 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5579 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5580 PATRIKA</t>
+  </si>
+  <si>
+    <t>5581 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>5582 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5583 PATRIKA</t>
+  </si>
+  <si>
+    <t>5584 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5585 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5586 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5587 PATRIKA</t>
+  </si>
+  <si>
+    <t>5588 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5589 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5590 PATRIKA</t>
+  </si>
+  <si>
+    <t>5591 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5592 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5593 PATRIKA</t>
+  </si>
+  <si>
+    <t>5594 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5595 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5596 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5597 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5599 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5600 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5601 PATRIKA</t>
+  </si>
+  <si>
+    <t>5602 PATRIKA</t>
+  </si>
+  <si>
+    <t>5603 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5604 PATRIKA</t>
+  </si>
+  <si>
+    <t>5605 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5606 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5607 PATRIKA</t>
+  </si>
+  <si>
+    <t>5608 PATRIKA</t>
+  </si>
+  <si>
+    <t>5609 PATRIKA</t>
+  </si>
+  <si>
+    <t>5610 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5611 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5612 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5613 PATRIKA (JC) (DC)</t>
+  </si>
+  <si>
+    <t>5614 PATRIKA *-* (M) Design Change</t>
+  </si>
+  <si>
+    <t>5615 PATRIKA</t>
+  </si>
+  <si>
+    <t>5616 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5618 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5619 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5620 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5621 PATRIKA (JC) *-* (M)</t>
+  </si>
+  <si>
+    <t>5622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>5623 PATRIKA</t>
+  </si>
+  <si>
+    <t>5624 PATRIKA (JC)</t>
+  </si>
+  <si>
+    <t>5625 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5626 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5627 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5628 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5629 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>5630 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6601 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6602 PATRIKA</t>
+  </si>
+  <si>
+    <t>6603 PATRIKA</t>
+  </si>
+  <si>
+    <t>6604 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6605 PATRIKA</t>
+  </si>
+  <si>
+    <t>6606 PATRIKA (*-*) R</t>
+  </si>
+  <si>
+    <t>6607 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6608 PATRIKA</t>
+  </si>
+  <si>
+    <t>6609 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6610 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6611 PATRIKA (DC)</t>
+  </si>
+  <si>
+    <t>6612 PATRIKA</t>
+  </si>
+  <si>
+    <t>6613 PATRIKA</t>
+  </si>
+  <si>
+    <t>6614 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6615 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6616 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6617 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6618 PATRIKA *-* (M)''Dc'''</t>
+  </si>
+  <si>
+    <t>6619 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6620 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6621 PATRIKA *-* (M) (ON ORDER)</t>
+  </si>
+  <si>
+    <t>6622 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6623 PATRIKA</t>
+  </si>
+  <si>
+    <t>6624 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6625 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6626 PATRIKA *-* (M) (Alter Available)</t>
+  </si>
+  <si>
+    <t>6627 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6628 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6629 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6630 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6631 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6632 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6633 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6634 PATRIKA</t>
+  </si>
+  <si>
+    <t>6635 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6636 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6637 PATRIKA</t>
+  </si>
+  <si>
+    <t>6638 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA</t>
+  </si>
+  <si>
+    <t>6639 PATRIKA (B)</t>
+  </si>
+  <si>
+    <t>6640 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6641 PATRIKA *-* (M) Dc</t>
+  </si>
+  <si>
+    <t>6642 PATRIKA *-* (M) 1800PCS 06.02.26</t>
+  </si>
+  <si>
+    <t>6643 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6644 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6645 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6646 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6647 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6648 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6649 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6650 PATRIKA *-* (M) DC</t>
+  </si>
+  <si>
+    <t>6651 PATRIKA</t>
+  </si>
+  <si>
+    <t>6652 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6653 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6654 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6655 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6656 PATRIKA (L)</t>
+  </si>
+  <si>
+    <t>6657 PATRIKA *-* (M)-DC</t>
+  </si>
+  <si>
+    <t>6658 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6659 PATRIKA</t>
+  </si>
+  <si>
+    <t>6660 PATRIKA</t>
+  </si>
+  <si>
+    <t>6661 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6662 PATRIKA</t>
+  </si>
+  <si>
+    <t>6663 PATRIKA</t>
+  </si>
+  <si>
+    <t>6664 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6665 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6666 PATRIKA *-* (M) (DC)</t>
+  </si>
+  <si>
+    <t>6667 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6668 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6669 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA - B (M)</t>
+  </si>
+  <si>
+    <t>6670 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6671 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6672 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6673 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6674 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6675 PATRIKA *-* (M)</t>
+  </si>
+  <si>
+    <t>6676 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>6677 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7265 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7283 PATRIKA {F} (O.C.)</t>
+  </si>
+  <si>
+    <t>7287 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7288 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7293 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7309 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7312 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7319 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7332 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7342 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7344 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7345 PATRIKA (O.C.)</t>
+  </si>
+  <si>
+    <t>7401 PATRIKA</t>
+  </si>
+  <si>
+    <t>7402 PATRIKA</t>
+  </si>
+  <si>
+    <t>7403 PATRIKA</t>
+  </si>
+  <si>
+    <t>7404 PATRIKA</t>
+  </si>
+  <si>
+    <t>7405 PATRIKA</t>
+  </si>
+  <si>
+    <t>7406 PATRIKA</t>
+  </si>
+  <si>
+    <t>7407 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7408 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7409 PATRIKA</t>
+  </si>
+  <si>
+    <t>7410 PATRIKA</t>
+  </si>
+  <si>
+    <t>7411 PATRIKA</t>
+  </si>
+  <si>
+    <t>7412 PATRIKA</t>
+  </si>
+  <si>
+    <t>7413 PATRIKA</t>
+  </si>
+  <si>
+    <t>7414 PATRIKA</t>
+  </si>
+  <si>
+    <t>7415 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7416 PATRIKA</t>
+  </si>
+  <si>
+    <t>7417 PATRIKA</t>
+  </si>
+  <si>
+    <t>7418 PATRIKA *-* (डोरी)</t>
+  </si>
+  <si>
+    <t>7419 PATRIKA</t>
+  </si>
+  <si>
+    <t>7420 PATRIKA</t>
+  </si>
+  <si>
+    <t>7421 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7422 PATRIKA</t>
+  </si>
+  <si>
+    <t>7423 PATRIKA</t>
+  </si>
+  <si>
+    <t>7424 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7425 PATRIKA</t>
+  </si>
+  <si>
+    <t>7426 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7427 PATRIKA</t>
+  </si>
+  <si>
+    <t>7428 PATRIKA</t>
+  </si>
+  <si>
+    <t>7429 PATRIKA (F/G) *-*</t>
+  </si>
+  <si>
+    <t>7430 PATRIKA</t>
+  </si>
+  <si>
+    <t>7431 PATRIKA</t>
+  </si>
+  <si>
+    <t>7432 PATRIKA</t>
+  </si>
+  <si>
+    <t>7433 PATRIKA</t>
+  </si>
+  <si>
+    <t>7434 PATRIKA</t>
+  </si>
+  <si>
+    <t>7435 PATRIKA</t>
+  </si>
+  <si>
+    <t>7436 PATRIKA</t>
+  </si>
+  <si>
+    <t>7437 PATRIKA</t>
+  </si>
+  <si>
+    <t>7438 PATRIKA</t>
+  </si>
+  <si>
+    <t>7439 PATRIKA</t>
+  </si>
+  <si>
+    <t>7440 PATRIKA</t>
+  </si>
+  <si>
+    <t>7441 PATRIKA *-* (F)</t>
+  </si>
+  <si>
+    <t>7442 PATRIKA</t>
+  </si>
+  <si>
+    <t>7443 PATRIKA</t>
+  </si>
+  <si>
+    <t>7444 PATRIKA</t>
+  </si>
+  <si>
+    <t>7445 PATRIKA</t>
+  </si>
+  <si>
+    <t>7446 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7447 PATRIKA</t>
+  </si>
+  <si>
+    <t>7448 PATRIKA</t>
+  </si>
+  <si>
+    <t>7449 PATRIKA</t>
+  </si>
+  <si>
+    <t>7450 PATRIKA (DCU)</t>
+  </si>
+  <si>
+    <t>7451 PATRIKA</t>
+  </si>
+  <si>
+    <t>7452 PATRIKA</t>
+  </si>
+  <si>
+    <t>7453 PATRIKA (ECO - 61) Blue</t>
+  </si>
+  <si>
+    <t>7454 PATRIKA (ECO -63) Green</t>
+  </si>
+  <si>
+    <t>7455 PATRIKA ( ECO 64 INV)</t>
+  </si>
+  <si>
+    <t>7456 PATRIKA ( ECO 62 INV)</t>
   </si>
   <si>
     <t>7457 PATRIKA</t>
@@ -1796,7 +1796,7 @@
     <t>7604 PATRIKA</t>
   </si>
   <si>
-    <t>9001 CARD (O.C.) (2498 Cream)</t>
+    <t>9001 CARD (O.C.)</t>
   </si>
   <si>
     <t>9221 CARDS - YELLOW</t>
@@ -1820,298 +1820,298 @@
     <t>9227 CARDS (9*5 OFFSET)</t>
   </si>
   <si>
-    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE (HALDI  WITH ONLY FOIL)</t>
-  </si>
-  <si>
-    <t>92-29 B Patrika (GOLDEN WITH GANESH JI &amp; FOIL)</t>
-  </si>
-  <si>
-    <t>9229 CARDS (C) (Biscuit WITH GANESH JI &amp; FOIL)</t>
+    <t>9228 CARDS (Y) GANESH JI FOIL SAME RATE</t>
+  </si>
+  <si>
+    <t>92-29 B Patrika</t>
+  </si>
+  <si>
+    <t>9229 CARDS (C)</t>
   </si>
   <si>
     <t>9230 (CARD) 9*5 SCREEN</t>
   </si>
   <si>
-    <t>9231 CARDS (DCU) (RIYAZ 9*5 PINK)</t>
-  </si>
-  <si>
-    <t>9232 CARDS (DCU) (RIYAZ 9*5 CREAM)</t>
-  </si>
-  <si>
-    <t>9233 CARDS (DCU) (RIYAZ 9*5 YELLOW)</t>
-  </si>
-  <si>
-    <t>9234 CARDS (DCU) (RIYAZ 9*4 PINK)</t>
-  </si>
-  <si>
-    <t>9235 CARDS (DCU) (RIYAZ 9*4 CREAM)</t>
-  </si>
-  <si>
-    <t>9236 CARDS (DCU) (RIYAZ 9*4 YELLOW)</t>
-  </si>
-  <si>
-    <t>9237 CARDS (DCU) (DCU 9*4 RED)</t>
-  </si>
-  <si>
-    <t>9238 CARDS (DCU) (9*5 RED DCU)</t>
-  </si>
-  <si>
-    <t>9239 CARDS (9*5 OFFSET PINK COMMON)</t>
-  </si>
-  <si>
-    <t>9240 CARDS (9*5 OFFSET CREAM COMMON)</t>
-  </si>
-  <si>
-    <t>9241 CARDS (9*5 OFFSET GANESH)</t>
-  </si>
-  <si>
-    <t>9242 CARDS (9*5 OFFSET GANESH JI)</t>
-  </si>
-  <si>
-    <t>9243 CARDS (PINK WITH GANESH JI AND FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9244 CARDS (CREAM COLOUR WITH GANESH JI &amp; FOIL 9*5)</t>
-  </si>
-  <si>
-    <t>9301 CARDS (4242)</t>
-  </si>
-  <si>
-    <t>9302 CARDS (5076)</t>
-  </si>
-  <si>
-    <t>9303 CARDS (5080 Pink)</t>
-  </si>
-  <si>
-    <t>9304 CARDS (5083 Blue)</t>
-  </si>
-  <si>
-    <t>9305 CARDS (9070) (4701 Nice)</t>
-  </si>
-  <si>
-    <t>9306 CARDS (0543 Nice)</t>
-  </si>
-  <si>
-    <t>9307 CARDS *-* (M) (5243 Nice)</t>
-  </si>
-  <si>
-    <t>9308 CARDS (9852)</t>
-  </si>
-  <si>
-    <t>9309 CARD - B  (DESIGN CHNG) (9565 VP)</t>
-  </si>
-  <si>
-    <t>9309 CARDS *-* (T) (Dc) (9561 Vp)</t>
-  </si>
-  <si>
-    <t>9310 CARDS (3103)</t>
-  </si>
-  <si>
-    <t>9311 CARDS (3115)</t>
-  </si>
-  <si>
-    <t>9312 CARDS *-* (T) (208 VV)</t>
-  </si>
-  <si>
-    <t>9313 CARDS *-* (T) (216)</t>
-  </si>
-  <si>
-    <t>9314 CARDS (P-1)</t>
-  </si>
-  <si>
-    <t>9315 CARDS (DCU) (P-2)</t>
-  </si>
-  <si>
-    <t>9316 CARDS (DCU) (P-3)</t>
-  </si>
-  <si>
-    <t>9317 CARDS (P-4)</t>
-  </si>
-  <si>
-    <t>9318 CARDS (25905)</t>
-  </si>
-  <si>
-    <t>9319 CARDS (25906)</t>
-  </si>
-  <si>
-    <t>9320 CARDS (S-20)</t>
-  </si>
-  <si>
-    <t>9321 CARDS - (DC) (22912 GANESH JI)</t>
-  </si>
-  <si>
-    <t>9322 CARDS *-* (M) - DC (22912 COMMON)</t>
-  </si>
-  <si>
-    <t>9323 CARDS (9005 OLD) (9*5 CREAM FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9324 CARDS (9*5 PINK FOIL NEW)</t>
-  </si>
-  <si>
-    <t>9325 CARDS (5229)</t>
-  </si>
-  <si>
-    <t>9326 CARDS (1601)</t>
-  </si>
-  <si>
-    <t>9327 CARDS (25908)</t>
-  </si>
-  <si>
-    <t>9328 CARDS (2543)</t>
-  </si>
-  <si>
-    <t>9329 CARDS (3606)</t>
-  </si>
-  <si>
-    <t>9330 CARDS *-* (T) (9557)</t>
-  </si>
-  <si>
-    <t>9331 CARDS *-*  (T) (9560)</t>
-  </si>
-  <si>
-    <t>9332 CARDS-DC (9847)</t>
-  </si>
-  <si>
-    <t>9333 CARDS (6042)</t>
-  </si>
-  <si>
-    <t>9334 CARDS (10X6 WHITE (2898))</t>
-  </si>
-  <si>
-    <t>9335 CARDS (9003 OLD) (9*5 WHITE)</t>
-  </si>
-  <si>
-    <t>9336 CARDS (Design Change) (2884)</t>
-  </si>
-  <si>
-    <t>9337 CARDS (DC) (1635 AP)</t>
-  </si>
-  <si>
-    <t>9338 CARDS (1637 AP)</t>
-  </si>
-  <si>
-    <t>9339 CARDS (5361)</t>
-  </si>
-  <si>
-    <t>9340 CARDS (5658)</t>
-  </si>
-  <si>
-    <t>9341 CARDS (5497)</t>
-  </si>
-  <si>
-    <t>9342 CARDS (2861)</t>
-  </si>
-  <si>
-    <t>9343 CARDS (9*5 WHTE GE HEAVY)</t>
-  </si>
-  <si>
-    <t>9344 CARDS (Dcu) (689)</t>
-  </si>
-  <si>
-    <t>9345 CARDS (358 KALYANI)</t>
-  </si>
-  <si>
-    <t>9346 CARDS (359)</t>
-  </si>
-  <si>
-    <t>9347 CARDS (2853)</t>
-  </si>
-  <si>
-    <t>9348 CARDS *-* (डोरी) (S-124)</t>
-  </si>
-  <si>
-    <t>9349 CARDS (W/o Window) (S-120)</t>
-  </si>
-  <si>
-    <t>9350 CARDS *-* (T) (1632)</t>
-  </si>
-  <si>
-    <t>9351 Card - B (1603 B)</t>
-  </si>
-  <si>
-    <t>9351 CARDS *-* (T) -DC (1603)</t>
-  </si>
-  <si>
-    <t>9352 CARDS *-* (T) -DC (1606 AP)</t>
-  </si>
-  <si>
-    <t>9353 CARDS (1618)</t>
-  </si>
-  <si>
-    <t>9354 CARDS (DCU) (345)</t>
-  </si>
-  <si>
-    <t>9355 CARDS (1624)</t>
-  </si>
-  <si>
-    <t>9356 CARDS (2895/2897)</t>
-  </si>
-  <si>
-    <t>9357 CARDS (2872)</t>
-  </si>
-  <si>
-    <t>9358 CARDS (WHITE PATTA)</t>
-  </si>
-  <si>
-    <t>9359 CARDS (Ri) (PITCH PATTA)</t>
-  </si>
-  <si>
-    <t>9360 CARDS *-* (M) Mil Jayega (GOL ANDA)</t>
-  </si>
-  <si>
-    <t>9361 CARDS (25426)</t>
-  </si>
-  <si>
-    <t>9362 CARDS (363)</t>
-  </si>
-  <si>
-    <t>9363 CARDS *-* (T) (1652)</t>
-  </si>
-  <si>
-    <t>9364 CARDS *-* (T) (1612)</t>
-  </si>
-  <si>
-    <t>9365 CARDS (25429)</t>
-  </si>
-  <si>
-    <t>9366 CARDS (25427 GOLDEN)</t>
-  </si>
-  <si>
-    <t>9367 CARDS (5652)</t>
-  </si>
-  <si>
-    <t>9368 CARDS (9*5 SET 25/26 GOLDEN (25425))</t>
-  </si>
-  <si>
-    <t>9369 CARDS (9*5 SET 25/26 YELLOW (25424))</t>
-  </si>
-  <si>
-    <t>9370 CARDS (9*5 SET 25/26 RED (25423))</t>
-  </si>
-  <si>
-    <t>9371 CARDS (3111 VP)</t>
-  </si>
-  <si>
-    <t>9372 CARDS (9*5 YLW SET (2841))</t>
-  </si>
-  <si>
-    <t>9373 CARDS (1482)</t>
-  </si>
-  <si>
-    <t>9374 CARDS (1485)</t>
-  </si>
-  <si>
-    <t>9375 CARDS (1452 WHITE)</t>
-  </si>
-  <si>
-    <t>9376 CARDS (1529 PRINCE)</t>
-  </si>
-  <si>
-    <t>9377 CARDS (DCU) (9*5 SET GREEN (009))</t>
-  </si>
-  <si>
-    <t>9378 CARDS (2892)</t>
+    <t>9231 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9232 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9233 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9234 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9235 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9236 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9237 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9238 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9239 CARDS</t>
+  </si>
+  <si>
+    <t>9240 CARDS</t>
+  </si>
+  <si>
+    <t>9241 CARDS</t>
+  </si>
+  <si>
+    <t>9242 CARDS</t>
+  </si>
+  <si>
+    <t>9243 CARDS</t>
+  </si>
+  <si>
+    <t>9244 CARDS</t>
+  </si>
+  <si>
+    <t>9301 CARDS</t>
+  </si>
+  <si>
+    <t>9302 CARDS</t>
+  </si>
+  <si>
+    <t>9303 CARDS</t>
+  </si>
+  <si>
+    <t>9304 CARDS</t>
+  </si>
+  <si>
+    <t>9305 CARDS (9070)</t>
+  </si>
+  <si>
+    <t>9306 CARDS</t>
+  </si>
+  <si>
+    <t>9307 CARDS *-* (M)</t>
+  </si>
+  <si>
+    <t>9308 CARDS</t>
+  </si>
+  <si>
+    <t>9309 CARD - B  (DESIGN CHNG)</t>
+  </si>
+  <si>
+    <t>9309 CARDS *-* (T) (Dc)</t>
+  </si>
+  <si>
+    <t>9310 CARDS</t>
+  </si>
+  <si>
+    <t>9311 CARDS</t>
+  </si>
+  <si>
+    <t>9312 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9313 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9314 CARDS</t>
+  </si>
+  <si>
+    <t>9315 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9316 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9317 CARDS</t>
+  </si>
+  <si>
+    <t>9318 CARDS</t>
+  </si>
+  <si>
+    <t>9319 CARDS</t>
+  </si>
+  <si>
+    <t>9320 CARDS</t>
+  </si>
+  <si>
+    <t>9321 CARDS - (DC)</t>
+  </si>
+  <si>
+    <t>9322 CARDS *-* (M) - DC</t>
+  </si>
+  <si>
+    <t>9323 CARDS (9005 OLD)</t>
+  </si>
+  <si>
+    <t>9324 CARDS</t>
+  </si>
+  <si>
+    <t>9325 CARDS</t>
+  </si>
+  <si>
+    <t>9326 CARDS</t>
+  </si>
+  <si>
+    <t>9327 CARDS</t>
+  </si>
+  <si>
+    <t>9328 CARDS</t>
+  </si>
+  <si>
+    <t>9329 CARDS</t>
+  </si>
+  <si>
+    <t>9330 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9331 CARDS *-*  (T)</t>
+  </si>
+  <si>
+    <t>9332 CARDS-DC</t>
+  </si>
+  <si>
+    <t>9333 CARDS</t>
+  </si>
+  <si>
+    <t>9334 CARDS</t>
+  </si>
+  <si>
+    <t>9335 CARDS (9003 OLD)</t>
+  </si>
+  <si>
+    <t>9336 CARDS (Design Change)</t>
+  </si>
+  <si>
+    <t>9337 CARDS (DC)</t>
+  </si>
+  <si>
+    <t>9338 CARDS</t>
+  </si>
+  <si>
+    <t>9339 CARDS</t>
+  </si>
+  <si>
+    <t>9340 CARDS</t>
+  </si>
+  <si>
+    <t>9341 CARDS</t>
+  </si>
+  <si>
+    <t>9342 CARDS</t>
+  </si>
+  <si>
+    <t>9343 CARDS</t>
+  </si>
+  <si>
+    <t>9344 CARDS (Dcu)</t>
+  </si>
+  <si>
+    <t>9345 CARDS</t>
+  </si>
+  <si>
+    <t>9346 CARDS</t>
+  </si>
+  <si>
+    <t>9347 CARDS</t>
+  </si>
+  <si>
+    <t>9348 CARDS *-* (डोरी) 3000 EXTRA WAPAS JAYEGAB</t>
+  </si>
+  <si>
+    <t>9349 CARDS (W/o Window)</t>
+  </si>
+  <si>
+    <t>9350 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9351 Card - B</t>
+  </si>
+  <si>
+    <t>9351 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9352 CARDS *-* (T) -DC</t>
+  </si>
+  <si>
+    <t>9353 CARDS</t>
+  </si>
+  <si>
+    <t>9354 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9355 CARDS</t>
+  </si>
+  <si>
+    <t>9356 CARDS</t>
+  </si>
+  <si>
+    <t>9357 CARDS</t>
+  </si>
+  <si>
+    <t>9358 CARDS</t>
+  </si>
+  <si>
+    <t>9359 CARDS (Ri)</t>
+  </si>
+  <si>
+    <t>9360 CARDS *-* (M) Mil Jayega</t>
+  </si>
+  <si>
+    <t>9361 CARDS</t>
+  </si>
+  <si>
+    <t>9362 CARDS</t>
+  </si>
+  <si>
+    <t>9363 CARDS *-* (T)</t>
+  </si>
+  <si>
+    <t>9364 CARDS *-* (T)  06.02.26 1700PCS</t>
+  </si>
+  <si>
+    <t>9365 CARDS</t>
+  </si>
+  <si>
+    <t>9366 CARDS</t>
+  </si>
+  <si>
+    <t>9367 CARDS</t>
+  </si>
+  <si>
+    <t>9368 CARDS</t>
+  </si>
+  <si>
+    <t>9369 CARDS</t>
+  </si>
+  <si>
+    <t>9370 CARDS</t>
+  </si>
+  <si>
+    <t>9371 CARDS</t>
+  </si>
+  <si>
+    <t>9372 CARDS</t>
+  </si>
+  <si>
+    <t>9373 CARDS</t>
+  </si>
+  <si>
+    <t>9374 CARDS</t>
+  </si>
+  <si>
+    <t>9375 CARDS</t>
+  </si>
+  <si>
+    <t>9376 CARDS</t>
+  </si>
+  <si>
+    <t>9377 CARDS (DCU)</t>
+  </si>
+  <si>
+    <t>9378 CARDS</t>
   </si>
   <si>
     <t>9379 CARDS - R</t>
@@ -2144,19 +2144,19 @@
     <t>9388 CARDS (DCU)</t>
   </si>
   <si>
-    <t>9389 CARDS (9147 RJ)</t>
-  </si>
-  <si>
-    <t>9390 CARDS (DCU) (118KBC)</t>
+    <t>9389 CARDS</t>
+  </si>
+  <si>
+    <t>9390 CARDS (DCU)</t>
   </si>
   <si>
     <t>9391 CARDS</t>
   </si>
   <si>
-    <t>9*4 ENVELOPE (SBC) (CHOTA ENVELOPE (60/40 BILL))</t>
-  </si>
-  <si>
-    <t>9*5 ENVELOPE (FOIL) SBC (BADA ENVLP WITH FOIL (60/40 BILL))</t>
+    <t>9*4 ENVELOPE (SBC)</t>
+  </si>
+  <si>
+    <t>9*5 ENVELOPE (FOIL) SBC</t>
   </si>
   <si>
     <t>ACRYLIC NAME PLATE</t>
@@ -2186,7 +2186,7 @@
     <t>DEV SAMPLE SET</t>
   </si>
   <si>
-    <t>FANCY GIFT ENVELOPE-(SR) (SR ENVELOPES)</t>
+    <t>FANCY GIFT ENVELOPE-(SR)</t>
   </si>
   <si>
     <t>FANCY SAMPLE SET</t>
@@ -2210,37 +2210,37 @@
     <t>RIBBON (रिबीन)</t>
   </si>
   <si>
-    <t>RX-01 ENVELOPE (DC) (LX01)</t>
-  </si>
-  <si>
-    <t>RX-02 ENVELOPE (DC) (LX02)</t>
-  </si>
-  <si>
-    <t>RX-03 ENVELOPE (LX03)</t>
-  </si>
-  <si>
-    <t>RX-04 ENVELOPE (DC) (LX04)</t>
-  </si>
-  <si>
-    <t>RX-05 ENVELOPE (DC) (LX05)</t>
-  </si>
-  <si>
-    <t>RX-06 ENVELOPE (LX06)</t>
-  </si>
-  <si>
-    <t>RX-07 ENVELOPE (DC) (LX07)</t>
-  </si>
-  <si>
-    <t>RX-08 ENVELOPE (DC) (LX08)</t>
-  </si>
-  <si>
-    <t>RX-09 ENVELOPE (DC) (LX09)</t>
+    <t>RX-01 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-02 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-03 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-04 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-05 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-06 ENVELOPE</t>
+  </si>
+  <si>
+    <t>RX-07 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-08 ENVELOPE (DC)</t>
+  </si>
+  <si>
+    <t>RX-09 ENVELOPE (DC)</t>
   </si>
   <si>
     <t>SR ENVELOPE- (100)</t>
   </si>
   <si>
-    <t>गोल गणेश / गोल फ्लावर (GOL GANESH OR GOL FLOWER)</t>
+    <t>गोल गणेश / गोल फ्लावर</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2770,7 +2770,7 @@
   <dimension ref="A1:E737"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="25">
-        <v>29.5</v>
+        <v>155.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>53.1</v>
+        <v>279.89999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C15" s="25">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2997,13 +2997,13 @@
         <v>45</v>
       </c>
       <c r="C17" s="25">
-        <v>133</v>
+        <v>283</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>279.3</v>
+        <v>594.29999999999995</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3126,9 +3126,15 @@
       <c r="B25" s="24">
         <v>46</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="28"/>
+      <c r="C25" s="25">
+        <v>60</v>
+      </c>
+      <c r="D25" s="26">
+        <v>1.65</v>
+      </c>
+      <c r="E25" s="27">
+        <v>99</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
@@ -3186,16 +3192,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="25">
-        <v>33.5</v>
+        <v>31</v>
       </c>
       <c r="D29" s="26">
         <v>2.6</v>
       </c>
       <c r="E29" s="27">
-        <v>87.1</v>
+        <v>80.599999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3203,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C30" s="25">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>69.02</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3226,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="25">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>102.6</v>
+        <v>74.099999999999994</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3299,16 +3305,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" s="25">
-        <v>46.5</v>
+        <v>118.5</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>106.95</v>
+        <v>272.55</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3384,16 +3390,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="25">
-        <v>62.5</v>
+        <v>59.5</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>133.75</v>
+        <v>127.33</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3438,13 +3444,13 @@
         <v>33</v>
       </c>
       <c r="C44" s="25">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D44" s="26">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="E44" s="27">
-        <v>29.77</v>
+        <v>134.78</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" s="25">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>139.65</v>
+        <v>135.84</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3520,16 +3526,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49" s="25">
-        <v>258.5</v>
+        <v>255</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>361.9</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,16 +3577,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52" s="25">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>117.5</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3690,16 +3696,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C59" s="25">
-        <v>7.75</v>
+        <v>64.75</v>
       </c>
       <c r="D59" s="26">
         <v>1.9</v>
       </c>
       <c r="E59" s="27">
-        <v>14.73</v>
+        <v>123.03</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,16 +3713,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C60" s="25">
-        <v>936.5</v>
+        <v>932.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1065.3399999999999</v>
+        <v>1060.79</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C61" s="25">
-        <v>1028.5</v>
+        <v>1024.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1171.81</v>
+        <v>1167.25</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,16 +3764,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C63" s="25">
-        <v>60.5</v>
+        <v>53</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>99.83</v>
+        <v>87.45</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3786,16 +3792,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C65" s="25">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>524.70000000000005</v>
+        <v>513.15</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3848,16 +3854,16 @@
         <v>71</v>
       </c>
       <c r="B69" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C69" s="25">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D69" s="26">
         <v>1.65</v>
       </c>
       <c r="E69" s="27">
-        <v>234.3</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3871,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="25">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>557.20000000000005</v>
+        <v>554.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3888,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C71" s="25">
-        <v>45.5</v>
+        <v>22.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>63.7</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3916,16 +3922,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C73" s="25">
-        <v>546.5</v>
+        <v>540</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>765.1</v>
+        <v>756</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,16 +3939,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C74" s="25">
-        <v>186.5</v>
+        <v>168.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>223.8</v>
+        <v>202.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3950,16 +3956,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C75" s="25">
-        <v>83.5</v>
+        <v>57</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>100.2</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,16 +3973,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="25">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>530.4</v>
+        <v>525.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +4007,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C78" s="25">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>433.2</v>
+        <v>397.2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,16 +4160,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C87" s="25">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1339.6</v>
+        <v>1319.2</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4325,16 +4331,16 @@
         <v>100</v>
       </c>
       <c r="B98" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" s="25">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D98" s="26">
         <v>1.65</v>
       </c>
       <c r="E98" s="27">
-        <v>214.5</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4342,16 +4348,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C99" s="25">
-        <v>419.5</v>
+        <v>409.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>692.18</v>
+        <v>675.68</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4438,16 +4444,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C105" s="25">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>817.5</v>
+        <v>807.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4472,16 +4478,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C107" s="25">
-        <v>325.5</v>
+        <v>317.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>813.75</v>
+        <v>793.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4595,10 +4601,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C116" s="25">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4816,16 +4822,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C133" s="25">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>162.5</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4867,16 +4873,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C136" s="25">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>50</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4904,13 +4910,13 @@
         <v>8</v>
       </c>
       <c r="C138" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D138" s="26">
         <v>12.5</v>
       </c>
       <c r="E138" s="27">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5290,16 +5296,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C161" s="25">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="D161" s="26">
         <v>11.5</v>
       </c>
       <c r="E161" s="27">
-        <v>-11.5</v>
+        <v>-80.5</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5437,16 +5443,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C170" s="25">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="D170" s="26">
         <v>0.88</v>
       </c>
       <c r="E170" s="27">
-        <v>142.15</v>
+        <v>115.66</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5557,16 +5563,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C178" s="25">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>132.30000000000001</v>
+        <v>364.5</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5761,13 +5767,13 @@
         <v>71</v>
       </c>
       <c r="C191" s="25">
-        <v>87.81</v>
+        <v>197.81</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>232.7</v>
+        <v>524.20000000000005</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5950,16 +5956,16 @@
         <v>205</v>
       </c>
       <c r="B203" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C203" s="25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D203" s="26">
         <v>4.5</v>
       </c>
       <c r="E203" s="27">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -6004,13 +6010,13 @@
         <v>35</v>
       </c>
       <c r="C206" s="25">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>72.900000000000006</v>
+        <v>461.7</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6018,16 +6024,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C207" s="25">
-        <v>37.5</v>
+        <v>35.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>97.5</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6052,16 +6058,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C209" s="25">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6103,16 +6109,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C212" s="25">
-        <v>272.5</v>
+        <v>271.5</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1071.25</v>
+        <v>1067.32</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6137,16 +6143,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C214" s="25">
-        <v>316.5</v>
+        <v>409.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>854.55</v>
+        <v>1105.6500000000001</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6157,13 +6163,13 @@
         <v>90</v>
       </c>
       <c r="C215" s="25">
-        <v>103.5</v>
+        <v>205.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>279.45</v>
+        <v>554.85</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6239,16 +6245,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C220" s="25">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D220" s="26">
         <v>3.93</v>
       </c>
       <c r="E220" s="27">
-        <v>719.04</v>
+        <v>699.39</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6256,16 +6262,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C221" s="25">
-        <v>107.75</v>
+        <v>104.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>350.19</v>
+        <v>338.81</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6273,16 +6279,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C222" s="25">
-        <v>99.5</v>
+        <v>96.5</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>362.21</v>
+        <v>351.29</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6426,16 +6432,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C231" s="25">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>140</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6454,16 +6460,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C233" s="25">
-        <v>80.88</v>
+        <v>77.38</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>262.86</v>
+        <v>251.49</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6647,16 +6653,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C246" s="25">
-        <v>48.9</v>
+        <v>94.9</v>
       </c>
       <c r="D246" s="26">
         <v>6.3</v>
       </c>
       <c r="E246" s="27">
-        <v>308.07</v>
+        <v>597.87</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6667,13 +6673,13 @@
         <v>69</v>
       </c>
       <c r="C247" s="25">
-        <v>58.5</v>
+        <v>153.5</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>175.5</v>
+        <v>460.5</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6715,16 +6721,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C250" s="25">
-        <v>181</v>
+        <v>176.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>705.9</v>
+        <v>688.35</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6811,16 +6817,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C256" s="25">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="D256" s="26">
         <v>4.25</v>
       </c>
       <c r="E256" s="27">
-        <v>48.88</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -7008,16 +7014,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C269" s="25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>27.9</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7053,16 +7059,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C272" s="25">
-        <v>32.5</v>
+        <v>23.5</v>
       </c>
       <c r="D272" s="26">
         <v>6.25</v>
       </c>
       <c r="E272" s="27">
-        <v>203.13</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7562,16 +7568,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C303" s="25">
-        <v>252.25</v>
+        <v>248.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1084.1500000000001</v>
+        <v>1066.96</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7613,16 +7619,16 @@
         <v>308</v>
       </c>
       <c r="B306" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C306" s="25">
-        <v>38.5</v>
+        <v>69</v>
       </c>
       <c r="D306" s="26">
         <v>5.13</v>
       </c>
       <c r="E306" s="27">
-        <v>197.51</v>
+        <v>353.97</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7739,16 +7745,16 @@
         <v>316</v>
       </c>
       <c r="B314" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C314" s="25">
-        <v>45.95</v>
+        <v>43.95</v>
       </c>
       <c r="D314" s="26">
         <v>9.4499999999999993</v>
       </c>
       <c r="E314" s="27">
-        <v>434.23</v>
+        <v>415.33</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -7942,16 +7948,16 @@
         <v>329</v>
       </c>
       <c r="B327" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C327" s="25">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="D327" s="26">
         <v>10</v>
       </c>
       <c r="E327" s="27">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -8121,16 +8127,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C338" s="25">
-        <v>31.5</v>
+        <v>30.5</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>283.5</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8328,16 +8334,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C351" s="25">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>368.28</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8558,16 +8564,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C365" s="25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>83.16</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8813,16 +8819,16 @@
         <v>382</v>
       </c>
       <c r="B380" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C380" s="25">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="D380" s="26">
         <v>9.5</v>
       </c>
       <c r="E380" s="27">
-        <v>185.25</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8847,16 +8853,16 @@
         <v>384</v>
       </c>
       <c r="B382" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C382" s="25">
-        <v>21.5</v>
+        <v>1.5</v>
       </c>
       <c r="D382" s="26">
         <v>6</v>
       </c>
       <c r="E382" s="27">
-        <v>129</v>
+        <v>9</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -9097,13 +9103,13 @@
         <v>42</v>
       </c>
       <c r="C397" s="25">
-        <v>5.5</v>
+        <v>41.5</v>
       </c>
       <c r="D397" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E397" s="27">
-        <v>47.03</v>
+        <v>354.83</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -9111,16 +9117,16 @@
         <v>400</v>
       </c>
       <c r="B398" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C398" s="25">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D398" s="26">
         <v>6.65</v>
       </c>
       <c r="E398" s="27">
-        <v>83.13</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -9272,16 +9278,16 @@
         <v>411</v>
       </c>
       <c r="B409" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C409" s="25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D409" s="26">
         <v>7.13</v>
       </c>
       <c r="E409" s="27">
-        <v>142.6</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -9337,13 +9343,13 @@
         <v>82</v>
       </c>
       <c r="C413" s="25">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>325</v>
+        <v>322.39999999999998</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9798,16 +9804,16 @@
         <v>445</v>
       </c>
       <c r="B443" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C443" s="25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D443" s="26">
         <v>9.75</v>
       </c>
       <c r="E443" s="27">
-        <v>117</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -9973,16 +9979,16 @@
         <v>456</v>
       </c>
       <c r="B454" s="24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C454" s="25">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D454" s="26">
         <v>9.75</v>
       </c>
       <c r="E454" s="27">
-        <v>48.75</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10291,11 +10297,17 @@
         <v>476</v>
       </c>
       <c r="B474" s="24">
-        <v>14</v>
-      </c>
-      <c r="C474" s="28"/>
-      <c r="D474" s="29"/>
-      <c r="E474" s="28"/>
+        <v>13</v>
+      </c>
+      <c r="C474" s="25">
+        <v>7</v>
+      </c>
+      <c r="D474" s="26">
+        <v>10</v>
+      </c>
+      <c r="E474" s="27">
+        <v>70</v>
+      </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="23" t="s">
@@ -10772,16 +10784,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C505" s="25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="D505" s="26">
         <v>18.5</v>
       </c>
       <c r="E505" s="27">
-        <v>249.75</v>
+        <v>231.25</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11130,16 +11142,16 @@
         <v>529</v>
       </c>
       <c r="B527" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C527" s="25">
-        <v>59.5</v>
+        <v>29.5</v>
       </c>
       <c r="D527" s="26">
         <v>1.4</v>
       </c>
       <c r="E527" s="27">
-        <v>83.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11198,16 +11210,16 @@
         <v>533</v>
       </c>
       <c r="B531" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C531" s="25">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D531" s="26">
         <v>2</v>
       </c>
       <c r="E531" s="27">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -11215,16 +11227,16 @@
         <v>534</v>
       </c>
       <c r="B532" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C532" s="25">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D532" s="26">
         <v>2.1</v>
       </c>
       <c r="E532" s="27">
-        <v>94.5</v>
+        <v>92.4</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -11235,13 +11247,13 @@
         <v>29</v>
       </c>
       <c r="C533" s="25">
-        <v>12.5</v>
+        <v>74.5</v>
       </c>
       <c r="D533" s="26">
         <v>3</v>
       </c>
       <c r="E533" s="27">
-        <v>37.5</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11381,16 +11393,16 @@
         <v>544</v>
       </c>
       <c r="B542" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C542" s="25">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="D542" s="26">
         <v>2</v>
       </c>
       <c r="E542" s="27">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11415,16 +11427,16 @@
         <v>546</v>
       </c>
       <c r="B544" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C544" s="25">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D544" s="26">
         <v>4.28</v>
       </c>
       <c r="E544" s="27">
-        <v>72.760000000000005</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11568,16 +11580,16 @@
         <v>555</v>
       </c>
       <c r="B553" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C553" s="25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D553" s="26">
         <v>3.1</v>
       </c>
       <c r="E553" s="27">
-        <v>68.2</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11653,16 +11665,16 @@
         <v>560</v>
       </c>
       <c r="B558" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C558" s="25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D558" s="26">
         <v>1.8</v>
       </c>
       <c r="E558" s="27">
-        <v>12.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -11755,16 +11767,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C564" s="25">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="D564" s="26">
         <v>3.14</v>
       </c>
       <c r="E564" s="27">
-        <v>92</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11775,13 +11787,13 @@
         <v>25</v>
       </c>
       <c r="C565" s="25">
-        <v>72.25</v>
+        <v>74.25</v>
       </c>
       <c r="D565" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E565" s="27">
-        <v>166.18</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11825,9 +11837,15 @@
       <c r="B568" s="24">
         <v>60</v>
       </c>
-      <c r="C568" s="28"/>
-      <c r="D568" s="29"/>
-      <c r="E568" s="28"/>
+      <c r="C568" s="25">
+        <v>48</v>
+      </c>
+      <c r="D568" s="26">
+        <v>3.5</v>
+      </c>
+      <c r="E568" s="27">
+        <v>168</v>
+      </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="23" t="s">
@@ -11868,16 +11886,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C571" s="25">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="D571" s="26">
         <v>2.14</v>
       </c>
       <c r="E571" s="27">
-        <v>31.03</v>
+        <v>28.89</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11885,16 +11903,16 @@
         <v>574</v>
       </c>
       <c r="B572" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C572" s="25">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="D572" s="26">
         <v>2.66</v>
       </c>
       <c r="E572" s="27">
-        <v>46.55</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -12004,16 +12022,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C579" s="25">
-        <v>86.5</v>
+        <v>83.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>121.1</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12021,16 +12039,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C580" s="25">
-        <v>89</v>
+        <v>84.5</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>160.19999999999999</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12162,10 +12180,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C589" s="25">
-        <v>269.5</v>
+        <v>266.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12244,16 +12262,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C595" s="25">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>408.9</v>
+        <v>406.58</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12261,16 +12279,16 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C596" s="25">
-        <v>431.5</v>
+        <v>430</v>
       </c>
       <c r="D596" s="26">
         <v>0.85</v>
       </c>
       <c r="E596" s="27">
-        <v>366.78</v>
+        <v>365.5</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -12289,16 +12307,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C598" s="25">
-        <v>147.5</v>
+        <v>137.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>125.38</v>
+        <v>116.88</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12602,16 +12620,16 @@
         <v>621</v>
       </c>
       <c r="B619" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C619" s="25">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="D619" s="26">
         <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>107.25</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12704,16 +12722,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C625" s="25">
-        <v>22.85</v>
+        <v>21.35</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>91.4</v>
+        <v>85.4</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12755,16 +12773,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C628" s="25">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D628" s="26">
         <v>2.77</v>
       </c>
       <c r="E628" s="27">
-        <v>193.91</v>
+        <v>191.14</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12826,13 +12844,13 @@
         <v>44</v>
       </c>
       <c r="C632" s="25">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12857,16 +12875,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C634" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D634" s="26">
         <v>1.5</v>
       </c>
       <c r="E634" s="27">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -12908,16 +12926,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C637" s="25">
-        <v>155.5</v>
+        <v>151.5</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>354.54</v>
+        <v>345.42</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13106,16 +13124,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C649" s="25">
-        <v>222.86</v>
+        <v>172.86</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>378.86</v>
+        <v>293.86</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13228,13 +13246,13 @@
         <v>142</v>
       </c>
       <c r="C656" s="25">
-        <v>81.5</v>
+        <v>168.5</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>232.28</v>
+        <v>480.23</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13307,13 +13325,13 @@
         <v>39</v>
       </c>
       <c r="C661" s="25">
-        <v>18.5</v>
+        <v>43.5</v>
       </c>
       <c r="D661" s="26">
         <v>3.1</v>
       </c>
       <c r="E661" s="27">
-        <v>57.35</v>
+        <v>134.85</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -13355,16 +13373,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C664" s="25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>50.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13474,16 +13492,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C671" s="25">
-        <v>148.5</v>
+        <v>164.5</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>460.35</v>
+        <v>509.95</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13494,13 +13512,13 @@
         <v>47</v>
       </c>
       <c r="C672" s="25">
-        <v>20.93</v>
+        <v>57.43</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>75.349999999999994</v>
+        <v>206.75</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13931,10 +13949,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C700" s="25">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13944,10 +13962,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C701" s="25">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -14157,16 +14175,16 @@
         <v>720</v>
       </c>
       <c r="B718" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C718" s="25">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D718" s="26">
         <v>1.6</v>
       </c>
       <c r="E718" s="27">
-        <v>81.599999999999994</v>
+        <v>78.400000000000006</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
@@ -14196,16 +14214,16 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C721" s="25">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="D721" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E721" s="27">
-        <v>121.8</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -14250,10 +14268,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C725" s="25">
-        <v>-91.15</v>
+        <v>-92.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14291,16 +14309,16 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C728" s="25">
-        <v>114.5</v>
+        <v>84.5</v>
       </c>
       <c r="D728" s="26">
         <v>2.5</v>
       </c>
       <c r="E728" s="27">
-        <v>286.25</v>
+        <v>211.25</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -14325,16 +14343,16 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C730" s="25">
-        <v>18.25</v>
+        <v>13.25</v>
       </c>
       <c r="D730" s="26">
         <v>2.5</v>
       </c>
       <c r="E730" s="27">
-        <v>45.63</v>
+        <v>33.130000000000003</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -14342,16 +14360,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C731" s="25">
-        <v>68.25</v>
+        <v>63.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>170.63</v>
+        <v>158.13</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14393,16 +14411,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C734" s="25">
-        <v>39.25</v>
+        <v>19.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>98.13</v>
+        <v>48.13</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14435,11 +14453,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44223.54</v>
+        <v>45202.54</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>106031.35</v>
+        <v>109411.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 31-Mar-26</t>
+    <t>1-Jul-25 to 3-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -77,7 +77,7 @@
     <t>1004 PATRIKA</t>
   </si>
   <si>
-    <t>1005 PATRIKA</t>
+    <t>1005 PATRIKA (12000 09.03)</t>
   </si>
   <si>
     <t>1006 PATRIKA</t>
@@ -137,10 +137,10 @@
     <t>1023 PATRIKA</t>
   </si>
   <si>
-    <t>1024 PATRIKA</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA</t>
+    <t>1024 PATRIKA (10k 05.03)</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA (6000 09.03)</t>
   </si>
   <si>
     <t>1026 PATRIKA (JC)</t>
@@ -485,7 +485,7 @@
     <t>2120 PATRIKA (L) (DCU)</t>
   </si>
   <si>
-    <t>2121 PATRIKA</t>
+    <t>2121 PATRIKA (DC)</t>
   </si>
   <si>
     <t>2122 PATRIKA</t>
@@ -566,7 +566,7 @@
     <t>4253 PATRIKA</t>
   </si>
   <si>
-    <t>4254 PATRIKA (4210)</t>
+    <t>4254 PATRIKA (4210) (4500 05.03)</t>
   </si>
   <si>
     <t>4255 PATRIKA - B (DCU)</t>
@@ -701,7 +701,7 @@
     <t>4296 PATRIKA</t>
   </si>
   <si>
-    <t>4297 PATRIKA</t>
+    <t>4297 PATRIKA (9600 05.03)</t>
   </si>
   <si>
     <t>4298 PATRIKA</t>
@@ -824,7 +824,7 @@
     <t>5071 PATRIKA *-* (डोरी)</t>
   </si>
   <si>
-    <t>5072 PATRIKA</t>
+    <t>5072 PATRIKA (09.03 200)</t>
   </si>
   <si>
     <t>5073 PATRIKA *-* (M)</t>
@@ -839,7 +839,7 @@
     <t>5076 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5077 PATRIKA</t>
+    <t>5077 PATRIKA (1000-1500 11.03)</t>
   </si>
   <si>
     <t>5078 PATRIKA (DCU)</t>
@@ -884,7 +884,7 @@
     <t>5092 PATRIKA</t>
   </si>
   <si>
-    <t>5093 PATRIKA</t>
+    <t>5093 PATRIKA (09.03 400)</t>
   </si>
   <si>
     <t>5094 PATRIKA</t>
@@ -914,7 +914,7 @@
     <t>5103 PATRIKA</t>
   </si>
   <si>
-    <t>5104 PATRIKA</t>
+    <t>5104 PATRIKA (09.03 1200)</t>
   </si>
   <si>
     <t>5105 PATRIKA (JC)</t>
@@ -941,7 +941,7 @@
     <t>5112 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5113 PATRIKA</t>
+    <t>5113 PATRIKA (09.03 3700)</t>
   </si>
   <si>
     <t>5114 PATRIKA *-* (डोरी)</t>
@@ -1007,7 +1007,7 @@
     <t>5516 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi) 2400 09.03</t>
   </si>
   <si>
     <t>5518 PATRIKA (JC) *-* (M)</t>
@@ -1178,7 +1178,7 @@
     <t>5573 PATRIKA</t>
   </si>
   <si>
-    <t>5574 PATRIKA 8/MARCH</t>
+    <t>5574 PATRIKA (09.03 4000)</t>
   </si>
   <si>
     <t>5575 PATRIKA *-* (M)</t>
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="25">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>329.55</v>
+        <v>319.8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2926,16 +2926,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="25">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>276.89999999999998</v>
+        <v>267.14999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="25">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>306</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="25">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" s="25">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>54.74</v>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3243,16 +3243,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="25">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>103.6</v>
+        <v>89.6</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,13 +3308,13 @@
         <v>44</v>
       </c>
       <c r="C36" s="25">
-        <v>118.5</v>
+        <v>117.5</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>272.55</v>
+        <v>270.25</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3373,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" s="25">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>102.72</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,10 +3447,10 @@
         <v>50</v>
       </c>
       <c r="D44" s="26">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="E44" s="27">
-        <v>134.78</v>
+        <v>136.94</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C47" s="25">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>135.84</v>
+        <v>130.76</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3764,16 +3764,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" s="25">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>87.45</v>
+        <v>84.15</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3792,16 +3792,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C65" s="25">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>513.15</v>
+        <v>496.65</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3854,16 +3854,16 @@
         <v>71</v>
       </c>
       <c r="B69" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="25">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D69" s="26">
         <v>1.65</v>
       </c>
       <c r="E69" s="27">
-        <v>217.8</v>
+        <v>234.3</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3956,16 +3956,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C75" s="25">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>68.400000000000006</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,16 +4109,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C84" s="25">
-        <v>1472.5</v>
+        <v>1469.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1914.25</v>
+        <v>1910.35</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,16 +4211,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C90" s="25">
-        <v>328.7</v>
+        <v>326.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>421.62</v>
+        <v>419.05</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4331,16 +4331,16 @@
         <v>100</v>
       </c>
       <c r="B98" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="25">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D98" s="26">
         <v>1.65</v>
       </c>
       <c r="E98" s="27">
-        <v>198</v>
+        <v>214.5</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4348,16 +4348,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C99" s="25">
-        <v>409.5</v>
+        <v>419.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>675.68</v>
+        <v>692.18</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4395,16 +4395,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C102" s="25">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>244.34</v>
+        <v>241.77</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4444,16 +4444,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C105" s="25">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>807.5</v>
+        <v>797.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4604,7 +4604,7 @@
         <v>8</v>
       </c>
       <c r="C116" s="25">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4617,7 +4617,7 @@
         <v>6</v>
       </c>
       <c r="C117" s="25">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4670,10 +4670,10 @@
         <v>123</v>
       </c>
       <c r="B121" s="24">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C121" s="25">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D121" s="29"/>
       <c r="E121" s="28"/>
@@ -4716,10 +4716,10 @@
         <v>127</v>
       </c>
       <c r="B125" s="24">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C125" s="25">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D125" s="29"/>
       <c r="E125" s="28"/>
@@ -5330,16 +5330,16 @@
         <v>165</v>
       </c>
       <c r="B163" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C163" s="25">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D163" s="26">
         <v>11.5</v>
       </c>
       <c r="E163" s="27">
-        <v>17.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,13 +5446,13 @@
         <v>40</v>
       </c>
       <c r="C170" s="25">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="D170" s="26">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>115.66</v>
+        <v>160.84</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5566,13 +5566,13 @@
         <v>24</v>
       </c>
       <c r="C178" s="25">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>364.5</v>
+        <v>172.8</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5764,16 +5764,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C191" s="25">
-        <v>197.81</v>
+        <v>192.81</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>524.20000000000005</v>
+        <v>510.95</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -6010,13 +6010,13 @@
         <v>35</v>
       </c>
       <c r="C206" s="25">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>461.7</v>
+        <v>610.20000000000005</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6075,16 +6075,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C210" s="25">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="D210" s="26">
         <v>3.5</v>
       </c>
       <c r="E210" s="27">
-        <v>180.25</v>
+        <v>176.75</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6146,13 +6146,13 @@
         <v>141</v>
       </c>
       <c r="C214" s="25">
-        <v>409.5</v>
+        <v>358.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>1105.6500000000001</v>
+        <v>967.95</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,16 +6160,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C215" s="25">
-        <v>205.5</v>
+        <v>266</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>554.85</v>
+        <v>718.2</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,16 +6262,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C221" s="25">
-        <v>104.25</v>
+        <v>88.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>338.81</v>
+        <v>286.81</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,16 +6432,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C231" s="25">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>318.5</v>
+        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6477,16 +6477,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C234" s="25">
-        <v>43.5</v>
+        <v>40.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>141.38</v>
+        <v>131.63</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6670,16 +6670,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C247" s="25">
-        <v>153.5</v>
+        <v>171</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>460.5</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6721,16 +6721,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C250" s="25">
-        <v>176.5</v>
+        <v>175.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>688.35</v>
+        <v>684.45</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6738,16 +6738,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C251" s="25">
-        <v>175.5</v>
+        <v>168</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>684.45</v>
+        <v>655.20000000000005</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6817,16 +6817,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C256" s="25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D256" s="26">
         <v>4.25</v>
       </c>
       <c r="E256" s="27">
-        <v>42.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6952,16 +6952,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C265" s="25">
-        <v>316.5</v>
+        <v>313</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1354.62</v>
+        <v>1339.64</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7014,16 +7014,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C269" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>18.600000000000001</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7228,16 +7228,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C283" s="25">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>406.44</v>
+        <v>401.71</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7296,16 +7296,16 @@
         <v>289</v>
       </c>
       <c r="B287" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C287" s="25">
-        <v>133</v>
+        <v>130.5</v>
       </c>
       <c r="D287" s="26">
         <v>5</v>
       </c>
       <c r="E287" s="27">
-        <v>665</v>
+        <v>652.5</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -7381,16 +7381,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C292" s="25">
-        <v>110.5</v>
+        <v>109.5</v>
       </c>
       <c r="D292" s="26">
         <v>4.5</v>
       </c>
       <c r="E292" s="27">
-        <v>497.25</v>
+        <v>492.75</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7415,16 +7415,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C294" s="25">
-        <v>98.5</v>
+        <v>98</v>
       </c>
       <c r="D294" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E294" s="27">
-        <v>481.47</v>
+        <v>479.02</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7500,16 +7500,16 @@
         <v>301</v>
       </c>
       <c r="B299" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C299" s="25">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D299" s="26">
         <v>4.2699999999999996</v>
       </c>
       <c r="E299" s="27">
-        <v>1054.27</v>
+        <v>1037.19</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7948,16 +7948,16 @@
         <v>329</v>
       </c>
       <c r="B327" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C327" s="25">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="D327" s="26">
         <v>10</v>
       </c>
       <c r="E327" s="27">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -8734,16 +8734,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C375" s="25">
-        <v>56.83</v>
+        <v>50.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>255.74</v>
+        <v>228.74</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -9340,16 +9340,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C413" s="25">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>322.39999999999998</v>
+        <v>312</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -10572,16 +10572,16 @@
         <v>493</v>
       </c>
       <c r="B491" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C491" s="25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="D491" s="26">
         <v>10.45</v>
       </c>
       <c r="E491" s="27">
-        <v>125.4</v>
+        <v>120.18</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -10745,16 +10745,16 @@
         <v>504</v>
       </c>
       <c r="B502" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C502" s="25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>123.75</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -11247,13 +11247,13 @@
         <v>29</v>
       </c>
       <c r="C533" s="25">
-        <v>74.5</v>
+        <v>52.5</v>
       </c>
       <c r="D533" s="26">
         <v>3</v>
       </c>
       <c r="E533" s="27">
-        <v>223.5</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11597,16 +11597,16 @@
         <v>556</v>
       </c>
       <c r="B554" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C554" s="25">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D554" s="26">
         <v>9.5</v>
       </c>
       <c r="E554" s="27">
-        <v>180.5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
@@ -11631,16 +11631,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C556" s="25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D556" s="26">
         <v>2.38</v>
       </c>
       <c r="E556" s="27">
-        <v>66.64</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11665,16 +11665,16 @@
         <v>560</v>
       </c>
       <c r="B558" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C558" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D558" s="26">
         <v>1.8</v>
       </c>
       <c r="E558" s="27">
-        <v>10.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -11787,13 +11787,13 @@
         <v>25</v>
       </c>
       <c r="C565" s="25">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="D565" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E565" s="27">
-        <v>170.78</v>
+        <v>173.08</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -12219,10 +12219,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C592" s="25">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12307,16 +12307,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C598" s="25">
-        <v>137.5</v>
+        <v>134.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>116.88</v>
+        <v>114.33</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12620,16 +12620,16 @@
         <v>621</v>
       </c>
       <c r="B619" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C619" s="25">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="D619" s="26">
         <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>79.75</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12722,16 +12722,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C625" s="25">
-        <v>21.35</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>85.4</v>
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12841,16 +12841,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C632" s="25">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12858,16 +12858,16 @@
         <v>635</v>
       </c>
       <c r="B633" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C633" s="25">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="D633" s="26">
         <v>4</v>
       </c>
       <c r="E633" s="27">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -12926,16 +12926,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C637" s="25">
-        <v>151.5</v>
+        <v>147.5</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>345.42</v>
+        <v>336.3</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13127,13 +13127,13 @@
         <v>127</v>
       </c>
       <c r="C649" s="25">
-        <v>172.86</v>
+        <v>180.86</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>293.86</v>
+        <v>307.45999999999998</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13884,10 +13884,10 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C695" s="25">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D695" s="29"/>
       <c r="E695" s="28"/>
@@ -13949,10 +13949,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C700" s="25">
-        <v>32.5</v>
+        <v>27.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14175,16 +14175,16 @@
         <v>720</v>
       </c>
       <c r="B718" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C718" s="25">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D718" s="26">
         <v>1.6</v>
       </c>
       <c r="E718" s="27">
-        <v>78.400000000000006</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
@@ -14214,16 +14214,16 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C721" s="25">
-        <v>70</v>
+        <v>68.5</v>
       </c>
       <c r="D721" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E721" s="27">
-        <v>81.2</v>
+        <v>79.459999999999994</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -14268,10 +14268,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C725" s="25">
-        <v>-92.15</v>
+        <v>-96.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14394,16 +14394,16 @@
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C733" s="25">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="D733" s="26">
         <v>2.5</v>
       </c>
       <c r="E733" s="27">
-        <v>136.25</v>
+        <v>133.75</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -14453,11 +14453,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>45202.54</v>
+        <v>45233.52</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>109411.02</v>
+        <v>108878.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 3-Mar-26</t>
+    <t>1-Jul-25 to 5-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -1934,7 +1934,7 @@
     <t>9319 CARDS</t>
   </si>
   <si>
-    <t>9320 CARDS</t>
+    <t>9320 CARDS (DC)</t>
   </si>
   <si>
     <t>9321 CARDS - (DC)</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="25">
-        <v>155.5</v>
+        <v>153.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>279.89999999999998</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2994,16 +2994,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="25">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>594.29999999999995</v>
+        <v>585.9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" s="25">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>99</v>
+        <v>92.4</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="25">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C28" s="25">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>35.700000000000003</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3226,16 +3226,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="25">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>74.099999999999994</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3271,16 +3271,16 @@
         <v>36</v>
       </c>
       <c r="B34" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="25">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D34" s="26">
         <v>2.5</v>
       </c>
       <c r="E34" s="27">
-        <v>92.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3305,16 +3305,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" s="25">
-        <v>117.5</v>
+        <v>112</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>270.25</v>
+        <v>257.60000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3373,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="25">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>49.22</v>
+        <v>74.900000000000006</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="25">
-        <v>123.5</v>
+        <v>120.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>304.48</v>
+        <v>297.08</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3441,16 +3441,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C44" s="25">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="D44" s="26">
         <v>2.74</v>
       </c>
       <c r="E44" s="27">
-        <v>136.94</v>
+        <v>132.84</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C47" s="25">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>130.76</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3543,16 +3543,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C50" s="25">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>95.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3577,16 +3577,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C52" s="25">
-        <v>43</v>
+        <v>39.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>107.5</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3594,16 +3594,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C53" s="25">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>6.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3662,17 +3662,11 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>27</v>
-      </c>
-      <c r="C57" s="25">
-        <v>1</v>
-      </c>
-      <c r="D57" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E57" s="27">
-        <v>1.9</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C57" s="28"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="28"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
@@ -3713,16 +3707,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C60" s="25">
-        <v>932.5</v>
+        <v>931.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1060.79</v>
+        <v>1059.6600000000001</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3724,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C61" s="25">
-        <v>1024.5</v>
+        <v>1008.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1167.25</v>
+        <v>1149.02</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3809,16 +3803,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C66" s="25">
-        <v>64.5</v>
+        <v>60</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>106.43</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,16 +3882,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C71" s="25">
-        <v>22.5</v>
+        <v>14.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>31.5</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3905,16 +3899,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C72" s="25">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>478.8</v>
+        <v>450.8</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3956,16 +3950,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C75" s="25">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>64.8</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4007,16 +4001,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="25">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>397.2</v>
+        <v>393.6</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C84" s="25">
-        <v>1469.5</v>
+        <v>1464.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1910.35</v>
+        <v>1903.85</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4177,16 +4171,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C88" s="25">
-        <v>1062.5</v>
+        <v>1057.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1806.25</v>
+        <v>1797.75</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C89" s="25">
-        <v>254.5</v>
+        <v>245.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>371.86</v>
+        <v>358.71</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,16 +4205,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C90" s="25">
-        <v>326.7</v>
+        <v>317.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>419.05</v>
+        <v>407.51</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,16 +4222,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C91" s="25">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>78.5</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,16 +4239,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92" s="25">
-        <v>746.5</v>
+        <v>744</v>
       </c>
       <c r="D92" s="26">
         <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>1349.44</v>
+        <v>1344.92</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4286,16 +4280,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C95" s="25">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>373.5</v>
+        <v>369</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4303,16 +4297,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C96" s="25">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>121.5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4395,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102" s="25">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>241.77</v>
+        <v>237.48</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4444,16 +4438,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C105" s="25">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>797.5</v>
+        <v>787.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4478,16 +4472,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C107" s="25">
-        <v>317.5</v>
+        <v>325.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>793.75</v>
+        <v>813.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4525,10 +4519,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C110" s="25">
-        <v>364</v>
+        <v>358.5</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4601,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C116" s="25">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4703,11 +4697,9 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>271</v>
-      </c>
-      <c r="C124" s="25">
-        <v>0.01</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C124" s="28"/>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
     </row>
@@ -4742,10 +4734,10 @@
         <v>129</v>
       </c>
       <c r="B127" s="24">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C127" s="25">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D127" s="29"/>
       <c r="E127" s="28"/>
@@ -4890,16 +4882,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C137" s="25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D137" s="26">
         <v>12.5</v>
       </c>
       <c r="E137" s="27">
-        <v>87.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4990,16 +4982,16 @@
         <v>145</v>
       </c>
       <c r="B143" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C143" s="25">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>83.25</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5330,17 +5322,11 @@
         <v>165</v>
       </c>
       <c r="B163" s="24">
-        <v>18</v>
-      </c>
-      <c r="C163" s="25">
-        <v>1</v>
-      </c>
-      <c r="D163" s="26">
-        <v>11.5</v>
-      </c>
-      <c r="E163" s="27">
-        <v>11.5</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C163" s="28"/>
+      <c r="D163" s="29"/>
+      <c r="E163" s="28"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="23" t="s">
@@ -5443,7 +5429,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C170" s="25">
         <v>181</v>
@@ -5990,16 +5976,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C205" s="25">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D205" s="26">
         <v>3.4</v>
       </c>
       <c r="E205" s="27">
-        <v>248.2</v>
+        <v>214.2</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,16 +5993,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C206" s="25">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>610.20000000000005</v>
+        <v>602.1</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,16 +6129,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C214" s="25">
-        <v>358.5</v>
+        <v>356.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>967.95</v>
+        <v>962.55</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,16 +6248,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C221" s="25">
-        <v>88.25</v>
+        <v>84.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>286.81</v>
+        <v>273.81</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,16 +6282,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C223" s="25">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>103.95</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,16 +6418,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C231" s="25">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>308</v>
+        <v>304.5</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6460,16 +6446,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C233" s="25">
-        <v>77.38</v>
+        <v>73.38</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>251.49</v>
+        <v>238.49</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6477,16 +6463,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C234" s="25">
-        <v>40.5</v>
+        <v>37.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>131.63</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6619,16 +6605,16 @@
         <v>246</v>
       </c>
       <c r="B244" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C244" s="25">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="D244" s="26">
         <v>5.75</v>
       </c>
       <c r="E244" s="27">
-        <v>117.88</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,16 +6639,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C246" s="25">
-        <v>94.9</v>
+        <v>92.9</v>
       </c>
       <c r="D246" s="26">
         <v>6.3</v>
       </c>
       <c r="E246" s="27">
-        <v>597.87</v>
+        <v>585.27</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6670,16 +6656,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C247" s="25">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6704,16 +6690,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C249" s="25">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D249" s="26">
         <v>3.8</v>
       </c>
       <c r="E249" s="27">
-        <v>414.2</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6738,16 +6724,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C251" s="25">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>655.20000000000005</v>
+        <v>643.5</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6935,16 +6921,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C264" s="25">
-        <v>30.5</v>
+        <v>25.5</v>
       </c>
       <c r="D264" s="26">
         <v>6.15</v>
       </c>
       <c r="E264" s="27">
-        <v>187.68</v>
+        <v>156.91</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -6955,13 +6941,13 @@
         <v>220</v>
       </c>
       <c r="C265" s="25">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1339.64</v>
+        <v>1348.2</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7014,16 +7000,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C269" s="25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>15.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7245,16 +7231,16 @@
         <v>286</v>
       </c>
       <c r="B284" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C284" s="25">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D284" s="26">
         <v>6.19</v>
       </c>
       <c r="E284" s="27">
-        <v>414.42</v>
+        <v>389.68</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7330,16 +7316,16 @@
         <v>291</v>
       </c>
       <c r="B289" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C289" s="25">
-        <v>26.25</v>
+        <v>24.75</v>
       </c>
       <c r="D289" s="26">
         <v>5.97</v>
       </c>
       <c r="E289" s="27">
-        <v>156.71</v>
+        <v>147.76</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7466,16 +7452,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C297" s="25">
-        <v>284</v>
+        <v>279.5</v>
       </c>
       <c r="D297" s="26">
-        <v>6.06</v>
+        <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1722.27</v>
+        <v>1695.2</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7568,16 +7554,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C303" s="25">
-        <v>248.25</v>
+        <v>245.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1066.96</v>
+        <v>1054.06</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -8385,16 +8371,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C354" s="25">
-        <v>32.85</v>
+        <v>30.85</v>
       </c>
       <c r="D354" s="26">
         <v>4.75</v>
       </c>
       <c r="E354" s="27">
-        <v>156.04</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8632,16 +8618,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C369" s="25">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="D369" s="26">
         <v>7</v>
       </c>
       <c r="E369" s="27">
-        <v>133</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8649,16 +8635,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C370" s="25">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>660</v>
+        <v>650.1</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8734,16 +8720,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C375" s="25">
-        <v>50.83</v>
+        <v>45.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>228.74</v>
+        <v>206.24</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8819,16 +8805,16 @@
         <v>382</v>
       </c>
       <c r="B380" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C380" s="25">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="D380" s="26">
         <v>9.5</v>
       </c>
       <c r="E380" s="27">
-        <v>161.5</v>
+        <v>137.75</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8938,16 +8924,16 @@
         <v>389</v>
       </c>
       <c r="B387" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C387" s="25">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D387" s="26">
         <v>8</v>
       </c>
       <c r="E387" s="27">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -9017,16 +9003,16 @@
         <v>394</v>
       </c>
       <c r="B392" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C392" s="25">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="D392" s="26">
         <v>3.6</v>
       </c>
       <c r="E392" s="27">
-        <v>37.799999999999997</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -9162,16 +9148,16 @@
         <v>403</v>
       </c>
       <c r="B401" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C401" s="25">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D401" s="26">
         <v>6.4</v>
       </c>
       <c r="E401" s="27">
-        <v>35.200000000000003</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9569,16 +9555,16 @@
         <v>430</v>
       </c>
       <c r="B428" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C428" s="25">
-        <v>28.5</v>
+        <v>24.5</v>
       </c>
       <c r="D428" s="26">
         <v>8.35</v>
       </c>
       <c r="E428" s="27">
-        <v>237.85</v>
+        <v>204.47</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -9821,11 +9807,17 @@
         <v>446</v>
       </c>
       <c r="B444" s="24">
-        <v>4</v>
-      </c>
-      <c r="C444" s="28"/>
-      <c r="D444" s="29"/>
-      <c r="E444" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="C444" s="25">
+        <v>-2</v>
+      </c>
+      <c r="D444" s="26">
+        <v>15.5</v>
+      </c>
+      <c r="E444" s="27">
+        <v>-31</v>
+      </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="23" t="s">
@@ -10171,16 +10163,16 @@
         <v>468</v>
       </c>
       <c r="B466" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C466" s="25">
-        <v>30.16</v>
+        <v>27.66</v>
       </c>
       <c r="D466" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E466" s="27">
-        <v>257.87</v>
+        <v>236.49</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -10314,16 +10306,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C475" s="25">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>237.5</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10748,13 +10740,13 @@
         <v>28</v>
       </c>
       <c r="C502" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>78.75</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -11359,16 +11351,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C540" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D540" s="26">
         <v>2.84</v>
       </c>
       <c r="E540" s="27">
-        <v>46.92</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11767,16 +11759,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C564" s="25">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="D564" s="26">
         <v>3.14</v>
       </c>
       <c r="E564" s="27">
-        <v>88.86</v>
+        <v>84.15</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -12193,10 +12185,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C590" s="25">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12232,10 +12224,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C593" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12262,16 +12254,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C595" s="25">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>406.58</v>
+        <v>405.42</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12307,16 +12299,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C598" s="25">
-        <v>134.5</v>
+        <v>130.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>114.33</v>
+        <v>110.93</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12824,16 +12816,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C631" s="25">
-        <v>65.5</v>
+        <v>64.5</v>
       </c>
       <c r="D631" s="26">
         <v>2.76</v>
       </c>
       <c r="E631" s="27">
-        <v>180.7</v>
+        <v>177.95</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12926,16 +12918,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C637" s="25">
-        <v>147.5</v>
+        <v>151.5</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>336.3</v>
+        <v>345.42</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13243,16 +13235,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C656" s="25">
-        <v>168.5</v>
+        <v>167.5</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>480.23</v>
+        <v>477.38</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13577,16 +13569,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C676" s="25">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="D676" s="26">
         <v>2.5</v>
       </c>
       <c r="E676" s="27">
-        <v>150</v>
+        <v>146.25</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13696,16 +13688,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C683" s="25">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="D683" s="26">
         <v>2.75</v>
       </c>
       <c r="E683" s="27">
-        <v>147.13</v>
+        <v>141.63</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13897,10 +13889,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C696" s="25">
-        <v>64.34</v>
+        <v>63.34</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13962,10 +13954,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C701" s="25">
-        <v>66.5</v>
+        <v>64.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -14271,7 +14263,7 @@
         <v>50</v>
       </c>
       <c r="C725" s="25">
-        <v>-96.15</v>
+        <v>-98.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14411,16 +14403,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C734" s="25">
-        <v>19.25</v>
+        <v>18.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>48.13</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14453,11 +14445,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>45233.52</v>
+        <v>44922</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>108878.13</v>
+        <v>108070.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -116,7 +116,7 @@
     <t>1016 PATRIKA</t>
   </si>
   <si>
-    <t>1017 PATRIKA</t>
+    <t>1017 PATRIKA  (09.03 8000)</t>
   </si>
   <si>
     <t>1018 PATRIKA</t>
@@ -428,10 +428,10 @@
     <t>2101 PATRIKA (L)-DC</t>
   </si>
   <si>
-    <t>2102 PATRIKA *-* (M)</t>
-  </si>
-  <si>
-    <t>2103 PATRIKA (L)</t>
+    <t>2102 PATRIKA *-* (M) (09.03 1000)</t>
+  </si>
+  <si>
+    <t>2103 PATRIKA (L) (09.03 2000)</t>
   </si>
   <si>
     <t>2104 PATRIKA (DCU)</t>
@@ -440,7 +440,7 @@
     <t>2105 PATRIKA (DC)</t>
   </si>
   <si>
-    <t>2106 PATRIKA (L)</t>
+    <t>2106 PATRIKA (L) (09.03 1000)</t>
   </si>
   <si>
     <t>2107 PATRIKA *-* (M)</t>
@@ -449,7 +449,7 @@
     <t>2108 PATRIKA *-* (M) (DCU)</t>
   </si>
   <si>
-    <t>2109 PATRIKA (L)</t>
+    <t>2109 PATRIKA (L) (09.03 1000)</t>
   </si>
   <si>
     <t>2110 PATRIKA (DC)</t>
@@ -461,7 +461,7 @@
     <t>2112 PATRIKA (L)</t>
   </si>
   <si>
-    <t>2113 PATRIKA (L)</t>
+    <t>2113 PATRIKA (L) (09.03 400)</t>
   </si>
   <si>
     <t>2114 PATRIKA (L) (DCU)</t>
@@ -488,7 +488,7 @@
     <t>2121 PATRIKA (DC)</t>
   </si>
   <si>
-    <t>2122 PATRIKA</t>
+    <t>2122 PATRIKA (09.03 800)</t>
   </si>
   <si>
     <t>2123 PATRIKA (DCU)</t>
@@ -500,7 +500,7 @@
     <t>2125 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>2126 PATRIKA *-* (M)</t>
+    <t>2126 PATRIKA *-* (M) (09.03 1000)</t>
   </si>
   <si>
     <t>2127 PATRIKA *-* (M) (DCU)</t>
@@ -515,7 +515,7 @@
     <t>2130 PATRIKA *-* (M) (DCU)</t>
   </si>
   <si>
-    <t>2131 PATRIKA *-* (M) (DCU)</t>
+    <t>2131 PATRIKA *-* (M) (DCU) (09.03 1000)</t>
   </si>
   <si>
     <t>2132 PATRIKA *-* (M) (DCU)</t>
@@ -524,7 +524,7 @@
     <t>2133 PATRIKA</t>
   </si>
   <si>
-    <t>2134 PATRIKA *-* (M)</t>
+    <t>2134 PATRIKA *-* (M) (09.03 1000)</t>
   </si>
   <si>
     <t>2135 PATRIKA *-* (M)</t>
@@ -839,7 +839,7 @@
     <t>5076 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5077 PATRIKA (1000-1500 11.03)</t>
+    <t>5077 PATRIKA (2500 11.03)</t>
   </si>
   <si>
     <t>5078 PATRIKA (DCU)</t>
@@ -860,7 +860,7 @@
     <t>5084 PATRIKA (05 march 4000)</t>
   </si>
   <si>
-    <t>5085 PATRIKA</t>
+    <t>5085 PATRIKA (09.03 2000)</t>
   </si>
   <si>
     <t>5086 PATRIKA (JC) *-* (M+D)</t>
@@ -1007,13 +1007,13 @@
     <t>5516 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5517 PATRIKA *-* (M) (Patti Aayegi) 2400 09.03</t>
+    <t>5517 PATRIKA *-* (M) (Patti Aayegi)</t>
   </si>
   <si>
     <t>5518 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5519 PATRIKA *-* (M)</t>
+    <t>5519 PATRIKA *-* (M) (09.03 2500)</t>
   </si>
   <si>
     <t>5520 PATRIKA</t>
@@ -1082,7 +1082,7 @@
     <t>5541 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5542 PATRIKA</t>
+    <t>5542 PATRIKA (09.03 2500)</t>
   </si>
   <si>
     <t>5543 PATRIKA</t>
@@ -1094,7 +1094,7 @@
     <t>5545 PATRIKA *-* (M) (DC)</t>
   </si>
   <si>
-    <t>5546 PATRIKA</t>
+    <t>5546 PATRIKA (09.03 3200)</t>
   </si>
   <si>
     <t>5547 PATRIKA *-* (M)</t>
@@ -1127,7 +1127,7 @@
     <t>5556 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>5557 PATRIKA</t>
+    <t>5557 PATRIKA (09.03 2800)</t>
   </si>
   <si>
     <t>5558 PATRIKA *-* (M)</t>
@@ -1457,7 +1457,7 @@
     <t>6637 PATRIKA</t>
   </si>
   <si>
-    <t>6638 PATRIKA *-* (M)</t>
+    <t>6638 PATRIKA *-* (M) (09.03 1000)</t>
   </si>
   <si>
     <t>6639 PATRIKA</t>
@@ -1532,7 +1532,7 @@
     <t>6661 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>6662 PATRIKA</t>
+    <t>6662 PATRIKA (09.03 1000)</t>
   </si>
   <si>
     <t>6663 PATRIKA</t>
@@ -1685,7 +1685,7 @@
     <t>7422 PATRIKA</t>
   </si>
   <si>
-    <t>7423 PATRIKA</t>
+    <t>7423 PATRIKA (09.03 2000)</t>
   </si>
   <si>
     <t>7424 PATRIKA *-* (F)</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="25">
-        <v>153.5</v>
+        <v>150.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>276.3</v>
+        <v>270.89999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C14" s="25">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>276</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" s="25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3107,16 +3107,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>90</v>
+        <v>86.4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="25">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>92.4</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,17 +3175,11 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>51</v>
-      </c>
-      <c r="C28" s="25">
-        <v>4.5</v>
-      </c>
-      <c r="D28" s="26">
-        <v>2</v>
-      </c>
-      <c r="E28" s="27">
-        <v>9</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="28"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
@@ -3288,16 +3282,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" s="25">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>144.9</v>
+        <v>135.69999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3367,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C40" s="25">
-        <v>35</v>
+        <v>29.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>74.900000000000006</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3418,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C43" s="25">
-        <v>120.5</v>
+        <v>113.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>297.08</v>
+        <v>279.83</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3486,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C47" s="25">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>124.42</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3503,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" s="25">
-        <v>1.35</v>
+        <v>0.35</v>
       </c>
       <c r="D48" s="26">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="E48" s="27">
-        <v>1.87</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3554,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C51" s="25">
-        <v>165.5</v>
+        <v>162.5</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>297.89999999999998</v>
+        <v>292.5</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3628,16 +3622,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C55" s="25">
-        <v>242.65</v>
+        <v>242.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>667.29</v>
+        <v>665.91</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,16 +3718,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C61" s="25">
-        <v>1008.5</v>
+        <v>1006.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1149.02</v>
+        <v>1146.75</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,16 +3752,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C63" s="25">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>84.15</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3803,16 +3797,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C66" s="25">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>99</v>
+        <v>84.15</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3859,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="25">
-        <v>396</v>
+        <v>392.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>554.4</v>
+        <v>549.5</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3876,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C71" s="25">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>20.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3916,16 +3910,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C73" s="25">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>756</v>
+        <v>747.6</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,16 +3927,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C74" s="25">
-        <v>168.5</v>
+        <v>100</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>202.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +3995,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C78" s="25">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>393.6</v>
+        <v>386.4</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4097,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C84" s="25">
-        <v>1464.5</v>
+        <v>1428.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1903.85</v>
+        <v>1857.05</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4120,16 +4114,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C85" s="25">
-        <v>1415.5</v>
+        <v>1385.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1840.15</v>
+        <v>1801.15</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4137,16 +4131,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C86" s="25">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2053.6</v>
+        <v>2050.1999999999998</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,16 +4148,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C87" s="25">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1319.2</v>
+        <v>1315.8</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,16 +4182,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C89" s="25">
-        <v>245.5</v>
+        <v>233</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>358.71</v>
+        <v>340.45</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4239,16 +4233,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C92" s="25">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D92" s="26">
         <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>1344.92</v>
+        <v>1339.5</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4389,16 +4383,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" s="25">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>237.48</v>
+        <v>230.62</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4421,16 +4415,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C104" s="25">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>412.5</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4441,13 +4435,13 @@
         <v>20</v>
       </c>
       <c r="C105" s="25">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>787.5</v>
+        <v>797.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4472,16 +4466,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C107" s="25">
-        <v>325.5</v>
+        <v>323.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>813.75</v>
+        <v>808.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4506,10 +4500,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C109" s="25">
-        <v>111.5</v>
+        <v>108</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4519,7 +4513,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C110" s="25">
         <v>358.5</v>
@@ -4532,10 +4526,10 @@
         <v>113</v>
       </c>
       <c r="B111" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C111" s="25">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D111" s="29"/>
       <c r="E111" s="28"/>
@@ -4558,10 +4552,10 @@
         <v>115</v>
       </c>
       <c r="B113" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" s="25">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D113" s="29"/>
       <c r="E113" s="28"/>
@@ -4582,10 +4576,10 @@
         <v>117</v>
       </c>
       <c r="B115" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C115" s="25">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D115" s="29"/>
       <c r="E115" s="28"/>
@@ -4664,10 +4658,10 @@
         <v>123</v>
       </c>
       <c r="B121" s="24">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C121" s="25">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D121" s="29"/>
       <c r="E121" s="28"/>
@@ -4697,9 +4691,11 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>272</v>
-      </c>
-      <c r="C124" s="28"/>
+        <v>273</v>
+      </c>
+      <c r="C124" s="25">
+        <v>-0.01</v>
+      </c>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
     </row>
@@ -4734,10 +4730,10 @@
         <v>129</v>
       </c>
       <c r="B127" s="24">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C127" s="25">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D127" s="29"/>
       <c r="E127" s="28"/>
@@ -4814,16 +4810,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C133" s="25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>131.25</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5425,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C170" s="25">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>160.84</v>
+        <v>151.96</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,10 +5459,10 @@
         <v>174</v>
       </c>
       <c r="B172" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C172" s="25">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D172" s="29"/>
       <c r="E172" s="28"/>
@@ -5549,16 +5545,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C178" s="25">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>172.8</v>
+        <v>162</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5750,16 +5746,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C191" s="25">
-        <v>192.81</v>
+        <v>190.31</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>510.95</v>
+        <v>504.32</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5880,16 +5876,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C199" s="25">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="D199" s="26">
         <v>4.5</v>
       </c>
       <c r="E199" s="27">
-        <v>72</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5993,16 +5989,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C206" s="25">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>602.1</v>
+        <v>596.70000000000005</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6010,16 +6006,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C207" s="25">
-        <v>35.5</v>
+        <v>32.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>92.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6129,16 +6125,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C214" s="25">
-        <v>356.5</v>
+        <v>355</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>962.55</v>
+        <v>958.5</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6146,16 +6142,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C215" s="25">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>718.2</v>
+        <v>685.8</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6197,16 +6193,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C218" s="25">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="D218" s="26">
         <v>3</v>
       </c>
       <c r="E218" s="27">
-        <v>118.5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6248,16 +6244,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C221" s="25">
-        <v>84.25</v>
+        <v>188.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>273.81</v>
+        <v>611.80999999999995</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6265,16 +6261,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C222" s="25">
-        <v>96.5</v>
+        <v>92.5</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>351.29</v>
+        <v>336.73</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6282,16 +6278,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C223" s="25">
-        <v>36.5</v>
+        <v>34</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>98.55</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6418,16 +6414,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C231" s="25">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>304.5</v>
+        <v>280</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6446,16 +6442,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C233" s="25">
-        <v>73.38</v>
+        <v>71.38</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>238.49</v>
+        <v>231.99</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6463,16 +6459,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C234" s="25">
-        <v>37.5</v>
+        <v>34.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>121.88</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6605,16 +6601,16 @@
         <v>246</v>
       </c>
       <c r="B244" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C244" s="25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D244" s="26">
         <v>5.75</v>
       </c>
       <c r="E244" s="27">
-        <v>97.75</v>
+        <v>94.88</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6622,16 +6618,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C245" s="25">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="D245" s="26">
         <v>4.8</v>
       </c>
       <c r="E245" s="27">
-        <v>225.6</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6656,16 +6652,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C247" s="25">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6786,16 +6782,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C255" s="25">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>199.5</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6803,16 +6799,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C256" s="25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D256" s="26">
         <v>4.25</v>
       </c>
       <c r="E256" s="27">
-        <v>51</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6921,16 +6917,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C264" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D264" s="26">
         <v>6.15</v>
       </c>
       <c r="E264" s="27">
-        <v>156.91</v>
+        <v>144.61000000000001</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -6938,16 +6934,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C265" s="25">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1348.2</v>
+        <v>1296.8399999999999</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7003,13 +6999,13 @@
         <v>81</v>
       </c>
       <c r="C269" s="25">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>3.1</v>
+        <v>-24.8</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7062,16 +7058,16 @@
         <v>275</v>
       </c>
       <c r="B273" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C273" s="25">
-        <v>108.37</v>
+        <v>106.37</v>
       </c>
       <c r="D273" s="26">
         <v>4.25</v>
       </c>
       <c r="E273" s="27">
-        <v>460.57</v>
+        <v>452.07</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7182,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C281" s="25">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D281" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E281" s="27">
-        <v>746.41</v>
+        <v>727.03</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,16 +7210,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C283" s="25">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>401.71</v>
+        <v>373.36</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7367,16 +7363,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C292" s="25">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="D292" s="26">
         <v>4.5</v>
       </c>
       <c r="E292" s="27">
-        <v>492.75</v>
+        <v>490.5</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7401,16 +7397,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C294" s="25">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D294" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E294" s="27">
-        <v>479.02</v>
+        <v>464.36</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7455,13 +7451,13 @@
         <v>141</v>
       </c>
       <c r="C297" s="25">
-        <v>279.5</v>
+        <v>276.5</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1695.2</v>
+        <v>1677.15</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,16 +7482,16 @@
         <v>301</v>
       </c>
       <c r="B299" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C299" s="25">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D299" s="26">
         <v>4.2699999999999996</v>
       </c>
       <c r="E299" s="27">
-        <v>1037.19</v>
+        <v>1024.3900000000001</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7554,16 +7550,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C303" s="25">
-        <v>245.25</v>
+        <v>243.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1054.06</v>
+        <v>1045.47</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7900,16 +7896,16 @@
         <v>327</v>
       </c>
       <c r="B325" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C325" s="25">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="D325" s="26">
-        <v>7.63</v>
+        <v>7.45</v>
       </c>
       <c r="E325" s="27">
-        <v>34.33</v>
+        <v>174.97</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -8034,16 +8030,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C333" s="25">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D333" s="26">
         <v>7.97</v>
       </c>
       <c r="E333" s="27">
-        <v>119.57</v>
+        <v>79.709999999999994</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8113,16 +8109,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C338" s="25">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>274.5</v>
+        <v>238.5</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8158,16 +8154,16 @@
         <v>343</v>
       </c>
       <c r="B341" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C341" s="25">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="D341" s="26">
         <v>9</v>
       </c>
       <c r="E341" s="27">
-        <v>175.5</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8337,16 +8333,16 @@
         <v>354</v>
       </c>
       <c r="B352" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C352" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D352" s="26">
         <v>6.4</v>
       </c>
       <c r="E352" s="27">
-        <v>57.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -8499,16 +8495,16 @@
         <v>364</v>
       </c>
       <c r="B362" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C362" s="25">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="D362" s="26">
         <v>7.76</v>
       </c>
       <c r="E362" s="27">
-        <v>290.94</v>
+        <v>271.54000000000002</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8638,13 +8634,13 @@
         <v>94</v>
       </c>
       <c r="C370" s="25">
-        <v>98.5</v>
+        <v>95.5</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>650.1</v>
+        <v>630.29999999999995</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8720,16 +8716,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C375" s="25">
-        <v>45.83</v>
+        <v>38.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>206.24</v>
+        <v>174.74</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8808,13 +8804,13 @@
         <v>14</v>
       </c>
       <c r="C380" s="25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D380" s="26">
         <v>9.5</v>
       </c>
       <c r="E380" s="27">
-        <v>137.75</v>
+        <v>133</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -9006,13 +9002,13 @@
         <v>23</v>
       </c>
       <c r="C392" s="25">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D392" s="26">
         <v>3.6</v>
       </c>
       <c r="E392" s="27">
-        <v>19.8</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -9020,16 +9016,16 @@
         <v>395</v>
       </c>
       <c r="B393" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C393" s="25">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="D393" s="26">
-        <v>9.85</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="E393" s="27">
-        <v>98.48</v>
+        <v>162.94999999999999</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -9103,16 +9099,16 @@
         <v>400</v>
       </c>
       <c r="B398" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C398" s="25">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="D398" s="26">
         <v>6.65</v>
       </c>
       <c r="E398" s="27">
-        <v>69.83</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -9326,16 +9322,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C413" s="25">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>312</v>
+        <v>306.8</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9378,13 +9374,13 @@
         <v>42</v>
       </c>
       <c r="C416" s="25">
-        <v>20.5</v>
+        <v>48</v>
       </c>
       <c r="D416" s="26">
         <v>5.3</v>
       </c>
       <c r="E416" s="27">
-        <v>108.65</v>
+        <v>254.4</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -10182,9 +10178,15 @@
       <c r="B467" s="24">
         <v>15</v>
       </c>
-      <c r="C467" s="28"/>
-      <c r="D467" s="29"/>
-      <c r="E467" s="28"/>
+      <c r="C467" s="25">
+        <v>10</v>
+      </c>
+      <c r="D467" s="26">
+        <v>15.5</v>
+      </c>
+      <c r="E467" s="27">
+        <v>155</v>
+      </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="23" t="s">
@@ -10385,16 +10387,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C480" s="25">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="D480" s="26">
         <v>10.32</v>
       </c>
       <c r="E480" s="27">
-        <v>-20.64</v>
+        <v>-72.25</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10737,16 +10739,16 @@
         <v>504</v>
       </c>
       <c r="B502" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C502" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>56.25</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -10857,16 +10859,16 @@
         <v>512</v>
       </c>
       <c r="B510" s="24">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C510" s="25">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="D510" s="26">
         <v>10.17</v>
       </c>
       <c r="E510" s="27">
-        <v>127.08</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -11151,16 +11153,16 @@
         <v>530</v>
       </c>
       <c r="B528" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C528" s="25">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D528" s="26">
         <v>1.4</v>
       </c>
       <c r="E528" s="27">
-        <v>114.8</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11351,16 +11353,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C540" s="25">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="D540" s="26">
         <v>2.84</v>
       </c>
       <c r="E540" s="27">
-        <v>44.08</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11385,16 +11387,16 @@
         <v>544</v>
       </c>
       <c r="B542" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C542" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D542" s="26">
         <v>2</v>
       </c>
       <c r="E542" s="27">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11640,16 +11642,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C557" s="25">
-        <v>50.2</v>
+        <v>44.7</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>195.78</v>
+        <v>174.33</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11725,17 +11727,11 @@
         <v>564</v>
       </c>
       <c r="B562" s="24">
-        <v>19</v>
-      </c>
-      <c r="C562" s="25">
-        <v>2</v>
-      </c>
-      <c r="D562" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E562" s="27">
-        <v>7.2</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C562" s="28"/>
+      <c r="D562" s="29"/>
+      <c r="E562" s="28"/>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="23" t="s">
@@ -11776,16 +11772,16 @@
         <v>567</v>
       </c>
       <c r="B565" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C565" s="25">
-        <v>75.25</v>
+        <v>74.25</v>
       </c>
       <c r="D565" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E565" s="27">
-        <v>173.08</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11827,16 +11823,16 @@
         <v>570</v>
       </c>
       <c r="B568" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C568" s="25">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="D568" s="26">
         <v>3.5</v>
       </c>
       <c r="E568" s="27">
-        <v>168</v>
+        <v>166.25</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -11963,16 +11959,16 @@
         <v>578</v>
       </c>
       <c r="B576" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C576" s="25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D576" s="26">
         <v>2.71</v>
       </c>
       <c r="E576" s="27">
-        <v>21.69</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12014,16 +12010,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C579" s="25">
-        <v>83.5</v>
+        <v>77</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>116.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12031,16 +12027,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C580" s="25">
-        <v>84.5</v>
+        <v>83.5</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>152.1</v>
+        <v>150.30000000000001</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12172,10 +12168,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C589" s="25">
-        <v>266.5</v>
+        <v>258.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12185,10 +12181,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C590" s="25">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12198,10 +12194,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C591" s="25">
-        <v>227.5</v>
+        <v>221.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12211,10 +12207,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C592" s="25">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12227,7 +12223,7 @@
         <v>51</v>
       </c>
       <c r="C593" s="25">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12237,16 +12233,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C594" s="25">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>335.82</v>
+        <v>328.86</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12370,10 +12366,10 @@
         <v>605</v>
       </c>
       <c r="B603" s="24">
+        <v>27</v>
+      </c>
+      <c r="C603" s="25">
         <v>26</v>
-      </c>
-      <c r="C603" s="25">
-        <v>66</v>
       </c>
       <c r="D603" s="29"/>
       <c r="E603" s="28"/>
@@ -12383,10 +12379,10 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C604" s="25">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="D604" s="29"/>
       <c r="E604" s="28"/>
@@ -12396,11 +12392,9 @@
         <v>607</v>
       </c>
       <c r="B605" s="24">
-        <v>31</v>
-      </c>
-      <c r="C605" s="25">
-        <v>23</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C605" s="28"/>
       <c r="D605" s="29"/>
       <c r="E605" s="28"/>
     </row>
@@ -12461,16 +12455,16 @@
         <v>612</v>
       </c>
       <c r="B610" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C610" s="25">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D610" s="26">
         <v>0.73</v>
       </c>
       <c r="E610" s="27">
-        <v>43.07</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
@@ -12478,16 +12472,16 @@
         <v>613</v>
       </c>
       <c r="B611" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C611" s="25">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D611" s="26">
         <v>0.73</v>
       </c>
       <c r="E611" s="27">
-        <v>46.72</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -12495,16 +12489,16 @@
         <v>614</v>
       </c>
       <c r="B612" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C612" s="25">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D612" s="26">
         <v>0.85</v>
       </c>
       <c r="E612" s="27">
-        <v>22.95</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -12512,16 +12506,16 @@
         <v>615</v>
       </c>
       <c r="B613" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C613" s="25">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D613" s="26">
         <v>0.85</v>
       </c>
       <c r="E613" s="27">
-        <v>110.5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
@@ -12612,16 +12606,16 @@
         <v>621</v>
       </c>
       <c r="B619" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C619" s="25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D619" s="26">
         <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>71.5</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12731,16 +12725,16 @@
         <v>628</v>
       </c>
       <c r="B626" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C626" s="25">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="D626" s="26">
         <v>6.5</v>
       </c>
       <c r="E626" s="27">
-        <v>87.75</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -12765,16 +12759,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C628" s="25">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D628" s="26">
         <v>2.77</v>
       </c>
       <c r="E628" s="27">
-        <v>191.14</v>
+        <v>177.29</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12918,16 +12912,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C637" s="25">
-        <v>151.5</v>
+        <v>148.5</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>345.42</v>
+        <v>338.58</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13116,16 +13110,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C649" s="25">
-        <v>180.86</v>
+        <v>179.86</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>307.45999999999998</v>
+        <v>305.76</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13235,16 +13229,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C656" s="25">
-        <v>167.5</v>
+        <v>166.5</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>477.38</v>
+        <v>474.53</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13331,16 +13325,16 @@
         <v>664</v>
       </c>
       <c r="B662" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C662" s="25">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="D662" s="26">
         <v>5.73</v>
       </c>
       <c r="E662" s="27">
-        <v>306.66000000000003</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -13501,16 +13495,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C672" s="25">
-        <v>57.43</v>
+        <v>55.93</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>206.75</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13569,7 +13563,7 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C676" s="25">
         <v>58.5</v>
@@ -13654,16 +13648,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C681" s="25">
-        <v>113.5</v>
+        <v>112</v>
       </c>
       <c r="D681" s="26">
         <v>2.25</v>
       </c>
       <c r="E681" s="27">
-        <v>255.38</v>
+        <v>252</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13671,16 +13665,16 @@
         <v>684</v>
       </c>
       <c r="B682" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C682" s="25">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D682" s="26">
         <v>8.84</v>
       </c>
       <c r="E682" s="27">
-        <v>110.48</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -13688,16 +13682,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C683" s="25">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="D683" s="26">
         <v>2.75</v>
       </c>
       <c r="E683" s="27">
-        <v>141.63</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13889,10 +13883,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C696" s="25">
-        <v>63.34</v>
+        <v>59.34</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13915,10 +13909,10 @@
         <v>700</v>
       </c>
       <c r="B698" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C698" s="25">
-        <v>94.5</v>
+        <v>84.5</v>
       </c>
       <c r="D698" s="29"/>
       <c r="E698" s="28"/>
@@ -13954,10 +13948,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C701" s="25">
-        <v>64.5</v>
+        <v>62.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -13989,16 +13983,16 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C704" s="25">
-        <v>168.5</v>
+        <v>163.5</v>
       </c>
       <c r="D704" s="26">
         <v>2.93</v>
       </c>
       <c r="E704" s="27">
-        <v>493.99</v>
+        <v>479.33</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
@@ -14206,16 +14200,16 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C721" s="25">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="D721" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E721" s="27">
-        <v>79.459999999999994</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -14260,10 +14254,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C725" s="25">
-        <v>-98.15</v>
+        <v>-100.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14352,16 +14346,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C731" s="25">
-        <v>63.25</v>
+        <v>59.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>158.13</v>
+        <v>148.13</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14431,10 +14425,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C736" s="25">
-        <v>-517</v>
+        <v>-522.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14445,11 +14439,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44922</v>
+        <v>44492.97</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>108070.48</v>
+        <v>107563.74</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 5-Mar-26</t>
+    <t>1-Jul-25 to 6-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3203,16 +3203,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>26.18</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,16 +3780,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65" s="25">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>496.65</v>
+        <v>493.35</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4114,16 +4114,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C85" s="25">
-        <v>1385.5</v>
+        <v>1373.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1801.15</v>
+        <v>1785.55</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4199,16 +4199,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90" s="25">
-        <v>317.7</v>
+        <v>308.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>407.51</v>
+        <v>395.97</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4274,16 +4274,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C95" s="25">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>369</v>
+        <v>361.8</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4827,16 +4827,16 @@
         <v>136</v>
       </c>
       <c r="B134" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134" s="25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D134" s="26">
         <v>12.5</v>
       </c>
       <c r="E134" s="27">
-        <v>225</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5199,17 +5199,11 @@
         <v>158</v>
       </c>
       <c r="B156" s="24">
-        <v>25</v>
-      </c>
-      <c r="C156" s="25">
-        <v>3</v>
-      </c>
-      <c r="D156" s="26">
-        <v>11.5</v>
-      </c>
-      <c r="E156" s="27">
-        <v>34.5</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C156" s="28"/>
+      <c r="D156" s="29"/>
+      <c r="E156" s="28"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="23" t="s">
@@ -5233,16 +5227,16 @@
         <v>160</v>
       </c>
       <c r="B158" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C158" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D158" s="26">
         <v>11.5</v>
       </c>
       <c r="E158" s="27">
-        <v>103.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5729,16 +5723,16 @@
         <v>192</v>
       </c>
       <c r="B190" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C190" s="25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D190" s="26">
         <v>2.76</v>
       </c>
       <c r="E190" s="27">
-        <v>58</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -6703,16 +6697,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C250" s="25">
-        <v>175.5</v>
+        <v>173.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>684.45</v>
+        <v>676.65</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -9172,16 +9166,16 @@
         <v>405</v>
       </c>
       <c r="B403" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C403" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D403" s="26">
         <v>6.65</v>
       </c>
       <c r="E403" s="27">
-        <v>212.8</v>
+        <v>199.5</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -11472,17 +11466,11 @@
         <v>549</v>
       </c>
       <c r="B547" s="24">
-        <v>12</v>
-      </c>
-      <c r="C547" s="25">
-        <v>3</v>
-      </c>
-      <c r="D547" s="26">
-        <v>6.5</v>
-      </c>
-      <c r="E547" s="27">
-        <v>19.5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C547" s="28"/>
+      <c r="D547" s="29"/>
+      <c r="E547" s="28"/>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="23" t="s">
@@ -11642,16 +11630,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C557" s="25">
-        <v>44.7</v>
+        <v>41.7</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>174.33</v>
+        <v>162.63</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -12061,16 +12049,16 @@
         <v>584</v>
       </c>
       <c r="B582" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C582" s="25">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D582" s="26">
         <v>1.2</v>
       </c>
       <c r="E582" s="27">
-        <v>433.2</v>
+        <v>426</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -12194,10 +12182,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C591" s="25">
-        <v>221.5</v>
+        <v>213.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12233,16 +12221,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C594" s="25">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>328.86</v>
+        <v>325.38</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12728,13 +12716,13 @@
         <v>15</v>
       </c>
       <c r="C626" s="25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D626" s="26">
         <v>6.5</v>
       </c>
       <c r="E626" s="27">
-        <v>35.75</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -12759,16 +12747,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C628" s="25">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D628" s="26">
         <v>2.77</v>
       </c>
       <c r="E628" s="27">
-        <v>177.29</v>
+        <v>166.21</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -13461,16 +13449,16 @@
         <v>672</v>
       </c>
       <c r="B670" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C670" s="25">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="D670" s="26">
         <v>5.5</v>
       </c>
       <c r="E670" s="27">
-        <v>19.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13546,16 +13534,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C675" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D675" s="26">
         <v>3.75</v>
       </c>
       <c r="E675" s="27">
-        <v>118.13</v>
+        <v>110.63</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13870,10 +13858,10 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C695" s="25">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D695" s="29"/>
       <c r="E695" s="28"/>
@@ -13935,10 +13923,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C700" s="25">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14295,16 +14283,16 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C728" s="25">
-        <v>84.5</v>
+        <v>81.5</v>
       </c>
       <c r="D728" s="26">
         <v>2.5</v>
       </c>
       <c r="E728" s="27">
-        <v>211.25</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -14425,10 +14413,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C736" s="25">
-        <v>-522.5</v>
+        <v>-525.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14439,11 +14427,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44492.97</v>
+        <v>44398.47</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>107563.74</v>
+        <v>107335.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -122,7 +122,7 @@
     <t>1018 PATRIKA</t>
   </si>
   <si>
-    <t>1019 PATRIKA</t>
+    <t>1019 PATRIKA (DC)</t>
   </si>
   <si>
     <t>1020 PATRIKA</t>
@@ -245,7 +245,7 @@
     <t>1123 PATRIKA (LED-51)</t>
   </si>
   <si>
-    <t>1124 PATRIKA (LED-52)</t>
+    <t>1124 PATRIKA (LED-52) 09.03</t>
   </si>
   <si>
     <t>1125 PATRIKA (LED-53)</t>
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="25">
-        <v>164</v>
+        <v>160.5</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>319.8</v>
+        <v>312.98</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" s="25">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="25">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="25">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3203,16 +3203,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>16.66</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3220,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C31" s="25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>68.400000000000006</v>
+        <v>59.85</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3237,16 +3237,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" s="25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>89.6</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3282,16 +3282,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" s="25">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>135.69999999999999</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3299,16 +3299,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C36" s="25">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>257.60000000000002</v>
+        <v>232.3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3367,16 +3367,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C40" s="25">
-        <v>29.5</v>
+        <v>25.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>63.13</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3927,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C74" s="25">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>120</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +3995,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C78" s="25">
-        <v>322</v>
+        <v>320.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>386.4</v>
+        <v>384.6</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,10 +4500,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C109" s="25">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4810,17 +4810,11 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>61</v>
-      </c>
-      <c r="C133" s="25">
-        <v>10</v>
-      </c>
-      <c r="D133" s="26">
-        <v>12.5</v>
-      </c>
-      <c r="E133" s="27">
-        <v>125</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C133" s="28"/>
+      <c r="D133" s="29"/>
+      <c r="E133" s="28"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="23" t="s">
@@ -4861,16 +4855,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C136" s="25">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>43.75</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5419,16 +5413,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C170" s="25">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>151.96</v>
+        <v>147.51</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5539,16 +5533,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C178" s="25">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>162</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5599,16 +5593,16 @@
         <v>184</v>
       </c>
       <c r="B182" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C182" s="25">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D182" s="26">
         <v>2.8</v>
       </c>
       <c r="E182" s="27">
-        <v>165.39</v>
+        <v>156.97999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5723,16 +5717,16 @@
         <v>192</v>
       </c>
       <c r="B190" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C190" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D190" s="26">
         <v>2.76</v>
       </c>
       <c r="E190" s="27">
-        <v>52.48</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5983,16 +5977,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C206" s="25">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>596.70000000000005</v>
+        <v>588.6</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6119,16 +6113,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C214" s="25">
-        <v>355</v>
+        <v>352.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>958.5</v>
+        <v>951.75</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6136,16 +6130,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C215" s="25">
-        <v>254</v>
+        <v>252.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>685.8</v>
+        <v>681.75</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6187,16 +6181,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C218" s="25">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D218" s="26">
         <v>3</v>
       </c>
       <c r="E218" s="27">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6238,16 +6232,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C221" s="25">
-        <v>188.25</v>
+        <v>186.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>611.80999999999995</v>
+        <v>605.30999999999995</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6306,16 +6300,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C225" s="25">
-        <v>130.5</v>
+        <v>123</v>
       </c>
       <c r="D225" s="26">
         <v>2.66</v>
       </c>
       <c r="E225" s="27">
-        <v>347.13</v>
+        <v>327.18</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6340,16 +6334,16 @@
         <v>229</v>
       </c>
       <c r="B227" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C227" s="25">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="D227" s="26">
         <v>4</v>
       </c>
       <c r="E227" s="27">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6408,16 +6402,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C231" s="25">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6436,16 +6430,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C233" s="25">
-        <v>71.38</v>
+        <v>68.38</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>231.99</v>
+        <v>222.24</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6697,16 +6691,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C250" s="25">
-        <v>173.5</v>
+        <v>172.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>676.65</v>
+        <v>672.75</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6810,16 +6804,16 @@
         <v>259</v>
       </c>
       <c r="B257" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C257" s="25">
-        <v>55.5</v>
+        <v>49.5</v>
       </c>
       <c r="D257" s="26">
         <v>3.5</v>
       </c>
       <c r="E257" s="27">
-        <v>194.25</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -7204,16 +7198,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C283" s="25">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>373.36</v>
+        <v>326.10000000000002</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7272,16 +7266,16 @@
         <v>289</v>
       </c>
       <c r="B287" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C287" s="25">
-        <v>130.5</v>
+        <v>128</v>
       </c>
       <c r="D287" s="26">
         <v>5</v>
       </c>
       <c r="E287" s="27">
-        <v>652.5</v>
+        <v>640</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -7289,16 +7283,16 @@
         <v>290</v>
       </c>
       <c r="B288" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C288" s="25">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D288" s="26">
         <v>6</v>
       </c>
       <c r="E288" s="27">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -7323,16 +7317,16 @@
         <v>292</v>
       </c>
       <c r="B290" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C290" s="25">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="D290" s="26">
         <v>4.66</v>
       </c>
       <c r="E290" s="27">
-        <v>237.65</v>
+        <v>226</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7442,16 +7436,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C297" s="25">
-        <v>276.5</v>
+        <v>275.5</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1677.15</v>
+        <v>1671.13</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -8148,16 +8142,16 @@
         <v>343</v>
       </c>
       <c r="B341" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C341" s="25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="D341" s="26">
         <v>9</v>
       </c>
       <c r="E341" s="27">
-        <v>157.5</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8427,16 +8421,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C358" s="25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D358" s="26">
         <v>7.98</v>
       </c>
       <c r="E358" s="27">
-        <v>279.45999999999998</v>
+        <v>271.47000000000003</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8489,16 +8483,16 @@
         <v>364</v>
       </c>
       <c r="B362" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C362" s="25">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="D362" s="26">
         <v>7.76</v>
       </c>
       <c r="E362" s="27">
-        <v>271.54000000000002</v>
+        <v>252.15</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8608,16 +8602,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C369" s="25">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="D369" s="26">
         <v>7</v>
       </c>
       <c r="E369" s="27">
-        <v>122.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -9893,16 +9887,16 @@
         <v>452</v>
       </c>
       <c r="B450" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C450" s="25">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D450" s="26">
         <v>10.5</v>
       </c>
       <c r="E450" s="27">
-        <v>131.25</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -11198,16 +11192,16 @@
         <v>533</v>
       </c>
       <c r="B531" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C531" s="25">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="D531" s="26">
         <v>2</v>
       </c>
       <c r="E531" s="27">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -11398,16 +11392,16 @@
         <v>545</v>
       </c>
       <c r="B543" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C543" s="25">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D543" s="26">
         <v>4.28</v>
       </c>
       <c r="E543" s="27">
-        <v>132.68</v>
+        <v>124.12</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11998,16 +11992,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C579" s="25">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>107.8</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12015,16 +12009,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C580" s="25">
-        <v>83.5</v>
+        <v>79.5</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>150.30000000000001</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12156,10 +12150,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C589" s="25">
-        <v>258.5</v>
+        <v>252.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12221,16 +12215,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C594" s="25">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>325.38</v>
+        <v>317.55</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12238,16 +12232,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C595" s="25">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>405.42</v>
+        <v>403.1</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12849,16 +12843,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C634" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D634" s="26">
         <v>1.5</v>
       </c>
       <c r="E634" s="27">
-        <v>6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -13483,16 +13477,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C672" s="25">
-        <v>55.93</v>
+        <v>54.43</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>201.35</v>
+        <v>195.95</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13500,16 +13494,16 @@
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C673" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D673" s="26">
         <v>3.5</v>
       </c>
       <c r="E673" s="27">
-        <v>52.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13923,10 +13917,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C700" s="25">
-        <v>25.5</v>
+        <v>21.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14266,16 +14260,16 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C727" s="25">
-        <v>15.25</v>
+        <v>10.25</v>
       </c>
       <c r="D727" s="26">
         <v>2.5</v>
       </c>
       <c r="E727" s="27">
-        <v>38.130000000000003</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -14283,16 +14277,16 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C728" s="25">
-        <v>81.5</v>
+        <v>76.5</v>
       </c>
       <c r="D728" s="26">
         <v>2.5</v>
       </c>
       <c r="E728" s="27">
-        <v>203.75</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -14317,16 +14311,16 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C730" s="25">
-        <v>13.25</v>
+        <v>8.25</v>
       </c>
       <c r="D730" s="26">
         <v>2.5</v>
       </c>
       <c r="E730" s="27">
-        <v>33.130000000000003</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -14334,16 +14328,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C731" s="25">
-        <v>59.25</v>
+        <v>54.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>148.13</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14368,16 +14362,16 @@
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C733" s="25">
-        <v>53.5</v>
+        <v>48.5</v>
       </c>
       <c r="D733" s="26">
         <v>2.5</v>
       </c>
       <c r="E733" s="27">
-        <v>133.75</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -14385,16 +14379,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C734" s="25">
-        <v>18.25</v>
+        <v>13.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>45.63</v>
+        <v>33.130000000000003</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14427,11 +14421,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44398.47</v>
+        <v>44194.47</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>107335.5</v>
+        <v>106687.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -77,7 +77,7 @@
     <t>1004 PATRIKA</t>
   </si>
   <si>
-    <t>1005 PATRIKA (12000 09.03)</t>
+    <t>1005 PATRIKA</t>
   </si>
   <si>
     <t>1006 PATRIKA</t>
@@ -137,10 +137,10 @@
     <t>1023 PATRIKA</t>
   </si>
   <si>
-    <t>1024 PATRIKA (10k 05.03)</t>
-  </si>
-  <si>
-    <t>1025 PATRIKA (6000 09.03)</t>
+    <t>1024 PATRIKA</t>
+  </si>
+  <si>
+    <t>1025 PATRIKA</t>
   </si>
   <si>
     <t>1026 PATRIKA (JC)</t>
@@ -176,7 +176,7 @@
     <t>1101 PATRIKA (O.2591)</t>
   </si>
   <si>
-    <t>1102 PATRIKA (P.2591) 6 MARCH</t>
+    <t>1102 PATRIKA (P.2591)</t>
   </si>
   <si>
     <t>1103 PATRIKA(N-271)</t>
@@ -191,7 +191,7 @@
     <t>1106 PATRIKA-YELLOW</t>
   </si>
   <si>
-    <t>1107 PATRIKA-RED 6/03</t>
+    <t>1107 PATRIKA-RED</t>
   </si>
   <si>
     <t>1109 PATRIKA-BIG Y</t>
@@ -203,7 +203,7 @@
     <t>1112 PATRIKA</t>
   </si>
   <si>
-    <t>1113 PATRIKA 5/03</t>
+    <t>1113 PATRIKA</t>
   </si>
   <si>
     <t>1114 PATRIKA-BROWN</t>
@@ -257,7 +257,7 @@
     <t>1127 PATRIKA (Eco-52)</t>
   </si>
   <si>
-    <t>1128 PATRIKA (Eco-55)</t>
+    <t>1128 PATRIKA (Eco-55)Stk Confirm First</t>
   </si>
   <si>
     <t>1129 PATRIKA (Eco-56)</t>
@@ -566,7 +566,7 @@
     <t>4253 PATRIKA</t>
   </si>
   <si>
-    <t>4254 PATRIKA (4210) (4500 05.03)</t>
+    <t>4254 PATRIKA (4210)</t>
   </si>
   <si>
     <t>4255 PATRIKA - B (DCU)</t>
@@ -701,7 +701,7 @@
     <t>4296 PATRIKA</t>
   </si>
   <si>
-    <t>4297 PATRIKA (9600 05.03)</t>
+    <t>4297 PATRIKA</t>
   </si>
   <si>
     <t>4298 PATRIKA</t>
@@ -824,7 +824,7 @@
     <t>5071 PATRIKA *-* (डोरी)</t>
   </si>
   <si>
-    <t>5072 PATRIKA (09.03 200)</t>
+    <t>5072 PATRIKA</t>
   </si>
   <si>
     <t>5073 PATRIKA *-* (M)</t>
@@ -857,7 +857,7 @@
     <t>5083 PATRIKA (DCU)</t>
   </si>
   <si>
-    <t>5084 PATRIKA (05 march 4000)</t>
+    <t>5084 PATRIKA</t>
   </si>
   <si>
     <t>5085 PATRIKA (09.03 2000)</t>
@@ -884,7 +884,7 @@
     <t>5092 PATRIKA</t>
   </si>
   <si>
-    <t>5093 PATRIKA (09.03 400)</t>
+    <t>5093 PATRIKA</t>
   </si>
   <si>
     <t>5094 PATRIKA</t>
@@ -914,7 +914,7 @@
     <t>5103 PATRIKA</t>
   </si>
   <si>
-    <t>5104 PATRIKA (09.03 1200)</t>
+    <t>5104 PATRIKA</t>
   </si>
   <si>
     <t>5105 PATRIKA (JC)</t>
@@ -941,7 +941,7 @@
     <t>5112 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5113 PATRIKA (09.03 3700)</t>
+    <t>5113 PATRIKA</t>
   </si>
   <si>
     <t>5114 PATRIKA *-* (डोरी)</t>
@@ -1031,7 +1031,7 @@
     <t>5524 PATRIKA (DCU)</t>
   </si>
   <si>
-    <t>5525 PATRIKA *-* (M) (05 march 2000)</t>
+    <t>5525 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>5526 PATRIKA (DCU)</t>
@@ -1106,7 +1106,7 @@
     <t>5549 PATRIKA</t>
   </si>
   <si>
-    <t>5550 PATRIKA *-* (M) (05 march 950)</t>
+    <t>5550 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>5551 PATRIKA</t>
@@ -1118,7 +1118,7 @@
     <t>5553 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>5554 PATRIKA *-* (F/G) (05 march 3000)</t>
+    <t>5554 PATRIKA *-* (F/G)</t>
   </si>
   <si>
     <t>5555 PATRIKA</t>
@@ -1178,7 +1178,7 @@
     <t>5573 PATRIKA</t>
   </si>
   <si>
-    <t>5574 PATRIKA (09.03 4000)</t>
+    <t>5574 PATRIKA</t>
   </si>
   <si>
     <t>5575 PATRIKA *-* (M)</t>
@@ -1472,7 +1472,7 @@
     <t>6641 PATRIKA *-* (M) Dc</t>
   </si>
   <si>
-    <t>6642 PATRIKA *-* (M) 1800PCS 06.02.26</t>
+    <t>6642 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>6643 PATRIKA *-* (M)</t>
@@ -2069,7 +2069,7 @@
     <t>9363 CARDS *-* (T)</t>
   </si>
   <si>
-    <t>9364 CARDS *-* (T)  06.02.26 1700PCS</t>
+    <t>9364 CARDS *-* (T)  09.03 1700</t>
   </si>
   <si>
     <t>9365 CARDS</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="25">
-        <v>150.5</v>
+        <v>141.5</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>270.89999999999998</v>
+        <v>254.7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" s="25">
-        <v>160.5</v>
+        <v>153</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>312.98</v>
+        <v>298.35000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="25">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2963,13 +2963,13 @@
         <v>69</v>
       </c>
       <c r="C15" s="25">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>4</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="25">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3220,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>59.85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3265,16 +3265,16 @@
         <v>36</v>
       </c>
       <c r="B34" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="25">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D34" s="26">
         <v>2.5</v>
       </c>
       <c r="E34" s="27">
-        <v>82.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3282,16 +3282,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" s="25">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>124.2</v>
+        <v>347.3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3299,16 +3299,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="25">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>232.3</v>
+        <v>351.9</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3367,16 +3367,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>54.57</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3418,16 +3418,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="25">
-        <v>113.5</v>
+        <v>103.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>279.83</v>
+        <v>255.17</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3435,16 +3435,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C44" s="25">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="D44" s="26">
         <v>2.74</v>
       </c>
       <c r="E44" s="27">
-        <v>132.84</v>
+        <v>124.62</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,16 +3486,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="25">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>121.88</v>
+        <v>244.44</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3503,16 +3503,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C48" s="25">
-        <v>0.35</v>
+        <v>97.35</v>
       </c>
       <c r="D48" s="26">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>0.59</v>
+        <v>123.78</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3554,16 +3554,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C51" s="25">
-        <v>162.5</v>
+        <v>156.5</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>292.5</v>
+        <v>281.7</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,16 +3571,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C52" s="25">
-        <v>39.5</v>
+        <v>23.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>98.75</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3591,13 +3591,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="25">
-        <v>0.5</v>
+        <v>280.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>1.25</v>
+        <v>701.25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3625,13 +3625,13 @@
         <v>20</v>
       </c>
       <c r="C55" s="25">
-        <v>242.15</v>
+        <v>280.14999999999998</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>665.91</v>
+        <v>770.41</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3639,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C56" s="25">
-        <v>163.5</v>
+        <v>153.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>294.3</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,11 +3656,17 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>28</v>
-      </c>
-      <c r="C57" s="28"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="C57" s="25">
+        <v>138</v>
+      </c>
+      <c r="D57" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E57" s="27">
+        <v>262.2</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
@@ -3718,16 +3724,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C61" s="25">
-        <v>1006.5</v>
+        <v>988.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1146.75</v>
+        <v>1126.24</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3752,16 +3758,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C63" s="25">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>79.2</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3797,16 +3803,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" s="25">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>84.15</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3825,16 +3831,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C68" s="25">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>633.6</v>
+        <v>608.85</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,16 +3865,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C70" s="25">
-        <v>392.5</v>
+        <v>376</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>549.5</v>
+        <v>526.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3893,16 +3899,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C72" s="25">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>450.8</v>
+        <v>429.8</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,16 +3916,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C73" s="25">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>747.6</v>
+        <v>732.2</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3933,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C74" s="25">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>112.8</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3944,16 +3950,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C75" s="25">
-        <v>49</v>
+        <v>40.5</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>58.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3961,16 +3967,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C76" s="25">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>525.6</v>
+        <v>513.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +4001,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C78" s="25">
-        <v>320.5</v>
+        <v>300.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>384.6</v>
+        <v>360.6</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4046,16 +4052,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C81" s="25">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>852</v>
+        <v>828</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4063,16 +4069,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="25">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>832.8</v>
+        <v>820.8</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4080,16 +4086,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="25">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>880.8</v>
+        <v>868.8</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C84" s="25">
-        <v>1428.5</v>
+        <v>1415.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1857.05</v>
+        <v>1840.15</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4114,16 +4120,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C85" s="25">
-        <v>1373.5</v>
+        <v>1356.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1785.55</v>
+        <v>1763.45</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4165,16 +4171,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C88" s="25">
-        <v>1057.5</v>
+        <v>1054.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1797.75</v>
+        <v>1792.65</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" s="25">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>340.45</v>
+        <v>311.22000000000003</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4199,16 +4205,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C90" s="25">
-        <v>308.7</v>
+        <v>288.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>395.97</v>
+        <v>370.31</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4274,16 +4280,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C95" s="25">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>361.8</v>
+        <v>359.1</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4291,16 +4297,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C96" s="25">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>117</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4336,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C99" s="25">
-        <v>419.5</v>
+        <v>416</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>692.18</v>
+        <v>686.4</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4383,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C102" s="25">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>230.62</v>
+        <v>197.19</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,16 +4438,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C105" s="25">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>797.5</v>
+        <v>772.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4455,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C106" s="25">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>680</v>
+        <v>655</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4472,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C107" s="25">
-        <v>323.5</v>
+        <v>313.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>808.75</v>
+        <v>783.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,10 +4506,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C109" s="25">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4589,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C116" s="25">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4602,10 +4608,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" s="25">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4812,9 +4818,15 @@
       <c r="B133" s="24">
         <v>62</v>
       </c>
-      <c r="C133" s="28"/>
-      <c r="D133" s="29"/>
-      <c r="E133" s="28"/>
+      <c r="C133" s="25">
+        <v>-10</v>
+      </c>
+      <c r="D133" s="26">
+        <v>12.5</v>
+      </c>
+      <c r="E133" s="27">
+        <v>-125</v>
+      </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="23" t="s">
@@ -4872,16 +4884,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C137" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D137" s="26">
         <v>12.5</v>
       </c>
       <c r="E137" s="27">
-        <v>75</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5091,16 +5103,16 @@
         <v>152</v>
       </c>
       <c r="B150" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C150" s="25">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="D150" s="26">
         <v>18.5</v>
       </c>
       <c r="E150" s="27">
-        <v>231.25</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -5413,16 +5425,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C170" s="25">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>147.51</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5536,13 +5548,13 @@
         <v>26</v>
       </c>
       <c r="C178" s="25">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>153.9</v>
+        <v>275.39999999999998</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5644,16 +5656,16 @@
         <v>187</v>
       </c>
       <c r="B185" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C185" s="25">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D185" s="26">
         <v>3.33</v>
       </c>
       <c r="E185" s="27">
-        <v>74.930000000000007</v>
+        <v>66.599999999999994</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5717,16 +5729,16 @@
         <v>192</v>
       </c>
       <c r="B190" s="24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C190" s="25">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D190" s="26">
         <v>2.76</v>
       </c>
       <c r="E190" s="27">
-        <v>46.95</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5734,16 +5746,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C191" s="25">
-        <v>190.31</v>
+        <v>185.31</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>504.32</v>
+        <v>491.07</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5994,16 +6006,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C207" s="25">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>84.5</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6079,16 +6091,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C212" s="25">
-        <v>271.5</v>
+        <v>270</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1067.32</v>
+        <v>1061.42</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6113,16 +6125,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C214" s="25">
-        <v>352.5</v>
+        <v>348.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>951.75</v>
+        <v>940.95</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6215,16 +6227,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C220" s="25">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D220" s="26">
         <v>3.93</v>
       </c>
       <c r="E220" s="27">
-        <v>699.39</v>
+        <v>695.46</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6232,16 +6244,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C221" s="25">
-        <v>186.25</v>
+        <v>180.25</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>605.30999999999995</v>
+        <v>585.80999999999995</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6249,16 +6261,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C222" s="25">
-        <v>92.5</v>
+        <v>79</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>336.73</v>
+        <v>287.58</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6266,16 +6278,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C223" s="25">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>91.8</v>
+        <v>334.8</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6402,16 +6414,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C231" s="25">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>273</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6430,16 +6442,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C233" s="25">
-        <v>68.38</v>
+        <v>64.38</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>222.24</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6447,16 +6459,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C234" s="25">
-        <v>34.5</v>
+        <v>30.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>112.13</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6606,16 +6618,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C245" s="25">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="D245" s="26">
         <v>4.8</v>
       </c>
       <c r="E245" s="27">
-        <v>232.8</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6623,16 +6635,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C246" s="25">
-        <v>92.9</v>
+        <v>88.9</v>
       </c>
       <c r="D246" s="26">
         <v>6.3</v>
       </c>
       <c r="E246" s="27">
-        <v>585.27</v>
+        <v>560.07000000000005</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6640,16 +6652,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C247" s="25">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6691,16 +6703,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C250" s="25">
-        <v>172.5</v>
+        <v>165</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>672.75</v>
+        <v>643.5</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6770,16 +6782,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C255" s="25">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>185.5</v>
+        <v>168</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6804,7 +6816,7 @@
         <v>259</v>
       </c>
       <c r="B257" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C257" s="25">
         <v>49.5</v>
@@ -6905,16 +6917,16 @@
         <v>266</v>
       </c>
       <c r="B264" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C264" s="25">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="D264" s="26">
-        <v>6.15</v>
+        <v>6.16</v>
       </c>
       <c r="E264" s="27">
-        <v>144.61000000000001</v>
+        <v>126.19</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -6922,16 +6934,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C265" s="25">
-        <v>303</v>
+        <v>289.5</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1296.8399999999999</v>
+        <v>1239.06</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7012,16 +7024,16 @@
         <v>273</v>
       </c>
       <c r="B271" s="24">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C271" s="25">
-        <v>29.5</v>
+        <v>18.5</v>
       </c>
       <c r="D271" s="26">
         <v>4.5</v>
       </c>
       <c r="E271" s="27">
-        <v>132.75</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -7083,13 +7095,13 @@
         <v>45</v>
       </c>
       <c r="C275" s="25">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D275" s="26">
-        <v>4.3899999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E275" s="27">
-        <v>338.02</v>
+        <v>515.05999999999995</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7198,16 +7210,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C283" s="25">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>326.10000000000002</v>
+        <v>321.37</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7215,16 +7227,16 @@
         <v>286</v>
       </c>
       <c r="B284" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C284" s="25">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D284" s="26">
         <v>6.19</v>
       </c>
       <c r="E284" s="27">
-        <v>389.68</v>
+        <v>402.14</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7388,13 +7400,13 @@
         <v>80</v>
       </c>
       <c r="C294" s="25">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D294" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E294" s="27">
-        <v>464.36</v>
+        <v>522.98</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7436,16 +7448,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C297" s="25">
-        <v>275.5</v>
+        <v>272.5</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1671.13</v>
+        <v>1653.09</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7541,13 +7553,13 @@
         <v>71</v>
       </c>
       <c r="C303" s="25">
-        <v>243.25</v>
+        <v>280.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1045.47</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7589,16 +7601,16 @@
         <v>308</v>
       </c>
       <c r="B306" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C306" s="25">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D306" s="26">
         <v>5.13</v>
       </c>
       <c r="E306" s="27">
-        <v>353.97</v>
+        <v>333.45</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7822,16 +7834,16 @@
         <v>323</v>
       </c>
       <c r="B321" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C321" s="25">
-        <v>21.5</v>
+        <v>16.5</v>
       </c>
       <c r="D321" s="26">
         <v>6.6</v>
       </c>
       <c r="E321" s="27">
-        <v>141.9</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -8021,13 +8033,13 @@
         <v>19</v>
       </c>
       <c r="C333" s="25">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D333" s="26">
-        <v>7.97</v>
+        <v>8</v>
       </c>
       <c r="E333" s="27">
-        <v>79.709999999999994</v>
+        <v>240.03</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8097,16 +8109,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C338" s="25">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>238.5</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8145,13 +8157,13 @@
         <v>23</v>
       </c>
       <c r="C341" s="25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="D341" s="26">
         <v>9</v>
       </c>
       <c r="E341" s="27">
-        <v>139.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8304,16 +8316,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C351" s="25">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>356.4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8424,13 +8436,13 @@
         <v>42</v>
       </c>
       <c r="C358" s="25">
-        <v>34</v>
+        <v>43.5</v>
       </c>
       <c r="D358" s="26">
-        <v>7.98</v>
+        <v>7.99</v>
       </c>
       <c r="E358" s="27">
-        <v>271.47000000000003</v>
+        <v>347.63</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8486,13 +8498,13 @@
         <v>58</v>
       </c>
       <c r="C362" s="25">
-        <v>32.5</v>
+        <v>61</v>
       </c>
       <c r="D362" s="26">
         <v>7.76</v>
       </c>
       <c r="E362" s="27">
-        <v>252.15</v>
+        <v>473.58</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8670,16 +8682,16 @@
         <v>375</v>
       </c>
       <c r="B373" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C373" s="25">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D373" s="26">
         <v>8.52</v>
       </c>
       <c r="E373" s="27">
-        <v>442.83</v>
+        <v>425.8</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8687,16 +8699,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C374" s="25">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D374" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E374" s="27">
-        <v>287</v>
+        <v>246</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8704,16 +8716,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C375" s="25">
-        <v>38.83</v>
+        <v>31.33</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>174.74</v>
+        <v>140.99</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8823,16 +8835,16 @@
         <v>384</v>
       </c>
       <c r="B382" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C382" s="25">
-        <v>1.5</v>
+        <v>31.5</v>
       </c>
       <c r="D382" s="26">
         <v>6</v>
       </c>
       <c r="E382" s="27">
-        <v>9</v>
+        <v>189</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -9070,16 +9082,16 @@
         <v>399</v>
       </c>
       <c r="B397" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C397" s="25">
-        <v>41.5</v>
+        <v>31.5</v>
       </c>
       <c r="D397" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E397" s="27">
-        <v>354.83</v>
+        <v>269.33</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -9427,9 +9439,15 @@
       <c r="B420" s="24">
         <v>4</v>
       </c>
-      <c r="C420" s="28"/>
-      <c r="D420" s="29"/>
-      <c r="E420" s="28"/>
+      <c r="C420" s="25">
+        <v>2</v>
+      </c>
+      <c r="D420" s="26">
+        <v>5.3</v>
+      </c>
+      <c r="E420" s="27">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="23" t="s">
@@ -10164,16 +10182,16 @@
         <v>469</v>
       </c>
       <c r="B467" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C467" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D467" s="26">
         <v>15.5</v>
       </c>
       <c r="E467" s="27">
-        <v>155</v>
+        <v>124</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10296,16 +10314,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C475" s="25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>218.5</v>
+        <v>190</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10378,13 +10396,13 @@
         <v>49</v>
       </c>
       <c r="C480" s="25">
-        <v>-7</v>
+        <v>12.5</v>
       </c>
       <c r="D480" s="26">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>-72.25</v>
+        <v>129.16</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10441,16 +10459,16 @@
         <v>486</v>
       </c>
       <c r="B484" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C484" s="25">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="D484" s="26">
         <v>11.88</v>
       </c>
       <c r="E484" s="27">
-        <v>17.82</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -11522,16 +11540,16 @@
         <v>553</v>
       </c>
       <c r="B551" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C551" s="25">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="D551" s="26">
         <v>4.75</v>
       </c>
       <c r="E551" s="27">
-        <v>49.88</v>
+        <v>40.380000000000003</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11992,16 +12010,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C579" s="25">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>106.4</v>
+        <v>91</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12009,16 +12027,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C580" s="25">
-        <v>79.5</v>
+        <v>72</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>143.1</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12107,10 +12125,10 @@
         <v>588</v>
       </c>
       <c r="B586" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C586" s="25">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D586" s="29"/>
       <c r="E586" s="28"/>
@@ -12176,10 +12194,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C591" s="25">
-        <v>213.5</v>
+        <v>211.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12189,10 +12207,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C592" s="25">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12202,10 +12220,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C593" s="25">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12218,13 +12236,13 @@
         <v>99</v>
       </c>
       <c r="C594" s="25">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>317.55</v>
+        <v>321.02999999999997</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12277,16 +12295,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C598" s="25">
-        <v>130.5</v>
+        <v>133.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>110.93</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12690,16 +12708,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C625" s="25">
-        <v>18.350000000000001</v>
+        <v>21.35</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>73.400000000000006</v>
+        <v>85.4</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -13092,16 +13110,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C649" s="25">
-        <v>179.86</v>
+        <v>156.86000000000001</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>305.76</v>
+        <v>266.66000000000003</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13211,16 +13229,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C656" s="25">
-        <v>166.5</v>
+        <v>160</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>474.53</v>
+        <v>456</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13341,16 +13359,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C664" s="25">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>55.2</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13409,16 +13427,16 @@
         <v>670</v>
       </c>
       <c r="B668" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C668" s="25">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D668" s="26">
         <v>6.75</v>
       </c>
       <c r="E668" s="27">
-        <v>33.75</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
@@ -13460,16 +13478,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C671" s="25">
-        <v>164.5</v>
+        <v>154.5</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>509.95</v>
+        <v>478.95</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13477,16 +13495,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C672" s="25">
-        <v>54.43</v>
+        <v>55.93</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>195.95</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13528,16 +13546,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C675" s="25">
-        <v>29.5</v>
+        <v>24.5</v>
       </c>
       <c r="D675" s="26">
         <v>3.75</v>
       </c>
       <c r="E675" s="27">
-        <v>110.63</v>
+        <v>91.88</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13545,16 +13563,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C676" s="25">
-        <v>58.5</v>
+        <v>53.5</v>
       </c>
       <c r="D676" s="26">
         <v>2.5</v>
       </c>
       <c r="E676" s="27">
-        <v>146.25</v>
+        <v>133.75</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13596,16 +13614,16 @@
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C679" s="25">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D679" s="26">
         <v>5.8</v>
       </c>
       <c r="E679" s="27">
-        <v>2.9</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13630,16 +13648,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C681" s="25">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D681" s="26">
         <v>2.25</v>
       </c>
       <c r="E681" s="27">
-        <v>252</v>
+        <v>245.25</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13930,10 +13948,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C701" s="25">
-        <v>62.5</v>
+        <v>52.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -13965,16 +13983,16 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C704" s="25">
-        <v>163.5</v>
+        <v>148.5</v>
       </c>
       <c r="D704" s="26">
         <v>2.93</v>
       </c>
       <c r="E704" s="27">
-        <v>479.33</v>
+        <v>435.35</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
@@ -14328,16 +14346,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C731" s="25">
-        <v>54.25</v>
+        <v>53.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>135.63</v>
+        <v>133.13</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14379,16 +14397,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C734" s="25">
-        <v>13.25</v>
+        <v>11.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>33.130000000000003</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14421,11 +14439,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44194.47</v>
+        <v>44717.47</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>106687.15</v>
+        <v>108509.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 6-Mar-26</t>
+    <t>1-Jul-25 to 7-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -2926,16 +2926,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="25">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>267.14999999999998</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="25">
-        <v>112</v>
+        <v>105.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="25">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3045,16 +3045,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="25">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D20" s="26">
         <v>0.64</v>
       </c>
       <c r="E20" s="27">
-        <v>34.81</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3090,16 +3090,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="25">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D23" s="26">
         <v>1.8</v>
       </c>
       <c r="E23" s="27">
-        <v>158.4</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C25" s="25">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>85.8</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" s="25">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3220,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>57</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3418,16 +3418,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="25">
-        <v>103.5</v>
+        <v>100.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>255.17</v>
+        <v>247.77</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,16 +3707,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C60" s="25">
-        <v>931.5</v>
+        <v>928.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1059.6600000000001</v>
+        <v>1056.24</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -4595,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C116" s="25">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4623,9 +4623,7 @@
       <c r="B118" s="24">
         <v>1</v>
       </c>
-      <c r="C118" s="25">
-        <v>-30</v>
-      </c>
+      <c r="C118" s="28"/>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
     </row>
@@ -4901,16 +4899,16 @@
         <v>140</v>
       </c>
       <c r="B138" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C138" s="25">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="D138" s="26">
         <v>12.5</v>
       </c>
       <c r="E138" s="27">
-        <v>37.5</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -6125,16 +6123,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C214" s="25">
-        <v>348.5</v>
+        <v>343.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>940.95</v>
+        <v>927.45</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6244,16 +6242,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C221" s="25">
-        <v>180.25</v>
+        <v>177.75</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>585.80999999999995</v>
+        <v>577.69000000000005</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6278,16 +6276,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C223" s="25">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>334.8</v>
+        <v>329.4</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6686,16 +6684,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C249" s="25">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D249" s="26">
         <v>3.8</v>
       </c>
       <c r="E249" s="27">
-        <v>402.8</v>
+        <v>383.8</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -7041,16 +7039,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C272" s="25">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="D272" s="26">
         <v>6.25</v>
       </c>
       <c r="E272" s="27">
-        <v>146.88</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7058,16 +7056,16 @@
         <v>275</v>
       </c>
       <c r="B273" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C273" s="25">
-        <v>106.37</v>
+        <v>101.37</v>
       </c>
       <c r="D273" s="26">
         <v>4.25</v>
       </c>
       <c r="E273" s="27">
-        <v>452.07</v>
+        <v>430.82</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7772,16 +7770,16 @@
         <v>319</v>
       </c>
       <c r="B317" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C317" s="25">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="D317" s="26">
         <v>8.1</v>
       </c>
       <c r="E317" s="27">
-        <v>68.849999999999994</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -8316,16 +8314,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C351" s="25">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>297</v>
+        <v>273.24</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8631,16 +8629,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C370" s="25">
-        <v>95.5</v>
+        <v>94.5</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>630.29999999999995</v>
+        <v>623.70000000000005</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8999,16 +8997,16 @@
         <v>394</v>
       </c>
       <c r="B392" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C392" s="25">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="D392" s="26">
         <v>3.6</v>
       </c>
       <c r="E392" s="27">
-        <v>23.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -10165,16 +10163,16 @@
         <v>468</v>
       </c>
       <c r="B466" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C466" s="25">
-        <v>27.66</v>
+        <v>25.16</v>
       </c>
       <c r="D466" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E466" s="27">
-        <v>236.49</v>
+        <v>215.12</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -11942,16 +11940,16 @@
         <v>577</v>
       </c>
       <c r="B575" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C575" s="25">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="D575" s="26">
         <v>2.35</v>
       </c>
       <c r="E575" s="27">
-        <v>50.53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12125,10 +12123,10 @@
         <v>588</v>
       </c>
       <c r="B586" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C586" s="25">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D586" s="29"/>
       <c r="E586" s="28"/>
@@ -12220,10 +12218,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C593" s="25">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12827,16 +12825,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C632" s="25">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -13048,16 +13046,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C645" s="25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D645" s="26">
         <v>3.5</v>
       </c>
       <c r="E645" s="27">
-        <v>52.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13359,16 +13357,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C664" s="25">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>40.799999999999997</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13512,16 +13510,16 @@
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C673" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D673" s="26">
         <v>3.5</v>
       </c>
       <c r="E673" s="27">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -14346,16 +14344,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C731" s="25">
-        <v>53.25</v>
+        <v>52.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>133.13</v>
+        <v>130.63</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14439,11 +14437,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44717.47</v>
+        <v>44598.47</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>108509.12</v>
+        <v>108072.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -116,7 +116,7 @@
     <t>1016 PATRIKA</t>
   </si>
   <si>
-    <t>1017 PATRIKA  (09.03 8000)</t>
+    <t>1017 PATRIKA</t>
   </si>
   <si>
     <t>1018 PATRIKA</t>
@@ -860,7 +860,7 @@
     <t>5084 PATRIKA</t>
   </si>
   <si>
-    <t>5085 PATRIKA (09.03 2000)</t>
+    <t>5085 PATRIKA</t>
   </si>
   <si>
     <t>5086 PATRIKA (JC) *-* (M+D)</t>
@@ -1013,7 +1013,7 @@
     <t>5518 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5519 PATRIKA *-* (M) (09.03 2500)</t>
+    <t>5519 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>5520 PATRIKA</t>
@@ -1082,7 +1082,7 @@
     <t>5541 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5542 PATRIKA (09.03 2500)</t>
+    <t>5542 PATRIKA</t>
   </si>
   <si>
     <t>5543 PATRIKA</t>
@@ -1094,7 +1094,7 @@
     <t>5545 PATRIKA *-* (M) (DC)</t>
   </si>
   <si>
-    <t>5546 PATRIKA (09.03 3200)</t>
+    <t>5546 PATRIKA</t>
   </si>
   <si>
     <t>5547 PATRIKA *-* (M)</t>
@@ -1127,7 +1127,7 @@
     <t>5556 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>5557 PATRIKA (09.03 2800)</t>
+    <t>5557 PATRIKA</t>
   </si>
   <si>
     <t>5558 PATRIKA *-* (M)</t>
@@ -1457,7 +1457,7 @@
     <t>6637 PATRIKA</t>
   </si>
   <si>
-    <t>6638 PATRIKA *-* (M) (09.03 1000)</t>
+    <t>6638 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>6639 PATRIKA</t>
@@ -1472,7 +1472,7 @@
     <t>6641 PATRIKA *-* (M) Dc</t>
   </si>
   <si>
-    <t>6642 PATRIKA *-* (M)</t>
+    <t>6642 PATRIKA *-* (M) %NO</t>
   </si>
   <si>
     <t>6643 PATRIKA *-* (M)</t>
@@ -1532,7 +1532,7 @@
     <t>6661 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>6662 PATRIKA (09.03 1000)</t>
+    <t>6662 PATRIKA</t>
   </si>
   <si>
     <t>6663 PATRIKA</t>
@@ -1685,7 +1685,7 @@
     <t>7422 PATRIKA</t>
   </si>
   <si>
-    <t>7423 PATRIKA (09.03 2000)</t>
+    <t>7423 PATRIKA</t>
   </si>
   <si>
     <t>7424 PATRIKA *-* (F)</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="25">
-        <v>141.5</v>
+        <v>139</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>254.7</v>
+        <v>250.2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="25">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>298.35000000000002</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" s="25">
-        <v>105.5</v>
+        <v>100.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="25">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2994,16 +2994,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="25">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>585.9</v>
+        <v>583.79999999999995</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C25" s="25">
-        <v>50.5</v>
+        <v>39</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>83.33</v>
+        <v>64.349999999999994</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="25">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,11 +3175,17 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>53</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="28"/>
+        <v>55</v>
+      </c>
+      <c r="C28" s="25">
+        <v>74</v>
+      </c>
+      <c r="D28" s="26">
+        <v>2</v>
+      </c>
+      <c r="E28" s="27">
+        <v>148</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
@@ -3220,16 +3226,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="25">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>45.6</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C47" s="25">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>244.44</v>
+        <v>231.77</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3503,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C48" s="25">
-        <v>97.35</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>123.78</v>
+        <v>97.74</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3608,13 +3614,13 @@
         <v>16</v>
       </c>
       <c r="C54" s="25">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>283.25</v>
+        <v>387.75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3625,13 +3631,13 @@
         <v>20</v>
       </c>
       <c r="C55" s="25">
-        <v>280.14999999999998</v>
+        <v>242.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>770.41</v>
+        <v>665.91</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,16 +3662,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C57" s="25">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>262.2</v>
+        <v>254.6</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C61" s="25">
-        <v>988.5</v>
+        <v>984.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1126.24</v>
+        <v>1121.68</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3786,16 +3792,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C65" s="25">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>493.35</v>
+        <v>486.75</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3831,16 +3837,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="25">
-        <v>369</v>
+        <v>368.5</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>608.85</v>
+        <v>608.03</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3871,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C70" s="25">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>526.4</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3885,13 +3891,13 @@
         <v>98</v>
       </c>
       <c r="C71" s="25">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>2.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3950,16 +3956,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C75" s="25">
-        <v>40.5</v>
+        <v>33.5</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>48.6</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +4007,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C78" s="25">
-        <v>300.5</v>
+        <v>289.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>360.6</v>
+        <v>347.4</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,16 +4058,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81" s="25">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>828</v>
+        <v>813.6</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4109,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C84" s="25">
-        <v>1415.5</v>
+        <v>1410.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1840.15</v>
+        <v>1833.65</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,16 +4194,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C89" s="25">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>311.22000000000003</v>
+        <v>300.99</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,16 +4211,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C90" s="25">
-        <v>288.7</v>
+        <v>286.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>370.31</v>
+        <v>367.75</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,16 +4303,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C96" s="25">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>115.2</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4342,16 +4348,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C99" s="25">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>686.4</v>
+        <v>684.75</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4421,16 +4427,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C104" s="25">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>387.5</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4438,16 +4444,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C105" s="25">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>772.5</v>
+        <v>770</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4472,16 +4478,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C107" s="25">
-        <v>313.5</v>
+        <v>309.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>783.75</v>
+        <v>773.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4519,10 +4525,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C110" s="25">
-        <v>358.5</v>
+        <v>356.5</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4595,10 +4601,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C116" s="25">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4695,10 +4701,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C124" s="25">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
@@ -4814,16 +4820,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C133" s="25">
-        <v>-10</v>
+        <v>-12.5</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>-125</v>
+        <v>-156.25</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4865,16 +4871,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C136" s="25">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>37.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4899,16 +4905,16 @@
         <v>140</v>
       </c>
       <c r="B138" s="24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C138" s="25">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="D138" s="26">
         <v>12.5</v>
       </c>
       <c r="E138" s="27">
-        <v>-62.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4982,16 +4988,16 @@
         <v>145</v>
       </c>
       <c r="B143" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C143" s="25">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>46.25</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5067,16 +5073,16 @@
         <v>150</v>
       </c>
       <c r="B148" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C148" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D148" s="26">
         <v>18.5</v>
       </c>
       <c r="E148" s="27">
-        <v>92.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5248,16 +5254,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C159" s="25">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D159" s="26">
         <v>11.5</v>
       </c>
       <c r="E159" s="27">
-        <v>57.5</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5423,16 +5429,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C170" s="25">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>138.63</v>
+        <v>129.74</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5543,16 +5549,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C178" s="25">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>275.39999999999998</v>
+        <v>259.2</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5603,16 +5609,16 @@
         <v>184</v>
       </c>
       <c r="B182" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C182" s="25">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D182" s="26">
         <v>2.8</v>
       </c>
       <c r="E182" s="27">
-        <v>156.97999999999999</v>
+        <v>142.96</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5744,16 +5750,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C191" s="25">
-        <v>185.31</v>
+        <v>182.31</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>491.07</v>
+        <v>483.12</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -6038,16 +6044,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C209" s="25">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6089,16 +6095,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C212" s="25">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1061.42</v>
+        <v>1037.83</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6123,16 +6129,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C214" s="25">
-        <v>343.5</v>
+        <v>340.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>927.45</v>
+        <v>919.35</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6140,16 +6146,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C215" s="25">
-        <v>252.5</v>
+        <v>250.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>681.75</v>
+        <v>676.35</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6157,16 +6163,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C216" s="25">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D216" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E216" s="27">
-        <v>264.5</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6191,16 +6197,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C218" s="25">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D218" s="26">
         <v>3</v>
       </c>
       <c r="E218" s="27">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6259,16 +6265,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C222" s="25">
-        <v>79</v>
+        <v>76.5</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>287.58</v>
+        <v>278.48</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6327,16 +6333,16 @@
         <v>228</v>
       </c>
       <c r="B226" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C226" s="25">
-        <v>42.5</v>
+        <v>39.5</v>
       </c>
       <c r="D226" s="26">
         <v>4</v>
       </c>
       <c r="E226" s="27">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6412,16 +6418,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C231" s="25">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>248.5</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6633,16 +6639,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C246" s="25">
-        <v>88.9</v>
+        <v>85.4</v>
       </c>
       <c r="D246" s="26">
         <v>6.3</v>
       </c>
       <c r="E246" s="27">
-        <v>560.07000000000005</v>
+        <v>538.02</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6650,16 +6656,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C247" s="25">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6684,16 +6690,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C249" s="25">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D249" s="26">
         <v>3.8</v>
       </c>
       <c r="E249" s="27">
-        <v>383.8</v>
+        <v>349.6</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6701,16 +6707,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C250" s="25">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>643.5</v>
+        <v>600.6</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6718,16 +6724,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C251" s="25">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>643.5</v>
+        <v>631.79999999999995</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6780,16 +6786,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C255" s="25">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>168</v>
+        <v>112</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6797,16 +6803,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C256" s="25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D256" s="26">
         <v>4.25</v>
       </c>
       <c r="E256" s="27">
-        <v>29.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6932,16 +6938,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C265" s="25">
-        <v>289.5</v>
+        <v>288</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1239.06</v>
+        <v>1232.6400000000001</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7110,13 +7116,13 @@
         <v>28</v>
       </c>
       <c r="C276" s="25">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D276" s="26">
         <v>4.28</v>
       </c>
       <c r="E276" s="27">
-        <v>47.08</v>
+        <v>132.68</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7180,16 +7186,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C281" s="25">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D281" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E281" s="27">
-        <v>727.03</v>
+        <v>712.49</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7429,16 +7435,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C296" s="25">
-        <v>71.5</v>
+        <v>68.5</v>
       </c>
       <c r="D296" s="26">
         <v>3.15</v>
       </c>
       <c r="E296" s="27">
-        <v>225.23</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7446,16 +7452,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C297" s="25">
-        <v>272.5</v>
+        <v>262</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1653.09</v>
+        <v>1589.92</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7894,16 +7900,16 @@
         <v>327</v>
       </c>
       <c r="B325" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C325" s="25">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="D325" s="26">
         <v>7.45</v>
       </c>
       <c r="E325" s="27">
-        <v>174.97</v>
+        <v>148.91</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -7931,13 +7937,13 @@
         <v>32</v>
       </c>
       <c r="C327" s="25">
-        <v>8.5</v>
+        <v>33.5</v>
       </c>
       <c r="D327" s="26">
         <v>10</v>
       </c>
       <c r="E327" s="27">
-        <v>85</v>
+        <v>335</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -8073,16 +8079,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C336" s="25">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="D336" s="26">
         <v>9</v>
       </c>
       <c r="E336" s="27">
-        <v>391.5</v>
+        <v>382.5</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8300,13 +8306,13 @@
         <v>27</v>
       </c>
       <c r="C350" s="25">
-        <v>16</v>
+        <v>40.5</v>
       </c>
       <c r="D350" s="26">
         <v>5.7</v>
       </c>
       <c r="E350" s="27">
-        <v>91.2</v>
+        <v>230.85</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8365,16 +8371,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C354" s="25">
-        <v>30.85</v>
+        <v>62.35</v>
       </c>
       <c r="D354" s="26">
         <v>4.75</v>
       </c>
       <c r="E354" s="27">
-        <v>146.54</v>
+        <v>296.16000000000003</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8431,16 +8437,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C358" s="25">
-        <v>43.5</v>
+        <v>40.5</v>
       </c>
       <c r="D358" s="26">
         <v>7.99</v>
       </c>
       <c r="E358" s="27">
-        <v>347.63</v>
+        <v>323.66000000000003</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8493,16 +8499,16 @@
         <v>364</v>
       </c>
       <c r="B362" s="24">
+        <v>59</v>
+      </c>
+      <c r="C362" s="25">
         <v>58</v>
-      </c>
-      <c r="C362" s="25">
-        <v>61</v>
       </c>
       <c r="D362" s="26">
         <v>7.76</v>
       </c>
       <c r="E362" s="27">
-        <v>473.58</v>
+        <v>450.29</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8547,13 +8553,13 @@
         <v>43</v>
       </c>
       <c r="C365" s="25">
-        <v>12.5</v>
+        <v>40.5</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>74.25</v>
+        <v>240.57</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8612,16 +8618,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C369" s="25">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="D369" s="26">
         <v>7</v>
       </c>
       <c r="E369" s="27">
-        <v>115.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8629,16 +8635,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C370" s="25">
-        <v>94.5</v>
+        <v>93</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>623.70000000000005</v>
+        <v>613.79999999999995</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -9170,16 +9176,16 @@
         <v>405</v>
       </c>
       <c r="B403" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C403" s="25">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D403" s="26">
         <v>6.65</v>
       </c>
       <c r="E403" s="27">
-        <v>199.5</v>
+        <v>189.53</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -9187,16 +9193,16 @@
         <v>406</v>
       </c>
       <c r="B404" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C404" s="25">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="D404" s="26">
         <v>7</v>
       </c>
       <c r="E404" s="27">
-        <v>73.5</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -9320,16 +9326,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C413" s="25">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>306.8</v>
+        <v>301.60000000000002</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9403,16 +9409,16 @@
         <v>420</v>
       </c>
       <c r="B418" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C418" s="25">
-        <v>56.5</v>
+        <v>52.5</v>
       </c>
       <c r="D418" s="26">
         <v>6.2</v>
       </c>
       <c r="E418" s="27">
-        <v>350.5</v>
+        <v>325.68</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -9472,13 +9478,13 @@
         <v>8</v>
       </c>
       <c r="C422" s="25">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D422" s="26">
         <v>6.46</v>
       </c>
       <c r="E422" s="27">
-        <v>12.92</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -9572,16 +9578,16 @@
         <v>431</v>
       </c>
       <c r="B429" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C429" s="25">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="D429" s="26">
         <v>6</v>
       </c>
       <c r="E429" s="27">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
@@ -10101,16 +10107,16 @@
         <v>464</v>
       </c>
       <c r="B462" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C462" s="25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D462" s="26">
         <v>10.5</v>
       </c>
       <c r="E462" s="27">
-        <v>168</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -10163,16 +10169,16 @@
         <v>468</v>
       </c>
       <c r="B466" s="24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C466" s="25">
-        <v>25.16</v>
+        <v>27.66</v>
       </c>
       <c r="D466" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E466" s="27">
-        <v>215.12</v>
+        <v>236.49</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -10180,16 +10186,16 @@
         <v>469</v>
       </c>
       <c r="B467" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C467" s="25">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="D467" s="26">
         <v>15.5</v>
       </c>
       <c r="E467" s="27">
-        <v>124</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10312,16 +10318,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C475" s="25">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>190</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10391,16 +10397,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C480" s="25">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D480" s="26">
         <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>129.16</v>
+        <v>103.33</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10694,16 +10700,16 @@
         <v>501</v>
       </c>
       <c r="B499" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C499" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D499" s="26">
         <v>13.43</v>
       </c>
       <c r="E499" s="27">
-        <v>120.87</v>
+        <v>107.44</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
@@ -10714,13 +10720,13 @@
         <v>25</v>
       </c>
       <c r="C500" s="25">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="D500" s="26">
         <v>9</v>
       </c>
       <c r="E500" s="27">
-        <v>121.5</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
@@ -10782,16 +10788,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C505" s="25">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="D505" s="26">
         <v>18.5</v>
       </c>
       <c r="E505" s="27">
-        <v>231.25</v>
+        <v>101.75</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11140,16 +11146,16 @@
         <v>529</v>
       </c>
       <c r="B527" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C527" s="25">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="D527" s="26">
         <v>1.4</v>
       </c>
       <c r="E527" s="27">
-        <v>41.3</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11174,16 +11180,16 @@
         <v>531</v>
       </c>
       <c r="B529" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C529" s="25">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D529" s="26">
         <v>1.8</v>
       </c>
       <c r="E529" s="27">
-        <v>210.6</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11191,16 +11197,16 @@
         <v>532</v>
       </c>
       <c r="B530" s="24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C530" s="25">
-        <v>51.5</v>
+        <v>44.5</v>
       </c>
       <c r="D530" s="26">
         <v>1.95</v>
       </c>
       <c r="E530" s="27">
-        <v>100.43</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -11259,16 +11265,16 @@
         <v>536</v>
       </c>
       <c r="B534" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C534" s="25">
-        <v>44.5</v>
+        <v>42.5</v>
       </c>
       <c r="D534" s="26">
         <v>3.8</v>
       </c>
       <c r="E534" s="27">
-        <v>169.1</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11391,16 +11397,16 @@
         <v>544</v>
       </c>
       <c r="B542" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C542" s="25">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D542" s="26">
         <v>2</v>
       </c>
       <c r="E542" s="27">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11408,16 +11414,16 @@
         <v>545</v>
       </c>
       <c r="B543" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C543" s="25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D543" s="26">
         <v>4.28</v>
       </c>
       <c r="E543" s="27">
-        <v>124.12</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11442,16 +11448,16 @@
         <v>547</v>
       </c>
       <c r="B545" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C545" s="25">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="D545" s="26">
         <v>3.56</v>
       </c>
       <c r="E545" s="27">
-        <v>33.82</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -11538,16 +11544,16 @@
         <v>553</v>
       </c>
       <c r="B551" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C551" s="25">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
       <c r="D551" s="26">
         <v>4.75</v>
       </c>
       <c r="E551" s="27">
-        <v>40.380000000000003</v>
+        <v>125.88</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11640,16 +11646,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C557" s="25">
-        <v>41.7</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>162.63</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11657,17 +11663,11 @@
         <v>560</v>
       </c>
       <c r="B558" s="24">
-        <v>31</v>
-      </c>
-      <c r="C558" s="25">
-        <v>4</v>
-      </c>
-      <c r="D558" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E558" s="27">
-        <v>7.2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C558" s="28"/>
+      <c r="D558" s="29"/>
+      <c r="E558" s="28"/>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="23" t="s">
@@ -12059,16 +12059,16 @@
         <v>584</v>
       </c>
       <c r="B582" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C582" s="25">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D582" s="26">
         <v>1.2</v>
       </c>
       <c r="E582" s="27">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -12110,10 +12110,10 @@
         <v>587</v>
       </c>
       <c r="B585" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C585" s="25">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D585" s="29"/>
       <c r="E585" s="28"/>
@@ -12179,10 +12179,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C590" s="25">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12248,16 +12248,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C595" s="25">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>403.1</v>
+        <v>399.62</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12293,16 +12293,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C598" s="25">
-        <v>133.5</v>
+        <v>132.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>113.48</v>
+        <v>112.63</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12425,17 +12425,11 @@
         <v>610</v>
       </c>
       <c r="B608" s="24">
-        <v>7</v>
-      </c>
-      <c r="C608" s="25">
-        <v>2</v>
-      </c>
-      <c r="D608" s="26">
-        <v>0.73</v>
-      </c>
-      <c r="E608" s="27">
-        <v>1.46</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C608" s="28"/>
+      <c r="D608" s="29"/>
+      <c r="E608" s="28"/>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="23" t="s">
@@ -12655,16 +12649,16 @@
         <v>624</v>
       </c>
       <c r="B622" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C622" s="25">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="D622" s="26">
         <v>3.5</v>
       </c>
       <c r="E622" s="27">
-        <v>50.75</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
@@ -12706,16 +12700,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C625" s="25">
-        <v>21.35</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>85.4</v>
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12757,16 +12751,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C628" s="25">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D628" s="26">
         <v>2.77</v>
       </c>
       <c r="E628" s="27">
-        <v>166.21</v>
+        <v>160.66999999999999</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12825,16 +12819,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C632" s="25">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -13108,16 +13102,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C649" s="25">
-        <v>156.86000000000001</v>
+        <v>149.86000000000001</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>266.66000000000003</v>
+        <v>254.76</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13159,16 +13153,16 @@
         <v>654</v>
       </c>
       <c r="B652" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C652" s="25">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="D652" s="26">
         <v>3.5</v>
       </c>
       <c r="E652" s="27">
-        <v>75.25</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13227,16 +13221,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C656" s="25">
-        <v>160</v>
+        <v>152.5</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>456</v>
+        <v>434.63</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13476,16 +13470,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C671" s="25">
-        <v>154.5</v>
+        <v>150</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>478.95</v>
+        <v>465</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13493,16 +13487,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C672" s="25">
-        <v>55.93</v>
+        <v>47.43</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>201.35</v>
+        <v>170.75</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13544,16 +13538,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C675" s="25">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="D675" s="26">
         <v>3.75</v>
       </c>
       <c r="E675" s="27">
-        <v>91.88</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13578,16 +13572,16 @@
         <v>679</v>
       </c>
       <c r="B677" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C677" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D677" s="26">
         <v>7.31</v>
       </c>
       <c r="E677" s="27">
-        <v>109.69</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -13646,16 +13640,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C681" s="25">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D681" s="26">
         <v>2.25</v>
       </c>
       <c r="E681" s="27">
-        <v>245.25</v>
+        <v>236.25</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13680,16 +13674,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C683" s="25">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D683" s="26">
         <v>2.75</v>
       </c>
       <c r="E683" s="27">
-        <v>140.25</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13868,10 +13862,10 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C695" s="25">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D695" s="29"/>
       <c r="E695" s="28"/>
@@ -13959,10 +13953,10 @@
         <v>704</v>
       </c>
       <c r="B702" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C702" s="25">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="D702" s="29"/>
       <c r="E702" s="28"/>
@@ -14423,10 +14417,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C736" s="25">
-        <v>-525.5</v>
+        <v>-530.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14437,11 +14431,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44598.47</v>
+        <v>44459.46</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>108072.26</v>
+        <v>108010.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 7-Mar-26</t>
+    <t>1-Jul-25 to 9-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" s="25">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>250.2</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="25">
-        <v>149</v>
+        <v>147.5</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>290.55</v>
+        <v>287.63</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="25">
-        <v>100.5</v>
+        <v>92.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="25">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2977,16 +2977,16 @@
         <v>18</v>
       </c>
       <c r="B16" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="25">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="26">
         <v>2.1</v>
       </c>
       <c r="E16" s="27">
-        <v>109.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3045,16 +3045,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="25">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D20" s="26">
         <v>0.64</v>
       </c>
       <c r="E20" s="27">
-        <v>15.47</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3192,16 +3192,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="25">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D29" s="26">
         <v>2.6</v>
       </c>
       <c r="E29" s="27">
-        <v>80.599999999999994</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3305,16 +3305,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" s="25">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>351.9</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3373,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C40" s="25">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>50.29</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3390,16 +3390,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" s="25">
-        <v>59.5</v>
+        <v>57</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>127.33</v>
+        <v>121.98</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C43" s="25">
-        <v>100.5</v>
+        <v>89.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>247.77</v>
+        <v>220.66</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3441,16 +3441,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C44" s="25">
-        <v>45.5</v>
+        <v>35.5</v>
       </c>
       <c r="D44" s="26">
         <v>2.74</v>
       </c>
       <c r="E44" s="27">
-        <v>124.62</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C47" s="25">
-        <v>183</v>
+        <v>177.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>231.77</v>
+        <v>224.81</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C48" s="25">
-        <v>76.849999999999994</v>
+        <v>72.349999999999994</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>97.74</v>
+        <v>92.03</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3577,16 +3577,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C52" s="25">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>58.75</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3594,16 +3594,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C53" s="25">
-        <v>280.5</v>
+        <v>274.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>701.25</v>
+        <v>686.25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3645,16 +3645,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C56" s="25">
-        <v>153.5</v>
+        <v>150.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>276.3</v>
+        <v>270.89999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3662,16 +3662,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C57" s="25">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>254.6</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3696,16 +3696,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C59" s="25">
-        <v>64.75</v>
+        <v>64.25</v>
       </c>
       <c r="D59" s="26">
         <v>1.9</v>
       </c>
       <c r="E59" s="27">
-        <v>123.03</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3713,16 +3713,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C60" s="25">
-        <v>928.5</v>
+        <v>912.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1056.24</v>
+        <v>1038.04</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C61" s="25">
-        <v>984.5</v>
+        <v>968.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1121.68</v>
+        <v>1103.45</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3792,16 +3792,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C65" s="25">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>486.75</v>
+        <v>481.8</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,16 +3888,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C71" s="25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>14</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3922,16 +3922,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C73" s="25">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>732.2</v>
+        <v>728</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3956,16 +3956,16 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C75" s="25">
-        <v>33.5</v>
+        <v>29.5</v>
       </c>
       <c r="D75" s="26">
         <v>1.2</v>
       </c>
       <c r="E75" s="27">
-        <v>40.200000000000003</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3990,16 +3990,16 @@
         <v>79</v>
       </c>
       <c r="B77" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" s="25">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D77" s="26">
         <v>1.2</v>
       </c>
       <c r="E77" s="27">
-        <v>33.6</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4007,16 +4007,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C78" s="25">
-        <v>289.5</v>
+        <v>269.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>347.4</v>
+        <v>323.39999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4024,16 +4024,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C79" s="25">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>760.8</v>
+        <v>736.8</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4041,16 +4041,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C80" s="25">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>734.4</v>
+        <v>698.4</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4058,16 +4058,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C81" s="25">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>813.6</v>
+        <v>765.6</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,16 +4109,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C84" s="25">
-        <v>1410.5</v>
+        <v>1375.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1833.65</v>
+        <v>1788.15</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4126,16 +4126,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C85" s="25">
-        <v>1356.5</v>
+        <v>1336.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1763.45</v>
+        <v>1737.45</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,16 +4194,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C89" s="25">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>300.99</v>
+        <v>293.69</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,16 +4228,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C91" s="25">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>74.02</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4303,16 +4303,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C96" s="25">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>114.3</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4348,16 +4348,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C99" s="25">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>684.75</v>
+        <v>683.1</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4395,16 +4395,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" s="25">
-        <v>230</v>
+        <v>227.5</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>197.19</v>
+        <v>195.04</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4512,10 +4512,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C109" s="25">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4614,10 +4614,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" s="25">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4820,16 +4820,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C133" s="25">
-        <v>-12.5</v>
+        <v>-15</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>-156.25</v>
+        <v>-187.5</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4939,16 +4939,16 @@
         <v>142</v>
       </c>
       <c r="B140" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" s="25">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="D140" s="26">
         <v>12.5</v>
       </c>
       <c r="E140" s="27">
-        <v>118.75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4988,16 +4988,16 @@
         <v>145</v>
       </c>
       <c r="B143" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C143" s="25">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>18.5</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5429,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C170" s="25">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>129.74</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5498,16 +5498,16 @@
         <v>177</v>
       </c>
       <c r="B175" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C175" s="25">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="D175" s="26">
         <v>3.5</v>
       </c>
       <c r="E175" s="27">
-        <v>36.75</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5549,16 +5549,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C178" s="25">
-        <v>96</v>
+        <v>95.5</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>259.2</v>
+        <v>257.85000000000002</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5660,16 +5660,16 @@
         <v>187</v>
       </c>
       <c r="B185" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C185" s="25">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D185" s="26">
         <v>3.33</v>
       </c>
       <c r="E185" s="27">
-        <v>66.599999999999994</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5750,16 +5750,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C191" s="25">
-        <v>182.31</v>
+        <v>181.81</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>483.12</v>
+        <v>481.8</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5880,16 +5880,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C199" s="25">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="D199" s="26">
         <v>4.5</v>
       </c>
       <c r="E199" s="27">
-        <v>60.75</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -6044,16 +6044,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C209" s="25">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6095,16 +6095,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C212" s="25">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1037.83</v>
+        <v>1026.04</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6129,16 +6129,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C214" s="25">
-        <v>340.5</v>
+        <v>325.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>919.35</v>
+        <v>878.85</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6146,16 +6146,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C215" s="25">
-        <v>250.5</v>
+        <v>248.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>676.35</v>
+        <v>670.95</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6163,16 +6163,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C216" s="25">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="D216" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E216" s="27">
-        <v>241.5</v>
+        <v>235.75</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6214,16 +6214,16 @@
         <v>221</v>
       </c>
       <c r="B219" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C219" s="25">
-        <v>41</v>
+        <v>38.5</v>
       </c>
       <c r="D219" s="26">
         <v>3</v>
       </c>
       <c r="E219" s="27">
-        <v>123</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6248,16 +6248,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C221" s="25">
-        <v>177.75</v>
+        <v>172.75</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>577.69000000000005</v>
+        <v>561.44000000000005</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6316,16 +6316,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C225" s="25">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D225" s="26">
         <v>2.66</v>
       </c>
       <c r="E225" s="27">
-        <v>327.18</v>
+        <v>316.54000000000002</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6656,16 +6656,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C247" s="25">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>480</v>
+        <v>478.5</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6707,16 +6707,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C250" s="25">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>600.6</v>
+        <v>577.20000000000005</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6786,16 +6786,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C255" s="25">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6938,16 +6938,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C265" s="25">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1232.6400000000001</v>
+        <v>1129.92</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7028,16 +7028,16 @@
         <v>273</v>
       </c>
       <c r="B271" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C271" s="25">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="D271" s="26">
         <v>4.5</v>
       </c>
       <c r="E271" s="27">
-        <v>83.25</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -7096,16 +7096,16 @@
         <v>277</v>
       </c>
       <c r="B275" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C275" s="25">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D275" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E275" s="27">
-        <v>515.05999999999995</v>
+        <v>506.25</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,16 +7214,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C283" s="25">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>321.37</v>
+        <v>302.47000000000003</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7435,16 +7435,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C296" s="25">
-        <v>68.5</v>
+        <v>61.5</v>
       </c>
       <c r="D296" s="26">
         <v>3.15</v>
       </c>
       <c r="E296" s="27">
-        <v>215.78</v>
+        <v>193.73</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7452,16 +7452,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C297" s="25">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1589.92</v>
+        <v>1559.85</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7554,16 +7554,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C303" s="25">
-        <v>280.25</v>
+        <v>270.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1204.52</v>
+        <v>1161.54</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7571,16 +7571,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C304" s="25">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="D304" s="26">
         <v>4.75</v>
       </c>
       <c r="E304" s="27">
-        <v>97.38</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -8303,16 +8303,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C350" s="25">
-        <v>40.5</v>
+        <v>32.5</v>
       </c>
       <c r="D350" s="26">
         <v>5.7</v>
       </c>
       <c r="E350" s="27">
-        <v>230.85</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8567,16 +8567,16 @@
         <v>368</v>
       </c>
       <c r="B366" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C366" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D366" s="26">
         <v>7.2</v>
       </c>
       <c r="E366" s="27">
-        <v>183.6</v>
+        <v>169.2</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8720,16 +8720,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C375" s="25">
-        <v>31.33</v>
+        <v>24.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>140.99</v>
+        <v>111.74</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8788,16 +8788,16 @@
         <v>381</v>
       </c>
       <c r="B379" s="24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C379" s="25">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
       <c r="D379" s="26">
         <v>7</v>
       </c>
       <c r="E379" s="27">
-        <v>241.5</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -9326,16 +9326,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C413" s="25">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>301.60000000000002</v>
+        <v>286</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -10480,16 +10480,16 @@
         <v>487</v>
       </c>
       <c r="B485" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C485" s="25">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="D485" s="26">
         <v>13</v>
       </c>
       <c r="E485" s="27">
-        <v>175.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
@@ -10749,16 +10749,16 @@
         <v>504</v>
       </c>
       <c r="B502" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C502" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>33.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -11180,16 +11180,16 @@
         <v>531</v>
       </c>
       <c r="B529" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C529" s="25">
-        <v>116</v>
+        <v>112.5</v>
       </c>
       <c r="D529" s="26">
         <v>1.8</v>
       </c>
       <c r="E529" s="27">
-        <v>208.8</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11265,16 +11265,16 @@
         <v>536</v>
       </c>
       <c r="B534" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C534" s="25">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="D534" s="26">
         <v>3.8</v>
       </c>
       <c r="E534" s="27">
-        <v>161.5</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11397,16 +11397,16 @@
         <v>544</v>
       </c>
       <c r="B542" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C542" s="25">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="D542" s="26">
         <v>2</v>
       </c>
       <c r="E542" s="27">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11448,16 +11448,16 @@
         <v>547</v>
       </c>
       <c r="B545" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C545" s="25">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D545" s="26">
         <v>3.56</v>
       </c>
       <c r="E545" s="27">
-        <v>26.7</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -11510,16 +11510,16 @@
         <v>551</v>
       </c>
       <c r="B549" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C549" s="25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D549" s="26">
         <v>2.65</v>
       </c>
       <c r="E549" s="27">
-        <v>159</v>
+        <v>145.75</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11612,16 +11612,16 @@
         <v>557</v>
       </c>
       <c r="B555" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C555" s="25">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D555" s="26">
         <v>2.8</v>
       </c>
       <c r="E555" s="27">
-        <v>25.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -11753,16 +11753,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C564" s="25">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="D564" s="26">
         <v>3.14</v>
       </c>
       <c r="E564" s="27">
-        <v>84.15</v>
+        <v>81.010000000000005</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11804,16 +11804,16 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C567" s="25">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="D567" s="26">
         <v>2.5</v>
       </c>
       <c r="E567" s="27">
-        <v>106.25</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -11889,16 +11889,16 @@
         <v>574</v>
       </c>
       <c r="B572" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C572" s="25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D572" s="26">
         <v>2.66</v>
       </c>
       <c r="E572" s="27">
-        <v>39.9</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -11957,16 +11957,16 @@
         <v>578</v>
       </c>
       <c r="B576" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C576" s="25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D576" s="26">
         <v>2.71</v>
       </c>
       <c r="E576" s="27">
-        <v>18.98</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12025,16 +12025,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C580" s="25">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>129.6</v>
+        <v>126</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12076,16 +12076,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C583" s="25">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="D583" s="26">
         <v>1.2</v>
       </c>
       <c r="E583" s="27">
-        <v>512.4</v>
+        <v>464.4</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12166,10 +12166,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C589" s="25">
-        <v>252.5</v>
+        <v>247.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12179,10 +12179,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C590" s="25">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12192,10 +12192,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C591" s="25">
-        <v>211.5</v>
+        <v>210.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12231,16 +12231,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C594" s="25">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>321.02999999999997</v>
+        <v>301.02</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12248,16 +12248,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C595" s="25">
-        <v>689</v>
+        <v>669</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>399.62</v>
+        <v>388.02</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12265,16 +12265,16 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C596" s="25">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D596" s="26">
         <v>0.85</v>
       </c>
       <c r="E596" s="27">
-        <v>365.5</v>
+        <v>343.4</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -12293,16 +12293,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C598" s="25">
-        <v>132.5</v>
+        <v>106.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>112.63</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12598,16 +12598,16 @@
         <v>621</v>
       </c>
       <c r="B619" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C619" s="25">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="D619" s="26">
         <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>68.75</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12819,16 +12819,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C632" s="25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12904,16 +12904,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C637" s="25">
-        <v>148.5</v>
+        <v>147</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>338.58</v>
+        <v>335.16</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13085,16 +13085,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C648" s="25">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D648" s="26">
         <v>3.1</v>
       </c>
       <c r="E648" s="27">
-        <v>170.5</v>
+        <v>155</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13102,16 +13102,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C649" s="25">
-        <v>149.86000000000001</v>
+        <v>145.86000000000001</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>254.76</v>
+        <v>247.96</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13436,16 +13436,16 @@
         <v>671</v>
       </c>
       <c r="B669" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C669" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D669" s="26">
         <v>6.75</v>
       </c>
       <c r="E669" s="27">
-        <v>47.25</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13504,16 +13504,16 @@
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C673" s="25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D673" s="26">
         <v>3.5</v>
       </c>
       <c r="E673" s="27">
-        <v>38.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13555,16 +13555,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C676" s="25">
-        <v>53.5</v>
+        <v>43.5</v>
       </c>
       <c r="D676" s="26">
         <v>2.5</v>
       </c>
       <c r="E676" s="27">
-        <v>133.75</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13640,16 +13640,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C681" s="25">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D681" s="26">
         <v>2.25</v>
       </c>
       <c r="E681" s="27">
-        <v>236.25</v>
+        <v>225</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13725,16 +13725,16 @@
         <v>688</v>
       </c>
       <c r="B686" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C686" s="25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D686" s="26">
         <v>4</v>
       </c>
       <c r="E686" s="27">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -13832,16 +13832,16 @@
         <v>695</v>
       </c>
       <c r="B693" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C693" s="25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D693" s="26">
         <v>3.6</v>
       </c>
       <c r="E693" s="27">
-        <v>97.2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
@@ -13927,10 +13927,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C700" s="25">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13953,10 +13953,10 @@
         <v>704</v>
       </c>
       <c r="B702" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C702" s="25">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="D702" s="29"/>
       <c r="E702" s="28"/>
@@ -14246,10 +14246,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C725" s="25">
-        <v>-100.15</v>
+        <v>-102.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14431,11 +14431,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44459.46</v>
+        <v>43715.96</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>108010.63</v>
+        <v>106355.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -386,7 +386,7 @@
     <t>1169 PATRIKA (BIRSA SELF)</t>
   </si>
   <si>
-    <t>1170 PATRIKA (G)</t>
+    <t>1170 PATRIKA (G) (MIL JYGA)</t>
   </si>
   <si>
     <t>190 NO. ENVELOPES (POCKET)</t>
@@ -485,7 +485,7 @@
     <t>2120 PATRIKA (L) (DCU)</t>
   </si>
   <si>
-    <t>2121 PATRIKA (DC)</t>
+    <t>2121 PATRIKA</t>
   </si>
   <si>
     <t>2122 PATRIKA (09.03 800)</t>
@@ -839,7 +839,7 @@
     <t>5076 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5077 PATRIKA (2500 11.03)</t>
+    <t>5077 PATRIKA</t>
   </si>
   <si>
     <t>5078 PATRIKA (DCU)</t>
@@ -1988,7 +1988,7 @@
     <t>9337 CARDS (DC)</t>
   </si>
   <si>
-    <t>9338 CARDS</t>
+    <t>9338 CARDS  (1400 14.03)</t>
   </si>
   <si>
     <t>9339 CARDS</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="25">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>246.6</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,16 +2960,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" s="25">
-        <v>116</v>
+        <v>108.5</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" s="25">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>64.349999999999994</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" s="25">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>23.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3305,16 +3305,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C36" s="25">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>333.5</v>
+        <v>308.2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3373,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="25">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>48.15</v>
+        <v>37.450000000000003</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3407,16 +3407,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42" s="25">
-        <v>59.5</v>
+        <v>54.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>145.69999999999999</v>
+        <v>133.46</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C43" s="25">
-        <v>89.5</v>
+        <v>77</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>220.66</v>
+        <v>189.84</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C47" s="25">
-        <v>177.5</v>
+        <v>135.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>224.81</v>
+        <v>171.75</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,13 +3512,13 @@
         <v>84</v>
       </c>
       <c r="C48" s="25">
-        <v>72.349999999999994</v>
+        <v>109.35</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>92.03</v>
+        <v>138.88999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3526,16 +3526,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C49" s="25">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>357</v>
+        <v>352.8</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3543,16 +3543,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C50" s="25">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>88.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3560,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C51" s="25">
-        <v>156.5</v>
+        <v>150</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>281.7</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3577,16 +3577,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C52" s="25">
-        <v>21.5</v>
+        <v>12.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>53.75</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3611,16 +3611,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="25">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>387.75</v>
+        <v>382.25</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3645,16 +3645,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C56" s="25">
-        <v>150.5</v>
+        <v>135.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>270.89999999999998</v>
+        <v>243.9</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3679,16 +3679,16 @@
         <v>60</v>
       </c>
       <c r="B58" s="24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C58" s="25">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D58" s="26">
         <v>2.1</v>
       </c>
       <c r="E58" s="27">
-        <v>79.8</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3696,16 +3696,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C59" s="25">
-        <v>64.25</v>
+        <v>61.25</v>
       </c>
       <c r="D59" s="26">
         <v>1.9</v>
       </c>
       <c r="E59" s="27">
-        <v>122.08</v>
+        <v>116.38</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3713,16 +3713,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C60" s="25">
-        <v>912.5</v>
+        <v>897.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1038.04</v>
+        <v>1020.98</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="25">
-        <v>968.5</v>
+        <v>965.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1103.45</v>
+        <v>1100.03</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3764,16 +3764,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C63" s="25">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>74.25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3809,16 +3809,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" s="25">
-        <v>31</v>
+        <v>26.5</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>51.15</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3837,16 +3837,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C68" s="25">
-        <v>368.5</v>
+        <v>364.5</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>608.03</v>
+        <v>601.42999999999995</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3854,16 +3854,16 @@
         <v>71</v>
       </c>
       <c r="B69" s="24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C69" s="25">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D69" s="26">
         <v>1.65</v>
       </c>
       <c r="E69" s="27">
-        <v>234.3</v>
+        <v>201.3</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,16 +3871,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C70" s="25">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>518</v>
+        <v>477.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3905,16 +3905,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C72" s="25">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>429.8</v>
+        <v>415.8</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3922,16 +3922,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C73" s="25">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3939,16 +3939,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C74" s="25">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>106.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3956,33 +3956,27 @@
         <v>77</v>
       </c>
       <c r="B75" s="24">
-        <v>119</v>
-      </c>
-      <c r="C75" s="25">
-        <v>29.5</v>
-      </c>
-      <c r="D75" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E75" s="27">
-        <v>35.4</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C75" s="28"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="28"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="23" t="s">
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C76" s="25">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>513.6</v>
+        <v>492</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4007,16 +4001,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C78" s="25">
-        <v>269.5</v>
+        <v>237.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>323.39999999999998</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4024,16 +4018,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C79" s="25">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>736.8</v>
+        <v>724.8</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C84" s="25">
-        <v>1375.5</v>
+        <v>1322.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1788.15</v>
+        <v>1719.25</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4126,16 +4120,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C85" s="25">
-        <v>1336.5</v>
+        <v>1319.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1737.45</v>
+        <v>1715.35</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4160,16 +4154,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C87" s="25">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1315.8</v>
+        <v>1305.5999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" s="25">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>293.69</v>
+        <v>319.12</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,16 +4205,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C90" s="25">
-        <v>286.7</v>
+        <v>283.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>367.75</v>
+        <v>363.9</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,16 +4222,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C91" s="25">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>71.77</v>
+        <v>67.290000000000006</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4286,16 +4280,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C95" s="25">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>359.1</v>
+        <v>354.6</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4303,16 +4297,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C96" s="25">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>111.6</v>
+        <v>98.1</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4331,16 +4325,16 @@
         <v>100</v>
       </c>
       <c r="B98" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98" s="25">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D98" s="26">
         <v>1.65</v>
       </c>
       <c r="E98" s="27">
-        <v>214.5</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4348,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C99" s="25">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>683.1</v>
+        <v>645.15</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4395,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C102" s="25">
-        <v>227.5</v>
+        <v>210.5</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>195.04</v>
+        <v>180.47</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4427,16 +4421,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C104" s="25">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>380</v>
+        <v>367.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4478,16 +4472,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C107" s="25">
-        <v>309.5</v>
+        <v>288.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>773.75</v>
+        <v>721.25</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4495,16 +4489,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C108" s="25">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>727.5</v>
+        <v>695</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4512,10 +4506,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C109" s="25">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4601,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C116" s="25">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4627,9 +4621,11 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>1</v>
-      </c>
-      <c r="C118" s="28"/>
+        <v>3</v>
+      </c>
+      <c r="C118" s="25">
+        <v>-10</v>
+      </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
     </row>
@@ -4668,10 +4664,10 @@
         <v>123</v>
       </c>
       <c r="B121" s="24">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C121" s="25">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D121" s="29"/>
       <c r="E121" s="28"/>
@@ -4701,10 +4697,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C124" s="25">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
@@ -4820,16 +4816,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C133" s="25">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>-187.5</v>
+        <v>-156.25</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4874,13 +4870,13 @@
         <v>29</v>
       </c>
       <c r="C136" s="25">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>6.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4955,15 +4951,17 @@
       <c r="A141" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B141" s="24"/>
+      <c r="B141" s="24">
+        <v>1</v>
+      </c>
       <c r="C141" s="25">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D141" s="26">
         <v>12.5</v>
       </c>
       <c r="E141" s="27">
-        <v>387.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5271,16 +5269,16 @@
         <v>162</v>
       </c>
       <c r="B160" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C160" s="25">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D160" s="26">
         <v>11.5</v>
       </c>
       <c r="E160" s="27">
-        <v>345</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5333,16 +5331,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C164" s="25">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>126.5</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5427,16 @@
         <v>172</v>
       </c>
       <c r="B170" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C170" s="25">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D170" s="26">
         <v>0.89</v>
       </c>
       <c r="E170" s="27">
-        <v>111.97</v>
+        <v>108.41</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,10 +5461,10 @@
         <v>174</v>
       </c>
       <c r="B172" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C172" s="25">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D172" s="29"/>
       <c r="E172" s="28"/>
@@ -5535,13 +5533,13 @@
         <v>8</v>
       </c>
       <c r="C177" s="25">
-        <v>0.95</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D177" s="26">
         <v>3.25</v>
       </c>
       <c r="E177" s="27">
-        <v>3.09</v>
+        <v>29.09</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -5549,16 +5547,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C178" s="25">
-        <v>95.5</v>
+        <v>71</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>257.85000000000002</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5609,16 +5607,16 @@
         <v>184</v>
       </c>
       <c r="B182" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C182" s="25">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D182" s="26">
         <v>2.8</v>
       </c>
       <c r="E182" s="27">
-        <v>142.96</v>
+        <v>128.94999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5660,16 +5658,16 @@
         <v>187</v>
       </c>
       <c r="B185" s="24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C185" s="25">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D185" s="26">
         <v>3.33</v>
       </c>
       <c r="E185" s="27">
-        <v>56.61</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5733,16 +5731,16 @@
         <v>192</v>
       </c>
       <c r="B190" s="24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C190" s="25">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="D190" s="26">
         <v>2.76</v>
       </c>
       <c r="E190" s="27">
-        <v>52.48</v>
+        <v>40.049999999999997</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5750,16 +5748,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C191" s="25">
-        <v>181.81</v>
+        <v>180.31</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>481.8</v>
+        <v>477.82</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5863,16 +5861,16 @@
         <v>200</v>
       </c>
       <c r="B198" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C198" s="25">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D198" s="26">
         <v>4.5</v>
       </c>
       <c r="E198" s="27">
-        <v>33.75</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -5925,16 +5923,16 @@
         <v>204</v>
       </c>
       <c r="B202" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C202" s="25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D202" s="26">
         <v>4.5</v>
       </c>
       <c r="E202" s="27">
-        <v>29.25</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5993,16 +5991,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C206" s="25">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>588.6</v>
+        <v>575.1</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6010,16 +6008,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C207" s="25">
-        <v>31.5</v>
+        <v>30.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>81.900000000000006</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6095,16 +6093,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C212" s="25">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1026.04</v>
+        <v>1022.11</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6146,16 +6144,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C215" s="25">
-        <v>248.5</v>
+        <v>240.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>670.95</v>
+        <v>649.35</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6214,16 +6212,16 @@
         <v>221</v>
       </c>
       <c r="B219" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C219" s="25">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
       <c r="D219" s="26">
         <v>3</v>
       </c>
       <c r="E219" s="27">
-        <v>115.5</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6418,16 +6416,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C231" s="25">
-        <v>69</v>
+        <v>62.5</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>241.5</v>
+        <v>218.75</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6446,16 +6444,16 @@
         <v>235</v>
       </c>
       <c r="B233" s="24">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C233" s="25">
-        <v>64.38</v>
+        <v>49.88</v>
       </c>
       <c r="D233" s="26">
         <v>3.25</v>
       </c>
       <c r="E233" s="27">
-        <v>209.24</v>
+        <v>162.11000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6463,16 +6461,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C234" s="25">
-        <v>30.5</v>
+        <v>27.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>99.13</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6622,16 +6620,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C245" s="25">
-        <v>46.5</v>
+        <v>43.5</v>
       </c>
       <c r="D245" s="26">
         <v>4.8</v>
       </c>
       <c r="E245" s="27">
-        <v>223.2</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6639,16 +6637,16 @@
         <v>248</v>
       </c>
       <c r="B246" s="24">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C246" s="25">
-        <v>85.4</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="D246" s="26">
         <v>6.3</v>
       </c>
       <c r="E246" s="27">
-        <v>538.02</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6656,16 +6654,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C247" s="25">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>478.5</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6707,16 +6705,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C250" s="25">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>577.20000000000005</v>
+        <v>557.70000000000005</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6724,16 +6722,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C251" s="25">
-        <v>162</v>
+        <v>154.5</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>631.79999999999995</v>
+        <v>602.54999999999995</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6786,16 +6784,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C255" s="25">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>77</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6938,16 +6936,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C265" s="25">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1129.92</v>
+        <v>1121.3599999999999</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7003,13 +7001,13 @@
         <v>81</v>
       </c>
       <c r="C269" s="25">
-        <v>-8</v>
+        <v>17</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>-24.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7028,16 +7026,16 @@
         <v>273</v>
       </c>
       <c r="B271" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C271" s="25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="D271" s="26">
         <v>4.5</v>
       </c>
       <c r="E271" s="27">
-        <v>60.75</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -7045,16 +7043,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C272" s="25">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="D272" s="26">
         <v>6.25</v>
       </c>
       <c r="E272" s="27">
-        <v>109.38</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7096,16 +7094,16 @@
         <v>277</v>
       </c>
       <c r="B275" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C275" s="25">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D275" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E275" s="27">
-        <v>506.25</v>
+        <v>479.84</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7155,13 +7153,13 @@
         <v>28</v>
       </c>
       <c r="C279" s="25">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D279" s="26">
         <v>6.5</v>
       </c>
       <c r="E279" s="27">
-        <v>104</v>
+        <v>169</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7184,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C281" s="25">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D281" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E281" s="27">
-        <v>712.49</v>
+        <v>649.48</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,16 +7212,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C283" s="25">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>302.47000000000003</v>
+        <v>278.83999999999997</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7231,16 +7229,16 @@
         <v>286</v>
       </c>
       <c r="B284" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C284" s="25">
-        <v>65</v>
+        <v>64.5</v>
       </c>
       <c r="D284" s="26">
         <v>6.19</v>
       </c>
       <c r="E284" s="27">
-        <v>402.14</v>
+        <v>399.05</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7316,16 +7314,16 @@
         <v>291</v>
       </c>
       <c r="B289" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C289" s="25">
-        <v>24.75</v>
+        <v>13.25</v>
       </c>
       <c r="D289" s="26">
         <v>5.97</v>
       </c>
       <c r="E289" s="27">
-        <v>147.76</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7401,16 +7399,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C294" s="25">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D294" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E294" s="27">
-        <v>522.98</v>
+        <v>493.66</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7452,16 +7450,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C297" s="25">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1559.85</v>
+        <v>1553.83</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,16 +7484,16 @@
         <v>301</v>
       </c>
       <c r="B299" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C299" s="25">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D299" s="26">
         <v>4.2699999999999996</v>
       </c>
       <c r="E299" s="27">
-        <v>1024.3900000000001</v>
+        <v>973.17</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7554,16 +7552,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C303" s="25">
-        <v>270.25</v>
+        <v>268.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1161.54</v>
+        <v>1152.95</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7731,16 +7729,16 @@
         <v>316</v>
       </c>
       <c r="B314" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C314" s="25">
-        <v>43.95</v>
+        <v>42.95</v>
       </c>
       <c r="D314" s="26">
         <v>9.4499999999999993</v>
       </c>
       <c r="E314" s="27">
-        <v>415.33</v>
+        <v>405.88</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -8034,16 +8032,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C333" s="25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D333" s="26">
         <v>8</v>
       </c>
       <c r="E333" s="27">
-        <v>240.03</v>
+        <v>208.03</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8079,16 +8077,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C336" s="25">
-        <v>42.5</v>
+        <v>33.5</v>
       </c>
       <c r="D336" s="26">
         <v>9</v>
       </c>
       <c r="E336" s="27">
-        <v>382.5</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8096,16 +8094,16 @@
         <v>339</v>
       </c>
       <c r="B337" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C337" s="25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="D337" s="26">
         <v>9</v>
       </c>
       <c r="E337" s="27">
-        <v>157.5</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -8320,16 +8318,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C351" s="25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>273.24</v>
+        <v>261.36</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8371,16 +8369,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C354" s="25">
-        <v>62.35</v>
+        <v>57.85</v>
       </c>
       <c r="D354" s="26">
         <v>4.75</v>
       </c>
       <c r="E354" s="27">
-        <v>296.16000000000003</v>
+        <v>274.79000000000002</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8454,16 +8452,16 @@
         <v>361</v>
       </c>
       <c r="B359" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C359" s="25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D359" s="26">
         <v>6.64</v>
       </c>
       <c r="E359" s="27">
-        <v>106.26</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8550,16 +8548,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C365" s="25">
-        <v>40.5</v>
+        <v>37.5</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>240.57</v>
+        <v>222.75</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8567,16 +8565,16 @@
         <v>368</v>
       </c>
       <c r="B366" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C366" s="25">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D366" s="26">
         <v>7.2</v>
       </c>
       <c r="E366" s="27">
-        <v>169.2</v>
+        <v>154.80000000000001</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8601,16 +8599,16 @@
         <v>370</v>
       </c>
       <c r="B368" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C368" s="25">
-        <v>36.5</v>
+        <v>34</v>
       </c>
       <c r="D368" s="26">
         <v>7.13</v>
       </c>
       <c r="E368" s="27">
-        <v>260.25</v>
+        <v>242.42</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8635,16 +8633,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C370" s="25">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>613.79999999999995</v>
+        <v>594</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8703,16 +8701,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C374" s="25">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D374" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E374" s="27">
-        <v>246</v>
+        <v>229.6</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8720,16 +8718,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C375" s="25">
-        <v>24.83</v>
+        <v>23.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>111.74</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8788,16 +8786,16 @@
         <v>381</v>
       </c>
       <c r="B379" s="24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C379" s="25">
-        <v>31.5</v>
+        <v>33</v>
       </c>
       <c r="D379" s="26">
         <v>7</v>
       </c>
       <c r="E379" s="27">
-        <v>220.5</v>
+        <v>231</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -8822,16 +8820,16 @@
         <v>383</v>
       </c>
       <c r="B381" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C381" s="25">
-        <v>88.5</v>
+        <v>86.5</v>
       </c>
       <c r="D381" s="26">
         <v>3.6</v>
       </c>
       <c r="E381" s="27">
-        <v>318.60000000000002</v>
+        <v>311.39999999999998</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -8856,16 +8854,16 @@
         <v>385</v>
       </c>
       <c r="B383" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C383" s="25">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="D383" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E383" s="27">
-        <v>219.3</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -9037,16 +9035,16 @@
         <v>396</v>
       </c>
       <c r="B394" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C394" s="25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D394" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E394" s="27">
-        <v>139.19999999999999</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -9086,16 +9084,16 @@
         <v>399</v>
       </c>
       <c r="B397" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C397" s="25">
-        <v>31.5</v>
+        <v>27.5</v>
       </c>
       <c r="D397" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E397" s="27">
-        <v>269.33</v>
+        <v>235.13</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -9221,16 +9219,16 @@
         <v>408</v>
       </c>
       <c r="B406" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C406" s="25">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D406" s="26">
         <v>7.5</v>
       </c>
       <c r="E406" s="27">
-        <v>225</v>
+        <v>213.75</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -9507,16 +9505,16 @@
         <v>426</v>
       </c>
       <c r="B424" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C424" s="25">
-        <v>3</v>
+        <v>-2.5</v>
       </c>
       <c r="D424" s="26">
         <v>9</v>
       </c>
       <c r="E424" s="27">
-        <v>27</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -9815,15 +9813,9 @@
       <c r="B444" s="24">
         <v>5</v>
       </c>
-      <c r="C444" s="25">
-        <v>-2</v>
-      </c>
-      <c r="D444" s="26">
-        <v>15.5</v>
-      </c>
-      <c r="E444" s="27">
-        <v>-31</v>
-      </c>
+      <c r="C444" s="28"/>
+      <c r="D444" s="29"/>
+      <c r="E444" s="28"/>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="23" t="s">
@@ -9912,13 +9904,13 @@
         <v>25</v>
       </c>
       <c r="C450" s="25">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="D450" s="26">
         <v>10.5</v>
       </c>
       <c r="E450" s="27">
-        <v>110.25</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -9943,16 +9935,16 @@
         <v>454</v>
       </c>
       <c r="B452" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C452" s="25">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D452" s="26">
         <v>16.3</v>
       </c>
       <c r="E452" s="27">
-        <v>73.349999999999994</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -10135,16 +10127,16 @@
         <v>466</v>
       </c>
       <c r="B464" s="24">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C464" s="25">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="D464" s="26">
         <v>11</v>
       </c>
       <c r="E464" s="27">
-        <v>22</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -10318,16 +10310,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C475" s="25">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>256.5</v>
+        <v>342</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10397,16 +10389,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C480" s="25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D480" s="26">
         <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>103.33</v>
+        <v>92.99</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10542,16 +10534,16 @@
         <v>491</v>
       </c>
       <c r="B489" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C489" s="25">
-        <v>15.5</v>
+        <v>7.5</v>
       </c>
       <c r="D489" s="26">
         <v>9</v>
       </c>
       <c r="E489" s="27">
-        <v>139.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -10752,13 +10744,13 @@
         <v>30</v>
       </c>
       <c r="C502" s="25">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>11.25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -11112,16 +11104,16 @@
         <v>527</v>
       </c>
       <c r="B525" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C525" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D525" s="26">
         <v>4.5</v>
       </c>
       <c r="E525" s="27">
-        <v>85.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -11248,16 +11240,16 @@
         <v>535</v>
       </c>
       <c r="B533" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C533" s="25">
-        <v>52.5</v>
+        <v>50.5</v>
       </c>
       <c r="D533" s="26">
         <v>3</v>
       </c>
       <c r="E533" s="27">
-        <v>157.5</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11363,16 +11355,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C540" s="25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="D540" s="26">
         <v>2.84</v>
       </c>
       <c r="E540" s="27">
-        <v>38.39</v>
+        <v>35.549999999999997</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11380,16 +11372,16 @@
         <v>543</v>
       </c>
       <c r="B541" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C541" s="25">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="D541" s="26">
         <v>1.8</v>
       </c>
       <c r="E541" s="27">
-        <v>58.5</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -11482,27 +11474,33 @@
         <v>549</v>
       </c>
       <c r="B547" s="24">
-        <v>13</v>
-      </c>
-      <c r="C547" s="28"/>
-      <c r="D547" s="29"/>
-      <c r="E547" s="28"/>
+        <v>12</v>
+      </c>
+      <c r="C547" s="25">
+        <v>3</v>
+      </c>
+      <c r="D547" s="26">
+        <v>6.5</v>
+      </c>
+      <c r="E547" s="27">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="23" t="s">
         <v>550</v>
       </c>
       <c r="B548" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C548" s="25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D548" s="26">
         <v>4.75</v>
       </c>
       <c r="E548" s="27">
-        <v>83.13</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -11578,16 +11576,16 @@
         <v>555</v>
       </c>
       <c r="B553" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C553" s="25">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D553" s="26">
         <v>3.1</v>
       </c>
       <c r="E553" s="27">
-        <v>65.099999999999994</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11598,13 +11596,13 @@
         <v>40</v>
       </c>
       <c r="C554" s="25">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D554" s="26">
         <v>9.5</v>
       </c>
       <c r="E554" s="27">
-        <v>133</v>
+        <v>190</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
@@ -11646,16 +11644,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C557" s="25">
-        <v>36.700000000000003</v>
+        <v>27.2</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>143.13</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11665,9 +11663,15 @@
       <c r="B558" s="24">
         <v>32</v>
       </c>
-      <c r="C558" s="28"/>
-      <c r="D558" s="29"/>
-      <c r="E558" s="28"/>
+      <c r="C558" s="25">
+        <v>11</v>
+      </c>
+      <c r="D558" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E558" s="27">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="23" t="s">
@@ -11753,16 +11757,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C564" s="25">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="D564" s="26">
         <v>3.14</v>
       </c>
       <c r="E564" s="27">
-        <v>81.010000000000005</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11821,16 +11825,16 @@
         <v>570</v>
       </c>
       <c r="B568" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C568" s="25">
-        <v>47.5</v>
+        <v>46</v>
       </c>
       <c r="D568" s="26">
         <v>3.5</v>
       </c>
       <c r="E568" s="27">
-        <v>166.25</v>
+        <v>161</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -11855,16 +11859,16 @@
         <v>572</v>
       </c>
       <c r="B570" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C570" s="25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D570" s="26">
         <v>3.6</v>
       </c>
       <c r="E570" s="27">
-        <v>64.8</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -11889,16 +11893,16 @@
         <v>574</v>
       </c>
       <c r="B572" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C572" s="25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D572" s="26">
         <v>2.66</v>
       </c>
       <c r="E572" s="27">
-        <v>37.24</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -11940,16 +11944,16 @@
         <v>577</v>
       </c>
       <c r="B575" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C575" s="25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D575" s="26">
         <v>2.35</v>
       </c>
       <c r="E575" s="27">
-        <v>47</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12008,16 +12012,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C579" s="25">
-        <v>65</v>
+        <v>58.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>91</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12059,16 +12063,16 @@
         <v>584</v>
       </c>
       <c r="B582" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C582" s="25">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D582" s="26">
         <v>1.2</v>
       </c>
       <c r="E582" s="27">
-        <v>420</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -12076,16 +12080,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C583" s="25">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D583" s="26">
         <v>1.2</v>
       </c>
       <c r="E583" s="27">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12110,10 +12114,10 @@
         <v>587</v>
       </c>
       <c r="B585" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C585" s="25">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D585" s="29"/>
       <c r="E585" s="28"/>
@@ -12126,7 +12130,7 @@
         <v>5</v>
       </c>
       <c r="C586" s="25">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="D586" s="29"/>
       <c r="E586" s="28"/>
@@ -12166,10 +12170,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C589" s="25">
-        <v>247.5</v>
+        <v>246.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12179,10 +12183,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C590" s="25">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12192,10 +12196,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C591" s="25">
-        <v>210.5</v>
+        <v>209.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12205,10 +12209,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C592" s="25">
-        <v>96</v>
+        <v>79.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12231,16 +12235,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C594" s="25">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>301.02</v>
+        <v>296.67</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12248,16 +12252,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C595" s="25">
-        <v>669</v>
+        <v>643</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>388.02</v>
+        <v>372.94</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12377,10 +12381,10 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C604" s="25">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D604" s="29"/>
       <c r="E604" s="28"/>
@@ -12601,13 +12605,13 @@
         <v>17</v>
       </c>
       <c r="C619" s="25">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="D619" s="26">
         <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>41.25</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12615,16 +12619,16 @@
         <v>622</v>
       </c>
       <c r="B620" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C620" s="25">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="D620" s="26">
         <v>5</v>
       </c>
       <c r="E620" s="27">
-        <v>52.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -12683,16 +12687,16 @@
         <v>626</v>
       </c>
       <c r="B624" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C624" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D624" s="26">
         <v>5.75</v>
       </c>
       <c r="E624" s="27">
-        <v>86.25</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -12700,16 +12704,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C625" s="25">
-        <v>19.850000000000001</v>
+        <v>31.85</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>79.400000000000006</v>
+        <v>127.4</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12802,16 +12806,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C631" s="25">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="D631" s="26">
         <v>2.76</v>
       </c>
       <c r="E631" s="27">
-        <v>177.95</v>
+        <v>175.19</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12822,13 +12826,13 @@
         <v>46</v>
       </c>
       <c r="C632" s="25">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D632" s="26">
         <v>4</v>
       </c>
       <c r="E632" s="27">
-        <v>68</v>
+        <v>164</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12839,13 +12843,13 @@
         <v>26</v>
       </c>
       <c r="C633" s="25">
-        <v>13.5</v>
+        <v>37.5</v>
       </c>
       <c r="D633" s="26">
         <v>4</v>
       </c>
       <c r="E633" s="27">
-        <v>54</v>
+        <v>150</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -12904,16 +12908,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C637" s="25">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>335.16</v>
+        <v>332.88</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13102,16 +13106,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C649" s="25">
-        <v>145.86000000000001</v>
+        <v>148.36000000000001</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>247.96</v>
+        <v>252.21</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13221,16 +13225,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C656" s="25">
-        <v>152.5</v>
+        <v>142.5</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>434.63</v>
+        <v>406.13</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13317,16 +13321,16 @@
         <v>664</v>
       </c>
       <c r="B662" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C662" s="25">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D662" s="26">
         <v>5.73</v>
       </c>
       <c r="E662" s="27">
-        <v>298.06</v>
+        <v>286.58999999999997</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -13436,16 +13440,16 @@
         <v>671</v>
       </c>
       <c r="B669" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C669" s="25">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D669" s="26">
         <v>6.75</v>
       </c>
       <c r="E669" s="27">
-        <v>30.38</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13606,16 +13610,16 @@
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C679" s="25">
-        <v>-0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="D679" s="26">
         <v>5.8</v>
       </c>
       <c r="E679" s="27">
-        <v>-2.9</v>
+        <v>-20.3</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13640,16 +13644,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C681" s="25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D681" s="26">
         <v>2.25</v>
       </c>
       <c r="E681" s="27">
-        <v>225</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13691,16 +13695,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C684" s="25">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D684" s="26">
         <v>2.75</v>
       </c>
       <c r="E684" s="27">
-        <v>214.5</v>
+        <v>211.75</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13708,16 +13712,16 @@
         <v>687</v>
       </c>
       <c r="B685" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C685" s="25">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D685" s="26">
         <v>2.75</v>
       </c>
       <c r="E685" s="27">
-        <v>96.25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -13725,16 +13729,16 @@
         <v>688</v>
       </c>
       <c r="B686" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C686" s="25">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="D686" s="26">
         <v>4</v>
       </c>
       <c r="E686" s="27">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -13770,16 +13774,16 @@
         <v>691</v>
       </c>
       <c r="B689" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C689" s="25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D689" s="26">
         <v>4.25</v>
       </c>
       <c r="E689" s="27">
-        <v>72.25</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -13875,10 +13879,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C696" s="25">
-        <v>59.34</v>
+        <v>55.84</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13927,10 +13931,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C700" s="25">
-        <v>20.5</v>
+        <v>14</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13940,10 +13944,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C701" s="25">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -13975,16 +13979,16 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C704" s="25">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="D704" s="26">
         <v>2.93</v>
       </c>
       <c r="E704" s="27">
-        <v>435.35</v>
+        <v>432.42</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
@@ -14209,10 +14213,10 @@
         <v>724</v>
       </c>
       <c r="B722" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C722" s="25">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="D722" s="29"/>
       <c r="E722" s="28"/>
@@ -14417,10 +14421,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C736" s="25">
-        <v>-530.5</v>
+        <v>-542.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14431,11 +14435,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>43715.96</v>
+        <v>43042.93</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>106355.56</v>
+        <v>104710.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 9-Mar-26</t>
+    <t>1-Jul-25 to 10-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -1304,7 +1304,7 @@
     <t>5616 PATRIKA (DCU)</t>
   </si>
   <si>
-    <t>5617 PATRIKA *-* (M)</t>
+    <t>5617 PATRIKA *-* (M) 16.03</t>
   </si>
   <si>
     <t>5618 PATRIKA (JC) *-* (M)</t>
@@ -1718,7 +1718,7 @@
     <t>7433 PATRIKA</t>
   </si>
   <si>
-    <t>7434 PATRIKA</t>
+    <t>7434 PATRIKA (AAGYI)</t>
   </si>
   <si>
     <t>7435 PATRIKA</t>
@@ -1760,7 +1760,7 @@
     <t>7447 PATRIKA</t>
   </si>
   <si>
-    <t>7448 PATRIKA</t>
+    <t>7448 PATRIKA (13.03)</t>
   </si>
   <si>
     <t>7449 PATRIKA</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" s="25">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>237.6</v>
+        <v>232.2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,16 +2909,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="25">
-        <v>147.5</v>
+        <v>144.5</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>287.63</v>
+        <v>281.77999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2977,16 +2977,16 @@
         <v>18</v>
       </c>
       <c r="B16" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="26">
         <v>2.1</v>
       </c>
       <c r="E16" s="27">
-        <v>105</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3107,16 +3107,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C24" s="25">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>86.4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>56.1</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="25">
-        <v>69</v>
+        <v>67.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3209,16 @@
         <v>32</v>
       </c>
       <c r="B30" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30" s="26">
         <v>2.38</v>
       </c>
       <c r="E30" s="27">
-        <v>11.9</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3226,16 +3226,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C31" s="25">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>31.35</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3390,16 +3390,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C41" s="25">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>121.98</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C43" s="25">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>189.84</v>
+        <v>175.04</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C47" s="25">
-        <v>135.5</v>
+        <v>133</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>171.75</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3560,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C51" s="25">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>270</v>
+        <v>583.20000000000005</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3611,16 +3611,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C54" s="25">
-        <v>139</v>
+        <v>134.5</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>382.25</v>
+        <v>369.88</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3648,13 +3648,13 @@
         <v>52</v>
       </c>
       <c r="C56" s="25">
-        <v>135.5</v>
+        <v>317.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>243.9</v>
+        <v>571.5</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3713,16 +3713,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C60" s="25">
-        <v>897.5</v>
+        <v>889.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>1020.98</v>
+        <v>1011.88</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="25">
-        <v>965.5</v>
+        <v>962.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1100.03</v>
+        <v>1096.6099999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3809,16 +3809,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66" s="25">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>43.73</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,16 +3871,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C70" s="25">
-        <v>341</v>
+        <v>601</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>477.4</v>
+        <v>841.4</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,16 +3888,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C71" s="25">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>9.8000000000000007</v>
+        <v>712.6</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3905,16 +3905,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C72" s="25">
-        <v>297</v>
+        <v>640</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>415.8</v>
+        <v>896</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3939,16 +3939,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C74" s="25">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>84</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,16 +3967,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C76" s="25">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>492</v>
+        <v>475.2</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +4001,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C78" s="25">
-        <v>237.5</v>
+        <v>226.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>285</v>
+        <v>271.8</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4018,16 +4018,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C79" s="25">
-        <v>604</v>
+        <v>558</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>724.8</v>
+        <v>669.6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4035,16 +4035,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C80" s="25">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>698.4</v>
+        <v>652.79999999999995</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,16 +4052,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C81" s="25">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>765.6</v>
+        <v>741.6</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4069,16 +4069,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C82" s="25">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>820.8</v>
+        <v>796.8</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4086,16 +4086,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C83" s="25">
-        <v>724</v>
+        <v>694</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>868.8</v>
+        <v>832.8</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C84" s="25">
-        <v>1322.5</v>
+        <v>1319.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1719.25</v>
+        <v>1715.35</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="25">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>319.12</v>
+        <v>316.19</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,16 +4205,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C90" s="25">
-        <v>283.7</v>
+        <v>280.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>363.9</v>
+        <v>360.05</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4222,16 +4222,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C91" s="25">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>67.290000000000006</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4280,16 +4280,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C95" s="25">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>354.6</v>
+        <v>341.1</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,16 +4297,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C96" s="25">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>98.1</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4389,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C102" s="25">
-        <v>210.5</v>
+        <v>203.5</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>180.47</v>
+        <v>174.47</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4421,16 +4421,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C104" s="25">
-        <v>147</v>
+        <v>133.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>367.5</v>
+        <v>333.75</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4489,16 +4489,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C108" s="25">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>695</v>
+        <v>667.5</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4506,10 +4506,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C109" s="25">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4519,10 +4519,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C110" s="25">
-        <v>356.5</v>
+        <v>353</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4595,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C116" s="25">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4621,10 +4621,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C118" s="25">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
@@ -4736,10 +4736,10 @@
         <v>129</v>
       </c>
       <c r="B127" s="24">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C127" s="25">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D127" s="29"/>
       <c r="E127" s="28"/>
@@ -4802,13 +4802,13 @@
         <v>36</v>
       </c>
       <c r="C132" s="25">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>87.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4816,16 +4816,16 @@
         <v>135</v>
       </c>
       <c r="B133" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C133" s="25">
-        <v>-12.5</v>
+        <v>6</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>-156.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4867,16 +4867,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C136" s="25">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>18.75</v>
+        <v>125</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4921,13 +4921,13 @@
         <v>38</v>
       </c>
       <c r="C139" s="25">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="D139" s="26">
-        <v>12.75</v>
+        <v>12.73</v>
       </c>
       <c r="E139" s="27">
-        <v>197.62</v>
+        <v>324.54000000000002</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4969,16 +4969,16 @@
         <v>144</v>
       </c>
       <c r="B142" s="24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C142" s="25">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D142" s="26">
         <v>18.5</v>
       </c>
       <c r="E142" s="27">
-        <v>148</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4989,13 +4989,13 @@
         <v>29</v>
       </c>
       <c r="C143" s="25">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>-37</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5003,16 +5003,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C144" s="25">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D144" s="26">
         <v>18.5</v>
       </c>
       <c r="E144" s="27">
-        <v>83.25</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5037,16 +5037,16 @@
         <v>148</v>
       </c>
       <c r="B146" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C146" s="25">
-        <v>9.77</v>
+        <v>8.27</v>
       </c>
       <c r="D146" s="26">
         <v>18.5</v>
       </c>
       <c r="E146" s="27">
-        <v>180.75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5088,16 +5088,16 @@
         <v>151</v>
       </c>
       <c r="B149" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C149" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D149" s="26">
         <v>18.5</v>
       </c>
       <c r="E149" s="27">
-        <v>74</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -5142,13 +5142,13 @@
         <v>38</v>
       </c>
       <c r="C152" s="25">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="D152" s="26">
         <v>18.5</v>
       </c>
       <c r="E152" s="27">
-        <v>157.25</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -5209,9 +5209,15 @@
       <c r="B156" s="24">
         <v>26</v>
       </c>
-      <c r="C156" s="28"/>
-      <c r="D156" s="29"/>
-      <c r="E156" s="28"/>
+      <c r="C156" s="25">
+        <v>10</v>
+      </c>
+      <c r="D156" s="26">
+        <v>11.5</v>
+      </c>
+      <c r="E156" s="27">
+        <v>115</v>
+      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="23" t="s">
@@ -5289,13 +5295,13 @@
         <v>10</v>
       </c>
       <c r="C161" s="25">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="26">
         <v>11.5</v>
       </c>
       <c r="E161" s="27">
-        <v>-80.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5320,11 +5326,17 @@
         <v>165</v>
       </c>
       <c r="B163" s="24">
-        <v>19</v>
-      </c>
-      <c r="C163" s="28"/>
-      <c r="D163" s="29"/>
-      <c r="E163" s="28"/>
+        <v>20</v>
+      </c>
+      <c r="C163" s="25">
+        <v>-1</v>
+      </c>
+      <c r="D163" s="26">
+        <v>11.5</v>
+      </c>
+      <c r="E163" s="27">
+        <v>-11.5</v>
+      </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="23" t="s">
@@ -5334,13 +5346,13 @@
         <v>42</v>
       </c>
       <c r="C164" s="25">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>97.75</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5607,16 +5619,16 @@
         <v>184</v>
       </c>
       <c r="B182" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C182" s="25">
-        <v>46</v>
+        <v>43.5</v>
       </c>
       <c r="D182" s="26">
         <v>2.8</v>
       </c>
       <c r="E182" s="27">
-        <v>128.94999999999999</v>
+        <v>121.94</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5991,16 +6003,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C206" s="25">
-        <v>213</v>
+        <v>208.5</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>575.1</v>
+        <v>562.95000000000005</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6008,16 +6020,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C207" s="25">
-        <v>30.5</v>
+        <v>27.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>79.3</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6042,16 +6054,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C209" s="25">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6093,16 +6105,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C212" s="25">
-        <v>260</v>
+        <v>256.5</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>1022.11</v>
+        <v>1008.35</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6263,16 +6275,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C222" s="25">
-        <v>76.5</v>
+        <v>74</v>
       </c>
       <c r="D222" s="26">
         <v>3.64</v>
       </c>
       <c r="E222" s="27">
-        <v>278.48</v>
+        <v>269.38</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6280,16 +6292,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C223" s="25">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>329.4</v>
+        <v>326.7</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6416,16 +6428,16 @@
         <v>233</v>
       </c>
       <c r="B231" s="24">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C231" s="25">
-        <v>62.5</v>
+        <v>58.5</v>
       </c>
       <c r="D231" s="26">
         <v>3.5</v>
       </c>
       <c r="E231" s="27">
-        <v>218.75</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6461,16 +6473,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C234" s="25">
-        <v>27.5</v>
+        <v>24.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>89.38</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6654,16 +6666,16 @@
         <v>249</v>
       </c>
       <c r="B247" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C247" s="25">
-        <v>157.5</v>
+        <v>155.5</v>
       </c>
       <c r="D247" s="26">
         <v>3</v>
       </c>
       <c r="E247" s="27">
-        <v>472.5</v>
+        <v>466.5</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6705,16 +6717,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C250" s="25">
-        <v>143</v>
+        <v>137.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>557.70000000000005</v>
+        <v>536.25</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6722,16 +6734,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C251" s="25">
-        <v>154.5</v>
+        <v>148</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>602.54999999999995</v>
+        <v>577.20000000000005</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6936,16 +6948,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C265" s="25">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1121.3599999999999</v>
+        <v>1104.24</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -6998,16 +7010,16 @@
         <v>271</v>
       </c>
       <c r="B269" s="24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C269" s="25">
-        <v>17</v>
+        <v>35.5</v>
       </c>
       <c r="D269" s="26">
         <v>3.1</v>
       </c>
       <c r="E269" s="27">
-        <v>52.7</v>
+        <v>110.05</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -7029,13 +7041,13 @@
         <v>41</v>
       </c>
       <c r="C271" s="25">
-        <v>11.5</v>
+        <v>34.5</v>
       </c>
       <c r="D271" s="26">
         <v>4.5</v>
       </c>
       <c r="E271" s="27">
-        <v>51.75</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -7060,16 +7072,16 @@
         <v>275</v>
       </c>
       <c r="B273" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C273" s="25">
-        <v>101.37</v>
+        <v>100.37</v>
       </c>
       <c r="D273" s="26">
         <v>4.25</v>
       </c>
       <c r="E273" s="27">
-        <v>430.82</v>
+        <v>426.57</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7094,16 +7106,16 @@
         <v>277</v>
       </c>
       <c r="B275" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C275" s="25">
-        <v>109</v>
+        <v>105.5</v>
       </c>
       <c r="D275" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E275" s="27">
-        <v>479.84</v>
+        <v>464.43</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7111,16 +7123,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
+        <v>29</v>
+      </c>
+      <c r="C276" s="25">
         <v>28</v>
-      </c>
-      <c r="C276" s="25">
-        <v>31</v>
       </c>
       <c r="D276" s="26">
         <v>4.28</v>
       </c>
       <c r="E276" s="27">
-        <v>132.68</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7170,13 +7182,13 @@
         <v>11</v>
       </c>
       <c r="C280" s="25">
-        <v>6.5</v>
+        <v>23.5</v>
       </c>
       <c r="D280" s="26">
         <v>5.23</v>
       </c>
       <c r="E280" s="27">
-        <v>34</v>
+        <v>122.91</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -7184,16 +7196,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C281" s="25">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D281" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E281" s="27">
-        <v>649.48</v>
+        <v>644.63</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7212,16 +7224,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C283" s="25">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>278.83999999999997</v>
+        <v>259.93</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7314,16 +7326,16 @@
         <v>291</v>
       </c>
       <c r="B289" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C289" s="25">
-        <v>13.25</v>
+        <v>13.23</v>
       </c>
       <c r="D289" s="26">
         <v>5.97</v>
       </c>
       <c r="E289" s="27">
-        <v>79.099999999999994</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7450,16 +7462,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C297" s="25">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D297" s="26">
         <v>6.07</v>
       </c>
       <c r="E297" s="27">
-        <v>1553.83</v>
+        <v>1529.77</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7864,16 +7876,16 @@
         <v>325</v>
       </c>
       <c r="B323" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C323" s="25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D323" s="26">
         <v>5.25</v>
       </c>
       <c r="E323" s="27">
-        <v>57.75</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -7898,16 +7910,16 @@
         <v>327</v>
       </c>
       <c r="B325" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C325" s="25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D325" s="26">
         <v>7.45</v>
       </c>
       <c r="E325" s="27">
-        <v>148.91</v>
+        <v>134.02000000000001</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -8032,16 +8044,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C333" s="25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D333" s="26">
         <v>8</v>
       </c>
       <c r="E333" s="27">
-        <v>208.03</v>
+        <v>200.03</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8077,16 +8089,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C336" s="25">
-        <v>33.5</v>
+        <v>24.5</v>
       </c>
       <c r="D336" s="26">
         <v>9</v>
       </c>
       <c r="E336" s="27">
-        <v>301.5</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8111,16 +8123,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C338" s="25">
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>211.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8318,16 +8330,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C351" s="25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>261.36</v>
+        <v>249.48</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8338,13 +8350,13 @@
         <v>30</v>
       </c>
       <c r="C352" s="25">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="D352" s="26">
         <v>6.4</v>
       </c>
       <c r="E352" s="27">
-        <v>51.2</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -8435,16 +8447,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C358" s="25">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="D358" s="26">
         <v>7.99</v>
       </c>
       <c r="E358" s="27">
-        <v>323.66000000000003</v>
+        <v>307.67</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8497,16 +8509,16 @@
         <v>364</v>
       </c>
       <c r="B362" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C362" s="25">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D362" s="26">
         <v>7.76</v>
       </c>
       <c r="E362" s="27">
-        <v>450.29</v>
+        <v>434.76</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8548,16 +8560,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C365" s="25">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>222.75</v>
+        <v>207.9</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8633,16 +8645,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C370" s="25">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D370" s="26">
         <v>6.6</v>
       </c>
       <c r="E370" s="27">
-        <v>594</v>
+        <v>554.4</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8718,16 +8730,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C375" s="25">
-        <v>23.83</v>
+        <v>16.329999999999998</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>107.24</v>
+        <v>73.489999999999995</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8984,16 +8996,16 @@
         <v>393</v>
       </c>
       <c r="B391" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C391" s="25">
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="D391" s="26">
         <v>5.7</v>
       </c>
       <c r="E391" s="27">
-        <v>128.25</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -9296,16 +9308,16 @@
         <v>413</v>
       </c>
       <c r="B411" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C411" s="25">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D411" s="26">
         <v>5.7</v>
       </c>
       <c r="E411" s="27">
-        <v>376.2</v>
+        <v>364.8</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -9341,16 +9353,16 @@
         <v>416</v>
       </c>
       <c r="B414" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C414" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D414" s="26">
         <v>8</v>
       </c>
       <c r="E414" s="27">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -10181,13 +10193,13 @@
         <v>17</v>
       </c>
       <c r="C467" s="25">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="D467" s="26">
         <v>15.5</v>
       </c>
       <c r="E467" s="27">
-        <v>85.25</v>
+        <v>162.75</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10242,16 +10254,16 @@
         <v>473</v>
       </c>
       <c r="B471" s="24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C471" s="25">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="D471" s="26">
         <v>12.5</v>
       </c>
       <c r="E471" s="27">
-        <v>68.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -10310,16 +10322,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C475" s="25">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>342</v>
+        <v>228</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10389,16 +10401,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C480" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D480" s="26">
         <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>92.99</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10455,16 +10467,16 @@
         <v>486</v>
       </c>
       <c r="B484" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C484" s="25">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="D484" s="26">
         <v>11.88</v>
       </c>
       <c r="E484" s="27">
-        <v>100.98</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -10741,16 +10753,16 @@
         <v>504</v>
       </c>
       <c r="B502" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C502" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>90</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -10780,16 +10792,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C505" s="25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D505" s="26">
         <v>18.5</v>
       </c>
       <c r="E505" s="27">
-        <v>101.75</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11090,13 +11102,13 @@
         <v>4</v>
       </c>
       <c r="C524" s="25">
-        <v>14.5</v>
+        <v>46.5</v>
       </c>
       <c r="D524" s="26">
         <v>6.75</v>
       </c>
       <c r="E524" s="27">
-        <v>97.88</v>
+        <v>313.88</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -11172,16 +11184,16 @@
         <v>531</v>
       </c>
       <c r="B529" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C529" s="25">
-        <v>112.5</v>
+        <v>111.5</v>
       </c>
       <c r="D529" s="26">
         <v>1.8</v>
       </c>
       <c r="E529" s="27">
-        <v>202.5</v>
+        <v>200.7</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11355,16 +11367,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C540" s="25">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="D540" s="26">
         <v>2.84</v>
       </c>
       <c r="E540" s="27">
-        <v>35.549999999999997</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11426,13 +11438,13 @@
         <v>38</v>
       </c>
       <c r="C544" s="25">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D544" s="26">
         <v>4.28</v>
       </c>
       <c r="E544" s="27">
-        <v>51.36</v>
+        <v>136.96</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11593,16 +11605,16 @@
         <v>556</v>
       </c>
       <c r="B554" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C554" s="25">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="D554" s="26">
         <v>9.5</v>
       </c>
       <c r="E554" s="27">
-        <v>190</v>
+        <v>156.75</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
@@ -11644,16 +11656,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C557" s="25">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>106.08</v>
+        <v>94.38</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11774,16 +11786,16 @@
         <v>567</v>
       </c>
       <c r="B565" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C565" s="25">
-        <v>74.25</v>
+        <v>71.25</v>
       </c>
       <c r="D565" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E565" s="27">
-        <v>170.78</v>
+        <v>163.88</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11825,16 +11837,16 @@
         <v>570</v>
       </c>
       <c r="B568" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C568" s="25">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D568" s="26">
         <v>3.5</v>
       </c>
       <c r="E568" s="27">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -12012,16 +12024,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C579" s="25">
-        <v>58.5</v>
+        <v>48.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>81.900000000000006</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12029,16 +12041,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C580" s="25">
-        <v>70</v>
+        <v>68.5</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>126</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12063,16 +12075,16 @@
         <v>584</v>
       </c>
       <c r="B582" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C582" s="25">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D582" s="26">
         <v>1.2</v>
       </c>
       <c r="E582" s="27">
-        <v>412.8</v>
+        <v>400.8</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -12170,10 +12182,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C589" s="25">
-        <v>246.5</v>
+        <v>229.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12183,10 +12195,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C590" s="25">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12209,10 +12221,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C592" s="25">
-        <v>79.5</v>
+        <v>76.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12235,16 +12247,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C594" s="25">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>296.67</v>
+        <v>287.97000000000003</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12297,16 +12309,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C598" s="25">
-        <v>106.5</v>
+        <v>104.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>90.53</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12619,16 +12631,16 @@
         <v>622</v>
       </c>
       <c r="B620" s="24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C620" s="25">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="D620" s="26">
         <v>5</v>
       </c>
       <c r="E620" s="27">
-        <v>37.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -12806,16 +12818,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C631" s="25">
-        <v>63.5</v>
+        <v>59.5</v>
       </c>
       <c r="D631" s="26">
         <v>2.76</v>
       </c>
       <c r="E631" s="27">
-        <v>175.19</v>
+        <v>164.15</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -13044,16 +13056,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C645" s="25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D645" s="26">
         <v>3.5</v>
       </c>
       <c r="E645" s="27">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13109,13 +13121,13 @@
         <v>138</v>
       </c>
       <c r="C649" s="25">
-        <v>148.36000000000001</v>
+        <v>144.36000000000001</v>
       </c>
       <c r="D649" s="26">
         <v>1.7</v>
       </c>
       <c r="E649" s="27">
-        <v>252.21</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13191,16 +13203,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C654" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D654" s="26">
         <v>8.75</v>
       </c>
       <c r="E654" s="27">
-        <v>30.63</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13287,16 +13299,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C660" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D660" s="26">
         <v>5.5</v>
       </c>
       <c r="E660" s="27">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13304,16 +13316,16 @@
         <v>663</v>
       </c>
       <c r="B661" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C661" s="25">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="D661" s="26">
         <v>3.1</v>
       </c>
       <c r="E661" s="27">
-        <v>134.85</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -13474,16 +13486,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C671" s="25">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>465</v>
+        <v>449.5</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13491,16 +13503,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C672" s="25">
-        <v>47.43</v>
+        <v>45.43</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>170.75</v>
+        <v>163.55000000000001</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13542,16 +13554,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C675" s="25">
-        <v>23.5</v>
+        <v>19.5</v>
       </c>
       <c r="D675" s="26">
         <v>3.75</v>
       </c>
       <c r="E675" s="27">
-        <v>88.13</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13613,13 +13625,13 @@
         <v>30</v>
       </c>
       <c r="C679" s="25">
-        <v>-3.5</v>
+        <v>13.5</v>
       </c>
       <c r="D679" s="26">
         <v>5.8</v>
       </c>
       <c r="E679" s="27">
-        <v>-20.3</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13879,10 +13891,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C696" s="25">
-        <v>55.84</v>
+        <v>48.84</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13892,10 +13904,10 @@
         <v>699</v>
       </c>
       <c r="B697" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C697" s="25">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="D697" s="29"/>
       <c r="E697" s="28"/>
@@ -13931,10 +13943,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C700" s="25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14250,10 +14262,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C725" s="25">
-        <v>-102.15</v>
+        <v>-104.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14421,10 +14433,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C736" s="25">
-        <v>-542.5</v>
+        <v>-545.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14435,11 +14447,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>43042.93</v>
+        <v>44116.4</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>104710.88</v>
+        <v>107118.61</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -431,7 +431,7 @@
     <t>2102 PATRIKA *-* (M) (09.03 1000)</t>
   </si>
   <si>
-    <t>2103 PATRIKA (L) (09.03 2000)</t>
+    <t>2103 PATRIKA (L)</t>
   </si>
   <si>
     <t>2104 PATRIKA (DCU)</t>
@@ -1718,7 +1718,7 @@
     <t>7433 PATRIKA</t>
   </si>
   <si>
-    <t>7434 PATRIKA (AAGYI)</t>
+    <t>7434 PATRIKA</t>
   </si>
   <si>
     <t>7435 PATRIKA</t>
@@ -2069,7 +2069,7 @@
     <t>9363 CARDS *-* (T)</t>
   </si>
   <si>
-    <t>9364 CARDS *-* (T)  09.03 1700</t>
+    <t>9364 CARDS *-* (T)</t>
   </si>
   <si>
     <t>9365 CARDS</t>
@@ -2926,16 +2926,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="25">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>263.25</v>
+        <v>253.5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2943,16 +2943,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" s="25">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3107,16 +3107,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="25">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>72</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3124,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" s="25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>52.8</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3192,16 +3192,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" s="26">
         <v>2.6</v>
       </c>
       <c r="E29" s="27">
-        <v>54.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3305,16 +3305,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" s="25">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>308.2</v>
+        <v>301.3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C47" s="25">
-        <v>133</v>
+        <v>129.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>168.58</v>
+        <v>164.15</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" s="25">
-        <v>109.35</v>
+        <v>107.35</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>138.88999999999999</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3560,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C51" s="25">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>583.20000000000005</v>
+        <v>568.79999999999995</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3645,16 +3645,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" s="25">
-        <v>317.5</v>
+        <v>314</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>571.5</v>
+        <v>565.20000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3792,16 +3792,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C65" s="25">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>481.8</v>
+        <v>476.85</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3922,16 +3922,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C73" s="25">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>714</v>
+        <v>709.8</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4103,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C84" s="25">
-        <v>1319.5</v>
+        <v>1311.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1715.35</v>
+        <v>1704.95</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,16 +4154,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C87" s="25">
-        <v>768</v>
+        <v>764.5</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1305.5999999999999</v>
+        <v>1299.6500000000001</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,16 +4188,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C89" s="25">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>316.19</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4342,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C99" s="25">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>645.15</v>
+        <v>640.20000000000005</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4389,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C102" s="25">
-        <v>203.5</v>
+        <v>201</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>174.47</v>
+        <v>172.32</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4595,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C116" s="25">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4608,10 +4608,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C117" s="25">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4867,16 +4867,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C136" s="25">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>125</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4918,16 +4918,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C139" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D139" s="26">
         <v>12.73</v>
       </c>
       <c r="E139" s="27">
-        <v>324.54000000000002</v>
+        <v>299.08999999999997</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,17 +5326,11 @@
         <v>165</v>
       </c>
       <c r="B163" s="24">
-        <v>20</v>
-      </c>
-      <c r="C163" s="25">
-        <v>-1</v>
-      </c>
-      <c r="D163" s="26">
-        <v>11.5</v>
-      </c>
-      <c r="E163" s="27">
-        <v>-11.5</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C163" s="28"/>
+      <c r="D163" s="29"/>
+      <c r="E163" s="28"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="23" t="s">
@@ -5636,16 +5630,16 @@
         <v>185</v>
       </c>
       <c r="B183" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C183" s="25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D183" s="26">
         <v>4.0999999999999996</v>
       </c>
       <c r="E183" s="27">
-        <v>45.1</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5670,16 +5664,16 @@
         <v>187</v>
       </c>
       <c r="B185" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C185" s="25">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D185" s="26">
         <v>3.33</v>
       </c>
       <c r="E185" s="27">
-        <v>33.299999999999997</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -6003,16 +5997,16 @@
         <v>208</v>
       </c>
       <c r="B206" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C206" s="25">
-        <v>208.5</v>
+        <v>206.5</v>
       </c>
       <c r="D206" s="26">
         <v>2.7</v>
       </c>
       <c r="E206" s="27">
-        <v>562.95000000000005</v>
+        <v>557.54999999999995</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6020,16 +6014,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C207" s="25">
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="D207" s="26">
         <v>2.6</v>
       </c>
       <c r="E207" s="27">
-        <v>71.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6156,16 +6150,16 @@
         <v>217</v>
       </c>
       <c r="B215" s="24">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C215" s="25">
-        <v>240.5</v>
+        <v>236.5</v>
       </c>
       <c r="D215" s="26">
         <v>2.7</v>
       </c>
       <c r="E215" s="27">
-        <v>649.35</v>
+        <v>638.54999999999995</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6173,16 +6167,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C216" s="25">
-        <v>102.5</v>
+        <v>100.5</v>
       </c>
       <c r="D216" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E216" s="27">
-        <v>235.75</v>
+        <v>231.15</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6241,16 +6235,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C220" s="25">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D220" s="26">
         <v>3.93</v>
       </c>
       <c r="E220" s="27">
-        <v>695.46</v>
+        <v>691.54</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6258,16 +6252,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C221" s="25">
-        <v>172.75</v>
+        <v>171.75</v>
       </c>
       <c r="D221" s="26">
         <v>3.25</v>
       </c>
       <c r="E221" s="27">
-        <v>561.44000000000005</v>
+        <v>558.19000000000005</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6292,16 +6286,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C223" s="25">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>326.7</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6473,16 +6467,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C234" s="25">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.25</v>
       </c>
       <c r="E234" s="27">
-        <v>79.63</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6948,16 +6942,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C265" s="25">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1104.24</v>
+        <v>1095.68</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7241,16 +7235,16 @@
         <v>286</v>
       </c>
       <c r="B284" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C284" s="25">
-        <v>64.5</v>
+        <v>62.5</v>
       </c>
       <c r="D284" s="26">
         <v>6.19</v>
       </c>
       <c r="E284" s="27">
-        <v>399.05</v>
+        <v>386.68</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7993,16 +7987,16 @@
         <v>332</v>
       </c>
       <c r="B330" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C330" s="25">
-        <v>125.91</v>
+        <v>115.91</v>
       </c>
       <c r="D330" s="26">
         <v>4.28</v>
       </c>
       <c r="E330" s="27">
-        <v>538.89</v>
+        <v>496.09</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -8010,16 +8004,16 @@
         <v>333</v>
       </c>
       <c r="B331" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C331" s="25">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D331" s="26">
         <v>4.28</v>
       </c>
       <c r="E331" s="27">
-        <v>714.76</v>
+        <v>671.96</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -8089,16 +8083,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C336" s="25">
-        <v>24.5</v>
+        <v>33.5</v>
       </c>
       <c r="D336" s="26">
         <v>9</v>
       </c>
       <c r="E336" s="27">
-        <v>220.5</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8313,16 +8307,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C350" s="25">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="D350" s="26">
         <v>5.7</v>
       </c>
       <c r="E350" s="27">
-        <v>185.25</v>
+        <v>173.85</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8611,16 +8605,16 @@
         <v>370</v>
       </c>
       <c r="B368" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C368" s="25">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="D368" s="26">
         <v>7.13</v>
       </c>
       <c r="E368" s="27">
-        <v>242.42</v>
+        <v>238.86</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -10254,16 +10248,16 @@
         <v>473</v>
       </c>
       <c r="B471" s="24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C471" s="25">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D471" s="26">
         <v>12.5</v>
       </c>
       <c r="E471" s="27">
-        <v>6.25</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -10322,16 +10316,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C475" s="25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10401,16 +10395,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C480" s="25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D480" s="26">
         <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>82.66</v>
+        <v>92.99</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10753,16 +10747,16 @@
         <v>504</v>
       </c>
       <c r="B502" s="24">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C502" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D502" s="26">
         <v>11.25</v>
       </c>
       <c r="E502" s="27">
-        <v>67.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -10792,16 +10786,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C505" s="25">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D505" s="26">
         <v>18.5</v>
       </c>
       <c r="E505" s="27">
-        <v>83.25</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11102,13 +11096,13 @@
         <v>4</v>
       </c>
       <c r="C524" s="25">
-        <v>46.5</v>
+        <v>14.5</v>
       </c>
       <c r="D524" s="26">
         <v>6.75</v>
       </c>
       <c r="E524" s="27">
-        <v>313.88</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -11150,16 +11144,16 @@
         <v>529</v>
       </c>
       <c r="B527" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C527" s="25">
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
       <c r="D527" s="26">
         <v>1.4</v>
       </c>
       <c r="E527" s="27">
-        <v>39.9</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11201,16 +11195,16 @@
         <v>532</v>
       </c>
       <c r="B530" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C530" s="25">
-        <v>44.5</v>
+        <v>39.5</v>
       </c>
       <c r="D530" s="26">
         <v>1.95</v>
       </c>
       <c r="E530" s="27">
-        <v>86.78</v>
+        <v>77.03</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -11401,17 +11395,11 @@
         <v>544</v>
       </c>
       <c r="B542" s="24">
-        <v>30</v>
-      </c>
-      <c r="C542" s="25">
-        <v>4.5</v>
-      </c>
-      <c r="D542" s="26">
-        <v>2</v>
-      </c>
-      <c r="E542" s="27">
-        <v>9</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C542" s="28"/>
+      <c r="D542" s="29"/>
+      <c r="E542" s="28"/>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="23" t="s">
@@ -11452,16 +11440,16 @@
         <v>547</v>
       </c>
       <c r="B545" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C545" s="25">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D545" s="26">
         <v>3.56</v>
       </c>
       <c r="E545" s="27">
-        <v>16.02</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -11554,16 +11542,16 @@
         <v>553</v>
       </c>
       <c r="B551" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C551" s="25">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="D551" s="26">
         <v>4.75</v>
       </c>
       <c r="E551" s="27">
-        <v>125.88</v>
+        <v>121.13</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11656,16 +11644,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C557" s="25">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>94.38</v>
+        <v>92.43</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11743,9 +11731,15 @@
       <c r="B562" s="24">
         <v>20</v>
       </c>
-      <c r="C562" s="28"/>
-      <c r="D562" s="29"/>
-      <c r="E562" s="28"/>
+      <c r="C562" s="25">
+        <v>32</v>
+      </c>
+      <c r="D562" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E562" s="27">
+        <v>115.2</v>
+      </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="23" t="s">
@@ -12182,10 +12176,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C589" s="25">
-        <v>229.5</v>
+        <v>225.5</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12195,10 +12189,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C590" s="25">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12264,16 +12258,16 @@
         <v>597</v>
       </c>
       <c r="B595" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C595" s="25">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D595" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E595" s="27">
-        <v>372.94</v>
+        <v>370.62</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -12393,10 +12387,10 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C604" s="25">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D604" s="29"/>
       <c r="E604" s="28"/>
@@ -12631,16 +12625,16 @@
         <v>622</v>
       </c>
       <c r="B620" s="24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C620" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D620" s="26">
         <v>5</v>
       </c>
       <c r="E620" s="27">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -12920,16 +12914,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C637" s="25">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>332.88</v>
+        <v>326.04000000000002</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13486,16 +13480,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C671" s="25">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>449.5</v>
+        <v>446.4</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13891,10 +13885,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C696" s="25">
-        <v>48.84</v>
+        <v>49.84</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -14262,10 +14256,10 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C725" s="25">
-        <v>-104.15</v>
+        <v>-102.15</v>
       </c>
       <c r="D725" s="29"/>
       <c r="E725" s="28"/>
@@ -14433,10 +14427,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C736" s="25">
-        <v>-545.5</v>
+        <v>-546.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14447,11 +14441,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>44116.4</v>
+        <v>43941.4</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>107118.61</v>
+        <v>106810.86</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -74,7 +74,7 @@
     <t>1003 PATRIKA</t>
   </si>
   <si>
-    <t>1004 PATRIKA</t>
+    <t>1004 PATRIKA ( 6000 17.03)</t>
   </si>
   <si>
     <t>1005 PATRIKA</t>
@@ -245,7 +245,7 @@
     <t>1123 PATRIKA (LED-51)</t>
   </si>
   <si>
-    <t>1124 PATRIKA (LED-52) 09.03</t>
+    <t>1124 PATRIKA (LED-52)</t>
   </si>
   <si>
     <t>1125 PATRIKA (LED-53)</t>
@@ -440,7 +440,7 @@
     <t>2105 PATRIKA (DC)</t>
   </si>
   <si>
-    <t>2106 PATRIKA (L) (09.03 1000)</t>
+    <t>2106 PATRIKA (L)</t>
   </si>
   <si>
     <t>2107 PATRIKA *-* (M)</t>
@@ -647,7 +647,7 @@
     <t>4279 PATRIKA</t>
   </si>
   <si>
-    <t>4280 PATRIKA</t>
+    <t>4280 PATRIKA (5200  17.03)</t>
   </si>
   <si>
     <t>4281 PATRIKA</t>
@@ -2892,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="25">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>232.2</v>
+        <v>226.8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3011,16 +3011,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="25">
-        <v>32.5</v>
+        <v>22.5</v>
       </c>
       <c r="D18" s="26">
         <v>1.8</v>
       </c>
       <c r="E18" s="27">
-        <v>58.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3028,17 +3028,11 @@
         <v>21</v>
       </c>
       <c r="B19" s="24">
-        <v>4</v>
-      </c>
-      <c r="C19" s="25">
-        <v>6</v>
-      </c>
-      <c r="D19" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E19" s="27">
-        <v>10.8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="28"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
@@ -3073,16 +3067,16 @@
         <v>24</v>
       </c>
       <c r="B22" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="25">
-        <v>73.5</v>
+        <v>71</v>
       </c>
       <c r="D22" s="26">
         <v>1.8</v>
       </c>
       <c r="E22" s="27">
-        <v>132.30000000000001</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3288,16 +3282,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" s="25">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>347.3</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3305,16 +3299,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="25">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>301.3</v>
+        <v>289.8</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3322,16 +3316,16 @@
         <v>39</v>
       </c>
       <c r="B37" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" s="25">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D37" s="26">
         <v>2.66</v>
       </c>
       <c r="E37" s="27">
-        <v>58.52</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3339,16 +3333,16 @@
         <v>40</v>
       </c>
       <c r="B38" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D38" s="26">
         <v>2.76</v>
       </c>
       <c r="E38" s="27">
-        <v>33.119999999999997</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3367,16 +3361,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40" s="25">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>37.450000000000003</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3384,16 +3378,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41" s="25">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>109.14</v>
+        <v>104.86</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,16 +3480,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C47" s="25">
-        <v>116.5</v>
+        <v>114.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>147.66999999999999</v>
+        <v>145.13</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3506,13 +3500,13 @@
         <v>88</v>
       </c>
       <c r="C48" s="25">
-        <v>91.35</v>
+        <v>88.35</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>116.05</v>
+        <v>112.24</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3537,16 +3531,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C50" s="25">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3554,16 +3548,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C51" s="25">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>568.79999999999995</v>
+        <v>561.6</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3588,16 +3582,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C53" s="25">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>667.5</v>
+        <v>662.5</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3605,16 +3599,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54" s="25">
-        <v>134.5</v>
+        <v>133.5</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>369.88</v>
+        <v>367.13</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3633,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C56" s="25">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>565.20000000000005</v>
+        <v>520.20000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,16 +3650,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C57" s="25">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>247</v>
+        <v>231.8</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,16 +3752,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C63" s="25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>66</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3786,16 +3780,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" s="25">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>476.85</v>
+        <v>427.35</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3831,16 +3825,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C68" s="25">
-        <v>364.5</v>
+        <v>334.5</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>601.42999999999995</v>
+        <v>551.92999999999995</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3859,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C70" s="25">
-        <v>586.5</v>
+        <v>580.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>821.1</v>
+        <v>812.7</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3876,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C71" s="25">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>697.2</v>
+        <v>651</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3899,16 +3893,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C72" s="25">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>868</v>
+        <v>851.2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,16 +3927,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C74" s="25">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>55.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3961,16 +3955,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" s="25">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>469.2</v>
+        <v>466.8</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +3989,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C78" s="25">
-        <v>219.5</v>
+        <v>209.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>263.39999999999998</v>
+        <v>251.4</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4012,16 +4006,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C79" s="25">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>645.6</v>
+        <v>633.6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4029,16 +4023,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C80" s="25">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>616.79999999999995</v>
+        <v>604.79999999999995</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4080,16 +4074,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C83" s="25">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>832.8</v>
+        <v>820.8</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4091,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C84" s="25">
-        <v>1297</v>
+        <v>1237</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1686.1</v>
+        <v>1608.1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4114,16 +4108,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C85" s="25">
-        <v>1316.5</v>
+        <v>1313.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1711.45</v>
+        <v>1707.55</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4131,16 +4125,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C86" s="25">
-        <v>1203</v>
+        <v>1183</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2045.1</v>
+        <v>2011.1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4148,16 +4142,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C87" s="25">
-        <v>764.5</v>
+        <v>742.5</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1299.6500000000001</v>
+        <v>1262.25</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4165,16 +4159,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C88" s="25">
-        <v>1054.5</v>
+        <v>1044.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1792.65</v>
+        <v>1775.65</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4176,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C89" s="25">
-        <v>187</v>
+        <v>180.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.46</v>
       </c>
       <c r="E89" s="27">
-        <v>273.74</v>
+        <v>264.23</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4199,16 +4193,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C90" s="25">
-        <v>277.7</v>
+        <v>274.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>356.2</v>
+        <v>352.35</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4336,16 +4330,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C99" s="25">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>613.79999999999995</v>
+        <v>605.54999999999995</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4415,16 +4409,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C104" s="25">
-        <v>128.5</v>
+        <v>118.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>321.25</v>
+        <v>296.25</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4443,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C106" s="25">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>655</v>
+        <v>605</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4460,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C107" s="25">
-        <v>288.5</v>
+        <v>268.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>721.25</v>
+        <v>671.25</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4477,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C108" s="25">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>657.5</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4615,10 +4609,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C118" s="25">
-        <v>-20</v>
+        <v>-46</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
@@ -4861,16 +4855,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C136" s="25">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>143.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4895,16 +4889,16 @@
         <v>140</v>
       </c>
       <c r="B138" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C138" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138" s="26">
         <v>12.5</v>
       </c>
       <c r="E138" s="27">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5692,17 +5686,11 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>8</v>
-      </c>
-      <c r="C187" s="25">
-        <v>11</v>
-      </c>
-      <c r="D187" s="26">
-        <v>3.56</v>
-      </c>
-      <c r="E187" s="27">
-        <v>39.159999999999997</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C187" s="28"/>
+      <c r="D187" s="29"/>
+      <c r="E187" s="28"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="23" t="s">
@@ -5748,16 +5736,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C191" s="25">
-        <v>176.31</v>
+        <v>173.31</v>
       </c>
       <c r="D191" s="26">
         <v>2.65</v>
       </c>
       <c r="E191" s="27">
-        <v>467.22</v>
+        <v>459.27</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -6093,16 +6081,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C212" s="25">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>959.21</v>
+        <v>935.62</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6127,16 +6115,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C214" s="25">
-        <v>323.5</v>
+        <v>315.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.7</v>
       </c>
       <c r="E214" s="27">
-        <v>873.45</v>
+        <v>851.85</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6229,16 +6217,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C220" s="25">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D220" s="26">
         <v>3.93</v>
       </c>
       <c r="E220" s="27">
-        <v>683.68</v>
+        <v>679.75</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6280,16 +6268,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C223" s="25">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D223" s="26">
         <v>2.7</v>
       </c>
       <c r="E223" s="27">
-        <v>297</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6314,16 +6302,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C225" s="25">
-        <v>119</v>
+        <v>115.5</v>
       </c>
       <c r="D225" s="26">
         <v>2.66</v>
       </c>
       <c r="E225" s="27">
-        <v>316.54000000000002</v>
+        <v>307.23</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6477,30 +6465,34 @@
       <c r="A235" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="B235" s="24"/>
+      <c r="B235" s="24">
+        <v>1</v>
+      </c>
       <c r="C235" s="25">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D235" s="26">
         <v>3.33</v>
       </c>
       <c r="E235" s="27">
-        <v>96.57</v>
+        <v>63.27</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="B236" s="24"/>
+      <c r="B236" s="24">
+        <v>1</v>
+      </c>
       <c r="C236" s="25">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D236" s="26">
         <v>3.33</v>
       </c>
       <c r="E236" s="27">
-        <v>99.9</v>
+        <v>66.599999999999994</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6688,16 +6680,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C249" s="25">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D249" s="26">
         <v>3.8</v>
       </c>
       <c r="E249" s="27">
-        <v>349.6</v>
+        <v>338.2</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6705,16 +6697,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C250" s="25">
-        <v>130.5</v>
+        <v>124.5</v>
       </c>
       <c r="D250" s="26">
         <v>3.9</v>
       </c>
       <c r="E250" s="27">
-        <v>508.95</v>
+        <v>485.55</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6722,16 +6714,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C251" s="25">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D251" s="26">
         <v>3.9</v>
       </c>
       <c r="E251" s="27">
-        <v>573.29999999999995</v>
+        <v>534.29999999999995</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6784,16 +6776,16 @@
         <v>257</v>
       </c>
       <c r="B255" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C255" s="25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D255" s="26">
         <v>3.5</v>
       </c>
       <c r="E255" s="27">
-        <v>94.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6936,16 +6928,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C265" s="25">
-        <v>255.78</v>
+        <v>252.78</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1094.74</v>
+        <v>1081.9000000000001</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7043,16 +7035,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C272" s="25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D272" s="26">
         <v>6.25</v>
       </c>
       <c r="E272" s="27">
-        <v>131.25</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7111,16 +7103,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C276" s="25">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D276" s="26">
         <v>4.28</v>
       </c>
       <c r="E276" s="27">
-        <v>107</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7212,16 +7204,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C283" s="25">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D283" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E283" s="27">
-        <v>259.93</v>
+        <v>241.03</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7280,16 +7272,16 @@
         <v>289</v>
       </c>
       <c r="B287" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C287" s="25">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D287" s="26">
         <v>5</v>
       </c>
       <c r="E287" s="27">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -7900,16 +7892,16 @@
         <v>327</v>
       </c>
       <c r="B325" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C325" s="25">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="D325" s="26">
         <v>7.45</v>
       </c>
       <c r="E325" s="27">
-        <v>134.02000000000001</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -7967,15 +7959,17 @@
       <c r="A329" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="B329" s="24"/>
+      <c r="B329" s="24">
+        <v>1</v>
+      </c>
       <c r="C329" s="25">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="D329" s="26">
         <v>5.7</v>
       </c>
       <c r="E329" s="27">
-        <v>82.65</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -8034,16 +8028,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C333" s="25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D333" s="26">
         <v>8</v>
       </c>
       <c r="E333" s="27">
-        <v>200.03</v>
+        <v>192.03</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8113,16 +8107,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C338" s="25">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="D338" s="26">
         <v>9</v>
       </c>
       <c r="E338" s="27">
-        <v>130.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8303,16 +8297,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C350" s="25">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="D350" s="26">
         <v>5.7</v>
       </c>
       <c r="E350" s="27">
-        <v>173.85</v>
+        <v>159.6</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8320,16 +8314,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C351" s="25">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D351" s="26">
         <v>5.94</v>
       </c>
       <c r="E351" s="27">
-        <v>249.48</v>
+        <v>201.96</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8371,16 +8365,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C354" s="25">
-        <v>57.85</v>
+        <v>55.85</v>
       </c>
       <c r="D354" s="26">
         <v>4.75</v>
       </c>
       <c r="E354" s="27">
-        <v>274.79000000000002</v>
+        <v>265.29000000000002</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8550,16 +8544,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C365" s="25">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D365" s="26">
         <v>5.94</v>
       </c>
       <c r="E365" s="27">
-        <v>207.9</v>
+        <v>160.38</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8601,16 +8595,16 @@
         <v>370</v>
       </c>
       <c r="B368" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C368" s="25">
-        <v>33.5</v>
+        <v>30</v>
       </c>
       <c r="D368" s="26">
         <v>7.13</v>
       </c>
       <c r="E368" s="27">
-        <v>238.86</v>
+        <v>213.9</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8720,16 +8714,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C375" s="25">
-        <v>13.83</v>
+        <v>11.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>62.24</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8856,16 +8850,16 @@
         <v>385</v>
       </c>
       <c r="B383" s="24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C383" s="25">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="D383" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E383" s="27">
-        <v>137.69999999999999</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -8941,16 +8935,16 @@
         <v>390</v>
       </c>
       <c r="B388" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C388" s="25">
-        <v>45.2</v>
+        <v>43.2</v>
       </c>
       <c r="D388" s="26">
         <v>5.29</v>
       </c>
       <c r="E388" s="27">
-        <v>238.95</v>
+        <v>228.38</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -8969,16 +8963,16 @@
         <v>392</v>
       </c>
       <c r="B390" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C390" s="25">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="D390" s="26">
         <v>5.7</v>
       </c>
       <c r="E390" s="27">
-        <v>111.15</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -9264,16 +9258,16 @@
         <v>411</v>
       </c>
       <c r="B409" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C409" s="25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D409" s="26">
         <v>7.13</v>
       </c>
       <c r="E409" s="27">
-        <v>128.34</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -9326,16 +9320,16 @@
         <v>415</v>
       </c>
       <c r="B413" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C413" s="25">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D413" s="26">
         <v>5.2</v>
       </c>
       <c r="E413" s="27">
-        <v>286</v>
+        <v>275.60000000000002</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9375,16 +9369,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C416" s="25">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="D416" s="26">
         <v>5.3</v>
       </c>
       <c r="E416" s="27">
-        <v>235.85</v>
+        <v>222.6</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -9458,16 +9452,16 @@
         <v>423</v>
       </c>
       <c r="B421" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C421" s="25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="D421" s="26">
         <v>6.46</v>
       </c>
       <c r="E421" s="27">
-        <v>74.290000000000006</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -9971,16 +9965,16 @@
         <v>456</v>
       </c>
       <c r="B454" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C454" s="25">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D454" s="26">
         <v>9.75</v>
       </c>
       <c r="E454" s="27">
-        <v>73.13</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10180,16 +10174,16 @@
         <v>469</v>
       </c>
       <c r="B467" s="24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C467" s="25">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="D467" s="26">
         <v>15.5</v>
       </c>
       <c r="E467" s="27">
-        <v>162.75</v>
+        <v>193.75</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10312,16 +10306,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C475" s="25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>218.5</v>
+        <v>199.5</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10391,16 +10385,16 @@
         <v>482</v>
       </c>
       <c r="B480" s="24">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C480" s="25">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D480" s="26">
         <v>10.33</v>
       </c>
       <c r="E480" s="27">
-        <v>36.159999999999997</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -11157,16 +11151,16 @@
         <v>530</v>
       </c>
       <c r="B528" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C528" s="25">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D528" s="26">
         <v>1.4</v>
       </c>
       <c r="E528" s="27">
-        <v>113.4</v>
+        <v>99.4</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11208,16 +11202,16 @@
         <v>533</v>
       </c>
       <c r="B531" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C531" s="25">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="D531" s="26">
         <v>2</v>
       </c>
       <c r="E531" s="27">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -11357,16 +11351,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C540" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D540" s="26">
         <v>2.84</v>
       </c>
       <c r="E540" s="27">
-        <v>25.6</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11419,16 +11413,16 @@
         <v>546</v>
       </c>
       <c r="B544" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C544" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D544" s="26">
         <v>4.28</v>
       </c>
       <c r="E544" s="27">
-        <v>136.96</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11538,16 +11532,16 @@
         <v>553</v>
       </c>
       <c r="B551" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C551" s="25">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="D551" s="26">
         <v>4.75</v>
       </c>
       <c r="E551" s="27">
-        <v>121.13</v>
+        <v>106.88</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11555,16 +11549,16 @@
         <v>554</v>
       </c>
       <c r="B552" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C552" s="25">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="D552" s="26">
         <v>3.45</v>
       </c>
       <c r="E552" s="27">
-        <v>255.3</v>
+        <v>250.13</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11640,16 +11634,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C557" s="25">
-        <v>20.2</v>
+        <v>18.2</v>
       </c>
       <c r="D557" s="26">
         <v>3.9</v>
       </c>
       <c r="E557" s="27">
-        <v>78.78</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11827,16 +11821,16 @@
         <v>570</v>
       </c>
       <c r="B568" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C568" s="25">
-        <v>42</v>
+        <v>38.5</v>
       </c>
       <c r="D568" s="26">
         <v>3.5</v>
       </c>
       <c r="E568" s="27">
-        <v>147</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -12014,16 +12008,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C579" s="25">
-        <v>48.5</v>
+        <v>44.5</v>
       </c>
       <c r="D579" s="26">
         <v>1.4</v>
       </c>
       <c r="E579" s="27">
-        <v>67.900000000000006</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12031,16 +12025,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C580" s="25">
-        <v>63.5</v>
+        <v>45</v>
       </c>
       <c r="D580" s="26">
         <v>1.8</v>
       </c>
       <c r="E580" s="27">
-        <v>114.3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12155,16 +12149,16 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C588" s="25">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D588" s="26">
         <v>1.5</v>
       </c>
       <c r="E588" s="27">
-        <v>408</v>
+        <v>394.5</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
@@ -12185,10 +12179,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C590" s="25">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12198,10 +12192,10 @@
         <v>593</v>
       </c>
       <c r="B591" s="24">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C591" s="25">
-        <v>208.5</v>
+        <v>204.5</v>
       </c>
       <c r="D591" s="29"/>
       <c r="E591" s="28"/>
@@ -12224,10 +12218,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C593" s="25">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12237,16 +12231,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C594" s="25">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>285.36</v>
+        <v>281.88</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12271,16 +12265,16 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C596" s="25">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D596" s="26">
         <v>0.85</v>
       </c>
       <c r="E596" s="27">
-        <v>343.4</v>
+        <v>334.9</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -12299,16 +12293,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C598" s="25">
-        <v>104.5</v>
+        <v>89.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>88.83</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12344,10 +12338,10 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C601" s="25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D601" s="29"/>
       <c r="E601" s="28"/>
@@ -12357,10 +12351,10 @@
         <v>604</v>
       </c>
       <c r="B602" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C602" s="25">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D602" s="29"/>
       <c r="E602" s="28"/>
@@ -12487,16 +12481,16 @@
         <v>614</v>
       </c>
       <c r="B612" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C612" s="25">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D612" s="26">
         <v>0.85</v>
       </c>
       <c r="E612" s="27">
-        <v>14.45</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -12706,16 +12700,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C625" s="25">
-        <v>31.85</v>
+        <v>26.85</v>
       </c>
       <c r="D625" s="26">
         <v>4</v>
       </c>
       <c r="E625" s="27">
-        <v>127.4</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12859,16 +12853,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C634" s="25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D634" s="26">
         <v>1.5</v>
       </c>
       <c r="E634" s="27">
-        <v>1.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -13289,16 +13283,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C660" s="25">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D660" s="26">
         <v>5.5</v>
       </c>
       <c r="E660" s="27">
-        <v>-5.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13323,16 +13317,16 @@
         <v>664</v>
       </c>
       <c r="B662" s="24">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C662" s="25">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D662" s="26">
         <v>5.73</v>
       </c>
       <c r="E662" s="27">
-        <v>275.13</v>
+        <v>286.58999999999997</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -13357,16 +13351,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C664" s="25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>38.4</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13476,16 +13470,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C671" s="25">
-        <v>144</v>
+        <v>140.5</v>
       </c>
       <c r="D671" s="26">
         <v>3.1</v>
       </c>
       <c r="E671" s="27">
-        <v>446.4</v>
+        <v>435.55</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13493,16 +13487,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C672" s="25">
-        <v>45.43</v>
+        <v>42.43</v>
       </c>
       <c r="D672" s="26">
         <v>3.6</v>
       </c>
       <c r="E672" s="27">
-        <v>163.55000000000001</v>
+        <v>152.75</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13612,16 +13606,16 @@
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C679" s="25">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="D679" s="26">
         <v>5.8</v>
       </c>
       <c r="E679" s="27">
-        <v>72.5</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13881,10 +13875,10 @@
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C696" s="25">
-        <v>49.84</v>
+        <v>47.34</v>
       </c>
       <c r="D696" s="29"/>
       <c r="E696" s="28"/>
@@ -13946,10 +13940,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C701" s="25">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -13981,16 +13975,16 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C704" s="25">
-        <v>147.5</v>
+        <v>139.5</v>
       </c>
       <c r="D704" s="26">
         <v>2.93</v>
       </c>
       <c r="E704" s="27">
-        <v>432.42</v>
+        <v>408.97</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
@@ -14344,16 +14338,16 @@
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C731" s="25">
-        <v>52.25</v>
+        <v>50.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>130.63</v>
+        <v>125.63</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14423,10 +14417,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C736" s="25">
-        <v>-550</v>
+        <v>-555.5</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14437,11 +14431,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>43626.18</v>
+        <v>42874.18</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>106134.94</v>
+        <v>104694.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 11-Mar-26</t>
+    <t>1-Jul-25 to 12-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -428,7 +428,7 @@
     <t>2101 PATRIKA (L)-DC</t>
   </si>
   <si>
-    <t>2102 PATRIKA *-* (M) (09.03 1000)</t>
+    <t>2102 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>2103 PATRIKA (L)</t>
@@ -461,7 +461,7 @@
     <t>2112 PATRIKA (L)</t>
   </si>
   <si>
-    <t>2113 PATRIKA (L) (09.03 400)</t>
+    <t>2113 PATRIKA (L)</t>
   </si>
   <si>
     <t>2114 PATRIKA (L) (DCU)</t>
@@ -500,7 +500,7 @@
     <t>2125 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>2126 PATRIKA *-* (M) (09.03 1000)</t>
+    <t>2126 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>2127 PATRIKA *-* (M) (DCU)</t>
@@ -1988,7 +1988,7 @@
     <t>9337 CARDS (DC)</t>
   </si>
   <si>
-    <t>9338 CARDS  (1400 14.03)</t>
+    <t>9338 CARDS</t>
   </si>
   <si>
     <t>9339 CARDS</t>
@@ -3152,16 +3152,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" s="25">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,13 +3206,13 @@
         <v>35</v>
       </c>
       <c r="C30" s="25">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D30" s="26">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="E30" s="27">
-        <v>4.76</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,16 +3220,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="25">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="26">
         <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>12.83</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3237,16 +3237,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="25">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>75.599999999999994</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3395,16 +3395,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C42" s="25">
-        <v>54.5</v>
+        <v>52.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>133.46</v>
+        <v>128.56</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3480,16 +3480,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C47" s="25">
-        <v>114.5</v>
+        <v>111.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>145.13</v>
+        <v>141.33000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3497,16 +3497,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C48" s="25">
-        <v>88.35</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>112.24</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3616,16 +3616,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C55" s="25">
-        <v>239.15</v>
+        <v>236.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>657.66</v>
+        <v>649.41</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3653,13 +3653,13 @@
         <v>34</v>
       </c>
       <c r="C57" s="25">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>231.8</v>
+        <v>239.4</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3718,16 +3718,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="25">
-        <v>962.5</v>
+        <v>956.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1096.6099999999999</v>
+        <v>1089.78</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,16 +3780,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C65" s="25">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>427.35</v>
+        <v>420.75</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,16 +3859,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C70" s="25">
-        <v>580.5</v>
+        <v>564.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>812.7</v>
+        <v>790.3</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3876,16 +3876,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="25">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>651</v>
+        <v>642.6</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3893,16 +3893,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C72" s="25">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>851.2</v>
+        <v>844.2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3927,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C74" s="25">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>31.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3955,16 +3955,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C76" s="25">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>466.8</v>
+        <v>459.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4091,16 +4091,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C84" s="25">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1608.1</v>
+        <v>1600.3</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4285,16 +4285,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C96" s="25">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>85.5</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,16 +4330,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C99" s="25">
-        <v>367</v>
+        <v>364.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>605.54999999999995</v>
+        <v>601.42999999999995</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4409,16 +4409,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C104" s="25">
-        <v>118.5</v>
+        <v>113.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>296.25</v>
+        <v>283.75</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4477,16 +4477,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C108" s="25">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>650</v>
+        <v>637.5</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4685,10 +4685,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="24">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="25">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D124" s="29"/>
       <c r="E124" s="28"/>
@@ -4790,13 +4790,13 @@
         <v>36</v>
       </c>
       <c r="C132" s="25">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D132" s="26">
         <v>12.5</v>
       </c>
       <c r="E132" s="27">
-        <v>212.5</v>
+        <v>337.5</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4807,13 +4807,13 @@
         <v>63</v>
       </c>
       <c r="C133" s="25">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D133" s="26">
         <v>12.5</v>
       </c>
       <c r="E133" s="27">
-        <v>62.5</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4855,16 +4855,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C136" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4875,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="C137" s="25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D137" s="26">
         <v>12.5</v>
       </c>
       <c r="E137" s="27">
-        <v>62.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4957,16 +4957,16 @@
         <v>144</v>
       </c>
       <c r="B142" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C142" s="25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D142" s="26">
         <v>18.5</v>
       </c>
       <c r="E142" s="27">
-        <v>18.5</v>
+        <v>111</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4977,13 +4977,13 @@
         <v>29</v>
       </c>
       <c r="C143" s="25">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D143" s="26">
         <v>18.5</v>
       </c>
       <c r="E143" s="27">
-        <v>37</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5059,17 +5059,11 @@
         <v>150</v>
       </c>
       <c r="B148" s="24">
-        <v>17</v>
-      </c>
-      <c r="C148" s="25">
-        <v>3</v>
-      </c>
-      <c r="D148" s="26">
-        <v>18.5</v>
-      </c>
-      <c r="E148" s="27">
-        <v>55.5</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C148" s="28"/>
+      <c r="D148" s="29"/>
+      <c r="E148" s="28"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
@@ -5113,13 +5107,13 @@
         <v>38</v>
       </c>
       <c r="C151" s="25">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D151" s="26">
         <v>18.5</v>
       </c>
       <c r="E151" s="27">
-        <v>129.5</v>
+        <v>425.5</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -5198,13 +5192,13 @@
         <v>26</v>
       </c>
       <c r="C156" s="25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D156" s="26">
         <v>11.5</v>
       </c>
       <c r="E156" s="27">
-        <v>115</v>
+        <v>230</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5325,16 +5319,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C164" s="25">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>212.75</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5541,16 +5535,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C178" s="25">
-        <v>70.5</v>
+        <v>66</v>
       </c>
       <c r="D178" s="26">
         <v>2.7</v>
       </c>
       <c r="E178" s="27">
-        <v>190.35</v>
+        <v>178.2</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5866,16 +5860,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C199" s="25">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="D199" s="26">
         <v>4.5</v>
       </c>
       <c r="E199" s="27">
-        <v>38.25</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -6081,16 +6075,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C212" s="25">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D212" s="26">
         <v>3.93</v>
       </c>
       <c r="E212" s="27">
-        <v>935.62</v>
+        <v>923.83</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6098,16 +6092,16 @@
         <v>215</v>
       </c>
       <c r="B213" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C213" s="25">
-        <v>32</v>
+        <v>27.5</v>
       </c>
       <c r="D213" s="26">
         <v>4.5</v>
       </c>
       <c r="E213" s="27">
-        <v>144</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -6287,15 +6281,9 @@
       <c r="B224" s="24">
         <v>38</v>
       </c>
-      <c r="C224" s="25">
-        <v>1.53</v>
-      </c>
-      <c r="D224" s="26">
-        <v>3.16</v>
-      </c>
-      <c r="E224" s="27">
-        <v>4.83</v>
-      </c>
+      <c r="C224" s="28"/>
+      <c r="D224" s="29"/>
+      <c r="E224" s="28"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -6612,16 +6600,16 @@
         <v>247</v>
       </c>
       <c r="B245" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C245" s="25">
-        <v>43.5</v>
+        <v>38.5</v>
       </c>
       <c r="D245" s="26">
         <v>4.8</v>
       </c>
       <c r="E245" s="27">
-        <v>208.8</v>
+        <v>184.8</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6928,16 +6916,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C265" s="25">
-        <v>252.78</v>
+        <v>249.78</v>
       </c>
       <c r="D265" s="26">
         <v>4.28</v>
       </c>
       <c r="E265" s="27">
-        <v>1081.9000000000001</v>
+        <v>1069.06</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7544,16 +7532,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C303" s="25">
-        <v>268.25</v>
+        <v>259.25</v>
       </c>
       <c r="D303" s="26">
         <v>4.3</v>
       </c>
       <c r="E303" s="27">
-        <v>1152.95</v>
+        <v>1114.26</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7561,16 +7549,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C304" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D304" s="26">
         <v>4.75</v>
       </c>
       <c r="E304" s="27">
-        <v>90.25</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -8152,16 +8140,16 @@
         <v>343</v>
       </c>
       <c r="B341" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C341" s="25">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="D341" s="26">
         <v>9</v>
       </c>
       <c r="E341" s="27">
-        <v>144</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8527,16 +8515,16 @@
         <v>366</v>
       </c>
       <c r="B364" s="24">
+        <v>27</v>
+      </c>
+      <c r="C364" s="25">
         <v>26</v>
-      </c>
-      <c r="C364" s="25">
-        <v>26.5</v>
       </c>
       <c r="D364" s="26">
         <v>6.65</v>
       </c>
       <c r="E364" s="27">
-        <v>176.23</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -8714,16 +8702,16 @@
         <v>377</v>
       </c>
       <c r="B375" s="24">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C375" s="25">
-        <v>11.83</v>
+        <v>9.83</v>
       </c>
       <c r="D375" s="26">
         <v>4.5</v>
       </c>
       <c r="E375" s="27">
-        <v>53.24</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -10306,16 +10294,16 @@
         <v>477</v>
       </c>
       <c r="B475" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C475" s="25">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="D475" s="26">
         <v>9.5</v>
       </c>
       <c r="E475" s="27">
-        <v>199.5</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -11202,16 +11190,16 @@
         <v>533</v>
       </c>
       <c r="B531" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C531" s="25">
-        <v>46.5</v>
+        <v>45</v>
       </c>
       <c r="D531" s="26">
         <v>2</v>
       </c>
       <c r="E531" s="27">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -12149,16 +12137,16 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C588" s="25">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D588" s="26">
         <v>1.5</v>
       </c>
       <c r="E588" s="27">
-        <v>394.5</v>
+        <v>387</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
@@ -12179,10 +12167,10 @@
         <v>592</v>
       </c>
       <c r="B590" s="24">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C590" s="25">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D590" s="29"/>
       <c r="E590" s="28"/>
@@ -12205,10 +12193,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C592" s="25">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12231,16 +12219,16 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C594" s="25">
-        <v>324</v>
+        <v>323.5</v>
       </c>
       <c r="D594" s="26">
         <v>0.87</v>
       </c>
       <c r="E594" s="27">
-        <v>281.88</v>
+        <v>281.45</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -12265,16 +12253,16 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C596" s="25">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D596" s="26">
         <v>0.85</v>
       </c>
       <c r="E596" s="27">
-        <v>334.9</v>
+        <v>324.7</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -12293,16 +12281,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C598" s="25">
-        <v>89.5</v>
+        <v>88.5</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>76.08</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12904,16 +12892,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C637" s="25">
-        <v>143</v>
+        <v>139.5</v>
       </c>
       <c r="D637" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E637" s="27">
-        <v>326.04000000000002</v>
+        <v>318.06</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -13156,13 +13144,13 @@
         <v>33</v>
       </c>
       <c r="C652" s="25">
-        <v>11.5</v>
+        <v>25.5</v>
       </c>
       <c r="D652" s="26">
         <v>3.5</v>
       </c>
       <c r="E652" s="27">
-        <v>40.25</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13221,16 +13209,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C656" s="25">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D656" s="26">
         <v>2.85</v>
       </c>
       <c r="E656" s="27">
-        <v>399</v>
+        <v>396.15</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13354,13 +13342,13 @@
         <v>44</v>
       </c>
       <c r="C664" s="25">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D664" s="26">
         <v>4.8</v>
       </c>
       <c r="E664" s="27">
-        <v>33.6</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13708,16 +13696,16 @@
         <v>687</v>
       </c>
       <c r="B685" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C685" s="25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D685" s="26">
         <v>2.75</v>
       </c>
       <c r="E685" s="27">
-        <v>88</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -14195,13 +14183,13 @@
         <v>35</v>
       </c>
       <c r="C721" s="25">
-        <v>70</v>
+        <v>295</v>
       </c>
       <c r="D721" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E721" s="27">
-        <v>81.2</v>
+        <v>342.2</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -14431,11 +14419,11 @@
       </c>
       <c r="B737" s="31"/>
       <c r="C737" s="32">
-        <v>42874.18</v>
+        <v>43029.34</v>
       </c>
       <c r="D737" s="33"/>
       <c r="E737" s="34">
-        <v>104694.92</v>
+        <v>105880.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 12-Mar-26</t>
+    <t>1-Jul-25 to 13-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -455,7 +455,7 @@
     <t>2108 PATRIKA *-* (M) (DCU)</t>
   </si>
   <si>
-    <t>2109 PATRIKA (L) (09.03 1000)</t>
+    <t>2109 PATRIKA (L)</t>
   </si>
   <si>
     <t>2110 PATRIKA (DC)</t>
@@ -494,7 +494,7 @@
     <t>2121 PATRIKA</t>
   </si>
   <si>
-    <t>2122 PATRIKA (09.03 800)</t>
+    <t>2122 PATRIKA</t>
   </si>
   <si>
     <t>2123 PATRIKA (DCU)</t>
@@ -521,7 +521,7 @@
     <t>2130 PATRIKA *-* (M) (DCU)</t>
   </si>
   <si>
-    <t>2131 PATRIKA *-* (M) (DCU) (09.03 1000)</t>
+    <t>2131 PATRIKA *-* (M) (DCU)</t>
   </si>
   <si>
     <t>2132 PATRIKA *-* (M) (DCU)</t>
@@ -530,7 +530,7 @@
     <t>2133 PATRIKA</t>
   </si>
   <si>
-    <t>2134 PATRIKA *-* (M) (09.03 1000)</t>
+    <t>2134 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>2135 PATRIKA *-* (M)</t>
@@ -2898,16 +2898,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="25">
-        <v>119.5</v>
+        <v>115</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>215.1</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2952,13 +2952,13 @@
         <v>92</v>
       </c>
       <c r="C14" s="25">
-        <v>231.5</v>
+        <v>291.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>463</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="25">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="25">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3418,16 +3418,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C43" s="25">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>157.79</v>
+        <v>145.46</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3503,16 +3503,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C48" s="25">
-        <v>64.349999999999994</v>
+        <v>60.85</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>81.78</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3520,16 +3520,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C49" s="25">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>352.8</v>
+        <v>348.6</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3554,16 +3554,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C51" s="25">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>561.6</v>
+        <v>558</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3605,16 +3605,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" s="25">
-        <v>133.5</v>
+        <v>132</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>367.13</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3639,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C56" s="25">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>513</v>
+        <v>502.2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,16 +3656,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C57" s="25">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>239.4</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,16 +3707,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C60" s="25">
-        <v>871.5</v>
+        <v>863.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>991.4</v>
+        <v>982.3</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,16 +3758,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C63" s="25">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D63" s="26">
         <v>1.65</v>
       </c>
       <c r="E63" s="27">
-        <v>52.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3865,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C70" s="25">
-        <v>535.5</v>
+        <v>531.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>749.7</v>
+        <v>744.1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3882,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C71" s="25">
-        <v>426.5</v>
+        <v>417.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>597.1</v>
+        <v>584.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,16 +3933,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C74" s="25">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>20.399999999999999</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +3995,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C78" s="25">
-        <v>168.5</v>
+        <v>158.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>202.2</v>
+        <v>190.2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4080,16 +4080,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C83" s="25">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>760.8</v>
+        <v>751.2</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4097,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C84" s="25">
-        <v>1223.5</v>
+        <v>1219.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1590.55</v>
+        <v>1585.35</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4114,16 +4114,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C85" s="25">
-        <v>1313.5</v>
+        <v>1308.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1707.55</v>
+        <v>1701.05</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4182,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C89" s="25">
-        <v>199.5</v>
+        <v>197.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>292.81</v>
+        <v>289.88</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4342,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C99" s="25">
-        <v>354.5</v>
+        <v>350.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>584.92999999999995</v>
+        <v>578.33000000000004</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4389,16 +4389,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C102" s="25">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D102" s="26">
         <v>0.86</v>
       </c>
       <c r="E102" s="27">
-        <v>168.89</v>
+        <v>165.46</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4421,16 +4421,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C104" s="25">
-        <v>108.5</v>
+        <v>103.5</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>271.25</v>
+        <v>258.75</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4595,10 +4595,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C116" s="25">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -5329,16 +5329,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C164" s="25">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>120.75</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5453,16 +5453,16 @@
         <v>174</v>
       </c>
       <c r="B172" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C172" s="25">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D172" s="26">
         <v>0.89</v>
       </c>
       <c r="E172" s="27">
-        <v>106.64</v>
+        <v>87.98</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -5813,16 +5813,16 @@
         <v>198</v>
       </c>
       <c r="B196" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C196" s="25">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="D196" s="26">
         <v>3.56</v>
       </c>
       <c r="E196" s="27">
-        <v>87.22</v>
+        <v>80.099999999999994</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -5994,16 +5994,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C207" s="25">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="D207" s="26">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="E207" s="27">
-        <v>214.2</v>
+        <v>424.51</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6011,16 +6011,16 @@
         <v>210</v>
       </c>
       <c r="B208" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C208" s="25">
-        <v>202.5</v>
+        <v>200.5</v>
       </c>
       <c r="D208" s="26">
         <v>2.7</v>
       </c>
       <c r="E208" s="27">
-        <v>546.75</v>
+        <v>541.35</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -6164,16 +6164,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="24">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C217" s="25">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D217" s="26">
         <v>2.7</v>
       </c>
       <c r="E217" s="27">
-        <v>631.79999999999995</v>
+        <v>626.4</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6266,16 +6266,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C223" s="25">
-        <v>171.75</v>
+        <v>166.75</v>
       </c>
       <c r="D223" s="26">
         <v>3.25</v>
       </c>
       <c r="E223" s="27">
-        <v>558.19000000000005</v>
+        <v>541.94000000000005</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6362,16 +6362,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C229" s="25">
-        <v>53.5</v>
+        <v>51</v>
       </c>
       <c r="D229" s="26">
         <v>4</v>
       </c>
       <c r="E229" s="27">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6672,16 +6672,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C249" s="25">
-        <v>150.5</v>
+        <v>147</v>
       </c>
       <c r="D249" s="26">
         <v>3</v>
       </c>
       <c r="E249" s="27">
-        <v>451.5</v>
+        <v>441</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6723,16 +6723,16 @@
         <v>254</v>
       </c>
       <c r="B252" s="24">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C252" s="25">
-        <v>124.5</v>
+        <v>122.5</v>
       </c>
       <c r="D252" s="26">
         <v>3.9</v>
       </c>
       <c r="E252" s="27">
-        <v>485.55</v>
+        <v>477.75</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -6785,16 +6785,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256" s="25">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D256" s="26">
         <v>6</v>
       </c>
       <c r="E256" s="27">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6971,16 +6971,16 @@
         <v>270</v>
       </c>
       <c r="B268" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C268" s="25">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="D268" s="26">
         <v>6.15</v>
       </c>
       <c r="E268" s="27">
-        <v>64.56</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,16 +7044,16 @@
         <v>275</v>
       </c>
       <c r="B273" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C273" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D273" s="26">
         <v>4.5</v>
       </c>
       <c r="E273" s="27">
-        <v>141.75</v>
+        <v>132.75</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7061,16 +7061,16 @@
         <v>276</v>
       </c>
       <c r="B274" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C274" s="25">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D274" s="26">
         <v>6.25</v>
       </c>
       <c r="E274" s="27">
-        <v>143.75</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -8295,16 +8295,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C350" s="25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D350" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E350" s="27">
-        <v>43.5</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8655,16 +8655,16 @@
         <v>374</v>
       </c>
       <c r="B372" s="24">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C372" s="25">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D372" s="26">
         <v>6.6</v>
       </c>
       <c r="E372" s="27">
-        <v>534.6</v>
+        <v>514.79999999999995</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -9057,16 +9057,16 @@
         <v>398</v>
       </c>
       <c r="B396" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C396" s="25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D396" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E396" s="27">
-        <v>130.5</v>
+        <v>126.15</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -9412,16 +9412,16 @@
         <v>421</v>
       </c>
       <c r="B419" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C419" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D419" s="26">
         <v>4.9000000000000004</v>
       </c>
       <c r="E419" s="27">
-        <v>63.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9816,16 +9816,16 @@
         <v>447</v>
       </c>
       <c r="B445" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C445" s="25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D445" s="26">
         <v>9.75</v>
       </c>
       <c r="E445" s="27">
-        <v>107.25</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -10332,16 +10332,16 @@
         <v>479</v>
       </c>
       <c r="B477" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C477" s="25">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="D477" s="26">
         <v>9.5</v>
       </c>
       <c r="E477" s="27">
-        <v>223.25</v>
+        <v>190</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -10556,16 +10556,16 @@
         <v>493</v>
       </c>
       <c r="B491" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C491" s="25">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D491" s="26">
         <v>9</v>
       </c>
       <c r="E491" s="27">
-        <v>67.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -10949,16 +10949,16 @@
         <v>518</v>
       </c>
       <c r="B516" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C516" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D516" s="26">
         <v>12.8</v>
       </c>
       <c r="E516" s="27">
-        <v>38.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -11228,16 +11228,16 @@
         <v>535</v>
       </c>
       <c r="B533" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C533" s="25">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D533" s="26">
         <v>2</v>
       </c>
       <c r="E533" s="27">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11496,17 +11496,11 @@
         <v>551</v>
       </c>
       <c r="B549" s="24">
-        <v>12</v>
-      </c>
-      <c r="C549" s="25">
-        <v>3</v>
-      </c>
-      <c r="D549" s="26">
-        <v>6.5</v>
-      </c>
-      <c r="E549" s="27">
-        <v>19.5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C549" s="28"/>
+      <c r="D549" s="29"/>
+      <c r="E549" s="28"/>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="23" t="s">
@@ -11666,16 +11660,16 @@
         <v>561</v>
       </c>
       <c r="B559" s="24">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C559" s="25">
-        <v>172.2</v>
+        <v>167.7</v>
       </c>
       <c r="D559" s="26">
         <v>3.9</v>
       </c>
       <c r="E559" s="27">
-        <v>671.58</v>
+        <v>654.03</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -12211,10 +12205,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C592" s="25">
-        <v>124</v>
+        <v>123.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12297,16 +12291,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C598" s="25">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D598" s="26">
         <v>0.85</v>
       </c>
       <c r="E598" s="27">
-        <v>316.2</v>
+        <v>303.45</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -13168,16 +13162,16 @@
         <v>655</v>
       </c>
       <c r="B653" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C653" s="25">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="D653" s="26">
         <v>3.5</v>
       </c>
       <c r="E653" s="27">
-        <v>99.75</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -13689,16 +13683,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C684" s="25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D684" s="26">
         <v>8.84</v>
       </c>
       <c r="E684" s="27">
-        <v>92.8</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13920,10 +13914,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C699" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -13933,10 +13927,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C700" s="25">
-        <v>82.5</v>
+        <v>79.5</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13972,10 +13966,10 @@
         <v>705</v>
       </c>
       <c r="B703" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C703" s="25">
-        <v>35.5</v>
+        <v>25.5</v>
       </c>
       <c r="D703" s="29"/>
       <c r="E703" s="28"/>
@@ -14278,10 +14272,10 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C727" s="25">
-        <v>-102.15</v>
+        <v>-106.15</v>
       </c>
       <c r="D727" s="29"/>
       <c r="E727" s="28"/>
@@ -14449,10 +14443,10 @@
         <v>740</v>
       </c>
       <c r="B738" s="24">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C738" s="25">
-        <v>-561.5</v>
+        <v>-566</v>
       </c>
       <c r="D738" s="29"/>
       <c r="E738" s="28"/>
@@ -14463,11 +14457,11 @@
       </c>
       <c r="B739" s="31"/>
       <c r="C739" s="32">
-        <v>42992.31</v>
+        <v>42839.31</v>
       </c>
       <c r="D739" s="33"/>
       <c r="E739" s="34">
-        <v>106534.02</v>
+        <v>106241.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 13-Mar-26</t>
+    <t>1-Jul-25 to 14-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -470,7 +470,7 @@
     <t>2113 PATRIKA (L)</t>
   </si>
   <si>
-    <t>2114 PATRIKA (L) (DCU)</t>
+    <t>2114 PATRIKA (L) (DCU) 800 17.03</t>
   </si>
   <si>
     <t>2115 PATRIKA (L) (DCU)</t>
@@ -2060,7 +2060,7 @@
     <t>9357 CARDS</t>
   </si>
   <si>
-    <t>9358 CARDS</t>
+    <t>9358 CARDS AGYA (2000)</t>
   </si>
   <si>
     <t>9359 CARDS (Ri)</t>
@@ -2901,16 +2901,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="25">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>207</v>
+        <v>203.4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,16 +3308,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C36" s="25">
-        <v>126</v>
+        <v>123.5</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>289.8</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3370,16 +3370,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" s="25">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>16.05</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3387,16 +3387,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C41" s="25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>98.44</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3710,16 +3710,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C60" s="25">
-        <v>860.5</v>
+        <v>858.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>978.89</v>
+        <v>976.61</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3817,11 +3817,17 @@
         <v>69</v>
       </c>
       <c r="B67" s="24">
-        <v>20</v>
-      </c>
-      <c r="C67" s="28"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="28"/>
+        <v>21</v>
+      </c>
+      <c r="C67" s="25">
+        <v>-3</v>
+      </c>
+      <c r="D67" s="26">
+        <v>1.65</v>
+      </c>
+      <c r="E67" s="27">
+        <v>-4.95</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
@@ -4009,16 +4015,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C79" s="25">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>597.6</v>
+        <v>585.6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4128,16 +4134,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C86" s="25">
-        <v>1183</v>
+        <v>1174</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>2011.1</v>
+        <v>1995.8</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4179,16 +4185,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C89" s="25">
-        <v>197.5</v>
+        <v>194.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>289.88</v>
+        <v>285.48</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4720,10 +4726,10 @@
         <v>128</v>
       </c>
       <c r="B126" s="24">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C126" s="25">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="D126" s="29"/>
       <c r="E126" s="28"/>
@@ -5026,11 +5032,17 @@
         <v>148</v>
       </c>
       <c r="B146" s="24">
-        <v>19</v>
-      </c>
-      <c r="C146" s="28"/>
-      <c r="D146" s="29"/>
-      <c r="E146" s="28"/>
+        <v>20</v>
+      </c>
+      <c r="C146" s="25">
+        <v>-1.5</v>
+      </c>
+      <c r="D146" s="26">
+        <v>18.5</v>
+      </c>
+      <c r="E146" s="27">
+        <v>-27.75</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
@@ -5218,16 +5230,16 @@
         <v>160</v>
       </c>
       <c r="B158" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C158" s="25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D158" s="26">
         <v>11.5</v>
       </c>
       <c r="E158" s="27">
-        <v>230</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5530,16 +5542,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C178" s="25">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="D178" s="26">
         <v>3.25</v>
       </c>
       <c r="E178" s="27">
-        <v>110.5</v>
+        <v>105.63</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5951,16 +5963,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C205" s="25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D205" s="26">
         <v>4.5</v>
       </c>
       <c r="E205" s="27">
-        <v>207</v>
+        <v>198</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -6746,16 +6758,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C254" s="25">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D254" s="26">
         <v>3.9</v>
       </c>
       <c r="E254" s="27">
-        <v>510.9</v>
+        <v>503.1</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -7084,16 +7096,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C276" s="25">
-        <v>100.37</v>
+        <v>98.37</v>
       </c>
       <c r="D276" s="26">
         <v>4.25</v>
       </c>
       <c r="E276" s="27">
-        <v>426.57</v>
+        <v>418.07</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7236,16 +7248,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C286" s="25">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D286" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E286" s="27">
-        <v>231.58</v>
+        <v>226.85</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7304,16 +7316,16 @@
         <v>292</v>
       </c>
       <c r="B290" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C290" s="25">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D290" s="26">
         <v>5</v>
       </c>
       <c r="E290" s="27">
-        <v>615</v>
+        <v>600</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7924,16 +7936,16 @@
         <v>330</v>
       </c>
       <c r="B328" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C328" s="25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D328" s="26">
         <v>7.45</v>
       </c>
       <c r="E328" s="27">
-        <v>104.24</v>
+        <v>96.79</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -8397,16 +8409,16 @@
         <v>359</v>
       </c>
       <c r="B357" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C357" s="25">
-        <v>55.85</v>
+        <v>51.85</v>
       </c>
       <c r="D357" s="26">
         <v>4.75</v>
       </c>
       <c r="E357" s="27">
-        <v>265.29000000000002</v>
+        <v>246.29</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -9912,16 +9924,16 @@
         <v>454</v>
       </c>
       <c r="B452" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C452" s="25">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D452" s="26">
         <v>9</v>
       </c>
       <c r="E452" s="27">
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -9997,17 +10009,11 @@
         <v>459</v>
       </c>
       <c r="B457" s="24">
-        <v>22</v>
-      </c>
-      <c r="C457" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="D457" s="26">
-        <v>9.75</v>
-      </c>
-      <c r="E457" s="27">
-        <v>24.38</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C457" s="28"/>
+      <c r="D457" s="29"/>
+      <c r="E457" s="28"/>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="23" t="s">
@@ -10338,16 +10344,16 @@
         <v>480</v>
       </c>
       <c r="B478" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C478" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D478" s="26">
         <v>9.5</v>
       </c>
       <c r="E478" s="27">
-        <v>180.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -11234,16 +11240,16 @@
         <v>536</v>
       </c>
       <c r="B534" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C534" s="25">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="D534" s="26">
         <v>2</v>
       </c>
       <c r="E534" s="27">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11268,16 +11274,16 @@
         <v>538</v>
       </c>
       <c r="B536" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C536" s="25">
-        <v>47.5</v>
+        <v>41.5</v>
       </c>
       <c r="D536" s="26">
         <v>3</v>
       </c>
       <c r="E536" s="27">
-        <v>142.5</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -11383,16 +11389,16 @@
         <v>545</v>
       </c>
       <c r="B543" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C543" s="25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D543" s="26">
         <v>2.84</v>
       </c>
       <c r="E543" s="27">
-        <v>19.91</v>
+        <v>17.059999999999999</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11598,16 +11604,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C556" s="25">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D556" s="26">
         <v>3.1</v>
       </c>
       <c r="E556" s="27">
-        <v>63.55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11666,16 +11672,16 @@
         <v>562</v>
       </c>
       <c r="B560" s="24">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C560" s="25">
-        <v>161.69999999999999</v>
+        <v>150.69999999999999</v>
       </c>
       <c r="D560" s="26">
         <v>3.9</v>
       </c>
       <c r="E560" s="27">
-        <v>630.63</v>
+        <v>587.73</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11694,7 +11700,7 @@
         <v>564</v>
       </c>
       <c r="B562" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C562" s="25">
         <v>13.5</v>
@@ -11745,16 +11751,16 @@
         <v>567</v>
       </c>
       <c r="B565" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C565" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D565" s="26">
         <v>3.6</v>
       </c>
       <c r="E565" s="27">
-        <v>115.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -12274,16 +12280,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C598" s="25">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D598" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E598" s="27">
-        <v>364.82</v>
+        <v>361.34</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12291,16 +12297,16 @@
         <v>601</v>
       </c>
       <c r="B599" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C599" s="25">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D599" s="26">
         <v>0.85</v>
       </c>
       <c r="E599" s="27">
-        <v>259.25</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -12540,15 +12546,17 @@
       <c r="A617" s="23" t="s">
         <v>619</v>
       </c>
-      <c r="B617" s="24"/>
+      <c r="B617" s="24">
+        <v>1</v>
+      </c>
       <c r="C617" s="25">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D617" s="26">
         <v>5.25</v>
       </c>
       <c r="E617" s="27">
-        <v>68.25</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
@@ -12828,16 +12836,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C634" s="25">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="D634" s="26">
         <v>2.76</v>
       </c>
       <c r="E634" s="27">
-        <v>150.36000000000001</v>
+        <v>146.22</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -12981,16 +12989,16 @@
         <v>645</v>
       </c>
       <c r="B643" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C643" s="25">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D643" s="26">
         <v>5.5</v>
       </c>
       <c r="E643" s="27">
-        <v>8.25</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -13901,10 +13909,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C699" s="25">
-        <v>37.340000000000003</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -13953,10 +13961,10 @@
         <v>705</v>
       </c>
       <c r="B703" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C703" s="25">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="D703" s="29"/>
       <c r="E703" s="28"/>
@@ -13966,10 +13974,10 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C704" s="25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="D704" s="29"/>
       <c r="E704" s="28"/>
@@ -14443,10 +14451,10 @@
         <v>741</v>
       </c>
       <c r="B739" s="24">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C739" s="25">
-        <v>-572</v>
+        <v>-583</v>
       </c>
       <c r="D739" s="29"/>
       <c r="E739" s="28"/>
@@ -14457,11 +14465,11 @@
       </c>
       <c r="B740" s="31"/>
       <c r="C740" s="32">
-        <v>42542.81</v>
+        <v>42386.8</v>
       </c>
       <c r="D740" s="33"/>
       <c r="E740" s="34">
-        <v>106702.88</v>
+        <v>106324.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="744">
   <si>
     <t>Order Estimate - (from 1-Jul-2023)</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 14-Mar-26</t>
+    <t>1-Jul-25 to 16-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -173,7 +173,7 @@
     <t>1035 PATRIKA (DCU)</t>
   </si>
   <si>
-    <t>1101 PATRIKA (O.2591)</t>
+    <t>1101 PATRIKA (O.2591) (5200 14.03)</t>
   </si>
   <si>
     <t>1102 PATRIKA (P.2591)</t>
@@ -188,7 +188,7 @@
     <t>1105 PATRIKA</t>
   </si>
   <si>
-    <t>1106 PATRIKA-YELLOW</t>
+    <t>1106 PATRIKA-YELLOW (18.03)</t>
   </si>
   <si>
     <t>1107 PATRIKA-RED</t>
@@ -734,7 +734,7 @@
     <t>4304 PATRIKA</t>
   </si>
   <si>
-    <t>4305 PATRIKA (9000 18.03)</t>
+    <t>4305 PATRIKA</t>
   </si>
   <si>
     <t>4306 PATRIKA (JC)</t>
@@ -806,10 +806,10 @@
     <t>5062 PATRIKA</t>
   </si>
   <si>
-    <t>5063 PATRIKA (3000 17.03)</t>
-  </si>
-  <si>
-    <t>5064 PATRIKA (2400 17.03)</t>
+    <t>5063 PATRIKA</t>
+  </si>
+  <si>
+    <t>5064 PATRIKA</t>
   </si>
   <si>
     <t>5065 PATRIKA</t>
@@ -857,7 +857,7 @@
     <t>5079 PATRIKA</t>
   </si>
   <si>
-    <t>5080 PATRIKA (2800 18.03)</t>
+    <t>5080 PATRIKA</t>
   </si>
   <si>
     <t>5081 PATRIKA</t>
@@ -878,7 +878,7 @@
     <t>5087 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>5088 PATRIKA (1400 18.03)</t>
+    <t>5088 PATRIKA</t>
   </si>
   <si>
     <t>5089 PATRIKA</t>
@@ -1328,7 +1328,7 @@
     <t>5621 PATRIKA (JC) *-* (M)</t>
   </si>
   <si>
-    <t>5622 PATRIKA *-* (M) (4000 16.03)</t>
+    <t>5622 PATRIKA *-* (M)</t>
   </si>
   <si>
     <t>5623 PATRIKA</t>
@@ -1391,7 +1391,7 @@
     <t>6612 PATRIKA</t>
   </si>
   <si>
-    <t>6613 PATRIKA (1600 17.03)</t>
+    <t>6613 PATRIKA</t>
   </si>
   <si>
     <t>6614 PATRIKA (DCU)</t>
@@ -1715,7 +1715,7 @@
     <t>7429 PATRIKA (F/G) *-*</t>
   </si>
   <si>
-    <t>7430 PATRIKA</t>
+    <t>7430 PATRIKA (21.03 Aproxe)</t>
   </si>
   <si>
     <t>7431 PATRIKA</t>
@@ -1769,7 +1769,7 @@
     <t>7447 PATRIKA</t>
   </si>
   <si>
-    <t>7448 PATRIKA (13.03)</t>
+    <t>7448 PATRIKA</t>
   </si>
   <si>
     <t>7449 PATRIKA</t>
@@ -1883,6 +1883,9 @@
     <t>9244 CARDS</t>
   </si>
   <si>
+    <t>9245 CARDS</t>
+  </si>
+  <si>
     <t>9301 CARDS</t>
   </si>
   <si>
@@ -2081,7 +2084,7 @@
     <t>9364 CARDS *-* (T)</t>
   </si>
   <si>
-    <t>9365 CARDS (2200 18.03)</t>
+    <t>9365 CARDS</t>
   </si>
   <si>
     <t>9366 CARDS</t>
@@ -2776,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E740"/>
+  <dimension ref="A1:E741"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
@@ -2918,16 +2921,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="25">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>269.10000000000002</v>
+        <v>261.3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2969,16 +2972,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" s="25">
-        <v>95.5</v>
+        <v>91</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3127,16 +3130,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="25">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>113.85</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3178,16 +3181,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C28" s="25">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3246,16 +3249,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="25">
-        <v>24.5</v>
+        <v>19.5</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>68.599999999999994</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3294,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" s="25">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>338.1</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3421,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C43" s="25">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>135.6</v>
+        <v>113.41</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,13 +3495,13 @@
         <v>86</v>
       </c>
       <c r="C47" s="25">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>88.09</v>
+        <v>93.15</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3506,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C48" s="25">
-        <v>76.849999999999994</v>
+        <v>51.85</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>97.52</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3608,16 +3611,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C54" s="25">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>363</v>
+        <v>343.75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3625,16 +3628,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" s="25">
-        <v>236.15</v>
+        <v>234.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>649.41</v>
+        <v>643.91</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3727,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C61" s="25">
-        <v>921.5</v>
+        <v>911.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1049.9000000000001</v>
+        <v>1038.51</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3783,16 +3786,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C65" s="25">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>404.25</v>
+        <v>400.95</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3800,16 +3803,16 @@
         <v>68</v>
       </c>
       <c r="B66" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C66" s="25">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="D66" s="26">
         <v>1.65</v>
       </c>
       <c r="E66" s="27">
-        <v>22.28</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3817,33 +3820,27 @@
         <v>69</v>
       </c>
       <c r="B67" s="24">
-        <v>21</v>
-      </c>
-      <c r="C67" s="25">
-        <v>-3</v>
-      </c>
-      <c r="D67" s="26">
-        <v>1.65</v>
-      </c>
-      <c r="E67" s="27">
-        <v>-4.95</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C67" s="28"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="28"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C68" s="25">
-        <v>317</v>
+        <v>313.5</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>523.04999999999995</v>
+        <v>517.28</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3868,16 +3865,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C70" s="25">
-        <v>480.5</v>
+        <v>442.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>672.7</v>
+        <v>619.5</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3885,16 +3882,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C71" s="25">
-        <v>520.5</v>
+        <v>462</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>728.7</v>
+        <v>646.79999999999995</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3902,16 +3899,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C72" s="25">
-        <v>505</v>
+        <v>472.5</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>707</v>
+        <v>661.5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3919,16 +3916,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C73" s="25">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>704.2</v>
+        <v>684.6</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3936,16 +3933,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C74" s="25">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>10.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3964,16 +3961,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C76" s="25">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>381.6</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3998,16 +3995,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C78" s="25">
-        <v>148.5</v>
+        <v>111.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>178.2</v>
+        <v>133.80000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4015,16 +4012,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C79" s="25">
-        <v>488</v>
+        <v>438</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>585.6</v>
+        <v>525.6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4049,16 +4046,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C81" s="25">
-        <v>608</v>
+        <v>564</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>729.6</v>
+        <v>676.8</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4066,16 +4063,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C82" s="25">
-        <v>604</v>
+        <v>502</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>724.8</v>
+        <v>602.4</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4083,16 +4080,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C83" s="25">
-        <v>596</v>
+        <v>552</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>715.2</v>
+        <v>662.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4100,16 +4097,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C84" s="25">
-        <v>1219.5</v>
+        <v>1182.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1585.35</v>
+        <v>1537.25</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4117,16 +4114,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C85" s="25">
-        <v>1301</v>
+        <v>1274</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1691.3</v>
+        <v>1656.2</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4134,16 +4131,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C86" s="25">
-        <v>1174</v>
+        <v>1126</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1995.8</v>
+        <v>1914.2</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4151,16 +4148,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C87" s="25">
-        <v>732.5</v>
+        <v>712.5</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1245.25</v>
+        <v>1211.25</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4185,16 +4182,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C89" s="25">
-        <v>194.5</v>
+        <v>184.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>285.48</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4202,16 +4199,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C90" s="25">
-        <v>274.7</v>
+        <v>268.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>352.35</v>
+        <v>344.66</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4283,16 +4280,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C95" s="25">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>327.60000000000002</v>
+        <v>324</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4345,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C99" s="25">
-        <v>300.5</v>
+        <v>297.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>495.83</v>
+        <v>490.88</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4376,15 +4373,17 @@
       <c r="A101" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B101" s="24"/>
+      <c r="B101" s="24">
+        <v>1</v>
+      </c>
       <c r="C101" s="25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D101" s="26">
         <v>0.85</v>
       </c>
       <c r="E101" s="27">
-        <v>8.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4392,16 +4391,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C102" s="25">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="D102" s="26">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="E102" s="27">
-        <v>144.88999999999999</v>
+        <v>247.2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4424,16 +4423,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C104" s="25">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>252.5</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4458,16 +4457,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C106" s="25">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>542.5</v>
+        <v>517.5</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4475,16 +4474,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C107" s="25">
-        <v>238.5</v>
+        <v>228.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>596.25</v>
+        <v>571.25</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4492,16 +4491,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C108" s="25">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>632.5</v>
+        <v>607.5</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4509,10 +4508,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C109" s="25">
-        <v>78.5</v>
+        <v>68.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4522,10 +4521,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C110" s="25">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4598,10 +4597,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C116" s="25">
-        <v>-29</v>
+        <v>-35</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4611,10 +4610,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C117" s="25">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4913,16 +4912,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C139" s="25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D139" s="26">
         <v>12.5</v>
       </c>
       <c r="E139" s="27">
-        <v>162.5</v>
+        <v>156.25</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4947,16 +4946,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C141" s="25">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="D141" s="26">
         <v>12.73</v>
       </c>
       <c r="E141" s="27">
-        <v>299.08999999999997</v>
+        <v>254.54</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5015,16 +5014,16 @@
         <v>147</v>
       </c>
       <c r="B145" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C145" s="25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D145" s="26">
         <v>18.5</v>
       </c>
       <c r="E145" s="27">
-        <v>314.5</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5162,16 +5161,16 @@
         <v>156</v>
       </c>
       <c r="B154" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C154" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D154" s="26">
         <v>18.5</v>
       </c>
       <c r="E154" s="27">
-        <v>305.25</v>
+        <v>286.75</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -5179,16 +5178,16 @@
         <v>157</v>
       </c>
       <c r="B155" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" s="25">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="D155" s="26">
         <v>18.5</v>
       </c>
       <c r="E155" s="27">
-        <v>175.75</v>
+        <v>120.25</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5247,16 +5246,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C159" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159" s="26">
         <v>11.5</v>
       </c>
       <c r="E159" s="27">
-        <v>34.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5576,16 +5575,16 @@
         <v>182</v>
       </c>
       <c r="B180" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C180" s="25">
-        <v>62.5</v>
+        <v>58.5</v>
       </c>
       <c r="D180" s="26">
         <v>2.7</v>
       </c>
       <c r="E180" s="27">
-        <v>168.75</v>
+        <v>157.94999999999999</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -5636,16 +5635,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C184" s="25">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D184" s="26">
         <v>2.8</v>
       </c>
       <c r="E184" s="27">
-        <v>109.32</v>
+        <v>95.31</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -5687,16 +5686,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C187" s="25">
-        <v>23.5</v>
+        <v>16</v>
       </c>
       <c r="D187" s="26">
         <v>3.33</v>
       </c>
       <c r="E187" s="27">
-        <v>78.260000000000005</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5997,16 +5996,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C207" s="25">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D207" s="26">
         <v>3.79</v>
       </c>
       <c r="E207" s="27">
-        <v>405.56</v>
+        <v>375.24</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6014,16 +6013,16 @@
         <v>210</v>
       </c>
       <c r="B208" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C208" s="25">
-        <v>191.5</v>
+        <v>189</v>
       </c>
       <c r="D208" s="26">
         <v>2.7</v>
       </c>
       <c r="E208" s="27">
-        <v>517.04999999999995</v>
+        <v>510.3</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -6031,16 +6030,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C209" s="25">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>46.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6150,16 +6149,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C216" s="25">
-        <v>304.5</v>
+        <v>284.5</v>
       </c>
       <c r="D216" s="26">
         <v>2.7</v>
       </c>
       <c r="E216" s="27">
-        <v>822.15</v>
+        <v>768.15</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6167,16 +6166,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="24">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C217" s="25">
-        <v>218.5</v>
+        <v>212.5</v>
       </c>
       <c r="D217" s="26">
         <v>2.7</v>
       </c>
       <c r="E217" s="27">
-        <v>589.95000000000005</v>
+        <v>573.75</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6184,16 +6183,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C218" s="25">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D218" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E218" s="27">
-        <v>220.8</v>
+        <v>209.3</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6218,16 +6217,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C220" s="25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D220" s="26">
         <v>3</v>
       </c>
       <c r="E220" s="27">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6272,13 +6271,13 @@
         <v>101</v>
       </c>
       <c r="C223" s="25">
-        <v>155.75</v>
+        <v>162.75</v>
       </c>
       <c r="D223" s="26">
         <v>3.25</v>
       </c>
       <c r="E223" s="27">
-        <v>506.19</v>
+        <v>528.94000000000005</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6286,16 +6285,16 @@
         <v>226</v>
       </c>
       <c r="B224" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C224" s="25">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D224" s="26">
         <v>3.64</v>
       </c>
       <c r="E224" s="27">
-        <v>269.38</v>
+        <v>262.10000000000002</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6346,16 +6345,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C228" s="25">
-        <v>112.5</v>
+        <v>109</v>
       </c>
       <c r="D228" s="26">
         <v>2.66</v>
       </c>
       <c r="E228" s="27">
-        <v>299.25</v>
+        <v>289.94</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6363,16 +6362,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C229" s="25">
-        <v>38.5</v>
+        <v>33.5</v>
       </c>
       <c r="D229" s="26">
         <v>4</v>
       </c>
       <c r="E229" s="27">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6380,16 +6379,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C230" s="25">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D230" s="26">
         <v>4</v>
       </c>
       <c r="E230" s="27">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6448,16 +6447,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C234" s="25">
-        <v>48</v>
+        <v>134.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.5</v>
       </c>
       <c r="E234" s="27">
-        <v>168</v>
+        <v>470.75</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6476,16 +6475,16 @@
         <v>238</v>
       </c>
       <c r="B236" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C236" s="25">
-        <v>35.880000000000003</v>
+        <v>32.880000000000003</v>
       </c>
       <c r="D236" s="26">
         <v>3.25</v>
       </c>
       <c r="E236" s="27">
-        <v>116.61</v>
+        <v>106.86</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6625,13 +6624,13 @@
         <v>22</v>
       </c>
       <c r="C246" s="25">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="D246" s="26">
         <v>8.25</v>
       </c>
       <c r="E246" s="27">
-        <v>115.5</v>
+        <v>127.88</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6673,16 +6672,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C249" s="25">
-        <v>74.900000000000006</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="D249" s="26">
         <v>6.3</v>
       </c>
       <c r="E249" s="27">
-        <v>471.87</v>
+        <v>427.77</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6690,16 +6689,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C250" s="25">
-        <v>144.5</v>
+        <v>142.5</v>
       </c>
       <c r="D250" s="26">
         <v>3</v>
       </c>
       <c r="E250" s="27">
-        <v>433.5</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6741,16 +6740,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C253" s="25">
-        <v>117.5</v>
+        <v>108</v>
       </c>
       <c r="D253" s="26">
         <v>3.9</v>
       </c>
       <c r="E253" s="27">
-        <v>458.25</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6758,16 +6757,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C254" s="25">
-        <v>129</v>
+        <v>125.5</v>
       </c>
       <c r="D254" s="26">
         <v>3.9</v>
       </c>
       <c r="E254" s="27">
-        <v>503.1</v>
+        <v>489.45</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6854,16 +6853,16 @@
         <v>262</v>
       </c>
       <c r="B260" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C260" s="25">
-        <v>48.5</v>
+        <v>42</v>
       </c>
       <c r="D260" s="26">
         <v>3.5</v>
       </c>
       <c r="E260" s="27">
-        <v>169.75</v>
+        <v>147</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -6972,16 +6971,16 @@
         <v>270</v>
       </c>
       <c r="B268" s="24">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C268" s="25">
-        <v>238.28</v>
+        <v>229.78</v>
       </c>
       <c r="D268" s="26">
         <v>4.28</v>
       </c>
       <c r="E268" s="27">
-        <v>1019.84</v>
+        <v>983.46</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -7034,16 +7033,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C272" s="25">
-        <v>109.5</v>
+        <v>104</v>
       </c>
       <c r="D272" s="26">
         <v>3.1</v>
       </c>
       <c r="E272" s="27">
-        <v>339.45</v>
+        <v>322.39999999999998</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7082,13 +7081,13 @@
         <v>42</v>
       </c>
       <c r="C275" s="25">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D275" s="26">
         <v>6.25</v>
       </c>
       <c r="E275" s="27">
-        <v>18.75</v>
+        <v>193.75</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7185,16 @@
         <v>284</v>
       </c>
       <c r="B282" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C282" s="25">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D282" s="26">
         <v>6.5</v>
       </c>
       <c r="E282" s="27">
-        <v>169</v>
+        <v>247</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7248,16 +7247,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C286" s="25">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D286" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E286" s="27">
-        <v>226.85</v>
+        <v>212.67</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7367,16 +7366,16 @@
         <v>295</v>
       </c>
       <c r="B293" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C293" s="25">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="D293" s="26">
         <v>4.66</v>
       </c>
       <c r="E293" s="27">
-        <v>226</v>
+        <v>221.34</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7401,16 +7400,16 @@
         <v>297</v>
       </c>
       <c r="B295" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C295" s="25">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D295" s="26">
         <v>4.5</v>
       </c>
       <c r="E295" s="27">
-        <v>477</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7435,16 +7434,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C297" s="25">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D297" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E297" s="27">
-        <v>508.3</v>
+        <v>498.53</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7469,16 +7468,16 @@
         <v>301</v>
       </c>
       <c r="B299" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C299" s="25">
-        <v>53.5</v>
+        <v>48.5</v>
       </c>
       <c r="D299" s="26">
         <v>3.15</v>
       </c>
       <c r="E299" s="27">
-        <v>168.53</v>
+        <v>152.78</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,16 +7485,16 @@
         <v>302</v>
       </c>
       <c r="B300" s="24">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C300" s="25">
-        <v>252</v>
+        <v>244.5</v>
       </c>
       <c r="D300" s="26">
         <v>6.07</v>
       </c>
       <c r="E300" s="27">
-        <v>1529.77</v>
+        <v>1484.65</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -7970,16 +7969,16 @@
         <v>332</v>
       </c>
       <c r="B330" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C330" s="25">
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
       <c r="D330" s="26">
         <v>10</v>
       </c>
       <c r="E330" s="27">
-        <v>335</v>
+        <v>325</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -8021,16 +8020,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C333" s="25">
-        <v>110.91</v>
+        <v>109.91</v>
       </c>
       <c r="D333" s="26">
         <v>4.28</v>
       </c>
       <c r="E333" s="27">
-        <v>474.69</v>
+        <v>470.41</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8117,16 +8116,16 @@
         <v>341</v>
       </c>
       <c r="B339" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C339" s="25">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="D339" s="26">
         <v>9</v>
       </c>
       <c r="E339" s="27">
-        <v>261</v>
+        <v>247.5</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -8313,16 +8312,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C351" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D351" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E351" s="27">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8358,16 +8357,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C354" s="25">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D354" s="26">
         <v>5.94</v>
       </c>
       <c r="E354" s="27">
-        <v>190.08</v>
+        <v>166.32</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8409,16 +8408,16 @@
         <v>359</v>
       </c>
       <c r="B357" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C357" s="25">
-        <v>51.85</v>
+        <v>41.85</v>
       </c>
       <c r="D357" s="26">
         <v>4.75</v>
       </c>
       <c r="E357" s="27">
-        <v>246.29</v>
+        <v>198.79</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -8426,16 +8425,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C358" s="25">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D358" s="26">
         <v>9.1999999999999993</v>
       </c>
       <c r="E358" s="27">
-        <v>174.8</v>
+        <v>138</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8537,16 +8536,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C365" s="25">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D365" s="26">
         <v>7.76</v>
       </c>
       <c r="E365" s="27">
-        <v>434.76</v>
+        <v>427</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8554,16 +8553,16 @@
         <v>368</v>
       </c>
       <c r="B366" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C366" s="25">
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
       <c r="D366" s="26">
         <v>7.13</v>
       </c>
       <c r="E366" s="27">
-        <v>245.99</v>
+        <v>238.86</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8605,16 +8604,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C369" s="25">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D369" s="26">
         <v>7.2</v>
       </c>
       <c r="E369" s="27">
-        <v>154.80000000000001</v>
+        <v>151.19999999999999</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8673,16 +8672,16 @@
         <v>375</v>
       </c>
       <c r="B373" s="24">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C373" s="25">
-        <v>77</v>
+        <v>140.5</v>
       </c>
       <c r="D373" s="26">
         <v>6.6</v>
       </c>
       <c r="E373" s="27">
-        <v>508.2</v>
+        <v>927.3</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8758,16 +8757,16 @@
         <v>380</v>
       </c>
       <c r="B378" s="24">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C378" s="25">
-        <v>80.33</v>
+        <v>78.33</v>
       </c>
       <c r="D378" s="26">
         <v>4.5</v>
       </c>
       <c r="E378" s="27">
-        <v>361.49</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -8880,13 +8879,13 @@
         <v>35</v>
       </c>
       <c r="C385" s="25">
-        <v>31.5</v>
+        <v>71.5</v>
       </c>
       <c r="D385" s="26">
         <v>6</v>
       </c>
       <c r="E385" s="27">
-        <v>189</v>
+        <v>429</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -9124,16 +9123,16 @@
         <v>402</v>
       </c>
       <c r="B400" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C400" s="25">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="D400" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E400" s="27">
-        <v>491.63</v>
+        <v>474.53</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -9141,16 +9140,16 @@
         <v>403</v>
       </c>
       <c r="B401" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C401" s="25">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="D401" s="26">
         <v>6.65</v>
       </c>
       <c r="E401" s="27">
-        <v>189.53</v>
+        <v>169.58</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9413,16 +9412,16 @@
         <v>421</v>
       </c>
       <c r="B419" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C419" s="25">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D419" s="26">
         <v>5.3</v>
       </c>
       <c r="E419" s="27">
-        <v>222.6</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9447,16 +9446,16 @@
         <v>423</v>
       </c>
       <c r="B421" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C421" s="25">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="D421" s="26">
         <v>6.2</v>
       </c>
       <c r="E421" s="27">
-        <v>164.39</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -9619,13 +9618,13 @@
         <v>16</v>
       </c>
       <c r="C432" s="25">
-        <v>54.5</v>
+        <v>14.5</v>
       </c>
       <c r="D432" s="26">
         <v>6</v>
       </c>
       <c r="E432" s="27">
-        <v>327</v>
+        <v>87</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -9633,16 +9632,16 @@
         <v>435</v>
       </c>
       <c r="B433" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C433" s="25">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D433" s="26">
         <v>5</v>
       </c>
       <c r="E433" s="27">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
@@ -10009,11 +10008,17 @@
         <v>459</v>
       </c>
       <c r="B457" s="24">
-        <v>23</v>
-      </c>
-      <c r="C457" s="28"/>
-      <c r="D457" s="29"/>
-      <c r="E457" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="C457" s="25">
+        <v>2.5</v>
+      </c>
+      <c r="D457" s="26">
+        <v>9.75</v>
+      </c>
+      <c r="E457" s="27">
+        <v>24.38</v>
+      </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="23" t="s">
@@ -10276,16 +10281,16 @@
         <v>476</v>
       </c>
       <c r="B474" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C474" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D474" s="26">
         <v>12.5</v>
       </c>
       <c r="E474" s="27">
-        <v>37.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -10344,16 +10349,16 @@
         <v>480</v>
       </c>
       <c r="B478" s="24">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C478" s="25">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D478" s="26">
         <v>9.5</v>
       </c>
       <c r="E478" s="27">
-        <v>161.5</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10551,16 +10556,16 @@
         <v>493</v>
       </c>
       <c r="B491" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C491" s="25">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D491" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E491" s="27">
-        <v>45.9</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -10602,16 +10607,16 @@
         <v>496</v>
       </c>
       <c r="B494" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C494" s="25">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="D494" s="26">
         <v>10.45</v>
       </c>
       <c r="E494" s="27">
-        <v>120.18</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
@@ -10636,17 +10641,11 @@
         <v>498</v>
       </c>
       <c r="B496" s="24">
-        <v>18</v>
-      </c>
-      <c r="C496" s="25">
-        <v>3.5</v>
-      </c>
-      <c r="D496" s="26">
-        <v>26</v>
-      </c>
-      <c r="E496" s="27">
-        <v>91</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C496" s="28"/>
+      <c r="D496" s="29"/>
+      <c r="E496" s="28"/>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="23" t="s">
@@ -10775,16 +10774,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C505" s="25">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D505" s="26">
         <v>11.25</v>
       </c>
       <c r="E505" s="27">
-        <v>90</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11291,16 +11290,16 @@
         <v>539</v>
       </c>
       <c r="B537" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C537" s="25">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="D537" s="26">
         <v>3.8</v>
       </c>
       <c r="E537" s="27">
-        <v>142.5</v>
+        <v>136.80000000000001</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11338,16 +11337,16 @@
         <v>542</v>
       </c>
       <c r="B540" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C540" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D540" s="26">
         <v>3.5</v>
       </c>
       <c r="E540" s="27">
-        <v>52.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11389,16 +11388,16 @@
         <v>545</v>
       </c>
       <c r="B543" s="24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C543" s="25">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D543" s="26">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E543" s="27">
-        <v>17.059999999999999</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11434,16 +11433,16 @@
         <v>548</v>
       </c>
       <c r="B546" s="24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C546" s="25">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D546" s="26">
         <v>4.28</v>
       </c>
       <c r="E546" s="27">
-        <v>119.84</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -11451,16 +11450,16 @@
         <v>549</v>
       </c>
       <c r="B547" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C547" s="25">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D547" s="26">
         <v>4.28</v>
       </c>
       <c r="E547" s="27">
-        <v>119.84</v>
+        <v>111.28</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -11621,16 +11620,16 @@
         <v>559</v>
       </c>
       <c r="B557" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C557" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D557" s="26">
         <v>9.5</v>
       </c>
       <c r="E557" s="27">
-        <v>156.75</v>
+        <v>147.25</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11672,16 +11671,16 @@
         <v>562</v>
       </c>
       <c r="B560" s="24">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C560" s="25">
-        <v>150.69999999999999</v>
+        <v>145.69999999999999</v>
       </c>
       <c r="D560" s="26">
         <v>3.9</v>
       </c>
       <c r="E560" s="27">
-        <v>587.73</v>
+        <v>568.23</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11703,13 +11702,13 @@
         <v>5</v>
       </c>
       <c r="C562" s="25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="D562" s="26">
         <v>4.5</v>
       </c>
       <c r="E562" s="27">
-        <v>60.75</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
@@ -11785,16 +11784,16 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C567" s="25">
-        <v>23.3</v>
+        <v>19.8</v>
       </c>
       <c r="D567" s="26">
         <v>3.14</v>
       </c>
       <c r="E567" s="27">
-        <v>73.16</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -11853,16 +11852,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C571" s="25">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
       <c r="D571" s="26">
         <v>3.5</v>
       </c>
       <c r="E571" s="27">
-        <v>134.75</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11904,16 +11903,16 @@
         <v>576</v>
       </c>
       <c r="B574" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C574" s="25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D574" s="26">
         <v>2.14</v>
       </c>
       <c r="E574" s="27">
-        <v>25.68</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -11938,16 +11937,16 @@
         <v>578</v>
       </c>
       <c r="B576" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C576" s="25">
-        <v>44.5</v>
+        <v>41.5</v>
       </c>
       <c r="D576" s="26">
         <v>2.66</v>
       </c>
       <c r="E576" s="27">
-        <v>118.37</v>
+        <v>110.39</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -11992,13 +11991,13 @@
         <v>23</v>
       </c>
       <c r="C579" s="25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="D579" s="26">
         <v>2.74</v>
       </c>
       <c r="E579" s="27">
-        <v>42.49</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12057,16 +12056,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C583" s="25">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="D583" s="26">
         <v>1.8</v>
       </c>
       <c r="E583" s="27">
-        <v>72.900000000000006</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12142,10 +12141,10 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C588" s="25">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D588" s="29"/>
       <c r="E588" s="28"/>
@@ -12211,10 +12210,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C593" s="25">
-        <v>102.5</v>
+        <v>99.5</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12224,10 +12223,10 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C594" s="25">
-        <v>203.5</v>
+        <v>195.5</v>
       </c>
       <c r="D594" s="29"/>
       <c r="E594" s="28"/>
@@ -12250,10 +12249,10 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C596" s="25">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D596" s="29"/>
       <c r="E596" s="28"/>
@@ -12263,16 +12262,16 @@
         <v>599</v>
       </c>
       <c r="B597" s="24">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C597" s="25">
-        <v>303.5</v>
+        <v>296.5</v>
       </c>
       <c r="D597" s="26">
         <v>0.87</v>
       </c>
       <c r="E597" s="27">
-        <v>264.05</v>
+        <v>257.95999999999998</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
@@ -12280,16 +12279,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C598" s="25">
-        <v>623</v>
+        <v>572</v>
       </c>
       <c r="D598" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E598" s="27">
-        <v>361.34</v>
+        <v>331.76</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12297,16 +12296,16 @@
         <v>601</v>
       </c>
       <c r="B599" s="24">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C599" s="25">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D599" s="26">
         <v>0.85</v>
       </c>
       <c r="E599" s="27">
-        <v>225.25</v>
+        <v>211.65</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -12325,16 +12324,16 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C601" s="25">
-        <v>45.5</v>
+        <v>40.5</v>
       </c>
       <c r="D601" s="26">
         <v>0.85</v>
       </c>
       <c r="E601" s="27">
-        <v>38.68</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -12479,16 +12478,16 @@
         <v>615</v>
       </c>
       <c r="B613" s="24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C613" s="25">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D613" s="26">
         <v>0.73</v>
       </c>
       <c r="E613" s="27">
-        <v>38.69</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
@@ -12496,16 +12495,16 @@
         <v>616</v>
       </c>
       <c r="B614" s="24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C614" s="25">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D614" s="26">
         <v>0.73</v>
       </c>
       <c r="E614" s="27">
-        <v>42.34</v>
+        <v>20.440000000000001</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
@@ -12546,34 +12545,26 @@
       <c r="A617" s="23" t="s">
         <v>619</v>
       </c>
-      <c r="B617" s="24">
-        <v>1</v>
-      </c>
-      <c r="C617" s="25">
-        <v>9</v>
-      </c>
-      <c r="D617" s="26">
-        <v>5.25</v>
-      </c>
-      <c r="E617" s="27">
-        <v>47.25</v>
-      </c>
+      <c r="B617" s="24"/>
+      <c r="C617" s="28"/>
+      <c r="D617" s="29"/>
+      <c r="E617" s="28"/>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="23" t="s">
         <v>620</v>
       </c>
       <c r="B618" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C618" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D618" s="26">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="E618" s="27">
-        <v>38.5</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
@@ -12581,16 +12572,16 @@
         <v>621</v>
       </c>
       <c r="B619" s="24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C619" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D619" s="26">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="E619" s="27">
-        <v>41.25</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -12598,16 +12589,16 @@
         <v>622</v>
       </c>
       <c r="B620" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C620" s="25">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D620" s="26">
         <v>8.25</v>
       </c>
       <c r="E620" s="27">
-        <v>20.63</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -12615,16 +12606,16 @@
         <v>623</v>
       </c>
       <c r="B621" s="24">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C621" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D621" s="26">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="E621" s="27">
-        <v>35</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
@@ -12632,16 +12623,16 @@
         <v>624</v>
       </c>
       <c r="B622" s="24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C622" s="25">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="D622" s="26">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="E622" s="27">
-        <v>63.25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
@@ -12649,16 +12640,16 @@
         <v>625</v>
       </c>
       <c r="B623" s="24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C623" s="25">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="D623" s="26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E623" s="27">
-        <v>25</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
@@ -12669,13 +12660,13 @@
         <v>9</v>
       </c>
       <c r="C624" s="25">
-        <v>4.01</v>
+        <v>5</v>
       </c>
       <c r="D624" s="26">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E624" s="27">
-        <v>18.05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -12683,16 +12674,16 @@
         <v>627</v>
       </c>
       <c r="B625" s="24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C625" s="25">
-        <v>12.5</v>
+        <v>4.01</v>
       </c>
       <c r="D625" s="26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E625" s="27">
-        <v>43.75</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -12700,16 +12691,16 @@
         <v>628</v>
       </c>
       <c r="B626" s="24">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C626" s="25">
-        <v>0.5</v>
+        <v>12.5</v>
       </c>
       <c r="D626" s="26">
         <v>3.5</v>
       </c>
       <c r="E626" s="27">
-        <v>1.75</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -12717,16 +12708,16 @@
         <v>629</v>
       </c>
       <c r="B627" s="24">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C627" s="25">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="D627" s="26">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="E627" s="27">
-        <v>74.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -12734,16 +12725,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C628" s="25">
-        <v>26.85</v>
+        <v>13</v>
       </c>
       <c r="D628" s="26">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="E628" s="27">
-        <v>107.4</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12751,16 +12742,16 @@
         <v>631</v>
       </c>
       <c r="B629" s="24">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C629" s="25">
-        <v>4.5</v>
+        <v>26.85</v>
       </c>
       <c r="D629" s="26">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="E629" s="27">
-        <v>29.25</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -12768,16 +12759,16 @@
         <v>632</v>
       </c>
       <c r="B630" s="24">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C630" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D630" s="26">
         <v>6.5</v>
       </c>
       <c r="E630" s="27">
-        <v>45.5</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -12785,16 +12776,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C631" s="25">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D631" s="26">
-        <v>2.77</v>
+        <v>6.5</v>
       </c>
       <c r="E631" s="27">
-        <v>138.51</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12802,16 +12793,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C632" s="25">
-        <v>1.5</v>
+        <v>50</v>
       </c>
       <c r="D632" s="26">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="E632" s="27">
-        <v>4.09</v>
+        <v>138.51</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12819,16 +12810,16 @@
         <v>635</v>
       </c>
       <c r="B633" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C633" s="25">
         <v>1.5</v>
       </c>
       <c r="D633" s="26">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="E633" s="27">
-        <v>3.99</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -12836,16 +12827,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C634" s="25">
-        <v>53</v>
+        <v>1.5</v>
       </c>
       <c r="D634" s="26">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="E634" s="27">
-        <v>146.22</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -12853,16 +12844,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C635" s="25">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D635" s="26">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="E635" s="27">
-        <v>164</v>
+        <v>110.35</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -12870,16 +12861,16 @@
         <v>638</v>
       </c>
       <c r="B636" s="24">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C636" s="25">
-        <v>35.5</v>
+        <v>41</v>
       </c>
       <c r="D636" s="26">
         <v>4</v>
       </c>
       <c r="E636" s="27">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -12887,16 +12878,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C637" s="25">
-        <v>10</v>
+        <v>25.5</v>
       </c>
       <c r="D637" s="26">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E637" s="27">
-        <v>15</v>
+        <v>102</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -12904,16 +12895,16 @@
         <v>640</v>
       </c>
       <c r="B638" s="24">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C638" s="25">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D638" s="26">
         <v>1.5</v>
       </c>
       <c r="E638" s="27">
-        <v>0.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
@@ -12921,16 +12912,16 @@
         <v>641</v>
       </c>
       <c r="B639" s="24">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C639" s="25">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D639" s="26">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="E639" s="27">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -12938,16 +12929,16 @@
         <v>642</v>
       </c>
       <c r="B640" s="24">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="C640" s="25">
-        <v>128.5</v>
+        <v>0.25</v>
       </c>
       <c r="D640" s="26">
-        <v>2.2799999999999998</v>
+        <v>1.52</v>
       </c>
       <c r="E640" s="27">
-        <v>292.98</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
@@ -12955,16 +12946,16 @@
         <v>643</v>
       </c>
       <c r="B641" s="24">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C641" s="25">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="D641" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E641" s="27">
-        <v>98.04</v>
+        <v>282.72000000000003</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -12972,16 +12963,16 @@
         <v>644</v>
       </c>
       <c r="B642" s="24">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C642" s="25">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D642" s="26">
-        <v>5</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E642" s="27">
-        <v>75</v>
+        <v>98.04</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
@@ -12989,16 +12980,16 @@
         <v>645</v>
       </c>
       <c r="B643" s="24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C643" s="25">
-        <v>-0.5</v>
+        <v>15</v>
       </c>
       <c r="D643" s="26">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E643" s="27">
-        <v>-2.75</v>
+        <v>75</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -13006,16 +12997,16 @@
         <v>646</v>
       </c>
       <c r="B644" s="24">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C644" s="25">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="D644" s="26">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="E644" s="27">
-        <v>25.5</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -13023,16 +13014,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C645" s="25">
-        <v>24.5</v>
+        <v>8.5</v>
       </c>
       <c r="D645" s="26">
-        <v>4.6500000000000004</v>
+        <v>3</v>
       </c>
       <c r="E645" s="27">
-        <v>113.93</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13040,16 +13031,16 @@
         <v>648</v>
       </c>
       <c r="B646" s="24">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C646" s="25">
-        <v>34.5</v>
+        <v>24.5</v>
       </c>
       <c r="D646" s="26">
-        <v>5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="E646" s="27">
-        <v>172.5</v>
+        <v>113.93</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -13057,16 +13048,16 @@
         <v>649</v>
       </c>
       <c r="B647" s="24">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C647" s="25">
-        <v>9</v>
+        <v>34.5</v>
       </c>
       <c r="D647" s="26">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E647" s="27">
-        <v>31.5</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -13074,16 +13065,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C648" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D648" s="26">
         <v>3.5</v>
       </c>
       <c r="E648" s="27">
-        <v>42</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13091,44 +13082,44 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>5</v>
-      </c>
-      <c r="C649" s="28"/>
-      <c r="D649" s="29"/>
-      <c r="E649" s="28"/>
+        <v>18</v>
+      </c>
+      <c r="C649" s="25">
+        <v>12</v>
+      </c>
+      <c r="D649" s="26">
+        <v>3.5</v>
+      </c>
+      <c r="E649" s="27">
+        <v>42</v>
+      </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="23" t="s">
         <v>652</v>
       </c>
       <c r="B650" s="24">
-        <v>12</v>
-      </c>
-      <c r="C650" s="25">
-        <v>15.5</v>
-      </c>
-      <c r="D650" s="26">
-        <v>5.45</v>
-      </c>
-      <c r="E650" s="27">
-        <v>84.48</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C650" s="28"/>
+      <c r="D650" s="29"/>
+      <c r="E650" s="28"/>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="23" t="s">
         <v>653</v>
       </c>
       <c r="B651" s="24">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C651" s="25">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="D651" s="26">
-        <v>3.1</v>
+        <v>5.45</v>
       </c>
       <c r="E651" s="27">
-        <v>155</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
@@ -13136,16 +13127,16 @@
         <v>654</v>
       </c>
       <c r="B652" s="24">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C652" s="25">
-        <v>136.36000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="D652" s="26">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="E652" s="27">
-        <v>231.81</v>
+        <v>134.85</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13153,16 +13144,16 @@
         <v>655</v>
       </c>
       <c r="B653" s="24">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="C653" s="25">
-        <v>35</v>
+        <v>136.36000000000001</v>
       </c>
       <c r="D653" s="26">
-        <v>3.33</v>
+        <v>1.7</v>
       </c>
       <c r="E653" s="27">
-        <v>116.55</v>
+        <v>231.81</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -13170,16 +13161,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C654" s="25">
-        <v>25.5</v>
+        <v>35</v>
       </c>
       <c r="D654" s="26">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="E654" s="27">
-        <v>89.25</v>
+        <v>116.55</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13187,7 +13178,7 @@
         <v>657</v>
       </c>
       <c r="B655" s="24">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C655" s="25">
         <v>25.5</v>
@@ -13204,16 +13195,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C656" s="25">
-        <v>2.5</v>
+        <v>24.5</v>
       </c>
       <c r="D656" s="26">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E656" s="27">
-        <v>18.75</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13221,16 +13212,16 @@
         <v>659</v>
       </c>
       <c r="B657" s="24">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C657" s="25">
         <v>2.5</v>
       </c>
       <c r="D657" s="26">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="E657" s="27">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
@@ -13238,16 +13229,16 @@
         <v>660</v>
       </c>
       <c r="B658" s="24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C658" s="25">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="D658" s="26">
-        <v>6.25</v>
+        <v>8.75</v>
       </c>
       <c r="E658" s="27">
-        <v>53.13</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
@@ -13255,16 +13246,16 @@
         <v>661</v>
       </c>
       <c r="B659" s="24">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="C659" s="25">
-        <v>136</v>
+        <v>8.5</v>
       </c>
       <c r="D659" s="26">
-        <v>2.85</v>
+        <v>6.25</v>
       </c>
       <c r="E659" s="27">
-        <v>387.6</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -13272,16 +13263,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="C660" s="25">
-        <v>58.99</v>
+        <v>132</v>
       </c>
       <c r="D660" s="26">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="E660" s="27">
-        <v>117.98</v>
+        <v>376.2</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13289,16 +13280,16 @@
         <v>663</v>
       </c>
       <c r="B661" s="24">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C661" s="25">
+        <v>58.99</v>
+      </c>
+      <c r="D661" s="26">
         <v>2</v>
       </c>
-      <c r="D661" s="26">
-        <v>5.6</v>
-      </c>
       <c r="E661" s="27">
-        <v>11.2</v>
+        <v>117.98</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -13306,44 +13297,44 @@
         <v>664</v>
       </c>
       <c r="B662" s="24">
-        <v>7</v>
-      </c>
-      <c r="C662" s="28"/>
-      <c r="D662" s="29"/>
-      <c r="E662" s="28"/>
+        <v>3</v>
+      </c>
+      <c r="C662" s="25">
+        <v>2</v>
+      </c>
+      <c r="D662" s="26">
+        <v>5.6</v>
+      </c>
+      <c r="E662" s="27">
+        <v>11.2</v>
+      </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="23" t="s">
         <v>665</v>
       </c>
       <c r="B663" s="24">
-        <v>6</v>
-      </c>
-      <c r="C663" s="25">
-        <v>1</v>
-      </c>
-      <c r="D663" s="26">
-        <v>5.5</v>
-      </c>
-      <c r="E663" s="27">
-        <v>5.5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C663" s="28"/>
+      <c r="D663" s="29"/>
+      <c r="E663" s="28"/>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="23" t="s">
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C664" s="25">
-        <v>42.5</v>
+        <v>1</v>
       </c>
       <c r="D664" s="26">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="E664" s="27">
-        <v>131.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13351,16 +13342,16 @@
         <v>667</v>
       </c>
       <c r="B665" s="24">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C665" s="25">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="D665" s="26">
-        <v>5.73</v>
+        <v>3.1</v>
       </c>
       <c r="E665" s="27">
-        <v>286.58999999999997</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
@@ -13368,16 +13359,16 @@
         <v>668</v>
       </c>
       <c r="B666" s="24">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C666" s="25">
-        <v>31.5</v>
+        <v>50</v>
       </c>
       <c r="D666" s="26">
-        <v>3.97</v>
+        <v>5.73</v>
       </c>
       <c r="E666" s="27">
-        <v>125.01</v>
+        <v>286.58999999999997</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -13385,16 +13376,16 @@
         <v>669</v>
       </c>
       <c r="B667" s="24">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="C667" s="25">
-        <v>17</v>
+        <v>31.5</v>
       </c>
       <c r="D667" s="26">
-        <v>4.8</v>
+        <v>3.97</v>
       </c>
       <c r="E667" s="27">
-        <v>81.599999999999994</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
@@ -13402,16 +13393,16 @@
         <v>670</v>
       </c>
       <c r="B668" s="24">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C668" s="25">
-        <v>0.5</v>
+        <v>17</v>
       </c>
       <c r="D668" s="26">
-        <v>6.76</v>
+        <v>4.8</v>
       </c>
       <c r="E668" s="27">
-        <v>3.38</v>
+        <v>81.599999999999994</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
@@ -13419,16 +13410,16 @@
         <v>671</v>
       </c>
       <c r="B669" s="24">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C669" s="25">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D669" s="26">
-        <v>6.75</v>
+        <v>6.76</v>
       </c>
       <c r="E669" s="27">
-        <v>16.88</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13436,16 +13427,16 @@
         <v>672</v>
       </c>
       <c r="B670" s="24">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C670" s="25">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D670" s="26">
         <v>6.75</v>
       </c>
       <c r="E670" s="27">
-        <v>6.75</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -13453,16 +13444,16 @@
         <v>673</v>
       </c>
       <c r="B671" s="24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C671" s="25">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="D671" s="26">
         <v>6.75</v>
       </c>
       <c r="E671" s="27">
-        <v>30.38</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -13470,16 +13461,16 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C672" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D672" s="26">
         <v>6.75</v>
       </c>
       <c r="E672" s="27">
-        <v>47.25</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -13487,16 +13478,16 @@
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C673" s="25">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="D673" s="26">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="E673" s="27">
-        <v>2.75</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13504,16 +13495,16 @@
         <v>676</v>
       </c>
       <c r="B674" s="24">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="C674" s="25">
-        <v>139.5</v>
+        <v>0.5</v>
       </c>
       <c r="D674" s="26">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="E674" s="27">
-        <v>432.45</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -13521,16 +13512,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="C675" s="25">
-        <v>42.43</v>
+        <v>128</v>
       </c>
       <c r="D675" s="26">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="E675" s="27">
-        <v>152.75</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13538,16 +13529,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C676" s="25">
-        <v>6</v>
+        <v>42.43</v>
       </c>
       <c r="D676" s="26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E676" s="27">
-        <v>21</v>
+        <v>152.75</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13555,16 +13546,16 @@
         <v>679</v>
       </c>
       <c r="B677" s="24">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="C677" s="25">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D677" s="26">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="E677" s="27">
-        <v>46.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -13572,16 +13563,16 @@
         <v>680</v>
       </c>
       <c r="B678" s="24">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C678" s="25">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="D678" s="26">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="E678" s="27">
-        <v>73.13</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
@@ -13589,16 +13580,16 @@
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C679" s="25">
-        <v>43.5</v>
+        <v>17</v>
       </c>
       <c r="D679" s="26">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="E679" s="27">
-        <v>108.75</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13606,16 +13597,16 @@
         <v>682</v>
       </c>
       <c r="B680" s="24">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C680" s="25">
-        <v>12</v>
+        <v>43.5</v>
       </c>
       <c r="D680" s="26">
-        <v>7.31</v>
+        <v>2.5</v>
       </c>
       <c r="E680" s="27">
-        <v>87.75</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -13623,16 +13614,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C681" s="25">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D681" s="26">
-        <v>5.75</v>
+        <v>7.31</v>
       </c>
       <c r="E681" s="27">
-        <v>17.25</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13640,16 +13631,16 @@
         <v>684</v>
       </c>
       <c r="B682" s="24">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C682" s="25">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="D682" s="26">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="E682" s="27">
-        <v>78.3</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -13657,16 +13648,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C683" s="25">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="D683" s="26">
-        <v>2.25</v>
+        <v>5.8</v>
       </c>
       <c r="E683" s="27">
-        <v>3.38</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13674,16 +13665,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C684" s="25">
-        <v>96</v>
+        <v>23.5</v>
       </c>
       <c r="D684" s="26">
         <v>2.25</v>
       </c>
       <c r="E684" s="27">
-        <v>216</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13691,16 +13682,16 @@
         <v>687</v>
       </c>
       <c r="B685" s="24">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="C685" s="25">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D685" s="26">
-        <v>8.84</v>
+        <v>2.25</v>
       </c>
       <c r="E685" s="27">
-        <v>88.38</v>
+        <v>216</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -13708,16 +13699,16 @@
         <v>688</v>
       </c>
       <c r="B686" s="24">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C686" s="25">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D686" s="26">
-        <v>2.75</v>
+        <v>8.84</v>
       </c>
       <c r="E686" s="27">
-        <v>132</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -13725,16 +13716,16 @@
         <v>689</v>
       </c>
       <c r="B687" s="24">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C687" s="25">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="D687" s="26">
         <v>2.75</v>
       </c>
       <c r="E687" s="27">
-        <v>211.75</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -13742,16 +13733,16 @@
         <v>690</v>
       </c>
       <c r="B688" s="24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C688" s="25">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D688" s="26">
         <v>2.75</v>
       </c>
       <c r="E688" s="27">
-        <v>85.25</v>
+        <v>184.25</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -13759,16 +13750,16 @@
         <v>691</v>
       </c>
       <c r="B689" s="24">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C689" s="25">
-        <v>13.5</v>
+        <v>31</v>
       </c>
       <c r="D689" s="26">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="E689" s="27">
-        <v>54</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -13776,44 +13767,44 @@
         <v>692</v>
       </c>
       <c r="B690" s="24">
-        <v>3</v>
-      </c>
-      <c r="C690" s="28"/>
-      <c r="D690" s="29"/>
-      <c r="E690" s="28"/>
+        <v>43</v>
+      </c>
+      <c r="C690" s="25">
+        <v>13.5</v>
+      </c>
+      <c r="D690" s="26">
+        <v>4</v>
+      </c>
+      <c r="E690" s="27">
+        <v>54</v>
+      </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="23" t="s">
         <v>693</v>
       </c>
       <c r="B691" s="24">
-        <v>4</v>
-      </c>
-      <c r="C691" s="25">
-        <v>11.5</v>
-      </c>
-      <c r="D691" s="26">
-        <v>4.25</v>
-      </c>
-      <c r="E691" s="27">
-        <v>48.88</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C691" s="28"/>
+      <c r="D691" s="29"/>
+      <c r="E691" s="28"/>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="23" t="s">
         <v>694</v>
       </c>
       <c r="B692" s="24">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C692" s="25">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="D692" s="26">
         <v>4.25</v>
       </c>
       <c r="E692" s="27">
-        <v>63.75</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -13821,16 +13812,16 @@
         <v>695</v>
       </c>
       <c r="B693" s="24">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C693" s="25">
-        <v>15.35</v>
+        <v>15</v>
       </c>
       <c r="D693" s="26">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="E693" s="27">
-        <v>84.43</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
@@ -13838,16 +13829,16 @@
         <v>696</v>
       </c>
       <c r="B694" s="24">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C694" s="25">
-        <v>30.5</v>
+        <v>15.35</v>
       </c>
       <c r="D694" s="26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E694" s="27">
-        <v>152.5</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
@@ -13855,51 +13846,55 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>8</v>
-      </c>
-      <c r="C695" s="28"/>
-      <c r="D695" s="29"/>
-      <c r="E695" s="28"/>
+        <v>18</v>
+      </c>
+      <c r="C695" s="25">
+        <v>30.5</v>
+      </c>
+      <c r="D695" s="26">
+        <v>5</v>
+      </c>
+      <c r="E695" s="27">
+        <v>152.5</v>
+      </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" s="23" t="s">
         <v>698</v>
       </c>
       <c r="B696" s="24">
-        <v>13</v>
-      </c>
-      <c r="C696" s="25">
-        <v>25</v>
-      </c>
-      <c r="D696" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E696" s="27">
-        <v>90</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C696" s="28"/>
+      <c r="D696" s="29"/>
+      <c r="E696" s="28"/>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" s="23" t="s">
         <v>699</v>
       </c>
       <c r="B697" s="24">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C697" s="25">
-        <v>14.5</v>
-      </c>
-      <c r="D697" s="29"/>
-      <c r="E697" s="28"/>
+        <v>25</v>
+      </c>
+      <c r="D697" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E697" s="27">
+        <v>90</v>
+      </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" s="23" t="s">
         <v>700</v>
       </c>
       <c r="B698" s="24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C698" s="25">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="D698" s="29"/>
       <c r="E698" s="28"/>
@@ -13909,10 +13904,10 @@
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C699" s="25">
-        <v>35.340000000000003</v>
+        <v>32</v>
       </c>
       <c r="D699" s="29"/>
       <c r="E699" s="28"/>
@@ -13922,10 +13917,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C700" s="25">
-        <v>2</v>
+        <v>31.34</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13935,10 +13930,10 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C701" s="25">
-        <v>73.5</v>
+        <v>2</v>
       </c>
       <c r="D701" s="29"/>
       <c r="E701" s="28"/>
@@ -13948,10 +13943,10 @@
         <v>704</v>
       </c>
       <c r="B702" s="24">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C702" s="25">
-        <v>48.5</v>
+        <v>73.5</v>
       </c>
       <c r="D702" s="29"/>
       <c r="E702" s="28"/>
@@ -13961,10 +13956,10 @@
         <v>705</v>
       </c>
       <c r="B703" s="24">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="C703" s="25">
-        <v>-2</v>
+        <v>48.5</v>
       </c>
       <c r="D703" s="29"/>
       <c r="E703" s="28"/>
@@ -13974,10 +13969,10 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C704" s="25">
-        <v>15.5</v>
+        <v>-4</v>
       </c>
       <c r="D704" s="29"/>
       <c r="E704" s="28"/>
@@ -13987,10 +13982,10 @@
         <v>707</v>
       </c>
       <c r="B705" s="24">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C705" s="25">
-        <v>50</v>
+        <v>23.5</v>
       </c>
       <c r="D705" s="29"/>
       <c r="E705" s="28"/>
@@ -13999,8 +13994,12 @@
       <c r="A706" s="23" t="s">
         <v>708</v>
       </c>
-      <c r="B706" s="24"/>
-      <c r="C706" s="28"/>
+      <c r="B706" s="24">
+        <v>44</v>
+      </c>
+      <c r="C706" s="25">
+        <v>50</v>
+      </c>
       <c r="D706" s="29"/>
       <c r="E706" s="28"/>
     </row>
@@ -14008,61 +14007,55 @@
       <c r="A707" s="23" t="s">
         <v>709</v>
       </c>
-      <c r="B707" s="24">
-        <v>58</v>
-      </c>
-      <c r="C707" s="25">
-        <v>139.5</v>
-      </c>
-      <c r="D707" s="26">
-        <v>2.93</v>
-      </c>
-      <c r="E707" s="27">
-        <v>408.97</v>
-      </c>
+      <c r="B707" s="24"/>
+      <c r="C707" s="28"/>
+      <c r="D707" s="29"/>
+      <c r="E707" s="28"/>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708" s="23" t="s">
         <v>710</v>
       </c>
-      <c r="B708" s="24"/>
+      <c r="B708" s="24">
+        <v>60</v>
+      </c>
       <c r="C708" s="25">
-        <v>14.5</v>
+        <v>127.5</v>
       </c>
       <c r="D708" s="26">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="E708" s="27">
-        <v>55.1</v>
+        <v>373.79</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" s="23" t="s">
         <v>711</v>
       </c>
-      <c r="B709" s="24">
-        <v>2</v>
-      </c>
+      <c r="B709" s="24"/>
       <c r="C709" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="D709" s="29"/>
-      <c r="E709" s="28"/>
+        <v>14.5</v>
+      </c>
+      <c r="D709" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="E709" s="27">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710" s="23" t="s">
         <v>712</v>
       </c>
-      <c r="B710" s="24"/>
+      <c r="B710" s="24">
+        <v>2</v>
+      </c>
       <c r="C710" s="25">
-        <v>1123</v>
-      </c>
-      <c r="D710" s="26">
-        <v>0.82</v>
-      </c>
-      <c r="E710" s="27">
-        <v>920.86</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="D710" s="29"/>
+      <c r="E710" s="28"/>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711" s="23" t="s">
@@ -14070,27 +14063,29 @@
       </c>
       <c r="B711" s="24"/>
       <c r="C711" s="25">
-        <v>787</v>
+        <v>1123</v>
       </c>
       <c r="D711" s="26">
-        <v>1.1499999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E711" s="27">
-        <v>905.05</v>
+        <v>920.86</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" s="23" t="s">
         <v>714</v>
       </c>
-      <c r="B712" s="24">
-        <v>1</v>
-      </c>
+      <c r="B712" s="24"/>
       <c r="C712" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="D712" s="29"/>
-      <c r="E712" s="28"/>
+        <v>787</v>
+      </c>
+      <c r="D712" s="26">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E712" s="27">
+        <v>905.05</v>
+      </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713" s="23" t="s">
@@ -14099,7 +14094,9 @@
       <c r="B713" s="24">
         <v>1</v>
       </c>
-      <c r="C713" s="28"/>
+      <c r="C713" s="25">
+        <v>-0.5</v>
+      </c>
       <c r="D713" s="29"/>
       <c r="E713" s="28"/>
     </row>
@@ -14108,7 +14105,7 @@
         <v>716</v>
       </c>
       <c r="B714" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C714" s="28"/>
       <c r="D714" s="29"/>
@@ -14119,7 +14116,7 @@
         <v>717</v>
       </c>
       <c r="B715" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C715" s="28"/>
       <c r="D715" s="29"/>
@@ -14152,7 +14149,7 @@
         <v>720</v>
       </c>
       <c r="B718" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C718" s="28"/>
       <c r="D718" s="29"/>
@@ -14163,7 +14160,7 @@
         <v>721</v>
       </c>
       <c r="B719" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C719" s="28"/>
       <c r="D719" s="29"/>
@@ -14174,11 +14171,9 @@
         <v>722</v>
       </c>
       <c r="B720" s="24">
-        <v>3</v>
-      </c>
-      <c r="C720" s="25">
-        <v>-0.03</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C720" s="28"/>
       <c r="D720" s="29"/>
       <c r="E720" s="28"/>
     </row>
@@ -14187,37 +14182,37 @@
         <v>723</v>
       </c>
       <c r="B721" s="24">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C721" s="25">
-        <v>47</v>
-      </c>
-      <c r="D721" s="26">
-        <v>1.6</v>
-      </c>
-      <c r="E721" s="27">
-        <v>75.2</v>
-      </c>
+        <v>-0.03</v>
+      </c>
+      <c r="D721" s="29"/>
+      <c r="E721" s="28"/>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" s="23" t="s">
         <v>724</v>
       </c>
-      <c r="B722" s="24"/>
-      <c r="C722" s="28"/>
-      <c r="D722" s="29"/>
-      <c r="E722" s="28"/>
+      <c r="B722" s="24">
+        <v>18</v>
+      </c>
+      <c r="C722" s="25">
+        <v>47</v>
+      </c>
+      <c r="D722" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="E722" s="27">
+        <v>75.2</v>
+      </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723" s="23" t="s">
         <v>725</v>
       </c>
-      <c r="B723" s="24">
-        <v>19</v>
-      </c>
-      <c r="C723" s="25">
-        <v>385</v>
-      </c>
+      <c r="B723" s="24"/>
+      <c r="C723" s="28"/>
       <c r="D723" s="29"/>
       <c r="E723" s="28"/>
     </row>
@@ -14226,40 +14221,40 @@
         <v>726</v>
       </c>
       <c r="B724" s="24">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C724" s="25">
-        <v>293.5</v>
-      </c>
-      <c r="D724" s="26">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="E724" s="27">
-        <v>340.46</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="D724" s="29"/>
+      <c r="E724" s="28"/>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725" s="23" t="s">
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C725" s="25">
-        <v>-0.45</v>
-      </c>
-      <c r="D725" s="29"/>
-      <c r="E725" s="28"/>
+        <v>253.5</v>
+      </c>
+      <c r="D725" s="26">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E725" s="27">
+        <v>294.06</v>
+      </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726" s="23" t="s">
         <v>728</v>
       </c>
       <c r="B726" s="24">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C726" s="25">
-        <v>-0.79</v>
+        <v>-0.45</v>
       </c>
       <c r="D726" s="29"/>
       <c r="E726" s="28"/>
@@ -14269,9 +14264,11 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>15</v>
-      </c>
-      <c r="C727" s="28"/>
+        <v>80</v>
+      </c>
+      <c r="C727" s="25">
+        <v>-0.79</v>
+      </c>
       <c r="D727" s="29"/>
       <c r="E727" s="28"/>
     </row>
@@ -14280,11 +14277,9 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>53</v>
-      </c>
-      <c r="C728" s="25">
-        <v>-106.15</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C728" s="28"/>
       <c r="D728" s="29"/>
       <c r="E728" s="28"/>
     </row>
@@ -14293,9 +14288,11 @@
         <v>731</v>
       </c>
       <c r="B729" s="24">
-        <v>25</v>
-      </c>
-      <c r="C729" s="28"/>
+        <v>54</v>
+      </c>
+      <c r="C729" s="25">
+        <v>-106.65</v>
+      </c>
       <c r="D729" s="29"/>
       <c r="E729" s="28"/>
     </row>
@@ -14304,33 +14301,27 @@
         <v>732</v>
       </c>
       <c r="B730" s="24">
-        <v>40</v>
-      </c>
-      <c r="C730" s="25">
-        <v>10.25</v>
-      </c>
-      <c r="D730" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E730" s="27">
-        <v>25.63</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C730" s="28"/>
+      <c r="D730" s="29"/>
+      <c r="E730" s="28"/>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731" s="23" t="s">
         <v>733</v>
       </c>
       <c r="B731" s="24">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="C731" s="25">
-        <v>74.5</v>
+        <v>10.25</v>
       </c>
       <c r="D731" s="26">
         <v>2.5</v>
       </c>
       <c r="E731" s="27">
-        <v>186.25</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
@@ -14338,16 +14329,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C732" s="25">
-        <v>5</v>
+        <v>74.5</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>12.5</v>
+        <v>186.25</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14355,16 +14346,16 @@
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C733" s="25">
-        <v>8.25</v>
+        <v>5</v>
       </c>
       <c r="D733" s="26">
         <v>2.5</v>
       </c>
       <c r="E733" s="27">
-        <v>20.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -14372,16 +14363,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C734" s="25">
-        <v>45.25</v>
+        <v>8.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>113.13</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14389,16 +14380,16 @@
         <v>737</v>
       </c>
       <c r="B735" s="24">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="C735" s="25">
-        <v>7.5</v>
+        <v>45.25</v>
       </c>
       <c r="D735" s="26">
         <v>2.5</v>
       </c>
       <c r="E735" s="27">
-        <v>18.75</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.25">
@@ -14406,16 +14397,16 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C736" s="25">
-        <v>48.5</v>
+        <v>7.5</v>
       </c>
       <c r="D736" s="26">
         <v>2.5</v>
       </c>
       <c r="E736" s="27">
-        <v>121.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.25">
@@ -14423,16 +14414,16 @@
         <v>739</v>
       </c>
       <c r="B737" s="24">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C737" s="25">
-        <v>11.25</v>
+        <v>48.5</v>
       </c>
       <c r="D737" s="26">
         <v>2.5</v>
       </c>
       <c r="E737" s="27">
-        <v>28.13</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
@@ -14440,36 +14431,53 @@
         <v>740</v>
       </c>
       <c r="B738" s="24">
-        <v>11</v>
-      </c>
-      <c r="C738" s="28"/>
-      <c r="D738" s="29"/>
-      <c r="E738" s="28"/>
+        <v>80</v>
+      </c>
+      <c r="C738" s="25">
+        <v>11.25</v>
+      </c>
+      <c r="D738" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E738" s="27">
+        <v>28.13</v>
+      </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A739" s="23" t="s">
         <v>741</v>
       </c>
       <c r="B739" s="24">
-        <v>197</v>
-      </c>
-      <c r="C739" s="25">
-        <v>-583</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C739" s="28"/>
       <c r="D739" s="29"/>
       <c r="E739" s="28"/>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A740" s="30" t="s">
+      <c r="A740" s="23" t="s">
         <v>742</v>
       </c>
-      <c r="B740" s="31"/>
-      <c r="C740" s="32">
-        <v>42386.8</v>
-      </c>
-      <c r="D740" s="33"/>
-      <c r="E740" s="34">
-        <v>106324.44</v>
+      <c r="B740" s="24">
+        <v>201</v>
+      </c>
+      <c r="C740" s="25">
+        <v>-588</v>
+      </c>
+      <c r="D740" s="29"/>
+      <c r="E740" s="28"/>
+    </row>
+    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A741" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B741" s="31"/>
+      <c r="C741" s="32">
+        <v>41404.800000000003</v>
+      </c>
+      <c r="D741" s="33"/>
+      <c r="E741" s="34">
+        <v>104859.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -3390,16 +3390,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>94.16</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C43" s="25">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>113.41</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C47" s="25">
-        <v>73.5</v>
+        <v>71.5</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>93.15</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C48" s="25">
-        <v>51.85</v>
+        <v>39.85</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>65.84</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3713,16 +3713,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C60" s="25">
-        <v>858.5</v>
+        <v>852</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>976.61</v>
+        <v>969.22</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C61" s="25">
-        <v>911.5</v>
+        <v>907</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1038.51</v>
+        <v>1033.3800000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3882,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C71" s="25">
-        <v>462</v>
+        <v>458.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>646.79999999999995</v>
+        <v>641.9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3916,16 +3916,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C73" s="25">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>684.6</v>
+        <v>680.4</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3961,16 +3961,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C76" s="25">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>340.8</v>
+        <v>333.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4097,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C84" s="25">
-        <v>1182.5</v>
+        <v>1178.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1537.25</v>
+        <v>1532.05</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4182,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C89" s="25">
-        <v>184.5</v>
+        <v>172.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>270.8</v>
+        <v>253.19</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4250,16 +4250,16 @@
         <v>95</v>
       </c>
       <c r="B93" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C93" s="25">
-        <v>247.5</v>
+        <v>242.5</v>
       </c>
       <c r="D93" s="26">
         <v>2.29</v>
       </c>
       <c r="E93" s="27">
-        <v>567.79</v>
+        <v>556.32000000000005</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,16 +4297,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C96" s="25">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>74.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4391,16 +4391,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C102" s="25">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D102" s="26">
         <v>0.87</v>
       </c>
       <c r="E102" s="27">
-        <v>247.2</v>
+        <v>242.85</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4423,16 +4423,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C104" s="25">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>177.5</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4474,16 +4474,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C107" s="25">
-        <v>228.5</v>
+        <v>223.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>571.25</v>
+        <v>558.75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4491,16 +4491,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C108" s="25">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>607.5</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5541,16 +5541,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C178" s="25">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="D178" s="26">
         <v>3.25</v>
       </c>
       <c r="E178" s="27">
-        <v>105.63</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -6740,16 +6740,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C253" s="25">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D253" s="26">
         <v>3.9</v>
       </c>
       <c r="E253" s="27">
-        <v>421.2</v>
+        <v>413.4</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -7794,16 +7794,16 @@
         <v>321</v>
       </c>
       <c r="B319" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C319" s="25">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D319" s="26">
         <v>4.0999999999999996</v>
       </c>
       <c r="E319" s="27">
-        <v>10.25</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -8020,16 +8020,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C333" s="25">
-        <v>109.91</v>
+        <v>104.91</v>
       </c>
       <c r="D333" s="26">
         <v>4.28</v>
       </c>
       <c r="E333" s="27">
-        <v>470.41</v>
+        <v>449.01</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -10573,16 +10573,16 @@
         <v>494</v>
       </c>
       <c r="B492" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C492" s="25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D492" s="26">
         <v>9</v>
       </c>
       <c r="E492" s="27">
-        <v>58.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -12223,10 +12223,10 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C594" s="25">
-        <v>195.5</v>
+        <v>195</v>
       </c>
       <c r="D594" s="29"/>
       <c r="E594" s="28"/>
@@ -12895,16 +12895,16 @@
         <v>640</v>
       </c>
       <c r="B638" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C638" s="25">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D638" s="26">
         <v>1.5</v>
       </c>
       <c r="E638" s="27">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
@@ -14473,11 +14473,11 @@
       </c>
       <c r="B741" s="31"/>
       <c r="C741" s="32">
-        <v>41404.800000000003</v>
+        <v>41291.800000000003</v>
       </c>
       <c r="D741" s="33"/>
       <c r="E741" s="34">
-        <v>104859.52</v>
+        <v>104635.14</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -2955,16 +2955,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="25">
-        <v>291.5</v>
+        <v>288</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3164,16 +3164,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" s="25">
-        <v>124</v>
+        <v>121.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3249,16 +3249,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" s="25">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>54.6</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3277,16 +3277,16 @@
         <v>36</v>
       </c>
       <c r="B34" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34" s="25">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D34" s="26">
         <v>2.5</v>
       </c>
       <c r="E34" s="27">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3294,16 +3294,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" s="25">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>331.2</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3441,16 +3441,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C44" s="25">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D44" s="26">
         <v>2.74</v>
       </c>
       <c r="E44" s="27">
-        <v>79.430000000000007</v>
+        <v>71.209999999999994</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C48" s="25">
-        <v>39.85</v>
+        <v>30.85</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>50.63</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3560,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" s="25">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3577,33 +3577,27 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>39</v>
-      </c>
-      <c r="C52" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="D52" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E52" s="27">
-        <v>6.25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="28"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C53" s="25">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>655</v>
+        <v>647.5</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3628,16 +3622,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" s="25">
-        <v>234.15</v>
+        <v>232.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>643.91</v>
+        <v>638.41</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3645,16 +3639,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="25">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>495</v>
+        <v>484.2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3730,16 +3724,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" s="25">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1033.3800000000001</v>
+        <v>1028.82</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3961,16 +3955,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C76" s="25">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>333.6</v>
+        <v>321.60000000000002</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +3989,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C78" s="25">
-        <v>111.5</v>
+        <v>101.5</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>133.80000000000001</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4029,16 +4023,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C80" s="25">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>556.79999999999995</v>
+        <v>544.79999999999995</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4063,16 +4057,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C82" s="25">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>602.4</v>
+        <v>590.4</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4131,16 +4125,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C86" s="25">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1914.2</v>
+        <v>1909.1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4233,16 +4227,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" s="25">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D92" s="26">
         <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>1316</v>
+        <v>1310.58</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,16 +4291,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C96" s="25">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>72</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4391,16 +4385,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C102" s="25">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D102" s="26">
         <v>0.87</v>
       </c>
       <c r="E102" s="27">
-        <v>242.85</v>
+        <v>234.15</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4423,16 +4417,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C104" s="25">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4457,16 +4451,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C106" s="25">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>517.5</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4997,16 +4991,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C144" s="25">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D144" s="26">
         <v>18.5</v>
       </c>
       <c r="E144" s="27">
-        <v>166.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5178,16 +5172,16 @@
         <v>157</v>
       </c>
       <c r="B155" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155" s="25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D155" s="26">
         <v>18.5</v>
       </c>
       <c r="E155" s="27">
-        <v>120.25</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5635,16 +5629,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C184" s="25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D184" s="26">
         <v>2.8</v>
       </c>
       <c r="E184" s="27">
-        <v>95.31</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -5686,16 +5680,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C187" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D187" s="26">
         <v>3.33</v>
       </c>
       <c r="E187" s="27">
-        <v>53.28</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5770,16 +5764,16 @@
         <v>195</v>
       </c>
       <c r="B193" s="24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C193" s="25">
-        <v>168.81</v>
+        <v>166.81</v>
       </c>
       <c r="D193" s="26">
         <v>2.65</v>
       </c>
       <c r="E193" s="27">
-        <v>447.35</v>
+        <v>442.05</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -5832,16 +5826,16 @@
         <v>199</v>
       </c>
       <c r="B197" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C197" s="25">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D197" s="26">
         <v>5</v>
       </c>
       <c r="E197" s="27">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -6149,16 +6143,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C216" s="25">
-        <v>284.5</v>
+        <v>283</v>
       </c>
       <c r="D216" s="26">
         <v>2.7</v>
       </c>
       <c r="E216" s="27">
-        <v>768.15</v>
+        <v>764.1</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6302,16 +6296,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C225" s="25">
-        <v>99.5</v>
+        <v>97.5</v>
       </c>
       <c r="D225" s="26">
         <v>2.7</v>
       </c>
       <c r="E225" s="27">
-        <v>268.64999999999998</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6447,16 +6441,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C234" s="25">
-        <v>134.5</v>
+        <v>129.5</v>
       </c>
       <c r="D234" s="26">
         <v>3.5</v>
       </c>
       <c r="E234" s="27">
-        <v>470.75</v>
+        <v>453.25</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6689,16 +6683,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C250" s="25">
-        <v>142.5</v>
+        <v>134.5</v>
       </c>
       <c r="D250" s="26">
         <v>3</v>
       </c>
       <c r="E250" s="27">
-        <v>427.5</v>
+        <v>403.5</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6740,16 +6734,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C253" s="25">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D253" s="26">
         <v>3.9</v>
       </c>
       <c r="E253" s="27">
-        <v>413.4</v>
+        <v>409.5</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6819,16 +6813,16 @@
         <v>260</v>
       </c>
       <c r="B258" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C258" s="25">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D258" s="26">
         <v>3.5</v>
       </c>
       <c r="E258" s="27">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -6853,16 +6847,16 @@
         <v>262</v>
       </c>
       <c r="B260" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C260" s="25">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D260" s="26">
         <v>3.5</v>
       </c>
       <c r="E260" s="27">
-        <v>147</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -7033,16 +7027,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C272" s="25">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D272" s="26">
         <v>3.1</v>
       </c>
       <c r="E272" s="27">
-        <v>322.39999999999998</v>
+        <v>319.3</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7112,16 +7106,16 @@
         <v>279</v>
       </c>
       <c r="B277" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C277" s="25">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D277" s="26">
         <v>4.42</v>
       </c>
       <c r="E277" s="27">
-        <v>119.31</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -7129,16 +7123,16 @@
         <v>280</v>
       </c>
       <c r="B278" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C278" s="25">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="D278" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E278" s="27">
-        <v>464.43</v>
+        <v>457.83</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -7247,16 +7241,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C286" s="25">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D286" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E286" s="27">
-        <v>212.67</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7451,16 +7445,16 @@
         <v>300</v>
       </c>
       <c r="B298" s="24">
+        <v>8</v>
+      </c>
+      <c r="C298" s="25">
         <v>7</v>
-      </c>
-      <c r="C298" s="25">
-        <v>8.5</v>
       </c>
       <c r="D298" s="26">
         <v>5.78</v>
       </c>
       <c r="E298" s="27">
-        <v>49.12</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -8020,16 +8014,16 @@
         <v>335</v>
       </c>
       <c r="B333" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C333" s="25">
-        <v>104.91</v>
+        <v>103.91</v>
       </c>
       <c r="D333" s="26">
         <v>4.28</v>
       </c>
       <c r="E333" s="27">
-        <v>449.01</v>
+        <v>444.73</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8071,16 +8065,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C336" s="25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D336" s="26">
         <v>8</v>
       </c>
       <c r="E336" s="27">
-        <v>136.02000000000001</v>
+        <v>128.02000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8604,16 +8598,16 @@
         <v>371</v>
       </c>
       <c r="B369" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C369" s="25">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D369" s="26">
         <v>7.2</v>
       </c>
       <c r="E369" s="27">
-        <v>151.19999999999999</v>
+        <v>108</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8740,16 +8734,16 @@
         <v>379</v>
       </c>
       <c r="B377" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C377" s="25">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D377" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E377" s="27">
-        <v>176.3</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8859,16 +8853,16 @@
         <v>386</v>
       </c>
       <c r="B384" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C384" s="25">
-        <v>84.5</v>
+        <v>79.5</v>
       </c>
       <c r="D384" s="26">
         <v>3.6</v>
       </c>
       <c r="E384" s="27">
-        <v>304.2</v>
+        <v>286.2</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -9363,16 +9357,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C416" s="25">
-        <v>47</v>
+        <v>74.5</v>
       </c>
       <c r="D416" s="26">
         <v>5.2</v>
       </c>
       <c r="E416" s="27">
-        <v>244.4</v>
+        <v>387.4</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -10008,16 +10002,16 @@
         <v>459</v>
       </c>
       <c r="B457" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C457" s="25">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D457" s="26">
         <v>9.75</v>
       </c>
       <c r="E457" s="27">
-        <v>24.38</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -10349,16 +10343,16 @@
         <v>480</v>
       </c>
       <c r="B478" s="24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C478" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D478" s="26">
         <v>9.5</v>
       </c>
       <c r="E478" s="27">
-        <v>180.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10556,16 +10550,16 @@
         <v>493</v>
       </c>
       <c r="B491" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C491" s="25">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D491" s="26">
         <v>10.199999999999999</v>
       </c>
       <c r="E491" s="27">
-        <v>25.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -11171,16 +11165,16 @@
         <v>532</v>
       </c>
       <c r="B530" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C530" s="25">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="D530" s="26">
         <v>1.4</v>
       </c>
       <c r="E530" s="27">
-        <v>37.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -12324,16 +12318,16 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C601" s="25">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="D601" s="26">
         <v>0.85</v>
       </c>
       <c r="E601" s="27">
-        <v>34.43</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -12844,16 +12838,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C635" s="25">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D635" s="26">
         <v>2.76</v>
       </c>
       <c r="E635" s="27">
-        <v>110.35</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -13767,16 +13761,16 @@
         <v>692</v>
       </c>
       <c r="B690" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C690" s="25">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="D690" s="26">
         <v>4</v>
       </c>
       <c r="E690" s="27">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
@@ -13969,10 +13963,10 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C704" s="25">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D704" s="29"/>
       <c r="E704" s="28"/>
@@ -14234,16 +14228,16 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C725" s="25">
-        <v>253.5</v>
+        <v>252.5</v>
       </c>
       <c r="D725" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E725" s="27">
-        <v>294.06</v>
+        <v>292.89999999999998</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
@@ -14414,16 +14408,16 @@
         <v>739</v>
       </c>
       <c r="B737" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C737" s="25">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="D737" s="26">
         <v>2.5</v>
       </c>
       <c r="E737" s="27">
-        <v>121.25</v>
+        <v>118.75</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
@@ -14473,11 +14467,11 @@
       </c>
       <c r="B741" s="31"/>
       <c r="C741" s="32">
-        <v>41291.800000000003</v>
+        <v>41057.300000000003</v>
       </c>
       <c r="D741" s="33"/>
       <c r="E741" s="34">
-        <v>104635.14</v>
+        <v>103980.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -125,7 +125,7 @@
     <t>1019 PATRIKA (DC)</t>
   </si>
   <si>
-    <t>1020 PATRIKA (18.03)</t>
+    <t>1020 PATRIKA (18.03) 1750 &amp; 10K 22.03</t>
   </si>
   <si>
     <t>1021 PATRIKA</t>
@@ -173,7 +173,7 @@
     <t>1035 PATRIKA (DCU)</t>
   </si>
   <si>
-    <t>1101 PATRIKA (O.2591) (5200 14.03)</t>
+    <t>1101 PATRIKA (O.2591) (5200 18.03)</t>
   </si>
   <si>
     <t>1102 PATRIKA (P.2591)</t>
@@ -188,7 +188,7 @@
     <t>1105 PATRIKA</t>
   </si>
   <si>
-    <t>1106 PATRIKA-YELLOW (18.03)</t>
+    <t>1106 PATRIKA-YELLOW (24000 19.03)</t>
   </si>
   <si>
     <t>1107 PATRIKA-RED</t>
@@ -593,7 +593,7 @@
     <t>4259 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>4260 PATRIKA</t>
+    <t>4260 PATRIKA (1100 18.03)</t>
   </si>
   <si>
     <t>4261 PATRIKA (JC)</t>
@@ -857,7 +857,7 @@
     <t>5079 PATRIKA</t>
   </si>
   <si>
-    <t>5080 PATRIKA</t>
+    <t>5080 PATRIKA (500 19.01)</t>
   </si>
   <si>
     <t>5081 PATRIKA</t>
@@ -2063,7 +2063,7 @@
     <t>9357 CARDS</t>
   </si>
   <si>
-    <t>9358 CARDS AGYA (2000)</t>
+    <t>9358 CARDS</t>
   </si>
   <si>
     <t>9359 CARDS (Ri)</t>
@@ -2904,16 +2904,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="24">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" s="25">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D11" s="26">
         <v>1.8</v>
       </c>
       <c r="E11" s="27">
-        <v>203.4</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2921,16 +2921,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="25">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>261.3</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2938,16 +2938,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="25">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>243.75</v>
+        <v>237.9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2955,16 +2955,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C14" s="25">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2972,16 +2972,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" s="25">
-        <v>91</v>
+        <v>77.5</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>182</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3006,16 +3006,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="25">
-        <v>268</v>
+        <v>264.5</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>562.79999999999995</v>
+        <v>555.45000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3096,16 +3096,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" s="25">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D23" s="26">
         <v>1.8</v>
       </c>
       <c r="E23" s="27">
-        <v>156.6</v>
+        <v>154.80000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3130,16 +3130,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="25">
-        <v>65</v>
+        <v>51.5</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>107.25</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3164,16 +3164,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="25">
-        <v>121.5</v>
+        <v>119.5</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3181,16 +3181,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C28" s="25">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>106</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3311,16 +3311,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C36" s="25">
-        <v>123.5</v>
+        <v>117</v>
       </c>
       <c r="D36" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E36" s="27">
-        <v>284.05</v>
+        <v>269.10000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3373,16 +3373,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C40" s="25">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D40" s="26">
         <v>2.14</v>
       </c>
       <c r="E40" s="27">
-        <v>11.77</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3390,16 +3390,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>89.88</v>
+        <v>85.6</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3407,16 +3407,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C42" s="25">
-        <v>52.5</v>
+        <v>82.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>128.56</v>
+        <v>202.42</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3424,16 +3424,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C43" s="25">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>64.099999999999994</v>
+        <v>325.82</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3441,16 +3441,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C44" s="25">
-        <v>26</v>
+        <v>89.5</v>
       </c>
       <c r="D44" s="26">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="E44" s="27">
-        <v>71.209999999999994</v>
+        <v>243.12</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,16 +3492,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C47" s="25">
-        <v>71.5</v>
+        <v>58</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>90.62</v>
+        <v>73.510000000000005</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3509,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C48" s="25">
-        <v>30.85</v>
+        <v>72.349999999999994</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>39.22</v>
+        <v>91.73</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3543,16 +3543,16 @@
         <v>52</v>
       </c>
       <c r="B50" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C50" s="25">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D50" s="26">
         <v>1.4</v>
       </c>
       <c r="E50" s="27">
-        <v>57.4</v>
+        <v>39.200000000000003</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3560,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C51" s="25">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>549</v>
+        <v>469.8</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3588,16 +3588,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C53" s="25">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>647.5</v>
+        <v>602.5</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3605,16 +3605,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C54" s="25">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D54" s="26">
         <v>2.75</v>
       </c>
       <c r="E54" s="27">
-        <v>343.75</v>
+        <v>313.5</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3639,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C56" s="25">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>484.2</v>
+        <v>462.6</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3656,16 +3656,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C57" s="25">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>172.9</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3673,16 +3673,16 @@
         <v>60</v>
       </c>
       <c r="B58" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="25">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D58" s="26">
         <v>2.1</v>
       </c>
       <c r="E58" s="27">
-        <v>58.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3690,16 +3690,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C59" s="25">
-        <v>58.25</v>
+        <v>55.25</v>
       </c>
       <c r="D59" s="26">
         <v>1.9</v>
       </c>
       <c r="E59" s="27">
-        <v>110.68</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3707,16 +3707,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C60" s="25">
-        <v>852</v>
+        <v>812</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>969.22</v>
+        <v>923.71</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,16 +3724,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C61" s="25">
-        <v>903</v>
+        <v>852</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>1028.82</v>
+        <v>970.72</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3758,7 +3758,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="24">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C63" s="28"/>
       <c r="D63" s="29"/>
@@ -3780,16 +3780,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C65" s="25">
-        <v>243</v>
+        <v>237.5</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>400.95</v>
+        <v>391.88</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3825,16 +3825,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C68" s="25">
-        <v>313.5</v>
+        <v>259</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>517.28</v>
+        <v>427.35</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,16 +3859,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C70" s="25">
-        <v>442.5</v>
+        <v>369</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>619.5</v>
+        <v>516.6</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3876,16 +3876,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C71" s="25">
-        <v>458.5</v>
+        <v>409</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>641.9</v>
+        <v>572.6</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3893,16 +3893,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C72" s="25">
-        <v>472.5</v>
+        <v>421.5</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>661.5</v>
+        <v>590.1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,16 +3910,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C73" s="25">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>680.4</v>
+        <v>620.20000000000005</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3927,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="24">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C74" s="25">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="D74" s="26">
         <v>1.2</v>
       </c>
       <c r="E74" s="27">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3955,16 +3955,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C76" s="25">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>321.60000000000002</v>
+        <v>268.8</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3989,16 +3989,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C78" s="25">
-        <v>101.5</v>
+        <v>85</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>121.8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4006,16 +4006,16 @@
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C79" s="25">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>525.6</v>
+        <v>487.2</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4023,16 +4023,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C80" s="25">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>544.79999999999995</v>
+        <v>537.6</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4074,16 +4074,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C83" s="25">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>662.4</v>
+        <v>650.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4091,16 +4091,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C84" s="25">
-        <v>1178.5</v>
+        <v>1087</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1532.05</v>
+        <v>1413.1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4108,16 +4108,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C85" s="25">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1656.2</v>
+        <v>1634.75</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4125,16 +4125,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C86" s="25">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1909.1</v>
+        <v>1902.3</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4142,16 +4142,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C87" s="25">
-        <v>712.5</v>
+        <v>708</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1211.25</v>
+        <v>1203.5999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4159,16 +4159,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C88" s="25">
-        <v>1032.5</v>
+        <v>1012.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1755.25</v>
+        <v>1721.25</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4176,16 +4176,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C89" s="25">
-        <v>172.5</v>
+        <v>162.5</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>253.19</v>
+        <v>238.51</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4193,16 +4193,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C90" s="25">
-        <v>268.7</v>
+        <v>254.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>344.66</v>
+        <v>326.7</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4210,16 +4210,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C91" s="25">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>60.56</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4227,16 +4227,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C92" s="25">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="D92" s="26">
         <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>1310.58</v>
+        <v>1288.8800000000001</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4274,16 +4274,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C95" s="25">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>324</v>
+        <v>312.3</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4291,16 +4291,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C96" s="25">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>69.3</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4308,27 +4308,33 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>45</v>
-      </c>
-      <c r="C97" s="28"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="28"/>
+        <v>46</v>
+      </c>
+      <c r="C97" s="25">
+        <v>118</v>
+      </c>
+      <c r="D97" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="E97" s="27">
+        <v>106.2</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="23" t="s">
         <v>100</v>
       </c>
       <c r="B98" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C98" s="25">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D98" s="26">
         <v>1.65</v>
       </c>
       <c r="E98" s="27">
-        <v>181.5</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4336,16 +4342,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C99" s="25">
-        <v>297.5</v>
+        <v>261</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>490.88</v>
+        <v>430.65</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4385,16 +4391,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C102" s="25">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="D102" s="26">
         <v>0.87</v>
       </c>
       <c r="E102" s="27">
-        <v>234.15</v>
+        <v>221.09</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4417,16 +4423,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C104" s="25">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4515,10 +4521,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C110" s="25">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4591,10 +4597,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C116" s="25">
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4604,10 +4610,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C117" s="25">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4617,10 +4623,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" s="25">
-        <v>-21</v>
+        <v>-31</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
@@ -4643,11 +4649,9 @@
         <v>122</v>
       </c>
       <c r="B120" s="24">
-        <v>1</v>
-      </c>
-      <c r="C120" s="25">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C120" s="28"/>
       <c r="D120" s="29"/>
       <c r="E120" s="28"/>
     </row>
@@ -4719,10 +4723,10 @@
         <v>128</v>
       </c>
       <c r="B126" s="24">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C126" s="25">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="D126" s="29"/>
       <c r="E126" s="28"/>
@@ -4855,16 +4859,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C136" s="25">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>212.5</v>
+        <v>168.75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4889,16 +4893,16 @@
         <v>140</v>
       </c>
       <c r="B138" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C138" s="25">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D138" s="26">
         <v>12.5</v>
       </c>
       <c r="E138" s="27">
-        <v>43.75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4923,16 +4927,16 @@
         <v>142</v>
       </c>
       <c r="B140" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C140" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" s="26">
         <v>12.5</v>
       </c>
       <c r="E140" s="27">
-        <v>50</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4991,16 +4995,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="24">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C144" s="25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D144" s="26">
         <v>18.5</v>
       </c>
       <c r="E144" s="27">
-        <v>92.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5095,9 +5099,15 @@
       <c r="B150" s="24">
         <v>18</v>
       </c>
-      <c r="C150" s="28"/>
-      <c r="D150" s="29"/>
-      <c r="E150" s="28"/>
+      <c r="C150" s="25">
+        <v>1</v>
+      </c>
+      <c r="D150" s="26">
+        <v>18.5</v>
+      </c>
+      <c r="E150" s="27">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
@@ -5155,16 +5165,16 @@
         <v>156</v>
       </c>
       <c r="B154" s="24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C154" s="25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="D154" s="26">
         <v>18.5</v>
       </c>
       <c r="E154" s="27">
-        <v>286.75</v>
+        <v>268.25</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -5206,16 +5216,16 @@
         <v>159</v>
       </c>
       <c r="B157" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C157" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D157" s="26">
         <v>11.5</v>
       </c>
       <c r="E157" s="27">
-        <v>80.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5240,16 +5250,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C159" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" s="26">
         <v>11.5</v>
       </c>
       <c r="E159" s="27">
-        <v>23</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5353,16 +5363,16 @@
         <v>168</v>
       </c>
       <c r="B166" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C166" s="25">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="D166" s="26">
         <v>11.5</v>
       </c>
       <c r="E166" s="27">
-        <v>166.75</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -5449,16 +5459,16 @@
         <v>174</v>
       </c>
       <c r="B172" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C172" s="25">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D172" s="26">
         <v>0.89</v>
       </c>
       <c r="E172" s="27">
-        <v>87.98</v>
+        <v>74.650000000000006</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -5535,16 +5545,16 @@
         <v>180</v>
       </c>
       <c r="B178" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C178" s="25">
-        <v>30.5</v>
+        <v>24.5</v>
       </c>
       <c r="D178" s="26">
         <v>3.25</v>
       </c>
       <c r="E178" s="27">
-        <v>99.13</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5629,16 +5639,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="24">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C184" s="25">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D184" s="26">
         <v>2.8</v>
       </c>
       <c r="E184" s="27">
-        <v>89.7</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -5680,16 +5690,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C187" s="25">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="D187" s="26">
         <v>3.33</v>
       </c>
       <c r="E187" s="27">
-        <v>43.29</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5747,16 +5757,16 @@
         <v>194</v>
       </c>
       <c r="B192" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C192" s="25">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="D192" s="26">
         <v>2.76</v>
       </c>
       <c r="E192" s="27">
-        <v>33.14</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -5764,16 +5774,16 @@
         <v>195</v>
       </c>
       <c r="B193" s="24">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C193" s="25">
-        <v>166.81</v>
+        <v>162.81</v>
       </c>
       <c r="D193" s="26">
         <v>2.65</v>
       </c>
       <c r="E193" s="27">
-        <v>442.05</v>
+        <v>431.45</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -5877,16 +5887,16 @@
         <v>202</v>
       </c>
       <c r="B200" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C200" s="25">
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="D200" s="26">
         <v>4.5</v>
       </c>
       <c r="E200" s="27">
-        <v>117</v>
+        <v>105.75</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -6024,16 +6034,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C209" s="25">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.6</v>
       </c>
       <c r="E209" s="27">
-        <v>22.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6041,16 +6051,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C210" s="25">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D210" s="26">
         <v>2.6</v>
       </c>
       <c r="E210" s="27">
-        <v>179.4</v>
+        <v>153.4</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,16 +6153,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C216" s="25">
-        <v>283</v>
+        <v>273.5</v>
       </c>
       <c r="D216" s="26">
         <v>2.7</v>
       </c>
       <c r="E216" s="27">
-        <v>764.1</v>
+        <v>738.45</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,16 +6170,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C217" s="25">
-        <v>212.5</v>
+        <v>209.5</v>
       </c>
       <c r="D217" s="26">
         <v>2.7</v>
       </c>
       <c r="E217" s="27">
-        <v>573.75</v>
+        <v>565.65</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6177,16 +6187,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C218" s="25">
-        <v>91</v>
+        <v>82.5</v>
       </c>
       <c r="D218" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E218" s="27">
-        <v>209.3</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6211,16 +6221,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C220" s="25">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D220" s="26">
         <v>3</v>
       </c>
       <c r="E220" s="27">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6228,16 +6238,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C221" s="25">
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
       <c r="D221" s="26">
         <v>3</v>
       </c>
       <c r="E221" s="27">
-        <v>109.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6245,16 +6255,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C222" s="25">
-        <v>173</v>
+        <v>167.5</v>
       </c>
       <c r="D222" s="26">
         <v>3.93</v>
       </c>
       <c r="E222" s="27">
-        <v>679.75</v>
+        <v>658.14</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,16 +6272,16 @@
         <v>225</v>
       </c>
       <c r="B223" s="24">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C223" s="25">
-        <v>162.75</v>
+        <v>155.25</v>
       </c>
       <c r="D223" s="26">
         <v>3.25</v>
       </c>
       <c r="E223" s="27">
-        <v>528.94000000000005</v>
+        <v>504.56</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6279,16 +6289,16 @@
         <v>226</v>
       </c>
       <c r="B224" s="24">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C224" s="25">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D224" s="26">
         <v>3.64</v>
       </c>
       <c r="E224" s="27">
-        <v>262.10000000000002</v>
+        <v>222.06</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,16 +6306,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C225" s="25">
-        <v>97.5</v>
+        <v>98.5</v>
       </c>
       <c r="D225" s="26">
         <v>2.7</v>
       </c>
       <c r="E225" s="27">
-        <v>263.25</v>
+        <v>265.95</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6339,16 +6349,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C228" s="25">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D228" s="26">
         <v>2.66</v>
       </c>
       <c r="E228" s="27">
-        <v>289.94</v>
+        <v>284.62</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6373,16 +6383,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C230" s="25">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D230" s="26">
         <v>4</v>
       </c>
       <c r="E230" s="27">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6407,16 +6417,16 @@
         <v>234</v>
       </c>
       <c r="B232" s="24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C232" s="25">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="D232" s="26">
         <v>3.33</v>
       </c>
       <c r="E232" s="27">
-        <v>31.64</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6441,16 +6451,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C234" s="25">
-        <v>129.5</v>
+        <v>125</v>
       </c>
       <c r="D234" s="26">
         <v>3.5</v>
       </c>
       <c r="E234" s="27">
-        <v>453.25</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6469,16 +6479,16 @@
         <v>238</v>
       </c>
       <c r="B236" s="24">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C236" s="25">
-        <v>32.880000000000003</v>
+        <v>168.88</v>
       </c>
       <c r="D236" s="26">
         <v>3.25</v>
       </c>
       <c r="E236" s="27">
-        <v>106.86</v>
+        <v>548.86</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6486,16 +6496,16 @@
         <v>239</v>
       </c>
       <c r="B237" s="24">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C237" s="25">
-        <v>21.5</v>
+        <v>45.5</v>
       </c>
       <c r="D237" s="26">
         <v>3.25</v>
       </c>
       <c r="E237" s="27">
-        <v>69.88</v>
+        <v>147.88</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -6649,16 +6659,16 @@
         <v>250</v>
       </c>
       <c r="B248" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C248" s="25">
-        <v>38.5</v>
+        <v>31</v>
       </c>
       <c r="D248" s="26">
         <v>4.8</v>
       </c>
       <c r="E248" s="27">
-        <v>184.8</v>
+        <v>148.80000000000001</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -6666,16 +6676,16 @@
         <v>251</v>
       </c>
       <c r="B249" s="24">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C249" s="25">
-        <v>67.900000000000006</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="D249" s="26">
         <v>6.3</v>
       </c>
       <c r="E249" s="27">
-        <v>427.77</v>
+        <v>421.47</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6683,16 +6693,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C250" s="25">
-        <v>134.5</v>
+        <v>122</v>
       </c>
       <c r="D250" s="26">
         <v>3</v>
       </c>
       <c r="E250" s="27">
-        <v>403.5</v>
+        <v>366</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6717,16 +6727,16 @@
         <v>254</v>
       </c>
       <c r="B252" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C252" s="25">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D252" s="26">
         <v>3.8</v>
       </c>
       <c r="E252" s="27">
-        <v>338.2</v>
+        <v>334.4</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -6734,16 +6744,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C253" s="25">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D253" s="26">
         <v>3.9</v>
       </c>
       <c r="E253" s="27">
-        <v>409.5</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6751,16 +6761,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C254" s="25">
-        <v>125.5</v>
+        <v>121.5</v>
       </c>
       <c r="D254" s="26">
         <v>3.9</v>
       </c>
       <c r="E254" s="27">
-        <v>489.45</v>
+        <v>473.85</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6813,16 +6823,16 @@
         <v>260</v>
       </c>
       <c r="B258" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C258" s="25">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D258" s="26">
         <v>3.5</v>
       </c>
       <c r="E258" s="27">
-        <v>182</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -6965,16 +6975,16 @@
         <v>270</v>
       </c>
       <c r="B268" s="24">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C268" s="25">
-        <v>229.78</v>
+        <v>214.28</v>
       </c>
       <c r="D268" s="26">
         <v>4.28</v>
       </c>
       <c r="E268" s="27">
-        <v>983.46</v>
+        <v>917.12</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -7027,16 +7037,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C272" s="25">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D272" s="26">
         <v>3.1</v>
       </c>
       <c r="E272" s="27">
-        <v>319.3</v>
+        <v>300.7</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7055,16 +7065,16 @@
         <v>276</v>
       </c>
       <c r="B274" s="24">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C274" s="25">
-        <v>29.5</v>
+        <v>19.5</v>
       </c>
       <c r="D274" s="26">
         <v>4.5</v>
       </c>
       <c r="E274" s="27">
-        <v>132.75</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -7075,13 +7085,13 @@
         <v>42</v>
       </c>
       <c r="C275" s="25">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D275" s="26">
         <v>6.25</v>
       </c>
       <c r="E275" s="27">
-        <v>193.75</v>
+        <v>243.75</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7089,16 +7099,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C276" s="25">
-        <v>98.37</v>
+        <v>92.37</v>
       </c>
       <c r="D276" s="26">
         <v>4.25</v>
       </c>
       <c r="E276" s="27">
-        <v>418.07</v>
+        <v>392.57</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7106,16 +7116,16 @@
         <v>279</v>
       </c>
       <c r="B277" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C277" s="25">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="D277" s="26">
         <v>4.42</v>
       </c>
       <c r="E277" s="27">
-        <v>117.1</v>
+        <v>112.68</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -7123,16 +7133,16 @@
         <v>280</v>
       </c>
       <c r="B278" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C278" s="25">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D278" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E278" s="27">
-        <v>457.83</v>
+        <v>413.81</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -7179,16 +7189,16 @@
         <v>284</v>
       </c>
       <c r="B282" s="24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C282" s="25">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D282" s="26">
         <v>6.5</v>
       </c>
       <c r="E282" s="27">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7196,16 +7206,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C283" s="25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="D283" s="26">
         <v>5.23</v>
       </c>
       <c r="E283" s="27">
-        <v>86.3</v>
+        <v>81.069999999999993</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7241,16 +7251,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C286" s="25">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D286" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E286" s="27">
-        <v>94.52</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7292,16 +7302,16 @@
         <v>291</v>
       </c>
       <c r="B289" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C289" s="25">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D289" s="26">
         <v>5.0999999999999996</v>
       </c>
       <c r="E289" s="27">
-        <v>188.57</v>
+        <v>178.38</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7309,16 +7319,16 @@
         <v>292</v>
       </c>
       <c r="B290" s="24">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C290" s="25">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D290" s="26">
         <v>5</v>
       </c>
       <c r="E290" s="27">
-        <v>600</v>
+        <v>535</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7326,16 +7336,16 @@
         <v>293</v>
       </c>
       <c r="B291" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C291" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D291" s="26">
         <v>6</v>
       </c>
       <c r="E291" s="27">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -7360,16 +7370,16 @@
         <v>295</v>
       </c>
       <c r="B293" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C293" s="25">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="D293" s="26">
         <v>4.66</v>
       </c>
       <c r="E293" s="27">
-        <v>221.34</v>
+        <v>216.68</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7394,16 +7404,16 @@
         <v>297</v>
       </c>
       <c r="B295" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C295" s="25">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D295" s="26">
         <v>4.5</v>
       </c>
       <c r="E295" s="27">
-        <v>472.5</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7428,16 +7438,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C297" s="25">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D297" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E297" s="27">
-        <v>498.53</v>
+        <v>454.54</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7445,16 +7455,16 @@
         <v>300</v>
       </c>
       <c r="B298" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C298" s="25">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="D298" s="26">
         <v>5.78</v>
       </c>
       <c r="E298" s="27">
-        <v>40.46</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -7479,16 +7489,16 @@
         <v>302</v>
       </c>
       <c r="B300" s="24">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C300" s="25">
-        <v>244.5</v>
+        <v>228.5</v>
       </c>
       <c r="D300" s="26">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="E300" s="27">
-        <v>1484.65</v>
+        <v>1388.4</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -7513,16 +7523,16 @@
         <v>304</v>
       </c>
       <c r="B302" s="24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C302" s="25">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D302" s="26">
         <v>4.2699999999999996</v>
       </c>
       <c r="E302" s="27">
-        <v>973.17</v>
+        <v>951.83</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -7584,13 +7594,13 @@
         <v>77</v>
       </c>
       <c r="C306" s="25">
-        <v>254.25</v>
+        <v>423.25</v>
       </c>
       <c r="D306" s="26">
         <v>4.3</v>
       </c>
       <c r="E306" s="27">
-        <v>1092.77</v>
+        <v>1819.3</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7632,16 +7642,16 @@
         <v>311</v>
       </c>
       <c r="B309" s="24">
+        <v>47</v>
+      </c>
+      <c r="C309" s="25">
         <v>45</v>
-      </c>
-      <c r="C309" s="25">
-        <v>52</v>
       </c>
       <c r="D309" s="26">
         <v>5.13</v>
       </c>
       <c r="E309" s="27">
-        <v>266.76</v>
+        <v>230.85</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -7895,16 +7905,16 @@
         <v>328</v>
       </c>
       <c r="B326" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C326" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D326" s="26">
         <v>5.25</v>
       </c>
       <c r="E326" s="27">
-        <v>36.75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -7997,16 +8007,16 @@
         <v>334</v>
       </c>
       <c r="B332" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C332" s="25">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="D332" s="26">
         <v>5.7</v>
       </c>
       <c r="E332" s="27">
-        <v>71.25</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -8031,16 +8041,16 @@
         <v>336</v>
       </c>
       <c r="B334" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C334" s="25">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D334" s="26">
         <v>4.28</v>
       </c>
       <c r="E334" s="27">
-        <v>659.12</v>
+        <v>650.55999999999995</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -8065,16 +8075,16 @@
         <v>338</v>
       </c>
       <c r="B336" s="24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C336" s="25">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="D336" s="26">
         <v>8</v>
       </c>
       <c r="E336" s="27">
-        <v>128.02000000000001</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8144,16 +8154,16 @@
         <v>343</v>
       </c>
       <c r="B341" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C341" s="25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D341" s="26">
         <v>9</v>
       </c>
       <c r="E341" s="27">
-        <v>166.5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8189,16 +8199,16 @@
         <v>346</v>
       </c>
       <c r="B344" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C344" s="25">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="D344" s="26">
         <v>9</v>
       </c>
       <c r="E344" s="27">
-        <v>112.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -8289,16 +8299,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C350" s="25">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D350" s="26">
         <v>6.46</v>
       </c>
       <c r="E350" s="27">
-        <v>38.76</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8306,16 +8316,16 @@
         <v>353</v>
       </c>
       <c r="B351" s="24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C351" s="25">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D351" s="26">
         <v>8.6999999999999993</v>
       </c>
       <c r="E351" s="27">
-        <v>26.1</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8334,16 +8344,16 @@
         <v>355</v>
       </c>
       <c r="B353" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C353" s="25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D353" s="26">
         <v>5.7</v>
       </c>
       <c r="E353" s="27">
-        <v>159.6</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -8351,16 +8361,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C354" s="25">
-        <v>28</v>
+        <v>33.5</v>
       </c>
       <c r="D354" s="26">
         <v>5.94</v>
       </c>
       <c r="E354" s="27">
-        <v>166.32</v>
+        <v>198.99</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8371,13 +8381,13 @@
         <v>32</v>
       </c>
       <c r="C355" s="25">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D355" s="26">
         <v>6.4</v>
       </c>
       <c r="E355" s="27">
-        <v>137.6</v>
+        <v>131.19999999999999</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -8468,16 +8478,16 @@
         <v>363</v>
       </c>
       <c r="B361" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C361" s="25">
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="D361" s="26">
         <v>7.99</v>
       </c>
       <c r="E361" s="27">
-        <v>295.69</v>
+        <v>259.73</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -8488,13 +8498,13 @@
         <v>15</v>
       </c>
       <c r="C362" s="25">
-        <v>15</v>
+        <v>26.5</v>
       </c>
       <c r="D362" s="26">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
       <c r="E362" s="27">
-        <v>99.62</v>
+        <v>176.44</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8530,16 +8540,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C365" s="25">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="D365" s="26">
         <v>7.76</v>
       </c>
       <c r="E365" s="27">
-        <v>427</v>
+        <v>407.59</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8564,16 +8574,16 @@
         <v>369</v>
       </c>
       <c r="B367" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C367" s="25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D367" s="26">
         <v>6.65</v>
       </c>
       <c r="E367" s="27">
-        <v>172.9</v>
+        <v>166.25</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -8581,16 +8591,16 @@
         <v>370</v>
       </c>
       <c r="B368" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C368" s="25">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D368" s="26">
         <v>5.94</v>
       </c>
       <c r="E368" s="27">
-        <v>142.56</v>
+        <v>106.92</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8632,16 +8642,16 @@
         <v>373</v>
       </c>
       <c r="B371" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C371" s="25">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D371" s="26">
         <v>7.13</v>
       </c>
       <c r="E371" s="27">
-        <v>213.9</v>
+        <v>203.21</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -8666,16 +8676,16 @@
         <v>375</v>
       </c>
       <c r="B373" s="24">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C373" s="25">
-        <v>140.5</v>
+        <v>137.5</v>
       </c>
       <c r="D373" s="26">
         <v>6.6</v>
       </c>
       <c r="E373" s="27">
-        <v>927.3</v>
+        <v>907.5</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8683,16 +8693,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C374" s="25">
-        <v>29.5</v>
+        <v>27</v>
       </c>
       <c r="D374" s="26">
         <v>7.68</v>
       </c>
       <c r="E374" s="27">
-        <v>226.48</v>
+        <v>207.29</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8737,13 +8747,13 @@
         <v>64</v>
       </c>
       <c r="C377" s="25">
-        <v>20.5</v>
+        <v>49</v>
       </c>
       <c r="D377" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E377" s="27">
-        <v>168.1</v>
+        <v>401.8</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8955,16 +8965,16 @@
         <v>392</v>
       </c>
       <c r="B390" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C390" s="25">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="D390" s="26">
         <v>8</v>
       </c>
       <c r="E390" s="27">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -9051,16 +9061,16 @@
         <v>398</v>
       </c>
       <c r="B396" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C396" s="25">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="D396" s="26">
         <v>9.8800000000000008</v>
       </c>
       <c r="E396" s="27">
-        <v>162.94999999999999</v>
+        <v>108.63</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -9117,16 +9127,16 @@
         <v>402</v>
       </c>
       <c r="B400" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C400" s="25">
-        <v>55.5</v>
+        <v>50.5</v>
       </c>
       <c r="D400" s="26">
         <v>8.5500000000000007</v>
       </c>
       <c r="E400" s="27">
-        <v>474.53</v>
+        <v>431.78</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -9207,16 +9217,16 @@
         <v>408</v>
       </c>
       <c r="B406" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C406" s="25">
-        <v>28.5</v>
+        <v>24.5</v>
       </c>
       <c r="D406" s="26">
         <v>6.65</v>
       </c>
       <c r="E406" s="27">
-        <v>189.53</v>
+        <v>162.93</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -9357,16 +9367,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="24">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C416" s="25">
-        <v>74.5</v>
+        <v>71</v>
       </c>
       <c r="D416" s="26">
         <v>5.2</v>
       </c>
       <c r="E416" s="27">
-        <v>387.4</v>
+        <v>369.2</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -9406,16 +9416,16 @@
         <v>421</v>
       </c>
       <c r="B419" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C419" s="25">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D419" s="26">
         <v>5.3</v>
       </c>
       <c r="E419" s="27">
-        <v>217.3</v>
+        <v>212</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9443,13 +9453,13 @@
         <v>84</v>
       </c>
       <c r="C421" s="25">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="D421" s="26">
         <v>6.2</v>
       </c>
       <c r="E421" s="27">
-        <v>155.09</v>
+        <v>108.56</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -10343,16 +10353,16 @@
         <v>480</v>
       </c>
       <c r="B478" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C478" s="25">
-        <v>17</v>
+        <v>34.5</v>
       </c>
       <c r="D478" s="26">
         <v>9.5</v>
       </c>
       <c r="E478" s="27">
-        <v>161.5</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10422,16 +10432,16 @@
         <v>485</v>
       </c>
       <c r="B483" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C483" s="25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D483" s="26">
         <v>10.34</v>
       </c>
       <c r="E483" s="27">
-        <v>248.18</v>
+        <v>227.49</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -10570,13 +10580,13 @@
         <v>19</v>
       </c>
       <c r="C492" s="25">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="D492" s="26">
         <v>9</v>
       </c>
       <c r="E492" s="27">
-        <v>40.5</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -10752,15 +10762,17 @@
       <c r="A504" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="B504" s="24"/>
+      <c r="B504" s="24">
+        <v>2</v>
+      </c>
       <c r="C504" s="25">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D504" s="26">
         <v>16.63</v>
       </c>
       <c r="E504" s="27">
-        <v>174.62</v>
+        <v>149.66999999999999</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -10768,16 +10780,16 @@
         <v>507</v>
       </c>
       <c r="B505" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C505" s="25">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D505" s="26">
         <v>11.25</v>
       </c>
       <c r="E505" s="27">
-        <v>84.38</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -11250,16 +11262,16 @@
         <v>537</v>
       </c>
       <c r="B535" s="24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C535" s="25">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D535" s="26">
         <v>2.1</v>
       </c>
       <c r="E535" s="27">
-        <v>92.4</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -11348,16 +11360,16 @@
         <v>543</v>
       </c>
       <c r="B541" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C541" s="25">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D541" s="26">
         <v>3.5</v>
       </c>
       <c r="E541" s="27">
-        <v>59.5</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -11382,16 +11394,16 @@
         <v>545</v>
       </c>
       <c r="B543" s="24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C543" s="25">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="D543" s="26">
         <v>2.83</v>
       </c>
       <c r="E543" s="27">
-        <v>98.91</v>
+        <v>91.85</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11399,16 +11411,16 @@
         <v>546</v>
       </c>
       <c r="B544" s="24">
+        <v>26</v>
+      </c>
+      <c r="C544" s="25">
         <v>24</v>
-      </c>
-      <c r="C544" s="25">
-        <v>29.5</v>
       </c>
       <c r="D544" s="26">
         <v>1.8</v>
       </c>
       <c r="E544" s="27">
-        <v>53.1</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11418,9 +11430,15 @@
       <c r="B545" s="24">
         <v>31</v>
       </c>
-      <c r="C545" s="28"/>
-      <c r="D545" s="29"/>
-      <c r="E545" s="28"/>
+      <c r="C545" s="25">
+        <v>40</v>
+      </c>
+      <c r="D545" s="26">
+        <v>2</v>
+      </c>
+      <c r="E545" s="27">
+        <v>80</v>
+      </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="23" t="s">
@@ -11512,16 +11530,16 @@
         <v>553</v>
       </c>
       <c r="B551" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C551" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D551" s="26">
         <v>4.75</v>
       </c>
       <c r="E551" s="27">
-        <v>71.25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11597,16 +11615,16 @@
         <v>558</v>
       </c>
       <c r="B556" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C556" s="25">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="D556" s="26">
         <v>3.1</v>
       </c>
       <c r="E556" s="27">
-        <v>62</v>
+        <v>57.35</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11665,16 +11683,16 @@
         <v>562</v>
       </c>
       <c r="B560" s="24">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C560" s="25">
-        <v>145.69999999999999</v>
+        <v>120.7</v>
       </c>
       <c r="D560" s="26">
         <v>3.9</v>
       </c>
       <c r="E560" s="27">
-        <v>568.23</v>
+        <v>470.73</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11744,16 +11762,16 @@
         <v>567</v>
       </c>
       <c r="B565" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C565" s="25">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D565" s="26">
         <v>3.6</v>
       </c>
       <c r="E565" s="27">
-        <v>108</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11778,16 +11796,16 @@
         <v>569</v>
       </c>
       <c r="B567" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C567" s="25">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="D567" s="26">
         <v>3.14</v>
       </c>
       <c r="E567" s="27">
-        <v>62.17</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -11795,16 +11813,16 @@
         <v>570</v>
       </c>
       <c r="B568" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C568" s="25">
-        <v>71.25</v>
+        <v>70.25</v>
       </c>
       <c r="D568" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E568" s="27">
-        <v>163.88</v>
+        <v>161.58000000000001</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -11846,16 +11864,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C571" s="25">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="D571" s="26">
         <v>3.5</v>
       </c>
       <c r="E571" s="27">
-        <v>127.75</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11863,16 +11881,16 @@
         <v>574</v>
       </c>
       <c r="B572" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C572" s="25">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="D572" s="26">
         <v>5.7</v>
       </c>
       <c r="E572" s="27">
-        <v>156.75</v>
+        <v>148.19999999999999</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -11917,13 +11935,13 @@
         <v>29</v>
       </c>
       <c r="C575" s="25">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D575" s="26">
         <v>2.66</v>
       </c>
       <c r="E575" s="27">
-        <v>29.26</v>
+        <v>109.06</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12033,16 +12051,16 @@
         <v>584</v>
       </c>
       <c r="B582" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C582" s="25">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D582" s="26">
         <v>1.4</v>
       </c>
       <c r="E582" s="27">
-        <v>50.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -12050,16 +12068,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C583" s="25">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="D583" s="26">
         <v>1.8</v>
       </c>
       <c r="E583" s="27">
-        <v>69.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12101,16 +12119,16 @@
         <v>588</v>
       </c>
       <c r="B586" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C586" s="25">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D586" s="26">
         <v>1.2</v>
       </c>
       <c r="E586" s="27">
-        <v>454.8</v>
+        <v>453.6</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
@@ -12135,10 +12153,10 @@
         <v>590</v>
       </c>
       <c r="B588" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C588" s="25">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D588" s="29"/>
       <c r="E588" s="28"/>
@@ -12148,10 +12166,10 @@
         <v>591</v>
       </c>
       <c r="B589" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C589" s="25">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D589" s="29"/>
       <c r="E589" s="28"/>
@@ -12191,10 +12209,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C592" s="25">
-        <v>224.5</v>
+        <v>145.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12204,10 +12222,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C593" s="25">
-        <v>99.5</v>
+        <v>93.5</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12217,10 +12235,10 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C594" s="25">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D594" s="29"/>
       <c r="E594" s="28"/>
@@ -12243,10 +12261,10 @@
         <v>598</v>
       </c>
       <c r="B596" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C596" s="25">
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="D596" s="29"/>
       <c r="E596" s="28"/>
@@ -12273,16 +12291,16 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C598" s="25">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D598" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E598" s="27">
-        <v>331.76</v>
+        <v>328.28</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -12318,16 +12336,16 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C601" s="25">
-        <v>39.5</v>
+        <v>31.5</v>
       </c>
       <c r="D601" s="26">
         <v>0.85</v>
       </c>
       <c r="E601" s="27">
-        <v>33.58</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -12402,10 +12420,10 @@
         <v>609</v>
       </c>
       <c r="B607" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C607" s="25">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D607" s="29"/>
       <c r="E607" s="28"/>
@@ -12719,16 +12737,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C628" s="25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D628" s="26">
         <v>5.75</v>
       </c>
       <c r="E628" s="27">
-        <v>74.75</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12736,16 +12754,16 @@
         <v>631</v>
       </c>
       <c r="B629" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C629" s="25">
-        <v>26.85</v>
+        <v>25.85</v>
       </c>
       <c r="D629" s="26">
         <v>4</v>
       </c>
       <c r="E629" s="27">
-        <v>107.4</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -12787,16 +12805,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C632" s="25">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D632" s="26">
         <v>2.77</v>
       </c>
       <c r="E632" s="27">
-        <v>138.51</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12940,16 +12958,16 @@
         <v>643</v>
       </c>
       <c r="B641" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C641" s="25">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D641" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E641" s="27">
-        <v>282.72000000000003</v>
+        <v>273.60000000000002</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -13008,16 +13026,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C645" s="25">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D645" s="26">
         <v>3</v>
       </c>
       <c r="E645" s="27">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13042,16 +13060,16 @@
         <v>649</v>
       </c>
       <c r="B647" s="24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C647" s="25">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
       <c r="D647" s="26">
         <v>5</v>
       </c>
       <c r="E647" s="27">
-        <v>172.5</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -13121,16 +13139,16 @@
         <v>654</v>
       </c>
       <c r="B652" s="24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C652" s="25">
-        <v>43.5</v>
+        <v>39</v>
       </c>
       <c r="D652" s="26">
         <v>3.1</v>
       </c>
       <c r="E652" s="27">
-        <v>134.85</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13138,16 +13156,16 @@
         <v>655</v>
       </c>
       <c r="B653" s="24">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C653" s="25">
-        <v>136.36000000000001</v>
+        <v>129.86000000000001</v>
       </c>
       <c r="D653" s="26">
         <v>1.7</v>
       </c>
       <c r="E653" s="27">
-        <v>231.81</v>
+        <v>220.76</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -13155,16 +13173,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C654" s="25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D654" s="26">
         <v>3.33</v>
       </c>
       <c r="E654" s="27">
-        <v>116.55</v>
+        <v>113.22</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13172,16 +13190,16 @@
         <v>657</v>
       </c>
       <c r="B655" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C655" s="25">
-        <v>25.5</v>
+        <v>23</v>
       </c>
       <c r="D655" s="26">
         <v>3.5</v>
       </c>
       <c r="E655" s="27">
-        <v>89.25</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -13257,16 +13275,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C660" s="25">
-        <v>132</v>
+        <v>125.5</v>
       </c>
       <c r="D660" s="26">
         <v>2.85</v>
       </c>
       <c r="E660" s="27">
-        <v>376.2</v>
+        <v>357.68</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13319,17 +13337,11 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>6</v>
-      </c>
-      <c r="C664" s="25">
-        <v>1</v>
-      </c>
-      <c r="D664" s="26">
-        <v>5.5</v>
-      </c>
-      <c r="E664" s="27">
-        <v>5.5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C664" s="28"/>
+      <c r="D664" s="29"/>
+      <c r="E664" s="28"/>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="23" t="s">
@@ -13506,16 +13518,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C675" s="25">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D675" s="26">
         <v>3.1</v>
       </c>
       <c r="E675" s="27">
-        <v>396.8</v>
+        <v>375.1</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13523,16 +13535,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C676" s="25">
-        <v>42.43</v>
+        <v>36.43</v>
       </c>
       <c r="D676" s="26">
         <v>3.6</v>
       </c>
       <c r="E676" s="27">
-        <v>152.75</v>
+        <v>131.15</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13540,16 +13552,16 @@
         <v>679</v>
       </c>
       <c r="B677" s="24">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C677" s="25">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="D677" s="26">
         <v>3.5</v>
       </c>
       <c r="E677" s="27">
-        <v>3.5</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -13591,16 +13603,16 @@
         <v>682</v>
       </c>
       <c r="B680" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C680" s="25">
-        <v>43.5</v>
+        <v>41.5</v>
       </c>
       <c r="D680" s="26">
         <v>2.5</v>
       </c>
       <c r="E680" s="27">
-        <v>108.75</v>
+        <v>103.75</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -13659,16 +13671,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C684" s="25">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="D684" s="26">
         <v>2.25</v>
       </c>
       <c r="E684" s="27">
-        <v>52.88</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13676,16 +13688,16 @@
         <v>687</v>
       </c>
       <c r="B685" s="24">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C685" s="25">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D685" s="26">
         <v>2.25</v>
       </c>
       <c r="E685" s="27">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -13914,7 +13926,7 @@
         <v>71</v>
       </c>
       <c r="C700" s="25">
-        <v>31.34</v>
+        <v>23.84</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -13937,10 +13949,10 @@
         <v>704</v>
       </c>
       <c r="B702" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C702" s="25">
-        <v>73.5</v>
+        <v>72</v>
       </c>
       <c r="D702" s="29"/>
       <c r="E702" s="28"/>
@@ -13963,10 +13975,10 @@
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C704" s="25">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="D704" s="29"/>
       <c r="E704" s="28"/>
@@ -13976,10 +13988,10 @@
         <v>707</v>
       </c>
       <c r="B705" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C705" s="25">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="D705" s="29"/>
       <c r="E705" s="28"/>
@@ -13989,10 +14001,10 @@
         <v>708</v>
       </c>
       <c r="B706" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C706" s="25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D706" s="29"/>
       <c r="E706" s="28"/>
@@ -14011,16 +14023,16 @@
         <v>710</v>
       </c>
       <c r="B708" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C708" s="25">
-        <v>127.5</v>
+        <v>107.5</v>
       </c>
       <c r="D708" s="26">
         <v>2.93</v>
       </c>
       <c r="E708" s="27">
-        <v>373.79</v>
+        <v>315.16000000000003</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
@@ -14228,16 +14240,16 @@
         <v>727</v>
       </c>
       <c r="B725" s="24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C725" s="25">
-        <v>252.5</v>
+        <v>237.5</v>
       </c>
       <c r="D725" s="26">
         <v>1.1599999999999999</v>
       </c>
       <c r="E725" s="27">
-        <v>292.89999999999998</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
@@ -14282,10 +14294,10 @@
         <v>731</v>
       </c>
       <c r="B729" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C729" s="25">
-        <v>-106.65</v>
+        <v>-108.65</v>
       </c>
       <c r="D729" s="29"/>
       <c r="E729" s="28"/>
@@ -14323,16 +14335,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C732" s="25">
-        <v>74.5</v>
+        <v>72.5</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>186.25</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14340,16 +14352,16 @@
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C733" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D733" s="26">
         <v>2.5</v>
       </c>
       <c r="E733" s="27">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -14374,16 +14386,16 @@
         <v>737</v>
       </c>
       <c r="B735" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C735" s="25">
-        <v>45.25</v>
+        <v>44.25</v>
       </c>
       <c r="D735" s="26">
         <v>2.5</v>
       </c>
       <c r="E735" s="27">
-        <v>113.13</v>
+        <v>110.63</v>
       </c>
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.25">
@@ -14425,16 +14437,16 @@
         <v>740</v>
       </c>
       <c r="B738" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C738" s="25">
-        <v>11.25</v>
+        <v>6.25</v>
       </c>
       <c r="D738" s="26">
         <v>2.5</v>
       </c>
       <c r="E738" s="27">
-        <v>28.13</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
@@ -14453,10 +14465,10 @@
         <v>742</v>
       </c>
       <c r="B740" s="24">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C740" s="25">
-        <v>-588</v>
+        <v>-614.5</v>
       </c>
       <c r="D740" s="29"/>
       <c r="E740" s="28"/>
@@ -14467,11 +14479,11 @@
       </c>
       <c r="B741" s="31"/>
       <c r="C741" s="32">
-        <v>41057.300000000003</v>
+        <v>40175.29</v>
       </c>
       <c r="D741" s="33"/>
       <c r="E741" s="34">
-        <v>103980.41</v>
+        <v>103248.68</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 16-Mar-26</t>
+    <t>1-Jul-25 to 17-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -3373,17 +3373,11 @@
         <v>42</v>
       </c>
       <c r="B40" s="24">
-        <v>42</v>
-      </c>
-      <c r="C40" s="25">
-        <v>3.5</v>
-      </c>
-      <c r="D40" s="26">
-        <v>2.14</v>
-      </c>
-      <c r="E40" s="27">
-        <v>7.49</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C40" s="28"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="28"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
@@ -3492,16 +3486,16 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47" s="25">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D47" s="26">
         <v>1.27</v>
       </c>
       <c r="E47" s="27">
-        <v>73.510000000000005</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3509,16 +3503,16 @@
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" s="25">
-        <v>72.349999999999994</v>
+        <v>69.349999999999994</v>
       </c>
       <c r="D48" s="26">
         <v>1.27</v>
       </c>
       <c r="E48" s="27">
-        <v>91.73</v>
+        <v>87.93</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3560,16 +3554,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="25">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>469.8</v>
+        <v>464.4</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3639,16 +3633,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C56" s="25">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>462.6</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3724,16 +3718,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="25">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>970.72</v>
+        <v>966.16</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3825,16 +3819,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C68" s="25">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>427.35</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,16 +3853,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C70" s="25">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>516.6</v>
+        <v>499.8</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3876,16 +3870,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C71" s="25">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>572.6</v>
+        <v>558.6</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3893,16 +3887,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C72" s="25">
-        <v>421.5</v>
+        <v>418.5</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>590.1</v>
+        <v>585.9</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,16 +3904,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C73" s="25">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>620.20000000000005</v>
+        <v>616</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3955,16 +3949,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C76" s="25">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>268.8</v>
+        <v>254.4</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3989,16 +3983,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C78" s="25">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>102</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4091,16 +4085,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C84" s="25">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1413.1</v>
+        <v>1406.6</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4125,16 +4119,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C86" s="25">
-        <v>1119</v>
+        <v>1111.5</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1902.3</v>
+        <v>1889.55</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4227,16 +4221,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C92" s="25">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D92" s="26">
         <v>1.81</v>
       </c>
       <c r="E92" s="27">
-        <v>1288.8800000000001</v>
+        <v>1285.27</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4274,16 +4268,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C95" s="25">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>312.3</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4291,16 +4285,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
+        <v>62</v>
+      </c>
+      <c r="C96" s="25">
         <v>61</v>
-      </c>
-      <c r="C96" s="25">
-        <v>64</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>57.6</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4423,16 +4417,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="25">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D104" s="26">
         <v>2.5</v>
       </c>
       <c r="E104" s="27">
-        <v>87.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4508,10 +4502,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C109" s="25">
-        <v>68.5</v>
+        <v>62.5</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4859,16 +4853,16 @@
         <v>138</v>
       </c>
       <c r="B136" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C136" s="25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="D136" s="26">
         <v>12.5</v>
       </c>
       <c r="E136" s="27">
-        <v>168.75</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5168,13 +5162,13 @@
         <v>41</v>
       </c>
       <c r="C154" s="25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="D154" s="26">
         <v>18.5</v>
       </c>
       <c r="E154" s="27">
-        <v>268.25</v>
+        <v>277.5</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -5639,16 +5633,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C184" s="25">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D184" s="26">
         <v>2.8</v>
       </c>
       <c r="E184" s="27">
-        <v>56.06</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -6349,16 +6343,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C228" s="25">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D228" s="26">
         <v>2.66</v>
       </c>
       <c r="E228" s="27">
-        <v>284.62</v>
+        <v>271.32</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6366,16 +6360,16 @@
         <v>231</v>
       </c>
       <c r="B229" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C229" s="25">
-        <v>33.5</v>
+        <v>31</v>
       </c>
       <c r="D229" s="26">
         <v>4</v>
       </c>
       <c r="E229" s="27">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6383,16 +6377,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C230" s="25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D230" s="26">
         <v>4</v>
       </c>
       <c r="E230" s="27">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6693,16 +6687,16 @@
         <v>252</v>
       </c>
       <c r="B250" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C250" s="25">
-        <v>122</v>
+        <v>119.5</v>
       </c>
       <c r="D250" s="26">
         <v>3</v>
       </c>
       <c r="E250" s="27">
-        <v>366</v>
+        <v>358.5</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -7133,16 +7127,16 @@
         <v>280</v>
       </c>
       <c r="B278" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C278" s="25">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D278" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E278" s="27">
-        <v>413.81</v>
+        <v>409.4</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -8302,13 +8296,13 @@
         <v>8</v>
       </c>
       <c r="C350" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D350" s="26">
         <v>6.46</v>
       </c>
       <c r="E350" s="27">
-        <v>22.61</v>
+        <v>16.149999999999999</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8540,16 +8534,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C365" s="25">
-        <v>52.5</v>
+        <v>50.5</v>
       </c>
       <c r="D365" s="26">
         <v>7.76</v>
       </c>
       <c r="E365" s="27">
-        <v>407.59</v>
+        <v>392.06</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8574,16 +8568,16 @@
         <v>369</v>
       </c>
       <c r="B367" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C367" s="25">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D367" s="26">
         <v>6.65</v>
       </c>
       <c r="E367" s="27">
-        <v>166.25</v>
+        <v>152.94999999999999</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -8880,16 +8874,16 @@
         <v>387</v>
       </c>
       <c r="B385" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C385" s="25">
-        <v>71.5</v>
+        <v>69.5</v>
       </c>
       <c r="D385" s="26">
         <v>6</v>
       </c>
       <c r="E385" s="27">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -8931,16 +8925,16 @@
         <v>390</v>
       </c>
       <c r="B388" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C388" s="25">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="D388" s="26">
         <v>9.75</v>
       </c>
       <c r="E388" s="27">
-        <v>34.130000000000003</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -9450,16 +9444,16 @@
         <v>423</v>
       </c>
       <c r="B421" s="24">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C421" s="25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="D421" s="26">
         <v>6.2</v>
       </c>
       <c r="E421" s="27">
-        <v>108.56</v>
+        <v>96.15</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -10268,16 +10262,16 @@
         <v>475</v>
       </c>
       <c r="B473" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C473" s="25">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="D473" s="26">
         <v>16</v>
       </c>
       <c r="E473" s="27">
-        <v>80</v>
+        <v>24</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -10577,16 +10571,16 @@
         <v>494</v>
       </c>
       <c r="B492" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C492" s="25">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="D492" s="26">
         <v>9</v>
       </c>
       <c r="E492" s="27">
-        <v>130.5</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -12209,10 +12203,10 @@
         <v>594</v>
       </c>
       <c r="B592" s="24">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C592" s="25">
-        <v>145.5</v>
+        <v>137.5</v>
       </c>
       <c r="D592" s="29"/>
       <c r="E592" s="28"/>
@@ -12222,10 +12216,10 @@
         <v>595</v>
       </c>
       <c r="B593" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C593" s="25">
-        <v>93.5</v>
+        <v>83.5</v>
       </c>
       <c r="D593" s="29"/>
       <c r="E593" s="28"/>
@@ -12235,10 +12229,10 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C594" s="25">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D594" s="29"/>
       <c r="E594" s="28"/>
@@ -12336,16 +12330,16 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C601" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D601" s="26">
         <v>0.85</v>
       </c>
       <c r="E601" s="27">
-        <v>26.78</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -12856,16 +12850,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C635" s="25">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="D635" s="26">
         <v>2.76</v>
       </c>
       <c r="E635" s="27">
-        <v>107.59</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -13923,10 +13917,10 @@
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C700" s="25">
-        <v>23.84</v>
+        <v>22.84</v>
       </c>
       <c r="D700" s="29"/>
       <c r="E700" s="28"/>
@@ -14335,16 +14329,16 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C732" s="25">
-        <v>72.5</v>
+        <v>71.5</v>
       </c>
       <c r="D732" s="26">
         <v>2.5</v>
       </c>
       <c r="E732" s="27">
-        <v>181.25</v>
+        <v>178.75</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -14369,16 +14363,16 @@
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C734" s="25">
-        <v>8.25</v>
+        <v>6.25</v>
       </c>
       <c r="D734" s="26">
         <v>2.5</v>
       </c>
       <c r="E734" s="27">
-        <v>20.63</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -14479,11 +14473,11 @@
       </c>
       <c r="B741" s="31"/>
       <c r="C741" s="32">
-        <v>40175.29</v>
+        <v>39991.79</v>
       </c>
       <c r="D741" s="33"/>
       <c r="E741" s="34">
-        <v>103248.68</v>
+        <v>102848.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="10215"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7650" windowHeight="8835"/>
   </bookViews>
   <sheets>
     <sheet name="PATRIKA 25-26" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 19-Mar-26</t>
+    <t>1-Jul-25 to 20-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -134,7 +134,7 @@
     <t>1022 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>1023 PATRIKA</t>
+    <t>1023 PATRIKA (25.03)</t>
   </si>
   <si>
     <t>1024 PATRIKA</t>
@@ -152,7 +152,7 @@
     <t>1028 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>1029 PATRIKA</t>
+    <t>1029 PATRIKA (26.03)</t>
   </si>
   <si>
     <t>1030 PATRIKA</t>
@@ -203,7 +203,7 @@
     <t>1112 PATRIKA</t>
   </si>
   <si>
-    <t>1113 PATRIKA</t>
+    <t>1113 PATRIKA (12800 25.03)</t>
   </si>
   <si>
     <t>1114 PATRIKA-BROWN</t>
@@ -695,7 +695,7 @@
     <t>4288 PATRIKA</t>
   </si>
   <si>
-    <t>4289 PATRIKA</t>
+    <t>4289 PATRIKA 3100 23.03</t>
   </si>
   <si>
     <t>4290 PATRIKA</t>
@@ -1265,7 +1265,7 @@
     <t>5595 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>5596 PATRIKA *-* (M) (5000 20.03)</t>
+    <t>5596 PATRIKA *-* (M) ( 6300 24.03)</t>
   </si>
   <si>
     <t>5597 PATRIKA (JC) *-* (M)</t>
@@ -1415,7 +1415,7 @@
     <t>6616 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>6617 PATRIKA *-* (M)</t>
+    <t>6617 PATRIKA *-* (M) (28.03 Apperox)</t>
   </si>
   <si>
     <t>6618 PATRIKA *-* (M)''Dc'''</t>
@@ -1442,7 +1442,7 @@
     <t>6625 PATRIKA *-* (M)</t>
   </si>
   <si>
-    <t>6626 PATRIKA *-* (M) (Alter Available)</t>
+    <t>6626 PATRIKA *-* (M) 1600 26.03</t>
   </si>
   <si>
     <t>6627 PATRIKA *-* (M)</t>
@@ -1655,7 +1655,7 @@
     <t>7405 PATRIKA</t>
   </si>
   <si>
-    <t>7406 PATRIKA</t>
+    <t>7406 PATRIKA (1700 27.03)</t>
   </si>
   <si>
     <t>7407 PATRIKA *-* (F)</t>
@@ -1673,7 +1673,7 @@
     <t>7411 PATRIKA</t>
   </si>
   <si>
-    <t>7412 PATRIKA</t>
+    <t>7412 PATRIKA (25.03)</t>
   </si>
   <si>
     <t>7413 PATRIKA</t>
@@ -1745,7 +1745,7 @@
     <t>7435 PATRIKA</t>
   </si>
   <si>
-    <t>7436 PATRIKA</t>
+    <t>7436 PATRIKA ( 2000 27.03)</t>
   </si>
   <si>
     <t>7437 PATRIKA</t>
@@ -1988,7 +1988,7 @@
     <t>9326 CARDS</t>
   </si>
   <si>
-    <t>9327 CARDS</t>
+    <t>9327 CARDS (DC)</t>
   </si>
   <si>
     <t>9328 CARDS</t>
@@ -2942,16 +2942,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="25">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>230.1</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2959,16 +2959,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="25">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D13" s="26">
         <v>1.95</v>
       </c>
       <c r="E13" s="27">
-        <v>185.25</v>
+        <v>177.45</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2976,16 +2976,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" s="25">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>544</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2993,16 +2993,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C15" s="25">
-        <v>65.5</v>
+        <v>60.5</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3027,16 +3027,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="25">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D17" s="26">
         <v>2.1</v>
       </c>
       <c r="E17" s="27">
-        <v>520.79999999999995</v>
+        <v>514.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3072,16 +3072,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="25">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D20" s="26">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="E20" s="27">
-        <v>9.02</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3100,16 +3100,16 @@
         <v>24</v>
       </c>
       <c r="B22" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" s="25">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D22" s="26">
         <v>1.8</v>
       </c>
       <c r="E22" s="27">
-        <v>122.4</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,16 +3151,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C25" s="25">
-        <v>26.5</v>
+        <v>18.5</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>43.73</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,16 +3202,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="25">
-        <v>32</v>
+        <v>26.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3315,16 +3315,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C35" s="25">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D35" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E35" s="27">
-        <v>310.5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3405,16 +3405,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" s="25">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>48.15</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3422,16 +3422,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" s="25">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>182.79</v>
+        <v>176.66</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3439,16 +3439,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" s="25">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>234.49</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3456,16 +3456,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C44" s="25">
-        <v>89.5</v>
+        <v>87.5</v>
       </c>
       <c r="D44" s="26">
         <v>2.72</v>
       </c>
       <c r="E44" s="27">
-        <v>243.12</v>
+        <v>237.69</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3507,33 +3507,27 @@
         <v>49</v>
       </c>
       <c r="B47" s="24">
-        <v>102</v>
-      </c>
-      <c r="C47" s="25">
-        <v>-16</v>
-      </c>
-      <c r="D47" s="26">
-        <v>1.27</v>
-      </c>
-      <c r="E47" s="27">
-        <v>-20.28</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="C47" s="28"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="28"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="24">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="25">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="D48" s="26">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="E48" s="27">
-        <v>1.37</v>
+        <v>-2.4300000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3541,16 +3535,16 @@
         <v>51</v>
       </c>
       <c r="B49" s="24">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C49" s="25">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D49" s="26">
         <v>1.4</v>
       </c>
       <c r="E49" s="27">
-        <v>291.2</v>
+        <v>270.2</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3575,16 +3569,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C51" s="25">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>633.6</v>
+        <v>628.20000000000005</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3609,16 +3603,16 @@
         <v>55</v>
       </c>
       <c r="B53" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C53" s="25">
-        <v>237</v>
+        <v>229.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>592.5</v>
+        <v>573.75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3660,16 +3654,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" s="25">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>534.6</v>
+        <v>529.20000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3677,16 +3671,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C57" s="25">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>83.6</v>
+        <v>77.900000000000006</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3711,16 +3705,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" s="25">
-        <v>52.25</v>
+        <v>47.25</v>
       </c>
       <c r="D59" s="26">
         <v>1.9</v>
       </c>
       <c r="E59" s="27">
-        <v>99.28</v>
+        <v>89.78</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3728,16 +3722,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C60" s="25">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>913.48</v>
+        <v>896.41</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3745,16 +3739,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C61" s="25">
-        <v>831</v>
+        <v>795.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>946.79</v>
+        <v>906.34</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3801,16 +3795,16 @@
         <v>67</v>
       </c>
       <c r="B65" s="24">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C65" s="25">
-        <v>148.5</v>
+        <v>133.5</v>
       </c>
       <c r="D65" s="26">
         <v>1.65</v>
       </c>
       <c r="E65" s="27">
-        <v>245.03</v>
+        <v>220.28</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3846,16 +3840,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C68" s="25">
-        <v>195.5</v>
+        <v>169</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>322.58</v>
+        <v>278.85000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3880,16 +3874,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C70" s="25">
-        <v>333.5</v>
+        <v>323.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>466.9</v>
+        <v>452.9</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3897,16 +3891,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C71" s="25">
-        <v>374.5</v>
+        <v>351.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>524.29999999999995</v>
+        <v>492.1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3914,16 +3908,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C72" s="25">
-        <v>390.5</v>
+        <v>387.5</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>546.70000000000005</v>
+        <v>542.5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3931,16 +3925,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C73" s="25">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>509.6</v>
+        <v>491.4</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3976,16 +3970,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="24">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C76" s="25">
-        <v>122.5</v>
+        <v>52</v>
       </c>
       <c r="D76" s="26">
         <v>1.2</v>
       </c>
       <c r="E76" s="27">
-        <v>147</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4012,25 +4006,31 @@
       <c r="B78" s="24">
         <v>117</v>
       </c>
-      <c r="C78" s="28"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="28"/>
+      <c r="C78" s="25">
+        <v>30</v>
+      </c>
+      <c r="D78" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E78" s="27">
+        <v>36</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="23" t="s">
         <v>81</v>
       </c>
       <c r="B79" s="24">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C79" s="25">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="D79" s="26">
         <v>1.2</v>
       </c>
       <c r="E79" s="27">
-        <v>439.2</v>
+        <v>410.4</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4038,16 +4038,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C80" s="25">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>422.4</v>
+        <v>393.6</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4055,16 +4055,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C81" s="25">
-        <v>504</v>
+        <v>475</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>604.79999999999995</v>
+        <v>570</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4072,16 +4072,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C82" s="25">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>314.39999999999998</v>
+        <v>285.60000000000002</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4089,16 +4089,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C83" s="25">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>607.20000000000005</v>
+        <v>574.79999999999995</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4106,16 +4106,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C84" s="25">
-        <v>1027.5</v>
+        <v>937.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1335.75</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4123,16 +4123,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C85" s="25">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1589.9</v>
+        <v>1596.4</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4140,16 +4140,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C86" s="25">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1870</v>
+        <v>1854.7</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4157,16 +4157,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C87" s="25">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1127.0999999999999</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4174,16 +4174,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C88" s="25">
-        <v>1012.5</v>
+        <v>1008.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1721.25</v>
+        <v>1714.45</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4191,16 +4191,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C89" s="25">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>154.11000000000001</v>
+        <v>148.24</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4208,16 +4208,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C90" s="25">
-        <v>224.7</v>
+        <v>221.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>288.22000000000003</v>
+        <v>284.37</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4225,16 +4225,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C91" s="25">
-        <v>-3</v>
+        <v>-4.5</v>
       </c>
       <c r="D91" s="26">
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="27">
-        <v>-3.36</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4242,16 +4242,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C92" s="25">
-        <v>828</v>
+        <v>826.5</v>
       </c>
       <c r="D92" s="26">
         <v>1.83</v>
       </c>
       <c r="E92" s="27">
-        <v>1513.97</v>
+        <v>1511.23</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4259,16 +4259,16 @@
         <v>95</v>
       </c>
       <c r="B93" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C93" s="25">
-        <v>285.5</v>
+        <v>280.5</v>
       </c>
       <c r="D93" s="26">
         <v>2.27</v>
       </c>
       <c r="E93" s="27">
-        <v>646.96</v>
+        <v>635.63</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4289,16 +4289,16 @@
         <v>97</v>
       </c>
       <c r="B95" s="24">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C95" s="25">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D95" s="26">
         <v>0.9</v>
       </c>
       <c r="E95" s="27">
-        <v>287.10000000000002</v>
+        <v>282.60000000000002</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4306,16 +4306,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C96" s="25">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>45.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4323,16 +4323,16 @@
         <v>99</v>
       </c>
       <c r="B97" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C97" s="25">
-        <v>-17</v>
+        <v>-23.5</v>
       </c>
       <c r="D97" s="26">
         <v>0.9</v>
       </c>
       <c r="E97" s="27">
-        <v>-15.3</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4357,16 +4357,16 @@
         <v>101</v>
       </c>
       <c r="B99" s="24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C99" s="25">
-        <v>216.5</v>
+        <v>201.5</v>
       </c>
       <c r="D99" s="26">
         <v>1.65</v>
       </c>
       <c r="E99" s="27">
-        <v>357.23</v>
+        <v>332.48</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4440,31 +4440,25 @@
       <c r="B104" s="24">
         <v>78</v>
       </c>
-      <c r="C104" s="25">
-        <v>2</v>
-      </c>
-      <c r="D104" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E104" s="27">
-        <v>5</v>
-      </c>
+      <c r="C104" s="28"/>
+      <c r="D104" s="29"/>
+      <c r="E104" s="28"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C105" s="25">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>757.5</v>
+        <v>727.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4472,16 +4466,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C106" s="25">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D106" s="26">
         <v>2.5</v>
       </c>
       <c r="E106" s="27">
-        <v>472.5</v>
+        <v>450</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4506,16 +4500,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C108" s="25">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D108" s="26">
         <v>2.5</v>
       </c>
       <c r="E108" s="27">
-        <v>600</v>
+        <v>577.5</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4523,10 +4517,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C109" s="25">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4612,10 +4606,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C116" s="25">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4638,10 +4632,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C118" s="25">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
@@ -4779,10 +4773,10 @@
         <v>131</v>
       </c>
       <c r="B129" s="24">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C129" s="25">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D129" s="29"/>
       <c r="E129" s="28"/>
@@ -4792,10 +4786,10 @@
         <v>132</v>
       </c>
       <c r="B130" s="24">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C130" s="25">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="D130" s="29"/>
       <c r="E130" s="28"/>
@@ -5057,16 +5051,16 @@
         <v>149</v>
       </c>
       <c r="B147" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C147" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D147" s="26">
         <v>18.5</v>
       </c>
       <c r="E147" s="27">
-        <v>92.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5074,16 +5068,16 @@
         <v>150</v>
       </c>
       <c r="B148" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C148" s="25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="D148" s="26">
         <v>18.5</v>
       </c>
       <c r="E148" s="27">
-        <v>286.75</v>
+        <v>268.25</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5340,16 +5334,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C164" s="25">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>11.5</v>
+        <v>-34.5</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5419,16 +5413,16 @@
         <v>171</v>
       </c>
       <c r="B169" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C169" s="25">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="D169" s="26">
         <v>11.5</v>
       </c>
       <c r="E169" s="27">
-        <v>155.25</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5515,16 +5509,16 @@
         <v>177</v>
       </c>
       <c r="B175" s="24">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C175" s="25">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="D175" s="26">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="E175" s="27">
-        <v>55.98</v>
+        <v>111.65</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5695,16 +5689,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C187" s="25">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="D187" s="26">
         <v>2.8</v>
       </c>
       <c r="E187" s="27">
-        <v>112.11</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5813,16 +5807,16 @@
         <v>197</v>
       </c>
       <c r="B195" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C195" s="25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D195" s="26">
         <v>2.76</v>
       </c>
       <c r="E195" s="27">
-        <v>17.95</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -5830,16 +5824,16 @@
         <v>198</v>
       </c>
       <c r="B196" s="24">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C196" s="25">
-        <v>158.81</v>
+        <v>145.81</v>
       </c>
       <c r="D196" s="26">
         <v>2.65</v>
       </c>
       <c r="E196" s="27">
-        <v>420.85</v>
+        <v>386.4</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -5875,16 +5869,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="24">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C199" s="25">
-        <v>22.5</v>
+        <v>16</v>
       </c>
       <c r="D199" s="26">
         <v>3.56</v>
       </c>
       <c r="E199" s="27">
-        <v>80.099999999999994</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5892,16 +5886,16 @@
         <v>202</v>
       </c>
       <c r="B200" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C200" s="25">
-        <v>47</v>
+        <v>43.5</v>
       </c>
       <c r="D200" s="26">
         <v>5</v>
       </c>
       <c r="E200" s="27">
-        <v>235</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -6022,16 +6016,16 @@
         <v>210</v>
       </c>
       <c r="B208" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C208" s="25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D208" s="26">
         <v>4.5</v>
       </c>
       <c r="E208" s="27">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -6039,16 +6033,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C209" s="25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D209" s="26">
         <v>2.85</v>
       </c>
       <c r="E209" s="27">
-        <v>28.5</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6056,16 +6050,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C210" s="25">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D210" s="26">
         <v>3.79</v>
       </c>
       <c r="E210" s="27">
-        <v>375.24</v>
+        <v>363.87</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6073,16 +6067,16 @@
         <v>213</v>
       </c>
       <c r="B211" s="24">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C211" s="25">
-        <v>185.5</v>
+        <v>183</v>
       </c>
       <c r="D211" s="26">
         <v>2.7</v>
       </c>
       <c r="E211" s="27">
-        <v>500.85</v>
+        <v>494.1</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -6090,16 +6084,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C212" s="25">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="D212" s="26">
         <v>2.6</v>
       </c>
       <c r="E212" s="27">
-        <v>132.6</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6124,16 +6118,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C214" s="25">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D214" s="26">
         <v>2.6</v>
       </c>
       <c r="E214" s="27">
-        <v>119.6</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6158,16 +6152,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C216" s="25">
-        <v>48.5</v>
+        <v>41</v>
       </c>
       <c r="D216" s="26">
         <v>3.5</v>
       </c>
       <c r="E216" s="27">
-        <v>169.75</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6192,16 +6186,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C218" s="25">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D218" s="26">
         <v>3.93</v>
       </c>
       <c r="E218" s="27">
-        <v>868.79</v>
+        <v>849.14</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6226,16 +6220,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C220" s="25">
-        <v>247.5</v>
+        <v>245</v>
       </c>
       <c r="D220" s="26">
         <v>2.7</v>
       </c>
       <c r="E220" s="27">
-        <v>668.25</v>
+        <v>661.5</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6243,16 +6237,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C221" s="25">
-        <v>167.5</v>
+        <v>156</v>
       </c>
       <c r="D221" s="26">
         <v>2.7</v>
       </c>
       <c r="E221" s="27">
-        <v>452.25</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6260,16 +6254,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C222" s="25">
-        <v>79.5</v>
+        <v>78.5</v>
       </c>
       <c r="D222" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E222" s="27">
-        <v>182.85</v>
+        <v>180.55</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6294,16 +6288,16 @@
         <v>226</v>
       </c>
       <c r="B224" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C224" s="25">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="D224" s="26">
         <v>3</v>
       </c>
       <c r="E224" s="27">
-        <v>43.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6328,16 +6322,16 @@
         <v>228</v>
       </c>
       <c r="B226" s="24">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C226" s="25">
-        <v>163.5</v>
+        <v>149.5</v>
       </c>
       <c r="D226" s="26">
         <v>3.93</v>
       </c>
       <c r="E226" s="27">
-        <v>642.41999999999996</v>
+        <v>587.41</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6345,16 +6339,16 @@
         <v>229</v>
       </c>
       <c r="B227" s="24">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C227" s="25">
-        <v>145.75</v>
+        <v>136.75</v>
       </c>
       <c r="D227" s="26">
         <v>3.25</v>
       </c>
       <c r="E227" s="27">
-        <v>473.69</v>
+        <v>444.44</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6362,16 +6356,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C228" s="25">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D228" s="26">
         <v>3.64</v>
       </c>
       <c r="E228" s="27">
-        <v>138.33000000000001</v>
+        <v>123.77</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6396,16 +6390,16 @@
         <v>232</v>
       </c>
       <c r="B230" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C230" s="25">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="D230" s="26">
         <v>3.16</v>
       </c>
       <c r="E230" s="27">
-        <v>83.74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6458,16 +6452,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C234" s="25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D234" s="26">
         <v>4</v>
       </c>
       <c r="E234" s="27">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6526,16 +6520,16 @@
         <v>240</v>
       </c>
       <c r="B238" s="24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C238" s="25">
-        <v>105.5</v>
+        <v>102.5</v>
       </c>
       <c r="D238" s="26">
         <v>3.5</v>
       </c>
       <c r="E238" s="27">
-        <v>369.25</v>
+        <v>358.75</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -6554,16 +6548,16 @@
         <v>242</v>
       </c>
       <c r="B240" s="24">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C240" s="25">
-        <v>160.38</v>
+        <v>157.38</v>
       </c>
       <c r="D240" s="26">
         <v>3.25</v>
       </c>
       <c r="E240" s="27">
-        <v>521.24</v>
+        <v>511.49</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -6571,16 +6565,16 @@
         <v>243</v>
       </c>
       <c r="B241" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C241" s="25">
-        <v>34.5</v>
+        <v>19.5</v>
       </c>
       <c r="D241" s="26">
         <v>3.25</v>
       </c>
       <c r="E241" s="27">
-        <v>112.13</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -6717,16 +6711,16 @@
         <v>253</v>
       </c>
       <c r="B251" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C251" s="25">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D251" s="26">
         <v>5.75</v>
       </c>
       <c r="E251" s="27">
-        <v>37.380000000000003</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6751,16 +6745,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C253" s="25">
-        <v>50.9</v>
+        <v>49.9</v>
       </c>
       <c r="D253" s="26">
         <v>6.3</v>
       </c>
       <c r="E253" s="27">
-        <v>320.67</v>
+        <v>314.37</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6768,16 +6762,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C254" s="25">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D254" s="26">
         <v>3</v>
       </c>
       <c r="E254" s="27">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6802,16 +6796,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C256" s="25">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D256" s="26">
         <v>3.8</v>
       </c>
       <c r="E256" s="27">
-        <v>330.6</v>
+        <v>304</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6819,16 +6813,16 @@
         <v>259</v>
       </c>
       <c r="B257" s="24">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C257" s="25">
-        <v>69.5</v>
+        <v>58</v>
       </c>
       <c r="D257" s="26">
         <v>3.9</v>
       </c>
       <c r="E257" s="27">
-        <v>271.05</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -6836,16 +6830,16 @@
         <v>260</v>
       </c>
       <c r="B258" s="24">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C258" s="25">
-        <v>102.85</v>
+        <v>87.35</v>
       </c>
       <c r="D258" s="26">
         <v>3.9</v>
       </c>
       <c r="E258" s="27">
-        <v>401.12</v>
+        <v>340.67</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -6898,16 +6892,16 @@
         <v>264</v>
       </c>
       <c r="B262" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C262" s="25">
-        <v>77.5</v>
+        <v>73.5</v>
       </c>
       <c r="D262" s="26">
         <v>3.5</v>
       </c>
       <c r="E262" s="27">
-        <v>271.25</v>
+        <v>257.25</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -6949,16 +6943,16 @@
         <v>267</v>
       </c>
       <c r="B265" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C265" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D265" s="26">
         <v>4</v>
       </c>
       <c r="E265" s="27">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -7050,16 +7044,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C272" s="25">
-        <v>162.28</v>
+        <v>150.28</v>
       </c>
       <c r="D272" s="26">
         <v>4.28</v>
       </c>
       <c r="E272" s="27">
-        <v>694.56</v>
+        <v>643.20000000000005</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7067,16 +7061,16 @@
         <v>275</v>
       </c>
       <c r="B273" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C273" s="25">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="D273" s="26">
         <v>6.15</v>
       </c>
       <c r="E273" s="27">
-        <v>64.56</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7140,17 +7134,11 @@
         <v>280</v>
       </c>
       <c r="B278" s="24">
-        <v>48</v>
-      </c>
-      <c r="C278" s="25">
-        <v>6.5</v>
-      </c>
-      <c r="D278" s="26">
-        <v>4.5</v>
-      </c>
-      <c r="E278" s="27">
-        <v>29.25</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C278" s="28"/>
+      <c r="D278" s="29"/>
+      <c r="E278" s="28"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="23" t="s">
@@ -7174,16 +7162,16 @@
         <v>282</v>
       </c>
       <c r="B280" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C280" s="25">
-        <v>75.37</v>
+        <v>73.37</v>
       </c>
       <c r="D280" s="26">
         <v>4.25</v>
       </c>
       <c r="E280" s="27">
-        <v>320.32</v>
+        <v>311.82</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -7191,16 +7179,16 @@
         <v>283</v>
       </c>
       <c r="B281" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C281" s="25">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="D281" s="26">
         <v>4.42</v>
       </c>
       <c r="E281" s="27">
-        <v>103.84</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7208,16 +7196,16 @@
         <v>284</v>
       </c>
       <c r="B282" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C282" s="25">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D282" s="26">
         <v>4.4000000000000004</v>
       </c>
       <c r="E282" s="27">
-        <v>387.39</v>
+        <v>382.99</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7225,16 +7213,16 @@
         <v>285</v>
       </c>
       <c r="B283" s="24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C283" s="25">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D283" s="26">
         <v>4.28</v>
       </c>
       <c r="E283" s="27">
-        <v>119.84</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7264,16 +7252,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C286" s="25">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="D286" s="26">
         <v>6.5</v>
       </c>
       <c r="E286" s="27">
-        <v>217.75</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7298,16 +7286,16 @@
         <v>290</v>
       </c>
       <c r="B288" s="24">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C288" s="25">
-        <v>122.5</v>
+        <v>90</v>
       </c>
       <c r="D288" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E288" s="27">
-        <v>593.87</v>
+        <v>436.31</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -7343,16 +7331,16 @@
         <v>293</v>
       </c>
       <c r="B291" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C291" s="25">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="D291" s="26">
         <v>6.19</v>
       </c>
       <c r="E291" s="27">
-        <v>380.49</v>
+        <v>368.12</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -7360,16 +7348,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C292" s="25">
-        <v>89.5</v>
+        <v>87.5</v>
       </c>
       <c r="D292" s="26">
         <v>5.16</v>
       </c>
       <c r="E292" s="27">
-        <v>461.82</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7394,16 +7382,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C294" s="25">
-        <v>72.5</v>
+        <v>69.5</v>
       </c>
       <c r="D294" s="26">
         <v>5</v>
       </c>
       <c r="E294" s="27">
-        <v>362.5</v>
+        <v>347.5</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7411,16 +7399,16 @@
         <v>297</v>
       </c>
       <c r="B295" s="24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C295" s="25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D295" s="26">
         <v>6</v>
       </c>
       <c r="E295" s="27">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7513,16 +7501,16 @@
         <v>303</v>
       </c>
       <c r="B301" s="24">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C301" s="25">
-        <v>86.5</v>
+        <v>83.5</v>
       </c>
       <c r="D301" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E301" s="27">
-        <v>422.77</v>
+        <v>408.11</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7564,16 +7552,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C304" s="25">
-        <v>227.5</v>
+        <v>223.5</v>
       </c>
       <c r="D304" s="26">
         <v>6.08</v>
       </c>
       <c r="E304" s="27">
-        <v>1382.39</v>
+        <v>1358.32</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -7598,16 +7586,16 @@
         <v>308</v>
       </c>
       <c r="B306" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C306" s="25">
-        <v>220</v>
+        <v>218.5</v>
       </c>
       <c r="D306" s="26">
         <v>4.2699999999999996</v>
       </c>
       <c r="E306" s="27">
-        <v>939.02</v>
+        <v>932.62</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7683,16 +7671,16 @@
         <v>313</v>
       </c>
       <c r="B311" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C311" s="25">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D311" s="26">
         <v>4.75</v>
       </c>
       <c r="E311" s="27">
-        <v>76</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -7845,16 +7833,16 @@
         <v>323</v>
       </c>
       <c r="B321" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C321" s="25">
-        <v>32.950000000000003</v>
+        <v>22.95</v>
       </c>
       <c r="D321" s="26">
         <v>9.4499999999999993</v>
       </c>
       <c r="E321" s="27">
-        <v>311.38</v>
+        <v>216.88</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -8014,16 +8002,16 @@
         <v>334</v>
       </c>
       <c r="B332" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C332" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D332" s="26">
         <v>7.45</v>
       </c>
       <c r="E332" s="27">
-        <v>96.79</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -8099,16 +8087,16 @@
         <v>339</v>
       </c>
       <c r="B337" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C337" s="25">
-        <v>100.91</v>
+        <v>99.41</v>
       </c>
       <c r="D337" s="26">
         <v>4.28</v>
       </c>
       <c r="E337" s="27">
-        <v>431.89</v>
+        <v>425.47</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -8274,16 +8262,16 @@
         <v>350</v>
       </c>
       <c r="B348" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C348" s="25">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="D348" s="26">
         <v>9</v>
       </c>
       <c r="E348" s="27">
-        <v>103.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -8374,16 +8362,16 @@
         <v>356</v>
       </c>
       <c r="B354" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C354" s="25">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D354" s="26">
         <v>6.46</v>
       </c>
       <c r="E354" s="27">
-        <v>16.149999999999999</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8436,16 +8424,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C358" s="25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D358" s="26">
         <v>5.94</v>
       </c>
       <c r="E358" s="27">
-        <v>166.32</v>
+        <v>136.62</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8453,16 +8441,16 @@
         <v>361</v>
       </c>
       <c r="B359" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C359" s="25">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="D359" s="26">
         <v>6.4</v>
       </c>
       <c r="E359" s="27">
-        <v>99.2</v>
+        <v>73.599999999999994</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8553,16 +8541,16 @@
         <v>367</v>
       </c>
       <c r="B365" s="24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C365" s="25">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D365" s="26">
         <v>7.99</v>
       </c>
       <c r="E365" s="27">
-        <v>239.75</v>
+        <v>227.76</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8683,16 +8671,16 @@
         <v>375</v>
       </c>
       <c r="B373" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C373" s="25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D373" s="26">
         <v>7.2</v>
       </c>
       <c r="E373" s="27">
-        <v>108</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8700,16 +8688,16 @@
         <v>376</v>
       </c>
       <c r="B374" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C374" s="25">
-        <v>21.5</v>
+        <v>18</v>
       </c>
       <c r="D374" s="26">
         <v>6.18</v>
       </c>
       <c r="E374" s="27">
-        <v>132.87</v>
+        <v>111.24</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8751,16 +8739,16 @@
         <v>379</v>
       </c>
       <c r="B377" s="24">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C377" s="25">
-        <v>137.5</v>
+        <v>132.5</v>
       </c>
       <c r="D377" s="26">
         <v>6.6</v>
       </c>
       <c r="E377" s="27">
-        <v>907.5</v>
+        <v>874.5</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8819,16 +8807,16 @@
         <v>383</v>
       </c>
       <c r="B381" s="24">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C381" s="25">
-        <v>47</v>
+        <v>40.5</v>
       </c>
       <c r="D381" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E381" s="27">
-        <v>385.4</v>
+        <v>332.1</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -8836,16 +8824,16 @@
         <v>384</v>
       </c>
       <c r="B382" s="24">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C382" s="25">
-        <v>59.33</v>
+        <v>52.83</v>
       </c>
       <c r="D382" s="26">
         <v>4.5</v>
       </c>
       <c r="E382" s="27">
-        <v>266.99</v>
+        <v>237.74</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -8853,16 +8841,16 @@
         <v>385</v>
       </c>
       <c r="B383" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C383" s="25">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="D383" s="26">
         <v>8.08</v>
       </c>
       <c r="E383" s="27">
-        <v>238.36</v>
+        <v>222.2</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -8904,16 +8892,16 @@
         <v>388</v>
       </c>
       <c r="B386" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C386" s="25">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="D386" s="26">
         <v>7</v>
       </c>
       <c r="E386" s="27">
-        <v>227.5</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -8955,16 +8943,16 @@
         <v>391</v>
       </c>
       <c r="B389" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C389" s="25">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="D389" s="26">
         <v>6</v>
       </c>
       <c r="E389" s="27">
-        <v>405</v>
+        <v>390</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -9040,16 +9028,16 @@
         <v>396</v>
       </c>
       <c r="B394" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C394" s="25">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="D394" s="26">
         <v>8</v>
       </c>
       <c r="E394" s="27">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -9309,17 +9297,11 @@
         <v>413</v>
       </c>
       <c r="B411" s="24">
-        <v>42</v>
-      </c>
-      <c r="C411" s="25">
-        <v>3</v>
-      </c>
-      <c r="D411" s="26">
-        <v>7</v>
-      </c>
-      <c r="E411" s="27">
-        <v>21</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C411" s="28"/>
+      <c r="D411" s="29"/>
+      <c r="E411" s="28"/>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="23" t="s">
@@ -9493,16 +9475,16 @@
         <v>425</v>
       </c>
       <c r="B423" s="24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C423" s="25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D423" s="26">
         <v>5.3</v>
       </c>
       <c r="E423" s="27">
-        <v>212</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -9510,16 +9492,16 @@
         <v>426</v>
       </c>
       <c r="B424" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C424" s="25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D424" s="26">
         <v>4.9000000000000004</v>
       </c>
       <c r="E424" s="27">
-        <v>53.9</v>
+        <v>39.200000000000003</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -9530,13 +9512,13 @@
         <v>88</v>
       </c>
       <c r="C425" s="25">
-        <v>1.5</v>
+        <v>21.5</v>
       </c>
       <c r="D425" s="26">
         <v>6.21</v>
       </c>
       <c r="E425" s="27">
-        <v>9.31</v>
+        <v>133.52000000000001</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -9679,16 +9661,16 @@
         <v>437</v>
       </c>
       <c r="B435" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C435" s="25">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="D435" s="26">
         <v>8.35</v>
       </c>
       <c r="E435" s="27">
-        <v>204.47</v>
+        <v>179.43</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -10089,16 +10071,16 @@
         <v>463</v>
       </c>
       <c r="B461" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C461" s="25">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="D461" s="26">
         <v>9.75</v>
       </c>
       <c r="E461" s="27">
-        <v>14.63</v>
+        <v>-14.63</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -10236,27 +10218,33 @@
         <v>472</v>
       </c>
       <c r="B470" s="24">
-        <v>13</v>
-      </c>
-      <c r="C470" s="28"/>
-      <c r="D470" s="29"/>
-      <c r="E470" s="28"/>
+        <v>14</v>
+      </c>
+      <c r="C470" s="25">
+        <v>-8</v>
+      </c>
+      <c r="D470" s="26">
+        <v>10</v>
+      </c>
+      <c r="E470" s="27">
+        <v>-80</v>
+      </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="23" t="s">
         <v>473</v>
       </c>
       <c r="B471" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C471" s="25">
-        <v>3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D471" s="26">
         <v>11</v>
       </c>
       <c r="E471" s="27">
-        <v>38.5</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -10362,16 +10350,16 @@
         <v>480</v>
       </c>
       <c r="B478" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C478" s="25">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D478" s="26">
         <v>12.5</v>
       </c>
       <c r="E478" s="27">
-        <v>25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10857,16 +10845,16 @@
         <v>511</v>
       </c>
       <c r="B509" s="24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C509" s="25">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D509" s="26">
         <v>11.25</v>
       </c>
       <c r="E509" s="27">
-        <v>61.88</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -11305,16 +11293,16 @@
         <v>539</v>
       </c>
       <c r="B537" s="24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C537" s="25">
-        <v>25.5</v>
+        <v>30.5</v>
       </c>
       <c r="D537" s="26">
         <v>1.95</v>
       </c>
       <c r="E537" s="27">
-        <v>49.73</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11389,15 +11377,17 @@
       <c r="A542" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="B542" s="24"/>
+      <c r="B542" s="24">
+        <v>1</v>
+      </c>
       <c r="C542" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D542" s="26">
         <v>7.3</v>
       </c>
       <c r="E542" s="27">
-        <v>65.7</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11482,16 +11472,16 @@
         <v>550</v>
       </c>
       <c r="B548" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C548" s="25">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D548" s="26">
         <v>1.8</v>
       </c>
       <c r="E548" s="27">
-        <v>37.799999999999997</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -11499,16 +11489,16 @@
         <v>551</v>
       </c>
       <c r="B549" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C549" s="25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D549" s="26">
         <v>2</v>
       </c>
       <c r="E549" s="27">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11754,16 +11744,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C564" s="25">
-        <v>70.7</v>
+        <v>68.7</v>
       </c>
       <c r="D564" s="26">
         <v>3.9</v>
       </c>
       <c r="E564" s="27">
-        <v>275.73</v>
+        <v>267.93</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11884,16 +11874,16 @@
         <v>574</v>
       </c>
       <c r="B572" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C572" s="25">
-        <v>68.75</v>
+        <v>63.75</v>
       </c>
       <c r="D572" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E572" s="27">
-        <v>158.13</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -11935,16 +11925,16 @@
         <v>577</v>
       </c>
       <c r="B575" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C575" s="25">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D575" s="26">
         <v>3.5</v>
       </c>
       <c r="E575" s="27">
-        <v>119</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -11969,16 +11959,16 @@
         <v>579</v>
       </c>
       <c r="B577" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C577" s="25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D577" s="26">
         <v>3.6</v>
       </c>
       <c r="E577" s="27">
-        <v>57.6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -12003,16 +11993,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C579" s="25">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D579" s="26">
         <v>2.66</v>
       </c>
       <c r="E579" s="27">
-        <v>82.46</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12020,16 +12010,16 @@
         <v>582</v>
       </c>
       <c r="B580" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C580" s="25">
-        <v>41.5</v>
+        <v>39</v>
       </c>
       <c r="D580" s="26">
         <v>2.66</v>
       </c>
       <c r="E580" s="27">
-        <v>110.39</v>
+        <v>103.74</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -12088,16 +12078,16 @@
         <v>586</v>
       </c>
       <c r="B584" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C584" s="25">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="D584" s="26">
         <v>3.8</v>
       </c>
       <c r="E584" s="27">
-        <v>169.1</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
@@ -12139,16 +12129,16 @@
         <v>589</v>
       </c>
       <c r="B587" s="24">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C587" s="25">
-        <v>33</v>
+        <v>26.5</v>
       </c>
       <c r="D587" s="26">
         <v>1.8</v>
       </c>
       <c r="E587" s="27">
-        <v>59.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -12176,13 +12166,13 @@
         <v>26</v>
       </c>
       <c r="C589" s="25">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="D589" s="26">
         <v>1.2</v>
       </c>
       <c r="E589" s="27">
-        <v>304.8</v>
+        <v>328.8</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
@@ -12250,10 +12240,10 @@
         <v>596</v>
       </c>
       <c r="B594" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C594" s="25">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="D594" s="29"/>
       <c r="E594" s="28"/>
@@ -12262,8 +12252,12 @@
       <c r="A595" s="23" t="s">
         <v>597</v>
       </c>
-      <c r="B595" s="24"/>
-      <c r="C595" s="28"/>
+      <c r="B595" s="24">
+        <v>1</v>
+      </c>
+      <c r="C595" s="25">
+        <v>-10</v>
+      </c>
       <c r="D595" s="29"/>
       <c r="E595" s="28"/>
     </row>
@@ -12302,10 +12296,10 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C598" s="25">
-        <v>114.5</v>
+        <v>102.5</v>
       </c>
       <c r="D598" s="29"/>
       <c r="E598" s="28"/>
@@ -12328,10 +12322,10 @@
         <v>602</v>
       </c>
       <c r="B600" s="24">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C600" s="25">
-        <v>157.5</v>
+        <v>154.5</v>
       </c>
       <c r="D600" s="29"/>
       <c r="E600" s="28"/>
@@ -12341,10 +12335,10 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C601" s="25">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D601" s="29"/>
       <c r="E601" s="28"/>
@@ -12354,10 +12348,10 @@
         <v>604</v>
       </c>
       <c r="B602" s="24">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C602" s="25">
-        <v>71.5</v>
+        <v>60.5</v>
       </c>
       <c r="D602" s="29"/>
       <c r="E602" s="28"/>
@@ -12384,16 +12378,16 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C604" s="25">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D604" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E604" s="27">
-        <v>315.52</v>
+        <v>314.36</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
@@ -12401,16 +12395,16 @@
         <v>607</v>
       </c>
       <c r="B605" s="24">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C605" s="25">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D605" s="26">
         <v>0.85</v>
       </c>
       <c r="E605" s="27">
-        <v>583.95000000000005</v>
+        <v>583.1</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -12429,16 +12423,16 @@
         <v>609</v>
       </c>
       <c r="B607" s="24">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C607" s="25">
-        <v>344.5</v>
+        <v>342</v>
       </c>
       <c r="D607" s="26">
         <v>0.85</v>
       </c>
       <c r="E607" s="27">
-        <v>292.83</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
@@ -12777,16 +12771,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C631" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D631" s="26">
         <v>5</v>
       </c>
       <c r="E631" s="27">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12845,16 +12839,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C635" s="25">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D635" s="26">
         <v>5.75</v>
       </c>
       <c r="E635" s="27">
-        <v>71.88</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -12913,16 +12907,16 @@
         <v>641</v>
       </c>
       <c r="B639" s="24">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C639" s="25">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D639" s="26">
         <v>2.77</v>
       </c>
       <c r="E639" s="27">
-        <v>124.66</v>
+        <v>121.89</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -12998,16 +12992,16 @@
         <v>646</v>
       </c>
       <c r="B644" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C644" s="25">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="D644" s="26">
         <v>4</v>
       </c>
       <c r="E644" s="27">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -13247,16 +13241,16 @@
         <v>661</v>
       </c>
       <c r="B659" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C659" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D659" s="26">
         <v>3.1</v>
       </c>
       <c r="E659" s="27">
-        <v>99.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -13264,16 +13258,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C660" s="25">
-        <v>115.36</v>
+        <v>112.36</v>
       </c>
       <c r="D660" s="26">
         <v>1.7</v>
       </c>
       <c r="E660" s="27">
-        <v>196.11</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13383,16 +13377,16 @@
         <v>669</v>
       </c>
       <c r="B667" s="24">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C667" s="25">
-        <v>119.5</v>
+        <v>115</v>
       </c>
       <c r="D667" s="26">
         <v>2.85</v>
       </c>
       <c r="E667" s="27">
-        <v>340.58</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
@@ -13620,16 +13614,16 @@
         <v>684</v>
       </c>
       <c r="B682" s="24">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C682" s="25">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D682" s="26">
         <v>3.1</v>
       </c>
       <c r="E682" s="27">
-        <v>341</v>
+        <v>337.9</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -13654,16 +13648,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C684" s="25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="D684" s="26">
         <v>3.5</v>
       </c>
       <c r="E684" s="27">
-        <v>40.25</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13705,16 +13699,16 @@
         <v>689</v>
       </c>
       <c r="B687" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C687" s="25">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="D687" s="26">
         <v>2.5</v>
       </c>
       <c r="E687" s="27">
-        <v>96.25</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -13790,16 +13784,16 @@
         <v>694</v>
       </c>
       <c r="B692" s="24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C692" s="25">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D692" s="26">
         <v>2.25</v>
       </c>
       <c r="E692" s="27">
-        <v>182.25</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -13875,16 +13869,16 @@
         <v>699</v>
       </c>
       <c r="B697" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C697" s="25">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D697" s="26">
         <v>4</v>
       </c>
       <c r="E697" s="27">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
@@ -14025,10 +14019,10 @@
         <v>709</v>
       </c>
       <c r="B707" s="24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C707" s="25">
-        <v>21.84</v>
+        <v>17.84</v>
       </c>
       <c r="D707" s="29"/>
       <c r="E707" s="28"/>
@@ -14051,10 +14045,10 @@
         <v>711</v>
       </c>
       <c r="B709" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C709" s="25">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D709" s="29"/>
       <c r="E709" s="28"/>
@@ -14077,10 +14071,10 @@
         <v>713</v>
       </c>
       <c r="B711" s="24">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C711" s="25">
-        <v>-21</v>
+        <v>-27</v>
       </c>
       <c r="D711" s="29"/>
       <c r="E711" s="28"/>
@@ -14103,10 +14097,10 @@
         <v>715</v>
       </c>
       <c r="B713" s="24">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C713" s="25">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D713" s="29"/>
       <c r="E713" s="28"/>
@@ -14396,10 +14390,10 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C736" s="25">
-        <v>-108.65</v>
+        <v>-111.65</v>
       </c>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
@@ -14420,16 +14414,16 @@
         <v>740</v>
       </c>
       <c r="B738" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C738" s="25">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="D738" s="26">
         <v>2.5</v>
       </c>
       <c r="E738" s="27">
-        <v>15.63</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
@@ -14482,16 +14476,16 @@
         <v>744</v>
       </c>
       <c r="B742" s="24">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C742" s="25">
-        <v>39.25</v>
+        <v>38.25</v>
       </c>
       <c r="D742" s="26">
         <v>2.5</v>
       </c>
       <c r="E742" s="27">
-        <v>98.13</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
@@ -14561,10 +14555,10 @@
         <v>749</v>
       </c>
       <c r="B747" s="24">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C747" s="25">
-        <v>-666</v>
+        <v>-668</v>
       </c>
       <c r="D747" s="29"/>
       <c r="E747" s="28"/>
@@ -14575,11 +14569,11 @@
       </c>
       <c r="B748" s="31"/>
       <c r="C748" s="32">
-        <v>38514.99</v>
+        <v>37514.959999999999</v>
       </c>
       <c r="D748" s="33"/>
       <c r="E748" s="34">
-        <v>96884.37</v>
+        <v>94190.74</v>
       </c>
     </row>
   </sheetData>
@@ -14595,6 +14589,6 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7650" windowHeight="8835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="10215"/>
   </bookViews>
   <sheets>
     <sheet name="PATRIKA 25-26" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>Stock Group Summary</t>
   </si>
   <si>
-    <t>1-Jul-25 to 20-Mar-26</t>
+    <t>1-Jul-25 to 21-Mar-26</t>
   </si>
   <si>
     <t/>
@@ -2942,16 +2942,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="25">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>216.45</v>
+        <v>212.55</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2976,16 +2976,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" s="25">
-        <v>265</v>
+        <v>262.5</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,16 +3202,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="25">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3270,16 +3270,16 @@
         <v>34</v>
       </c>
       <c r="B32" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="26">
         <v>2.8</v>
       </c>
       <c r="E32" s="27">
-        <v>28</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3405,16 +3405,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C41" s="25">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>43.87</v>
+        <v>36.380000000000003</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3439,16 +3439,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C43" s="25">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>219.68</v>
+        <v>199.94</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3586,16 +3586,16 @@
         <v>54</v>
       </c>
       <c r="B52" s="24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C52" s="25">
-        <v>231.5</v>
+        <v>224.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>578.75</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3654,16 +3654,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C56" s="25">
-        <v>294</v>
+        <v>291.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>529.20000000000005</v>
+        <v>524.70000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3722,16 +3722,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="24">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C60" s="25">
-        <v>788</v>
+        <v>779.5</v>
       </c>
       <c r="D60" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E60" s="27">
-        <v>896.41</v>
+        <v>886.74</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,16 +3739,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C61" s="25">
-        <v>795.5</v>
+        <v>788.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>906.34</v>
+        <v>898.37</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3840,16 +3840,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C68" s="25">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>278.85000000000002</v>
+        <v>273.89999999999998</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3925,16 +3925,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C73" s="25">
-        <v>351</v>
+        <v>348.5</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>491.4</v>
+        <v>487.9</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4038,16 +4038,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C80" s="25">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D80" s="26">
         <v>1.2</v>
       </c>
       <c r="E80" s="27">
-        <v>393.6</v>
+        <v>381.6</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4055,16 +4055,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C81" s="25">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="D81" s="26">
         <v>1.2</v>
       </c>
       <c r="E81" s="27">
-        <v>570</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4106,16 +4106,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C84" s="25">
-        <v>937.5</v>
+        <v>926.5</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1218.75</v>
+        <v>1204.45</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4123,16 +4123,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C85" s="25">
-        <v>1228</v>
+        <v>1225.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1596.4</v>
+        <v>1593.15</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4140,16 +4140,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C86" s="25">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1854.7</v>
+        <v>1849.6</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4191,16 +4191,16 @@
         <v>91</v>
       </c>
       <c r="B89" s="24">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C89" s="25">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D89" s="26">
         <v>1.47</v>
       </c>
       <c r="E89" s="27">
-        <v>148.24</v>
+        <v>143.84</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4306,16 +4306,16 @@
         <v>98</v>
       </c>
       <c r="B96" s="24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C96" s="25">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D96" s="26">
         <v>0.9</v>
       </c>
       <c r="E96" s="27">
-        <v>45</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4406,16 +4406,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C102" s="25">
-        <v>269</v>
+        <v>265.5</v>
       </c>
       <c r="D102" s="26">
         <v>0.87</v>
       </c>
       <c r="E102" s="27">
-        <v>234.15</v>
+        <v>231.1</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4449,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C105" s="25">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>727.5</v>
+        <v>725</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -5051,16 +5051,16 @@
         <v>149</v>
       </c>
       <c r="B147" s="24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C147" s="25">
-        <v>2</v>
+        <v>-3.5</v>
       </c>
       <c r="D147" s="26">
         <v>18.5</v>
       </c>
       <c r="E147" s="27">
-        <v>37</v>
+        <v>-64.75</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5266,16 +5266,16 @@
         <v>162</v>
       </c>
       <c r="B160" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C160" s="25">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D160" s="26">
         <v>11.5</v>
       </c>
       <c r="E160" s="27">
-        <v>46</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5283,16 +5283,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C161" s="25">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="D161" s="26">
         <v>11.5</v>
       </c>
       <c r="E161" s="27">
-        <v>218.5</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5334,16 +5334,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C164" s="25">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D164" s="26">
         <v>11.5</v>
       </c>
       <c r="E164" s="27">
-        <v>-34.5</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5509,16 +5509,16 @@
         <v>177</v>
       </c>
       <c r="B175" s="24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C175" s="25">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D175" s="26">
         <v>0.9</v>
       </c>
       <c r="E175" s="27">
-        <v>111.65</v>
+        <v>110.75</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5629,16 +5629,16 @@
         <v>185</v>
       </c>
       <c r="B183" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C183" s="25">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="D183" s="26">
         <v>2.7</v>
       </c>
       <c r="E183" s="27">
-        <v>149.85</v>
+        <v>144.44999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5689,16 +5689,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C187" s="25">
-        <v>38.5</v>
+        <v>33.5</v>
       </c>
       <c r="D187" s="26">
         <v>2.8</v>
       </c>
       <c r="E187" s="27">
-        <v>107.91</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -6118,16 +6118,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C214" s="25">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D214" s="26">
         <v>2.6</v>
       </c>
       <c r="E214" s="27">
-        <v>111.8</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6152,16 +6152,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C216" s="25">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D216" s="26">
         <v>3.5</v>
       </c>
       <c r="E216" s="27">
-        <v>143.5</v>
+        <v>140</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6186,16 +6186,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C218" s="25">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D218" s="26">
         <v>3.93</v>
       </c>
       <c r="E218" s="27">
-        <v>849.14</v>
+        <v>841.27</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6237,16 +6237,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C221" s="25">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D221" s="26">
         <v>2.7</v>
       </c>
       <c r="E221" s="27">
-        <v>421.2</v>
+        <v>410.4</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6305,16 +6305,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C225" s="25">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="D225" s="26">
         <v>3</v>
       </c>
       <c r="E225" s="27">
-        <v>43.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6322,16 +6322,16 @@
         <v>228</v>
       </c>
       <c r="B226" s="24">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C226" s="25">
-        <v>149.5</v>
+        <v>148.5</v>
       </c>
       <c r="D226" s="26">
         <v>3.93</v>
       </c>
       <c r="E226" s="27">
-        <v>587.41</v>
+        <v>583.48</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6339,16 +6339,16 @@
         <v>229</v>
       </c>
       <c r="B227" s="24">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C227" s="25">
-        <v>136.75</v>
+        <v>134.75</v>
       </c>
       <c r="D227" s="26">
         <v>3.25</v>
       </c>
       <c r="E227" s="27">
-        <v>444.44</v>
+        <v>437.94</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6356,16 +6356,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C228" s="25">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D228" s="26">
         <v>3.64</v>
       </c>
       <c r="E228" s="27">
-        <v>123.77</v>
+        <v>91.01</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6452,16 +6452,16 @@
         <v>236</v>
       </c>
       <c r="B234" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C234" s="25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D234" s="26">
         <v>4</v>
       </c>
       <c r="E234" s="27">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6520,16 +6520,16 @@
         <v>240</v>
       </c>
       <c r="B238" s="24">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C238" s="25">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="D238" s="26">
         <v>3.5</v>
       </c>
       <c r="E238" s="27">
-        <v>358.75</v>
+        <v>355.25</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -6565,16 +6565,16 @@
         <v>243</v>
       </c>
       <c r="B241" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C241" s="25">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="D241" s="26">
         <v>3.25</v>
       </c>
       <c r="E241" s="27">
-        <v>63.38</v>
+        <v>56.88</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -6745,16 +6745,16 @@
         <v>255</v>
       </c>
       <c r="B253" s="24">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C253" s="25">
-        <v>49.9</v>
+        <v>48.4</v>
       </c>
       <c r="D253" s="26">
         <v>6.3</v>
       </c>
       <c r="E253" s="27">
-        <v>314.37</v>
+        <v>304.92</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6762,16 +6762,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C254" s="25">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D254" s="26">
         <v>3</v>
       </c>
       <c r="E254" s="27">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6813,16 +6813,16 @@
         <v>259</v>
       </c>
       <c r="B257" s="24">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C257" s="25">
-        <v>58</v>
+        <v>55.5</v>
       </c>
       <c r="D257" s="26">
         <v>3.9</v>
       </c>
       <c r="E257" s="27">
-        <v>226.2</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -6892,16 +6892,16 @@
         <v>264</v>
       </c>
       <c r="B262" s="24">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C262" s="25">
-        <v>73.5</v>
+        <v>71.5</v>
       </c>
       <c r="D262" s="26">
         <v>3.5</v>
       </c>
       <c r="E262" s="27">
-        <v>257.25</v>
+        <v>250.25</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,16 +7044,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C272" s="25">
-        <v>150.28</v>
+        <v>135.28</v>
       </c>
       <c r="D272" s="26">
         <v>4.28</v>
       </c>
       <c r="E272" s="27">
-        <v>643.20000000000005</v>
+        <v>579</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7106,16 +7106,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C276" s="25">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D276" s="26">
         <v>3.1</v>
       </c>
       <c r="E276" s="27">
-        <v>232.5</v>
+        <v>226.3</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7252,16 +7252,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C286" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D286" s="26">
         <v>6.5</v>
       </c>
       <c r="E286" s="27">
-        <v>204.75</v>
+        <v>191.75</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7348,16 +7348,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C292" s="25">
-        <v>87.5</v>
+        <v>83</v>
       </c>
       <c r="D292" s="26">
         <v>5.16</v>
       </c>
       <c r="E292" s="27">
-        <v>451.5</v>
+        <v>428.28</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7382,16 +7382,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C294" s="25">
-        <v>69.5</v>
+        <v>64</v>
       </c>
       <c r="D294" s="26">
         <v>5</v>
       </c>
       <c r="E294" s="27">
-        <v>347.5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7416,16 +7416,16 @@
         <v>298</v>
       </c>
       <c r="B296" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C296" s="25">
-        <v>16.75</v>
+        <v>14.75</v>
       </c>
       <c r="D296" s="26">
         <v>5.97</v>
       </c>
       <c r="E296" s="27">
-        <v>100</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7501,16 +7501,16 @@
         <v>303</v>
       </c>
       <c r="B301" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C301" s="25">
-        <v>83.5</v>
+        <v>81.5</v>
       </c>
       <c r="D301" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E301" s="27">
-        <v>408.11</v>
+        <v>398.33</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7552,16 +7552,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C304" s="25">
-        <v>223.5</v>
+        <v>215</v>
       </c>
       <c r="D304" s="26">
         <v>6.08</v>
       </c>
       <c r="E304" s="27">
-        <v>1358.32</v>
+        <v>1307.19</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -8217,16 +8217,16 @@
         <v>347</v>
       </c>
       <c r="B345" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C345" s="25">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="D345" s="26">
         <v>9</v>
       </c>
       <c r="E345" s="27">
-        <v>301.5</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -8262,16 +8262,16 @@
         <v>350</v>
       </c>
       <c r="B348" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C348" s="25">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D348" s="26">
         <v>9</v>
       </c>
       <c r="E348" s="27">
-        <v>76.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -8424,16 +8424,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C358" s="25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D358" s="26">
         <v>5.94</v>
       </c>
       <c r="E358" s="27">
-        <v>136.62</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8441,16 +8441,16 @@
         <v>361</v>
       </c>
       <c r="B359" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C359" s="25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="D359" s="26">
         <v>6.4</v>
       </c>
       <c r="E359" s="27">
-        <v>73.599999999999994</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8654,16 +8654,16 @@
         <v>374</v>
       </c>
       <c r="B372" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C372" s="25">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="D372" s="26">
         <v>5.94</v>
       </c>
       <c r="E372" s="27">
-        <v>26.73</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -8739,16 +8739,16 @@
         <v>379</v>
       </c>
       <c r="B377" s="24">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C377" s="25">
-        <v>132.5</v>
+        <v>128.5</v>
       </c>
       <c r="D377" s="26">
         <v>6.6</v>
       </c>
       <c r="E377" s="27">
-        <v>874.5</v>
+        <v>848.1</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8790,16 +8790,16 @@
         <v>382</v>
       </c>
       <c r="B380" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C380" s="25">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D380" s="26">
         <v>8.52</v>
       </c>
       <c r="E380" s="27">
-        <v>400.25</v>
+        <v>374.7</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8892,16 +8892,16 @@
         <v>388</v>
       </c>
       <c r="B386" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C386" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D386" s="26">
         <v>7</v>
       </c>
       <c r="E386" s="27">
-        <v>220.5</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -9280,16 +9280,16 @@
         <v>412</v>
       </c>
       <c r="B410" s="24">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C410" s="25">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="D410" s="26">
         <v>6.65</v>
       </c>
       <c r="E410" s="27">
-        <v>156.28</v>
+        <v>146.30000000000001</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -9426,16 +9426,16 @@
         <v>422</v>
       </c>
       <c r="B420" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C420" s="25">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D420" s="26">
         <v>5.2</v>
       </c>
       <c r="E420" s="27">
-        <v>317.2</v>
+        <v>306.8</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -10037,17 +10037,11 @@
         <v>461</v>
       </c>
       <c r="B459" s="24">
-        <v>10</v>
-      </c>
-      <c r="C459" s="25">
-        <v>1.5</v>
-      </c>
-      <c r="D459" s="26">
-        <v>16.3</v>
-      </c>
-      <c r="E459" s="27">
-        <v>24.45</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C459" s="28"/>
+      <c r="D459" s="29"/>
+      <c r="E459" s="28"/>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="23" t="s">
@@ -10184,16 +10178,16 @@
         <v>470</v>
       </c>
       <c r="B468" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C468" s="25">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D468" s="26">
         <v>14</v>
       </c>
       <c r="E468" s="27">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -10497,16 +10491,16 @@
         <v>489</v>
       </c>
       <c r="B487" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C487" s="25">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="D487" s="26">
         <v>10.34</v>
       </c>
       <c r="E487" s="27">
-        <v>180.96</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -11857,16 +11851,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C571" s="25">
-        <v>16.3</v>
+        <v>11.3</v>
       </c>
       <c r="D571" s="26">
         <v>3.14</v>
       </c>
       <c r="E571" s="27">
-        <v>51.18</v>
+        <v>35.479999999999997</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11993,16 +11987,16 @@
         <v>581</v>
       </c>
       <c r="B579" s="24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C579" s="25">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D579" s="26">
         <v>2.66</v>
       </c>
       <c r="E579" s="27">
-        <v>77.14</v>
+        <v>71.819999999999993</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12335,10 +12329,10 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C601" s="25">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D601" s="29"/>
       <c r="E601" s="28"/>
@@ -12348,10 +12342,10 @@
         <v>604</v>
       </c>
       <c r="B602" s="24">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C602" s="25">
-        <v>60.5</v>
+        <v>45.5</v>
       </c>
       <c r="D602" s="29"/>
       <c r="E602" s="28"/>
@@ -12361,16 +12355,16 @@
         <v>605</v>
       </c>
       <c r="B603" s="24">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C603" s="25">
-        <v>292.5</v>
+        <v>289.5</v>
       </c>
       <c r="D603" s="26">
         <v>0.87</v>
       </c>
       <c r="E603" s="27">
-        <v>254.48</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
@@ -12378,16 +12372,16 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C604" s="25">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="D604" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E604" s="27">
-        <v>314.36</v>
+        <v>308.56</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
@@ -12395,16 +12389,16 @@
         <v>607</v>
       </c>
       <c r="B605" s="24">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C605" s="25">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D605" s="26">
         <v>0.85</v>
       </c>
       <c r="E605" s="27">
-        <v>583.1</v>
+        <v>579.70000000000005</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -12839,16 +12833,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C635" s="25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D635" s="26">
         <v>5.75</v>
       </c>
       <c r="E635" s="27">
-        <v>57.5</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -13009,16 +13003,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C645" s="25">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D645" s="26">
         <v>1.5</v>
       </c>
       <c r="E645" s="27">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13258,16 +13252,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C660" s="25">
-        <v>112.36</v>
+        <v>110.36</v>
       </c>
       <c r="D660" s="26">
         <v>1.7</v>
       </c>
       <c r="E660" s="27">
-        <v>191.01</v>
+        <v>187.61</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13309,16 +13303,16 @@
         <v>665</v>
       </c>
       <c r="B663" s="24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C663" s="25">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="D663" s="26">
         <v>3.5</v>
       </c>
       <c r="E663" s="27">
-        <v>85.75</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -13716,16 +13710,16 @@
         <v>690</v>
       </c>
       <c r="B688" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C688" s="25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D688" s="26">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="E688" s="27">
-        <v>51.19</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -13835,16 +13829,16 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C695" s="25">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D695" s="26">
         <v>2.75</v>
       </c>
       <c r="E695" s="27">
-        <v>178.75</v>
+        <v>176</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
@@ -13993,10 +13987,10 @@
         <v>707</v>
       </c>
       <c r="B705" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C705" s="25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="D705" s="29"/>
       <c r="E705" s="28"/>
@@ -14006,10 +14000,10 @@
         <v>708</v>
       </c>
       <c r="B706" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C706" s="25">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="D706" s="29"/>
       <c r="E706" s="28"/>
@@ -14019,10 +14013,10 @@
         <v>709</v>
       </c>
       <c r="B707" s="24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C707" s="25">
-        <v>17.84</v>
+        <v>16.84</v>
       </c>
       <c r="D707" s="29"/>
       <c r="E707" s="28"/>
@@ -14045,10 +14039,10 @@
         <v>711</v>
       </c>
       <c r="B709" s="24">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C709" s="25">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="D709" s="29"/>
       <c r="E709" s="28"/>
@@ -14084,10 +14078,10 @@
         <v>714</v>
       </c>
       <c r="B712" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C712" s="25">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D712" s="29"/>
       <c r="E712" s="28"/>
@@ -14569,11 +14563,11 @@
       </c>
       <c r="B748" s="31"/>
       <c r="C748" s="32">
-        <v>37514.959999999999</v>
+        <v>37214.959999999999</v>
       </c>
       <c r="D748" s="33"/>
       <c r="E748" s="34">
-        <v>94190.74</v>
+        <v>93113.98</v>
       </c>
     </row>
   </sheetData>
@@ -14589,6 +14583,6 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/website stock.xlsx
+++ b/data/website stock.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="752">
   <si>
     <t>Order Estimate - (from 1-Jul-2023)</t>
   </si>
@@ -125,7 +125,7 @@
     <t>1019 PATRIKA (DC)</t>
   </si>
   <si>
-    <t>1020 PATRIKA (18.03) 1750 &amp; 10K 22.03</t>
+    <t>1020 PATRIKA</t>
   </si>
   <si>
     <t>1021 PATRIKA</t>
@@ -134,7 +134,7 @@
     <t>1022 PATRIKA (JC)</t>
   </si>
   <si>
-    <t>1023 PATRIKA (25.03)</t>
+    <t>1023 PATRIKA (25.03 3600)</t>
   </si>
   <si>
     <t>1024 PATRIKA</t>
@@ -359,7 +359,7 @@
     <t>1160 PATRIKA-PINK</t>
   </si>
   <si>
-    <t>1161 PATRIKA (01)</t>
+    <t>1161 PATRIKA (01) (Not Avlbl , Alter Proide)</t>
   </si>
   <si>
     <t>1162 PATRIKA (02)</t>
@@ -704,7 +704,7 @@
     <t>4291 PATRIKA</t>
   </si>
   <si>
-    <t>4292 PATRIKA</t>
+    <t>4292 PATRIKA (1000 25.03)</t>
   </si>
   <si>
     <t>4293 PATRIKA</t>
@@ -1445,7 +1445,7 @@
     <t>6626 PATRIKA *-* (M) 1600 26.03</t>
   </si>
   <si>
-    <t>6627 PATRIKA *-* (M)</t>
+    <t>6627 PATRIKA *-* (M) (800 25.03)</t>
   </si>
   <si>
     <t>6628 PATRIKA *-* (M)</t>
@@ -1905,6 +1905,9 @@
   </si>
   <si>
     <t>9246 CARDS</t>
+  </si>
+  <si>
+    <t>9247 CARDAS</t>
   </si>
   <si>
     <t>9301 CARDS</t>
@@ -2800,7 +2803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E748"/>
+  <dimension ref="A1:E749"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
@@ -2942,16 +2945,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="24">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="25">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D12" s="26">
         <v>1.95</v>
       </c>
       <c r="E12" s="27">
-        <v>212.55</v>
+        <v>200.85</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2976,16 +2979,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="24">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C14" s="25">
-        <v>262.5</v>
+        <v>258</v>
       </c>
       <c r="D14" s="26">
         <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2993,16 +2996,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="24">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C15" s="25">
-        <v>60.5</v>
+        <v>54</v>
       </c>
       <c r="D15" s="26">
         <v>2</v>
       </c>
       <c r="E15" s="27">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3134,16 +3137,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="25">
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
       <c r="D24" s="26">
         <v>1.8</v>
       </c>
       <c r="E24" s="27">
-        <v>74.7</v>
+        <v>72.900000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,16 +3154,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="25">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="D25" s="26">
         <v>1.65</v>
       </c>
       <c r="E25" s="27">
-        <v>30.53</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3185,16 +3188,16 @@
         <v>29</v>
       </c>
       <c r="B27" s="24">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" s="25">
-        <v>115.5</v>
+        <v>109</v>
       </c>
       <c r="D27" s="26">
         <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,16 +3205,16 @@
         <v>30</v>
       </c>
       <c r="B28" s="24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" s="25">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="D28" s="26">
         <v>2</v>
       </c>
       <c r="E28" s="27">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3219,16 +3222,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D29" s="26">
         <v>2.6</v>
       </c>
       <c r="E29" s="27">
-        <v>124.8</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3256,13 +3259,13 @@
         <v>48</v>
       </c>
       <c r="C31" s="25">
-        <v>0.5</v>
+        <v>102.5</v>
       </c>
       <c r="D31" s="26">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E31" s="27">
-        <v>1.43</v>
+        <v>292.13</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3298,16 +3301,16 @@
         <v>36</v>
       </c>
       <c r="B34" s="24">
+        <v>14</v>
+      </c>
+      <c r="C34" s="25">
         <v>13</v>
-      </c>
-      <c r="C34" s="25">
-        <v>15</v>
       </c>
       <c r="D34" s="26">
         <v>2.5</v>
       </c>
       <c r="E34" s="27">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3405,16 +3408,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="24">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="25">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="D41" s="26">
         <v>2.14</v>
       </c>
       <c r="E41" s="27">
-        <v>36.380000000000003</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3422,16 +3425,16 @@
         <v>44</v>
       </c>
       <c r="B42" s="24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="25">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="D42" s="26">
         <v>2.4500000000000002</v>
       </c>
       <c r="E42" s="27">
-        <v>176.66</v>
+        <v>175.43</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3439,16 +3442,16 @@
         <v>45</v>
       </c>
       <c r="B43" s="24">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C43" s="25">
-        <v>81</v>
+        <v>75.5</v>
       </c>
       <c r="D43" s="26">
         <v>2.4700000000000002</v>
       </c>
       <c r="E43" s="27">
-        <v>199.94</v>
+        <v>186.36</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3456,16 +3459,16 @@
         <v>46</v>
       </c>
       <c r="B44" s="24">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C44" s="25">
-        <v>87.5</v>
+        <v>86.5</v>
       </c>
       <c r="D44" s="26">
         <v>2.72</v>
       </c>
       <c r="E44" s="27">
-        <v>237.69</v>
+        <v>234.97</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3569,16 +3572,16 @@
         <v>53</v>
       </c>
       <c r="B51" s="24">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C51" s="25">
-        <v>349</v>
+        <v>345.5</v>
       </c>
       <c r="D51" s="26">
         <v>1.8</v>
       </c>
       <c r="E51" s="27">
-        <v>628.20000000000005</v>
+        <v>621.9</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3589,13 +3592,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="25">
-        <v>224.5</v>
+        <v>188.5</v>
       </c>
       <c r="D52" s="26">
         <v>2.5</v>
       </c>
       <c r="E52" s="27">
-        <v>561.25</v>
+        <v>471.25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3606,13 +3609,13 @@
         <v>46</v>
       </c>
       <c r="C53" s="25">
-        <v>229.5</v>
+        <v>265.5</v>
       </c>
       <c r="D53" s="26">
         <v>2.5</v>
       </c>
       <c r="E53" s="27">
-        <v>573.75</v>
+        <v>663.75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3637,16 +3640,16 @@
         <v>57</v>
       </c>
       <c r="B55" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" s="25">
-        <v>220.15</v>
+        <v>217.15</v>
       </c>
       <c r="D55" s="26">
         <v>2.75</v>
       </c>
       <c r="E55" s="27">
-        <v>605.41</v>
+        <v>597.16</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3654,16 +3657,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="24">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C56" s="25">
-        <v>291.5</v>
+        <v>276.5</v>
       </c>
       <c r="D56" s="26">
         <v>1.8</v>
       </c>
       <c r="E56" s="27">
-        <v>524.70000000000005</v>
+        <v>497.7</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3671,16 +3674,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="24">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C57" s="25">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D57" s="26">
         <v>1.9</v>
       </c>
       <c r="E57" s="27">
-        <v>77.900000000000006</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,16 +3742,16 @@
         <v>63</v>
       </c>
       <c r="B61" s="24">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C61" s="25">
-        <v>788.5</v>
+        <v>778.5</v>
       </c>
       <c r="D61" s="26">
         <v>1.1399999999999999</v>
       </c>
       <c r="E61" s="27">
-        <v>898.37</v>
+        <v>886.98</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3840,16 +3843,16 @@
         <v>70</v>
       </c>
       <c r="B68" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C68" s="25">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D68" s="26">
         <v>1.65</v>
       </c>
       <c r="E68" s="27">
-        <v>273.89999999999998</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3874,16 +3877,16 @@
         <v>72</v>
       </c>
       <c r="B70" s="24">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C70" s="25">
-        <v>323.5</v>
+        <v>299.5</v>
       </c>
       <c r="D70" s="26">
         <v>1.4</v>
       </c>
       <c r="E70" s="27">
-        <v>452.9</v>
+        <v>419.3</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3891,16 +3894,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="24">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C71" s="25">
-        <v>351.5</v>
+        <v>341.5</v>
       </c>
       <c r="D71" s="26">
         <v>1.4</v>
       </c>
       <c r="E71" s="27">
-        <v>492.1</v>
+        <v>478.1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3908,16 +3911,16 @@
         <v>74</v>
       </c>
       <c r="B72" s="24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C72" s="25">
-        <v>387.5</v>
+        <v>362.5</v>
       </c>
       <c r="D72" s="26">
         <v>1.4</v>
       </c>
       <c r="E72" s="27">
-        <v>542.5</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3925,16 +3928,16 @@
         <v>75</v>
       </c>
       <c r="B73" s="24">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C73" s="25">
-        <v>348.5</v>
+        <v>338.5</v>
       </c>
       <c r="D73" s="26">
         <v>1.4</v>
       </c>
       <c r="E73" s="27">
-        <v>487.9</v>
+        <v>473.9</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4004,16 +4007,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="24">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C78" s="25">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D78" s="26">
         <v>1.2</v>
       </c>
       <c r="E78" s="27">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4072,16 +4075,16 @@
         <v>84</v>
       </c>
       <c r="B82" s="24">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C82" s="25">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D82" s="26">
         <v>1.2</v>
       </c>
       <c r="E82" s="27">
-        <v>285.60000000000002</v>
+        <v>267.60000000000002</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4089,16 +4092,16 @@
         <v>85</v>
       </c>
       <c r="B83" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C83" s="25">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D83" s="26">
         <v>1.2</v>
       </c>
       <c r="E83" s="27">
-        <v>574.79999999999995</v>
+        <v>568.79999999999995</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4106,16 +4109,16 @@
         <v>86</v>
       </c>
       <c r="B84" s="24">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C84" s="25">
-        <v>926.5</v>
+        <v>893</v>
       </c>
       <c r="D84" s="26">
         <v>1.3</v>
       </c>
       <c r="E84" s="27">
-        <v>1204.45</v>
+        <v>1160.9000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4123,16 +4126,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="24">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C85" s="25">
-        <v>1225.5</v>
+        <v>1219.5</v>
       </c>
       <c r="D85" s="26">
         <v>1.3</v>
       </c>
       <c r="E85" s="27">
-        <v>1593.15</v>
+        <v>1585.35</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4140,16 +4143,16 @@
         <v>88</v>
       </c>
       <c r="B86" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C86" s="25">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="D86" s="26">
         <v>1.7</v>
       </c>
       <c r="E86" s="27">
-        <v>1849.6</v>
+        <v>1839.4</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4157,16 +4160,16 @@
         <v>89</v>
       </c>
       <c r="B87" s="24">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C87" s="25">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="D87" s="26">
         <v>1.7</v>
       </c>
       <c r="E87" s="27">
-        <v>1122</v>
+        <v>1106.7</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4174,16 +4177,16 @@
         <v>90</v>
       </c>
       <c r="B88" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C88" s="25">
-        <v>1008.5</v>
+        <v>1004.5</v>
       </c>
       <c r="D88" s="26">
         <v>1.7</v>
       </c>
       <c r="E88" s="27">
-        <v>1714.45</v>
+        <v>1707.65</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4208,16 +4211,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="24">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C90" s="25">
-        <v>221.7</v>
+        <v>201.7</v>
       </c>
       <c r="D90" s="26">
         <v>1.28</v>
       </c>
       <c r="E90" s="27">
-        <v>284.37</v>
+        <v>258.72000000000003</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4225,16 +4228,16 @@
         <v>93</v>
       </c>
       <c r="B91" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C91" s="25">
-        <v>-4.5</v>
+        <v>48.5</v>
       </c>
       <c r="D91" s="26">
-        <v>1.1200000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="E91" s="27">
-        <v>-5.05</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4452,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C105" s="25">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D105" s="26">
         <v>2.5</v>
       </c>
       <c r="E105" s="27">
-        <v>725</v>
+        <v>717.5</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4486,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C107" s="25">
-        <v>223.5</v>
+        <v>220.5</v>
       </c>
       <c r="D107" s="26">
         <v>2.5</v>
       </c>
       <c r="E107" s="27">
-        <v>558.75</v>
+        <v>551.25</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4517,10 +4520,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C109" s="25">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D109" s="29"/>
       <c r="E109" s="28"/>
@@ -4533,7 +4536,7 @@
         <v>47</v>
       </c>
       <c r="C110" s="25">
-        <v>322</v>
+        <v>124</v>
       </c>
       <c r="D110" s="29"/>
       <c r="E110" s="28"/>
@@ -4543,10 +4546,10 @@
         <v>113</v>
       </c>
       <c r="B111" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C111" s="25">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D111" s="29"/>
       <c r="E111" s="28"/>
@@ -4606,10 +4609,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C116" s="25">
-        <v>30</v>
+        <v>203</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="28"/>
@@ -4619,10 +4622,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C117" s="25">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="28"/>
@@ -4632,10 +4635,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C118" s="25">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="28"/>
@@ -4645,10 +4648,10 @@
         <v>121</v>
       </c>
       <c r="B119" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119" s="25">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D119" s="29"/>
       <c r="E119" s="28"/>
@@ -4658,10 +4661,10 @@
         <v>122</v>
       </c>
       <c r="B120" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C120" s="25">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D120" s="29"/>
       <c r="E120" s="28"/>
@@ -4812,10 +4815,10 @@
         <v>134</v>
       </c>
       <c r="B132" s="24">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C132" s="25">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="D132" s="29"/>
       <c r="E132" s="28"/>
@@ -4881,16 +4884,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C137" s="25">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="D137" s="26">
         <v>12.5</v>
       </c>
       <c r="E137" s="27">
-        <v>306.25</v>
+        <v>293.75</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4949,16 +4952,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C141" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" s="26">
         <v>12.5</v>
       </c>
       <c r="E141" s="27">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5000,16 +5003,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C144" s="25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="D144" s="26">
         <v>12.73</v>
       </c>
       <c r="E144" s="27">
-        <v>222.72</v>
+        <v>197.27</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5051,16 +5054,16 @@
         <v>149</v>
       </c>
       <c r="B147" s="24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C147" s="25">
-        <v>-3.5</v>
+        <v>2</v>
       </c>
       <c r="D147" s="26">
         <v>18.5</v>
       </c>
       <c r="E147" s="27">
-        <v>-64.75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5198,16 +5201,16 @@
         <v>158</v>
       </c>
       <c r="B156" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C156" s="25">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D156" s="26">
         <v>18.5</v>
       </c>
       <c r="E156" s="27">
-        <v>425.5</v>
+        <v>296</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5215,16 +5218,16 @@
         <v>159</v>
       </c>
       <c r="B157" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C157" s="25">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D157" s="26">
         <v>18.5</v>
       </c>
       <c r="E157" s="27">
-        <v>240.5</v>
+        <v>111</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5232,16 +5235,16 @@
         <v>160</v>
       </c>
       <c r="B158" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C158" s="25">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D158" s="26">
         <v>18.5</v>
       </c>
       <c r="E158" s="27">
-        <v>83.25</v>
+        <v>74</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5283,16 +5286,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C161" s="25">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="D161" s="26">
         <v>11.5</v>
       </c>
       <c r="E161" s="27">
-        <v>189.75</v>
+        <v>138</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5509,16 +5512,16 @@
         <v>177</v>
       </c>
       <c r="B175" s="24">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C175" s="25">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D175" s="26">
         <v>0.9</v>
       </c>
       <c r="E175" s="27">
-        <v>110.75</v>
+        <v>88.24</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5807,16 +5810,16 @@
         <v>197</v>
       </c>
       <c r="B195" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C195" s="25">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D195" s="26">
         <v>2.76</v>
       </c>
       <c r="E195" s="27">
-        <v>12.43</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -5824,16 +5827,16 @@
         <v>198</v>
       </c>
       <c r="B196" s="24">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C196" s="25">
-        <v>145.81</v>
+        <v>140.81</v>
       </c>
       <c r="D196" s="26">
         <v>2.65</v>
       </c>
       <c r="E196" s="27">
-        <v>386.4</v>
+        <v>373.15</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -5971,16 +5974,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="24">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C205" s="25">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="D205" s="26">
         <v>4.5</v>
       </c>
       <c r="E205" s="27">
-        <v>126</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -6033,16 +6036,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C209" s="25">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D209" s="26">
         <v>2.85</v>
       </c>
       <c r="E209" s="27">
-        <v>25.65</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6050,16 +6053,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C210" s="25">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D210" s="26">
         <v>3.79</v>
       </c>
       <c r="E210" s="27">
-        <v>363.87</v>
+        <v>344.92</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6084,16 +6087,16 @@
         <v>214</v>
       </c>
       <c r="B212" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C212" s="25">
-        <v>48.5</v>
+        <v>44.5</v>
       </c>
       <c r="D212" s="26">
         <v>2.6</v>
       </c>
       <c r="E212" s="27">
-        <v>126.1</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6118,16 +6121,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C214" s="25">
-        <v>41</v>
+        <v>37.5</v>
       </c>
       <c r="D214" s="26">
         <v>2.6</v>
       </c>
       <c r="E214" s="27">
-        <v>106.6</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6186,16 +6189,16 @@
         <v>220</v>
       </c>
       <c r="B218" s="24">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C218" s="25">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D218" s="26">
         <v>3.93</v>
       </c>
       <c r="E218" s="27">
-        <v>841.27</v>
+        <v>821.62</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6220,16 +6223,16 @@
         <v>222</v>
       </c>
       <c r="B220" s="24">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C220" s="25">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D220" s="26">
         <v>2.7</v>
       </c>
       <c r="E220" s="27">
-        <v>661.5</v>
+        <v>656.1</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6237,16 +6240,16 @@
         <v>223</v>
       </c>
       <c r="B221" s="24">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C221" s="25">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D221" s="26">
         <v>2.7</v>
       </c>
       <c r="E221" s="27">
-        <v>410.4</v>
+        <v>361.8</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6254,16 +6257,16 @@
         <v>224</v>
       </c>
       <c r="B222" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C222" s="25">
-        <v>78.5</v>
+        <v>76</v>
       </c>
       <c r="D222" s="26">
         <v>2.2999999999999998</v>
       </c>
       <c r="E222" s="27">
-        <v>180.55</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6305,16 +6308,16 @@
         <v>227</v>
       </c>
       <c r="B225" s="24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C225" s="25">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="D225" s="26">
         <v>3</v>
       </c>
       <c r="E225" s="27">
-        <v>28.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6322,16 +6325,16 @@
         <v>228</v>
       </c>
       <c r="B226" s="24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C226" s="25">
-        <v>148.5</v>
+        <v>146.5</v>
       </c>
       <c r="D226" s="26">
         <v>3.93</v>
       </c>
       <c r="E226" s="27">
-        <v>583.48</v>
+        <v>575.62</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6339,16 +6342,16 @@
         <v>229</v>
       </c>
       <c r="B227" s="24">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C227" s="25">
-        <v>134.75</v>
+        <v>124.25</v>
       </c>
       <c r="D227" s="26">
         <v>3.25</v>
       </c>
       <c r="E227" s="27">
-        <v>437.94</v>
+        <v>403.81</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6356,16 +6359,16 @@
         <v>230</v>
       </c>
       <c r="B228" s="24">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C228" s="25">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D228" s="26">
         <v>3.64</v>
       </c>
       <c r="E228" s="27">
-        <v>91.01</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6548,16 +6551,16 @@
         <v>242</v>
       </c>
       <c r="B240" s="24">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C240" s="25">
-        <v>157.38</v>
+        <v>156.38</v>
       </c>
       <c r="D240" s="26">
         <v>3.25</v>
       </c>
       <c r="E240" s="27">
-        <v>511.49</v>
+        <v>508.24</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -6565,16 +6568,16 @@
         <v>243</v>
       </c>
       <c r="B241" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C241" s="25">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="D241" s="26">
         <v>3.25</v>
       </c>
       <c r="E241" s="27">
-        <v>56.88</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -6762,16 +6765,16 @@
         <v>256</v>
       </c>
       <c r="B254" s="24">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C254" s="25">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D254" s="26">
         <v>3</v>
       </c>
       <c r="E254" s="27">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6796,16 +6799,16 @@
         <v>258</v>
       </c>
       <c r="B256" s="24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C256" s="25">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D256" s="26">
         <v>3.8</v>
       </c>
       <c r="E256" s="27">
-        <v>304</v>
+        <v>288.8</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6813,16 +6816,16 @@
         <v>259</v>
       </c>
       <c r="B257" s="24">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C257" s="25">
-        <v>55.5</v>
+        <v>48.5</v>
       </c>
       <c r="D257" s="26">
         <v>3.9</v>
       </c>
       <c r="E257" s="27">
-        <v>216.45</v>
+        <v>189.15</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,16 +7047,16 @@
         <v>274</v>
       </c>
       <c r="B272" s="24">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C272" s="25">
-        <v>135.28</v>
+        <v>110.78</v>
       </c>
       <c r="D272" s="26">
         <v>4.28</v>
       </c>
       <c r="E272" s="27">
-        <v>579</v>
+        <v>474.14</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -7106,16 +7109,16 @@
         <v>278</v>
       </c>
       <c r="B276" s="24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C276" s="25">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D276" s="26">
         <v>3.1</v>
       </c>
       <c r="E276" s="27">
-        <v>226.3</v>
+        <v>213.9</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7145,16 +7148,16 @@
         <v>281</v>
       </c>
       <c r="B279" s="24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C279" s="25">
-        <v>31.5</v>
+        <v>26.5</v>
       </c>
       <c r="D279" s="26">
         <v>6.25</v>
       </c>
       <c r="E279" s="27">
-        <v>196.88</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -7162,16 +7165,16 @@
         <v>282</v>
       </c>
       <c r="B280" s="24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C280" s="25">
-        <v>73.37</v>
+        <v>69.37</v>
       </c>
       <c r="D280" s="26">
         <v>4.25</v>
       </c>
       <c r="E280" s="27">
-        <v>311.82</v>
+        <v>294.82</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -7252,16 +7255,16 @@
         <v>288</v>
       </c>
       <c r="B286" s="24">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C286" s="25">
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
       <c r="D286" s="26">
         <v>6.5</v>
       </c>
       <c r="E286" s="27">
-        <v>191.75</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7286,16 +7289,16 @@
         <v>290</v>
       </c>
       <c r="B288" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C288" s="25">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D288" s="26">
         <v>4.8499999999999996</v>
       </c>
       <c r="E288" s="27">
-        <v>436.31</v>
+        <v>431.46</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -7314,16 +7317,16 @@
         <v>292</v>
       </c>
       <c r="B290" s="24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C290" s="25">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="D290" s="26">
         <v>4.7300000000000004</v>
       </c>
       <c r="E290" s="27">
-        <v>47.26</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7348,16 +7351,16 @@
         <v>294</v>
       </c>
       <c r="B292" s="24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C292" s="25">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D292" s="26">
         <v>5.16</v>
       </c>
       <c r="E292" s="27">
-        <v>428.28</v>
+        <v>433.44</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7382,16 +7385,16 @@
         <v>296</v>
       </c>
       <c r="B294" s="24">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C294" s="25">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D294" s="26">
         <v>5</v>
       </c>
       <c r="E294" s="27">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7433,16 +7436,16 @@
         <v>299</v>
       </c>
       <c r="B297" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C297" s="25">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="D297" s="26">
         <v>4.66</v>
       </c>
       <c r="E297" s="27">
-        <v>202.7</v>
+        <v>198.04</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7467,16 +7470,16 @@
         <v>301</v>
       </c>
       <c r="B299" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C299" s="25">
-        <v>92.5</v>
+        <v>89.5</v>
       </c>
       <c r="D299" s="26">
         <v>4.5</v>
       </c>
       <c r="E299" s="27">
-        <v>416.25</v>
+        <v>402.75</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7501,16 +7504,16 @@
         <v>303</v>
       </c>
       <c r="B301" s="24">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C301" s="25">
-        <v>81.5</v>
+        <v>79.5</v>
       </c>
       <c r="D301" s="26">
         <v>4.8899999999999997</v>
       </c>
       <c r="E301" s="27">
-        <v>398.33</v>
+        <v>388.56</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7535,16 +7538,16 @@
         <v>305</v>
       </c>
       <c r="B303" s="24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C303" s="25">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="D303" s="26">
         <v>3.15</v>
       </c>
       <c r="E303" s="27">
-        <v>118.13</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7552,16 +7555,16 @@
         <v>306</v>
       </c>
       <c r="B304" s="24">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C304" s="25">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D304" s="26">
         <v>6.08</v>
       </c>
       <c r="E304" s="27">
-        <v>1307.19</v>
+        <v>1283.1300000000001</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -7705,16 +7708,16 @@
         <v>315</v>
       </c>
       <c r="B313" s="24">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C313" s="25">
-        <v>38</v>
+        <v>34.5</v>
       </c>
       <c r="D313" s="26">
         <v>5.13</v>
       </c>
       <c r="E313" s="27">
-        <v>194.94</v>
+        <v>176.99</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -8104,16 +8107,16 @@
         <v>340</v>
       </c>
       <c r="B338" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C338" s="25">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D338" s="26">
         <v>4.28</v>
       </c>
       <c r="E338" s="27">
-        <v>646.28</v>
+        <v>642</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8217,16 +8220,16 @@
         <v>347</v>
       </c>
       <c r="B345" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C345" s="25">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="D345" s="26">
         <v>9</v>
       </c>
       <c r="E345" s="27">
-        <v>283.5</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -8424,16 +8427,16 @@
         <v>360</v>
       </c>
       <c r="B358" s="24">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C358" s="25">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D358" s="26">
         <v>5.94</v>
       </c>
       <c r="E358" s="27">
-        <v>118.8</v>
+        <v>133.65</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8492,16 +8495,16 @@
         <v>364</v>
       </c>
       <c r="B362" s="24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C362" s="25">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D362" s="26">
         <v>9.1999999999999993</v>
       </c>
       <c r="E362" s="27">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8558,16 +8561,16 @@
         <v>368</v>
       </c>
       <c r="B366" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C366" s="25">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="D366" s="26">
         <v>6.66</v>
       </c>
       <c r="E366" s="27">
-        <v>176.44</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8620,16 +8623,16 @@
         <v>372</v>
       </c>
       <c r="B370" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C370" s="25">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="D370" s="26">
         <v>7.13</v>
       </c>
       <c r="E370" s="27">
-        <v>224.6</v>
+        <v>206.77</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8637,16 +8640,16 @@
         <v>373</v>
       </c>
       <c r="B371" s="24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C371" s="25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D371" s="26">
         <v>6.65</v>
       </c>
       <c r="E371" s="27">
-        <v>152.94999999999999</v>
+        <v>146.30000000000001</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -8656,15 +8659,9 @@
       <c r="B372" s="24">
         <v>57</v>
       </c>
-      <c r="C372" s="25">
-        <v>1</v>
-      </c>
-      <c r="D372" s="26">
-        <v>5.94</v>
-      </c>
-      <c r="E372" s="27">
-        <v>5.94</v>
-      </c>
+      <c r="C372" s="28"/>
+      <c r="D372" s="29"/>
+      <c r="E372" s="28"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="23" t="s">
@@ -8739,16 +8736,16 @@
         <v>379</v>
       </c>
       <c r="B377" s="24">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C377" s="25">
-        <v>128.5</v>
+        <v>124</v>
       </c>
       <c r="D377" s="26">
         <v>6.6</v>
       </c>
       <c r="E377" s="27">
-        <v>848.1</v>
+        <v>818.4</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8793,13 +8790,13 @@
         <v>26</v>
       </c>
       <c r="C380" s="25">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="D380" s="26">
         <v>8.52</v>
       </c>
       <c r="E380" s="27">
-        <v>374.7</v>
+        <v>378.96</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8807,16 +8804,16 @@
         <v>383</v>
       </c>
       <c r="B381" s="24">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C381" s="25">
-        <v>40.5</v>
+        <v>33.5</v>
       </c>
       <c r="D381" s="26">
         <v>8.1999999999999993</v>
       </c>
       <c r="E381" s="27">
-        <v>332.1</v>
+        <v>274.7</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -8824,16 +8821,16 @@
         <v>384</v>
       </c>
       <c r="B382" s="24">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C382" s="25">
-        <v>52.83</v>
+        <v>51.33</v>
       </c>
       <c r="D382" s="26">
         <v>4.5</v>
       </c>
       <c r="E382" s="27">
-        <v>237.74</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -8875,16 +8872,16 @@
         <v>387</v>
       </c>
       <c r="B385" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C385" s="25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D385" s="26">
         <v>8.25</v>
       </c>
       <c r="E385" s="27">
-        <v>189.75</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -8909,16 +8906,16 @@
         <v>389</v>
       </c>
       <c r="B387" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C387" s="25">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D387" s="26">
         <v>9.5</v>
       </c>
       <c r="E387" s="27">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -8926,16 +8923,16 @@
         <v>390</v>
       </c>
       <c r="B388" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C388" s="25">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="D388" s="26">
         <v>3.6</v>
       </c>
       <c r="E388" s="27">
-        <v>275.39999999999998</v>
+        <v>271.8</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -8943,16 +8940,16 @@
         <v>391</v>
       </c>
       <c r="B389" s="24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C389" s="25">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D389" s="26">
         <v>6</v>
       </c>
       <c r="E389" s="27">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -9207,16 +9204,16 @@
         <v>407</v>
       </c>
       <c r="B405" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C405" s="25">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="D405" s="26">
         <v>6.65</v>
       </c>
       <c r="E405" s="27">
-        <v>169.58</v>
+        <v>156.28</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
@@ -9297,11 +9294,17 @@
         <v>413</v>
       </c>
       <c r="B411" s="24">
-        <v>43</v>
-      </c>
-      <c r="C411" s="28"/>
-      <c r="D411" s="29"/>
-      <c r="E411" s="28"/>
+        <v>42</v>
+      </c>
+      <c r="C411" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="D411" s="26">
+        <v>7</v>
+      </c>
+      <c r="E411" s="27">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="23" t="s">
@@ -9426,16 +9429,16 @@
         <v>422</v>
       </c>
       <c r="B420" s="24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C420" s="25">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D420" s="26">
         <v>5.2</v>
       </c>
       <c r="E420" s="27">
-        <v>306.8</v>
+        <v>286</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -9558,16 +9561,16 @@
         <v>430</v>
       </c>
       <c r="B428" s="24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C428" s="25">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D428" s="26">
         <v>6.46</v>
       </c>
       <c r="E428" s="27">
-        <v>48.45</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -9862,16 +9865,16 @@
         <v>450</v>
       </c>
       <c r="B448" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C448" s="25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="D448" s="26">
         <v>11.75</v>
       </c>
       <c r="E448" s="27">
-        <v>164.5</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -9958,16 +9961,16 @@
         <v>456</v>
       </c>
       <c r="B454" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C454" s="25">
-        <v>4.5</v>
+        <v>-5.5</v>
       </c>
       <c r="D454" s="26">
         <v>11</v>
       </c>
       <c r="E454" s="27">
-        <v>49.5</v>
+        <v>-60.5</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10113,13 +10116,13 @@
         <v>3</v>
       </c>
       <c r="C464" s="25">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D464" s="26">
         <v>29.7</v>
       </c>
       <c r="E464" s="27">
-        <v>103.95</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -10429,16 +10432,16 @@
         <v>485</v>
       </c>
       <c r="B483" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C483" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D483" s="26">
         <v>13.5</v>
       </c>
       <c r="E483" s="27">
-        <v>67.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -10491,16 +10494,16 @@
         <v>489</v>
       </c>
       <c r="B487" s="24">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C487" s="25">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="D487" s="26">
         <v>10.34</v>
       </c>
       <c r="E487" s="27">
-        <v>87.9</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -10647,16 +10650,16 @@
         <v>499</v>
       </c>
       <c r="B497" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C497" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D497" s="26">
         <v>9.26</v>
       </c>
       <c r="E497" s="27">
-        <v>55.56</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -10839,16 +10842,16 @@
         <v>511</v>
       </c>
       <c r="B509" s="24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C509" s="25">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D509" s="26">
         <v>11.25</v>
       </c>
       <c r="E509" s="27">
-        <v>28.13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -11738,16 +11741,16 @@
         <v>566</v>
       </c>
       <c r="B564" s="24">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C564" s="25">
-        <v>68.7</v>
+        <v>64.7</v>
       </c>
       <c r="D564" s="26">
         <v>3.9</v>
       </c>
       <c r="E564" s="27">
-        <v>267.93</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11851,16 +11854,16 @@
         <v>573</v>
       </c>
       <c r="B571" s="24">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C571" s="25">
-        <v>11.3</v>
+        <v>6.3</v>
       </c>
       <c r="D571" s="26">
         <v>3.14</v>
       </c>
       <c r="E571" s="27">
-        <v>35.479999999999997</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -11936,16 +11939,16 @@
         <v>578</v>
       </c>
       <c r="B576" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C576" s="25">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="D576" s="26">
         <v>5.7</v>
       </c>
       <c r="E576" s="27">
-        <v>128.25</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12055,16 +12058,16 @@
         <v>585</v>
       </c>
       <c r="B583" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C583" s="25">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D583" s="26">
         <v>2.74</v>
       </c>
       <c r="E583" s="27">
-        <v>35.64</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -12106,16 +12109,16 @@
         <v>588</v>
       </c>
       <c r="B586" s="24">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C586" s="25">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D586" s="26">
         <v>1.4</v>
       </c>
       <c r="E586" s="27">
-        <v>36.4</v>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
@@ -12123,16 +12126,16 @@
         <v>589</v>
       </c>
       <c r="B587" s="24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C587" s="25">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="D587" s="26">
         <v>1.8</v>
       </c>
       <c r="E587" s="27">
-        <v>47.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -12290,10 +12293,10 @@
         <v>600</v>
       </c>
       <c r="B598" s="24">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C598" s="25">
-        <v>102.5</v>
+        <v>92.5</v>
       </c>
       <c r="D598" s="29"/>
       <c r="E598" s="28"/>
@@ -12316,10 +12319,10 @@
         <v>602</v>
       </c>
       <c r="B600" s="24">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C600" s="25">
-        <v>154.5</v>
+        <v>152.5</v>
       </c>
       <c r="D600" s="29"/>
       <c r="E600" s="28"/>
@@ -12329,10 +12332,10 @@
         <v>603</v>
       </c>
       <c r="B601" s="24">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C601" s="25">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D601" s="29"/>
       <c r="E601" s="28"/>
@@ -12342,10 +12345,10 @@
         <v>604</v>
       </c>
       <c r="B602" s="24">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C602" s="25">
-        <v>45.5</v>
+        <v>33.5</v>
       </c>
       <c r="D602" s="29"/>
       <c r="E602" s="28"/>
@@ -12355,16 +12358,16 @@
         <v>605</v>
       </c>
       <c r="B603" s="24">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C603" s="25">
-        <v>289.5</v>
+        <v>283.5</v>
       </c>
       <c r="D603" s="26">
         <v>0.87</v>
       </c>
       <c r="E603" s="27">
-        <v>251.87</v>
+        <v>246.65</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
@@ -12372,16 +12375,16 @@
         <v>606</v>
       </c>
       <c r="B604" s="24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C604" s="25">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D604" s="26">
         <v>0.57999999999999996</v>
       </c>
       <c r="E604" s="27">
-        <v>308.56</v>
+        <v>307.39999999999998</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
@@ -12417,16 +12420,16 @@
         <v>609</v>
       </c>
       <c r="B607" s="24">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C607" s="25">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D607" s="26">
         <v>0.85</v>
       </c>
       <c r="E607" s="27">
-        <v>290.7</v>
+        <v>289.85000000000002</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
@@ -12451,9 +12454,11 @@
         <v>611</v>
       </c>
       <c r="B609" s="24">
-        <v>32</v>
-      </c>
-      <c r="C609" s="28"/>
+        <v>33</v>
+      </c>
+      <c r="C609" s="25">
+        <v>108</v>
+      </c>
       <c r="D609" s="29"/>
       <c r="E609" s="28"/>
     </row>
@@ -12475,10 +12480,10 @@
         <v>613</v>
       </c>
       <c r="B611" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C611" s="25">
-        <v>98</v>
+        <v>240</v>
       </c>
       <c r="D611" s="29"/>
       <c r="E611" s="28"/>
@@ -12651,9 +12656,11 @@
       <c r="A624" s="23" t="s">
         <v>626</v>
       </c>
-      <c r="B624" s="24"/>
+      <c r="B624" s="24">
+        <v>1</v>
+      </c>
       <c r="C624" s="25">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="D624" s="29"/>
       <c r="E624" s="28"/>
@@ -12662,34 +12669,28 @@
       <c r="A625" s="23" t="s">
         <v>627</v>
       </c>
-      <c r="B625" s="24">
-        <v>1</v>
-      </c>
+      <c r="B625" s="24"/>
       <c r="C625" s="25">
-        <v>9</v>
-      </c>
-      <c r="D625" s="26">
-        <v>5.25</v>
-      </c>
-      <c r="E625" s="27">
-        <v>47.25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D625" s="29"/>
+      <c r="E625" s="28"/>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="23" t="s">
         <v>628</v>
       </c>
       <c r="B626" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C626" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D626" s="26">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="E626" s="27">
-        <v>38.5</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -12697,16 +12698,16 @@
         <v>629</v>
       </c>
       <c r="B627" s="24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C627" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D627" s="26">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="E627" s="27">
-        <v>41.25</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -12714,16 +12715,16 @@
         <v>630</v>
       </c>
       <c r="B628" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C628" s="25">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D628" s="26">
         <v>8.25</v>
       </c>
       <c r="E628" s="27">
-        <v>20.63</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -12731,16 +12732,16 @@
         <v>631</v>
       </c>
       <c r="B629" s="24">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C629" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D629" s="26">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="E629" s="27">
-        <v>35</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -12748,16 +12749,16 @@
         <v>632</v>
       </c>
       <c r="B630" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C630" s="25">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="D630" s="26">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="E630" s="27">
-        <v>57.75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -12765,16 +12766,16 @@
         <v>633</v>
       </c>
       <c r="B631" s="24">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C631" s="25">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="D631" s="26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E631" s="27">
-        <v>5</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -12782,16 +12783,16 @@
         <v>634</v>
       </c>
       <c r="B632" s="24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C632" s="25">
-        <v>4.01</v>
+        <v>1</v>
       </c>
       <c r="D632" s="26">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E632" s="27">
-        <v>18.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -12799,16 +12800,16 @@
         <v>635</v>
       </c>
       <c r="B633" s="24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C633" s="25">
-        <v>12.5</v>
+        <v>4.01</v>
       </c>
       <c r="D633" s="26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E633" s="27">
-        <v>43.75</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -12816,16 +12817,16 @@
         <v>636</v>
       </c>
       <c r="B634" s="24">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C634" s="25">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="D634" s="26">
         <v>3.5</v>
       </c>
       <c r="E634" s="27">
-        <v>1.75</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -12833,16 +12834,16 @@
         <v>637</v>
       </c>
       <c r="B635" s="24">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C635" s="25">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="D635" s="26">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="E635" s="27">
-        <v>51.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -12850,16 +12851,16 @@
         <v>638</v>
       </c>
       <c r="B636" s="24">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C636" s="25">
-        <v>24.35</v>
+        <v>10.5</v>
       </c>
       <c r="D636" s="26">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="E636" s="27">
-        <v>97.4</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -12867,16 +12868,16 @@
         <v>639</v>
       </c>
       <c r="B637" s="24">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C637" s="25">
-        <v>4.5</v>
+        <v>24.35</v>
       </c>
       <c r="D637" s="26">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="E637" s="27">
-        <v>29.25</v>
+        <v>97.4</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -12884,16 +12885,16 @@
         <v>640</v>
       </c>
       <c r="B638" s="24">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C638" s="25">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="D638" s="26">
         <v>6.5</v>
       </c>
       <c r="E638" s="27">
-        <v>45.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
@@ -12901,16 +12902,16 @@
         <v>641</v>
       </c>
       <c r="B639" s="24">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="C639" s="25">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D639" s="26">
-        <v>2.77</v>
+        <v>6.5</v>
       </c>
       <c r="E639" s="27">
-        <v>121.89</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -12918,16 +12919,16 @@
         <v>642</v>
       </c>
       <c r="B640" s="24">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C640" s="25">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="D640" s="26">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="E640" s="27">
-        <v>4.09</v>
+        <v>110.81</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
@@ -12935,16 +12936,16 @@
         <v>643</v>
       </c>
       <c r="B641" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C641" s="25">
         <v>1.5</v>
       </c>
       <c r="D641" s="26">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="E641" s="27">
-        <v>3.99</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -12952,16 +12953,16 @@
         <v>644</v>
       </c>
       <c r="B642" s="24">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="C642" s="25">
-        <v>38</v>
+        <v>1.5</v>
       </c>
       <c r="D642" s="26">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="E642" s="27">
-        <v>104.84</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
@@ -12969,16 +12970,16 @@
         <v>645</v>
       </c>
       <c r="B643" s="24">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C643" s="25">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D643" s="26">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="E643" s="27">
-        <v>164</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -12986,16 +12987,16 @@
         <v>646</v>
       </c>
       <c r="B644" s="24">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C644" s="25">
-        <v>23.5</v>
+        <v>41</v>
       </c>
       <c r="D644" s="26">
         <v>4</v>
       </c>
       <c r="E644" s="27">
-        <v>94</v>
+        <v>164</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -13003,16 +13004,16 @@
         <v>647</v>
       </c>
       <c r="B645" s="24">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C645" s="25">
-        <v>-1</v>
+        <v>21.5</v>
       </c>
       <c r="D645" s="26">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E645" s="27">
-        <v>-1.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -13020,33 +13021,27 @@
         <v>648</v>
       </c>
       <c r="B646" s="24">
-        <v>3</v>
-      </c>
-      <c r="C646" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="D646" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="E646" s="27">
-        <v>0.75</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C646" s="28"/>
+      <c r="D646" s="29"/>
+      <c r="E646" s="28"/>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="23" t="s">
         <v>649</v>
       </c>
       <c r="B647" s="24">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C647" s="25">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D647" s="26">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="E647" s="27">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -13054,16 +13049,16 @@
         <v>650</v>
       </c>
       <c r="B648" s="24">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C648" s="25">
-        <v>120</v>
+        <v>0.25</v>
       </c>
       <c r="D648" s="26">
-        <v>2.2799999999999998</v>
+        <v>1.52</v>
       </c>
       <c r="E648" s="27">
-        <v>273.60000000000002</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -13071,16 +13066,16 @@
         <v>651</v>
       </c>
       <c r="B649" s="24">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C649" s="25">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="D649" s="26">
         <v>2.2799999999999998</v>
       </c>
       <c r="E649" s="27">
-        <v>98.04</v>
+        <v>271.32</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -13088,16 +13083,16 @@
         <v>652</v>
       </c>
       <c r="B650" s="24">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C650" s="25">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D650" s="26">
-        <v>5</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E650" s="27">
-        <v>75</v>
+        <v>86.64</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
@@ -13105,16 +13100,16 @@
         <v>653</v>
       </c>
       <c r="B651" s="24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C651" s="25">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="D651" s="26">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E651" s="27">
-        <v>2.75</v>
+        <v>75</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
@@ -13122,16 +13117,16 @@
         <v>654</v>
       </c>
       <c r="B652" s="24">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C652" s="25">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D652" s="26">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="E652" s="27">
-        <v>7.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -13139,16 +13134,16 @@
         <v>655</v>
       </c>
       <c r="B653" s="24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C653" s="25">
-        <v>24.5</v>
+        <v>2.5</v>
       </c>
       <c r="D653" s="26">
-        <v>4.6500000000000004</v>
+        <v>3</v>
       </c>
       <c r="E653" s="27">
-        <v>113.93</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -13156,16 +13151,16 @@
         <v>656</v>
       </c>
       <c r="B654" s="24">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C654" s="25">
-        <v>30.5</v>
+        <v>24.5</v>
       </c>
       <c r="D654" s="26">
-        <v>5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="E654" s="27">
-        <v>152.5</v>
+        <v>113.93</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -13173,16 +13168,16 @@
         <v>657</v>
       </c>
       <c r="B655" s="24">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C655" s="25">
-        <v>7.5</v>
+        <v>30.5</v>
       </c>
       <c r="D655" s="26">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E655" s="27">
-        <v>26.25</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -13190,16 +13185,16 @@
         <v>658</v>
       </c>
       <c r="B656" s="24">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C656" s="25">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="D656" s="26">
         <v>3.5</v>
       </c>
       <c r="E656" s="27">
-        <v>38.5</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -13207,44 +13202,44 @@
         <v>659</v>
       </c>
       <c r="B657" s="24">
-        <v>5</v>
-      </c>
-      <c r="C657" s="28"/>
-      <c r="D657" s="29"/>
-      <c r="E657" s="28"/>
+        <v>19</v>
+      </c>
+      <c r="C657" s="25">
+        <v>11</v>
+      </c>
+      <c r="D657" s="26">
+        <v>3.5</v>
+      </c>
+      <c r="E657" s="27">
+        <v>38.5</v>
+      </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="23" t="s">
         <v>660</v>
       </c>
       <c r="B658" s="24">
-        <v>12</v>
-      </c>
-      <c r="C658" s="25">
-        <v>15.5</v>
-      </c>
-      <c r="D658" s="26">
-        <v>5.45</v>
-      </c>
-      <c r="E658" s="27">
-        <v>84.48</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C658" s="28"/>
+      <c r="D658" s="29"/>
+      <c r="E658" s="28"/>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="23" t="s">
         <v>661</v>
       </c>
       <c r="B659" s="24">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C659" s="25">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="D659" s="26">
-        <v>3.1</v>
+        <v>5.45</v>
       </c>
       <c r="E659" s="27">
-        <v>93</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -13252,16 +13247,16 @@
         <v>662</v>
       </c>
       <c r="B660" s="24">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="C660" s="25">
-        <v>110.36</v>
+        <v>27</v>
       </c>
       <c r="D660" s="26">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="E660" s="27">
-        <v>187.61</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -13269,16 +13264,16 @@
         <v>663</v>
       </c>
       <c r="B661" s="24">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="C661" s="25">
-        <v>34</v>
+        <v>110.36</v>
       </c>
       <c r="D661" s="26">
-        <v>3.33</v>
+        <v>1.7</v>
       </c>
       <c r="E661" s="27">
-        <v>113.22</v>
+        <v>187.61</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -13286,16 +13281,16 @@
         <v>664</v>
       </c>
       <c r="B662" s="24">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C662" s="25">
-        <v>23</v>
+        <v>32.5</v>
       </c>
       <c r="D662" s="26">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="E662" s="27">
-        <v>80.5</v>
+        <v>108.23</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -13303,16 +13298,16 @@
         <v>665</v>
       </c>
       <c r="B663" s="24">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C663" s="25">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="D663" s="26">
         <v>3.5</v>
       </c>
       <c r="E663" s="27">
-        <v>75.25</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -13320,16 +13315,16 @@
         <v>666</v>
       </c>
       <c r="B664" s="24">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C664" s="25">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="D664" s="26">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E664" s="27">
-        <v>18.75</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -13337,16 +13332,16 @@
         <v>667</v>
       </c>
       <c r="B665" s="24">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C665" s="25">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D665" s="26">
-        <v>8.76</v>
+        <v>7.5</v>
       </c>
       <c r="E665" s="27">
-        <v>-4.38</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
@@ -13354,16 +13349,16 @@
         <v>668</v>
       </c>
       <c r="B666" s="24">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C666" s="25">
-        <v>8.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D666" s="26">
-        <v>6.25</v>
+        <v>8.76</v>
       </c>
       <c r="E666" s="27">
-        <v>53.13</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -13371,16 +13366,16 @@
         <v>669</v>
       </c>
       <c r="B667" s="24">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="C667" s="25">
-        <v>115</v>
+        <v>8.5</v>
       </c>
       <c r="D667" s="26">
-        <v>2.85</v>
+        <v>6.25</v>
       </c>
       <c r="E667" s="27">
-        <v>327.75</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
@@ -13388,16 +13383,16 @@
         <v>670</v>
       </c>
       <c r="B668" s="24">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="C668" s="25">
-        <v>58.99</v>
+        <v>102</v>
       </c>
       <c r="D668" s="26">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="E668" s="27">
-        <v>117.98</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
@@ -13405,16 +13400,16 @@
         <v>671</v>
       </c>
       <c r="B669" s="24">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C669" s="25">
+        <v>58.99</v>
+      </c>
+      <c r="D669" s="26">
         <v>2</v>
       </c>
-      <c r="D669" s="26">
-        <v>5.6</v>
-      </c>
       <c r="E669" s="27">
-        <v>11.2</v>
+        <v>117.98</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13422,7 +13417,7 @@
         <v>672</v>
       </c>
       <c r="B670" s="24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C670" s="28"/>
       <c r="D670" s="29"/>
@@ -13444,33 +13439,27 @@
         <v>674</v>
       </c>
       <c r="B672" s="24">
-        <v>40</v>
-      </c>
-      <c r="C672" s="25">
-        <v>42.5</v>
-      </c>
-      <c r="D672" s="26">
-        <v>3.1</v>
-      </c>
-      <c r="E672" s="27">
-        <v>131.75</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C672" s="28"/>
+      <c r="D672" s="29"/>
+      <c r="E672" s="28"/>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="23" t="s">
         <v>675</v>
       </c>
       <c r="B673" s="24">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C673" s="25">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="D673" s="26">
-        <v>5.73</v>
+        <v>3.1</v>
       </c>
       <c r="E673" s="27">
-        <v>286.58999999999997</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -13478,16 +13467,16 @@
         <v>676</v>
       </c>
       <c r="B674" s="24">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C674" s="25">
-        <v>31.5</v>
+        <v>50</v>
       </c>
       <c r="D674" s="26">
-        <v>3.97</v>
+        <v>5.73</v>
       </c>
       <c r="E674" s="27">
-        <v>125.01</v>
+        <v>286.58999999999997</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -13495,16 +13484,16 @@
         <v>677</v>
       </c>
       <c r="B675" s="24">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="C675" s="25">
-        <v>12</v>
+        <v>31.5</v>
       </c>
       <c r="D675" s="26">
-        <v>4.8</v>
+        <v>3.97</v>
       </c>
       <c r="E675" s="27">
-        <v>57.6</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -13512,16 +13501,16 @@
         <v>678</v>
       </c>
       <c r="B676" s="24">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C676" s="25">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D676" s="26">
-        <v>6.76</v>
+        <v>4.8</v>
       </c>
       <c r="E676" s="27">
-        <v>3.38</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -13529,44 +13518,44 @@
         <v>679</v>
       </c>
       <c r="B677" s="24">
-        <v>18</v>
-      </c>
-      <c r="C677" s="28"/>
-      <c r="D677" s="29"/>
-      <c r="E677" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="C677" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="D677" s="26">
+        <v>6.76</v>
+      </c>
+      <c r="E677" s="27">
+        <v>3.38</v>
+      </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="23" t="s">
         <v>680</v>
       </c>
       <c r="B678" s="24">
-        <v>7</v>
-      </c>
-      <c r="C678" s="25">
-        <v>1</v>
-      </c>
-      <c r="D678" s="26">
-        <v>6.75</v>
-      </c>
-      <c r="E678" s="27">
-        <v>6.75</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C678" s="28"/>
+      <c r="D678" s="29"/>
+      <c r="E678" s="28"/>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="23" t="s">
         <v>681</v>
       </c>
       <c r="B679" s="24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C679" s="25">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="D679" s="26">
         <v>6.75</v>
       </c>
       <c r="E679" s="27">
-        <v>30.38</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -13574,16 +13563,16 @@
         <v>682</v>
       </c>
       <c r="B680" s="24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C680" s="25">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D680" s="26">
         <v>6.75</v>
       </c>
       <c r="E680" s="27">
-        <v>47.25</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -13591,16 +13580,16 @@
         <v>683</v>
       </c>
       <c r="B681" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C681" s="25">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="D681" s="26">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="E681" s="27">
-        <v>2.75</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -13608,16 +13597,16 @@
         <v>684</v>
       </c>
       <c r="B682" s="24">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="C682" s="25">
-        <v>109</v>
+        <v>0.5</v>
       </c>
       <c r="D682" s="26">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="E682" s="27">
-        <v>337.9</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -13625,16 +13614,16 @@
         <v>685</v>
       </c>
       <c r="B683" s="24">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="C683" s="25">
-        <v>32.43</v>
+        <v>101</v>
       </c>
       <c r="D683" s="26">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="E683" s="27">
-        <v>116.75</v>
+        <v>313.10000000000002</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -13642,16 +13631,16 @@
         <v>686</v>
       </c>
       <c r="B684" s="24">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C684" s="25">
-        <v>10.5</v>
+        <v>32.43</v>
       </c>
       <c r="D684" s="26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E684" s="27">
-        <v>36.75</v>
+        <v>116.75</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -13659,16 +13648,16 @@
         <v>687</v>
       </c>
       <c r="B685" s="24">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C685" s="25">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="D685" s="26">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="E685" s="27">
-        <v>46.75</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -13676,16 +13665,16 @@
         <v>688</v>
       </c>
       <c r="B686" s="24">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C686" s="25">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="D686" s="26">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="E686" s="27">
-        <v>61.88</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -13693,16 +13682,16 @@
         <v>689</v>
       </c>
       <c r="B687" s="24">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C687" s="25">
-        <v>37.5</v>
+        <v>15.5</v>
       </c>
       <c r="D687" s="26">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="E687" s="27">
-        <v>93.75</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -13710,16 +13699,16 @@
         <v>690</v>
       </c>
       <c r="B688" s="24">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C688" s="25">
-        <v>2</v>
+        <v>37.5</v>
       </c>
       <c r="D688" s="26">
-        <v>7.32</v>
+        <v>2.5</v>
       </c>
       <c r="E688" s="27">
-        <v>14.63</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -13727,16 +13716,16 @@
         <v>691</v>
       </c>
       <c r="B689" s="24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C689" s="25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D689" s="26">
-        <v>5.75</v>
+        <v>7.31</v>
       </c>
       <c r="E689" s="27">
-        <v>17.25</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -13744,16 +13733,16 @@
         <v>692</v>
       </c>
       <c r="B690" s="24">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C690" s="25">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="D690" s="26">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="E690" s="27">
-        <v>78.3</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
@@ -13761,16 +13750,16 @@
         <v>693</v>
       </c>
       <c r="B691" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C691" s="25">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="D691" s="26">
-        <v>2.25</v>
+        <v>5.8</v>
       </c>
       <c r="E691" s="27">
-        <v>46.13</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
@@ -13778,16 +13767,16 @@
         <v>694</v>
       </c>
       <c r="B692" s="24">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C692" s="25">
-        <v>79</v>
+        <v>20.5</v>
       </c>
       <c r="D692" s="26">
         <v>2.25</v>
       </c>
       <c r="E692" s="27">
-        <v>177.75</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -13795,16 +13784,16 @@
         <v>695</v>
       </c>
       <c r="B693" s="24">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C693" s="25">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D693" s="26">
-        <v>8.84</v>
+        <v>2.25</v>
       </c>
       <c r="E693" s="27">
-        <v>88.38</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
@@ -13812,16 +13801,16 @@
         <v>696</v>
       </c>
       <c r="B694" s="24">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C694" s="25">
-        <v>35.5</v>
+        <v>10</v>
       </c>
       <c r="D694" s="26">
-        <v>2.75</v>
+        <v>8.84</v>
       </c>
       <c r="E694" s="27">
-        <v>97.63</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
@@ -13829,16 +13818,16 @@
         <v>697</v>
       </c>
       <c r="B695" s="24">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C695" s="25">
-        <v>64</v>
+        <v>35.5</v>
       </c>
       <c r="D695" s="26">
         <v>2.75</v>
       </c>
       <c r="E695" s="27">
-        <v>176</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
@@ -13849,13 +13838,13 @@
         <v>21</v>
       </c>
       <c r="C696" s="25">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D696" s="26">
         <v>2.75</v>
       </c>
       <c r="E696" s="27">
-        <v>79.75</v>
+        <v>176</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
@@ -13863,16 +13852,16 @@
         <v>699</v>
       </c>
       <c r="B697" s="24">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C697" s="25">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="D697" s="26">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="E697" s="27">
-        <v>22</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
@@ -13880,44 +13869,44 @@
         <v>700</v>
       </c>
       <c r="B698" s="24">
-        <v>3</v>
-      </c>
-      <c r="C698" s="28"/>
-      <c r="D698" s="29"/>
-      <c r="E698" s="28"/>
+        <v>47</v>
+      </c>
+      <c r="C698" s="25">
+        <v>3.5</v>
+      </c>
+      <c r="D698" s="26">
+        <v>4</v>
+      </c>
+      <c r="E698" s="27">
+        <v>14</v>
+      </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" s="23" t="s">
         <v>701</v>
       </c>
       <c r="B699" s="24">
-        <v>4</v>
-      </c>
-      <c r="C699" s="25">
-        <v>11.5</v>
-      </c>
-      <c r="D699" s="26">
-        <v>4.25</v>
-      </c>
-      <c r="E699" s="27">
-        <v>48.88</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C699" s="28"/>
+      <c r="D699" s="29"/>
+      <c r="E699" s="28"/>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700" s="23" t="s">
         <v>702</v>
       </c>
       <c r="B700" s="24">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C700" s="25">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="D700" s="26">
         <v>4.25</v>
       </c>
       <c r="E700" s="27">
-        <v>63.75</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.25">
@@ -13925,16 +13914,16 @@
         <v>703</v>
       </c>
       <c r="B701" s="24">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C701" s="25">
-        <v>15.35</v>
+        <v>15</v>
       </c>
       <c r="D701" s="26">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="E701" s="27">
-        <v>84.43</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.25">
@@ -13942,16 +13931,16 @@
         <v>704</v>
       </c>
       <c r="B702" s="24">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C702" s="25">
-        <v>28</v>
+        <v>15.35</v>
       </c>
       <c r="D702" s="26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E702" s="27">
-        <v>140</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.25">
@@ -13959,51 +13948,55 @@
         <v>705</v>
       </c>
       <c r="B703" s="24">
-        <v>8</v>
-      </c>
-      <c r="C703" s="28"/>
-      <c r="D703" s="29"/>
-      <c r="E703" s="28"/>
+        <v>19</v>
+      </c>
+      <c r="C703" s="25">
+        <v>28</v>
+      </c>
+      <c r="D703" s="26">
+        <v>5</v>
+      </c>
+      <c r="E703" s="27">
+        <v>140</v>
+      </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704" s="23" t="s">
         <v>706</v>
       </c>
       <c r="B704" s="24">
-        <v>13</v>
-      </c>
-      <c r="C704" s="25">
-        <v>25</v>
-      </c>
-      <c r="D704" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E704" s="27">
-        <v>90</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C704" s="28"/>
+      <c r="D704" s="29"/>
+      <c r="E704" s="28"/>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" s="23" t="s">
         <v>707</v>
       </c>
       <c r="B705" s="24">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C705" s="25">
-        <v>12.5</v>
-      </c>
-      <c r="D705" s="29"/>
-      <c r="E705" s="28"/>
+        <v>25</v>
+      </c>
+      <c r="D705" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E705" s="27">
+        <v>90</v>
+      </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" s="23" t="s">
         <v>708</v>
       </c>
       <c r="B706" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C706" s="25">
-        <v>29.5</v>
+        <v>13.5</v>
       </c>
       <c r="D706" s="29"/>
       <c r="E706" s="28"/>
@@ -14013,10 +14006,10 @@
         <v>709</v>
       </c>
       <c r="B707" s="24">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C707" s="25">
-        <v>16.84</v>
+        <v>29.5</v>
       </c>
       <c r="D707" s="29"/>
       <c r="E707" s="28"/>
@@ -14026,10 +14019,10 @@
         <v>710</v>
       </c>
       <c r="B708" s="24">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="C708" s="25">
-        <v>2</v>
+        <v>19.84</v>
       </c>
       <c r="D708" s="29"/>
       <c r="E708" s="28"/>
@@ -14039,10 +14032,10 @@
         <v>711</v>
       </c>
       <c r="B709" s="24">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C709" s="25">
-        <v>63.5</v>
+        <v>2</v>
       </c>
       <c r="D709" s="29"/>
       <c r="E709" s="28"/>
@@ -14052,10 +14045,10 @@
         <v>712</v>
       </c>
       <c r="B710" s="24">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C710" s="25">
-        <v>46.5</v>
+        <v>58.5</v>
       </c>
       <c r="D710" s="29"/>
       <c r="E710" s="28"/>
@@ -14065,10 +14058,10 @@
         <v>713</v>
       </c>
       <c r="B711" s="24">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C711" s="25">
-        <v>-27</v>
+        <v>46.5</v>
       </c>
       <c r="D711" s="29"/>
       <c r="E711" s="28"/>
@@ -14078,10 +14071,10 @@
         <v>714</v>
       </c>
       <c r="B712" s="24">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C712" s="25">
-        <v>10</v>
+        <v>-27</v>
       </c>
       <c r="D712" s="29"/>
       <c r="E712" s="28"/>
@@ -14091,10 +14084,10 @@
         <v>715</v>
       </c>
       <c r="B713" s="24">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C713" s="25">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D713" s="29"/>
       <c r="E713" s="28"/>
@@ -14103,8 +14096,12 @@
       <c r="A714" s="23" t="s">
         <v>716</v>
       </c>
-      <c r="B714" s="24"/>
-      <c r="C714" s="28"/>
+      <c r="B714" s="24">
+        <v>49</v>
+      </c>
+      <c r="C714" s="25">
+        <v>39</v>
+      </c>
       <c r="D714" s="29"/>
       <c r="E714" s="28"/>
     </row>
@@ -14112,61 +14109,55 @@
       <c r="A715" s="23" t="s">
         <v>717</v>
       </c>
-      <c r="B715" s="24">
-        <v>62</v>
-      </c>
-      <c r="C715" s="25">
-        <v>87.5</v>
-      </c>
-      <c r="D715" s="26">
-        <v>2.93</v>
-      </c>
-      <c r="E715" s="27">
-        <v>256.52</v>
-      </c>
+      <c r="B715" s="24"/>
+      <c r="C715" s="28"/>
+      <c r="D715" s="29"/>
+      <c r="E715" s="28"/>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" s="23" t="s">
         <v>718</v>
       </c>
-      <c r="B716" s="24"/>
+      <c r="B716" s="24">
+        <v>63</v>
+      </c>
       <c r="C716" s="25">
-        <v>14.5</v>
+        <v>86.5</v>
       </c>
       <c r="D716" s="26">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="E716" s="27">
-        <v>55.1</v>
+        <v>253.59</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" s="23" t="s">
         <v>719</v>
       </c>
-      <c r="B717" s="24">
-        <v>2</v>
-      </c>
+      <c r="B717" s="24"/>
       <c r="C717" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="D717" s="29"/>
-      <c r="E717" s="28"/>
+        <v>14.5</v>
+      </c>
+      <c r="D717" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="E717" s="27">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718" s="23" t="s">
         <v>720</v>
       </c>
-      <c r="B718" s="24"/>
+      <c r="B718" s="24">
+        <v>2</v>
+      </c>
       <c r="C718" s="25">
-        <v>1123</v>
-      </c>
-      <c r="D718" s="26">
-        <v>0.82</v>
-      </c>
-      <c r="E718" s="27">
-        <v>920.86</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="D718" s="29"/>
+      <c r="E718" s="28"/>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719" s="23" t="s">
@@ -14174,27 +14165,29 @@
       </c>
       <c r="B719" s="24"/>
       <c r="C719" s="25">
-        <v>787</v>
+        <v>1123</v>
       </c>
       <c r="D719" s="26">
-        <v>1.1499999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E719" s="27">
-        <v>905.05</v>
+        <v>920.86</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720" s="23" t="s">
         <v>722</v>
       </c>
-      <c r="B720" s="24">
-        <v>1</v>
-      </c>
+      <c r="B720" s="24"/>
       <c r="C720" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="D720" s="29"/>
-      <c r="E720" s="28"/>
+        <v>787</v>
+      </c>
+      <c r="D720" s="26">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E720" s="27">
+        <v>905.05</v>
+      </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" s="23" t="s">
@@ -14203,7 +14196,9 @@
       <c r="B721" s="24">
         <v>1</v>
       </c>
-      <c r="C721" s="28"/>
+      <c r="C721" s="25">
+        <v>-0.5</v>
+      </c>
       <c r="D721" s="29"/>
       <c r="E721" s="28"/>
     </row>
@@ -14212,7 +14207,7 @@
         <v>724</v>
       </c>
       <c r="B722" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C722" s="28"/>
       <c r="D722" s="29"/>
@@ -14223,7 +14218,7 @@
         <v>725</v>
       </c>
       <c r="B723" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C723" s="28"/>
       <c r="D723" s="29"/>
@@ -14256,7 +14251,7 @@
         <v>728</v>
       </c>
       <c r="B726" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C726" s="28"/>
       <c r="D726" s="29"/>
@@ -14267,7 +14262,7 @@
         <v>729</v>
       </c>
       <c r="B727" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C727" s="28"/>
       <c r="D727" s="29"/>
@@ -14278,11 +14273,9 @@
         <v>730</v>
       </c>
       <c r="B728" s="24">
-        <v>3</v>
-      </c>
-      <c r="C728" s="25">
-        <v>-0.03</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C728" s="28"/>
       <c r="D728" s="29"/>
       <c r="E728" s="28"/>
     </row>
@@ -14291,37 +14284,37 @@
         <v>731</v>
       </c>
       <c r="B729" s="24">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C729" s="25">
-        <v>47</v>
-      </c>
-      <c r="D729" s="26">
-        <v>1.6</v>
-      </c>
-      <c r="E729" s="27">
-        <v>75.2</v>
-      </c>
+        <v>-0.03</v>
+      </c>
+      <c r="D729" s="29"/>
+      <c r="E729" s="28"/>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A730" s="23" t="s">
         <v>732</v>
       </c>
-      <c r="B730" s="24"/>
-      <c r="C730" s="28"/>
-      <c r="D730" s="29"/>
-      <c r="E730" s="28"/>
+      <c r="B730" s="24">
+        <v>18</v>
+      </c>
+      <c r="C730" s="25">
+        <v>47</v>
+      </c>
+      <c r="D730" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="E730" s="27">
+        <v>75.2</v>
+      </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731" s="23" t="s">
         <v>733</v>
       </c>
-      <c r="B731" s="24">
-        <v>19</v>
-      </c>
-      <c r="C731" s="25">
-        <v>385</v>
-      </c>
+      <c r="B731" s="24"/>
+      <c r="C731" s="28"/>
       <c r="D731" s="29"/>
       <c r="E731" s="28"/>
     </row>
@@ -14330,40 +14323,40 @@
         <v>734</v>
       </c>
       <c r="B732" s="24">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="C732" s="25">
-        <v>195.5</v>
-      </c>
-      <c r="D732" s="26">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="E732" s="27">
-        <v>226.78</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="D732" s="29"/>
+      <c r="E732" s="28"/>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A733" s="23" t="s">
         <v>735</v>
       </c>
       <c r="B733" s="24">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C733" s="25">
-        <v>-0.45</v>
-      </c>
-      <c r="D733" s="29"/>
-      <c r="E733" s="28"/>
+        <v>193.5</v>
+      </c>
+      <c r="D733" s="26">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E733" s="27">
+        <v>224.46</v>
+      </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A734" s="23" t="s">
         <v>736</v>
       </c>
       <c r="B734" s="24">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C734" s="25">
-        <v>-0.79</v>
+        <v>-0.45</v>
       </c>
       <c r="D734" s="29"/>
       <c r="E734" s="28"/>
@@ -14373,9 +14366,11 @@
         <v>737</v>
       </c>
       <c r="B735" s="24">
-        <v>15</v>
-      </c>
-      <c r="C735" s="28"/>
+        <v>80</v>
+      </c>
+      <c r="C735" s="25">
+        <v>-0.79</v>
+      </c>
       <c r="D735" s="29"/>
       <c r="E735" s="28"/>
     </row>
@@ -14384,11 +14379,9 @@
         <v>738</v>
       </c>
       <c r="B736" s="24">
-        <v>57</v>
-      </c>
-      <c r="C736" s="25">
-        <v>-111.65</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C736" s="28"/>
       <c r="D736" s="29"/>
       <c r="E736" s="28"/>
     </row>
@@ -14397,9 +14390,11 @@
         <v>739</v>
       </c>
       <c r="B737" s="24">
-        <v>25</v>
-      </c>
-      <c r="C737" s="28"/>
+        <v>56</v>
+      </c>
+      <c r="C737" s="25">
+        <v>-110.15</v>
+      </c>
       <c r="D737" s="29"/>
       <c r="E737" s="28"/>
     </row>
@@ -14408,33 +14403,27 @@
         <v>740</v>
       </c>
       <c r="B738" s="24">
-        <v>44</v>
-      </c>
-      <c r="C738" s="25">
-        <v>4.25</v>
-      </c>
-      <c r="D738" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E738" s="27">
-        <v>10.63</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C738" s="28"/>
+      <c r="D738" s="29"/>
+      <c r="E738" s="28"/>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A739" s="23" t="s">
         <v>741</v>
       </c>
       <c r="B739" s="24">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C739" s="25">
-        <v>60.5</v>
+        <v>5.25</v>
       </c>
       <c r="D739" s="26">
         <v>2.5</v>
       </c>
       <c r="E739" s="27">
-        <v>151.25</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
@@ -14442,44 +14431,44 @@
         <v>742</v>
       </c>
       <c r="B740" s="24">
-        <v>44</v>
-      </c>
-      <c r="C740" s="28"/>
-      <c r="D740" s="29"/>
-      <c r="E740" s="28"/>
+        <v>96</v>
+      </c>
+      <c r="C740" s="25">
+        <v>60.5</v>
+      </c>
+      <c r="D740" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E740" s="27">
+        <v>151.25</v>
+      </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A741" s="23" t="s">
         <v>743</v>
       </c>
       <c r="B741" s="24">
-        <v>49</v>
-      </c>
-      <c r="C741" s="25">
-        <v>0.25</v>
-      </c>
-      <c r="D741" s="26">
-        <v>2.52</v>
-      </c>
-      <c r="E741" s="27">
-        <v>0.63</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C741" s="28"/>
+      <c r="D741" s="29"/>
+      <c r="E741" s="28"/>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A742" s="23" t="s">
         <v>744</v>
       </c>
       <c r="B742" s="24">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C742" s="25">
-        <v>38.25</v>
+        <v>0.25</v>
       </c>
       <c r="D742" s="26">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="E742" s="27">
-        <v>95.63</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
@@ -14487,16 +14476,16 @@
         <v>745</v>
       </c>
       <c r="B743" s="24">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C743" s="25">
-        <v>2.5</v>
+        <v>37.25</v>
       </c>
       <c r="D743" s="26">
         <v>2.5</v>
       </c>
       <c r="E743" s="27">
-        <v>6.25</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
@@ -14504,16 +14493,16 @@
         <v>746</v>
       </c>
       <c r="B744" s="24">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C744" s="25">
-        <v>47.5</v>
+        <v>2.5</v>
       </c>
       <c r="D744" s="26">
         <v>2.5</v>
       </c>
       <c r="E744" s="27">
-        <v>118.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.25">
@@ -14521,16 +14510,16 @@
         <v>747</v>
       </c>
       <c r="B745" s="24">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C745" s="25">
-        <v>-0.25</v>
+        